--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -742,12 +742,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -769,7 +769,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>118.3</v>
+        <v>118.1</v>
       </c>
       <c r="O3" t="n">
         <v>39.9</v>
@@ -792,13 +792,13 @@
         <v>28.567</v>
       </c>
       <c r="U3" t="n">
-        <v>85.926</v>
+        <v>84.363</v>
       </c>
       <c r="V3" t="n">
         <v>41.769</v>
       </c>
       <c r="W3" t="n">
-        <v>-74.354</v>
+        <v>-73.729</v>
       </c>
     </row>
     <row r="4">
@@ -817,12 +817,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -840,14 +840,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +1.05% / +1.83% / -3.96% | TKFEN.IS: -1.70% / +1.16% / -2.24%</t>
+          <t>BRSAN.IS: +4.02% / +4.95% / -3.96% | TKFEN.IS: -1.18% / +1.16% / -2.24%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>3.867964979127092</v>
+        <v>5.686000979987926</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -856,13 +856,13 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>121.8</v>
+        <v>121.5</v>
       </c>
       <c r="O4" t="n">
         <v>43.3</v>
       </c>
       <c r="P4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -879,13 +879,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>95.297</v>
+        <v>96.589</v>
       </c>
       <c r="V4" t="n">
-        <v>49.401</v>
+        <v>52.016</v>
       </c>
       <c r="W4" t="n">
-        <v>-34.481</v>
+        <v>-30.73</v>
       </c>
     </row>
     <row r="5">
@@ -904,12 +904,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -931,7 +931,7 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>94.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="O5" t="n">
         <v>37.4</v>
@@ -954,13 +954,13 @@
         <v>35.687</v>
       </c>
       <c r="U5" t="n">
-        <v>36.671</v>
+        <v>29.475</v>
       </c>
       <c r="V5" t="n">
         <v>12.323</v>
       </c>
       <c r="W5" t="n">
-        <v>-75.839</v>
+        <v>-71.846</v>
       </c>
     </row>
     <row r="6">
@@ -979,12 +979,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -1006,7 +1006,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>118.3</v>
+        <v>118.1</v>
       </c>
       <c r="O6" t="n">
         <v>39.9</v>
@@ -1029,13 +1029,13 @@
         <v>28.567</v>
       </c>
       <c r="U6" t="n">
-        <v>85.926</v>
+        <v>84.363</v>
       </c>
       <c r="V6" t="n">
         <v>41.769</v>
       </c>
       <c r="W6" t="n">
-        <v>-74.354</v>
+        <v>-73.729</v>
       </c>
     </row>
     <row r="7">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1077,14 +1077,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +1.05% / +1.83% / -3.96% | TKFEN.IS: -1.70% / +1.16% / -2.24%</t>
+          <t>BRSAN.IS: +4.02% / +4.95% / -3.96% | TKFEN.IS: -1.18% / +1.16% / -2.24%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>3.867964979127092</v>
+        <v>5.686000979987926</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1093,13 +1093,13 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>121.8</v>
+        <v>121.5</v>
       </c>
       <c r="O7" t="n">
         <v>43.3</v>
       </c>
       <c r="P7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1116,13 +1116,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>95.297</v>
+        <v>96.589</v>
       </c>
       <c r="V7" t="n">
-        <v>49.401</v>
+        <v>52.016</v>
       </c>
       <c r="W7" t="n">
-        <v>-34.481</v>
+        <v>-30.73</v>
       </c>
     </row>
     <row r="8">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -1168,7 +1168,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N8" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="O8" t="n">
         <v>51.1</v>
@@ -1191,13 +1191,13 @@
         <v>29.993</v>
       </c>
       <c r="U8" t="n">
-        <v>10.204</v>
+        <v>9.574999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>-6.769</v>
       </c>
       <c r="W8" t="n">
-        <v>-46.699</v>
+        <v>-46.433</v>
       </c>
     </row>
     <row r="9">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>118.3</v>
+        <v>118.1</v>
       </c>
       <c r="O9" t="n">
         <v>39.9</v>
@@ -1266,13 +1266,13 @@
         <v>28.567</v>
       </c>
       <c r="U9" t="n">
-        <v>85.926</v>
+        <v>84.363</v>
       </c>
       <c r="V9" t="n">
         <v>41.769</v>
       </c>
       <c r="W9" t="n">
-        <v>-74.354</v>
+        <v>-73.729</v>
       </c>
     </row>
     <row r="10">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1318,7 +1318,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="O10" t="n">
         <v>51.1</v>
@@ -1341,13 +1341,13 @@
         <v>29.993</v>
       </c>
       <c r="U10" t="n">
-        <v>10.204</v>
+        <v>9.574999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-6.769</v>
       </c>
       <c r="W10" t="n">
-        <v>-46.699</v>
+        <v>-46.433</v>
       </c>
     </row>
     <row r="11">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1393,7 +1393,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>72.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>38.4</v>
@@ -1416,13 +1416,13 @@
         <v>29.287</v>
       </c>
       <c r="U11" t="n">
-        <v>43.888</v>
+        <v>40.954</v>
       </c>
       <c r="V11" t="n">
         <v>14.374</v>
       </c>
       <c r="W11" t="n">
-        <v>-51.142</v>
+        <v>-50.099</v>
       </c>
     </row>
     <row r="12">
@@ -1436,68 +1436,80 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ENJSA.IS, RALYH.IS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ENJSA.IS: 2026-08-13 | RALYH.IS: 2026-08-14</t>
+        </is>
+      </c>
       <c r="H12" t="n">
-        <v>3.443912532931592</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>35.05565740671337</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ENJSA.IS: +3.61% / +4.93% / -2.89% | RALYH.IS: +2.41% / +2.53% / -3.00%</t>
+        </is>
+      </c>
       <c r="J12" t="n">
-        <v>-1.862436885442242</v>
+        <v>5.880320398884153</v>
       </c>
       <c r="K12" t="n">
-        <v>9.760986497744174</v>
+        <v>9.882953953266771</v>
       </c>
       <c r="L12" t="n">
-        <v>7.902828022135555</v>
+        <v>17.97495932189197</v>
       </c>
       <c r="M12" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>32.3</v>
+        <v>141.4</v>
       </c>
       <c r="O12" t="n">
-        <v>46.2</v>
+        <v>46.7</v>
       </c>
       <c r="P12" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>8.954000000000001</v>
+        <v>21.61</v>
       </c>
       <c r="T12" t="n">
-        <v>8.954000000000001</v>
+        <v>21.61</v>
       </c>
       <c r="U12" t="n">
-        <v>10.011</v>
+        <v>92.16</v>
       </c>
       <c r="V12" t="n">
-        <v>9.042999999999999</v>
+        <v>71.974</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.724</v>
+        <v>-24.44</v>
       </c>
     </row>
     <row r="13">
@@ -1511,68 +1523,80 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>BIMAS.IS: 2026-08-19</t>
+        </is>
+      </c>
       <c r="H13" t="n">
-        <v>34.62553795007752</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>12.43146471706449</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>BIMAS.IS: +2.25% / +3.13% / 0.00%</t>
+        </is>
+      </c>
       <c r="J13" t="n">
-        <v>8.431557803491319</v>
+        <v>-6.412181273130146</v>
       </c>
       <c r="K13" t="n">
-        <v>7.764976042490113</v>
+        <v>8.268371467800995</v>
       </c>
       <c r="L13" t="n">
-        <v>32.1397934777012</v>
+        <v>12.30894614425559</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>233.1</v>
+        <v>140.4</v>
       </c>
       <c r="O13" t="n">
-        <v>49.5</v>
+        <v>48.1</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>20.274</v>
+        <v>12.004</v>
       </c>
       <c r="T13" t="n">
-        <v>20.274</v>
+        <v>11.714</v>
       </c>
       <c r="U13" t="n">
-        <v>89.714</v>
+        <v>12.255</v>
       </c>
       <c r="V13" t="n">
-        <v>43.671</v>
+        <v>21.879</v>
       </c>
       <c r="W13" t="n">
-        <v>-27.723</v>
+        <v>-0.612</v>
       </c>
     </row>
     <row r="14">
@@ -1586,57 +1610,57 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>ALARK.IS, BIMAS.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BIMAS.IS: 2026-08-19</t>
+          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>12.43146471706449</v>
+        <v>34.62553795007752</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BIMAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BIMAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-6.412181273130146</v>
+        <v>8.431557803491319</v>
       </c>
       <c r="K14" t="n">
-        <v>7.454377431053905</v>
+        <v>7.721874362672154</v>
       </c>
       <c r="L14" t="n">
-        <v>12.30894614425559</v>
+        <v>32.1397934777012</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>140.7</v>
+        <v>233.6</v>
       </c>
       <c r="O14" t="n">
-        <v>47.7</v>
+        <v>49.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1644,22 +1668,22 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>12.004</v>
+        <v>20.274</v>
       </c>
       <c r="T14" t="n">
-        <v>11.714</v>
+        <v>20.274</v>
       </c>
       <c r="U14" t="n">
-        <v>11.411</v>
+        <v>87.407</v>
       </c>
       <c r="V14" t="n">
-        <v>20.962</v>
+        <v>43.614</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.456</v>
+        <v>-27.471</v>
       </c>
     </row>
     <row r="16">
@@ -1804,12 +1828,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1831,7 +1855,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>118.3</v>
+        <v>118.1</v>
       </c>
       <c r="O18" t="n">
         <v>39.9</v>
@@ -1854,13 +1878,13 @@
         <v>28.567</v>
       </c>
       <c r="U18" t="n">
-        <v>85.926</v>
+        <v>84.363</v>
       </c>
       <c r="V18" t="n">
         <v>41.769</v>
       </c>
       <c r="W18" t="n">
-        <v>-74.354</v>
+        <v>-73.729</v>
       </c>
     </row>
     <row r="19">
@@ -1881,12 +1905,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1904,14 +1928,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +1.05% / +1.83% / -3.96% | TKFEN.IS: -1.70% / +1.16% / -2.24%</t>
+          <t>BRSAN.IS: +4.02% / +4.95% / -3.96% | TKFEN.IS: -1.18% / +1.16% / -2.24%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>3.867964979127092</v>
+        <v>5.686000979987926</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1920,13 +1944,13 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>121.8</v>
+        <v>121.5</v>
       </c>
       <c r="O19" t="n">
         <v>43.3</v>
       </c>
       <c r="P19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1943,13 +1967,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>95.297</v>
+        <v>96.589</v>
       </c>
       <c r="V19" t="n">
-        <v>49.401</v>
+        <v>52.016</v>
       </c>
       <c r="W19" t="n">
-        <v>-34.481</v>
+        <v>-30.73</v>
       </c>
     </row>
     <row r="20">
@@ -1970,12 +1994,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1997,7 +2021,7 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>94.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="O20" t="n">
         <v>37.4</v>
@@ -2020,13 +2044,13 @@
         <v>35.687</v>
       </c>
       <c r="U20" t="n">
-        <v>36.671</v>
+        <v>29.475</v>
       </c>
       <c r="V20" t="n">
         <v>12.323</v>
       </c>
       <c r="W20" t="n">
-        <v>-75.839</v>
+        <v>-71.846</v>
       </c>
     </row>
     <row r="21">
@@ -2047,12 +2071,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2074,7 +2098,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N21" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="O21" t="n">
         <v>51.1</v>
@@ -2097,13 +2121,13 @@
         <v>29.993</v>
       </c>
       <c r="U21" t="n">
-        <v>10.204</v>
+        <v>9.574999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-6.769</v>
       </c>
       <c r="W21" t="n">
-        <v>-46.699</v>
+        <v>-46.433</v>
       </c>
     </row>
     <row r="22">
@@ -2124,12 +2148,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2151,7 +2175,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>72.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="O22" t="n">
         <v>38.4</v>
@@ -2174,13 +2198,13 @@
         <v>29.287</v>
       </c>
       <c r="U22" t="n">
-        <v>43.888</v>
+        <v>40.954</v>
       </c>
       <c r="V22" t="n">
         <v>14.374</v>
       </c>
       <c r="W22" t="n">
-        <v>-51.142</v>
+        <v>-50.099</v>
       </c>
     </row>
     <row r="23">
@@ -2191,73 +2215,85 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ENJSA.IS, RALYH.IS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ENJSA.IS: 2026-08-13 | RALYH.IS: 2026-08-14</t>
+        </is>
+      </c>
       <c r="H23" t="n">
-        <v>34.62553795007752</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>35.05565740671337</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ENJSA.IS: +3.61% / +4.93% / -2.89% | RALYH.IS: +2.41% / +2.53% / -3.00%</t>
+        </is>
+      </c>
       <c r="J23" t="n">
-        <v>8.431557803491319</v>
+        <v>5.880320398884153</v>
       </c>
       <c r="K23" t="n">
-        <v>7.764976042490113</v>
+        <v>9.882953953266771</v>
       </c>
       <c r="L23" t="n">
-        <v>32.1397934777012</v>
+        <v>17.97495932189197</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>233.1</v>
+        <v>141.4</v>
       </c>
       <c r="O23" t="n">
-        <v>49.5</v>
+        <v>46.7</v>
       </c>
       <c r="P23" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>20.274</v>
+        <v>21.61</v>
       </c>
       <c r="T23" t="n">
-        <v>20.274</v>
+        <v>21.61</v>
       </c>
       <c r="U23" t="n">
-        <v>89.714</v>
+        <v>92.16</v>
       </c>
       <c r="V23" t="n">
-        <v>43.671</v>
+        <v>71.974</v>
       </c>
       <c r="W23" t="n">
-        <v>-27.723</v>
+        <v>-24.44</v>
       </c>
     </row>
     <row r="24">
@@ -2273,57 +2309,57 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>ALARK.IS, BIMAS.IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>BIMAS.IS: 2026-08-19</t>
+          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>12.43146471706449</v>
+        <v>34.62553795007752</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>BIMAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BIMAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>-6.412181273130146</v>
+        <v>8.431557803491319</v>
       </c>
       <c r="K24" t="n">
-        <v>7.454377431053905</v>
+        <v>7.721874362672154</v>
       </c>
       <c r="L24" t="n">
-        <v>12.30894614425559</v>
+        <v>32.1397934777012</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>140.7</v>
+        <v>233.6</v>
       </c>
       <c r="O24" t="n">
-        <v>47.7</v>
+        <v>49.3</v>
       </c>
       <c r="P24" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2331,22 +2367,22 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>12.004</v>
+        <v>20.274</v>
       </c>
       <c r="T24" t="n">
-        <v>11.714</v>
+        <v>20.274</v>
       </c>
       <c r="U24" t="n">
-        <v>11.411</v>
+        <v>87.407</v>
       </c>
       <c r="V24" t="n">
-        <v>20.962</v>
+        <v>43.614</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.456</v>
+        <v>-27.471</v>
       </c>
     </row>
     <row r="25">
@@ -2357,73 +2393,85 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>BIMAS.IS: 2026-08-19</t>
+        </is>
+      </c>
       <c r="H25" t="n">
-        <v>3.443912532931592</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>12.43146471706449</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>BIMAS.IS: +2.25% / +3.13% / 0.00%</t>
+        </is>
+      </c>
       <c r="J25" t="n">
-        <v>-1.862436885442242</v>
+        <v>-6.412181273130146</v>
       </c>
       <c r="K25" t="n">
-        <v>9.760986497744174</v>
+        <v>8.268371467800995</v>
       </c>
       <c r="L25" t="n">
-        <v>7.902828022135555</v>
+        <v>12.30894614425559</v>
       </c>
       <c r="M25" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>32.3</v>
+        <v>140.4</v>
       </c>
       <c r="O25" t="n">
-        <v>46.2</v>
+        <v>48.1</v>
       </c>
       <c r="P25" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>8.954000000000001</v>
+        <v>12.004</v>
       </c>
       <c r="T25" t="n">
-        <v>8.954000000000001</v>
+        <v>11.714</v>
       </c>
       <c r="U25" t="n">
-        <v>10.011</v>
+        <v>12.255</v>
       </c>
       <c r="V25" t="n">
-        <v>9.042999999999999</v>
+        <v>21.879</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.724</v>
+        <v>-0.612</v>
       </c>
     </row>
   </sheetData>
@@ -2613,12 +2661,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2640,7 +2688,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>66.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="O3" t="n">
         <v>45.9</v>
@@ -2663,13 +2711,13 @@
         <v>31.839</v>
       </c>
       <c r="U3" t="n">
-        <v>26.319</v>
+        <v>24.207</v>
       </c>
       <c r="V3" t="n">
         <v>27.773</v>
       </c>
       <c r="W3" t="n">
-        <v>-59.005</v>
+        <v>-58.018</v>
       </c>
     </row>
     <row r="4">
@@ -2688,12 +2736,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2715,7 +2763,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N4" t="n">
-        <v>59.9</v>
+        <v>59.8</v>
       </c>
       <c r="O4" t="n">
         <v>46.7</v>
@@ -2738,13 +2786,13 @@
         <v>30.704</v>
       </c>
       <c r="U4" t="n">
-        <v>10.473</v>
+        <v>11.171</v>
       </c>
       <c r="V4" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>-48.949</v>
+        <v>-49.258</v>
       </c>
     </row>
     <row r="5">
@@ -2763,12 +2811,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -2790,7 +2838,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>59.9</v>
+        <v>59.8</v>
       </c>
       <c r="O5" t="n">
         <v>46.7</v>
@@ -2813,13 +2861,13 @@
         <v>30.704</v>
       </c>
       <c r="U5" t="n">
-        <v>10.473</v>
+        <v>11.171</v>
       </c>
       <c r="V5" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-48.949</v>
+        <v>-49.258</v>
       </c>
     </row>
     <row r="6">
@@ -2838,12 +2886,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -2865,7 +2913,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>59.9</v>
+        <v>59.8</v>
       </c>
       <c r="O6" t="n">
         <v>46.7</v>
@@ -2888,13 +2936,13 @@
         <v>30.704</v>
       </c>
       <c r="U6" t="n">
-        <v>10.473</v>
+        <v>11.171</v>
       </c>
       <c r="V6" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>-48.949</v>
+        <v>-49.258</v>
       </c>
     </row>
     <row r="7">
@@ -2913,12 +2961,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -2940,7 +2988,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N7" t="n">
-        <v>59.9</v>
+        <v>59.8</v>
       </c>
       <c r="O7" t="n">
         <v>46.7</v>
@@ -2963,13 +3011,13 @@
         <v>30.704</v>
       </c>
       <c r="U7" t="n">
-        <v>10.473</v>
+        <v>11.171</v>
       </c>
       <c r="V7" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>-48.949</v>
+        <v>-49.258</v>
       </c>
     </row>
     <row r="8">
@@ -2988,12 +3036,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -3015,7 +3063,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>111.8</v>
+        <v>111.6</v>
       </c>
       <c r="O8" t="n">
         <v>38.4</v>
@@ -3038,13 +3086,13 @@
         <v>28.888</v>
       </c>
       <c r="U8" t="n">
-        <v>44.648</v>
+        <v>49.806</v>
       </c>
       <c r="V8" t="n">
         <v>14.358</v>
       </c>
       <c r="W8" t="n">
-        <v>-58.76</v>
+        <v>-60.856</v>
       </c>
     </row>
     <row r="9">
@@ -3063,12 +3111,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3090,7 +3138,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="N9" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
       <c r="O9" t="n">
         <v>57.4</v>
@@ -3138,12 +3186,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3165,7 +3213,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>68.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="O10" t="n">
         <v>45.7</v>
@@ -3188,13 +3236,13 @@
         <v>13.513</v>
       </c>
       <c r="U10" t="n">
-        <v>18.059</v>
+        <v>19.433</v>
       </c>
       <c r="V10" t="n">
         <v>13.389</v>
       </c>
       <c r="W10" t="n">
-        <v>-17.697</v>
+        <v>-17.903</v>
       </c>
     </row>
     <row r="11">
@@ -3213,12 +3261,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3240,7 +3288,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>59.9</v>
+        <v>59.8</v>
       </c>
       <c r="O11" t="n">
         <v>44.2</v>
@@ -3263,13 +3311,13 @@
         <v>13.42</v>
       </c>
       <c r="U11" t="n">
-        <v>19.888</v>
+        <v>21.246</v>
       </c>
       <c r="V11" t="n">
         <v>12.908</v>
       </c>
       <c r="W11" t="n">
-        <v>-18.583</v>
+        <v>-18.794</v>
       </c>
     </row>
     <row r="12">
@@ -3288,12 +3336,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -3315,7 +3363,7 @@
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>233.5</v>
+        <v>233.1</v>
       </c>
       <c r="O12" t="n">
         <v>41.9</v>
@@ -3338,13 +3386,13 @@
         <v>15.334</v>
       </c>
       <c r="U12" t="n">
-        <v>12.988</v>
+        <v>12.581</v>
       </c>
       <c r="V12" t="n">
         <v>55.16</v>
       </c>
       <c r="W12" t="n">
-        <v>-13.38</v>
+        <v>-13.332</v>
       </c>
     </row>
     <row r="13">
@@ -3358,19 +3406,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>AKBNK.IS, BRSAN.IS</t>
@@ -3378,37 +3426,37 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-07-29 | BRSAN.IS: 2026-08-13</t>
+          <t>AKBNK.IS: 2026-08-17 | BRSAN.IS: 2026-08-19</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.84922237136889</v>
+        <v>18.78300085000422</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +7.84% / +9.28% / -3.77% | BRSAN.IS: +5.16% / +6.39% / -0.05%</t>
+          <t>AKBNK.IS: +4.08% / +4.61% / -1.19% | BRSAN.IS: +2.92% / +3.85% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-7.945335963406319</v>
+        <v>-0.2995012191682078</v>
       </c>
       <c r="K13" t="n">
-        <v>12.94651976894712</v>
+        <v>14.47381043114224</v>
       </c>
       <c r="L13" t="n">
-        <v>31.58073864491333</v>
+        <v>28.49280591027672</v>
       </c>
       <c r="M13" t="n">
         <v>88.88888888888889</v>
       </c>
       <c r="N13" t="n">
-        <v>48.4</v>
+        <v>81.7</v>
       </c>
       <c r="O13" t="n">
-        <v>49.5</v>
+        <v>48.8</v>
       </c>
       <c r="P13" t="n">
-        <v>6.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3419,19 +3467,19 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>11.1</v>
+        <v>13.617</v>
       </c>
       <c r="T13" t="n">
-        <v>11.1</v>
+        <v>13.617</v>
       </c>
       <c r="U13" t="n">
-        <v>36.871</v>
+        <v>41.478</v>
       </c>
       <c r="V13" t="n">
-        <v>15.059</v>
+        <v>21.041</v>
       </c>
       <c r="W13" t="n">
-        <v>-6.223</v>
+        <v>-5.51</v>
       </c>
     </row>
     <row r="14">
@@ -3450,12 +3498,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3473,14 +3521,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AKBNK.IS: +2.14% / +2.67% / 0.00% | BRSAN.IS: +2.92% / +3.85% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>8.508817436331251</v>
+        <v>11.27741561158297</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3489,10 +3537,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N14" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="O14" t="n">
-        <v>54.5</v>
+        <v>57.1</v>
       </c>
       <c r="P14" t="n">
         <v>7.4</v>
@@ -3506,19 +3554,19 @@
         <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>13.412</v>
+        <v>13.394</v>
       </c>
       <c r="T14" t="n">
-        <v>13.412</v>
+        <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>40.507</v>
+        <v>41.175</v>
       </c>
       <c r="V14" t="n">
-        <v>28.611</v>
+        <v>31.892</v>
       </c>
       <c r="W14" t="n">
-        <v>-21.763</v>
+        <v>-17.81</v>
       </c>
     </row>
     <row r="16">
@@ -3663,12 +3711,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -3690,7 +3738,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>66.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="O18" t="n">
         <v>45.9</v>
@@ -3713,13 +3761,13 @@
         <v>31.839</v>
       </c>
       <c r="U18" t="n">
-        <v>26.319</v>
+        <v>24.207</v>
       </c>
       <c r="V18" t="n">
         <v>27.773</v>
       </c>
       <c r="W18" t="n">
-        <v>-59.005</v>
+        <v>-58.018</v>
       </c>
     </row>
     <row r="19">
@@ -3740,12 +3788,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -3767,7 +3815,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>59.9</v>
+        <v>59.8</v>
       </c>
       <c r="O19" t="n">
         <v>46.7</v>
@@ -3790,13 +3838,13 @@
         <v>30.704</v>
       </c>
       <c r="U19" t="n">
-        <v>10.473</v>
+        <v>11.171</v>
       </c>
       <c r="V19" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>-48.949</v>
+        <v>-49.258</v>
       </c>
     </row>
     <row r="20">
@@ -3817,12 +3865,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -3844,7 +3892,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>59.9</v>
+        <v>59.8</v>
       </c>
       <c r="O20" t="n">
         <v>46.7</v>
@@ -3867,13 +3915,13 @@
         <v>30.704</v>
       </c>
       <c r="U20" t="n">
-        <v>10.473</v>
+        <v>11.171</v>
       </c>
       <c r="V20" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-48.949</v>
+        <v>-49.258</v>
       </c>
     </row>
     <row r="21">
@@ -3894,12 +3942,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -3921,7 +3969,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>111.8</v>
+        <v>111.6</v>
       </c>
       <c r="O21" t="n">
         <v>38.4</v>
@@ -3944,13 +3992,13 @@
         <v>28.888</v>
       </c>
       <c r="U21" t="n">
-        <v>44.648</v>
+        <v>49.806</v>
       </c>
       <c r="V21" t="n">
         <v>14.358</v>
       </c>
       <c r="W21" t="n">
-        <v>-58.76</v>
+        <v>-60.856</v>
       </c>
     </row>
     <row r="22">
@@ -3971,12 +4019,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -3998,7 +4046,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>59.9</v>
+        <v>59.8</v>
       </c>
       <c r="O22" t="n">
         <v>44.2</v>
@@ -4021,13 +4069,13 @@
         <v>13.42</v>
       </c>
       <c r="U22" t="n">
-        <v>19.888</v>
+        <v>21.246</v>
       </c>
       <c r="V22" t="n">
         <v>12.908</v>
       </c>
       <c r="W22" t="n">
-        <v>-18.583</v>
+        <v>-18.794</v>
       </c>
     </row>
     <row r="23">
@@ -4048,12 +4096,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -4075,7 +4123,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N23" t="n">
-        <v>68.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="O23" t="n">
         <v>45.7</v>
@@ -4098,13 +4146,13 @@
         <v>13.513</v>
       </c>
       <c r="U23" t="n">
-        <v>18.059</v>
+        <v>19.433</v>
       </c>
       <c r="V23" t="n">
         <v>13.389</v>
       </c>
       <c r="W23" t="n">
-        <v>-17.697</v>
+        <v>-17.903</v>
       </c>
     </row>
     <row r="24">
@@ -4125,12 +4173,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4152,7 +4200,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="N24" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
       <c r="O24" t="n">
         <v>57.4</v>
@@ -4202,12 +4250,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4225,14 +4273,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AKBNK.IS: +2.14% / +2.67% / 0.00% | BRSAN.IS: +2.92% / +3.85% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>8.508817436331251</v>
+        <v>11.27741561158297</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4241,10 +4289,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N25" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="O25" t="n">
-        <v>54.5</v>
+        <v>57.1</v>
       </c>
       <c r="P25" t="n">
         <v>7.4</v>
@@ -4258,19 +4306,19 @@
         <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>13.412</v>
+        <v>13.394</v>
       </c>
       <c r="T25" t="n">
-        <v>13.412</v>
+        <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>40.507</v>
+        <v>41.175</v>
       </c>
       <c r="V25" t="n">
-        <v>28.611</v>
+        <v>31.892</v>
       </c>
       <c r="W25" t="n">
-        <v>-21.763</v>
+        <v>-17.81</v>
       </c>
     </row>
     <row r="26">
@@ -4286,19 +4334,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>AKBNK.IS, BRSAN.IS</t>
@@ -4306,37 +4354,37 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-07-29 | BRSAN.IS: 2026-08-13</t>
+          <t>AKBNK.IS: 2026-08-17 | BRSAN.IS: 2026-08-19</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.84922237136889</v>
+        <v>18.78300085000422</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +7.84% / +9.28% / -3.77% | BRSAN.IS: +5.16% / +6.39% / -0.05%</t>
+          <t>AKBNK.IS: +4.08% / +4.61% / -1.19% | BRSAN.IS: +2.92% / +3.85% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-7.945335963406319</v>
+        <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>12.94651976894712</v>
+        <v>14.47381043114224</v>
       </c>
       <c r="L26" t="n">
-        <v>31.58073864491333</v>
+        <v>28.49280591027672</v>
       </c>
       <c r="M26" t="n">
         <v>88.88888888888889</v>
       </c>
       <c r="N26" t="n">
-        <v>48.4</v>
+        <v>81.7</v>
       </c>
       <c r="O26" t="n">
-        <v>49.5</v>
+        <v>48.8</v>
       </c>
       <c r="P26" t="n">
-        <v>6.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4347,19 +4395,19 @@
         <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>11.1</v>
+        <v>13.617</v>
       </c>
       <c r="T26" t="n">
-        <v>11.1</v>
+        <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>36.871</v>
+        <v>41.478</v>
       </c>
       <c r="V26" t="n">
-        <v>15.059</v>
+        <v>21.041</v>
       </c>
       <c r="W26" t="n">
-        <v>-6.223</v>
+        <v>-5.51</v>
       </c>
     </row>
     <row r="27">
@@ -4380,12 +4428,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -4407,7 +4455,7 @@
         <v>100</v>
       </c>
       <c r="N27" t="n">
-        <v>233.5</v>
+        <v>233.1</v>
       </c>
       <c r="O27" t="n">
         <v>41.9</v>
@@ -4430,13 +4478,13 @@
         <v>15.334</v>
       </c>
       <c r="U27" t="n">
-        <v>12.988</v>
+        <v>12.581</v>
       </c>
       <c r="V27" t="n">
         <v>55.16</v>
       </c>
       <c r="W27" t="n">
-        <v>-13.38</v>
+        <v>-13.332</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -840,14 +840,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +4.02% / +4.95% / -3.96% | TKFEN.IS: -1.18% / +1.16% / -2.24%</t>
+          <t>BRSAN.IS: +5.92% / +7.70% / -3.96% | TKFEN.IS: -0.11% / +1.16% / -2.24%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>5.686000979987926</v>
+        <v>7.239702690965699</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -879,13 +879,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>96.589</v>
+        <v>99.479</v>
       </c>
       <c r="V4" t="n">
-        <v>52.016</v>
+        <v>54.251</v>
       </c>
       <c r="W4" t="n">
-        <v>-30.73</v>
+        <v>-27.84</v>
       </c>
     </row>
     <row r="5">
@@ -1077,14 +1077,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +4.02% / +4.95% / -3.96% | TKFEN.IS: -1.18% / +1.16% / -2.24%</t>
+          <t>BRSAN.IS: +5.92% / +7.70% / -3.96% | TKFEN.IS: -0.11% / +1.16% / -2.24%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>5.686000979987926</v>
+        <v>7.239702690965699</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1116,13 +1116,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>96.589</v>
+        <v>99.479</v>
       </c>
       <c r="V7" t="n">
-        <v>52.016</v>
+        <v>54.251</v>
       </c>
       <c r="W7" t="n">
-        <v>-30.73</v>
+        <v>-27.84</v>
       </c>
     </row>
     <row r="8">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1449,67 +1449,55 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ENJSA.IS, RALYH.IS</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ENJSA.IS: 2026-08-13 | RALYH.IS: 2026-08-14</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>35.05565740671337</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>ENJSA.IS: +3.61% / +4.93% / -2.89% | RALYH.IS: +2.41% / +2.53% / -3.00%</t>
-        </is>
-      </c>
+        <v>3.443912532931592</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>5.880320398884153</v>
+        <v>-1.862436885442242</v>
       </c>
       <c r="K12" t="n">
-        <v>9.882953953266771</v>
+        <v>9.760986497744174</v>
       </c>
       <c r="L12" t="n">
-        <v>17.97495932189197</v>
+        <v>7.902828022135555</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="N12" t="n">
-        <v>141.4</v>
+        <v>32.2</v>
       </c>
       <c r="O12" t="n">
-        <v>46.7</v>
+        <v>46.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>21.61</v>
+        <v>8.954000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>21.61</v>
+        <v>8.954000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>92.16</v>
+        <v>10.011</v>
       </c>
       <c r="V12" t="n">
-        <v>71.974</v>
+        <v>9.042999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>-24.44</v>
+        <v>-0.724</v>
       </c>
     </row>
     <row r="13">
@@ -1523,7 +1511,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1538,42 +1526,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>ALARK.IS, BIMAS.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BIMAS.IS: 2026-08-19</t>
+          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>12.43146471706449</v>
+        <v>34.62553795007752</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BIMAS.IS: +2.25% / +3.13% / 0.00%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BIMAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-6.412181273130146</v>
+        <v>8.431557803491319</v>
       </c>
       <c r="K13" t="n">
-        <v>8.268371467800995</v>
+        <v>7.721874362672154</v>
       </c>
       <c r="L13" t="n">
-        <v>12.30894614425559</v>
+        <v>32.1397934777012</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>140.4</v>
+        <v>233.6</v>
       </c>
       <c r="O13" t="n">
-        <v>48.1</v>
+        <v>49.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1581,22 +1569,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>12.004</v>
+        <v>20.274</v>
       </c>
       <c r="T13" t="n">
-        <v>11.714</v>
+        <v>20.274</v>
       </c>
       <c r="U13" t="n">
-        <v>12.255</v>
+        <v>87.407</v>
       </c>
       <c r="V13" t="n">
-        <v>21.879</v>
+        <v>43.614</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.612</v>
+        <v>-27.471</v>
       </c>
     </row>
     <row r="14">
@@ -1610,7 +1598,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1625,42 +1613,42 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ALARK.IS, BIMAS.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
+          <t>BIMAS.IS: 2026-08-19</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>34.62553795007752</v>
+        <v>12.43146471706449</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BIMAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BIMAS.IS: +0.41% / +3.13% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8.431557803491319</v>
+        <v>-6.412181273130146</v>
       </c>
       <c r="K14" t="n">
-        <v>7.721874362672154</v>
+        <v>7.608376302870923</v>
       </c>
       <c r="L14" t="n">
-        <v>32.1397934777012</v>
+        <v>12.30894614425559</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>233.6</v>
+        <v>140.4</v>
       </c>
       <c r="O14" t="n">
-        <v>49.3</v>
+        <v>48.1</v>
       </c>
       <c r="P14" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1668,22 +1656,22 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>20.274</v>
+        <v>12.004</v>
       </c>
       <c r="T14" t="n">
-        <v>20.274</v>
+        <v>11.714</v>
       </c>
       <c r="U14" t="n">
-        <v>87.407</v>
+        <v>11.571</v>
       </c>
       <c r="V14" t="n">
-        <v>43.614</v>
+        <v>21.136</v>
       </c>
       <c r="W14" t="n">
-        <v>-27.471</v>
+        <v>-1.296</v>
       </c>
     </row>
     <row r="16">
@@ -1928,14 +1916,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +4.02% / +4.95% / -3.96% | TKFEN.IS: -1.18% / +1.16% / -2.24%</t>
+          <t>BRSAN.IS: +5.92% / +7.70% / -3.96% | TKFEN.IS: -0.11% / +1.16% / -2.24%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>5.686000979987926</v>
+        <v>7.239702690965699</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1967,13 +1955,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>96.589</v>
+        <v>99.479</v>
       </c>
       <c r="V19" t="n">
-        <v>52.016</v>
+        <v>54.251</v>
       </c>
       <c r="W19" t="n">
-        <v>-30.73</v>
+        <v>-27.84</v>
       </c>
     </row>
     <row r="20">
@@ -2215,12 +2203,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2235,42 +2223,42 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ENJSA.IS, RALYH.IS</t>
+          <t>ALARK.IS, BIMAS.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ENJSA.IS: 2026-08-13 | RALYH.IS: 2026-08-14</t>
+          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>35.05565740671337</v>
+        <v>34.62553795007752</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENJSA.IS: +3.61% / +4.93% / -2.89% | RALYH.IS: +2.41% / +2.53% / -3.00%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BIMAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>5.880320398884153</v>
+        <v>8.431557803491319</v>
       </c>
       <c r="K23" t="n">
-        <v>9.882953953266771</v>
+        <v>7.721874362672154</v>
       </c>
       <c r="L23" t="n">
-        <v>17.97495932189197</v>
+        <v>32.1397934777012</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>141.4</v>
+        <v>233.6</v>
       </c>
       <c r="O23" t="n">
-        <v>46.7</v>
+        <v>49.3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2281,19 +2269,19 @@
         <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>21.61</v>
+        <v>20.274</v>
       </c>
       <c r="T23" t="n">
-        <v>21.61</v>
+        <v>20.274</v>
       </c>
       <c r="U23" t="n">
-        <v>92.16</v>
+        <v>87.407</v>
       </c>
       <c r="V23" t="n">
-        <v>71.974</v>
+        <v>43.614</v>
       </c>
       <c r="W23" t="n">
-        <v>-24.44</v>
+        <v>-27.471</v>
       </c>
     </row>
     <row r="24">
@@ -2309,7 +2297,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2324,42 +2312,42 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ALARK.IS, BIMAS.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
+          <t>BIMAS.IS: 2026-08-19</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>34.62553795007752</v>
+        <v>12.43146471706449</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BIMAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BIMAS.IS: +0.41% / +3.13% / 0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>8.431557803491319</v>
+        <v>-6.412181273130146</v>
       </c>
       <c r="K24" t="n">
-        <v>7.721874362672154</v>
+        <v>7.608376302870923</v>
       </c>
       <c r="L24" t="n">
-        <v>32.1397934777012</v>
+        <v>12.30894614425559</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>233.6</v>
+        <v>140.4</v>
       </c>
       <c r="O24" t="n">
-        <v>49.3</v>
+        <v>48.1</v>
       </c>
       <c r="P24" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2367,22 +2355,22 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>20.274</v>
+        <v>12.004</v>
       </c>
       <c r="T24" t="n">
-        <v>20.274</v>
+        <v>11.714</v>
       </c>
       <c r="U24" t="n">
-        <v>87.407</v>
+        <v>11.571</v>
       </c>
       <c r="V24" t="n">
-        <v>43.614</v>
+        <v>21.136</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.471</v>
+        <v>-1.296</v>
       </c>
     </row>
     <row r="25">
@@ -2393,12 +2381,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2411,67 +2399,55 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>BIMAS.IS: 2026-08-19</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>12.43146471706449</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>BIMAS.IS: +2.25% / +3.13% / 0.00%</t>
-        </is>
-      </c>
+        <v>3.443912532931592</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>-6.412181273130146</v>
+        <v>-1.862436885442242</v>
       </c>
       <c r="K25" t="n">
-        <v>8.268371467800995</v>
+        <v>9.760986497744174</v>
       </c>
       <c r="L25" t="n">
-        <v>12.30894614425559</v>
+        <v>7.902828022135555</v>
       </c>
       <c r="M25" t="n">
-        <v>100</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="N25" t="n">
-        <v>140.4</v>
+        <v>32.2</v>
       </c>
       <c r="O25" t="n">
-        <v>48.1</v>
+        <v>46.2</v>
       </c>
       <c r="P25" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>12.004</v>
+        <v>8.954000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>11.714</v>
+        <v>8.954000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>12.255</v>
+        <v>10.011</v>
       </c>
       <c r="V25" t="n">
-        <v>21.879</v>
+        <v>9.042999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.612</v>
+        <v>-0.724</v>
       </c>
     </row>
   </sheetData>
@@ -3434,14 +3410,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.08% / +4.61% / -1.19% | BRSAN.IS: +2.92% / +3.85% / 0.00%</t>
+          <t>AKBNK.IS: +3.49% / +5.34% / -1.19% | BRSAN.IS: +4.81% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K13" t="n">
-        <v>14.47381043114224</v>
+        <v>15.1640985780058</v>
       </c>
       <c r="L13" t="n">
         <v>28.49280591027672</v>
@@ -3473,13 +3449,13 @@
         <v>13.617</v>
       </c>
       <c r="U13" t="n">
-        <v>41.478</v>
+        <v>42.331</v>
       </c>
       <c r="V13" t="n">
-        <v>21.041</v>
+        <v>21.771</v>
       </c>
       <c r="W13" t="n">
-        <v>-5.51</v>
+        <v>-4.656</v>
       </c>
     </row>
     <row r="14">
@@ -3521,14 +3497,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +2.14% / +2.67% / 0.00% | BRSAN.IS: +2.92% / +3.85% / 0.00%</t>
+          <t>AKBNK.IS: +1.56% / +3.39% / 0.00% | BRSAN.IS: +4.81% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>11.27741561158297</v>
+        <v>11.98754243474287</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3560,13 +3536,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>41.175</v>
+        <v>42.076</v>
       </c>
       <c r="V14" t="n">
-        <v>31.892</v>
+        <v>32.734</v>
       </c>
       <c r="W14" t="n">
-        <v>-17.81</v>
+        <v>-16.909</v>
       </c>
     </row>
     <row r="16">
@@ -4273,14 +4249,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +2.14% / +2.67% / 0.00% | BRSAN.IS: +2.92% / +3.85% / 0.00%</t>
+          <t>AKBNK.IS: +1.56% / +3.39% / 0.00% | BRSAN.IS: +4.81% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>11.27741561158297</v>
+        <v>11.98754243474287</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4312,13 +4288,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>41.175</v>
+        <v>42.076</v>
       </c>
       <c r="V25" t="n">
-        <v>31.892</v>
+        <v>32.734</v>
       </c>
       <c r="W25" t="n">
-        <v>-17.81</v>
+        <v>-16.909</v>
       </c>
     </row>
     <row r="26">
@@ -4362,14 +4338,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.08% / +4.61% / -1.19% | BRSAN.IS: +2.92% / +3.85% / 0.00%</t>
+          <t>AKBNK.IS: +3.49% / +5.34% / -1.19% | BRSAN.IS: +4.81% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>14.47381043114224</v>
+        <v>15.1640985780058</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4401,13 +4377,13 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>41.478</v>
+        <v>42.331</v>
       </c>
       <c r="V26" t="n">
-        <v>21.041</v>
+        <v>21.771</v>
       </c>
       <c r="W26" t="n">
-        <v>-5.51</v>
+        <v>-4.656</v>
       </c>
     </row>
     <row r="27">

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -840,14 +840,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +5.92% / +7.70% / -3.96% | TKFEN.IS: -0.11% / +1.16% / -2.24%</t>
+          <t>BRSAN.IS: +5.92% / +7.70% / -3.96% | TKFEN.IS: -0.28% / +1.16% / -2.24%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>7.239702690965699</v>
+        <v>7.149965098891542</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -879,13 +879,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>99.479</v>
+        <v>99.312</v>
       </c>
       <c r="V4" t="n">
-        <v>54.251</v>
+        <v>54.122</v>
       </c>
       <c r="W4" t="n">
-        <v>-27.84</v>
+        <v>-28.007</v>
       </c>
     </row>
     <row r="5">
@@ -1077,14 +1077,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +5.92% / +7.70% / -3.96% | TKFEN.IS: -0.11% / +1.16% / -2.24%</t>
+          <t>BRSAN.IS: +5.92% / +7.70% / -3.96% | TKFEN.IS: -0.28% / +1.16% / -2.24%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>7.239702690965699</v>
+        <v>7.149965098891542</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1116,13 +1116,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>99.479</v>
+        <v>99.312</v>
       </c>
       <c r="V7" t="n">
-        <v>54.251</v>
+        <v>54.122</v>
       </c>
       <c r="W7" t="n">
-        <v>-27.84</v>
+        <v>-28.007</v>
       </c>
     </row>
     <row r="8">
@@ -1626,14 +1626,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BIMAS.IS: +0.41% / +3.13% / 0.00%</t>
+          <t>BIMAS.IS: +0.59% / +3.13% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-6.412181273130146</v>
       </c>
       <c r="K14" t="n">
-        <v>7.608376302870923</v>
+        <v>7.674375819363943</v>
       </c>
       <c r="L14" t="n">
         <v>12.30894614425559</v>
@@ -1665,13 +1665,13 @@
         <v>11.714</v>
       </c>
       <c r="U14" t="n">
-        <v>11.571</v>
+        <v>11.639</v>
       </c>
       <c r="V14" t="n">
-        <v>21.136</v>
+        <v>21.21</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.296</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="16">
@@ -1916,14 +1916,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +5.92% / +7.70% / -3.96% | TKFEN.IS: -0.11% / +1.16% / -2.24%</t>
+          <t>BRSAN.IS: +5.92% / +7.70% / -3.96% | TKFEN.IS: -0.28% / +1.16% / -2.24%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>7.239702690965699</v>
+        <v>7.149965098891542</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1955,13 +1955,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>99.479</v>
+        <v>99.312</v>
       </c>
       <c r="V19" t="n">
-        <v>54.251</v>
+        <v>54.122</v>
       </c>
       <c r="W19" t="n">
-        <v>-27.84</v>
+        <v>-28.007</v>
       </c>
     </row>
     <row r="20">
@@ -2325,14 +2325,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>BIMAS.IS: +0.41% / +3.13% / 0.00%</t>
+          <t>BIMAS.IS: +0.59% / +3.13% / 0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-6.412181273130146</v>
       </c>
       <c r="K24" t="n">
-        <v>7.608376302870923</v>
+        <v>7.674375819363943</v>
       </c>
       <c r="L24" t="n">
         <v>12.30894614425559</v>
@@ -2364,13 +2364,13 @@
         <v>11.714</v>
       </c>
       <c r="U24" t="n">
-        <v>11.571</v>
+        <v>11.639</v>
       </c>
       <c r="V24" t="n">
-        <v>21.136</v>
+        <v>21.21</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.296</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="25">
@@ -3410,14 +3410,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.49% / +5.34% / -1.19% | BRSAN.IS: +4.81% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: +3.12% / +5.34% / -1.19% | BRSAN.IS: +4.81% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K13" t="n">
-        <v>15.1640985780058</v>
+        <v>14.95708206523323</v>
       </c>
       <c r="L13" t="n">
         <v>28.49280591027672</v>
@@ -3449,13 +3449,13 @@
         <v>13.617</v>
       </c>
       <c r="U13" t="n">
-        <v>42.331</v>
+        <v>42.075</v>
       </c>
       <c r="V13" t="n">
-        <v>21.771</v>
+        <v>21.552</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.656</v>
+        <v>-4.912</v>
       </c>
     </row>
     <row r="14">
@@ -3497,14 +3497,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.56% / +3.39% / 0.00% | BRSAN.IS: +4.81% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: +1.20% / +3.39% / 0.00% | BRSAN.IS: +4.81% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>11.98754243474287</v>
+        <v>11.79206238944681</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3536,13 +3536,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>42.076</v>
+        <v>41.828</v>
       </c>
       <c r="V14" t="n">
-        <v>32.734</v>
+        <v>32.502</v>
       </c>
       <c r="W14" t="n">
-        <v>-16.909</v>
+        <v>-17.157</v>
       </c>
     </row>
     <row r="16">
@@ -4249,14 +4249,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.56% / +3.39% / 0.00% | BRSAN.IS: +4.81% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: +1.20% / +3.39% / 0.00% | BRSAN.IS: +4.81% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>11.98754243474287</v>
+        <v>11.79206238944681</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4288,13 +4288,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>42.076</v>
+        <v>41.828</v>
       </c>
       <c r="V25" t="n">
-        <v>32.734</v>
+        <v>32.502</v>
       </c>
       <c r="W25" t="n">
-        <v>-16.909</v>
+        <v>-17.157</v>
       </c>
     </row>
     <row r="26">
@@ -4338,14 +4338,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.49% / +5.34% / -1.19% | BRSAN.IS: +4.81% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: +3.12% / +5.34% / -1.19% | BRSAN.IS: +4.81% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>15.1640985780058</v>
+        <v>14.95708206523323</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4377,13 +4377,13 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>42.331</v>
+        <v>42.075</v>
       </c>
       <c r="V26" t="n">
-        <v>21.771</v>
+        <v>21.552</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.656</v>
+        <v>-4.912</v>
       </c>
     </row>
     <row r="27">

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -840,14 +840,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +5.92% / +7.70% / -3.96% | TKFEN.IS: -0.28% / +1.16% / -2.24%</t>
+          <t>BRSAN.IS: +6.69% / +7.70% / -3.96% | TKFEN.IS: -1.35% / +1.16% / -2.24%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>7.149965098891542</v>
+        <v>6.986229878091099</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -879,13 +879,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>99.312</v>
+        <v>99.00700000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>54.122</v>
+        <v>53.887</v>
       </c>
       <c r="W4" t="n">
-        <v>-28.007</v>
+        <v>-28.311</v>
       </c>
     </row>
     <row r="5">
@@ -1077,14 +1077,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +5.92% / +7.70% / -3.96% | TKFEN.IS: -0.28% / +1.16% / -2.24%</t>
+          <t>BRSAN.IS: +6.69% / +7.70% / -3.96% | TKFEN.IS: -1.35% / +1.16% / -2.24%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>7.149965098891542</v>
+        <v>6.986229878091099</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1116,13 +1116,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>99.312</v>
+        <v>99.00700000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>54.122</v>
+        <v>53.887</v>
       </c>
       <c r="W7" t="n">
-        <v>-28.007</v>
+        <v>-28.311</v>
       </c>
     </row>
     <row r="8">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1526,42 +1526,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ALARK.IS, BIMAS.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
+          <t>BIMAS.IS: 2026-08-19</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>34.62553795007752</v>
+        <v>12.43146471706449</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BIMAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BIMAS.IS: +0.84% / +3.13% / -0.86%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8.431557803491319</v>
+        <v>-6.412181273130146</v>
       </c>
       <c r="K13" t="n">
-        <v>7.721874362672154</v>
+        <v>7.762375174687941</v>
       </c>
       <c r="L13" t="n">
-        <v>32.1397934777012</v>
+        <v>12.30894614425559</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>233.6</v>
+        <v>140.4</v>
       </c>
       <c r="O13" t="n">
-        <v>49.3</v>
+        <v>48.1</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1569,22 +1569,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>20.274</v>
+        <v>12.004</v>
       </c>
       <c r="T13" t="n">
-        <v>20.274</v>
+        <v>11.714</v>
       </c>
       <c r="U13" t="n">
-        <v>87.407</v>
+        <v>11.731</v>
       </c>
       <c r="V13" t="n">
-        <v>43.614</v>
+        <v>21.309</v>
       </c>
       <c r="W13" t="n">
-        <v>-27.471</v>
+        <v>-1.137</v>
       </c>
     </row>
     <row r="14">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1613,42 +1613,42 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>ALARK.IS, BIMAS.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BIMAS.IS: 2026-08-19</t>
+          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>12.43146471706449</v>
+        <v>34.62553795007752</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BIMAS.IS: +0.59% / +3.13% / 0.00%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BIMAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-6.412181273130146</v>
+        <v>8.431557803491319</v>
       </c>
       <c r="K14" t="n">
-        <v>7.674375819363943</v>
+        <v>7.721874362672154</v>
       </c>
       <c r="L14" t="n">
-        <v>12.30894614425559</v>
+        <v>32.1397934777012</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>140.4</v>
+        <v>233.6</v>
       </c>
       <c r="O14" t="n">
-        <v>48.1</v>
+        <v>49.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1656,22 +1656,22 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>12.004</v>
+        <v>20.274</v>
       </c>
       <c r="T14" t="n">
-        <v>11.714</v>
+        <v>20.274</v>
       </c>
       <c r="U14" t="n">
-        <v>11.639</v>
+        <v>87.407</v>
       </c>
       <c r="V14" t="n">
-        <v>21.21</v>
+        <v>43.614</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.228</v>
+        <v>-27.471</v>
       </c>
     </row>
     <row r="16">
@@ -1916,14 +1916,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +5.92% / +7.70% / -3.96% | TKFEN.IS: -0.28% / +1.16% / -2.24%</t>
+          <t>BRSAN.IS: +6.69% / +7.70% / -3.96% | TKFEN.IS: -1.35% / +1.16% / -2.24%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>7.149965098891542</v>
+        <v>6.986229878091099</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1955,13 +1955,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>99.312</v>
+        <v>99.00700000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>54.122</v>
+        <v>53.887</v>
       </c>
       <c r="W19" t="n">
-        <v>-28.007</v>
+        <v>-28.311</v>
       </c>
     </row>
     <row r="20">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2325,14 +2325,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>BIMAS.IS: +0.59% / +3.13% / 0.00%</t>
+          <t>BIMAS.IS: +0.84% / +3.13% / -0.86%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-6.412181273130146</v>
       </c>
       <c r="K24" t="n">
-        <v>7.674375819363943</v>
+        <v>7.762375174687941</v>
       </c>
       <c r="L24" t="n">
         <v>12.30894614425559</v>
@@ -2364,13 +2364,13 @@
         <v>11.714</v>
       </c>
       <c r="U24" t="n">
-        <v>11.639</v>
+        <v>11.731</v>
       </c>
       <c r="V24" t="n">
-        <v>21.21</v>
+        <v>21.309</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.228</v>
+        <v>-1.137</v>
       </c>
     </row>
     <row r="25">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3402,37 +3402,37 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-17 | BRSAN.IS: 2026-08-19</t>
+          <t>AKBNK.IS: 2026-07-29 | BRSAN.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>18.78300085000422</v>
+        <v>5.84922237136889</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.12% / +5.34% / -1.19% | BRSAN.IS: +4.81% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: +7.30% / +11.52% / -3.77% | BRSAN.IS: +11.03% / +12.09% / -0.05%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-0.2995012191682078</v>
+        <v>-7.945335963406319</v>
       </c>
       <c r="K13" t="n">
-        <v>14.95708206523323</v>
+        <v>14.41220149466471</v>
       </c>
       <c r="L13" t="n">
-        <v>28.49280591027672</v>
+        <v>31.58073864491333</v>
       </c>
       <c r="M13" t="n">
         <v>88.88888888888889</v>
       </c>
       <c r="N13" t="n">
-        <v>81.7</v>
+        <v>48.3</v>
       </c>
       <c r="O13" t="n">
-        <v>48.8</v>
+        <v>49.5</v>
       </c>
       <c r="P13" t="n">
-        <v>3.6</v>
+        <v>6.1</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3443,19 +3443,19 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>13.617</v>
+        <v>11.1</v>
       </c>
       <c r="T13" t="n">
-        <v>13.617</v>
+        <v>11.1</v>
       </c>
       <c r="U13" t="n">
-        <v>42.075</v>
+        <v>37.185</v>
       </c>
       <c r="V13" t="n">
-        <v>21.552</v>
+        <v>16.552</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.912</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="14">
@@ -3497,14 +3497,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.20% / +3.39% / 0.00% | BRSAN.IS: +4.81% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: -0.52% / +3.39% / -0.58% | BRSAN.IS: +5.56% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>11.79206238944681</v>
+        <v>11.26291899367098</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3516,7 +3516,7 @@
         <v>38.3</v>
       </c>
       <c r="O14" t="n">
-        <v>57.1</v>
+        <v>55.8</v>
       </c>
       <c r="P14" t="n">
         <v>7.4</v>
@@ -3536,13 +3536,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>41.828</v>
+        <v>41.157</v>
       </c>
       <c r="V14" t="n">
-        <v>32.502</v>
+        <v>31.875</v>
       </c>
       <c r="W14" t="n">
-        <v>-17.157</v>
+        <v>-17.828</v>
       </c>
     </row>
     <row r="16">
@@ -4249,14 +4249,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.20% / +3.39% / 0.00% | BRSAN.IS: +4.81% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: -0.52% / +3.39% / -0.58% | BRSAN.IS: +5.56% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>11.79206238944681</v>
+        <v>11.26291899367098</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4268,7 +4268,7 @@
         <v>38.3</v>
       </c>
       <c r="O25" t="n">
-        <v>57.1</v>
+        <v>55.8</v>
       </c>
       <c r="P25" t="n">
         <v>7.4</v>
@@ -4288,13 +4288,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>41.828</v>
+        <v>41.157</v>
       </c>
       <c r="V25" t="n">
-        <v>32.502</v>
+        <v>31.875</v>
       </c>
       <c r="W25" t="n">
-        <v>-17.157</v>
+        <v>-17.828</v>
       </c>
     </row>
     <row r="26">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4330,37 +4330,37 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-17 | BRSAN.IS: 2026-08-19</t>
+          <t>AKBNK.IS: 2026-07-29 | BRSAN.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18.78300085000422</v>
+        <v>5.84922237136889</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.12% / +5.34% / -1.19% | BRSAN.IS: +4.81% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: +7.30% / +11.52% / -3.77% | BRSAN.IS: +11.03% / +12.09% / -0.05%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-0.2995012191682078</v>
+        <v>-7.945335963406319</v>
       </c>
       <c r="K26" t="n">
-        <v>14.95708206523323</v>
+        <v>14.41220149466471</v>
       </c>
       <c r="L26" t="n">
-        <v>28.49280591027672</v>
+        <v>31.58073864491333</v>
       </c>
       <c r="M26" t="n">
         <v>88.88888888888889</v>
       </c>
       <c r="N26" t="n">
-        <v>81.7</v>
+        <v>48.3</v>
       </c>
       <c r="O26" t="n">
-        <v>48.8</v>
+        <v>49.5</v>
       </c>
       <c r="P26" t="n">
-        <v>3.6</v>
+        <v>6.1</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4371,19 +4371,19 @@
         <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>13.617</v>
+        <v>11.1</v>
       </c>
       <c r="T26" t="n">
-        <v>13.617</v>
+        <v>11.1</v>
       </c>
       <c r="U26" t="n">
-        <v>42.075</v>
+        <v>37.185</v>
       </c>
       <c r="V26" t="n">
-        <v>21.552</v>
+        <v>16.552</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.912</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="27">

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -840,14 +840,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.69% / +7.70% / -3.96% | TKFEN.IS: -1.35% / +1.16% / -2.24%</t>
+          <t>BRSAN.IS: +5.62% / +7.70% / -3.96% | TKFEN.IS: -1.66% / +1.16% / -3.10%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>6.986229878091099</v>
+        <v>6.273197363943561</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -879,13 +879,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>99.00700000000001</v>
+        <v>97.681</v>
       </c>
       <c r="V4" t="n">
-        <v>53.887</v>
+        <v>52.861</v>
       </c>
       <c r="W4" t="n">
-        <v>-28.311</v>
+        <v>-29.638</v>
       </c>
     </row>
     <row r="5">
@@ -1077,14 +1077,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.69% / +7.70% / -3.96% | TKFEN.IS: -1.35% / +1.16% / -2.24%</t>
+          <t>BRSAN.IS: +5.62% / +7.70% / -3.96% | TKFEN.IS: -1.66% / +1.16% / -3.10%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>6.986229878091099</v>
+        <v>6.273197363943561</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1116,13 +1116,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>99.00700000000001</v>
+        <v>97.681</v>
       </c>
       <c r="V7" t="n">
-        <v>53.887</v>
+        <v>52.861</v>
       </c>
       <c r="W7" t="n">
-        <v>-28.311</v>
+        <v>-29.638</v>
       </c>
     </row>
     <row r="8">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1449,55 +1449,67 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, BSOKE.IS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-19 | BSOKE.IS: 2026-08-14</t>
+        </is>
+      </c>
       <c r="H12" t="n">
-        <v>3.443912532931592</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>35.19994501826646</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: +4.50% / +6.56% / 0.00% | BSOKE.IS: +1.04% / +1.59% / -2.17%</t>
+        </is>
+      </c>
       <c r="J12" t="n">
-        <v>-1.862436885442242</v>
+        <v>11.12989926884889</v>
       </c>
       <c r="K12" t="n">
-        <v>9.760986497744174</v>
+        <v>9.96290774769184</v>
       </c>
       <c r="L12" t="n">
-        <v>7.902828022135555</v>
+        <v>18.10083632820908</v>
       </c>
       <c r="M12" t="n">
-        <v>33.33333333333333</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N12" t="n">
-        <v>32.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>46.2</v>
+        <v>51.7</v>
       </c>
       <c r="P12" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>8.954000000000001</v>
+        <v>13.39</v>
       </c>
       <c r="T12" t="n">
-        <v>8.954000000000001</v>
+        <v>13.39</v>
       </c>
       <c r="U12" t="n">
-        <v>10.011</v>
+        <v>27.27</v>
       </c>
       <c r="V12" t="n">
-        <v>9.042999999999999</v>
+        <v>18.931</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.724</v>
+        <v>-6.462</v>
       </c>
     </row>
     <row r="13">
@@ -1511,7 +1523,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1526,42 +1538,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>ALARK.IS, BIMAS.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BIMAS.IS: 2026-08-19</t>
+          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>12.43146471706449</v>
+        <v>34.62553795007752</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BIMAS.IS: +0.84% / +3.13% / -0.86%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BIMAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-6.412181273130146</v>
+        <v>8.431557803491319</v>
       </c>
       <c r="K13" t="n">
-        <v>7.762375174687941</v>
+        <v>7.721874362672154</v>
       </c>
       <c r="L13" t="n">
-        <v>12.30894614425559</v>
+        <v>32.1397934777012</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>140.4</v>
+        <v>233.6</v>
       </c>
       <c r="O13" t="n">
-        <v>48.1</v>
+        <v>49.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1569,22 +1581,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>12.004</v>
+        <v>20.274</v>
       </c>
       <c r="T13" t="n">
-        <v>11.714</v>
+        <v>20.274</v>
       </c>
       <c r="U13" t="n">
-        <v>11.731</v>
+        <v>87.407</v>
       </c>
       <c r="V13" t="n">
-        <v>21.309</v>
+        <v>43.614</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.137</v>
+        <v>-27.471</v>
       </c>
     </row>
     <row r="14">
@@ -1598,7 +1610,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1613,42 +1625,42 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ALARK.IS, BIMAS.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
+          <t>BIMAS.IS: 2026-08-19</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>34.62553795007752</v>
+        <v>12.43146471706449</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BIMAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BIMAS.IS: +0.47% / +3.13% / -0.86%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8.431557803491319</v>
+        <v>-6.412181273130146</v>
       </c>
       <c r="K14" t="n">
-        <v>7.721874362672154</v>
+        <v>7.630376141701922</v>
       </c>
       <c r="L14" t="n">
-        <v>32.1397934777012</v>
+        <v>12.30894614425559</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>233.6</v>
+        <v>140.4</v>
       </c>
       <c r="O14" t="n">
-        <v>49.3</v>
+        <v>48.1</v>
       </c>
       <c r="P14" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1656,22 +1668,22 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>20.274</v>
+        <v>12.004</v>
       </c>
       <c r="T14" t="n">
-        <v>20.274</v>
+        <v>11.714</v>
       </c>
       <c r="U14" t="n">
-        <v>87.407</v>
+        <v>11.594</v>
       </c>
       <c r="V14" t="n">
-        <v>43.614</v>
+        <v>21.16</v>
       </c>
       <c r="W14" t="n">
-        <v>-27.471</v>
+        <v>-1.273</v>
       </c>
     </row>
     <row r="16">
@@ -1916,14 +1928,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.69% / +7.70% / -3.96% | TKFEN.IS: -1.35% / +1.16% / -2.24%</t>
+          <t>BRSAN.IS: +5.62% / +7.70% / -3.96% | TKFEN.IS: -1.66% / +1.16% / -3.10%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>6.986229878091099</v>
+        <v>6.273197363943561</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1955,13 +1967,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>99.00700000000001</v>
+        <v>97.681</v>
       </c>
       <c r="V19" t="n">
-        <v>53.887</v>
+        <v>52.861</v>
       </c>
       <c r="W19" t="n">
-        <v>-28.311</v>
+        <v>-29.638</v>
       </c>
     </row>
     <row r="20">
@@ -2203,12 +2215,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2223,42 +2235,42 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ALARK.IS, BIMAS.IS</t>
+          <t>BRSAN.IS, BSOKE.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
+          <t>BRSAN.IS: 2026-08-19 | BSOKE.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>34.62553795007752</v>
+        <v>35.19994501826646</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BIMAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +4.50% / +6.56% / 0.00% | BSOKE.IS: +1.04% / +1.59% / -2.17%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>8.431557803491319</v>
+        <v>11.12989926884889</v>
       </c>
       <c r="K23" t="n">
-        <v>7.721874362672154</v>
+        <v>9.96290774769184</v>
       </c>
       <c r="L23" t="n">
-        <v>32.1397934777012</v>
+        <v>18.10083632820908</v>
       </c>
       <c r="M23" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N23" t="n">
-        <v>233.6</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>49.3</v>
+        <v>51.7</v>
       </c>
       <c r="P23" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2269,19 +2281,19 @@
         <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>20.274</v>
+        <v>13.39</v>
       </c>
       <c r="T23" t="n">
-        <v>20.274</v>
+        <v>13.39</v>
       </c>
       <c r="U23" t="n">
-        <v>87.407</v>
+        <v>27.27</v>
       </c>
       <c r="V23" t="n">
-        <v>43.614</v>
+        <v>18.931</v>
       </c>
       <c r="W23" t="n">
-        <v>-27.471</v>
+        <v>-6.462</v>
       </c>
     </row>
     <row r="24">
@@ -2297,7 +2309,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2312,42 +2324,42 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>ALARK.IS, BIMAS.IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>BIMAS.IS: 2026-08-19</t>
+          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>12.43146471706449</v>
+        <v>34.62553795007752</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>BIMAS.IS: +0.84% / +3.13% / -0.86%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BIMAS.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>-6.412181273130146</v>
+        <v>8.431557803491319</v>
       </c>
       <c r="K24" t="n">
-        <v>7.762375174687941</v>
+        <v>7.721874362672154</v>
       </c>
       <c r="L24" t="n">
-        <v>12.30894614425559</v>
+        <v>32.1397934777012</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>140.4</v>
+        <v>233.6</v>
       </c>
       <c r="O24" t="n">
-        <v>48.1</v>
+        <v>49.3</v>
       </c>
       <c r="P24" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2355,22 +2367,22 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>12.004</v>
+        <v>20.274</v>
       </c>
       <c r="T24" t="n">
-        <v>11.714</v>
+        <v>20.274</v>
       </c>
       <c r="U24" t="n">
-        <v>11.731</v>
+        <v>87.407</v>
       </c>
       <c r="V24" t="n">
-        <v>21.309</v>
+        <v>43.614</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.137</v>
+        <v>-27.471</v>
       </c>
     </row>
     <row r="25">
@@ -2381,12 +2393,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2399,55 +2411,67 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>BIMAS.IS: 2026-08-19</t>
+        </is>
+      </c>
       <c r="H25" t="n">
-        <v>3.443912532931592</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>12.43146471706449</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>BIMAS.IS: +0.47% / +3.13% / -0.86%</t>
+        </is>
+      </c>
       <c r="J25" t="n">
-        <v>-1.862436885442242</v>
+        <v>-6.412181273130146</v>
       </c>
       <c r="K25" t="n">
-        <v>9.760986497744174</v>
+        <v>7.630376141701922</v>
       </c>
       <c r="L25" t="n">
-        <v>7.902828022135555</v>
+        <v>12.30894614425559</v>
       </c>
       <c r="M25" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>32.2</v>
+        <v>140.4</v>
       </c>
       <c r="O25" t="n">
-        <v>46.2</v>
+        <v>48.1</v>
       </c>
       <c r="P25" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>8.954000000000001</v>
+        <v>12.004</v>
       </c>
       <c r="T25" t="n">
-        <v>8.954000000000001</v>
+        <v>11.714</v>
       </c>
       <c r="U25" t="n">
-        <v>10.011</v>
+        <v>11.594</v>
       </c>
       <c r="V25" t="n">
-        <v>9.042999999999999</v>
+        <v>21.16</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.724</v>
+        <v>-1.273</v>
       </c>
     </row>
   </sheetData>
@@ -3410,14 +3434,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +7.30% / +11.52% / -3.77% | BRSAN.IS: +11.03% / +12.09% / -0.05%</t>
+          <t>AKBNK.IS: +7.38% / +11.52% / -3.77% | BRSAN.IS: +9.92% / +12.09% / -0.05%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-7.945335963406319</v>
       </c>
       <c r="K13" t="n">
-        <v>14.41220149466471</v>
+        <v>14.1280064963272</v>
       </c>
       <c r="L13" t="n">
         <v>31.58073864491333</v>
@@ -3449,13 +3473,13 @@
         <v>11.1</v>
       </c>
       <c r="U13" t="n">
-        <v>37.185</v>
+        <v>36.844</v>
       </c>
       <c r="V13" t="n">
-        <v>16.552</v>
+        <v>16.263</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.4</v>
+        <v>-4.741</v>
       </c>
     </row>
     <row r="14">
@@ -3497,14 +3521,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.52% / +3.39% / -0.58% | BRSAN.IS: +5.56% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: -0.45% / +3.39% / -0.79% | BRSAN.IS: +4.50% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>11.26291899367098</v>
+        <v>10.72918961003173</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3536,13 +3560,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>41.157</v>
+        <v>40.48</v>
       </c>
       <c r="V14" t="n">
-        <v>31.875</v>
+        <v>31.243</v>
       </c>
       <c r="W14" t="n">
-        <v>-17.828</v>
+        <v>-18.506</v>
       </c>
     </row>
     <row r="16">
@@ -4249,14 +4273,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.52% / +3.39% / -0.58% | BRSAN.IS: +5.56% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: -0.45% / +3.39% / -0.79% | BRSAN.IS: +4.50% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>11.26291899367098</v>
+        <v>10.72918961003173</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4288,13 +4312,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>41.157</v>
+        <v>40.48</v>
       </c>
       <c r="V25" t="n">
-        <v>31.875</v>
+        <v>31.243</v>
       </c>
       <c r="W25" t="n">
-        <v>-17.828</v>
+        <v>-18.506</v>
       </c>
     </row>
     <row r="26">
@@ -4338,14 +4362,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +7.30% / +11.52% / -3.77% | BRSAN.IS: +11.03% / +12.09% / -0.05%</t>
+          <t>AKBNK.IS: +7.38% / +11.52% / -3.77% | BRSAN.IS: +9.92% / +12.09% / -0.05%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-7.945335963406319</v>
       </c>
       <c r="K26" t="n">
-        <v>14.41220149466471</v>
+        <v>14.1280064963272</v>
       </c>
       <c r="L26" t="n">
         <v>31.58073864491333</v>
@@ -4377,13 +4401,13 @@
         <v>11.1</v>
       </c>
       <c r="U26" t="n">
-        <v>37.185</v>
+        <v>36.844</v>
       </c>
       <c r="V26" t="n">
-        <v>16.552</v>
+        <v>16.263</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.4</v>
+        <v>-4.741</v>
       </c>
     </row>
     <row r="27">

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -742,12 +742,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -769,7 +769,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>118.1</v>
+        <v>117.8</v>
       </c>
       <c r="O3" t="n">
         <v>39.9</v>
@@ -792,13 +792,13 @@
         <v>28.567</v>
       </c>
       <c r="U3" t="n">
-        <v>84.363</v>
+        <v>80.15300000000001</v>
       </c>
       <c r="V3" t="n">
         <v>41.769</v>
       </c>
       <c r="W3" t="n">
-        <v>-73.729</v>
+        <v>-72.045</v>
       </c>
     </row>
     <row r="4">
@@ -817,12 +817,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -840,14 +840,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +5.62% / +7.70% / -3.96% | TKFEN.IS: -1.66% / +1.16% / -3.10%</t>
+          <t>BRSAN.IS: +6.76% / +7.70% / -3.96% | TKFEN.IS: -1.79% / +1.16% / -3.10%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>6.273197363943561</v>
+        <v>6.801595804898586</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -856,7 +856,7 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>121.5</v>
+        <v>121.3</v>
       </c>
       <c r="O4" t="n">
         <v>43.3</v>
@@ -879,13 +879,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>97.681</v>
+        <v>97.91500000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>52.861</v>
+        <v>53.621</v>
       </c>
       <c r="W4" t="n">
-        <v>-29.638</v>
+        <v>-28.547</v>
       </c>
     </row>
     <row r="5">
@@ -904,12 +904,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -931,7 +931,7 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>94.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>37.4</v>
@@ -954,13 +954,13 @@
         <v>35.687</v>
       </c>
       <c r="U5" t="n">
-        <v>29.475</v>
+        <v>27.118</v>
       </c>
       <c r="V5" t="n">
         <v>12.323</v>
       </c>
       <c r="W5" t="n">
-        <v>-71.846</v>
+        <v>-70.538</v>
       </c>
     </row>
     <row r="6">
@@ -979,12 +979,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -1006,7 +1006,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>118.1</v>
+        <v>117.8</v>
       </c>
       <c r="O6" t="n">
         <v>39.9</v>
@@ -1029,13 +1029,13 @@
         <v>28.567</v>
       </c>
       <c r="U6" t="n">
-        <v>84.363</v>
+        <v>80.15300000000001</v>
       </c>
       <c r="V6" t="n">
         <v>41.769</v>
       </c>
       <c r="W6" t="n">
-        <v>-73.729</v>
+        <v>-72.045</v>
       </c>
     </row>
     <row r="7">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1077,14 +1077,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +5.62% / +7.70% / -3.96% | TKFEN.IS: -1.66% / +1.16% / -3.10%</t>
+          <t>BRSAN.IS: +6.76% / +7.70% / -3.96% | TKFEN.IS: -1.79% / +1.16% / -3.10%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>6.273197363943561</v>
+        <v>6.801595804898586</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1093,7 +1093,7 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>121.5</v>
+        <v>121.3</v>
       </c>
       <c r="O7" t="n">
         <v>43.3</v>
@@ -1116,13 +1116,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>97.681</v>
+        <v>97.91500000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>52.861</v>
+        <v>53.621</v>
       </c>
       <c r="W7" t="n">
-        <v>-29.638</v>
+        <v>-28.547</v>
       </c>
     </row>
     <row r="8">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -1168,7 +1168,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N8" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="O8" t="n">
         <v>51.1</v>
@@ -1191,13 +1191,13 @@
         <v>29.993</v>
       </c>
       <c r="U8" t="n">
-        <v>9.574999999999999</v>
+        <v>7.224</v>
       </c>
       <c r="V8" t="n">
         <v>-6.769</v>
       </c>
       <c r="W8" t="n">
-        <v>-46.433</v>
+        <v>-45.437</v>
       </c>
     </row>
     <row r="9">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>118.1</v>
+        <v>117.8</v>
       </c>
       <c r="O9" t="n">
         <v>39.9</v>
@@ -1266,13 +1266,13 @@
         <v>28.567</v>
       </c>
       <c r="U9" t="n">
-        <v>84.363</v>
+        <v>80.15300000000001</v>
       </c>
       <c r="V9" t="n">
         <v>41.769</v>
       </c>
       <c r="W9" t="n">
-        <v>-73.729</v>
+        <v>-72.045</v>
       </c>
     </row>
     <row r="10">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1318,7 +1318,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="O10" t="n">
         <v>51.1</v>
@@ -1341,13 +1341,13 @@
         <v>29.993</v>
       </c>
       <c r="U10" t="n">
-        <v>9.574999999999999</v>
+        <v>7.224</v>
       </c>
       <c r="V10" t="n">
         <v>-6.769</v>
       </c>
       <c r="W10" t="n">
-        <v>-46.433</v>
+        <v>-45.437</v>
       </c>
     </row>
     <row r="11">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1393,7 +1393,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="O11" t="n">
         <v>38.4</v>
@@ -1416,13 +1416,13 @@
         <v>29.287</v>
       </c>
       <c r="U11" t="n">
-        <v>40.954</v>
+        <v>39.263</v>
       </c>
       <c r="V11" t="n">
         <v>14.374</v>
       </c>
       <c r="W11" t="n">
-        <v>-50.099</v>
+        <v>-49.498</v>
       </c>
     </row>
     <row r="12">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>BRSAN.IS, BSOKE.IS</t>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-19 | BSOKE.IS: 2026-08-14</t>
+          <t>BRSAN.IS: 2026-08-21 | BSOKE.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1464,14 +1464,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +4.50% / +6.56% / 0.00% | BSOKE.IS: +1.04% / +1.59% / -2.17%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: +0.98% / +1.59% / -2.17%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>11.12989926884889</v>
       </c>
       <c r="K12" t="n">
-        <v>9.96290774769184</v>
+        <v>10.49874179376298</v>
       </c>
       <c r="L12" t="n">
         <v>18.10083632820908</v>
@@ -1480,10 +1480,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N12" t="n">
-        <v>72.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="O12" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
       <c r="P12" t="n">
         <v>3.8</v>
@@ -1503,13 +1503,13 @@
         <v>13.39</v>
       </c>
       <c r="U12" t="n">
-        <v>27.27</v>
+        <v>27.404</v>
       </c>
       <c r="V12" t="n">
-        <v>18.931</v>
+        <v>19.511</v>
       </c>
       <c r="W12" t="n">
-        <v>-6.462</v>
+        <v>-5.819</v>
       </c>
     </row>
     <row r="13">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1551,14 +1551,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BIMAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +0.44% / +0.46% / -0.56% | BIMAS.IS: +0.65% / +1.34% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>8.431557803491319</v>
       </c>
       <c r="K13" t="n">
-        <v>7.721874362672154</v>
+        <v>8.333657242217463</v>
       </c>
       <c r="L13" t="n">
         <v>32.1397934777012</v>
@@ -1567,10 +1567,10 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>233.6</v>
+        <v>233.2</v>
       </c>
       <c r="O13" t="n">
-        <v>49.3</v>
+        <v>49.7</v>
       </c>
       <c r="P13" t="n">
         <v>3.1</v>
@@ -1590,13 +1590,13 @@
         <v>20.274</v>
       </c>
       <c r="U13" t="n">
-        <v>87.407</v>
+        <v>83.06399999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>43.614</v>
+        <v>44.43</v>
       </c>
       <c r="W13" t="n">
-        <v>-27.471</v>
+        <v>-25.649</v>
       </c>
     </row>
     <row r="14">
@@ -1615,37 +1615,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>BIMAS.IS: 2026-08-19</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>12.43146471706449</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>BIMAS.IS: +0.47% / +3.13% / -0.86%</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
         <v>-6.412181273130146</v>
       </c>
       <c r="K14" t="n">
-        <v>7.630376141701922</v>
+        <v>7.872374368842938</v>
       </c>
       <c r="L14" t="n">
         <v>12.30894614425559</v>
@@ -1654,7 +1642,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>140.4</v>
+        <v>140.1</v>
       </c>
       <c r="O14" t="n">
         <v>48.1</v>
@@ -1664,11 +1652,11 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>12.004</v>
@@ -1677,13 +1665,13 @@
         <v>11.714</v>
       </c>
       <c r="U14" t="n">
-        <v>11.594</v>
+        <v>11.845</v>
       </c>
       <c r="V14" t="n">
-        <v>21.16</v>
+        <v>21.433</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.273</v>
+        <v>-1.022</v>
       </c>
     </row>
     <row r="16">
@@ -1828,12 +1816,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1855,7 +1843,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>118.1</v>
+        <v>117.8</v>
       </c>
       <c r="O18" t="n">
         <v>39.9</v>
@@ -1878,13 +1866,13 @@
         <v>28.567</v>
       </c>
       <c r="U18" t="n">
-        <v>84.363</v>
+        <v>80.15300000000001</v>
       </c>
       <c r="V18" t="n">
         <v>41.769</v>
       </c>
       <c r="W18" t="n">
-        <v>-73.729</v>
+        <v>-72.045</v>
       </c>
     </row>
     <row r="19">
@@ -1905,12 +1893,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1928,14 +1916,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +5.62% / +7.70% / -3.96% | TKFEN.IS: -1.66% / +1.16% / -3.10%</t>
+          <t>BRSAN.IS: +6.76% / +7.70% / -3.96% | TKFEN.IS: -1.79% / +1.16% / -3.10%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>6.273197363943561</v>
+        <v>6.801595804898586</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1944,7 +1932,7 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>121.5</v>
+        <v>121.3</v>
       </c>
       <c r="O19" t="n">
         <v>43.3</v>
@@ -1967,13 +1955,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>97.681</v>
+        <v>97.91500000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>52.861</v>
+        <v>53.621</v>
       </c>
       <c r="W19" t="n">
-        <v>-29.638</v>
+        <v>-28.547</v>
       </c>
     </row>
     <row r="20">
@@ -1994,12 +1982,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2021,7 +2009,7 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>94.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O20" t="n">
         <v>37.4</v>
@@ -2044,13 +2032,13 @@
         <v>35.687</v>
       </c>
       <c r="U20" t="n">
-        <v>29.475</v>
+        <v>27.118</v>
       </c>
       <c r="V20" t="n">
         <v>12.323</v>
       </c>
       <c r="W20" t="n">
-        <v>-71.846</v>
+        <v>-70.538</v>
       </c>
     </row>
     <row r="21">
@@ -2071,12 +2059,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2098,7 +2086,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N21" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="O21" t="n">
         <v>51.1</v>
@@ -2121,13 +2109,13 @@
         <v>29.993</v>
       </c>
       <c r="U21" t="n">
-        <v>9.574999999999999</v>
+        <v>7.224</v>
       </c>
       <c r="V21" t="n">
         <v>-6.769</v>
       </c>
       <c r="W21" t="n">
-        <v>-46.433</v>
+        <v>-45.437</v>
       </c>
     </row>
     <row r="22">
@@ -2148,12 +2136,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2175,7 +2163,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="O22" t="n">
         <v>38.4</v>
@@ -2198,13 +2186,13 @@
         <v>29.287</v>
       </c>
       <c r="U22" t="n">
-        <v>40.954</v>
+        <v>39.263</v>
       </c>
       <c r="V22" t="n">
         <v>14.374</v>
       </c>
       <c r="W22" t="n">
-        <v>-50.099</v>
+        <v>-49.498</v>
       </c>
     </row>
     <row r="23">
@@ -2225,14 +2213,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>BRSAN.IS, BSOKE.IS</t>
@@ -2240,7 +2228,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-19 | BSOKE.IS: 2026-08-14</t>
+          <t>BRSAN.IS: 2026-08-21 | BSOKE.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2248,14 +2236,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +4.50% / +6.56% / 0.00% | BSOKE.IS: +1.04% / +1.59% / -2.17%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: +0.98% / +1.59% / -2.17%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>11.12989926884889</v>
       </c>
       <c r="K23" t="n">
-        <v>9.96290774769184</v>
+        <v>10.49874179376298</v>
       </c>
       <c r="L23" t="n">
         <v>18.10083632820908</v>
@@ -2264,10 +2252,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N23" t="n">
-        <v>72.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="O23" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
       <c r="P23" t="n">
         <v>3.8</v>
@@ -2287,13 +2275,13 @@
         <v>13.39</v>
       </c>
       <c r="U23" t="n">
-        <v>27.27</v>
+        <v>27.404</v>
       </c>
       <c r="V23" t="n">
-        <v>18.931</v>
+        <v>19.511</v>
       </c>
       <c r="W23" t="n">
-        <v>-6.462</v>
+        <v>-5.819</v>
       </c>
     </row>
     <row r="24">
@@ -2314,12 +2302,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2337,14 +2325,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BIMAS.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +0.44% / +0.46% / -0.56% | BIMAS.IS: +0.65% / +1.34% / 0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>8.431557803491319</v>
       </c>
       <c r="K24" t="n">
-        <v>7.721874362672154</v>
+        <v>8.333657242217463</v>
       </c>
       <c r="L24" t="n">
         <v>32.1397934777012</v>
@@ -2353,10 +2341,10 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>233.6</v>
+        <v>233.2</v>
       </c>
       <c r="O24" t="n">
-        <v>49.3</v>
+        <v>49.7</v>
       </c>
       <c r="P24" t="n">
         <v>3.1</v>
@@ -2376,13 +2364,13 @@
         <v>20.274</v>
       </c>
       <c r="U24" t="n">
-        <v>87.407</v>
+        <v>83.06399999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>43.614</v>
+        <v>44.43</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.471</v>
+        <v>-25.649</v>
       </c>
     </row>
     <row r="25">
@@ -2403,37 +2391,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>BIMAS.IS: 2026-08-19</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>12.43146471706449</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>BIMAS.IS: +0.47% / +3.13% / -0.86%</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
         <v>-6.412181273130146</v>
       </c>
       <c r="K25" t="n">
-        <v>7.630376141701922</v>
+        <v>7.872374368842938</v>
       </c>
       <c r="L25" t="n">
         <v>12.30894614425559</v>
@@ -2442,7 +2418,7 @@
         <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>140.4</v>
+        <v>140.1</v>
       </c>
       <c r="O25" t="n">
         <v>48.1</v>
@@ -2452,11 +2428,11 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>12.004</v>
@@ -2465,13 +2441,13 @@
         <v>11.714</v>
       </c>
       <c r="U25" t="n">
-        <v>11.594</v>
+        <v>11.845</v>
       </c>
       <c r="V25" t="n">
-        <v>21.16</v>
+        <v>21.433</v>
       </c>
       <c r="W25" t="n">
-        <v>-1.273</v>
+        <v>-1.022</v>
       </c>
     </row>
   </sheetData>
@@ -2661,12 +2637,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2688,7 +2664,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>66.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="O3" t="n">
         <v>45.9</v>
@@ -2711,13 +2687,13 @@
         <v>31.839</v>
       </c>
       <c r="U3" t="n">
-        <v>24.207</v>
+        <v>22.994</v>
       </c>
       <c r="V3" t="n">
         <v>27.773</v>
       </c>
       <c r="W3" t="n">
-        <v>-58.018</v>
+        <v>-57.452</v>
       </c>
     </row>
     <row r="4">
@@ -2736,12 +2712,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2763,7 +2739,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N4" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="O4" t="n">
         <v>46.7</v>
@@ -2786,13 +2762,13 @@
         <v>30.704</v>
       </c>
       <c r="U4" t="n">
-        <v>11.171</v>
+        <v>4.937</v>
       </c>
       <c r="V4" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>-49.258</v>
+        <v>-46.496</v>
       </c>
     </row>
     <row r="5">
@@ -2811,12 +2787,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -2838,7 +2814,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="O5" t="n">
         <v>46.7</v>
@@ -2861,13 +2837,13 @@
         <v>30.704</v>
       </c>
       <c r="U5" t="n">
-        <v>11.171</v>
+        <v>4.937</v>
       </c>
       <c r="V5" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-49.258</v>
+        <v>-46.496</v>
       </c>
     </row>
     <row r="6">
@@ -2886,12 +2862,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -2913,7 +2889,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="O6" t="n">
         <v>46.7</v>
@@ -2936,13 +2912,13 @@
         <v>30.704</v>
       </c>
       <c r="U6" t="n">
-        <v>11.171</v>
+        <v>4.937</v>
       </c>
       <c r="V6" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>-49.258</v>
+        <v>-46.496</v>
       </c>
     </row>
     <row r="7">
@@ -2961,12 +2937,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -2988,7 +2964,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N7" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="O7" t="n">
         <v>46.7</v>
@@ -3011,13 +2987,13 @@
         <v>30.704</v>
       </c>
       <c r="U7" t="n">
-        <v>11.171</v>
+        <v>4.937</v>
       </c>
       <c r="V7" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>-49.258</v>
+        <v>-46.496</v>
       </c>
     </row>
     <row r="8">
@@ -3036,12 +3012,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -3063,7 +3039,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>111.6</v>
+        <v>111.3</v>
       </c>
       <c r="O8" t="n">
         <v>38.4</v>
@@ -3086,13 +3062,13 @@
         <v>28.888</v>
       </c>
       <c r="U8" t="n">
-        <v>49.806</v>
+        <v>42.965</v>
       </c>
       <c r="V8" t="n">
         <v>14.358</v>
       </c>
       <c r="W8" t="n">
-        <v>-60.856</v>
+        <v>-58.077</v>
       </c>
     </row>
     <row r="9">
@@ -3111,12 +3087,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3138,7 +3114,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="N9" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="O9" t="n">
         <v>57.4</v>
@@ -3186,12 +3162,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3213,7 +3189,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="O10" t="n">
         <v>45.7</v>
@@ -3236,13 +3212,13 @@
         <v>13.513</v>
       </c>
       <c r="U10" t="n">
-        <v>19.433</v>
+        <v>17.704</v>
       </c>
       <c r="V10" t="n">
         <v>13.389</v>
       </c>
       <c r="W10" t="n">
-        <v>-17.903</v>
+        <v>-17.644</v>
       </c>
     </row>
     <row r="11">
@@ -3261,12 +3237,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3288,7 +3264,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="O11" t="n">
         <v>44.2</v>
@@ -3311,13 +3287,13 @@
         <v>13.42</v>
       </c>
       <c r="U11" t="n">
-        <v>21.246</v>
+        <v>19.558</v>
       </c>
       <c r="V11" t="n">
         <v>12.908</v>
       </c>
       <c r="W11" t="n">
-        <v>-18.794</v>
+        <v>-18.532</v>
       </c>
     </row>
     <row r="12">
@@ -3336,12 +3312,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -3363,7 +3339,7 @@
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>233.1</v>
+        <v>232.6</v>
       </c>
       <c r="O12" t="n">
         <v>41.9</v>
@@ -3386,13 +3362,13 @@
         <v>15.334</v>
       </c>
       <c r="U12" t="n">
-        <v>12.581</v>
+        <v>10.025</v>
       </c>
       <c r="V12" t="n">
         <v>55.16</v>
       </c>
       <c r="W12" t="n">
-        <v>-13.332</v>
+        <v>-13.029</v>
       </c>
     </row>
     <row r="13">
@@ -3406,57 +3382,57 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AKBNK.IS, BRSAN.IS</t>
+          <t>AKBNK.IS, ASTOR.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-07-29 | BRSAN.IS: 2026-08-13</t>
+          <t>AKBNK.IS: 2026-08-17 | ASTOR.IS: 2026-08-21</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.84922237136889</v>
+        <v>18.78300085000422</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +7.38% / +11.52% / -3.77% | BRSAN.IS: +9.92% / +12.09% / -0.05%</t>
+          <t>AKBNK.IS: +1.80% / +5.34% / -1.19% | ASTOR.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-7.945335963406319</v>
+        <v>-0.2995012191682078</v>
       </c>
       <c r="K13" t="n">
-        <v>14.1280064963272</v>
+        <v>14.63839435579952</v>
       </c>
       <c r="L13" t="n">
-        <v>31.58073864491333</v>
+        <v>28.49280591027672</v>
       </c>
       <c r="M13" t="n">
         <v>88.88888888888889</v>
       </c>
       <c r="N13" t="n">
-        <v>48.3</v>
+        <v>82</v>
       </c>
       <c r="O13" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="P13" t="n">
-        <v>6.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3467,19 +3443,19 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>11.1</v>
+        <v>13.617</v>
       </c>
       <c r="T13" t="n">
-        <v>11.1</v>
+        <v>13.617</v>
       </c>
       <c r="U13" t="n">
-        <v>36.844</v>
+        <v>41.393</v>
       </c>
       <c r="V13" t="n">
-        <v>16.263</v>
+        <v>21.215</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.741</v>
+        <v>-5.295</v>
       </c>
     </row>
     <row r="14">
@@ -3498,12 +3474,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3521,14 +3497,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.45% / +3.39% / -0.79% | BRSAN.IS: +4.50% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: -0.09% / +3.39% / -0.79% | BRSAN.IS: +5.63% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>10.72918961003173</v>
+        <v>11.53840731051064</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3560,13 +3536,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>40.48</v>
+        <v>41.202</v>
       </c>
       <c r="V14" t="n">
-        <v>31.243</v>
+        <v>32.202</v>
       </c>
       <c r="W14" t="n">
-        <v>-18.506</v>
+        <v>-17.441</v>
       </c>
     </row>
     <row r="16">
@@ -3711,12 +3687,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -3738,7 +3714,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>66.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="O18" t="n">
         <v>45.9</v>
@@ -3761,13 +3737,13 @@
         <v>31.839</v>
       </c>
       <c r="U18" t="n">
-        <v>24.207</v>
+        <v>22.994</v>
       </c>
       <c r="V18" t="n">
         <v>27.773</v>
       </c>
       <c r="W18" t="n">
-        <v>-58.018</v>
+        <v>-57.452</v>
       </c>
     </row>
     <row r="19">
@@ -3788,12 +3764,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -3815,7 +3791,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="O19" t="n">
         <v>46.7</v>
@@ -3838,13 +3814,13 @@
         <v>30.704</v>
       </c>
       <c r="U19" t="n">
-        <v>11.171</v>
+        <v>4.937</v>
       </c>
       <c r="V19" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>-49.258</v>
+        <v>-46.496</v>
       </c>
     </row>
     <row r="20">
@@ -3865,12 +3841,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -3892,7 +3868,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="O20" t="n">
         <v>46.7</v>
@@ -3915,13 +3891,13 @@
         <v>30.704</v>
       </c>
       <c r="U20" t="n">
-        <v>11.171</v>
+        <v>4.937</v>
       </c>
       <c r="V20" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-49.258</v>
+        <v>-46.496</v>
       </c>
     </row>
     <row r="21">
@@ -3942,12 +3918,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -3969,7 +3945,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>111.6</v>
+        <v>111.3</v>
       </c>
       <c r="O21" t="n">
         <v>38.4</v>
@@ -3992,13 +3968,13 @@
         <v>28.888</v>
       </c>
       <c r="U21" t="n">
-        <v>49.806</v>
+        <v>42.965</v>
       </c>
       <c r="V21" t="n">
         <v>14.358</v>
       </c>
       <c r="W21" t="n">
-        <v>-60.856</v>
+        <v>-58.077</v>
       </c>
     </row>
     <row r="22">
@@ -4019,12 +3995,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4046,7 +4022,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="O22" t="n">
         <v>44.2</v>
@@ -4069,13 +4045,13 @@
         <v>13.42</v>
       </c>
       <c r="U22" t="n">
-        <v>21.246</v>
+        <v>19.558</v>
       </c>
       <c r="V22" t="n">
         <v>12.908</v>
       </c>
       <c r="W22" t="n">
-        <v>-18.794</v>
+        <v>-18.532</v>
       </c>
     </row>
     <row r="23">
@@ -4096,12 +4072,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -4123,7 +4099,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N23" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="O23" t="n">
         <v>45.7</v>
@@ -4146,13 +4122,13 @@
         <v>13.513</v>
       </c>
       <c r="U23" t="n">
-        <v>19.433</v>
+        <v>17.704</v>
       </c>
       <c r="V23" t="n">
         <v>13.389</v>
       </c>
       <c r="W23" t="n">
-        <v>-17.903</v>
+        <v>-17.644</v>
       </c>
     </row>
     <row r="24">
@@ -4173,12 +4149,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4200,7 +4176,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="N24" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="O24" t="n">
         <v>57.4</v>
@@ -4250,12 +4226,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4273,14 +4249,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.45% / +3.39% / -0.79% | BRSAN.IS: +4.50% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: -0.09% / +3.39% / -0.79% | BRSAN.IS: +5.63% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>10.72918961003173</v>
+        <v>11.53840731051064</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4312,13 +4288,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>40.48</v>
+        <v>41.202</v>
       </c>
       <c r="V25" t="n">
-        <v>31.243</v>
+        <v>32.202</v>
       </c>
       <c r="W25" t="n">
-        <v>-18.506</v>
+        <v>-17.441</v>
       </c>
     </row>
     <row r="26">
@@ -4334,57 +4310,57 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AKBNK.IS, BRSAN.IS</t>
+          <t>AKBNK.IS, ASTOR.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-07-29 | BRSAN.IS: 2026-08-13</t>
+          <t>AKBNK.IS: 2026-08-17 | ASTOR.IS: 2026-08-21</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.84922237136889</v>
+        <v>18.78300085000422</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +7.38% / +11.52% / -3.77% | BRSAN.IS: +9.92% / +12.09% / -0.05%</t>
+          <t>AKBNK.IS: +1.80% / +5.34% / -1.19% | ASTOR.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-7.945335963406319</v>
+        <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>14.1280064963272</v>
+        <v>14.63839435579952</v>
       </c>
       <c r="L26" t="n">
-        <v>31.58073864491333</v>
+        <v>28.49280591027672</v>
       </c>
       <c r="M26" t="n">
         <v>88.88888888888889</v>
       </c>
       <c r="N26" t="n">
-        <v>48.3</v>
+        <v>82</v>
       </c>
       <c r="O26" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="P26" t="n">
-        <v>6.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4395,19 +4371,19 @@
         <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>11.1</v>
+        <v>13.617</v>
       </c>
       <c r="T26" t="n">
-        <v>11.1</v>
+        <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>36.844</v>
+        <v>41.393</v>
       </c>
       <c r="V26" t="n">
-        <v>16.263</v>
+        <v>21.215</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.741</v>
+        <v>-5.295</v>
       </c>
     </row>
     <row r="27">
@@ -4428,12 +4404,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -4455,7 +4431,7 @@
         <v>100</v>
       </c>
       <c r="N27" t="n">
-        <v>233.1</v>
+        <v>232.6</v>
       </c>
       <c r="O27" t="n">
         <v>41.9</v>
@@ -4478,13 +4454,13 @@
         <v>15.334</v>
       </c>
       <c r="U27" t="n">
-        <v>12.581</v>
+        <v>10.025</v>
       </c>
       <c r="V27" t="n">
         <v>55.16</v>
       </c>
       <c r="W27" t="n">
-        <v>-13.332</v>
+        <v>-13.029</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -582,7 +582,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -827,12 +827,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
+          <t>ALARK.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-17 | TKFEN.IS: 2026-08-17</t>
+          <t>ALARK.IS: 2026-08-21 | BRSAN.IS: 2026-08-17</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -840,14 +840,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.76% / +7.70% / -3.96% | TKFEN.IS: -1.79% / +1.16% / -3.10%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +3.26% / +7.70% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>6.801595804898586</v>
+        <v>3.790866636608925</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -856,13 +856,13 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>121.3</v>
+        <v>121.8</v>
       </c>
       <c r="O4" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="P4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -879,13 +879,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>97.91500000000001</v>
+        <v>92.336</v>
       </c>
       <c r="V4" t="n">
-        <v>53.621</v>
+        <v>49.29</v>
       </c>
       <c r="W4" t="n">
-        <v>-28.547</v>
+        <v>-34.126</v>
       </c>
     </row>
     <row r="5">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
+          <t>ALARK.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-17 | TKFEN.IS: 2026-08-17</t>
+          <t>ALARK.IS: 2026-08-21 | BRSAN.IS: 2026-08-17</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1077,14 +1077,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.76% / +7.70% / -3.96% | TKFEN.IS: -1.79% / +1.16% / -3.10%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +3.26% / +7.70% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>6.801595804898586</v>
+        <v>3.790866636608925</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1093,13 +1093,13 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>121.3</v>
+        <v>121.8</v>
       </c>
       <c r="O7" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="P7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1116,13 +1116,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>97.91500000000001</v>
+        <v>92.336</v>
       </c>
       <c r="V7" t="n">
-        <v>53.621</v>
+        <v>49.29</v>
       </c>
       <c r="W7" t="n">
-        <v>-28.547</v>
+        <v>-34.126</v>
       </c>
     </row>
     <row r="8">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1451,42 +1451,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BRSAN.IS, BSOKE.IS</t>
+          <t>BRSAN.IS, BSOKE.IS, CANTE.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-21 | BSOKE.IS: 2026-08-14</t>
+          <t>BRSAN.IS: 2026-08-21 | BSOKE.IS: 2026-08-21 | CANTE.IS: 2026-08-21</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>35.19994501826646</v>
+        <v>3.443912532931592</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: +0.98% / +1.59% / -2.17%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>11.12989926884889</v>
+        <v>-1.862436885442242</v>
       </c>
       <c r="K12" t="n">
-        <v>10.49874179376298</v>
+        <v>9.717087957064363</v>
       </c>
       <c r="L12" t="n">
-        <v>18.10083632820908</v>
+        <v>7.902828022135555</v>
       </c>
       <c r="M12" t="n">
-        <v>83.33333333333334</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="N12" t="n">
-        <v>73.3</v>
+        <v>33.7</v>
       </c>
       <c r="O12" t="n">
-        <v>51.4</v>
+        <v>44.1</v>
       </c>
       <c r="P12" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1494,22 +1494,22 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>13.39</v>
+        <v>8.954000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>13.39</v>
+        <v>8.954000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>27.404</v>
+        <v>9.967000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>19.511</v>
+        <v>9</v>
       </c>
       <c r="W12" t="n">
-        <v>-5.819</v>
+        <v>-0.768</v>
       </c>
     </row>
     <row r="13">
@@ -1551,14 +1551,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.44% / +0.46% / -0.56% | BIMAS.IS: +0.65% / +1.34% / 0.00%</t>
+          <t>ALARK.IS: +0.91% / +1.95% / -0.56% | BIMAS.IS: +1.45% / +2.02% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>8.431557803491319</v>
       </c>
       <c r="K13" t="n">
-        <v>8.333657242217463</v>
+        <v>9.011284788243579</v>
       </c>
       <c r="L13" t="n">
         <v>32.1397934777012</v>
@@ -1590,13 +1590,13 @@
         <v>20.274</v>
       </c>
       <c r="U13" t="n">
-        <v>83.06399999999999</v>
+        <v>84.209</v>
       </c>
       <c r="V13" t="n">
-        <v>44.43</v>
+        <v>45.333</v>
       </c>
       <c r="W13" t="n">
-        <v>-25.649</v>
+        <v>-24.504</v>
       </c>
     </row>
     <row r="14">
@@ -1633,7 +1633,7 @@
         <v>-6.412181273130146</v>
       </c>
       <c r="K14" t="n">
-        <v>7.872374368842938</v>
+        <v>8.158372273645975</v>
       </c>
       <c r="L14" t="n">
         <v>12.30894614425559</v>
@@ -1665,13 +1665,13 @@
         <v>11.714</v>
       </c>
       <c r="U14" t="n">
-        <v>11.845</v>
+        <v>12.141</v>
       </c>
       <c r="V14" t="n">
-        <v>21.433</v>
+        <v>21.755</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.022</v>
+        <v>-0.726</v>
       </c>
     </row>
     <row r="16">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
+          <t>ALARK.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-17 | TKFEN.IS: 2026-08-17</t>
+          <t>ALARK.IS: 2026-08-21 | BRSAN.IS: 2026-08-17</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1916,14 +1916,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +6.76% / +7.70% / -3.96% | TKFEN.IS: -1.79% / +1.16% / -3.10%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +3.26% / +7.70% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>6.801595804898586</v>
+        <v>3.790866636608925</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1932,13 +1932,13 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>121.3</v>
+        <v>121.8</v>
       </c>
       <c r="O19" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="P19" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1955,13 +1955,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>97.91500000000001</v>
+        <v>92.336</v>
       </c>
       <c r="V19" t="n">
-        <v>53.621</v>
+        <v>49.29</v>
       </c>
       <c r="W19" t="n">
-        <v>-28.547</v>
+        <v>-34.126</v>
       </c>
     </row>
     <row r="20">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2223,42 +2223,42 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BRSAN.IS, BSOKE.IS</t>
+          <t>ALARK.IS, BIMAS.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-21 | BSOKE.IS: 2026-08-14</t>
+          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>35.19994501826646</v>
+        <v>34.62553795007752</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: +0.98% / +1.59% / -2.17%</t>
+          <t>ALARK.IS: +0.91% / +1.95% / -0.56% | BIMAS.IS: +1.45% / +2.02% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>11.12989926884889</v>
+        <v>8.431557803491319</v>
       </c>
       <c r="K23" t="n">
-        <v>10.49874179376298</v>
+        <v>9.011284788243579</v>
       </c>
       <c r="L23" t="n">
-        <v>18.10083632820908</v>
+        <v>32.1397934777012</v>
       </c>
       <c r="M23" t="n">
-        <v>83.33333333333334</v>
+        <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>73.3</v>
+        <v>233.2</v>
       </c>
       <c r="O23" t="n">
-        <v>51.4</v>
+        <v>49.7</v>
       </c>
       <c r="P23" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2269,19 +2269,19 @@
         <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>13.39</v>
+        <v>20.274</v>
       </c>
       <c r="T23" t="n">
-        <v>13.39</v>
+        <v>20.274</v>
       </c>
       <c r="U23" t="n">
-        <v>27.404</v>
+        <v>84.209</v>
       </c>
       <c r="V23" t="n">
-        <v>19.511</v>
+        <v>45.333</v>
       </c>
       <c r="W23" t="n">
-        <v>-5.819</v>
+        <v>-24.504</v>
       </c>
     </row>
     <row r="24">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2310,67 +2310,55 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ALARK.IS, BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>34.62553795007752</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>ALARK.IS: +0.44% / +0.46% / -0.56% | BIMAS.IS: +0.65% / +1.34% / 0.00%</t>
-        </is>
-      </c>
+        <v>12.43146471706449</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>8.431557803491319</v>
+        <v>-6.412181273130146</v>
       </c>
       <c r="K24" t="n">
-        <v>8.333657242217463</v>
+        <v>8.158372273645975</v>
       </c>
       <c r="L24" t="n">
-        <v>32.1397934777012</v>
+        <v>12.30894614425559</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>233.2</v>
+        <v>140.1</v>
       </c>
       <c r="O24" t="n">
-        <v>49.7</v>
+        <v>48.1</v>
       </c>
       <c r="P24" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>20.274</v>
+        <v>12.004</v>
       </c>
       <c r="T24" t="n">
-        <v>20.274</v>
+        <v>11.714</v>
       </c>
       <c r="U24" t="n">
-        <v>83.06399999999999</v>
+        <v>12.141</v>
       </c>
       <c r="V24" t="n">
-        <v>44.43</v>
+        <v>21.755</v>
       </c>
       <c r="W24" t="n">
-        <v>-25.649</v>
+        <v>-0.726</v>
       </c>
     </row>
     <row r="25">
@@ -2381,12 +2369,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2399,55 +2387,67 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, BSOKE.IS, CANTE.IS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-21 | BSOKE.IS: 2026-08-21 | CANTE.IS: 2026-08-21</t>
+        </is>
+      </c>
       <c r="H25" t="n">
-        <v>12.43146471706449</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>3.443912532931592</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J25" t="n">
-        <v>-6.412181273130146</v>
+        <v>-1.862436885442242</v>
       </c>
       <c r="K25" t="n">
-        <v>7.872374368842938</v>
+        <v>9.717087957064363</v>
       </c>
       <c r="L25" t="n">
-        <v>12.30894614425559</v>
+        <v>7.902828022135555</v>
       </c>
       <c r="M25" t="n">
-        <v>100</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="N25" t="n">
-        <v>140.1</v>
+        <v>33.7</v>
       </c>
       <c r="O25" t="n">
-        <v>48.1</v>
+        <v>44.1</v>
       </c>
       <c r="P25" t="n">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S25" t="n">
-        <v>12.004</v>
+        <v>8.954000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>11.714</v>
+        <v>8.954000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>11.845</v>
+        <v>9.967000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>21.433</v>
+        <v>9</v>
       </c>
       <c r="W25" t="n">
-        <v>-1.022</v>
+        <v>-0.768</v>
       </c>
     </row>
   </sheetData>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3397,42 +3397,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AKBNK.IS, ASTOR.IS</t>
+          <t>AKBNK.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-17 | ASTOR.IS: 2026-08-21</t>
+          <t>AKBNK.IS: 2026-07-29 | BRSAN.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>18.78300085000422</v>
+        <v>5.84922237136889</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.80% / +5.34% / -1.19% | ASTOR.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AKBNK.IS: +9.16% / +11.52% / -3.77% | BRSAN.IS: +7.46% / +12.09% / -0.05%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-0.2995012191682078</v>
+        <v>-7.945335963406319</v>
       </c>
       <c r="K13" t="n">
-        <v>14.63839435579952</v>
+        <v>13.94106897269149</v>
       </c>
       <c r="L13" t="n">
-        <v>28.49280591027672</v>
+        <v>31.58073864491333</v>
       </c>
       <c r="M13" t="n">
         <v>88.88888888888889</v>
       </c>
       <c r="N13" t="n">
-        <v>82</v>
+        <v>48.2</v>
       </c>
       <c r="O13" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="P13" t="n">
-        <v>3.6</v>
+        <v>6.1</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3443,19 +3443,19 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>13.617</v>
+        <v>11.1</v>
       </c>
       <c r="T13" t="n">
-        <v>13.617</v>
+        <v>11.1</v>
       </c>
       <c r="U13" t="n">
-        <v>41.393</v>
+        <v>36.468</v>
       </c>
       <c r="V13" t="n">
-        <v>21.215</v>
+        <v>16.072</v>
       </c>
       <c r="W13" t="n">
-        <v>-5.295</v>
+        <v>-4.959</v>
       </c>
     </row>
     <row r="14">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AKBNK.IS, BRSAN.IS</t>
+          <t>AKBNK.IS, ALARK.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-19 | BRSAN.IS: 2026-08-19</t>
+          <t>AKBNK.IS: 2026-08-19 | ALARK.IS: 2026-08-21</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -3497,14 +3497,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.09% / +3.39% / -0.79% | BRSAN.IS: +5.63% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: +1.20% / +3.39% / -0.79% | ALARK.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>11.53840731051064</v>
+        <v>10.33793366147944</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3513,13 +3513,13 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N14" t="n">
-        <v>38.3</v>
+        <v>38.8</v>
       </c>
       <c r="O14" t="n">
-        <v>55.8</v>
+        <v>56.4</v>
       </c>
       <c r="P14" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3536,13 +3536,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>41.202</v>
+        <v>39.682</v>
       </c>
       <c r="V14" t="n">
-        <v>32.202</v>
+        <v>30.779</v>
       </c>
       <c r="W14" t="n">
-        <v>-17.441</v>
+        <v>-18.961</v>
       </c>
     </row>
     <row r="16">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AKBNK.IS, BRSAN.IS</t>
+          <t>AKBNK.IS, ALARK.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-19 | BRSAN.IS: 2026-08-19</t>
+          <t>AKBNK.IS: 2026-08-19 | ALARK.IS: 2026-08-21</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -4249,14 +4249,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.09% / +3.39% / -0.79% | BRSAN.IS: +5.63% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: +1.20% / +3.39% / -0.79% | ALARK.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>11.53840731051064</v>
+        <v>10.33793366147944</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4265,13 +4265,13 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N25" t="n">
-        <v>38.3</v>
+        <v>38.8</v>
       </c>
       <c r="O25" t="n">
-        <v>55.8</v>
+        <v>56.4</v>
       </c>
       <c r="P25" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4288,13 +4288,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>41.202</v>
+        <v>39.682</v>
       </c>
       <c r="V25" t="n">
-        <v>32.202</v>
+        <v>30.779</v>
       </c>
       <c r="W25" t="n">
-        <v>-17.441</v>
+        <v>-18.961</v>
       </c>
     </row>
     <row r="26">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4325,42 +4325,42 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AKBNK.IS, ASTOR.IS</t>
+          <t>AKBNK.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-17 | ASTOR.IS: 2026-08-21</t>
+          <t>AKBNK.IS: 2026-07-29 | BRSAN.IS: 2026-08-13</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18.78300085000422</v>
+        <v>5.84922237136889</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.80% / +5.34% / -1.19% | ASTOR.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AKBNK.IS: +9.16% / +11.52% / -3.77% | BRSAN.IS: +7.46% / +12.09% / -0.05%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-0.2995012191682078</v>
+        <v>-7.945335963406319</v>
       </c>
       <c r="K26" t="n">
-        <v>14.63839435579952</v>
+        <v>13.94106897269149</v>
       </c>
       <c r="L26" t="n">
-        <v>28.49280591027672</v>
+        <v>31.58073864491333</v>
       </c>
       <c r="M26" t="n">
         <v>88.88888888888889</v>
       </c>
       <c r="N26" t="n">
-        <v>82</v>
+        <v>48.2</v>
       </c>
       <c r="O26" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="P26" t="n">
-        <v>3.6</v>
+        <v>6.1</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4371,19 +4371,19 @@
         <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>13.617</v>
+        <v>11.1</v>
       </c>
       <c r="T26" t="n">
-        <v>13.617</v>
+        <v>11.1</v>
       </c>
       <c r="U26" t="n">
-        <v>41.393</v>
+        <v>36.468</v>
       </c>
       <c r="V26" t="n">
-        <v>21.215</v>
+        <v>16.072</v>
       </c>
       <c r="W26" t="n">
-        <v>-5.295</v>
+        <v>-4.959</v>
       </c>
     </row>
     <row r="27">

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -840,14 +840,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +3.26% / +7.70% / -3.96%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +4.63% / +7.70% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>3.790866636608925</v>
+        <v>4.505706545842991</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -879,13 +879,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>92.336</v>
+        <v>93.66</v>
       </c>
       <c r="V4" t="n">
-        <v>49.29</v>
+        <v>50.319</v>
       </c>
       <c r="W4" t="n">
-        <v>-34.126</v>
+        <v>-32.801</v>
       </c>
     </row>
     <row r="5">
@@ -1077,14 +1077,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +3.26% / +7.70% / -3.96%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +4.63% / +7.70% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>3.790866636608925</v>
+        <v>4.505706545842991</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1116,13 +1116,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>92.336</v>
+        <v>93.66</v>
       </c>
       <c r="V7" t="n">
-        <v>49.29</v>
+        <v>50.319</v>
       </c>
       <c r="W7" t="n">
-        <v>-34.126</v>
+        <v>-32.801</v>
       </c>
     </row>
     <row r="8">
@@ -1551,14 +1551,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.91% / +1.95% / -0.56% | BIMAS.IS: +1.45% / +2.02% / 0.00%</t>
+          <t>ALARK.IS: +0.26% / +1.95% / -1.58% | BIMAS.IS: +2.06% / +2.32% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>8.431557803491319</v>
       </c>
       <c r="K13" t="n">
-        <v>9.011284788243579</v>
+        <v>8.991013734510123</v>
       </c>
       <c r="L13" t="n">
         <v>32.1397934777012</v>
@@ -1590,13 +1590,13 @@
         <v>20.274</v>
       </c>
       <c r="U13" t="n">
-        <v>84.209</v>
+        <v>84.175</v>
       </c>
       <c r="V13" t="n">
-        <v>45.333</v>
+        <v>45.306</v>
       </c>
       <c r="W13" t="n">
-        <v>-24.504</v>
+        <v>-24.539</v>
       </c>
     </row>
     <row r="14">
@@ -1633,7 +1633,7 @@
         <v>-6.412181273130146</v>
       </c>
       <c r="K14" t="n">
-        <v>8.158372273645975</v>
+        <v>8.378370661955991</v>
       </c>
       <c r="L14" t="n">
         <v>12.30894614425559</v>
@@ -1665,13 +1665,13 @@
         <v>11.714</v>
       </c>
       <c r="U14" t="n">
-        <v>12.141</v>
+        <v>12.369</v>
       </c>
       <c r="V14" t="n">
-        <v>21.755</v>
+        <v>22.002</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.726</v>
+        <v>-0.498</v>
       </c>
     </row>
     <row r="16">
@@ -1916,14 +1916,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +3.26% / +7.70% / -3.96%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +4.63% / +7.70% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>3.790866636608925</v>
+        <v>4.505706545842991</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1955,13 +1955,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>92.336</v>
+        <v>93.66</v>
       </c>
       <c r="V19" t="n">
-        <v>49.29</v>
+        <v>50.319</v>
       </c>
       <c r="W19" t="n">
-        <v>-34.126</v>
+        <v>-32.801</v>
       </c>
     </row>
     <row r="20">
@@ -2236,14 +2236,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.91% / +1.95% / -0.56% | BIMAS.IS: +1.45% / +2.02% / 0.00%</t>
+          <t>ALARK.IS: +0.26% / +1.95% / -1.58% | BIMAS.IS: +2.06% / +2.32% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>8.431557803491319</v>
       </c>
       <c r="K23" t="n">
-        <v>9.011284788243579</v>
+        <v>8.991013734510123</v>
       </c>
       <c r="L23" t="n">
         <v>32.1397934777012</v>
@@ -2275,13 +2275,13 @@
         <v>20.274</v>
       </c>
       <c r="U23" t="n">
-        <v>84.209</v>
+        <v>84.175</v>
       </c>
       <c r="V23" t="n">
-        <v>45.333</v>
+        <v>45.306</v>
       </c>
       <c r="W23" t="n">
-        <v>-24.504</v>
+        <v>-24.539</v>
       </c>
     </row>
     <row r="24">
@@ -2320,7 +2320,7 @@
         <v>-6.412181273130146</v>
       </c>
       <c r="K24" t="n">
-        <v>8.158372273645975</v>
+        <v>8.378370661955991</v>
       </c>
       <c r="L24" t="n">
         <v>12.30894614425559</v>
@@ -2352,13 +2352,13 @@
         <v>11.714</v>
       </c>
       <c r="U24" t="n">
-        <v>12.141</v>
+        <v>12.369</v>
       </c>
       <c r="V24" t="n">
-        <v>21.755</v>
+        <v>22.002</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.726</v>
+        <v>-0.498</v>
       </c>
     </row>
     <row r="25">
@@ -3410,14 +3410,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +9.16% / +11.52% / -3.77% | BRSAN.IS: +7.46% / +12.09% / -0.05%</t>
+          <t>AKBNK.IS: +8.31% / +11.52% / -3.77% | BRSAN.IS: +8.89% / +12.09% / -0.05%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-7.945335963406319</v>
       </c>
       <c r="K13" t="n">
-        <v>13.94106897269149</v>
+        <v>14.09972638365291</v>
       </c>
       <c r="L13" t="n">
         <v>31.58073864491333</v>
@@ -3449,13 +3449,13 @@
         <v>11.1</v>
       </c>
       <c r="U13" t="n">
-        <v>36.468</v>
+        <v>36.658</v>
       </c>
       <c r="V13" t="n">
-        <v>16.072</v>
+        <v>16.234</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.959</v>
+        <v>-4.769</v>
       </c>
     </row>
     <row r="14">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AKBNK.IS, ALARK.IS</t>
+          <t>AKBNK.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-19 | ALARK.IS: 2026-08-21</t>
+          <t>AKBNK.IS: 2026-08-19 | BRSAN.IS: 2026-08-19</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -3497,14 +3497,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.20% / +3.39% / -0.79% | ALARK.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AKBNK.IS: +0.41% / +3.39% / -0.79% | BRSAN.IS: +3.52% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>10.33793366147944</v>
+        <v>10.6664345623984</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3513,13 +3513,13 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N14" t="n">
-        <v>38.8</v>
+        <v>38.3</v>
       </c>
       <c r="O14" t="n">
-        <v>56.4</v>
+        <v>57.1</v>
       </c>
       <c r="P14" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3536,13 +3536,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>39.682</v>
+        <v>40.098</v>
       </c>
       <c r="V14" t="n">
-        <v>30.779</v>
+        <v>31.168</v>
       </c>
       <c r="W14" t="n">
-        <v>-18.961</v>
+        <v>-18.545</v>
       </c>
     </row>
     <row r="16">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AKBNK.IS, ALARK.IS</t>
+          <t>AKBNK.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-19 | ALARK.IS: 2026-08-21</t>
+          <t>AKBNK.IS: 2026-08-19 | BRSAN.IS: 2026-08-19</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -4249,14 +4249,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.20% / +3.39% / -0.79% | ALARK.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AKBNK.IS: +0.41% / +3.39% / -0.79% | BRSAN.IS: +3.52% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>10.33793366147944</v>
+        <v>10.6664345623984</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4265,13 +4265,13 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N25" t="n">
-        <v>38.8</v>
+        <v>38.3</v>
       </c>
       <c r="O25" t="n">
-        <v>56.4</v>
+        <v>57.1</v>
       </c>
       <c r="P25" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4288,13 +4288,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>39.682</v>
+        <v>40.098</v>
       </c>
       <c r="V25" t="n">
-        <v>30.779</v>
+        <v>31.168</v>
       </c>
       <c r="W25" t="n">
-        <v>-18.961</v>
+        <v>-18.545</v>
       </c>
     </row>
     <row r="26">
@@ -4338,14 +4338,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +9.16% / +11.52% / -3.77% | BRSAN.IS: +7.46% / +12.09% / -0.05%</t>
+          <t>AKBNK.IS: +8.31% / +11.52% / -3.77% | BRSAN.IS: +8.89% / +12.09% / -0.05%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-7.945335963406319</v>
       </c>
       <c r="K26" t="n">
-        <v>13.94106897269149</v>
+        <v>14.09972638365291</v>
       </c>
       <c r="L26" t="n">
         <v>31.58073864491333</v>
@@ -4377,13 +4377,13 @@
         <v>11.1</v>
       </c>
       <c r="U26" t="n">
-        <v>36.468</v>
+        <v>36.658</v>
       </c>
       <c r="V26" t="n">
-        <v>16.072</v>
+        <v>16.234</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.959</v>
+        <v>-4.769</v>
       </c>
     </row>
     <row r="27">

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -840,14 +840,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +4.63% / +7.70% / -3.96%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +5.24% / +7.70% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>4.505706545842991</v>
+        <v>4.823413172169233</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -879,13 +879,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>93.66</v>
+        <v>94.249</v>
       </c>
       <c r="V4" t="n">
-        <v>50.319</v>
+        <v>50.776</v>
       </c>
       <c r="W4" t="n">
-        <v>-32.801</v>
+        <v>-32.213</v>
       </c>
     </row>
     <row r="5">
@@ -1077,14 +1077,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +4.63% / +7.70% / -3.96%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +5.24% / +7.70% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>4.505706545842991</v>
+        <v>4.823413172169233</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1116,13 +1116,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>93.66</v>
+        <v>94.249</v>
       </c>
       <c r="V7" t="n">
-        <v>50.319</v>
+        <v>50.776</v>
       </c>
       <c r="W7" t="n">
-        <v>-32.801</v>
+        <v>-32.213</v>
       </c>
     </row>
     <row r="8">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1536,67 +1536,55 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ALARK.IS, BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>34.62553795007752</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ALARK.IS: +0.26% / +1.95% / -1.58% | BIMAS.IS: +2.06% / +2.32% / 0.00%</t>
-        </is>
-      </c>
+        <v>12.43146471706449</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>8.431557803491319</v>
+        <v>-6.412181273130146</v>
       </c>
       <c r="K13" t="n">
-        <v>8.991013734510123</v>
+        <v>8.290371306631972</v>
       </c>
       <c r="L13" t="n">
-        <v>32.1397934777012</v>
+        <v>12.30894614425559</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>233.2</v>
+        <v>140.1</v>
       </c>
       <c r="O13" t="n">
-        <v>49.7</v>
+        <v>48.1</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>20.274</v>
+        <v>12.004</v>
       </c>
       <c r="T13" t="n">
-        <v>20.274</v>
+        <v>11.714</v>
       </c>
       <c r="U13" t="n">
-        <v>84.175</v>
+        <v>12.278</v>
       </c>
       <c r="V13" t="n">
-        <v>45.306</v>
+        <v>21.903</v>
       </c>
       <c r="W13" t="n">
-        <v>-24.539</v>
+        <v>-0.589</v>
       </c>
     </row>
     <row r="14">
@@ -1610,7 +1598,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1623,55 +1611,67 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ALARK.IS, BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
+        </is>
+      </c>
       <c r="H14" t="n">
-        <v>12.43146471706449</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>34.62553795007752</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -1.50% / +1.95% / -1.58% | BIMAS.IS: +1.81% / +2.32% / 0.00%</t>
+        </is>
+      </c>
       <c r="J14" t="n">
-        <v>-6.412181273130146</v>
+        <v>8.431557803491319</v>
       </c>
       <c r="K14" t="n">
-        <v>8.378370661955991</v>
+        <v>7.910706034300108</v>
       </c>
       <c r="L14" t="n">
-        <v>12.30894614425559</v>
+        <v>32.1397934777012</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>140.1</v>
+        <v>233.2</v>
       </c>
       <c r="O14" t="n">
-        <v>48.1</v>
+        <v>49.5</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>12.004</v>
+        <v>20.274</v>
       </c>
       <c r="T14" t="n">
-        <v>11.714</v>
+        <v>20.274</v>
       </c>
       <c r="U14" t="n">
-        <v>12.369</v>
+        <v>82.349</v>
       </c>
       <c r="V14" t="n">
-        <v>22.002</v>
+        <v>43.866</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.498</v>
+        <v>-26.364</v>
       </c>
     </row>
     <row r="16">
@@ -1916,14 +1916,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +4.63% / +7.70% / -3.96%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +5.24% / +7.70% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>4.505706545842991</v>
+        <v>4.823413172169233</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1955,13 +1955,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>93.66</v>
+        <v>94.249</v>
       </c>
       <c r="V19" t="n">
-        <v>50.319</v>
+        <v>50.776</v>
       </c>
       <c r="W19" t="n">
-        <v>-32.801</v>
+        <v>-32.213</v>
       </c>
     </row>
     <row r="20">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2236,14 +2236,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.26% / +1.95% / -1.58% | BIMAS.IS: +2.06% / +2.32% / 0.00%</t>
+          <t>ALARK.IS: -1.50% / +1.95% / -1.58% | BIMAS.IS: +1.81% / +2.32% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>8.431557803491319</v>
       </c>
       <c r="K23" t="n">
-        <v>8.991013734510123</v>
+        <v>7.910706034300108</v>
       </c>
       <c r="L23" t="n">
         <v>32.1397934777012</v>
@@ -2255,7 +2255,7 @@
         <v>233.2</v>
       </c>
       <c r="O23" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="P23" t="n">
         <v>3.1</v>
@@ -2275,13 +2275,13 @@
         <v>20.274</v>
       </c>
       <c r="U23" t="n">
-        <v>84.175</v>
+        <v>82.349</v>
       </c>
       <c r="V23" t="n">
-        <v>45.306</v>
+        <v>43.866</v>
       </c>
       <c r="W23" t="n">
-        <v>-24.539</v>
+        <v>-26.364</v>
       </c>
     </row>
     <row r="24">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2320,7 +2320,7 @@
         <v>-6.412181273130146</v>
       </c>
       <c r="K24" t="n">
-        <v>8.378370661955991</v>
+        <v>8.290371306631972</v>
       </c>
       <c r="L24" t="n">
         <v>12.30894614425559</v>
@@ -2352,13 +2352,13 @@
         <v>11.714</v>
       </c>
       <c r="U24" t="n">
-        <v>12.369</v>
+        <v>12.278</v>
       </c>
       <c r="V24" t="n">
-        <v>22.002</v>
+        <v>21.903</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.498</v>
+        <v>-0.589</v>
       </c>
     </row>
     <row r="25">
@@ -3410,14 +3410,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +8.31% / +11.52% / -3.77% | BRSAN.IS: +8.89% / +12.09% / -0.05%</t>
+          <t>AKBNK.IS: +8.31% / +11.52% / -3.77% | BRSAN.IS: +9.53% / +12.09% / -0.05%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-7.945335963406319</v>
       </c>
       <c r="K13" t="n">
-        <v>14.09972638365291</v>
+        <v>14.27428313833436</v>
       </c>
       <c r="L13" t="n">
         <v>31.58073864491333</v>
@@ -3449,13 +3449,13 @@
         <v>11.1</v>
       </c>
       <c r="U13" t="n">
-        <v>36.658</v>
+        <v>36.867</v>
       </c>
       <c r="V13" t="n">
-        <v>16.234</v>
+        <v>16.412</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.769</v>
+        <v>-4.56</v>
       </c>
     </row>
     <row r="14">
@@ -3497,14 +3497,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.41% / +3.39% / -0.79% | BRSAN.IS: +3.52% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: +0.41% / +3.39% / -0.79% | BRSAN.IS: +4.13% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>10.6664345623984</v>
+        <v>10.99376131182925</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3536,13 +3536,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>40.098</v>
+        <v>40.512</v>
       </c>
       <c r="V14" t="n">
-        <v>31.168</v>
+        <v>31.556</v>
       </c>
       <c r="W14" t="n">
-        <v>-18.545</v>
+        <v>-18.131</v>
       </c>
     </row>
     <row r="16">
@@ -4249,14 +4249,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.41% / +3.39% / -0.79% | BRSAN.IS: +3.52% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: +0.41% / +3.39% / -0.79% | BRSAN.IS: +4.13% / +6.56% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>10.6664345623984</v>
+        <v>10.99376131182925</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4288,13 +4288,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>40.098</v>
+        <v>40.512</v>
       </c>
       <c r="V25" t="n">
-        <v>31.168</v>
+        <v>31.556</v>
       </c>
       <c r="W25" t="n">
-        <v>-18.545</v>
+        <v>-18.131</v>
       </c>
     </row>
     <row r="26">
@@ -4338,14 +4338,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +8.31% / +11.52% / -3.77% | BRSAN.IS: +8.89% / +12.09% / -0.05%</t>
+          <t>AKBNK.IS: +8.31% / +11.52% / -3.77% | BRSAN.IS: +9.53% / +12.09% / -0.05%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-7.945335963406319</v>
       </c>
       <c r="K26" t="n">
-        <v>14.09972638365291</v>
+        <v>14.27428313833436</v>
       </c>
       <c r="L26" t="n">
         <v>31.58073864491333</v>
@@ -4377,13 +4377,13 @@
         <v>11.1</v>
       </c>
       <c r="U26" t="n">
-        <v>36.658</v>
+        <v>36.867</v>
       </c>
       <c r="V26" t="n">
-        <v>16.234</v>
+        <v>16.412</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.769</v>
+        <v>-4.56</v>
       </c>
     </row>
     <row r="27">

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -57,7 +54,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -65,20 +62,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -582,7 +573,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -742,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -769,7 +760,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>117.8</v>
+        <v>117.6</v>
       </c>
       <c r="O3" t="n">
         <v>39.9</v>
@@ -792,13 +783,13 @@
         <v>28.567</v>
       </c>
       <c r="U3" t="n">
-        <v>80.15300000000001</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>41.769</v>
       </c>
       <c r="W3" t="n">
-        <v>-72.045</v>
+        <v>-72.512</v>
       </c>
     </row>
     <row r="4">
@@ -817,12 +808,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -840,14 +831,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +5.24% / +7.70% / -3.96%</t>
+          <t>ALARK.IS: -2.18% / +1.41% / -2.35% | BRSAN.IS: +14.76% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>4.823413172169233</v>
+        <v>8.70596533744019</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -856,7 +847,7 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>121.8</v>
+        <v>121.6</v>
       </c>
       <c r="O4" t="n">
         <v>43.1</v>
@@ -879,13 +870,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>94.249</v>
+        <v>102.114</v>
       </c>
       <c r="V4" t="n">
-        <v>50.776</v>
+        <v>56.36</v>
       </c>
       <c r="W4" t="n">
-        <v>-32.213</v>
+        <v>-25.101</v>
       </c>
     </row>
     <row r="5">
@@ -904,12 +895,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -931,7 +922,7 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>94.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>37.4</v>
@@ -954,13 +945,13 @@
         <v>35.687</v>
       </c>
       <c r="U5" t="n">
-        <v>27.118</v>
+        <v>26.268</v>
       </c>
       <c r="V5" t="n">
         <v>12.323</v>
       </c>
       <c r="W5" t="n">
-        <v>-70.538</v>
+        <v>-70.066</v>
       </c>
     </row>
     <row r="6">
@@ -979,12 +970,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -1006,7 +997,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>117.8</v>
+        <v>117.6</v>
       </c>
       <c r="O6" t="n">
         <v>39.9</v>
@@ -1029,13 +1020,13 @@
         <v>28.567</v>
       </c>
       <c r="U6" t="n">
-        <v>80.15300000000001</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>41.769</v>
       </c>
       <c r="W6" t="n">
-        <v>-72.045</v>
+        <v>-72.512</v>
       </c>
     </row>
     <row r="7">
@@ -1054,12 +1045,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1077,14 +1068,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +5.24% / +7.70% / -3.96%</t>
+          <t>ALARK.IS: -2.18% / +1.41% / -2.35% | BRSAN.IS: +14.76% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>4.823413172169233</v>
+        <v>8.70596533744019</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1093,7 +1084,7 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>121.8</v>
+        <v>121.6</v>
       </c>
       <c r="O7" t="n">
         <v>43.1</v>
@@ -1116,13 +1107,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>94.249</v>
+        <v>102.114</v>
       </c>
       <c r="V7" t="n">
-        <v>50.776</v>
+        <v>56.36</v>
       </c>
       <c r="W7" t="n">
-        <v>-32.213</v>
+        <v>-25.101</v>
       </c>
     </row>
     <row r="8">
@@ -1141,12 +1132,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -1168,7 +1159,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N8" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="O8" t="n">
         <v>51.1</v>
@@ -1191,13 +1182,13 @@
         <v>29.993</v>
       </c>
       <c r="U8" t="n">
-        <v>7.224</v>
+        <v>6.823</v>
       </c>
       <c r="V8" t="n">
         <v>-6.769</v>
       </c>
       <c r="W8" t="n">
-        <v>-45.437</v>
+        <v>-45.267</v>
       </c>
     </row>
     <row r="9">
@@ -1216,12 +1207,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1243,7 +1234,7 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>117.8</v>
+        <v>117.6</v>
       </c>
       <c r="O9" t="n">
         <v>39.9</v>
@@ -1266,13 +1257,13 @@
         <v>28.567</v>
       </c>
       <c r="U9" t="n">
-        <v>80.15300000000001</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>41.769</v>
       </c>
       <c r="W9" t="n">
-        <v>-72.045</v>
+        <v>-72.512</v>
       </c>
     </row>
     <row r="10">
@@ -1291,12 +1282,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1318,7 +1309,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="O10" t="n">
         <v>51.1</v>
@@ -1341,13 +1332,13 @@
         <v>29.993</v>
       </c>
       <c r="U10" t="n">
-        <v>7.224</v>
+        <v>6.823</v>
       </c>
       <c r="V10" t="n">
         <v>-6.769</v>
       </c>
       <c r="W10" t="n">
-        <v>-45.437</v>
+        <v>-45.267</v>
       </c>
     </row>
     <row r="11">
@@ -1366,12 +1357,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1393,7 +1384,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="O11" t="n">
         <v>38.4</v>
@@ -1416,13 +1407,13 @@
         <v>29.287</v>
       </c>
       <c r="U11" t="n">
-        <v>39.263</v>
+        <v>40.723</v>
       </c>
       <c r="V11" t="n">
         <v>14.374</v>
       </c>
       <c r="W11" t="n">
-        <v>-49.498</v>
+        <v>-50.017</v>
       </c>
     </row>
     <row r="12">
@@ -1441,12 +1432,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1464,14 +1455,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +9.03% / +9.99% / 0.00% | BSOKE.IS: -0.26% / +1.85% / -1.13% | CANTE.IS: +1.63% / +2.48% / 0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K12" t="n">
-        <v>9.717087957064363</v>
+        <v>13.54508918924444</v>
       </c>
       <c r="L12" t="n">
         <v>7.902828022135555</v>
@@ -1480,13 +1471,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="N12" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="O12" t="n">
-        <v>44.1</v>
+        <v>47.1</v>
       </c>
       <c r="P12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1503,13 +1494,13 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>9.967000000000001</v>
+        <v>13.804</v>
       </c>
       <c r="V12" t="n">
-        <v>9</v>
+        <v>12.803</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1523,68 +1514,80 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
+        </is>
+      </c>
       <c r="H13" t="n">
-        <v>12.43146471706449</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>22.83095636113686</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -2.18% / +1.41% / -2.35% | ASTOR.IS: +17.85% / +21.93% / 0.00% | BIMAS.IS: +1.27% / +3.13% / -0.86% | BRSAN.IS: +44.36% / +45.64% / -0.48% | CANTE.IS: +1.63% / +2.48% / -0.83%</t>
+        </is>
+      </c>
       <c r="J13" t="n">
-        <v>-6.412181273130146</v>
+        <v>-5.037231846603429</v>
       </c>
       <c r="K13" t="n">
-        <v>8.290371306631972</v>
+        <v>8.749458804957477</v>
       </c>
       <c r="L13" t="n">
-        <v>12.30894614425559</v>
+        <v>23.4189376077676</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>140.1</v>
+        <v>181.8</v>
       </c>
       <c r="O13" t="n">
-        <v>48.1</v>
+        <v>45.7</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S13" t="n">
-        <v>12.004</v>
+        <v>22.513</v>
       </c>
       <c r="T13" t="n">
-        <v>11.714</v>
+        <v>22.513</v>
       </c>
       <c r="U13" t="n">
-        <v>12.278</v>
+        <v>53.688</v>
       </c>
       <c r="V13" t="n">
-        <v>21.903</v>
+        <v>44.094</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.589</v>
+        <v>-2.646</v>
       </c>
     </row>
     <row r="14">
@@ -1598,57 +1601,57 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ALARK.IS, BIMAS.IS</t>
+          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
+          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>34.62553795007752</v>
+        <v>22.83095636113686</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.50% / +1.95% / -1.58% | BIMAS.IS: +1.81% / +2.32% / 0.00%</t>
+          <t>ALARK.IS: -2.18% / +1.41% / -2.35% | ASTOR.IS: +17.85% / +21.93% / 0.00% | BIMAS.IS: +1.27% / +3.13% / -0.86% | BRSAN.IS: +44.36% / +45.64% / -0.48% | CANTE.IS: +1.63% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8.431557803491319</v>
+        <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>7.910706034300108</v>
+        <v>8.749458804957477</v>
       </c>
       <c r="L14" t="n">
-        <v>32.1397934777012</v>
+        <v>23.4189376077676</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>233.2</v>
+        <v>181.8</v>
       </c>
       <c r="O14" t="n">
-        <v>49.5</v>
+        <v>45.7</v>
       </c>
       <c r="P14" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1656,22 +1659,22 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S14" t="n">
-        <v>20.274</v>
+        <v>22.513</v>
       </c>
       <c r="T14" t="n">
-        <v>20.274</v>
+        <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>82.349</v>
+        <v>53.688</v>
       </c>
       <c r="V14" t="n">
-        <v>43.866</v>
+        <v>44.094</v>
       </c>
       <c r="W14" t="n">
-        <v>-26.364</v>
+        <v>-2.646</v>
       </c>
     </row>
     <row r="16">
@@ -1816,12 +1819,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1843,7 +1846,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>117.8</v>
+        <v>117.6</v>
       </c>
       <c r="O18" t="n">
         <v>39.9</v>
@@ -1866,13 +1869,13 @@
         <v>28.567</v>
       </c>
       <c r="U18" t="n">
-        <v>80.15300000000001</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>41.769</v>
       </c>
       <c r="W18" t="n">
-        <v>-72.045</v>
+        <v>-72.512</v>
       </c>
     </row>
     <row r="19">
@@ -1893,12 +1896,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1916,14 +1919,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +5.24% / +7.70% / -3.96%</t>
+          <t>ALARK.IS: -2.18% / +1.41% / -2.35% | BRSAN.IS: +14.76% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>4.823413172169233</v>
+        <v>8.70596533744019</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1932,7 +1935,7 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>121.8</v>
+        <v>121.6</v>
       </c>
       <c r="O19" t="n">
         <v>43.1</v>
@@ -1955,13 +1958,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>94.249</v>
+        <v>102.114</v>
       </c>
       <c r="V19" t="n">
-        <v>50.776</v>
+        <v>56.36</v>
       </c>
       <c r="W19" t="n">
-        <v>-32.213</v>
+        <v>-25.101</v>
       </c>
     </row>
     <row r="20">
@@ -1982,12 +1985,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2009,7 +2012,7 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>94.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>37.4</v>
@@ -2032,13 +2035,13 @@
         <v>35.687</v>
       </c>
       <c r="U20" t="n">
-        <v>27.118</v>
+        <v>26.268</v>
       </c>
       <c r="V20" t="n">
         <v>12.323</v>
       </c>
       <c r="W20" t="n">
-        <v>-70.538</v>
+        <v>-70.066</v>
       </c>
     </row>
     <row r="21">
@@ -2059,12 +2062,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2086,7 +2089,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N21" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="O21" t="n">
         <v>51.1</v>
@@ -2109,13 +2112,13 @@
         <v>29.993</v>
       </c>
       <c r="U21" t="n">
-        <v>7.224</v>
+        <v>6.823</v>
       </c>
       <c r="V21" t="n">
         <v>-6.769</v>
       </c>
       <c r="W21" t="n">
-        <v>-45.437</v>
+        <v>-45.267</v>
       </c>
     </row>
     <row r="22">
@@ -2136,12 +2139,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2163,7 +2166,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="O22" t="n">
         <v>38.4</v>
@@ -2186,13 +2189,13 @@
         <v>29.287</v>
       </c>
       <c r="U22" t="n">
-        <v>39.263</v>
+        <v>40.723</v>
       </c>
       <c r="V22" t="n">
         <v>14.374</v>
       </c>
       <c r="W22" t="n">
-        <v>-49.498</v>
+        <v>-50.017</v>
       </c>
     </row>
     <row r="23">
@@ -2203,62 +2206,62 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ALARK.IS, BIMAS.IS</t>
+          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-20 | BIMAS.IS: 2026-08-20</t>
+          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>34.62553795007752</v>
+        <v>22.83095636113686</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.50% / +1.95% / -1.58% | BIMAS.IS: +1.81% / +2.32% / 0.00%</t>
+          <t>ALARK.IS: -2.18% / +1.41% / -2.35% | ASTOR.IS: +17.85% / +21.93% / 0.00% | BIMAS.IS: +1.27% / +3.13% / -0.86% | BRSAN.IS: +44.36% / +45.64% / -0.48% | CANTE.IS: +1.63% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>8.431557803491319</v>
+        <v>-5.037231846603429</v>
       </c>
       <c r="K23" t="n">
-        <v>7.910706034300108</v>
+        <v>8.749458804957477</v>
       </c>
       <c r="L23" t="n">
-        <v>32.1397934777012</v>
+        <v>23.4189376077676</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>233.2</v>
+        <v>181.8</v>
       </c>
       <c r="O23" t="n">
-        <v>49.5</v>
+        <v>45.7</v>
       </c>
       <c r="P23" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2266,22 +2269,22 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S23" t="n">
-        <v>20.274</v>
+        <v>22.513</v>
       </c>
       <c r="T23" t="n">
-        <v>20.274</v>
+        <v>22.513</v>
       </c>
       <c r="U23" t="n">
-        <v>82.349</v>
+        <v>53.688</v>
       </c>
       <c r="V23" t="n">
-        <v>43.866</v>
+        <v>44.094</v>
       </c>
       <c r="W23" t="n">
-        <v>-26.364</v>
+        <v>-2.646</v>
       </c>
     </row>
     <row r="24">
@@ -2292,73 +2295,85 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
+        </is>
+      </c>
       <c r="H24" t="n">
-        <v>12.43146471706449</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>22.83095636113686</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -2.18% / +1.41% / -2.35% | ASTOR.IS: +17.85% / +21.93% / 0.00% | BIMAS.IS: +1.27% / +3.13% / -0.86% | BRSAN.IS: +44.36% / +45.64% / -0.48% | CANTE.IS: +1.63% / +2.48% / -0.83%</t>
+        </is>
+      </c>
       <c r="J24" t="n">
-        <v>-6.412181273130146</v>
+        <v>-5.037231846603429</v>
       </c>
       <c r="K24" t="n">
-        <v>8.290371306631972</v>
+        <v>8.749458804957477</v>
       </c>
       <c r="L24" t="n">
-        <v>12.30894614425559</v>
+        <v>23.4189376077676</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>140.1</v>
+        <v>181.8</v>
       </c>
       <c r="O24" t="n">
-        <v>48.1</v>
+        <v>45.7</v>
       </c>
       <c r="P24" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S24" t="n">
-        <v>12.004</v>
+        <v>22.513</v>
       </c>
       <c r="T24" t="n">
-        <v>11.714</v>
+        <v>22.513</v>
       </c>
       <c r="U24" t="n">
-        <v>12.278</v>
+        <v>53.688</v>
       </c>
       <c r="V24" t="n">
-        <v>21.903</v>
+        <v>44.094</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.589</v>
+        <v>-2.646</v>
       </c>
     </row>
     <row r="25">
@@ -2379,12 +2394,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2402,14 +2417,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | BSOKE.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +9.03% / +9.99% / 0.00% | BSOKE.IS: -0.26% / +1.85% / -1.13% | CANTE.IS: +1.63% / +2.48% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K25" t="n">
-        <v>9.717087957064363</v>
+        <v>13.54508918924444</v>
       </c>
       <c r="L25" t="n">
         <v>7.902828022135555</v>
@@ -2418,13 +2433,13 @@
         <v>33.33333333333333</v>
       </c>
       <c r="N25" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="O25" t="n">
-        <v>44.1</v>
+        <v>47.1</v>
       </c>
       <c r="P25" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2441,19 +2456,19 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>9.967000000000001</v>
+        <v>13.804</v>
       </c>
       <c r="V25" t="n">
-        <v>9</v>
+        <v>12.803</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.768</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:W1"/>
     <mergeCell ref="A16:W16"/>
-    <mergeCell ref="A1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="2">
@@ -2637,12 +2652,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2664,7 +2679,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>66.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="O3" t="n">
         <v>45.9</v>
@@ -2687,13 +2702,13 @@
         <v>31.839</v>
       </c>
       <c r="U3" t="n">
-        <v>22.994</v>
+        <v>24.727</v>
       </c>
       <c r="V3" t="n">
         <v>27.773</v>
       </c>
       <c r="W3" t="n">
-        <v>-57.452</v>
+        <v>-58.261</v>
       </c>
     </row>
     <row r="4">
@@ -2712,12 +2727,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2739,7 +2754,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N4" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="O4" t="n">
         <v>46.7</v>
@@ -2762,13 +2777,13 @@
         <v>30.704</v>
       </c>
       <c r="U4" t="n">
-        <v>4.937</v>
+        <v>6.365</v>
       </c>
       <c r="V4" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>-46.496</v>
+        <v>-47.129</v>
       </c>
     </row>
     <row r="5">
@@ -2787,12 +2802,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -2814,7 +2829,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="O5" t="n">
         <v>46.7</v>
@@ -2837,13 +2852,13 @@
         <v>30.704</v>
       </c>
       <c r="U5" t="n">
-        <v>4.937</v>
+        <v>6.365</v>
       </c>
       <c r="V5" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-46.496</v>
+        <v>-47.129</v>
       </c>
     </row>
     <row r="6">
@@ -2862,12 +2877,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -2889,7 +2904,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="O6" t="n">
         <v>46.7</v>
@@ -2912,13 +2927,13 @@
         <v>30.704</v>
       </c>
       <c r="U6" t="n">
-        <v>4.937</v>
+        <v>6.365</v>
       </c>
       <c r="V6" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>-46.496</v>
+        <v>-47.129</v>
       </c>
     </row>
     <row r="7">
@@ -2937,12 +2952,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -2964,7 +2979,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N7" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="O7" t="n">
         <v>46.7</v>
@@ -2987,13 +3002,13 @@
         <v>30.704</v>
       </c>
       <c r="U7" t="n">
-        <v>4.937</v>
+        <v>6.365</v>
       </c>
       <c r="V7" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>-46.496</v>
+        <v>-47.129</v>
       </c>
     </row>
     <row r="8">
@@ -3012,12 +3027,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -3039,7 +3054,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>111.3</v>
+        <v>111.1</v>
       </c>
       <c r="O8" t="n">
         <v>38.4</v>
@@ -3062,13 +3077,13 @@
         <v>28.888</v>
       </c>
       <c r="U8" t="n">
-        <v>42.965</v>
+        <v>46.583</v>
       </c>
       <c r="V8" t="n">
         <v>14.358</v>
       </c>
       <c r="W8" t="n">
-        <v>-58.077</v>
+        <v>-59.547</v>
       </c>
     </row>
     <row r="9">
@@ -3087,12 +3102,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3114,7 +3129,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="N9" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="O9" t="n">
         <v>57.4</v>
@@ -3162,12 +3177,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3189,7 +3204,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="O10" t="n">
         <v>45.7</v>
@@ -3212,13 +3227,13 @@
         <v>13.513</v>
       </c>
       <c r="U10" t="n">
-        <v>17.704</v>
+        <v>17.606</v>
       </c>
       <c r="V10" t="n">
         <v>13.389</v>
       </c>
       <c r="W10" t="n">
-        <v>-17.644</v>
+        <v>-17.629</v>
       </c>
     </row>
     <row r="11">
@@ -3237,12 +3252,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3264,7 +3279,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="O11" t="n">
         <v>44.2</v>
@@ -3287,13 +3302,13 @@
         <v>13.42</v>
       </c>
       <c r="U11" t="n">
-        <v>19.558</v>
+        <v>21.206</v>
       </c>
       <c r="V11" t="n">
         <v>12.908</v>
       </c>
       <c r="W11" t="n">
-        <v>-18.532</v>
+        <v>-18.787</v>
       </c>
     </row>
     <row r="12">
@@ -3307,68 +3322,80 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M20|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AKBNK.IS, ASTOR.IS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AKBNK.IS: 2026-08-24 | ASTOR.IS: 2026-08-24</t>
+        </is>
+      </c>
       <c r="H12" t="n">
-        <v>-31.68030208588772</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>18.78300085000422</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J12" t="n">
-        <v>-42.73273215208214</v>
+        <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>18.91282273316368</v>
+        <v>20.9255370334958</v>
       </c>
       <c r="L12" t="n">
-        <v>55.03591015625</v>
+        <v>28.49280591027672</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N12" t="n">
-        <v>232.6</v>
+        <v>82.3</v>
       </c>
       <c r="O12" t="n">
-        <v>41.9</v>
+        <v>48.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>13.617</v>
+      </c>
+      <c r="T12" t="n">
+        <v>13.617</v>
+      </c>
+      <c r="U12" t="n">
+        <v>51.129</v>
+      </c>
+      <c r="V12" t="n">
+        <v>27.863</v>
+      </c>
+      <c r="W12" t="n">
         <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>31.369</v>
-      </c>
-      <c r="T12" t="n">
-        <v>15.334</v>
-      </c>
-      <c r="U12" t="n">
-        <v>10.025</v>
-      </c>
-      <c r="V12" t="n">
-        <v>55.16</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-13.029</v>
       </c>
     </row>
     <row r="13">
@@ -3382,57 +3409,57 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AKBNK.IS, BRSAN.IS</t>
+          <t>AKBNK.IS, ASTOR.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-07-29 | BRSAN.IS: 2026-08-13</t>
+          <t>AKBNK.IS: 2026-08-14 | ASTOR.IS: 2026-08-24</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.84922237136889</v>
+        <v>13.9199517857125</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +8.31% / +11.52% / -3.77% | BRSAN.IS: +9.53% / +12.09% / -0.05%</t>
+          <t>AKBNK.IS: +4.44% / +6.27% / -2.24% | ASTOR.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-7.945335963406319</v>
+        <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>14.27428313833436</v>
+        <v>20.2290704461636</v>
       </c>
       <c r="L13" t="n">
-        <v>31.58073864491333</v>
+        <v>28.84422545304696</v>
       </c>
       <c r="M13" t="n">
         <v>88.88888888888889</v>
       </c>
       <c r="N13" t="n">
-        <v>48.2</v>
+        <v>128.5</v>
       </c>
       <c r="O13" t="n">
-        <v>49.5</v>
+        <v>49.8</v>
       </c>
       <c r="P13" t="n">
-        <v>6.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3443,19 +3470,19 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>11.1</v>
+        <v>10.914</v>
       </c>
       <c r="T13" t="n">
-        <v>11.1</v>
+        <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>36.867</v>
+        <v>52.73</v>
       </c>
       <c r="V13" t="n">
-        <v>16.412</v>
+        <v>40.386</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3474,12 +3501,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3497,14 +3524,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.41% / +3.39% / -0.79% | BRSAN.IS: +4.13% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: +3.65% / +5.47% / -0.81% | BRSAN.IS: +13.31% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>10.99376131182925</v>
+        <v>17.73675736407423</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3513,7 +3540,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N14" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="O14" t="n">
         <v>57.1</v>
@@ -3536,13 +3563,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>40.512</v>
+        <v>51.049</v>
       </c>
       <c r="V14" t="n">
-        <v>31.556</v>
+        <v>39.548</v>
       </c>
       <c r="W14" t="n">
-        <v>-18.131</v>
+        <v>-9.723000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -3687,12 +3714,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -3714,7 +3741,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>66.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="O18" t="n">
         <v>45.9</v>
@@ -3737,13 +3764,13 @@
         <v>31.839</v>
       </c>
       <c r="U18" t="n">
-        <v>22.994</v>
+        <v>24.727</v>
       </c>
       <c r="V18" t="n">
         <v>27.773</v>
       </c>
       <c r="W18" t="n">
-        <v>-57.452</v>
+        <v>-58.261</v>
       </c>
     </row>
     <row r="19">
@@ -3764,12 +3791,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -3791,7 +3818,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="O19" t="n">
         <v>46.7</v>
@@ -3814,13 +3841,13 @@
         <v>30.704</v>
       </c>
       <c r="U19" t="n">
-        <v>4.937</v>
+        <v>6.365</v>
       </c>
       <c r="V19" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>-46.496</v>
+        <v>-47.129</v>
       </c>
     </row>
     <row r="20">
@@ -3841,12 +3868,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -3868,7 +3895,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="O20" t="n">
         <v>46.7</v>
@@ -3891,13 +3918,13 @@
         <v>30.704</v>
       </c>
       <c r="U20" t="n">
-        <v>4.937</v>
+        <v>6.365</v>
       </c>
       <c r="V20" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-46.496</v>
+        <v>-47.129</v>
       </c>
     </row>
     <row r="21">
@@ -3918,12 +3945,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -3945,7 +3972,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>111.3</v>
+        <v>111.1</v>
       </c>
       <c r="O21" t="n">
         <v>38.4</v>
@@ -3968,13 +3995,13 @@
         <v>28.888</v>
       </c>
       <c r="U21" t="n">
-        <v>42.965</v>
+        <v>46.583</v>
       </c>
       <c r="V21" t="n">
         <v>14.358</v>
       </c>
       <c r="W21" t="n">
-        <v>-58.077</v>
+        <v>-59.547</v>
       </c>
     </row>
     <row r="22">
@@ -3995,12 +4022,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4022,7 +4049,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="O22" t="n">
         <v>44.2</v>
@@ -4045,13 +4072,13 @@
         <v>13.42</v>
       </c>
       <c r="U22" t="n">
-        <v>19.558</v>
+        <v>21.206</v>
       </c>
       <c r="V22" t="n">
         <v>12.908</v>
       </c>
       <c r="W22" t="n">
-        <v>-18.532</v>
+        <v>-18.787</v>
       </c>
     </row>
     <row r="23">
@@ -4072,12 +4099,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -4099,7 +4126,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N23" t="n">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="O23" t="n">
         <v>45.7</v>
@@ -4122,13 +4149,13 @@
         <v>13.513</v>
       </c>
       <c r="U23" t="n">
-        <v>17.704</v>
+        <v>17.606</v>
       </c>
       <c r="V23" t="n">
         <v>13.389</v>
       </c>
       <c r="W23" t="n">
-        <v>-17.644</v>
+        <v>-17.629</v>
       </c>
     </row>
     <row r="24">
@@ -4149,12 +4176,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4176,7 +4203,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="N24" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="O24" t="n">
         <v>57.4</v>
@@ -4226,12 +4253,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4249,14 +4276,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.41% / +3.39% / -0.79% | BRSAN.IS: +4.13% / +6.56% / 0.00%</t>
+          <t>AKBNK.IS: +3.65% / +5.47% / -0.81% | BRSAN.IS: +13.31% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>10.99376131182925</v>
+        <v>17.73675736407423</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4265,7 +4292,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N25" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="O25" t="n">
         <v>57.1</v>
@@ -4288,13 +4315,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>40.512</v>
+        <v>51.049</v>
       </c>
       <c r="V25" t="n">
-        <v>31.556</v>
+        <v>39.548</v>
       </c>
       <c r="W25" t="n">
-        <v>-18.131</v>
+        <v>-9.723000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -4305,62 +4332,62 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AKBNK.IS, BRSAN.IS</t>
+          <t>AKBNK.IS, ASTOR.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-07-29 | BRSAN.IS: 2026-08-13</t>
+          <t>AKBNK.IS: 2026-08-24 | ASTOR.IS: 2026-08-24</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.84922237136889</v>
+        <v>18.78300085000422</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +8.31% / +11.52% / -3.77% | BRSAN.IS: +9.53% / +12.09% / -0.05%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-7.945335963406319</v>
+        <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>14.27428313833436</v>
+        <v>20.9255370334958</v>
       </c>
       <c r="L26" t="n">
-        <v>31.58073864491333</v>
+        <v>28.49280591027672</v>
       </c>
       <c r="M26" t="n">
         <v>88.88888888888889</v>
       </c>
       <c r="N26" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="O26" t="n">
         <v>48.2</v>
       </c>
-      <c r="O26" t="n">
-        <v>49.5</v>
-      </c>
       <c r="P26" t="n">
-        <v>6.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4371,19 +4398,19 @@
         <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>11.1</v>
+        <v>13.617</v>
       </c>
       <c r="T26" t="n">
-        <v>11.1</v>
+        <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>36.867</v>
+        <v>51.129</v>
       </c>
       <c r="V26" t="n">
-        <v>16.412</v>
+        <v>27.863</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -4394,79 +4421,91 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M20|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>AKBNK.IS, ASTOR.IS</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>AKBNK.IS: 2026-08-14 | ASTOR.IS: 2026-08-24</t>
+        </is>
+      </c>
       <c r="H27" t="n">
-        <v>-31.68030208588772</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>13.9199517857125</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>AKBNK.IS: +4.44% / +6.27% / -2.24% | ASTOR.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J27" t="n">
-        <v>-42.73273215208214</v>
+        <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>18.91282273316368</v>
+        <v>20.2290704461636</v>
       </c>
       <c r="L27" t="n">
-        <v>55.03591015625</v>
+        <v>28.84422545304696</v>
       </c>
       <c r="M27" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N27" t="n">
-        <v>232.6</v>
+        <v>128.5</v>
       </c>
       <c r="O27" t="n">
-        <v>41.9</v>
+        <v>49.8</v>
       </c>
       <c r="P27" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10.914</v>
+      </c>
+      <c r="T27" t="n">
+        <v>10.914</v>
+      </c>
+      <c r="U27" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="V27" t="n">
+        <v>40.386</v>
+      </c>
+      <c r="W27" t="n">
         <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>31.369</v>
-      </c>
-      <c r="T27" t="n">
-        <v>15.334</v>
-      </c>
-      <c r="U27" t="n">
-        <v>10.025</v>
-      </c>
-      <c r="V27" t="n">
-        <v>55.16</v>
-      </c>
-      <c r="W27" t="n">
-        <v>-13.029</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:W1"/>
     <mergeCell ref="A16:W16"/>
-    <mergeCell ref="A1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="2">

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -760,7 +760,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>117.6</v>
+        <v>117.4</v>
       </c>
       <c r="O3" t="n">
         <v>39.9</v>
@@ -783,13 +783,13 @@
         <v>28.567</v>
       </c>
       <c r="U3" t="n">
-        <v>81.31999999999999</v>
+        <v>71.535</v>
       </c>
       <c r="V3" t="n">
         <v>41.769</v>
       </c>
       <c r="W3" t="n">
-        <v>-72.512</v>
+        <v>-68.599</v>
       </c>
     </row>
     <row r="4">
@@ -808,12 +808,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -831,14 +831,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.18% / +1.41% / -2.35% | BRSAN.IS: +14.76% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: -2.00% / +1.41% / -2.45% | BRSAN.IS: +13.62% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>8.70596533744019</v>
+        <v>8.204317234137148</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -847,13 +847,13 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>121.6</v>
+        <v>121.3</v>
       </c>
       <c r="O4" t="n">
         <v>43.1</v>
       </c>
       <c r="P4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>102.114</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>56.36</v>
+        <v>55.639</v>
       </c>
       <c r="W4" t="n">
-        <v>-25.101</v>
+        <v>-25.354</v>
       </c>
     </row>
     <row r="5">
@@ -895,12 +895,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>93.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="O5" t="n">
         <v>37.4</v>
@@ -945,13 +945,13 @@
         <v>35.687</v>
       </c>
       <c r="U5" t="n">
-        <v>26.268</v>
+        <v>22.887</v>
       </c>
       <c r="V5" t="n">
         <v>12.323</v>
       </c>
       <c r="W5" t="n">
-        <v>-70.066</v>
+        <v>-68.19</v>
       </c>
     </row>
     <row r="6">
@@ -970,12 +970,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -997,7 +997,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>117.6</v>
+        <v>117.4</v>
       </c>
       <c r="O6" t="n">
         <v>39.9</v>
@@ -1020,13 +1020,13 @@
         <v>28.567</v>
       </c>
       <c r="U6" t="n">
-        <v>81.31999999999999</v>
+        <v>71.535</v>
       </c>
       <c r="V6" t="n">
         <v>41.769</v>
       </c>
       <c r="W6" t="n">
-        <v>-72.512</v>
+        <v>-68.599</v>
       </c>
     </row>
     <row r="7">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1068,14 +1068,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.18% / +1.41% / -2.35% | BRSAN.IS: +14.76% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: -2.00% / +1.41% / -2.45% | BRSAN.IS: +13.62% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>8.70596533744019</v>
+        <v>8.204317234137148</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1084,13 +1084,13 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>121.6</v>
+        <v>121.3</v>
       </c>
       <c r="O7" t="n">
         <v>43.1</v>
       </c>
       <c r="P7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>102.114</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>56.36</v>
+        <v>55.639</v>
       </c>
       <c r="W7" t="n">
-        <v>-25.101</v>
+        <v>-25.354</v>
       </c>
     </row>
     <row r="8">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -1182,13 +1182,13 @@
         <v>29.993</v>
       </c>
       <c r="U8" t="n">
-        <v>6.823</v>
+        <v>6.3</v>
       </c>
       <c r="V8" t="n">
         <v>-6.769</v>
       </c>
       <c r="W8" t="n">
-        <v>-45.267</v>
+        <v>-45.045</v>
       </c>
     </row>
     <row r="9">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1234,7 +1234,7 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>117.6</v>
+        <v>117.4</v>
       </c>
       <c r="O9" t="n">
         <v>39.9</v>
@@ -1257,13 +1257,13 @@
         <v>28.567</v>
       </c>
       <c r="U9" t="n">
-        <v>81.31999999999999</v>
+        <v>71.535</v>
       </c>
       <c r="V9" t="n">
         <v>41.769</v>
       </c>
       <c r="W9" t="n">
-        <v>-72.512</v>
+        <v>-68.599</v>
       </c>
     </row>
     <row r="10">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1332,13 +1332,13 @@
         <v>29.993</v>
       </c>
       <c r="U10" t="n">
-        <v>6.823</v>
+        <v>6.3</v>
       </c>
       <c r="V10" t="n">
         <v>-6.769</v>
       </c>
       <c r="W10" t="n">
-        <v>-45.267</v>
+        <v>-45.045</v>
       </c>
     </row>
     <row r="11">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>72.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="O11" t="n">
         <v>38.4</v>
@@ -1407,13 +1407,13 @@
         <v>29.287</v>
       </c>
       <c r="U11" t="n">
-        <v>40.723</v>
+        <v>36.452</v>
       </c>
       <c r="V11" t="n">
         <v>14.374</v>
       </c>
       <c r="W11" t="n">
-        <v>-50.017</v>
+        <v>-48.499</v>
       </c>
     </row>
     <row r="12">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.03% / +9.99% / 0.00% | BSOKE.IS: -0.26% / +1.85% / -1.13% | CANTE.IS: +1.63% / +2.48% / 0.00%</t>
+          <t>BRSAN.IS: +7.94% / +9.99% / 0.00% | BSOKE.IS: -0.38% / +1.85% / -1.13% | CANTE.IS: +2.46% / +2.48% / 0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K12" t="n">
-        <v>13.54508918924444</v>
+        <v>13.40628799511849</v>
       </c>
       <c r="L12" t="n">
         <v>7.902828022135555</v>
@@ -1471,7 +1471,7 @@
         <v>33.33333333333333</v>
       </c>
       <c r="N12" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="O12" t="n">
         <v>47.1</v>
@@ -1494,13 +1494,13 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>13.804</v>
+        <v>13.664</v>
       </c>
       <c r="V12" t="n">
-        <v>12.803</v>
+        <v>12.665</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.162</v>
       </c>
     </row>
     <row r="13">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1542,14 +1542,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.18% / +1.41% / -2.35% | ASTOR.IS: +17.85% / +21.93% / 0.00% | BIMAS.IS: +1.27% / +3.13% / -0.86% | BRSAN.IS: +44.36% / +45.64% / -0.48% | CANTE.IS: +1.63% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: -2.00% / +1.41% / -2.45% | ASTOR.IS: +16.21% / +21.93% / 0.00% | BIMAS.IS: +0.96% / +3.13% / -0.86% | BRSAN.IS: +42.92% / +45.64% / -0.48% | CANTE.IS: +2.46% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K13" t="n">
-        <v>8.749458804957477</v>
+        <v>8.300425101697574</v>
       </c>
       <c r="L13" t="n">
         <v>23.4189376077676</v>
@@ -1558,7 +1558,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>181.8</v>
+        <v>181.5</v>
       </c>
       <c r="O13" t="n">
         <v>45.7</v>
@@ -1581,13 +1581,13 @@
         <v>22.513</v>
       </c>
       <c r="U13" t="n">
-        <v>53.688</v>
+        <v>50.99</v>
       </c>
       <c r="V13" t="n">
-        <v>44.094</v>
+        <v>43.499</v>
       </c>
       <c r="W13" t="n">
-        <v>-2.646</v>
+        <v>-3.236</v>
       </c>
     </row>
     <row r="14">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1629,14 +1629,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.18% / +1.41% / -2.35% | ASTOR.IS: +17.85% / +21.93% / 0.00% | BIMAS.IS: +1.27% / +3.13% / -0.86% | BRSAN.IS: +44.36% / +45.64% / -0.48% | CANTE.IS: +1.63% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: -2.00% / +1.41% / -2.45% | ASTOR.IS: +16.21% / +21.93% / 0.00% | BIMAS.IS: +0.96% / +3.13% / -0.86% | BRSAN.IS: +42.92% / +45.64% / -0.48% | CANTE.IS: +2.46% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>8.749458804957477</v>
+        <v>8.300425101697574</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1645,7 +1645,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>181.8</v>
+        <v>181.5</v>
       </c>
       <c r="O14" t="n">
         <v>45.7</v>
@@ -1668,13 +1668,13 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>53.688</v>
+        <v>50.99</v>
       </c>
       <c r="V14" t="n">
-        <v>44.094</v>
+        <v>43.499</v>
       </c>
       <c r="W14" t="n">
-        <v>-2.646</v>
+        <v>-3.236</v>
       </c>
     </row>
     <row r="16">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1846,7 +1846,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>117.6</v>
+        <v>117.4</v>
       </c>
       <c r="O18" t="n">
         <v>39.9</v>
@@ -1869,13 +1869,13 @@
         <v>28.567</v>
       </c>
       <c r="U18" t="n">
-        <v>81.31999999999999</v>
+        <v>71.535</v>
       </c>
       <c r="V18" t="n">
         <v>41.769</v>
       </c>
       <c r="W18" t="n">
-        <v>-72.512</v>
+        <v>-68.599</v>
       </c>
     </row>
     <row r="19">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1919,14 +1919,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.18% / +1.41% / -2.35% | BRSAN.IS: +14.76% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: -2.00% / +1.41% / -2.45% | BRSAN.IS: +13.62% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>8.70596533744019</v>
+        <v>8.204317234137148</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1935,13 +1935,13 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>121.6</v>
+        <v>121.3</v>
       </c>
       <c r="O19" t="n">
         <v>43.1</v>
       </c>
       <c r="P19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1958,13 +1958,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>102.114</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>56.36</v>
+        <v>55.639</v>
       </c>
       <c r="W19" t="n">
-        <v>-25.101</v>
+        <v>-25.354</v>
       </c>
     </row>
     <row r="20">
@@ -1985,12 +1985,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2012,7 +2012,7 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>93.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="O20" t="n">
         <v>37.4</v>
@@ -2035,13 +2035,13 @@
         <v>35.687</v>
       </c>
       <c r="U20" t="n">
-        <v>26.268</v>
+        <v>22.887</v>
       </c>
       <c r="V20" t="n">
         <v>12.323</v>
       </c>
       <c r="W20" t="n">
-        <v>-70.066</v>
+        <v>-68.19</v>
       </c>
     </row>
     <row r="21">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2112,13 +2112,13 @@
         <v>29.993</v>
       </c>
       <c r="U21" t="n">
-        <v>6.823</v>
+        <v>6.3</v>
       </c>
       <c r="V21" t="n">
         <v>-6.769</v>
       </c>
       <c r="W21" t="n">
-        <v>-45.267</v>
+        <v>-45.045</v>
       </c>
     </row>
     <row r="22">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2166,7 +2166,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>72.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="O22" t="n">
         <v>38.4</v>
@@ -2189,13 +2189,13 @@
         <v>29.287</v>
       </c>
       <c r="U22" t="n">
-        <v>40.723</v>
+        <v>36.452</v>
       </c>
       <c r="V22" t="n">
         <v>14.374</v>
       </c>
       <c r="W22" t="n">
-        <v>-50.017</v>
+        <v>-48.499</v>
       </c>
     </row>
     <row r="23">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2239,14 +2239,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.18% / +1.41% / -2.35% | ASTOR.IS: +17.85% / +21.93% / 0.00% | BIMAS.IS: +1.27% / +3.13% / -0.86% | BRSAN.IS: +44.36% / +45.64% / -0.48% | CANTE.IS: +1.63% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: -2.00% / +1.41% / -2.45% | ASTOR.IS: +16.21% / +21.93% / 0.00% | BIMAS.IS: +0.96% / +3.13% / -0.86% | BRSAN.IS: +42.92% / +45.64% / -0.48% | CANTE.IS: +2.46% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K23" t="n">
-        <v>8.749458804957477</v>
+        <v>8.300425101697574</v>
       </c>
       <c r="L23" t="n">
         <v>23.4189376077676</v>
@@ -2255,7 +2255,7 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>181.8</v>
+        <v>181.5</v>
       </c>
       <c r="O23" t="n">
         <v>45.7</v>
@@ -2278,13 +2278,13 @@
         <v>22.513</v>
       </c>
       <c r="U23" t="n">
-        <v>53.688</v>
+        <v>50.99</v>
       </c>
       <c r="V23" t="n">
-        <v>44.094</v>
+        <v>43.499</v>
       </c>
       <c r="W23" t="n">
-        <v>-2.646</v>
+        <v>-3.236</v>
       </c>
     </row>
     <row r="24">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2328,14 +2328,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.18% / +1.41% / -2.35% | ASTOR.IS: +17.85% / +21.93% / 0.00% | BIMAS.IS: +1.27% / +3.13% / -0.86% | BRSAN.IS: +44.36% / +45.64% / -0.48% | CANTE.IS: +1.63% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: -2.00% / +1.41% / -2.45% | ASTOR.IS: +16.21% / +21.93% / 0.00% | BIMAS.IS: +0.96% / +3.13% / -0.86% | BRSAN.IS: +42.92% / +45.64% / -0.48% | CANTE.IS: +2.46% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K24" t="n">
-        <v>8.749458804957477</v>
+        <v>8.300425101697574</v>
       </c>
       <c r="L24" t="n">
         <v>23.4189376077676</v>
@@ -2344,7 +2344,7 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>181.8</v>
+        <v>181.5</v>
       </c>
       <c r="O24" t="n">
         <v>45.7</v>
@@ -2367,13 +2367,13 @@
         <v>22.513</v>
       </c>
       <c r="U24" t="n">
-        <v>53.688</v>
+        <v>50.99</v>
       </c>
       <c r="V24" t="n">
-        <v>44.094</v>
+        <v>43.499</v>
       </c>
       <c r="W24" t="n">
-        <v>-2.646</v>
+        <v>-3.236</v>
       </c>
     </row>
     <row r="25">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2417,14 +2417,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.03% / +9.99% / 0.00% | BSOKE.IS: -0.26% / +1.85% / -1.13% | CANTE.IS: +1.63% / +2.48% / 0.00%</t>
+          <t>BRSAN.IS: +7.94% / +9.99% / 0.00% | BSOKE.IS: -0.38% / +1.85% / -1.13% | CANTE.IS: +2.46% / +2.48% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K25" t="n">
-        <v>13.54508918924444</v>
+        <v>13.40628799511849</v>
       </c>
       <c r="L25" t="n">
         <v>7.902828022135555</v>
@@ -2433,7 +2433,7 @@
         <v>33.33333333333333</v>
       </c>
       <c r="N25" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="O25" t="n">
         <v>47.1</v>
@@ -2456,13 +2456,13 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>13.804</v>
+        <v>13.664</v>
       </c>
       <c r="V25" t="n">
-        <v>12.803</v>
+        <v>12.665</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.162</v>
       </c>
     </row>
   </sheetData>
@@ -2652,12 +2652,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2679,7 +2679,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>66</v>
+        <v>65.8</v>
       </c>
       <c r="O3" t="n">
         <v>45.9</v>
@@ -2702,13 +2702,13 @@
         <v>31.839</v>
       </c>
       <c r="U3" t="n">
-        <v>24.727</v>
+        <v>16.523</v>
       </c>
       <c r="V3" t="n">
         <v>27.773</v>
       </c>
       <c r="W3" t="n">
-        <v>-58.261</v>
+        <v>-54.429</v>
       </c>
     </row>
     <row r="4">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2754,7 +2754,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N4" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="O4" t="n">
         <v>46.7</v>
@@ -2777,13 +2777,13 @@
         <v>30.704</v>
       </c>
       <c r="U4" t="n">
-        <v>6.365</v>
+        <v>3.325</v>
       </c>
       <c r="V4" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>-47.129</v>
+        <v>-45.782</v>
       </c>
     </row>
     <row r="5">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -2829,7 +2829,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="O5" t="n">
         <v>46.7</v>
@@ -2852,13 +2852,13 @@
         <v>30.704</v>
       </c>
       <c r="U5" t="n">
-        <v>6.365</v>
+        <v>3.325</v>
       </c>
       <c r="V5" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-47.129</v>
+        <v>-45.782</v>
       </c>
     </row>
     <row r="6">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -2904,7 +2904,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="O6" t="n">
         <v>46.7</v>
@@ -2927,13 +2927,13 @@
         <v>30.704</v>
       </c>
       <c r="U6" t="n">
-        <v>6.365</v>
+        <v>3.325</v>
       </c>
       <c r="V6" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>-47.129</v>
+        <v>-45.782</v>
       </c>
     </row>
     <row r="7">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -2979,7 +2979,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N7" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="O7" t="n">
         <v>46.7</v>
@@ -3002,13 +3002,13 @@
         <v>30.704</v>
       </c>
       <c r="U7" t="n">
-        <v>6.365</v>
+        <v>3.325</v>
       </c>
       <c r="V7" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>-47.129</v>
+        <v>-45.782</v>
       </c>
     </row>
     <row r="8">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -3054,7 +3054,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>111.1</v>
+        <v>110.9</v>
       </c>
       <c r="O8" t="n">
         <v>38.4</v>
@@ -3077,13 +3077,13 @@
         <v>28.888</v>
       </c>
       <c r="U8" t="n">
-        <v>46.583</v>
+        <v>38.772</v>
       </c>
       <c r="V8" t="n">
         <v>14.358</v>
       </c>
       <c r="W8" t="n">
-        <v>-59.547</v>
+        <v>-56.373</v>
       </c>
     </row>
     <row r="9">
@@ -3102,12 +3102,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3129,7 +3129,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="N9" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="O9" t="n">
         <v>57.4</v>
@@ -3177,12 +3177,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3204,7 +3204,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>68.5</v>
+        <v>68.3</v>
       </c>
       <c r="O10" t="n">
         <v>45.7</v>
@@ -3227,13 +3227,13 @@
         <v>13.513</v>
       </c>
       <c r="U10" t="n">
-        <v>17.606</v>
+        <v>14.92</v>
       </c>
       <c r="V10" t="n">
         <v>13.389</v>
       </c>
       <c r="W10" t="n">
-        <v>-17.629</v>
+        <v>-17.227</v>
       </c>
     </row>
     <row r="11">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3279,7 +3279,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="O11" t="n">
         <v>44.2</v>
@@ -3302,13 +3302,13 @@
         <v>13.42</v>
       </c>
       <c r="U11" t="n">
-        <v>21.206</v>
+        <v>19.007</v>
       </c>
       <c r="V11" t="n">
         <v>12.908</v>
       </c>
       <c r="W11" t="n">
-        <v>-18.787</v>
+        <v>-18.447</v>
       </c>
     </row>
     <row r="12">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3350,14 +3350,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AKBNK.IS: +0.12% / +0.21% / -0.35% | ASTOR.IS: -1.41% / +0.37% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>20.9255370334958</v>
+        <v>20.16780582965436</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3366,10 +3366,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N12" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="O12" t="n">
-        <v>48.2</v>
+        <v>48.8</v>
       </c>
       <c r="P12" t="n">
         <v>3.6</v>
@@ -3389,13 +3389,13 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>51.129</v>
+        <v>50.34</v>
       </c>
       <c r="V12" t="n">
-        <v>27.863</v>
+        <v>27.061</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.978</v>
       </c>
     </row>
     <row r="13">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.44% / +6.27% / -2.24% | ASTOR.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AKBNK.IS: +4.58% / +6.27% / -2.24% | ASTOR.IS: -1.41% / +0.37% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>20.2290704461636</v>
+        <v>19.47441328866748</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3453,7 +3453,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N13" t="n">
-        <v>128.5</v>
+        <v>128.2</v>
       </c>
       <c r="O13" t="n">
         <v>49.8</v>
@@ -3476,13 +3476,13 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>52.73</v>
+        <v>50.566</v>
       </c>
       <c r="V13" t="n">
-        <v>40.386</v>
+        <v>39.505</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.981</v>
       </c>
     </row>
     <row r="14">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3524,14 +3524,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.65% / +5.47% / -0.81% | BRSAN.IS: +13.31% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +3.80% / +5.47% / -0.81% | BRSAN.IS: +12.18% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>17.73675736407423</v>
+        <v>17.20233656228456</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3540,13 +3540,13 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N14" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="O14" t="n">
         <v>57.1</v>
       </c>
       <c r="P14" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3563,13 +3563,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>51.049</v>
+        <v>50.532</v>
       </c>
       <c r="V14" t="n">
-        <v>39.548</v>
+        <v>38.915</v>
       </c>
       <c r="W14" t="n">
-        <v>-9.723000000000001</v>
+        <v>-10.421</v>
       </c>
     </row>
     <row r="16">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -3741,7 +3741,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>66</v>
+        <v>65.8</v>
       </c>
       <c r="O18" t="n">
         <v>45.9</v>
@@ -3764,13 +3764,13 @@
         <v>31.839</v>
       </c>
       <c r="U18" t="n">
-        <v>24.727</v>
+        <v>16.523</v>
       </c>
       <c r="V18" t="n">
         <v>27.773</v>
       </c>
       <c r="W18" t="n">
-        <v>-58.261</v>
+        <v>-54.429</v>
       </c>
     </row>
     <row r="19">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -3818,7 +3818,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="O19" t="n">
         <v>46.7</v>
@@ -3841,13 +3841,13 @@
         <v>30.704</v>
       </c>
       <c r="U19" t="n">
-        <v>6.365</v>
+        <v>3.325</v>
       </c>
       <c r="V19" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>-47.129</v>
+        <v>-45.782</v>
       </c>
     </row>
     <row r="20">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -3895,7 +3895,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="O20" t="n">
         <v>46.7</v>
@@ -3918,13 +3918,13 @@
         <v>30.704</v>
       </c>
       <c r="U20" t="n">
-        <v>6.365</v>
+        <v>3.325</v>
       </c>
       <c r="V20" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-47.129</v>
+        <v>-45.782</v>
       </c>
     </row>
     <row r="21">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -3972,7 +3972,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>111.1</v>
+        <v>110.9</v>
       </c>
       <c r="O21" t="n">
         <v>38.4</v>
@@ -3995,13 +3995,13 @@
         <v>28.888</v>
       </c>
       <c r="U21" t="n">
-        <v>46.583</v>
+        <v>38.772</v>
       </c>
       <c r="V21" t="n">
         <v>14.358</v>
       </c>
       <c r="W21" t="n">
-        <v>-59.547</v>
+        <v>-56.373</v>
       </c>
     </row>
     <row r="22">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4049,7 +4049,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="O22" t="n">
         <v>44.2</v>
@@ -4072,13 +4072,13 @@
         <v>13.42</v>
       </c>
       <c r="U22" t="n">
-        <v>21.206</v>
+        <v>19.007</v>
       </c>
       <c r="V22" t="n">
         <v>12.908</v>
       </c>
       <c r="W22" t="n">
-        <v>-18.787</v>
+        <v>-18.447</v>
       </c>
     </row>
     <row r="23">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -4126,7 +4126,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N23" t="n">
-        <v>68.5</v>
+        <v>68.3</v>
       </c>
       <c r="O23" t="n">
         <v>45.7</v>
@@ -4149,13 +4149,13 @@
         <v>13.513</v>
       </c>
       <c r="U23" t="n">
-        <v>17.606</v>
+        <v>14.92</v>
       </c>
       <c r="V23" t="n">
         <v>13.389</v>
       </c>
       <c r="W23" t="n">
-        <v>-17.629</v>
+        <v>-17.227</v>
       </c>
     </row>
     <row r="24">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4203,7 +4203,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="N24" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="O24" t="n">
         <v>57.4</v>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4276,14 +4276,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.65% / +5.47% / -0.81% | BRSAN.IS: +13.31% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +3.80% / +5.47% / -0.81% | BRSAN.IS: +12.18% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>17.73675736407423</v>
+        <v>17.20233656228456</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4292,13 +4292,13 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N25" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="O25" t="n">
         <v>57.1</v>
       </c>
       <c r="P25" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>51.049</v>
+        <v>50.532</v>
       </c>
       <c r="V25" t="n">
-        <v>39.548</v>
+        <v>38.915</v>
       </c>
       <c r="W25" t="n">
-        <v>-9.723000000000001</v>
+        <v>-10.421</v>
       </c>
     </row>
     <row r="26">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4365,14 +4365,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AKBNK.IS: +0.12% / +0.21% / -0.35% | ASTOR.IS: -1.41% / +0.37% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>20.9255370334958</v>
+        <v>20.16780582965436</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4381,10 +4381,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N26" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="O26" t="n">
-        <v>48.2</v>
+        <v>48.8</v>
       </c>
       <c r="P26" t="n">
         <v>3.6</v>
@@ -4404,13 +4404,13 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>51.129</v>
+        <v>50.34</v>
       </c>
       <c r="V26" t="n">
-        <v>27.863</v>
+        <v>27.061</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>-0.978</v>
       </c>
     </row>
     <row r="27">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4454,14 +4454,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.44% / +6.27% / -2.24% | ASTOR.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AKBNK.IS: +4.58% / +6.27% / -2.24% | ASTOR.IS: -1.41% / +0.37% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>20.2290704461636</v>
+        <v>19.47441328866748</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4470,7 +4470,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N27" t="n">
-        <v>128.5</v>
+        <v>128.2</v>
       </c>
       <c r="O27" t="n">
         <v>49.8</v>
@@ -4493,13 +4493,13 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>52.73</v>
+        <v>50.566</v>
       </c>
       <c r="V27" t="n">
-        <v>40.386</v>
+        <v>39.505</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>-0.981</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -831,14 +831,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.00% / +1.41% / -2.45% | BRSAN.IS: +13.62% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: -1.34% / +1.41% / -3.86% | BRSAN.IS: +9.89% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>8.204317234137148</v>
+        <v>6.587552695506349</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -870,13 +870,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>95.93000000000001</v>
+        <v>93.002</v>
       </c>
       <c r="V4" t="n">
-        <v>55.639</v>
+        <v>53.313</v>
       </c>
       <c r="W4" t="n">
-        <v>-25.354</v>
+        <v>-28.282</v>
       </c>
     </row>
     <row r="5">
@@ -1068,14 +1068,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.00% / +1.41% / -2.45% | BRSAN.IS: +13.62% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: -1.34% / +1.41% / -3.86% | BRSAN.IS: +9.89% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>8.204317234137148</v>
+        <v>6.587552695506349</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1107,13 +1107,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>95.93000000000001</v>
+        <v>93.002</v>
       </c>
       <c r="V7" t="n">
-        <v>55.639</v>
+        <v>53.313</v>
       </c>
       <c r="W7" t="n">
-        <v>-25.354</v>
+        <v>-28.282</v>
       </c>
     </row>
     <row r="8">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +7.94% / +9.99% / 0.00% | BSOKE.IS: -0.38% / +1.85% / -1.13% | CANTE.IS: +2.46% / +2.48% / 0.00%</t>
+          <t>BRSAN.IS: +4.40% / +9.99% / 0.00% | BSOKE.IS: -1.81% / +1.85% / -2.03% | CANTE.IS: +1.63% / +2.48% / 0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K12" t="n">
-        <v>13.40628799511849</v>
+        <v>11.28206848072826</v>
       </c>
       <c r="L12" t="n">
         <v>7.902828022135555</v>
@@ -1494,13 +1494,13 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>13.664</v>
+        <v>11.535</v>
       </c>
       <c r="V12" t="n">
-        <v>12.665</v>
+        <v>10.554</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.162</v>
+        <v>-2.291</v>
       </c>
     </row>
     <row r="13">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1527,67 +1527,55 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>22.83095636113686</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ALARK.IS: -2.00% / +1.41% / -2.45% | ASTOR.IS: +16.21% / +21.93% / 0.00% | BIMAS.IS: +0.96% / +3.13% / -0.86% | BRSAN.IS: +42.92% / +45.64% / -0.48% | CANTE.IS: +2.46% / +2.48% / -0.83%</t>
-        </is>
-      </c>
+        <v>12.43146471706449</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>-5.037231846603429</v>
+        <v>-6.412181273130146</v>
       </c>
       <c r="K13" t="n">
-        <v>8.300425101697574</v>
+        <v>8.290371306631972</v>
       </c>
       <c r="L13" t="n">
-        <v>23.4189376077676</v>
+        <v>12.30894614425559</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>181.5</v>
+        <v>139.6</v>
       </c>
       <c r="O13" t="n">
-        <v>45.7</v>
+        <v>48.1</v>
       </c>
       <c r="P13" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>22.513</v>
+        <v>12.004</v>
       </c>
       <c r="T13" t="n">
-        <v>22.513</v>
+        <v>11.714</v>
       </c>
       <c r="U13" t="n">
-        <v>50.99</v>
+        <v>11.372</v>
       </c>
       <c r="V13" t="n">
-        <v>43.499</v>
+        <v>21.903</v>
       </c>
       <c r="W13" t="n">
-        <v>-3.236</v>
+        <v>-0.584</v>
       </c>
     </row>
     <row r="14">
@@ -1601,7 +1589,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
+          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1629,14 +1617,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.00% / +1.41% / -2.45% | ASTOR.IS: +16.21% / +21.93% / 0.00% | BIMAS.IS: +0.96% / +3.13% / -0.86% | BRSAN.IS: +42.92% / +45.64% / -0.48% | CANTE.IS: +2.46% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: -1.34% / +1.41% / -3.86% | ASTOR.IS: +17.59% / +21.93% / 0.00% | BIMAS.IS: +1.45% / +3.13% / -0.86% | BRSAN.IS: +38.23% / +45.64% / -0.48% | CANTE.IS: +1.63% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>8.300425101697574</v>
+        <v>7.724959044865054</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1668,13 +1656,13 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>50.99</v>
+        <v>50.187</v>
       </c>
       <c r="V14" t="n">
-        <v>43.499</v>
+        <v>42.736</v>
       </c>
       <c r="W14" t="n">
-        <v>-3.236</v>
+        <v>-4.038</v>
       </c>
     </row>
     <row r="16">
@@ -1919,14 +1907,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.00% / +1.41% / -2.45% | BRSAN.IS: +13.62% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: -1.34% / +1.41% / -3.86% | BRSAN.IS: +9.89% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>8.204317234137148</v>
+        <v>6.587552695506349</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1958,13 +1946,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>95.93000000000001</v>
+        <v>93.002</v>
       </c>
       <c r="V19" t="n">
-        <v>55.639</v>
+        <v>53.313</v>
       </c>
       <c r="W19" t="n">
-        <v>-25.354</v>
+        <v>-28.282</v>
       </c>
     </row>
     <row r="20">
@@ -2206,7 +2194,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2239,14 +2227,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.00% / +1.41% / -2.45% | ASTOR.IS: +16.21% / +21.93% / 0.00% | BIMAS.IS: +0.96% / +3.13% / -0.86% | BRSAN.IS: +42.92% / +45.64% / -0.48% | CANTE.IS: +2.46% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: -1.34% / +1.41% / -3.86% | ASTOR.IS: +17.59% / +21.93% / 0.00% | BIMAS.IS: +1.45% / +3.13% / -0.86% | BRSAN.IS: +38.23% / +45.64% / -0.48% | CANTE.IS: +1.63% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K23" t="n">
-        <v>8.300425101697574</v>
+        <v>7.724959044865054</v>
       </c>
       <c r="L23" t="n">
         <v>23.4189376077676</v>
@@ -2278,13 +2266,13 @@
         <v>22.513</v>
       </c>
       <c r="U23" t="n">
-        <v>50.99</v>
+        <v>50.187</v>
       </c>
       <c r="V23" t="n">
-        <v>43.499</v>
+        <v>42.736</v>
       </c>
       <c r="W23" t="n">
-        <v>-3.236</v>
+        <v>-4.038</v>
       </c>
     </row>
     <row r="24">
@@ -2295,12 +2283,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
+          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2313,67 +2301,55 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>22.83095636113686</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>ALARK.IS: -2.00% / +1.41% / -2.45% | ASTOR.IS: +16.21% / +21.93% / 0.00% | BIMAS.IS: +0.96% / +3.13% / -0.86% | BRSAN.IS: +42.92% / +45.64% / -0.48% | CANTE.IS: +2.46% / +2.48% / -0.83%</t>
-        </is>
-      </c>
+        <v>12.43146471706449</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>-5.037231846603429</v>
+        <v>-6.412181273130146</v>
       </c>
       <c r="K24" t="n">
-        <v>8.300425101697574</v>
+        <v>8.290371306631972</v>
       </c>
       <c r="L24" t="n">
-        <v>23.4189376077676</v>
+        <v>12.30894614425559</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>181.5</v>
+        <v>139.6</v>
       </c>
       <c r="O24" t="n">
-        <v>45.7</v>
+        <v>48.1</v>
       </c>
       <c r="P24" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>22.513</v>
+        <v>12.004</v>
       </c>
       <c r="T24" t="n">
-        <v>22.513</v>
+        <v>11.714</v>
       </c>
       <c r="U24" t="n">
-        <v>50.99</v>
+        <v>11.372</v>
       </c>
       <c r="V24" t="n">
-        <v>43.499</v>
+        <v>21.903</v>
       </c>
       <c r="W24" t="n">
-        <v>-3.236</v>
+        <v>-0.584</v>
       </c>
     </row>
     <row r="25">
@@ -2417,14 +2393,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +7.94% / +9.99% / 0.00% | BSOKE.IS: -0.38% / +1.85% / -1.13% | CANTE.IS: +2.46% / +2.48% / 0.00%</t>
+          <t>BRSAN.IS: +4.40% / +9.99% / 0.00% | BSOKE.IS: -1.81% / +1.85% / -2.03% | CANTE.IS: +1.63% / +2.48% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K25" t="n">
-        <v>13.40628799511849</v>
+        <v>11.28206848072826</v>
       </c>
       <c r="L25" t="n">
         <v>7.902828022135555</v>
@@ -2456,13 +2432,13 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>13.664</v>
+        <v>11.535</v>
       </c>
       <c r="V25" t="n">
-        <v>12.665</v>
+        <v>10.554</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.162</v>
+        <v>-2.291</v>
       </c>
     </row>
   </sheetData>
@@ -3350,14 +3326,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.12% / +0.21% / -0.35% | ASTOR.IS: -1.41% / +0.37% / -2.12%</t>
+          <t>AKBNK.IS: -0.44% / +1.11% / -0.63% | ASTOR.IS: -0.24% / +1.47% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>20.16780582965436</v>
+        <v>20.54102655116912</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3369,7 +3345,7 @@
         <v>82.2</v>
       </c>
       <c r="O12" t="n">
-        <v>48.8</v>
+        <v>48.2</v>
       </c>
       <c r="P12" t="n">
         <v>3.6</v>
@@ -3389,13 +3365,13 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>50.34</v>
+        <v>50.807</v>
       </c>
       <c r="V12" t="n">
-        <v>27.061</v>
+        <v>27.456</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.978</v>
+        <v>-0.511</v>
       </c>
     </row>
     <row r="13">
@@ -3437,14 +3413,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.58% / +6.27% / -2.24% | ASTOR.IS: -1.41% / +0.37% / -2.12%</t>
+          <t>AKBNK.IS: +4.00% / +6.27% / -2.24% | ASTOR.IS: -0.24% / +1.47% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>19.47441328866748</v>
+        <v>19.85038426491912</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3476,13 +3452,13 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>50.566</v>
+        <v>51.04</v>
       </c>
       <c r="V13" t="n">
-        <v>39.505</v>
+        <v>39.944</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.981</v>
+        <v>-0.507</v>
       </c>
     </row>
     <row r="14">
@@ -3524,14 +3500,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.80% / +5.47% / -0.81% | BRSAN.IS: +12.18% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +3.22% / +5.47% / -0.81% | BRSAN.IS: +8.50% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>17.20233656228456</v>
+        <v>14.88956991496835</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3563,13 +3539,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>50.532</v>
+        <v>47.562</v>
       </c>
       <c r="V14" t="n">
-        <v>38.915</v>
+        <v>36.174</v>
       </c>
       <c r="W14" t="n">
-        <v>-10.421</v>
+        <v>-13.391</v>
       </c>
     </row>
     <row r="16">
@@ -4276,14 +4252,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.80% / +5.47% / -0.81% | BRSAN.IS: +12.18% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +3.22% / +5.47% / -0.81% | BRSAN.IS: +8.50% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>17.20233656228456</v>
+        <v>14.88956991496835</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4315,13 +4291,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>50.532</v>
+        <v>47.562</v>
       </c>
       <c r="V25" t="n">
-        <v>38.915</v>
+        <v>36.174</v>
       </c>
       <c r="W25" t="n">
-        <v>-10.421</v>
+        <v>-13.391</v>
       </c>
     </row>
     <row r="26">
@@ -4365,14 +4341,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.12% / +0.21% / -0.35% | ASTOR.IS: -1.41% / +0.37% / -2.12%</t>
+          <t>AKBNK.IS: -0.44% / +1.11% / -0.63% | ASTOR.IS: -0.24% / +1.47% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>20.16780582965436</v>
+        <v>20.54102655116912</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4384,7 +4360,7 @@
         <v>82.2</v>
       </c>
       <c r="O26" t="n">
-        <v>48.8</v>
+        <v>48.2</v>
       </c>
       <c r="P26" t="n">
         <v>3.6</v>
@@ -4404,13 +4380,13 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>50.34</v>
+        <v>50.807</v>
       </c>
       <c r="V26" t="n">
-        <v>27.061</v>
+        <v>27.456</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.978</v>
+        <v>-0.511</v>
       </c>
     </row>
     <row r="27">
@@ -4454,14 +4430,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.58% / +6.27% / -2.24% | ASTOR.IS: -1.41% / +0.37% / -2.12%</t>
+          <t>AKBNK.IS: +4.00% / +6.27% / -2.24% | ASTOR.IS: -0.24% / +1.47% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>19.47441328866748</v>
+        <v>19.85038426491912</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4493,13 +4469,13 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>50.566</v>
+        <v>51.04</v>
       </c>
       <c r="V27" t="n">
-        <v>39.505</v>
+        <v>39.944</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.981</v>
+        <v>-0.507</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -831,14 +831,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.34% / +1.41% / -3.86% | BRSAN.IS: +9.89% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: -1.15% / +1.41% / -3.86% | BRSAN.IS: +9.12% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>6.587552695506349</v>
+        <v>6.284471228954547</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -870,13 +870,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>93.002</v>
+        <v>92.453</v>
       </c>
       <c r="V4" t="n">
-        <v>53.313</v>
+        <v>52.877</v>
       </c>
       <c r="W4" t="n">
-        <v>-28.282</v>
+        <v>-28.831</v>
       </c>
     </row>
     <row r="5">
@@ -1068,14 +1068,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.34% / +1.41% / -3.86% | BRSAN.IS: +9.89% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: -1.15% / +1.41% / -3.86% | BRSAN.IS: +9.12% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>6.587552695506349</v>
+        <v>6.284471228954547</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1107,13 +1107,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>93.002</v>
+        <v>92.453</v>
       </c>
       <c r="V7" t="n">
-        <v>53.313</v>
+        <v>52.877</v>
       </c>
       <c r="W7" t="n">
-        <v>-28.282</v>
+        <v>-28.831</v>
       </c>
     </row>
     <row r="8">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +4.40% / +9.99% / 0.00% | BSOKE.IS: -1.81% / +1.85% / -2.03% | CANTE.IS: +1.63% / +2.48% / 0.00%</t>
+          <t>BRSAN.IS: +3.67% / +9.99% / 0.00% | BSOKE.IS: -1.39% / +1.85% / -2.87% | CANTE.IS: -0.02% / +2.48% / 0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K12" t="n">
-        <v>11.28206848072826</v>
+        <v>10.56567961570272</v>
       </c>
       <c r="L12" t="n">
         <v>7.902828022135555</v>
@@ -1474,7 +1474,7 @@
         <v>33.5</v>
       </c>
       <c r="O12" t="n">
-        <v>47.1</v>
+        <v>45.6</v>
       </c>
       <c r="P12" t="n">
         <v>4.4</v>
@@ -1494,13 +1494,13 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>11.535</v>
+        <v>10.817</v>
       </c>
       <c r="V12" t="n">
-        <v>10.554</v>
+        <v>9.843</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.291</v>
+        <v>-3.009</v>
       </c>
     </row>
     <row r="13">
@@ -1617,14 +1617,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.34% / +1.41% / -3.86% | ASTOR.IS: +17.59% / +21.93% / 0.00% | BIMAS.IS: +1.45% / +3.13% / -0.86% | BRSAN.IS: +38.23% / +45.64% / -0.48% | CANTE.IS: +1.63% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: -1.15% / +1.41% / -3.86% | ASTOR.IS: +17.42% / +21.93% / 0.00% | BIMAS.IS: +2.25% / +3.13% / -0.86% | BRSAN.IS: +37.27% / +45.64% / -0.48% | CANTE.IS: -0.02% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>7.724959044865054</v>
+        <v>7.355761010910378</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1636,7 +1636,7 @@
         <v>181.5</v>
       </c>
       <c r="O14" t="n">
-        <v>45.7</v>
+        <v>45.4</v>
       </c>
       <c r="P14" t="n">
         <v>5.5</v>
@@ -1656,13 +1656,13 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>50.187</v>
+        <v>49.673</v>
       </c>
       <c r="V14" t="n">
-        <v>42.736</v>
+        <v>42.247</v>
       </c>
       <c r="W14" t="n">
-        <v>-4.038</v>
+        <v>-4.553</v>
       </c>
     </row>
     <row r="16">
@@ -1907,14 +1907,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.34% / +1.41% / -3.86% | BRSAN.IS: +9.89% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: -1.15% / +1.41% / -3.86% | BRSAN.IS: +9.12% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>6.587552695506349</v>
+        <v>6.284471228954547</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1946,13 +1946,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>93.002</v>
+        <v>92.453</v>
       </c>
       <c r="V19" t="n">
-        <v>53.313</v>
+        <v>52.877</v>
       </c>
       <c r="W19" t="n">
-        <v>-28.282</v>
+        <v>-28.831</v>
       </c>
     </row>
     <row r="20">
@@ -2227,14 +2227,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.34% / +1.41% / -3.86% | ASTOR.IS: +17.59% / +21.93% / 0.00% | BIMAS.IS: +1.45% / +3.13% / -0.86% | BRSAN.IS: +38.23% / +45.64% / -0.48% | CANTE.IS: +1.63% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: -1.15% / +1.41% / -3.86% | ASTOR.IS: +17.42% / +21.93% / 0.00% | BIMAS.IS: +2.25% / +3.13% / -0.86% | BRSAN.IS: +37.27% / +45.64% / -0.48% | CANTE.IS: -0.02% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K23" t="n">
-        <v>7.724959044865054</v>
+        <v>7.355761010910378</v>
       </c>
       <c r="L23" t="n">
         <v>23.4189376077676</v>
@@ -2246,7 +2246,7 @@
         <v>181.5</v>
       </c>
       <c r="O23" t="n">
-        <v>45.7</v>
+        <v>45.4</v>
       </c>
       <c r="P23" t="n">
         <v>5.5</v>
@@ -2266,13 +2266,13 @@
         <v>22.513</v>
       </c>
       <c r="U23" t="n">
-        <v>50.187</v>
+        <v>49.673</v>
       </c>
       <c r="V23" t="n">
-        <v>42.736</v>
+        <v>42.247</v>
       </c>
       <c r="W23" t="n">
-        <v>-4.038</v>
+        <v>-4.553</v>
       </c>
     </row>
     <row r="24">
@@ -2393,14 +2393,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +4.40% / +9.99% / 0.00% | BSOKE.IS: -1.81% / +1.85% / -2.03% | CANTE.IS: +1.63% / +2.48% / 0.00%</t>
+          <t>BRSAN.IS: +3.67% / +9.99% / 0.00% | BSOKE.IS: -1.39% / +1.85% / -2.87% | CANTE.IS: -0.02% / +2.48% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K25" t="n">
-        <v>11.28206848072826</v>
+        <v>10.56567961570272</v>
       </c>
       <c r="L25" t="n">
         <v>7.902828022135555</v>
@@ -2412,7 +2412,7 @@
         <v>33.5</v>
       </c>
       <c r="O25" t="n">
-        <v>47.1</v>
+        <v>45.6</v>
       </c>
       <c r="P25" t="n">
         <v>4.4</v>
@@ -2432,13 +2432,13 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>11.535</v>
+        <v>10.817</v>
       </c>
       <c r="V25" t="n">
-        <v>10.554</v>
+        <v>9.843</v>
       </c>
       <c r="W25" t="n">
-        <v>-2.291</v>
+        <v>-3.009</v>
       </c>
     </row>
   </sheetData>
@@ -3326,14 +3326,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.44% / +1.11% / -0.63% | ASTOR.IS: -0.24% / +1.47% / -2.12%</t>
+          <t>AKBNK.IS: -0.44% / +1.11% / -0.90% | ASTOR.IS: -0.39% / +1.47% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>20.54102655116912</v>
+        <v>20.45243641414827</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3365,13 +3365,13 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>50.807</v>
+        <v>50.696</v>
       </c>
       <c r="V12" t="n">
-        <v>27.456</v>
+        <v>27.362</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.511</v>
+        <v>-0.622</v>
       </c>
     </row>
     <row r="13">
@@ -3413,14 +3413,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.00% / +6.27% / -2.24% | ASTOR.IS: -0.24% / +1.47% / -2.12%</t>
+          <t>AKBNK.IS: +4.00% / +6.27% / -2.24% | ASTOR.IS: -0.39% / +1.47% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>19.85038426491912</v>
+        <v>19.76229567591343</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3452,13 +3452,13 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>51.04</v>
+        <v>50.929</v>
       </c>
       <c r="V13" t="n">
-        <v>39.944</v>
+        <v>39.841</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.507</v>
+        <v>-0.618</v>
       </c>
     </row>
     <row r="14">
@@ -3500,14 +3500,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.22% / +5.47% / -0.81% | BRSAN.IS: +8.50% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +3.22% / +5.47% / -0.81% | BRSAN.IS: +7.75% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>14.88956991496835</v>
+        <v>14.48127176174996</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3539,13 +3539,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>47.562</v>
+        <v>47.037</v>
       </c>
       <c r="V14" t="n">
-        <v>36.174</v>
+        <v>35.69</v>
       </c>
       <c r="W14" t="n">
-        <v>-13.391</v>
+        <v>-13.915</v>
       </c>
     </row>
     <row r="16">
@@ -4252,14 +4252,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.22% / +5.47% / -0.81% | BRSAN.IS: +8.50% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +3.22% / +5.47% / -0.81% | BRSAN.IS: +7.75% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>14.88956991496835</v>
+        <v>14.48127176174996</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4291,13 +4291,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>47.562</v>
+        <v>47.037</v>
       </c>
       <c r="V25" t="n">
-        <v>36.174</v>
+        <v>35.69</v>
       </c>
       <c r="W25" t="n">
-        <v>-13.391</v>
+        <v>-13.915</v>
       </c>
     </row>
     <row r="26">
@@ -4341,14 +4341,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.44% / +1.11% / -0.63% | ASTOR.IS: -0.24% / +1.47% / -2.12%</t>
+          <t>AKBNK.IS: -0.44% / +1.11% / -0.90% | ASTOR.IS: -0.39% / +1.47% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>20.54102655116912</v>
+        <v>20.45243641414827</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4380,13 +4380,13 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>50.807</v>
+        <v>50.696</v>
       </c>
       <c r="V26" t="n">
-        <v>27.456</v>
+        <v>27.362</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.511</v>
+        <v>-0.622</v>
       </c>
     </row>
     <row r="27">
@@ -4430,14 +4430,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.00% / +6.27% / -2.24% | ASTOR.IS: -0.24% / +1.47% / -2.12%</t>
+          <t>AKBNK.IS: +4.00% / +6.27% / -2.24% | ASTOR.IS: -0.39% / +1.47% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>19.85038426491912</v>
+        <v>19.76229567591343</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4469,13 +4469,13 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>51.04</v>
+        <v>50.929</v>
       </c>
       <c r="V27" t="n">
-        <v>39.944</v>
+        <v>39.841</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.507</v>
+        <v>-0.618</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -831,14 +831,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.15% / +1.41% / -3.86% | BRSAN.IS: +9.12% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: -0.40% / +1.41% / -3.86% | BRSAN.IS: +10.04% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>6.284471228954547</v>
+        <v>7.137245628942024</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -870,13 +870,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>92.453</v>
+        <v>93.998</v>
       </c>
       <c r="V4" t="n">
-        <v>52.877</v>
+        <v>54.104</v>
       </c>
       <c r="W4" t="n">
-        <v>-28.831</v>
+        <v>-27.286</v>
       </c>
     </row>
     <row r="5">
@@ -1068,14 +1068,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.15% / +1.41% / -3.86% | BRSAN.IS: +9.12% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: -0.40% / +1.41% / -3.86% | BRSAN.IS: +10.04% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>6.284471228954547</v>
+        <v>7.137245628942024</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1107,13 +1107,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>92.453</v>
+        <v>93.998</v>
       </c>
       <c r="V7" t="n">
-        <v>52.877</v>
+        <v>54.104</v>
       </c>
       <c r="W7" t="n">
-        <v>-28.831</v>
+        <v>-27.286</v>
       </c>
     </row>
     <row r="8">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +3.67% / +9.99% / 0.00% | BSOKE.IS: -1.39% / +1.85% / -2.87% | CANTE.IS: -0.02% / +2.48% / 0.00%</t>
+          <t>BRSAN.IS: +4.54% / +9.99% / 0.00% | BSOKE.IS: -1.87% / +1.85% / -2.87% | CANTE.IS: -0.02% / +2.48% / 0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K12" t="n">
-        <v>10.56567961570272</v>
+        <v>10.70882469769458</v>
       </c>
       <c r="L12" t="n">
         <v>7.902828022135555</v>
@@ -1494,13 +1494,13 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>10.817</v>
+        <v>10.961</v>
       </c>
       <c r="V12" t="n">
-        <v>9.843</v>
+        <v>9.984999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>-3.009</v>
+        <v>-2.865</v>
       </c>
     </row>
     <row r="13">
@@ -1617,14 +1617,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.15% / +1.41% / -3.86% | ASTOR.IS: +17.42% / +21.93% / 0.00% | BIMAS.IS: +2.25% / +3.13% / -0.86% | BRSAN.IS: +37.27% / +45.64% / -0.48% | CANTE.IS: -0.02% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: -0.40% / +1.41% / -3.86% | ASTOR.IS: +17.08% / +21.93% / 0.00% | BIMAS.IS: +2.56% / +3.13% / -0.86% | BRSAN.IS: +38.42% / +45.64% / -0.48% | CANTE.IS: -0.02% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>7.355761010910378</v>
+        <v>7.717311087982681</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1656,13 +1656,13 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>49.673</v>
+        <v>50.177</v>
       </c>
       <c r="V14" t="n">
-        <v>42.247</v>
+        <v>42.726</v>
       </c>
       <c r="W14" t="n">
-        <v>-4.553</v>
+        <v>-4.049</v>
       </c>
     </row>
     <row r="16">
@@ -1907,14 +1907,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.15% / +1.41% / -3.86% | BRSAN.IS: +9.12% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: -0.40% / +1.41% / -3.86% | BRSAN.IS: +10.04% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>6.284471228954547</v>
+        <v>7.137245628942024</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1946,13 +1946,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>92.453</v>
+        <v>93.998</v>
       </c>
       <c r="V19" t="n">
-        <v>52.877</v>
+        <v>54.104</v>
       </c>
       <c r="W19" t="n">
-        <v>-28.831</v>
+        <v>-27.286</v>
       </c>
     </row>
     <row r="20">
@@ -2227,14 +2227,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.15% / +1.41% / -3.86% | ASTOR.IS: +17.42% / +21.93% / 0.00% | BIMAS.IS: +2.25% / +3.13% / -0.86% | BRSAN.IS: +37.27% / +45.64% / -0.48% | CANTE.IS: -0.02% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: -0.40% / +1.41% / -3.86% | ASTOR.IS: +17.08% / +21.93% / 0.00% | BIMAS.IS: +2.56% / +3.13% / -0.86% | BRSAN.IS: +38.42% / +45.64% / -0.48% | CANTE.IS: -0.02% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K23" t="n">
-        <v>7.355761010910378</v>
+        <v>7.717311087982681</v>
       </c>
       <c r="L23" t="n">
         <v>23.4189376077676</v>
@@ -2266,13 +2266,13 @@
         <v>22.513</v>
       </c>
       <c r="U23" t="n">
-        <v>49.673</v>
+        <v>50.177</v>
       </c>
       <c r="V23" t="n">
-        <v>42.247</v>
+        <v>42.726</v>
       </c>
       <c r="W23" t="n">
-        <v>-4.553</v>
+        <v>-4.049</v>
       </c>
     </row>
     <row r="24">
@@ -2393,14 +2393,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +3.67% / +9.99% / 0.00% | BSOKE.IS: -1.39% / +1.85% / -2.87% | CANTE.IS: -0.02% / +2.48% / 0.00%</t>
+          <t>BRSAN.IS: +4.54% / +9.99% / 0.00% | BSOKE.IS: -1.87% / +1.85% / -2.87% | CANTE.IS: -0.02% / +2.48% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K25" t="n">
-        <v>10.56567961570272</v>
+        <v>10.70882469769458</v>
       </c>
       <c r="L25" t="n">
         <v>7.902828022135555</v>
@@ -2432,13 +2432,13 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>10.817</v>
+        <v>10.961</v>
       </c>
       <c r="V25" t="n">
-        <v>9.843</v>
+        <v>9.984999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>-3.009</v>
+        <v>-2.865</v>
       </c>
     </row>
   </sheetData>
@@ -3326,14 +3326,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.44% / +1.11% / -0.90% | ASTOR.IS: -0.39% / +1.47% / -2.12%</t>
+          <t>AKBNK.IS: -0.16% / +1.11% / -0.90% | ASTOR.IS: -0.68% / +1.47% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>20.45243641414827</v>
+        <v>20.44300632743263</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3365,13 +3365,13 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>50.696</v>
+        <v>50.685</v>
       </c>
       <c r="V12" t="n">
-        <v>27.362</v>
+        <v>27.352</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.622</v>
+        <v>-0.634</v>
       </c>
     </row>
     <row r="13">
@@ -3413,14 +3413,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.00% / +6.27% / -2.24% | ASTOR.IS: -0.39% / +1.47% / -2.12%</t>
+          <t>AKBNK.IS: +4.29% / +6.27% / -2.24% | ASTOR.IS: -0.68% / +1.47% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>19.76229567591343</v>
+        <v>19.75048736579896</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3452,13 +3452,13 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>50.929</v>
+        <v>50.914</v>
       </c>
       <c r="V13" t="n">
-        <v>39.841</v>
+        <v>39.827</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.618</v>
+        <v>-0.633</v>
       </c>
     </row>
     <row r="14">
@@ -3500,14 +3500,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.22% / +5.47% / -0.81% | BRSAN.IS: +7.75% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +3.51% / +5.47% / -0.81% | BRSAN.IS: +8.65% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>14.48127176174996</v>
+        <v>15.12728239388508</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3539,13 +3539,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>47.037</v>
+        <v>47.867</v>
       </c>
       <c r="V14" t="n">
-        <v>35.69</v>
+        <v>36.456</v>
       </c>
       <c r="W14" t="n">
-        <v>-13.915</v>
+        <v>-13.086</v>
       </c>
     </row>
     <row r="16">
@@ -4252,14 +4252,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.22% / +5.47% / -0.81% | BRSAN.IS: +7.75% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +3.51% / +5.47% / -0.81% | BRSAN.IS: +8.65% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>14.48127176174996</v>
+        <v>15.12728239388508</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4291,13 +4291,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>47.037</v>
+        <v>47.867</v>
       </c>
       <c r="V25" t="n">
-        <v>35.69</v>
+        <v>36.456</v>
       </c>
       <c r="W25" t="n">
-        <v>-13.915</v>
+        <v>-13.086</v>
       </c>
     </row>
     <row r="26">
@@ -4341,14 +4341,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.44% / +1.11% / -0.90% | ASTOR.IS: -0.39% / +1.47% / -2.12%</t>
+          <t>AKBNK.IS: -0.16% / +1.11% / -0.90% | ASTOR.IS: -0.68% / +1.47% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>20.45243641414827</v>
+        <v>20.44300632743263</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4380,13 +4380,13 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>50.696</v>
+        <v>50.685</v>
       </c>
       <c r="V26" t="n">
-        <v>27.362</v>
+        <v>27.352</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.622</v>
+        <v>-0.634</v>
       </c>
     </row>
     <row r="27">
@@ -4430,14 +4430,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.00% / +6.27% / -2.24% | ASTOR.IS: -0.39% / +1.47% / -2.12%</t>
+          <t>AKBNK.IS: +4.29% / +6.27% / -2.24% | ASTOR.IS: -0.68% / +1.47% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>19.76229567591343</v>
+        <v>19.75048736579896</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4469,13 +4469,13 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>50.929</v>
+        <v>50.914</v>
       </c>
       <c r="V27" t="n">
-        <v>39.841</v>
+        <v>39.827</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.618</v>
+        <v>-0.633</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -760,7 +760,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>117.4</v>
+        <v>117.1</v>
       </c>
       <c r="O3" t="n">
         <v>39.9</v>
@@ -783,13 +783,13 @@
         <v>28.567</v>
       </c>
       <c r="U3" t="n">
-        <v>71.535</v>
+        <v>72.258</v>
       </c>
       <c r="V3" t="n">
         <v>41.769</v>
       </c>
       <c r="W3" t="n">
-        <v>-68.599</v>
+        <v>-68.88800000000001</v>
       </c>
     </row>
     <row r="4">
@@ -808,12 +808,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -831,14 +831,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.40% / +1.41% / -3.86% | BRSAN.IS: +10.04% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +0.07% / +1.41% / -3.86% | BRSAN.IS: +9.35% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>7.137245628942024</v>
+        <v>7.01495881275207</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -847,10 +847,10 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>121.3</v>
+        <v>121.1</v>
       </c>
       <c r="O4" t="n">
-        <v>43.1</v>
+        <v>43.5</v>
       </c>
       <c r="P4" t="n">
         <v>5.9</v>
@@ -870,13 +870,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>93.998</v>
+        <v>90.3</v>
       </c>
       <c r="V4" t="n">
-        <v>54.104</v>
+        <v>53.928</v>
       </c>
       <c r="W4" t="n">
-        <v>-27.286</v>
+        <v>-27.014</v>
       </c>
     </row>
     <row r="5">
@@ -895,12 +895,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>93.7</v>
+        <v>93.5</v>
       </c>
       <c r="O5" t="n">
         <v>37.4</v>
@@ -945,13 +945,13 @@
         <v>35.687</v>
       </c>
       <c r="U5" t="n">
-        <v>22.887</v>
+        <v>18.143</v>
       </c>
       <c r="V5" t="n">
         <v>12.323</v>
       </c>
       <c r="W5" t="n">
-        <v>-68.19</v>
+        <v>-65.557</v>
       </c>
     </row>
     <row r="6">
@@ -970,12 +970,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -997,7 +997,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>117.4</v>
+        <v>117.1</v>
       </c>
       <c r="O6" t="n">
         <v>39.9</v>
@@ -1020,13 +1020,13 @@
         <v>28.567</v>
       </c>
       <c r="U6" t="n">
-        <v>71.535</v>
+        <v>72.258</v>
       </c>
       <c r="V6" t="n">
         <v>41.769</v>
       </c>
       <c r="W6" t="n">
-        <v>-68.599</v>
+        <v>-68.88800000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1068,14 +1068,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.40% / +1.41% / -3.86% | BRSAN.IS: +10.04% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +0.07% / +1.41% / -3.86% | BRSAN.IS: +9.35% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>7.137245628942024</v>
+        <v>7.01495881275207</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1084,10 +1084,10 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>121.3</v>
+        <v>121.1</v>
       </c>
       <c r="O7" t="n">
-        <v>43.1</v>
+        <v>43.5</v>
       </c>
       <c r="P7" t="n">
         <v>5.9</v>
@@ -1107,13 +1107,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>93.998</v>
+        <v>90.3</v>
       </c>
       <c r="V7" t="n">
-        <v>54.104</v>
+        <v>53.928</v>
       </c>
       <c r="W7" t="n">
-        <v>-27.286</v>
+        <v>-27.014</v>
       </c>
     </row>
     <row r="8">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -1159,7 +1159,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N8" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="O8" t="n">
         <v>51.1</v>
@@ -1182,13 +1182,13 @@
         <v>29.993</v>
       </c>
       <c r="U8" t="n">
-        <v>6.3</v>
+        <v>1.107</v>
       </c>
       <c r="V8" t="n">
         <v>-6.769</v>
       </c>
       <c r="W8" t="n">
-        <v>-45.045</v>
+        <v>-42.845</v>
       </c>
     </row>
     <row r="9">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1234,7 +1234,7 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>117.4</v>
+        <v>117.1</v>
       </c>
       <c r="O9" t="n">
         <v>39.9</v>
@@ -1257,13 +1257,13 @@
         <v>28.567</v>
       </c>
       <c r="U9" t="n">
-        <v>71.535</v>
+        <v>72.258</v>
       </c>
       <c r="V9" t="n">
         <v>41.769</v>
       </c>
       <c r="W9" t="n">
-        <v>-68.599</v>
+        <v>-68.88800000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1309,7 +1309,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="O10" t="n">
         <v>51.1</v>
@@ -1332,13 +1332,13 @@
         <v>29.993</v>
       </c>
       <c r="U10" t="n">
-        <v>6.3</v>
+        <v>1.107</v>
       </c>
       <c r="V10" t="n">
         <v>-6.769</v>
       </c>
       <c r="W10" t="n">
-        <v>-45.045</v>
+        <v>-42.845</v>
       </c>
     </row>
     <row r="11">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>72</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>38.4</v>
@@ -1407,13 +1407,13 @@
         <v>29.287</v>
       </c>
       <c r="U11" t="n">
-        <v>36.452</v>
+        <v>32.864</v>
       </c>
       <c r="V11" t="n">
         <v>14.374</v>
       </c>
       <c r="W11" t="n">
-        <v>-48.499</v>
+        <v>-47.224</v>
       </c>
     </row>
     <row r="12">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +4.54% / +9.99% / 0.00% | BSOKE.IS: -1.87% / +1.85% / -2.87% | CANTE.IS: -0.02% / +2.48% / 0.00%</t>
+          <t>BRSAN.IS: +3.89% / +9.99% / 0.00% | BSOKE.IS: -2.23% / +1.85% / -2.87% | CANTE.IS: +0.81% / +2.48% / 0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K12" t="n">
-        <v>10.70882469769458</v>
+        <v>10.64158979326142</v>
       </c>
       <c r="L12" t="n">
         <v>7.902828022135555</v>
@@ -1474,10 +1474,10 @@
         <v>33.5</v>
       </c>
       <c r="O12" t="n">
-        <v>45.6</v>
+        <v>47.1</v>
       </c>
       <c r="P12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1494,13 +1494,13 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>10.961</v>
+        <v>10.893</v>
       </c>
       <c r="V12" t="n">
-        <v>9.984999999999999</v>
+        <v>9.917999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.865</v>
+        <v>-2.933</v>
       </c>
     </row>
     <row r="13">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1546,7 +1546,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>139.6</v>
+        <v>139.3</v>
       </c>
       <c r="O13" t="n">
         <v>48.1</v>
@@ -1569,13 +1569,13 @@
         <v>11.714</v>
       </c>
       <c r="U13" t="n">
-        <v>11.372</v>
+        <v>11.106</v>
       </c>
       <c r="V13" t="n">
         <v>21.903</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.584</v>
+        <v>-0.583</v>
       </c>
     </row>
     <row r="14">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1617,14 +1617,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.40% / +1.41% / -3.86% | ASTOR.IS: +17.08% / +21.93% / 0.00% | BIMAS.IS: +2.56% / +3.13% / -0.86% | BRSAN.IS: +38.42% / +45.64% / -0.48% | CANTE.IS: -0.02% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +0.07% / +1.41% / -3.86% | ASTOR.IS: +17.77% / +21.93% / 0.00% | BIMAS.IS: +1.76% / +3.13% / -0.86% | BRSAN.IS: +37.56% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>7.717311087982681</v>
+        <v>7.809503294389053</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1633,10 +1633,10 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>181.5</v>
+        <v>181.1</v>
       </c>
       <c r="O14" t="n">
-        <v>45.4</v>
+        <v>45.9</v>
       </c>
       <c r="P14" t="n">
         <v>5.5</v>
@@ -1656,13 +1656,13 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>50.177</v>
+        <v>46.528</v>
       </c>
       <c r="V14" t="n">
-        <v>42.726</v>
+        <v>42.848</v>
       </c>
       <c r="W14" t="n">
-        <v>-4.049</v>
+        <v>-3.822</v>
       </c>
     </row>
     <row r="16">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1834,7 +1834,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>117.4</v>
+        <v>117.1</v>
       </c>
       <c r="O18" t="n">
         <v>39.9</v>
@@ -1857,13 +1857,13 @@
         <v>28.567</v>
       </c>
       <c r="U18" t="n">
-        <v>71.535</v>
+        <v>72.258</v>
       </c>
       <c r="V18" t="n">
         <v>41.769</v>
       </c>
       <c r="W18" t="n">
-        <v>-68.599</v>
+        <v>-68.88800000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1907,14 +1907,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.40% / +1.41% / -3.86% | BRSAN.IS: +10.04% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +0.07% / +1.41% / -3.86% | BRSAN.IS: +9.35% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>7.137245628942024</v>
+        <v>7.01495881275207</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1923,10 +1923,10 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>121.3</v>
+        <v>121.1</v>
       </c>
       <c r="O19" t="n">
-        <v>43.1</v>
+        <v>43.5</v>
       </c>
       <c r="P19" t="n">
         <v>5.9</v>
@@ -1946,13 +1946,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>93.998</v>
+        <v>90.3</v>
       </c>
       <c r="V19" t="n">
-        <v>54.104</v>
+        <v>53.928</v>
       </c>
       <c r="W19" t="n">
-        <v>-27.286</v>
+        <v>-27.014</v>
       </c>
     </row>
     <row r="20">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>93.7</v>
+        <v>93.5</v>
       </c>
       <c r="O20" t="n">
         <v>37.4</v>
@@ -2023,13 +2023,13 @@
         <v>35.687</v>
       </c>
       <c r="U20" t="n">
-        <v>22.887</v>
+        <v>18.143</v>
       </c>
       <c r="V20" t="n">
         <v>12.323</v>
       </c>
       <c r="W20" t="n">
-        <v>-68.19</v>
+        <v>-65.557</v>
       </c>
     </row>
     <row r="21">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N21" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="O21" t="n">
         <v>51.1</v>
@@ -2100,13 +2100,13 @@
         <v>29.993</v>
       </c>
       <c r="U21" t="n">
-        <v>6.3</v>
+        <v>1.107</v>
       </c>
       <c r="V21" t="n">
         <v>-6.769</v>
       </c>
       <c r="W21" t="n">
-        <v>-45.045</v>
+        <v>-42.845</v>
       </c>
     </row>
     <row r="22">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2154,7 +2154,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>72</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O22" t="n">
         <v>38.4</v>
@@ -2177,13 +2177,13 @@
         <v>29.287</v>
       </c>
       <c r="U22" t="n">
-        <v>36.452</v>
+        <v>32.864</v>
       </c>
       <c r="V22" t="n">
         <v>14.374</v>
       </c>
       <c r="W22" t="n">
-        <v>-48.499</v>
+        <v>-47.224</v>
       </c>
     </row>
     <row r="23">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2227,14 +2227,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.40% / +1.41% / -3.86% | ASTOR.IS: +17.08% / +21.93% / 0.00% | BIMAS.IS: +2.56% / +3.13% / -0.86% | BRSAN.IS: +38.42% / +45.64% / -0.48% | CANTE.IS: -0.02% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +0.07% / +1.41% / -3.86% | ASTOR.IS: +17.77% / +21.93% / 0.00% | BIMAS.IS: +1.76% / +3.13% / -0.86% | BRSAN.IS: +37.56% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K23" t="n">
-        <v>7.717311087982681</v>
+        <v>7.809503294389053</v>
       </c>
       <c r="L23" t="n">
         <v>23.4189376077676</v>
@@ -2243,10 +2243,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>181.5</v>
+        <v>181.1</v>
       </c>
       <c r="O23" t="n">
-        <v>45.4</v>
+        <v>45.9</v>
       </c>
       <c r="P23" t="n">
         <v>5.5</v>
@@ -2266,13 +2266,13 @@
         <v>22.513</v>
       </c>
       <c r="U23" t="n">
-        <v>50.177</v>
+        <v>46.528</v>
       </c>
       <c r="V23" t="n">
-        <v>42.726</v>
+        <v>42.848</v>
       </c>
       <c r="W23" t="n">
-        <v>-4.049</v>
+        <v>-3.822</v>
       </c>
     </row>
     <row r="24">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2320,7 +2320,7 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>139.6</v>
+        <v>139.3</v>
       </c>
       <c r="O24" t="n">
         <v>48.1</v>
@@ -2343,13 +2343,13 @@
         <v>11.714</v>
       </c>
       <c r="U24" t="n">
-        <v>11.372</v>
+        <v>11.106</v>
       </c>
       <c r="V24" t="n">
         <v>21.903</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.584</v>
+        <v>-0.583</v>
       </c>
     </row>
     <row r="25">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2393,14 +2393,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +4.54% / +9.99% / 0.00% | BSOKE.IS: -1.87% / +1.85% / -2.87% | CANTE.IS: -0.02% / +2.48% / 0.00%</t>
+          <t>BRSAN.IS: +3.89% / +9.99% / 0.00% | BSOKE.IS: -2.23% / +1.85% / -2.87% | CANTE.IS: +0.81% / +2.48% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K25" t="n">
-        <v>10.70882469769458</v>
+        <v>10.64158979326142</v>
       </c>
       <c r="L25" t="n">
         <v>7.902828022135555</v>
@@ -2412,10 +2412,10 @@
         <v>33.5</v>
       </c>
       <c r="O25" t="n">
-        <v>45.6</v>
+        <v>47.1</v>
       </c>
       <c r="P25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2432,13 +2432,13 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>10.961</v>
+        <v>10.893</v>
       </c>
       <c r="V25" t="n">
-        <v>9.984999999999999</v>
+        <v>9.917999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>-2.865</v>
+        <v>-2.933</v>
       </c>
     </row>
   </sheetData>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2655,7 +2655,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
       <c r="O3" t="n">
         <v>45.9</v>
@@ -2678,13 +2678,13 @@
         <v>31.839</v>
       </c>
       <c r="U3" t="n">
-        <v>16.523</v>
+        <v>11.666</v>
       </c>
       <c r="V3" t="n">
         <v>27.773</v>
       </c>
       <c r="W3" t="n">
-        <v>-54.429</v>
+        <v>-52.161</v>
       </c>
     </row>
     <row r="4">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2730,7 +2730,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N4" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="O4" t="n">
         <v>46.7</v>
@@ -2753,13 +2753,13 @@
         <v>30.704</v>
       </c>
       <c r="U4" t="n">
-        <v>3.325</v>
+        <v>-0.924</v>
       </c>
       <c r="V4" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>-45.782</v>
+        <v>-43.899</v>
       </c>
     </row>
     <row r="5">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -2805,7 +2805,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="O5" t="n">
         <v>46.7</v>
@@ -2828,13 +2828,13 @@
         <v>30.704</v>
       </c>
       <c r="U5" t="n">
-        <v>3.325</v>
+        <v>-0.924</v>
       </c>
       <c r="V5" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-45.782</v>
+        <v>-43.899</v>
       </c>
     </row>
     <row r="6">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -2880,7 +2880,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="O6" t="n">
         <v>46.7</v>
@@ -2903,13 +2903,13 @@
         <v>30.704</v>
       </c>
       <c r="U6" t="n">
-        <v>3.325</v>
+        <v>-0.924</v>
       </c>
       <c r="V6" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>-45.782</v>
+        <v>-43.899</v>
       </c>
     </row>
     <row r="7">
@@ -2928,12 +2928,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N7" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="O7" t="n">
         <v>46.7</v>
@@ -2978,13 +2978,13 @@
         <v>30.704</v>
       </c>
       <c r="U7" t="n">
-        <v>3.325</v>
+        <v>-0.924</v>
       </c>
       <c r="V7" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>-45.782</v>
+        <v>-43.899</v>
       </c>
     </row>
     <row r="8">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -3030,7 +3030,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>110.9</v>
+        <v>110.7</v>
       </c>
       <c r="O8" t="n">
         <v>38.4</v>
@@ -3053,13 +3053,13 @@
         <v>28.888</v>
       </c>
       <c r="U8" t="n">
-        <v>38.772</v>
+        <v>41.398</v>
       </c>
       <c r="V8" t="n">
         <v>14.358</v>
       </c>
       <c r="W8" t="n">
-        <v>-56.373</v>
+        <v>-57.44</v>
       </c>
     </row>
     <row r="9">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="N9" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="O9" t="n">
         <v>57.4</v>
@@ -3153,12 +3153,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3180,7 +3180,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="O10" t="n">
         <v>45.7</v>
@@ -3203,13 +3203,13 @@
         <v>13.513</v>
       </c>
       <c r="U10" t="n">
-        <v>14.92</v>
+        <v>12.231</v>
       </c>
       <c r="V10" t="n">
         <v>13.389</v>
       </c>
       <c r="W10" t="n">
-        <v>-17.227</v>
+        <v>-16.824</v>
       </c>
     </row>
     <row r="11">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3255,7 +3255,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="O11" t="n">
         <v>44.2</v>
@@ -3278,13 +3278,13 @@
         <v>13.42</v>
       </c>
       <c r="U11" t="n">
-        <v>19.007</v>
+        <v>16.222</v>
       </c>
       <c r="V11" t="n">
         <v>12.908</v>
       </c>
       <c r="W11" t="n">
-        <v>-18.447</v>
+        <v>-18.015</v>
       </c>
     </row>
     <row r="12">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3326,14 +3326,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.16% / +1.11% / -0.90% | ASTOR.IS: -0.68% / +1.47% / -2.12%</t>
+          <t>AKBNK.IS: +0.95% / +1.11% / -0.90% | ASTOR.IS: -0.09% / +1.47% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>20.44300632743263</v>
+        <v>21.46838041596748</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3342,10 +3342,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N12" t="n">
-        <v>82.2</v>
+        <v>82</v>
       </c>
       <c r="O12" t="n">
-        <v>48.2</v>
+        <v>48.8</v>
       </c>
       <c r="P12" t="n">
         <v>3.6</v>
@@ -3365,13 +3365,13 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>50.685</v>
+        <v>45.194</v>
       </c>
       <c r="V12" t="n">
-        <v>27.352</v>
+        <v>28.437</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3390,14 +3390,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>AKBNK.IS, ASTOR.IS</t>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-14 | ASTOR.IS: 2026-08-24</t>
+          <t>AKBNK.IS: 2026-08-26 | ASTOR.IS: 2026-08-24</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -3413,14 +3413,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.29% / +6.27% / -2.24% | ASTOR.IS: -0.68% / +1.47% / -2.12%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: -0.09% / +1.47% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>19.75048736579896</v>
+        <v>20.73617525724345</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3429,10 +3429,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N13" t="n">
-        <v>128.2</v>
+        <v>128.5</v>
       </c>
       <c r="O13" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="P13" t="n">
         <v>3.9</v>
@@ -3452,13 +3452,13 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>50.914</v>
+        <v>53.581</v>
       </c>
       <c r="V13" t="n">
-        <v>39.827</v>
+        <v>40.978</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3500,14 +3500,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.51% / +5.47% / -0.81% | BRSAN.IS: +8.65% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +4.66% / +5.47% / -0.81% | BRSAN.IS: +7.97% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>15.12728239388508</v>
+        <v>15.38403734829192</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3516,7 +3516,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N14" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="O14" t="n">
         <v>57.1</v>
@@ -3539,13 +3539,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>47.867</v>
+        <v>50.446</v>
       </c>
       <c r="V14" t="n">
-        <v>36.456</v>
+        <v>36.76</v>
       </c>
       <c r="W14" t="n">
-        <v>-13.086</v>
+        <v>-12.95</v>
       </c>
     </row>
     <row r="16">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -3717,7 +3717,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
       <c r="O18" t="n">
         <v>45.9</v>
@@ -3740,13 +3740,13 @@
         <v>31.839</v>
       </c>
       <c r="U18" t="n">
-        <v>16.523</v>
+        <v>11.666</v>
       </c>
       <c r="V18" t="n">
         <v>27.773</v>
       </c>
       <c r="W18" t="n">
-        <v>-54.429</v>
+        <v>-52.161</v>
       </c>
     </row>
     <row r="19">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -3794,7 +3794,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="O19" t="n">
         <v>46.7</v>
@@ -3817,13 +3817,13 @@
         <v>30.704</v>
       </c>
       <c r="U19" t="n">
-        <v>3.325</v>
+        <v>-0.924</v>
       </c>
       <c r="V19" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>-45.782</v>
+        <v>-43.899</v>
       </c>
     </row>
     <row r="20">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -3871,7 +3871,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="O20" t="n">
         <v>46.7</v>
@@ -3894,13 +3894,13 @@
         <v>30.704</v>
       </c>
       <c r="U20" t="n">
-        <v>3.325</v>
+        <v>-0.924</v>
       </c>
       <c r="V20" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-45.782</v>
+        <v>-43.899</v>
       </c>
     </row>
     <row r="21">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -3948,7 +3948,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>110.9</v>
+        <v>110.7</v>
       </c>
       <c r="O21" t="n">
         <v>38.4</v>
@@ -3971,13 +3971,13 @@
         <v>28.888</v>
       </c>
       <c r="U21" t="n">
-        <v>38.772</v>
+        <v>41.398</v>
       </c>
       <c r="V21" t="n">
         <v>14.358</v>
       </c>
       <c r="W21" t="n">
-        <v>-56.373</v>
+        <v>-57.44</v>
       </c>
     </row>
     <row r="22">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4025,7 +4025,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="O22" t="n">
         <v>44.2</v>
@@ -4048,13 +4048,13 @@
         <v>13.42</v>
       </c>
       <c r="U22" t="n">
-        <v>19.007</v>
+        <v>16.222</v>
       </c>
       <c r="V22" t="n">
         <v>12.908</v>
       </c>
       <c r="W22" t="n">
-        <v>-18.447</v>
+        <v>-18.015</v>
       </c>
     </row>
     <row r="23">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -4102,7 +4102,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N23" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="O23" t="n">
         <v>45.7</v>
@@ -4125,13 +4125,13 @@
         <v>13.513</v>
       </c>
       <c r="U23" t="n">
-        <v>14.92</v>
+        <v>12.231</v>
       </c>
       <c r="V23" t="n">
         <v>13.389</v>
       </c>
       <c r="W23" t="n">
-        <v>-17.227</v>
+        <v>-16.824</v>
       </c>
     </row>
     <row r="24">
@@ -4152,12 +4152,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4179,7 +4179,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="N24" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="O24" t="n">
         <v>57.4</v>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4252,14 +4252,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.51% / +5.47% / -0.81% | BRSAN.IS: +8.65% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +4.66% / +5.47% / -0.81% | BRSAN.IS: +7.97% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>15.12728239388508</v>
+        <v>15.38403734829192</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4268,7 +4268,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N25" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="O25" t="n">
         <v>57.1</v>
@@ -4291,13 +4291,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>47.867</v>
+        <v>50.446</v>
       </c>
       <c r="V25" t="n">
-        <v>36.456</v>
+        <v>36.76</v>
       </c>
       <c r="W25" t="n">
-        <v>-13.086</v>
+        <v>-12.95</v>
       </c>
     </row>
     <row r="26">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4341,14 +4341,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.16% / +1.11% / -0.90% | ASTOR.IS: -0.68% / +1.47% / -2.12%</t>
+          <t>AKBNK.IS: +0.95% / +1.11% / -0.90% | ASTOR.IS: -0.09% / +1.47% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>20.44300632743263</v>
+        <v>21.46838041596748</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4357,10 +4357,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N26" t="n">
-        <v>82.2</v>
+        <v>82</v>
       </c>
       <c r="O26" t="n">
-        <v>48.2</v>
+        <v>48.8</v>
       </c>
       <c r="P26" t="n">
         <v>3.6</v>
@@ -4380,13 +4380,13 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>50.685</v>
+        <v>45.194</v>
       </c>
       <c r="V26" t="n">
-        <v>27.352</v>
+        <v>28.437</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -4407,14 +4407,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>AKBNK.IS, ASTOR.IS</t>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-14 | ASTOR.IS: 2026-08-24</t>
+          <t>AKBNK.IS: 2026-08-26 | ASTOR.IS: 2026-08-24</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -4430,14 +4430,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.29% / +6.27% / -2.24% | ASTOR.IS: -0.68% / +1.47% / -2.12%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: -0.09% / +1.47% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>19.75048736579896</v>
+        <v>20.73617525724345</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4446,10 +4446,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N27" t="n">
-        <v>128.2</v>
+        <v>128.5</v>
       </c>
       <c r="O27" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="P27" t="n">
         <v>3.9</v>
@@ -4469,13 +4469,13 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>50.914</v>
+        <v>53.581</v>
       </c>
       <c r="V27" t="n">
-        <v>39.827</v>
+        <v>40.978</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.633</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -831,14 +831,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.07% / +1.41% / -3.86% | BRSAN.IS: +9.35% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.33% / +2.54% / -3.86% | BRSAN.IS: +9.20% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>7.01495881275207</v>
+        <v>8.064171935425147</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -870,13 +870,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>90.3</v>
+        <v>92.166</v>
       </c>
       <c r="V4" t="n">
-        <v>53.928</v>
+        <v>55.437</v>
       </c>
       <c r="W4" t="n">
-        <v>-27.014</v>
+        <v>-25.149</v>
       </c>
     </row>
     <row r="5">
@@ -1068,14 +1068,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.07% / +1.41% / -3.86% | BRSAN.IS: +9.35% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.33% / +2.54% / -3.86% | BRSAN.IS: +9.20% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>7.01495881275207</v>
+        <v>8.064171935425147</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1107,13 +1107,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>90.3</v>
+        <v>92.166</v>
       </c>
       <c r="V7" t="n">
-        <v>53.928</v>
+        <v>55.437</v>
       </c>
       <c r="W7" t="n">
-        <v>-27.014</v>
+        <v>-25.149</v>
       </c>
     </row>
     <row r="8">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1442,42 +1442,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BRSAN.IS, BSOKE.IS, CANTE.IS</t>
+          <t>AKBNK.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-21 | BSOKE.IS: 2026-08-21 | CANTE.IS: 2026-08-21</t>
+          <t>AKBNK.IS: 2026-08-25 | BRSAN.IS: 2026-08-25</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3.443912532931592</v>
+        <v>35.19994501826646</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +3.89% / +9.99% / 0.00% | BSOKE.IS: -2.23% / +1.85% / -2.87% | CANTE.IS: +0.81% / +2.48% / 0.00%</t>
+          <t>AKBNK.IS: +3.31% / +3.96% / 0.00% | BRSAN.IS: -0.78% / +0.28% / -1.59%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-1.862436885442242</v>
+        <v>11.12989926884889</v>
       </c>
       <c r="K12" t="n">
-        <v>10.64158979326142</v>
+        <v>10.98991287135462</v>
       </c>
       <c r="L12" t="n">
-        <v>7.902828022135555</v>
+        <v>18.10083632820908</v>
       </c>
       <c r="M12" t="n">
-        <v>33.33333333333333</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N12" t="n">
-        <v>33.5</v>
+        <v>73.8</v>
       </c>
       <c r="O12" t="n">
-        <v>47.1</v>
+        <v>50.7</v>
       </c>
       <c r="P12" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1485,22 +1485,22 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>8.954000000000001</v>
+        <v>13.39</v>
       </c>
       <c r="T12" t="n">
-        <v>8.954000000000001</v>
+        <v>13.39</v>
       </c>
       <c r="U12" t="n">
-        <v>10.893</v>
+        <v>29.055</v>
       </c>
       <c r="V12" t="n">
-        <v>9.917999999999999</v>
+        <v>20.042</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.933</v>
+        <v>-5.298</v>
       </c>
     </row>
     <row r="13">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1527,55 +1527,67 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
+        </is>
+      </c>
       <c r="H13" t="n">
-        <v>12.43146471706449</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>22.83095636113686</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ALARK.IS: +2.33% / +2.54% / -3.86% | ASTOR.IS: +19.15% / +21.93% / 0.00% | BIMAS.IS: +3.23% / +3.26% / -0.86% | BRSAN.IS: +37.36% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+        </is>
+      </c>
       <c r="J13" t="n">
-        <v>-6.412181273130146</v>
+        <v>-5.037231846603429</v>
       </c>
       <c r="K13" t="n">
-        <v>8.290371306631972</v>
+        <v>8.763928611666682</v>
       </c>
       <c r="L13" t="n">
-        <v>12.30894614425559</v>
+        <v>23.4189376077676</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>139.3</v>
+        <v>181.1</v>
       </c>
       <c r="O13" t="n">
-        <v>48.1</v>
+        <v>45.9</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S13" t="n">
-        <v>12.004</v>
+        <v>22.513</v>
       </c>
       <c r="T13" t="n">
-        <v>11.714</v>
+        <v>22.513</v>
       </c>
       <c r="U13" t="n">
-        <v>11.106</v>
+        <v>47.825</v>
       </c>
       <c r="V13" t="n">
-        <v>21.903</v>
+        <v>44.113</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.583</v>
+        <v>-2.525</v>
       </c>
     </row>
     <row r="14">
@@ -1589,7 +1601,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1617,14 +1629,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.07% / +1.41% / -3.86% | ASTOR.IS: +17.77% / +21.93% / 0.00% | BIMAS.IS: +1.76% / +3.13% / -0.86% | BRSAN.IS: +37.56% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +2.33% / +2.54% / -3.86% | ASTOR.IS: +19.15% / +21.93% / 0.00% | BIMAS.IS: +3.23% / +3.26% / -0.86% | BRSAN.IS: +37.36% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>7.809503294389053</v>
+        <v>8.763928611666682</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1656,13 +1668,13 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>46.528</v>
+        <v>47.825</v>
       </c>
       <c r="V14" t="n">
-        <v>42.848</v>
+        <v>44.113</v>
       </c>
       <c r="W14" t="n">
-        <v>-3.822</v>
+        <v>-2.525</v>
       </c>
     </row>
     <row r="16">
@@ -1907,14 +1919,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.07% / +1.41% / -3.86% | BRSAN.IS: +9.35% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.33% / +2.54% / -3.86% | BRSAN.IS: +9.20% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>7.01495881275207</v>
+        <v>8.064171935425147</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1946,13 +1958,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>90.3</v>
+        <v>92.166</v>
       </c>
       <c r="V19" t="n">
-        <v>53.928</v>
+        <v>55.437</v>
       </c>
       <c r="W19" t="n">
-        <v>-27.014</v>
+        <v>-25.149</v>
       </c>
     </row>
     <row r="20">
@@ -2194,12 +2206,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2214,42 +2226,42 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
+          <t>AKBNK.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
+          <t>AKBNK.IS: 2026-08-25 | BRSAN.IS: 2026-08-25</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>22.83095636113686</v>
+        <v>35.19994501826646</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.07% / +1.41% / -3.86% | ASTOR.IS: +17.77% / +21.93% / 0.00% | BIMAS.IS: +1.76% / +3.13% / -0.86% | BRSAN.IS: +37.56% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>AKBNK.IS: +3.31% / +3.96% / 0.00% | BRSAN.IS: -0.78% / +0.28% / -1.59%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>-5.037231846603429</v>
+        <v>11.12989926884889</v>
       </c>
       <c r="K23" t="n">
-        <v>7.809503294389053</v>
+        <v>10.98991287135462</v>
       </c>
       <c r="L23" t="n">
-        <v>23.4189376077676</v>
+        <v>18.10083632820908</v>
       </c>
       <c r="M23" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="N23" t="n">
-        <v>181.1</v>
+        <v>73.8</v>
       </c>
       <c r="O23" t="n">
-        <v>45.9</v>
+        <v>50.7</v>
       </c>
       <c r="P23" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2257,22 +2269,22 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>22.513</v>
+        <v>13.39</v>
       </c>
       <c r="T23" t="n">
-        <v>22.513</v>
+        <v>13.39</v>
       </c>
       <c r="U23" t="n">
-        <v>46.528</v>
+        <v>29.055</v>
       </c>
       <c r="V23" t="n">
-        <v>42.848</v>
+        <v>20.042</v>
       </c>
       <c r="W23" t="n">
-        <v>-3.822</v>
+        <v>-5.298</v>
       </c>
     </row>
     <row r="24">
@@ -2288,7 +2300,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2301,55 +2313,67 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
+        </is>
+      </c>
       <c r="H24" t="n">
-        <v>12.43146471706449</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>22.83095636113686</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ALARK.IS: +2.33% / +2.54% / -3.86% | ASTOR.IS: +19.15% / +21.93% / 0.00% | BIMAS.IS: +3.23% / +3.26% / -0.86% | BRSAN.IS: +37.36% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+        </is>
+      </c>
       <c r="J24" t="n">
-        <v>-6.412181273130146</v>
+        <v>-5.037231846603429</v>
       </c>
       <c r="K24" t="n">
-        <v>8.290371306631972</v>
+        <v>8.763928611666682</v>
       </c>
       <c r="L24" t="n">
-        <v>12.30894614425559</v>
+        <v>23.4189376077676</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>139.3</v>
+        <v>181.1</v>
       </c>
       <c r="O24" t="n">
-        <v>48.1</v>
+        <v>45.9</v>
       </c>
       <c r="P24" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S24" t="n">
-        <v>12.004</v>
+        <v>22.513</v>
       </c>
       <c r="T24" t="n">
-        <v>11.714</v>
+        <v>22.513</v>
       </c>
       <c r="U24" t="n">
-        <v>11.106</v>
+        <v>47.825</v>
       </c>
       <c r="V24" t="n">
-        <v>21.903</v>
+        <v>44.113</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.583</v>
+        <v>-2.525</v>
       </c>
     </row>
     <row r="25">
@@ -2360,12 +2384,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2380,42 +2404,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BRSAN.IS, BSOKE.IS, CANTE.IS</t>
+          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-21 | BSOKE.IS: 2026-08-21 | CANTE.IS: 2026-08-21</t>
+          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>3.443912532931592</v>
+        <v>22.83095636113686</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +3.89% / +9.99% / 0.00% | BSOKE.IS: -2.23% / +1.85% / -2.87% | CANTE.IS: +0.81% / +2.48% / 0.00%</t>
+          <t>ALARK.IS: +2.33% / +2.54% / -3.86% | ASTOR.IS: +19.15% / +21.93% / 0.00% | BIMAS.IS: +3.23% / +3.26% / -0.86% | BRSAN.IS: +37.36% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>-1.862436885442242</v>
+        <v>-5.037231846603429</v>
       </c>
       <c r="K25" t="n">
-        <v>10.64158979326142</v>
+        <v>8.763928611666682</v>
       </c>
       <c r="L25" t="n">
-        <v>7.902828022135555</v>
+        <v>23.4189376077676</v>
       </c>
       <c r="M25" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>33.5</v>
+        <v>181.1</v>
       </c>
       <c r="O25" t="n">
-        <v>47.1</v>
+        <v>45.9</v>
       </c>
       <c r="P25" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2423,22 +2447,22 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S25" t="n">
-        <v>8.954000000000001</v>
+        <v>22.513</v>
       </c>
       <c r="T25" t="n">
-        <v>8.954000000000001</v>
+        <v>22.513</v>
       </c>
       <c r="U25" t="n">
-        <v>10.893</v>
+        <v>47.825</v>
       </c>
       <c r="V25" t="n">
-        <v>9.917999999999999</v>
+        <v>44.113</v>
       </c>
       <c r="W25" t="n">
-        <v>-2.933</v>
+        <v>-2.525</v>
       </c>
     </row>
   </sheetData>
@@ -3326,14 +3350,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.95% / +1.11% / -0.90% | ASTOR.IS: -0.09% / +1.47% / -2.12%</t>
+          <t>AKBNK.IS: +3.17% / +3.81% / -0.90% | ASTOR.IS: +1.08% / +1.91% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>21.46838041596748</v>
+        <v>23.51912220165753</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3345,7 +3369,7 @@
         <v>82</v>
       </c>
       <c r="O12" t="n">
-        <v>48.8</v>
+        <v>49.4</v>
       </c>
       <c r="P12" t="n">
         <v>3.6</v>
@@ -3365,10 +3389,10 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>45.194</v>
+        <v>47.645</v>
       </c>
       <c r="V12" t="n">
-        <v>28.437</v>
+        <v>30.605</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -3413,14 +3437,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: -0.09% / +1.47% / -2.12%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +1.08% / +1.91% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>20.73617525724345</v>
+        <v>22.75544975266273</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3432,7 +3456,7 @@
         <v>128.5</v>
       </c>
       <c r="O13" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="P13" t="n">
         <v>3.9</v>
@@ -3452,10 +3476,10 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>53.581</v>
+        <v>56.15</v>
       </c>
       <c r="V13" t="n">
-        <v>40.978</v>
+        <v>43.336</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -3500,14 +3524,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.66% / +5.47% / -0.81% | BRSAN.IS: +7.97% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +6.96% / +7.63% / -0.81% | BRSAN.IS: +7.82% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>15.38403734829192</v>
+        <v>16.55081835655081</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3539,13 +3563,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>50.446</v>
+        <v>51.967</v>
       </c>
       <c r="V14" t="n">
-        <v>36.76</v>
+        <v>38.143</v>
       </c>
       <c r="W14" t="n">
-        <v>-12.95</v>
+        <v>-11.428</v>
       </c>
     </row>
     <row r="16">
@@ -4252,14 +4276,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.66% / +5.47% / -0.81% | BRSAN.IS: +7.97% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +6.96% / +7.63% / -0.81% | BRSAN.IS: +7.82% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>15.38403734829192</v>
+        <v>16.55081835655081</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4291,13 +4315,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>50.446</v>
+        <v>51.967</v>
       </c>
       <c r="V25" t="n">
-        <v>36.76</v>
+        <v>38.143</v>
       </c>
       <c r="W25" t="n">
-        <v>-12.95</v>
+        <v>-11.428</v>
       </c>
     </row>
     <row r="26">
@@ -4341,14 +4365,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.95% / +1.11% / -0.90% | ASTOR.IS: -0.09% / +1.47% / -2.12%</t>
+          <t>AKBNK.IS: +3.17% / +3.81% / -0.90% | ASTOR.IS: +1.08% / +1.91% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>21.46838041596748</v>
+        <v>23.51912220165753</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4360,7 +4384,7 @@
         <v>82</v>
       </c>
       <c r="O26" t="n">
-        <v>48.8</v>
+        <v>49.4</v>
       </c>
       <c r="P26" t="n">
         <v>3.6</v>
@@ -4380,10 +4404,10 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>45.194</v>
+        <v>47.645</v>
       </c>
       <c r="V26" t="n">
-        <v>28.437</v>
+        <v>30.605</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4430,14 +4454,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: -0.09% / +1.47% / -2.12%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +1.08% / +1.91% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>20.73617525724345</v>
+        <v>22.75544975266273</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4449,7 +4473,7 @@
         <v>128.5</v>
       </c>
       <c r="O27" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="P27" t="n">
         <v>3.9</v>
@@ -4469,10 +4493,10 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>53.581</v>
+        <v>56.15</v>
       </c>
       <c r="V27" t="n">
-        <v>40.978</v>
+        <v>43.336</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -831,14 +831,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.33% / +2.54% / -3.86% | BRSAN.IS: +9.20% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.52% / +3.29% / -3.86% | BRSAN.IS: +7.68% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>8.064171935425147</v>
+        <v>7.363957190668202</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -870,13 +870,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>92.166</v>
+        <v>90.92100000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>55.437</v>
+        <v>54.43</v>
       </c>
       <c r="W4" t="n">
-        <v>-25.149</v>
+        <v>-26.394</v>
       </c>
     </row>
     <row r="5">
@@ -1068,14 +1068,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.33% / +2.54% / -3.86% | BRSAN.IS: +9.20% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.52% / +3.29% / -3.86% | BRSAN.IS: +7.68% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>8.064171935425147</v>
+        <v>7.363957190668202</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1107,13 +1107,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>92.166</v>
+        <v>90.92100000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>55.437</v>
+        <v>54.43</v>
       </c>
       <c r="W7" t="n">
-        <v>-25.149</v>
+        <v>-26.394</v>
       </c>
     </row>
     <row r="8">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1442,42 +1442,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AKBNK.IS, BRSAN.IS</t>
+          <t>BRSAN.IS, RALYH.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-25 | BRSAN.IS: 2026-08-25</t>
+          <t>BRSAN.IS: 2026-08-26 | RALYH.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>35.19994501826646</v>
+        <v>35.05565740671337</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.31% / +3.96% / 0.00% | BRSAN.IS: -0.78% / +0.28% / -1.59%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: -0.30% / +5.24% / -3.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>11.12989926884889</v>
+        <v>5.880320398884153</v>
       </c>
       <c r="K12" t="n">
-        <v>10.98991287135462</v>
+        <v>9.76917110958604</v>
       </c>
       <c r="L12" t="n">
-        <v>18.10083632820908</v>
+        <v>17.97495932189197</v>
       </c>
       <c r="M12" t="n">
-        <v>83.33333333333334</v>
+        <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>73.8</v>
+        <v>140.8</v>
       </c>
       <c r="O12" t="n">
-        <v>50.7</v>
+        <v>46.2</v>
       </c>
       <c r="P12" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1488,19 +1488,19 @@
         <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>13.39</v>
+        <v>21.61</v>
       </c>
       <c r="T12" t="n">
-        <v>13.39</v>
+        <v>21.61</v>
       </c>
       <c r="U12" t="n">
-        <v>29.055</v>
+        <v>81.328</v>
       </c>
       <c r="V12" t="n">
-        <v>20.042</v>
+        <v>71.79600000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>-5.298</v>
+        <v>-23.274</v>
       </c>
     </row>
     <row r="13">
@@ -1542,14 +1542,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.33% / +2.54% / -3.86% | ASTOR.IS: +19.15% / +21.93% / 0.00% | BIMAS.IS: +3.23% / +3.26% / -0.86% | BRSAN.IS: +37.36% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +2.52% / +3.29% / -3.86% | ASTOR.IS: +18.54% / +21.93% / 0.00% | BIMAS.IS: +3.30% / +3.87% / -0.86% | BRSAN.IS: +35.45% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K13" t="n">
-        <v>8.763928611666682</v>
+        <v>8.325948259619388</v>
       </c>
       <c r="L13" t="n">
         <v>23.4189376077676</v>
@@ -1581,13 +1581,13 @@
         <v>22.513</v>
       </c>
       <c r="U13" t="n">
-        <v>47.825</v>
+        <v>47.23</v>
       </c>
       <c r="V13" t="n">
-        <v>44.113</v>
+        <v>43.533</v>
       </c>
       <c r="W13" t="n">
-        <v>-2.525</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="14">
@@ -1629,14 +1629,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.33% / +2.54% / -3.86% | ASTOR.IS: +19.15% / +21.93% / 0.00% | BIMAS.IS: +3.23% / +3.26% / -0.86% | BRSAN.IS: +37.36% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +2.52% / +3.29% / -3.86% | ASTOR.IS: +18.54% / +21.93% / 0.00% | BIMAS.IS: +3.30% / +3.87% / -0.86% | BRSAN.IS: +35.45% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>8.763928611666682</v>
+        <v>8.325948259619388</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1668,13 +1668,13 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>47.825</v>
+        <v>47.23</v>
       </c>
       <c r="V14" t="n">
-        <v>44.113</v>
+        <v>43.533</v>
       </c>
       <c r="W14" t="n">
-        <v>-2.525</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="16">
@@ -1919,14 +1919,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.33% / +2.54% / -3.86% | BRSAN.IS: +9.20% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.52% / +3.29% / -3.86% | BRSAN.IS: +7.68% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>8.064171935425147</v>
+        <v>7.363957190668202</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1958,13 +1958,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>92.166</v>
+        <v>90.92100000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>55.437</v>
+        <v>54.43</v>
       </c>
       <c r="W19" t="n">
-        <v>-25.149</v>
+        <v>-26.394</v>
       </c>
     </row>
     <row r="20">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2226,42 +2226,42 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AKBNK.IS, BRSAN.IS</t>
+          <t>BRSAN.IS, RALYH.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-25 | BRSAN.IS: 2026-08-25</t>
+          <t>BRSAN.IS: 2026-08-26 | RALYH.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>35.19994501826646</v>
+        <v>35.05565740671337</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.31% / +3.96% / 0.00% | BRSAN.IS: -0.78% / +0.28% / -1.59%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: -0.30% / +5.24% / -3.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>11.12989926884889</v>
+        <v>5.880320398884153</v>
       </c>
       <c r="K23" t="n">
-        <v>10.98991287135462</v>
+        <v>9.76917110958604</v>
       </c>
       <c r="L23" t="n">
-        <v>18.10083632820908</v>
+        <v>17.97495932189197</v>
       </c>
       <c r="M23" t="n">
-        <v>83.33333333333334</v>
+        <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>73.8</v>
+        <v>140.8</v>
       </c>
       <c r="O23" t="n">
-        <v>50.7</v>
+        <v>46.2</v>
       </c>
       <c r="P23" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2272,19 +2272,19 @@
         <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>13.39</v>
+        <v>21.61</v>
       </c>
       <c r="T23" t="n">
-        <v>13.39</v>
+        <v>21.61</v>
       </c>
       <c r="U23" t="n">
-        <v>29.055</v>
+        <v>81.328</v>
       </c>
       <c r="V23" t="n">
-        <v>20.042</v>
+        <v>71.79600000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>-5.298</v>
+        <v>-23.274</v>
       </c>
     </row>
     <row r="24">
@@ -2328,14 +2328,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.33% / +2.54% / -3.86% | ASTOR.IS: +19.15% / +21.93% / 0.00% | BIMAS.IS: +3.23% / +3.26% / -0.86% | BRSAN.IS: +37.36% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +2.52% / +3.29% / -3.86% | ASTOR.IS: +18.54% / +21.93% / 0.00% | BIMAS.IS: +3.30% / +3.87% / -0.86% | BRSAN.IS: +35.45% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K24" t="n">
-        <v>8.763928611666682</v>
+        <v>8.325948259619388</v>
       </c>
       <c r="L24" t="n">
         <v>23.4189376077676</v>
@@ -2367,13 +2367,13 @@
         <v>22.513</v>
       </c>
       <c r="U24" t="n">
-        <v>47.825</v>
+        <v>47.23</v>
       </c>
       <c r="V24" t="n">
-        <v>44.113</v>
+        <v>43.533</v>
       </c>
       <c r="W24" t="n">
-        <v>-2.525</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="25">
@@ -2417,14 +2417,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.33% / +2.54% / -3.86% | ASTOR.IS: +19.15% / +21.93% / 0.00% | BIMAS.IS: +3.23% / +3.26% / -0.86% | BRSAN.IS: +37.36% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +2.52% / +3.29% / -3.86% | ASTOR.IS: +18.54% / +21.93% / 0.00% | BIMAS.IS: +3.30% / +3.87% / -0.86% | BRSAN.IS: +35.45% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K25" t="n">
-        <v>8.763928611666682</v>
+        <v>8.325948259619388</v>
       </c>
       <c r="L25" t="n">
         <v>23.4189376077676</v>
@@ -2456,13 +2456,13 @@
         <v>22.513</v>
       </c>
       <c r="U25" t="n">
-        <v>47.825</v>
+        <v>47.23</v>
       </c>
       <c r="V25" t="n">
-        <v>44.113</v>
+        <v>43.533</v>
       </c>
       <c r="W25" t="n">
-        <v>-2.525</v>
+        <v>-3.12</v>
       </c>
     </row>
   </sheetData>
@@ -3350,14 +3350,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.17% / +3.81% / -0.90% | ASTOR.IS: +1.08% / +1.91% / -2.12%</t>
+          <t>AKBNK.IS: +1.64% / +3.81% / -0.90% | ASTOR.IS: +0.57% / +2.56% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>23.51912220165753</v>
+        <v>22.28641789645016</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3389,10 +3389,10 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>47.645</v>
+        <v>46.171</v>
       </c>
       <c r="V12" t="n">
-        <v>30.605</v>
+        <v>29.302</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -3437,14 +3437,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +1.08% / +1.91% / -2.12%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +0.57% / +2.56% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>22.75544975266273</v>
+        <v>21.5433408628932</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3476,10 +3476,10 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>56.15</v>
+        <v>54.608</v>
       </c>
       <c r="V13" t="n">
-        <v>43.336</v>
+        <v>41.921</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -3524,14 +3524,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +6.96% / +7.63% / -0.81% | BRSAN.IS: +7.82% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +5.38% / +7.63% / -0.81% | BRSAN.IS: +6.32% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>16.55081835655081</v>
+        <v>14.87591948149969</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3563,13 +3563,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>51.967</v>
+        <v>49.783</v>
       </c>
       <c r="V14" t="n">
-        <v>38.143</v>
+        <v>36.158</v>
       </c>
       <c r="W14" t="n">
-        <v>-11.428</v>
+        <v>-13.612</v>
       </c>
     </row>
     <row r="16">
@@ -4276,14 +4276,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +6.96% / +7.63% / -0.81% | BRSAN.IS: +7.82% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +5.38% / +7.63% / -0.81% | BRSAN.IS: +6.32% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>16.55081835655081</v>
+        <v>14.87591948149969</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4315,13 +4315,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>51.967</v>
+        <v>49.783</v>
       </c>
       <c r="V25" t="n">
-        <v>38.143</v>
+        <v>36.158</v>
       </c>
       <c r="W25" t="n">
-        <v>-11.428</v>
+        <v>-13.612</v>
       </c>
     </row>
     <row r="26">
@@ -4365,14 +4365,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +3.17% / +3.81% / -0.90% | ASTOR.IS: +1.08% / +1.91% / -2.12%</t>
+          <t>AKBNK.IS: +1.64% / +3.81% / -0.90% | ASTOR.IS: +0.57% / +2.56% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>23.51912220165753</v>
+        <v>22.28641789645016</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4404,10 +4404,10 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>47.645</v>
+        <v>46.171</v>
       </c>
       <c r="V26" t="n">
-        <v>30.605</v>
+        <v>29.302</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4454,14 +4454,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +1.08% / +1.91% / -2.12%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +0.57% / +2.56% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>22.75544975266273</v>
+        <v>21.5433408628932</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4493,10 +4493,10 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>56.15</v>
+        <v>54.608</v>
       </c>
       <c r="V27" t="n">
-        <v>43.336</v>
+        <v>41.921</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -831,14 +831,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.52% / +3.29% / -3.86% | BRSAN.IS: +7.68% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.05% / +3.29% / -3.86% | BRSAN.IS: +7.60% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>7.363957190668202</v>
+        <v>7.089110723950376</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -870,13 +870,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>90.92100000000001</v>
+        <v>90.432</v>
       </c>
       <c r="V4" t="n">
-        <v>54.43</v>
+        <v>54.034</v>
       </c>
       <c r="W4" t="n">
-        <v>-26.394</v>
+        <v>-26.882</v>
       </c>
     </row>
     <row r="5">
@@ -1068,14 +1068,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.52% / +3.29% / -3.86% | BRSAN.IS: +7.68% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.05% / +3.29% / -3.86% | BRSAN.IS: +7.60% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>7.363957190668202</v>
+        <v>7.089110723950376</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1107,13 +1107,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>90.92100000000001</v>
+        <v>90.432</v>
       </c>
       <c r="V7" t="n">
-        <v>54.43</v>
+        <v>54.034</v>
       </c>
       <c r="W7" t="n">
-        <v>-26.394</v>
+        <v>-26.882</v>
       </c>
     </row>
     <row r="8">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: -0.30% / +5.24% / -3.00%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: -1.33% / +5.24% / -3.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>5.880320398884153</v>
       </c>
       <c r="K12" t="n">
-        <v>9.76917110958604</v>
+        <v>9.722300049739951</v>
       </c>
       <c r="L12" t="n">
         <v>17.97495932189197</v>
@@ -1494,13 +1494,13 @@
         <v>21.61</v>
       </c>
       <c r="U12" t="n">
-        <v>81.328</v>
+        <v>81.25</v>
       </c>
       <c r="V12" t="n">
-        <v>71.79600000000001</v>
+        <v>71.72199999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>-23.274</v>
+        <v>-23.351</v>
       </c>
     </row>
     <row r="13">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1527,67 +1527,55 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>22.83095636113686</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ALARK.IS: +2.52% / +3.29% / -3.86% | ASTOR.IS: +18.54% / +21.93% / 0.00% | BIMAS.IS: +3.30% / +3.87% / -0.86% | BRSAN.IS: +35.45% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
-        </is>
-      </c>
+        <v>12.43146471706449</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>-5.037231846603429</v>
+        <v>-6.412181273130146</v>
       </c>
       <c r="K13" t="n">
-        <v>8.325948259619388</v>
+        <v>8.290371306631972</v>
       </c>
       <c r="L13" t="n">
-        <v>23.4189376077676</v>
+        <v>12.30894614425559</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>181.1</v>
+        <v>139.3</v>
       </c>
       <c r="O13" t="n">
-        <v>45.9</v>
+        <v>48.1</v>
       </c>
       <c r="P13" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>22.513</v>
+        <v>12.004</v>
       </c>
       <c r="T13" t="n">
-        <v>22.513</v>
+        <v>11.714</v>
       </c>
       <c r="U13" t="n">
-        <v>47.23</v>
+        <v>11.106</v>
       </c>
       <c r="V13" t="n">
-        <v>43.533</v>
+        <v>21.903</v>
       </c>
       <c r="W13" t="n">
-        <v>-3.12</v>
+        <v>-0.583</v>
       </c>
     </row>
     <row r="14">
@@ -1601,7 +1589,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
+          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1629,14 +1617,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.52% / +3.29% / -3.86% | ASTOR.IS: +18.54% / +21.93% / 0.00% | BIMAS.IS: +3.30% / +3.87% / -0.86% | BRSAN.IS: +35.45% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +2.05% / +3.29% / -3.86% | ASTOR.IS: +16.99% / +21.93% / 0.00% | BIMAS.IS: +2.74% / +3.87% / -0.86% | BRSAN.IS: +35.35% / +45.64% / -0.48% | CANTE.IS: -0.02% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>8.325948259619388</v>
+        <v>7.645862941764658</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1648,7 +1636,7 @@
         <v>181.1</v>
       </c>
       <c r="O14" t="n">
-        <v>45.9</v>
+        <v>45.7</v>
       </c>
       <c r="P14" t="n">
         <v>5.5</v>
@@ -1668,13 +1656,13 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>47.23</v>
+        <v>46.305</v>
       </c>
       <c r="V14" t="n">
-        <v>43.533</v>
+        <v>42.632</v>
       </c>
       <c r="W14" t="n">
-        <v>-3.12</v>
+        <v>-4.044</v>
       </c>
     </row>
     <row r="16">
@@ -1919,14 +1907,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.52% / +3.29% / -3.86% | BRSAN.IS: +7.68% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.05% / +3.29% / -3.86% | BRSAN.IS: +7.60% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>7.363957190668202</v>
+        <v>7.089110723950376</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1958,13 +1946,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>90.92100000000001</v>
+        <v>90.432</v>
       </c>
       <c r="V19" t="n">
-        <v>54.43</v>
+        <v>54.034</v>
       </c>
       <c r="W19" t="n">
-        <v>-26.394</v>
+        <v>-26.882</v>
       </c>
     </row>
     <row r="20">
@@ -2239,14 +2227,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: -0.30% / +5.24% / -3.00%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: -1.33% / +5.24% / -3.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>5.880320398884153</v>
       </c>
       <c r="K23" t="n">
-        <v>9.76917110958604</v>
+        <v>9.722300049739951</v>
       </c>
       <c r="L23" t="n">
         <v>17.97495932189197</v>
@@ -2278,13 +2266,13 @@
         <v>21.61</v>
       </c>
       <c r="U23" t="n">
-        <v>81.328</v>
+        <v>81.25</v>
       </c>
       <c r="V23" t="n">
-        <v>71.79600000000001</v>
+        <v>71.72199999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>-23.274</v>
+        <v>-23.351</v>
       </c>
     </row>
     <row r="24">
@@ -2295,7 +2283,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2328,14 +2316,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.52% / +3.29% / -3.86% | ASTOR.IS: +18.54% / +21.93% / 0.00% | BIMAS.IS: +3.30% / +3.87% / -0.86% | BRSAN.IS: +35.45% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +2.05% / +3.29% / -3.86% | ASTOR.IS: +16.99% / +21.93% / 0.00% | BIMAS.IS: +2.74% / +3.87% / -0.86% | BRSAN.IS: +35.35% / +45.64% / -0.48% | CANTE.IS: -0.02% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K24" t="n">
-        <v>8.325948259619388</v>
+        <v>7.645862941764658</v>
       </c>
       <c r="L24" t="n">
         <v>23.4189376077676</v>
@@ -2347,7 +2335,7 @@
         <v>181.1</v>
       </c>
       <c r="O24" t="n">
-        <v>45.9</v>
+        <v>45.7</v>
       </c>
       <c r="P24" t="n">
         <v>5.5</v>
@@ -2367,13 +2355,13 @@
         <v>22.513</v>
       </c>
       <c r="U24" t="n">
-        <v>47.23</v>
+        <v>46.305</v>
       </c>
       <c r="V24" t="n">
-        <v>43.533</v>
+        <v>42.632</v>
       </c>
       <c r="W24" t="n">
-        <v>-3.12</v>
+        <v>-4.044</v>
       </c>
     </row>
     <row r="25">
@@ -2384,12 +2372,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
+          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2402,67 +2390,55 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>22.83095636113686</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>ALARK.IS: +2.52% / +3.29% / -3.86% | ASTOR.IS: +18.54% / +21.93% / 0.00% | BIMAS.IS: +3.30% / +3.87% / -0.86% | BRSAN.IS: +35.45% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
-        </is>
-      </c>
+        <v>12.43146471706449</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>-5.037231846603429</v>
+        <v>-6.412181273130146</v>
       </c>
       <c r="K25" t="n">
-        <v>8.325948259619388</v>
+        <v>8.290371306631972</v>
       </c>
       <c r="L25" t="n">
-        <v>23.4189376077676</v>
+        <v>12.30894614425559</v>
       </c>
       <c r="M25" t="n">
         <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>181.1</v>
+        <v>139.3</v>
       </c>
       <c r="O25" t="n">
-        <v>45.9</v>
+        <v>48.1</v>
       </c>
       <c r="P25" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>22.513</v>
+        <v>12.004</v>
       </c>
       <c r="T25" t="n">
-        <v>22.513</v>
+        <v>11.714</v>
       </c>
       <c r="U25" t="n">
-        <v>47.23</v>
+        <v>11.106</v>
       </c>
       <c r="V25" t="n">
-        <v>43.533</v>
+        <v>21.903</v>
       </c>
       <c r="W25" t="n">
-        <v>-3.12</v>
+        <v>-0.583</v>
       </c>
     </row>
   </sheetData>
@@ -3350,14 +3326,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.64% / +3.81% / -0.90% | ASTOR.IS: +0.57% / +2.56% / -2.12%</t>
+          <t>AKBNK.IS: +1.44% / +3.81% / -0.90% | ASTOR.IS: -0.75% / +2.56% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>22.28641789645016</v>
+        <v>21.36329082917474</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3369,7 +3345,7 @@
         <v>82</v>
       </c>
       <c r="O12" t="n">
-        <v>49.4</v>
+        <v>48.8</v>
       </c>
       <c r="P12" t="n">
         <v>3.6</v>
@@ -3389,10 +3365,10 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>46.171</v>
+        <v>45.068</v>
       </c>
       <c r="V12" t="n">
-        <v>29.302</v>
+        <v>28.326</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -3437,14 +3413,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +0.57% / +2.56% / -2.12%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: -0.75% / +2.56% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>21.5433408628932</v>
+        <v>20.62744702883403</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3456,7 +3432,7 @@
         <v>128.5</v>
       </c>
       <c r="O13" t="n">
-        <v>50</v>
+        <v>49.6</v>
       </c>
       <c r="P13" t="n">
         <v>3.9</v>
@@ -3476,10 +3452,10 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>54.608</v>
+        <v>53.443</v>
       </c>
       <c r="V13" t="n">
-        <v>41.921</v>
+        <v>40.851</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -3524,14 +3500,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +5.38% / +7.63% / -0.81% | BRSAN.IS: +6.32% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +5.16% / +7.63% / -0.81% | BRSAN.IS: +6.24% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>14.87591948149969</v>
+        <v>14.71804705907167</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3563,13 +3539,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>49.783</v>
+        <v>49.577</v>
       </c>
       <c r="V14" t="n">
-        <v>36.158</v>
+        <v>35.971</v>
       </c>
       <c r="W14" t="n">
-        <v>-13.612</v>
+        <v>-13.818</v>
       </c>
     </row>
     <row r="16">
@@ -4276,14 +4252,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +5.38% / +7.63% / -0.81% | BRSAN.IS: +6.32% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +5.16% / +7.63% / -0.81% | BRSAN.IS: +6.24% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>14.87591948149969</v>
+        <v>14.71804705907167</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4315,13 +4291,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>49.783</v>
+        <v>49.577</v>
       </c>
       <c r="V25" t="n">
-        <v>36.158</v>
+        <v>35.971</v>
       </c>
       <c r="W25" t="n">
-        <v>-13.612</v>
+        <v>-13.818</v>
       </c>
     </row>
     <row r="26">
@@ -4365,14 +4341,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.64% / +3.81% / -0.90% | ASTOR.IS: +0.57% / +2.56% / -2.12%</t>
+          <t>AKBNK.IS: +1.44% / +3.81% / -0.90% | ASTOR.IS: -0.75% / +2.56% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>22.28641789645016</v>
+        <v>21.36329082917474</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4384,7 +4360,7 @@
         <v>82</v>
       </c>
       <c r="O26" t="n">
-        <v>49.4</v>
+        <v>48.8</v>
       </c>
       <c r="P26" t="n">
         <v>3.6</v>
@@ -4404,10 +4380,10 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>46.171</v>
+        <v>45.068</v>
       </c>
       <c r="V26" t="n">
-        <v>29.302</v>
+        <v>28.326</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4454,14 +4430,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +0.57% / +2.56% / -2.12%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: -0.75% / +2.56% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>21.5433408628932</v>
+        <v>20.62744702883403</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4473,7 +4449,7 @@
         <v>128.5</v>
       </c>
       <c r="O27" t="n">
-        <v>50</v>
+        <v>49.6</v>
       </c>
       <c r="P27" t="n">
         <v>3.9</v>
@@ -4493,10 +4469,10 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>54.608</v>
+        <v>53.443</v>
       </c>
       <c r="V27" t="n">
-        <v>41.921</v>
+        <v>40.851</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -760,7 +760,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>117.1</v>
+        <v>116.9</v>
       </c>
       <c r="O3" t="n">
         <v>39.9</v>
@@ -783,13 +783,13 @@
         <v>28.567</v>
       </c>
       <c r="U3" t="n">
-        <v>72.258</v>
+        <v>75.807</v>
       </c>
       <c r="V3" t="n">
         <v>41.769</v>
       </c>
       <c r="W3" t="n">
-        <v>-68.88800000000001</v>
+        <v>-70.307</v>
       </c>
     </row>
     <row r="4">
@@ -808,12 +808,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -831,14 +831,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.05% / +3.29% / -3.86% | BRSAN.IS: +7.60% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.71% / +3.57% / -3.86% | BRSAN.IS: +9.12% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>7.089110723950376</v>
+        <v>8.212562249251732</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -847,7 +847,7 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>121.1</v>
+        <v>120.8</v>
       </c>
       <c r="O4" t="n">
         <v>43.5</v>
@@ -870,13 +870,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>90.432</v>
+        <v>96.80800000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>54.034</v>
+        <v>55.65</v>
       </c>
       <c r="W4" t="n">
-        <v>-26.882</v>
+        <v>-25.451</v>
       </c>
     </row>
     <row r="5">
@@ -895,25 +895,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ALARK.IS, DOHOL.IS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>115.6477996753693</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J5" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K5" t="n">
-        <v>-28.64788373547042</v>
+        <v>-28.67642172789157</v>
       </c>
       <c r="L5" t="n">
         <v>25.50508358988237</v>
@@ -922,36 +934,36 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>93.5</v>
+        <v>94.3</v>
       </c>
       <c r="O5" t="n">
-        <v>37.4</v>
+        <v>37</v>
       </c>
       <c r="P5" t="n">
         <v>3.9</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>35.687</v>
+        <v>35.713</v>
       </c>
       <c r="T5" t="n">
-        <v>35.687</v>
+        <v>35.713</v>
       </c>
       <c r="U5" t="n">
-        <v>18.143</v>
+        <v>21.504</v>
       </c>
       <c r="V5" t="n">
-        <v>12.323</v>
+        <v>12.278</v>
       </c>
       <c r="W5" t="n">
-        <v>-65.557</v>
+        <v>-67.498</v>
       </c>
     </row>
     <row r="6">
@@ -970,12 +982,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -997,7 +1009,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>117.1</v>
+        <v>116.9</v>
       </c>
       <c r="O6" t="n">
         <v>39.9</v>
@@ -1020,13 +1032,13 @@
         <v>28.567</v>
       </c>
       <c r="U6" t="n">
-        <v>72.258</v>
+        <v>75.807</v>
       </c>
       <c r="V6" t="n">
         <v>41.769</v>
       </c>
       <c r="W6" t="n">
-        <v>-68.88800000000001</v>
+        <v>-70.307</v>
       </c>
     </row>
     <row r="7">
@@ -1045,12 +1057,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1068,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.05% / +3.29% / -3.86% | BRSAN.IS: +7.60% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.71% / +3.57% / -3.86% | BRSAN.IS: +9.12% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>7.089110723950376</v>
+        <v>8.212562249251732</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1084,7 +1096,7 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>121.1</v>
+        <v>120.8</v>
       </c>
       <c r="O7" t="n">
         <v>43.5</v>
@@ -1107,13 +1119,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>90.432</v>
+        <v>96.80800000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>54.034</v>
+        <v>55.65</v>
       </c>
       <c r="W7" t="n">
-        <v>-26.882</v>
+        <v>-25.451</v>
       </c>
     </row>
     <row r="8">
@@ -1132,25 +1144,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, TAVHL.IS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>96.86982435918456</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TAVHL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J8" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3078108772402999</v>
+        <v>0.2676917652018496</v>
       </c>
       <c r="L8" t="n">
         <v>13.72502171397572</v>
@@ -1159,21 +1183,21 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N8" t="n">
-        <v>46.3</v>
+        <v>47.2</v>
       </c>
       <c r="O8" t="n">
-        <v>51.1</v>
+        <v>50</v>
       </c>
       <c r="P8" t="n">
         <v>4.6</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>29.993</v>
@@ -1182,13 +1206,13 @@
         <v>29.993</v>
       </c>
       <c r="U8" t="n">
-        <v>1.107</v>
+        <v>3.94</v>
       </c>
       <c r="V8" t="n">
-        <v>-6.769</v>
+        <v>-6.806</v>
       </c>
       <c r="W8" t="n">
-        <v>-42.845</v>
+        <v>-44.104</v>
       </c>
     </row>
     <row r="9">
@@ -1207,12 +1231,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1234,7 +1258,7 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>117.1</v>
+        <v>116.9</v>
       </c>
       <c r="O9" t="n">
         <v>39.9</v>
@@ -1257,13 +1281,13 @@
         <v>28.567</v>
       </c>
       <c r="U9" t="n">
-        <v>72.258</v>
+        <v>75.807</v>
       </c>
       <c r="V9" t="n">
         <v>41.769</v>
       </c>
       <c r="W9" t="n">
-        <v>-68.88800000000001</v>
+        <v>-70.307</v>
       </c>
     </row>
     <row r="10">
@@ -1282,25 +1306,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, TAVHL.IS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>96.86982435918456</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TAVHL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J10" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3078108772402999</v>
+        <v>0.2676917652018496</v>
       </c>
       <c r="L10" t="n">
         <v>13.72502171397572</v>
@@ -1309,21 +1345,21 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>46.3</v>
+        <v>47.2</v>
       </c>
       <c r="O10" t="n">
-        <v>51.1</v>
+        <v>50</v>
       </c>
       <c r="P10" t="n">
         <v>4.6</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
         <v>29.993</v>
@@ -1332,13 +1368,13 @@
         <v>29.993</v>
       </c>
       <c r="U10" t="n">
-        <v>1.107</v>
+        <v>3.94</v>
       </c>
       <c r="V10" t="n">
-        <v>-6.769</v>
+        <v>-6.806</v>
       </c>
       <c r="W10" t="n">
-        <v>-42.845</v>
+        <v>-44.104</v>
       </c>
     </row>
     <row r="11">
@@ -1357,25 +1393,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ALARK.IS, DOHOL.IS, TAVHL.IS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>87.24519408485627</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00% | TAVHL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J11" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7349222980747139</v>
+        <v>-0.774623035017985</v>
       </c>
       <c r="L11" t="n">
         <v>10.56563994340933</v>
@@ -1384,21 +1432,21 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>71.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="O11" t="n">
-        <v>38.4</v>
+        <v>37.6</v>
       </c>
       <c r="P11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
         <v>29.287</v>
@@ -1407,13 +1455,13 @@
         <v>29.287</v>
       </c>
       <c r="U11" t="n">
-        <v>32.864</v>
+        <v>37.054</v>
       </c>
       <c r="V11" t="n">
-        <v>14.374</v>
+        <v>14.328</v>
       </c>
       <c r="W11" t="n">
-        <v>-47.224</v>
+        <v>-48.788</v>
       </c>
     </row>
     <row r="12">
@@ -1432,12 +1480,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1455,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: -1.33% / +5.24% / -3.00%</t>
+          <t>BRSAN.IS: +1.40% / +1.77% / 0.00% | RALYH.IS: -0.58% / +5.24% / -3.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>5.880320398884153</v>
       </c>
       <c r="K12" t="n">
-        <v>9.722300049739951</v>
+        <v>10.89665867070169</v>
       </c>
       <c r="L12" t="n">
         <v>17.97495932189197</v>
@@ -1471,10 +1519,10 @@
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>140.8</v>
+        <v>140.5</v>
       </c>
       <c r="O12" t="n">
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="P12" t="n">
         <v>2.9</v>
@@ -1494,13 +1542,13 @@
         <v>21.61</v>
       </c>
       <c r="U12" t="n">
-        <v>81.25</v>
+        <v>91.074</v>
       </c>
       <c r="V12" t="n">
-        <v>71.72199999999999</v>
+        <v>73.56</v>
       </c>
       <c r="W12" t="n">
-        <v>-23.351</v>
+        <v>-22.333</v>
       </c>
     </row>
     <row r="13">
@@ -1514,68 +1562,80 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
+        </is>
+      </c>
       <c r="H13" t="n">
-        <v>12.43146471706449</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>22.83095636113686</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ALARK.IS: +2.71% / +3.57% / -3.86% | ASTOR.IS: +18.80% / +21.93% / 0.00% | BIMAS.IS: +2.44% / +3.87% / -0.86% | BRSAN.IS: +37.27% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+        </is>
+      </c>
       <c r="J13" t="n">
-        <v>-6.412181273130146</v>
+        <v>-5.037231846603429</v>
       </c>
       <c r="K13" t="n">
-        <v>8.290371306631972</v>
+        <v>8.616858291213214</v>
       </c>
       <c r="L13" t="n">
-        <v>12.30894614425559</v>
+        <v>23.4189376077676</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>139.3</v>
+        <v>180.8</v>
       </c>
       <c r="O13" t="n">
-        <v>48.1</v>
+        <v>45.9</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S13" t="n">
-        <v>12.004</v>
+        <v>22.513</v>
       </c>
       <c r="T13" t="n">
-        <v>11.714</v>
+        <v>22.513</v>
       </c>
       <c r="U13" t="n">
-        <v>11.106</v>
+        <v>51.916</v>
       </c>
       <c r="V13" t="n">
-        <v>21.903</v>
+        <v>43.918</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.583</v>
+        <v>-2.804</v>
       </c>
     </row>
     <row r="14">
@@ -1589,17 +1649,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1617,14 +1677,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.05% / +3.29% / -3.86% | ASTOR.IS: +16.99% / +21.93% / 0.00% | BIMAS.IS: +2.74% / +3.87% / -0.86% | BRSAN.IS: +35.35% / +45.64% / -0.48% | CANTE.IS: -0.02% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +2.71% / +3.57% / -3.86% | ASTOR.IS: +18.80% / +21.93% / 0.00% | BIMAS.IS: +2.44% / +3.87% / -0.86% | BRSAN.IS: +37.27% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>7.645862941764658</v>
+        <v>8.616858291213214</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1633,13 +1693,13 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>181.1</v>
+        <v>180.8</v>
       </c>
       <c r="O14" t="n">
-        <v>45.7</v>
+        <v>45.9</v>
       </c>
       <c r="P14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1656,13 +1716,13 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>46.305</v>
+        <v>51.916</v>
       </c>
       <c r="V14" t="n">
-        <v>42.632</v>
+        <v>43.918</v>
       </c>
       <c r="W14" t="n">
-        <v>-4.044</v>
+        <v>-2.804</v>
       </c>
     </row>
     <row r="16">
@@ -1807,12 +1867,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1834,7 +1894,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>117.1</v>
+        <v>116.9</v>
       </c>
       <c r="O18" t="n">
         <v>39.9</v>
@@ -1857,13 +1917,13 @@
         <v>28.567</v>
       </c>
       <c r="U18" t="n">
-        <v>72.258</v>
+        <v>75.807</v>
       </c>
       <c r="V18" t="n">
         <v>41.769</v>
       </c>
       <c r="W18" t="n">
-        <v>-68.88800000000001</v>
+        <v>-70.307</v>
       </c>
     </row>
     <row r="19">
@@ -1884,12 +1944,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1907,14 +1967,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.05% / +3.29% / -3.86% | BRSAN.IS: +7.60% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.71% / +3.57% / -3.86% | BRSAN.IS: +9.12% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>7.089110723950376</v>
+        <v>8.212562249251732</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1923,7 +1983,7 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>121.1</v>
+        <v>120.8</v>
       </c>
       <c r="O19" t="n">
         <v>43.5</v>
@@ -1946,13 +2006,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>90.432</v>
+        <v>96.80800000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>54.034</v>
+        <v>55.65</v>
       </c>
       <c r="W19" t="n">
-        <v>-26.882</v>
+        <v>-25.451</v>
       </c>
     </row>
     <row r="20">
@@ -1973,25 +2033,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ALARK.IS, DOHOL.IS</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>115.6477996753693</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J20" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K20" t="n">
-        <v>-28.64788373547042</v>
+        <v>-28.67642172789157</v>
       </c>
       <c r="L20" t="n">
         <v>25.50508358988237</v>
@@ -2000,36 +2072,36 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>93.5</v>
+        <v>94.3</v>
       </c>
       <c r="O20" t="n">
-        <v>37.4</v>
+        <v>37</v>
       </c>
       <c r="P20" t="n">
         <v>3.9</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>35.687</v>
+        <v>35.713</v>
       </c>
       <c r="T20" t="n">
-        <v>35.687</v>
+        <v>35.713</v>
       </c>
       <c r="U20" t="n">
-        <v>18.143</v>
+        <v>21.504</v>
       </c>
       <c r="V20" t="n">
-        <v>12.323</v>
+        <v>12.278</v>
       </c>
       <c r="W20" t="n">
-        <v>-65.557</v>
+        <v>-67.498</v>
       </c>
     </row>
     <row r="21">
@@ -2050,25 +2122,37 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, TAVHL.IS</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>96.86982435918456</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TAVHL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J21" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3078108772402999</v>
+        <v>0.2676917652018496</v>
       </c>
       <c r="L21" t="n">
         <v>13.72502171397572</v>
@@ -2077,21 +2161,21 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N21" t="n">
-        <v>46.3</v>
+        <v>47.2</v>
       </c>
       <c r="O21" t="n">
-        <v>51.1</v>
+        <v>50</v>
       </c>
       <c r="P21" t="n">
         <v>4.6</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
         <v>29.993</v>
@@ -2100,13 +2184,13 @@
         <v>29.993</v>
       </c>
       <c r="U21" t="n">
-        <v>1.107</v>
+        <v>3.94</v>
       </c>
       <c r="V21" t="n">
-        <v>-6.769</v>
+        <v>-6.806</v>
       </c>
       <c r="W21" t="n">
-        <v>-42.845</v>
+        <v>-44.104</v>
       </c>
     </row>
     <row r="22">
@@ -2127,25 +2211,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ALARK.IS, DOHOL.IS, TAVHL.IS</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>87.24519408485627</v>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00% | TAVHL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J22" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7349222980747139</v>
+        <v>-0.774623035017985</v>
       </c>
       <c r="L22" t="n">
         <v>10.56563994340933</v>
@@ -2154,21 +2250,21 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>71.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="O22" t="n">
-        <v>38.4</v>
+        <v>37.6</v>
       </c>
       <c r="P22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S22" t="n">
         <v>29.287</v>
@@ -2177,13 +2273,13 @@
         <v>29.287</v>
       </c>
       <c r="U22" t="n">
-        <v>32.864</v>
+        <v>37.054</v>
       </c>
       <c r="V22" t="n">
-        <v>14.374</v>
+        <v>14.328</v>
       </c>
       <c r="W22" t="n">
-        <v>-47.224</v>
+        <v>-48.788</v>
       </c>
     </row>
     <row r="23">
@@ -2204,12 +2300,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2227,14 +2323,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: -1.33% / +5.24% / -3.00%</t>
+          <t>BRSAN.IS: +1.40% / +1.77% / 0.00% | RALYH.IS: -0.58% / +5.24% / -3.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>5.880320398884153</v>
       </c>
       <c r="K23" t="n">
-        <v>9.722300049739951</v>
+        <v>10.89665867070169</v>
       </c>
       <c r="L23" t="n">
         <v>17.97495932189197</v>
@@ -2243,10 +2339,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>140.8</v>
+        <v>140.5</v>
       </c>
       <c r="O23" t="n">
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="P23" t="n">
         <v>2.9</v>
@@ -2266,13 +2362,13 @@
         <v>21.61</v>
       </c>
       <c r="U23" t="n">
-        <v>81.25</v>
+        <v>91.074</v>
       </c>
       <c r="V23" t="n">
-        <v>71.72199999999999</v>
+        <v>73.56</v>
       </c>
       <c r="W23" t="n">
-        <v>-23.351</v>
+        <v>-22.333</v>
       </c>
     </row>
     <row r="24">
@@ -2283,7 +2379,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2293,12 +2389,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2316,14 +2412,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.05% / +3.29% / -3.86% | ASTOR.IS: +16.99% / +21.93% / 0.00% | BIMAS.IS: +2.74% / +3.87% / -0.86% | BRSAN.IS: +35.35% / +45.64% / -0.48% | CANTE.IS: -0.02% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +2.71% / +3.57% / -3.86% | ASTOR.IS: +18.80% / +21.93% / 0.00% | BIMAS.IS: +2.44% / +3.87% / -0.86% | BRSAN.IS: +37.27% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K24" t="n">
-        <v>7.645862941764658</v>
+        <v>8.616858291213214</v>
       </c>
       <c r="L24" t="n">
         <v>23.4189376077676</v>
@@ -2332,13 +2428,13 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>181.1</v>
+        <v>180.8</v>
       </c>
       <c r="O24" t="n">
-        <v>45.7</v>
+        <v>45.9</v>
       </c>
       <c r="P24" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2355,13 +2451,13 @@
         <v>22.513</v>
       </c>
       <c r="U24" t="n">
-        <v>46.305</v>
+        <v>51.916</v>
       </c>
       <c r="V24" t="n">
-        <v>42.632</v>
+        <v>43.918</v>
       </c>
       <c r="W24" t="n">
-        <v>-4.044</v>
+        <v>-2.804</v>
       </c>
     </row>
     <row r="25">
@@ -2372,73 +2468,85 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S3|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
+        </is>
+      </c>
       <c r="H25" t="n">
-        <v>12.43146471706449</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>22.83095636113686</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ALARK.IS: +2.71% / +3.57% / -3.86% | ASTOR.IS: +18.80% / +21.93% / 0.00% | BIMAS.IS: +2.44% / +3.87% / -0.86% | BRSAN.IS: +37.27% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+        </is>
+      </c>
       <c r="J25" t="n">
-        <v>-6.412181273130146</v>
+        <v>-5.037231846603429</v>
       </c>
       <c r="K25" t="n">
-        <v>8.290371306631972</v>
+        <v>8.616858291213214</v>
       </c>
       <c r="L25" t="n">
-        <v>12.30894614425559</v>
+        <v>23.4189376077676</v>
       </c>
       <c r="M25" t="n">
         <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>139.3</v>
+        <v>180.8</v>
       </c>
       <c r="O25" t="n">
-        <v>48.1</v>
+        <v>45.9</v>
       </c>
       <c r="P25" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S25" t="n">
-        <v>12.004</v>
+        <v>22.513</v>
       </c>
       <c r="T25" t="n">
-        <v>11.714</v>
+        <v>22.513</v>
       </c>
       <c r="U25" t="n">
-        <v>11.106</v>
+        <v>51.916</v>
       </c>
       <c r="V25" t="n">
-        <v>21.903</v>
+        <v>43.918</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.583</v>
+        <v>-2.804</v>
       </c>
     </row>
   </sheetData>
@@ -2468,7 +2576,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -2628,12 +2736,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2655,7 +2763,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>65.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="O3" t="n">
         <v>45.9</v>
@@ -2678,13 +2786,13 @@
         <v>31.839</v>
       </c>
       <c r="U3" t="n">
-        <v>11.666</v>
+        <v>15.209</v>
       </c>
       <c r="V3" t="n">
         <v>27.773</v>
       </c>
       <c r="W3" t="n">
-        <v>-52.161</v>
+        <v>-53.815</v>
       </c>
     </row>
     <row r="4">
@@ -2703,12 +2811,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2730,7 +2838,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N4" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="O4" t="n">
         <v>46.7</v>
@@ -2753,13 +2861,13 @@
         <v>30.704</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.924</v>
+        <v>2.192</v>
       </c>
       <c r="V4" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>-43.899</v>
+        <v>-45.28</v>
       </c>
     </row>
     <row r="5">
@@ -2778,12 +2886,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -2805,7 +2913,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="O5" t="n">
         <v>46.7</v>
@@ -2828,13 +2936,13 @@
         <v>30.704</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.924</v>
+        <v>2.192</v>
       </c>
       <c r="V5" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-43.899</v>
+        <v>-45.28</v>
       </c>
     </row>
     <row r="6">
@@ -2853,12 +2961,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -2880,7 +2988,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="O6" t="n">
         <v>46.7</v>
@@ -2903,13 +3011,13 @@
         <v>30.704</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.924</v>
+        <v>2.192</v>
       </c>
       <c r="V6" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>-43.899</v>
+        <v>-45.28</v>
       </c>
     </row>
     <row r="7">
@@ -2928,12 +3036,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -2955,7 +3063,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N7" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="O7" t="n">
         <v>46.7</v>
@@ -2978,13 +3086,13 @@
         <v>30.704</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.924</v>
+        <v>2.192</v>
       </c>
       <c r="V7" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>-43.899</v>
+        <v>-45.28</v>
       </c>
     </row>
     <row r="8">
@@ -3003,25 +3111,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ASTOR.IS, BRSAN.IS, TRALT.IS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ASTOR.IS: 2026-08-27 | BRSAN.IS: 2026-08-27 | TRALT.IS: 2026-08-27</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>65.37996855043156</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J8" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K8" t="n">
-        <v>-21.69466663273255</v>
+        <v>-21.725984589795</v>
       </c>
       <c r="L8" t="n">
         <v>16.84258916554939</v>
@@ -3030,36 +3150,36 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>110.7</v>
+        <v>111.9</v>
       </c>
       <c r="O8" t="n">
-        <v>38.4</v>
+        <v>37.9</v>
       </c>
       <c r="P8" t="n">
         <v>4.9</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>28.888</v>
+        <v>28.916</v>
       </c>
       <c r="T8" t="n">
-        <v>28.888</v>
+        <v>28.916</v>
       </c>
       <c r="U8" t="n">
-        <v>41.398</v>
+        <v>44.043</v>
       </c>
       <c r="V8" t="n">
-        <v>14.358</v>
+        <v>14.312</v>
       </c>
       <c r="W8" t="n">
-        <v>-57.44</v>
+        <v>-58.596</v>
       </c>
     </row>
     <row r="9">
@@ -3078,12 +3198,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3153,12 +3273,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3180,7 +3300,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>68.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="O10" t="n">
         <v>45.7</v>
@@ -3203,13 +3323,13 @@
         <v>13.513</v>
       </c>
       <c r="U10" t="n">
-        <v>12.231</v>
+        <v>14.45</v>
       </c>
       <c r="V10" t="n">
         <v>13.389</v>
       </c>
       <c r="W10" t="n">
-        <v>-16.824</v>
+        <v>-17.156</v>
       </c>
     </row>
     <row r="11">
@@ -3228,12 +3348,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3255,7 +3375,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="O11" t="n">
         <v>44.2</v>
@@ -3278,13 +3398,13 @@
         <v>13.42</v>
       </c>
       <c r="U11" t="n">
-        <v>16.222</v>
+        <v>18.52</v>
       </c>
       <c r="V11" t="n">
         <v>12.908</v>
       </c>
       <c r="W11" t="n">
-        <v>-18.015</v>
+        <v>-18.371</v>
       </c>
     </row>
     <row r="12">
@@ -3303,12 +3423,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3326,14 +3446,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.44% / +3.81% / -0.90% | ASTOR.IS: -0.75% / +2.56% / -2.12%</t>
+          <t>AKBNK.IS: +1.99% / +3.81% / -0.90% | ASTOR.IS: +0.79% / +2.56% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>21.36329082917474</v>
+        <v>22.6289940339258</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3342,10 +3462,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N12" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>48.8</v>
+        <v>49.4</v>
       </c>
       <c r="P12" t="n">
         <v>3.6</v>
@@ -3365,10 +3485,10 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>45.068</v>
+        <v>49.613</v>
       </c>
       <c r="V12" t="n">
-        <v>28.326</v>
+        <v>29.664</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -3390,12 +3510,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3413,14 +3533,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: -0.75% / +2.56% / -2.12%</t>
+          <t>AKBNK.IS: +0.53% / +1.57% / 0.00% | ASTOR.IS: +0.79% / +2.56% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>20.62744702883403</v>
+        <v>21.88221956835365</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3429,10 +3549,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N13" t="n">
-        <v>128.5</v>
+        <v>128.2</v>
       </c>
       <c r="O13" t="n">
-        <v>49.6</v>
+        <v>50.4</v>
       </c>
       <c r="P13" t="n">
         <v>3.9</v>
@@ -3452,10 +3572,10 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>53.443</v>
+        <v>56.368</v>
       </c>
       <c r="V13" t="n">
-        <v>40.851</v>
+        <v>42.316</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -3477,12 +3597,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3500,14 +3620,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +5.16% / +7.63% / -0.81% | BRSAN.IS: +6.24% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +5.74% / +7.63% / -0.81% | BRSAN.IS: +7.75% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>14.71804705907167</v>
+        <v>15.84675500775874</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3539,13 +3659,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>49.577</v>
+        <v>52.249</v>
       </c>
       <c r="V14" t="n">
-        <v>35.971</v>
+        <v>37.308</v>
       </c>
       <c r="W14" t="n">
-        <v>-13.818</v>
+        <v>-12.444</v>
       </c>
     </row>
     <row r="16">
@@ -3690,12 +3810,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -3717,7 +3837,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>65.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="O18" t="n">
         <v>45.9</v>
@@ -3740,13 +3860,13 @@
         <v>31.839</v>
       </c>
       <c r="U18" t="n">
-        <v>11.666</v>
+        <v>15.209</v>
       </c>
       <c r="V18" t="n">
         <v>27.773</v>
       </c>
       <c r="W18" t="n">
-        <v>-52.161</v>
+        <v>-53.815</v>
       </c>
     </row>
     <row r="19">
@@ -3767,12 +3887,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -3794,7 +3914,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="O19" t="n">
         <v>46.7</v>
@@ -3817,13 +3937,13 @@
         <v>30.704</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.924</v>
+        <v>2.192</v>
       </c>
       <c r="V19" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>-43.899</v>
+        <v>-45.28</v>
       </c>
     </row>
     <row r="20">
@@ -3844,12 +3964,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -3871,7 +3991,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="O20" t="n">
         <v>46.7</v>
@@ -3894,13 +4014,13 @@
         <v>30.704</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.924</v>
+        <v>2.192</v>
       </c>
       <c r="V20" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-43.899</v>
+        <v>-45.28</v>
       </c>
     </row>
     <row r="21">
@@ -3921,25 +4041,37 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ASTOR.IS, BRSAN.IS, TRALT.IS</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ASTOR.IS: 2026-08-27 | BRSAN.IS: 2026-08-27 | TRALT.IS: 2026-08-27</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>65.37996855043156</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J21" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K21" t="n">
-        <v>-21.69466663273255</v>
+        <v>-21.725984589795</v>
       </c>
       <c r="L21" t="n">
         <v>16.84258916554939</v>
@@ -3948,36 +4080,36 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>110.7</v>
+        <v>111.9</v>
       </c>
       <c r="O21" t="n">
-        <v>38.4</v>
+        <v>37.9</v>
       </c>
       <c r="P21" t="n">
         <v>4.9</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>28.888</v>
+        <v>28.916</v>
       </c>
       <c r="T21" t="n">
-        <v>28.888</v>
+        <v>28.916</v>
       </c>
       <c r="U21" t="n">
-        <v>41.398</v>
+        <v>44.043</v>
       </c>
       <c r="V21" t="n">
-        <v>14.358</v>
+        <v>14.312</v>
       </c>
       <c r="W21" t="n">
-        <v>-57.44</v>
+        <v>-58.596</v>
       </c>
     </row>
     <row r="22">
@@ -3998,12 +4130,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4025,7 +4157,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="O22" t="n">
         <v>44.2</v>
@@ -4048,13 +4180,13 @@
         <v>13.42</v>
       </c>
       <c r="U22" t="n">
-        <v>16.222</v>
+        <v>18.52</v>
       </c>
       <c r="V22" t="n">
         <v>12.908</v>
       </c>
       <c r="W22" t="n">
-        <v>-18.015</v>
+        <v>-18.371</v>
       </c>
     </row>
     <row r="23">
@@ -4075,12 +4207,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -4102,7 +4234,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N23" t="n">
-        <v>68.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="O23" t="n">
         <v>45.7</v>
@@ -4125,13 +4257,13 @@
         <v>13.513</v>
       </c>
       <c r="U23" t="n">
-        <v>12.231</v>
+        <v>14.45</v>
       </c>
       <c r="V23" t="n">
         <v>13.389</v>
       </c>
       <c r="W23" t="n">
-        <v>-16.824</v>
+        <v>-17.156</v>
       </c>
     </row>
     <row r="24">
@@ -4152,12 +4284,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4229,12 +4361,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4252,14 +4384,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +5.16% / +7.63% / -0.81% | BRSAN.IS: +6.24% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +5.74% / +7.63% / -0.81% | BRSAN.IS: +7.75% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>14.71804705907167</v>
+        <v>15.84675500775874</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4291,13 +4423,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>49.577</v>
+        <v>52.249</v>
       </c>
       <c r="V25" t="n">
-        <v>35.971</v>
+        <v>37.308</v>
       </c>
       <c r="W25" t="n">
-        <v>-13.818</v>
+        <v>-12.444</v>
       </c>
     </row>
     <row r="26">
@@ -4318,12 +4450,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4341,14 +4473,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.44% / +3.81% / -0.90% | ASTOR.IS: -0.75% / +2.56% / -2.12%</t>
+          <t>AKBNK.IS: +1.99% / +3.81% / -0.90% | ASTOR.IS: +0.79% / +2.56% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>21.36329082917474</v>
+        <v>22.6289940339258</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4357,10 +4489,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N26" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>48.8</v>
+        <v>49.4</v>
       </c>
       <c r="P26" t="n">
         <v>3.6</v>
@@ -4380,10 +4512,10 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>45.068</v>
+        <v>49.613</v>
       </c>
       <c r="V26" t="n">
-        <v>28.326</v>
+        <v>29.664</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4407,12 +4539,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4430,14 +4562,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: -0.75% / +2.56% / -2.12%</t>
+          <t>AKBNK.IS: +0.53% / +1.57% / 0.00% | ASTOR.IS: +0.79% / +2.56% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>20.62744702883403</v>
+        <v>21.88221956835365</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4446,10 +4578,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N27" t="n">
-        <v>128.5</v>
+        <v>128.2</v>
       </c>
       <c r="O27" t="n">
-        <v>49.6</v>
+        <v>50.4</v>
       </c>
       <c r="P27" t="n">
         <v>3.9</v>
@@ -4469,10 +4601,10 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>53.443</v>
+        <v>56.368</v>
       </c>
       <c r="V27" t="n">
-        <v>40.851</v>
+        <v>42.316</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -831,14 +831,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.71% / +3.57% / -3.86% | BRSAN.IS: +9.12% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +4.21% / +4.70% / -3.86% | BRSAN.IS: +10.72% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>8.212562249251732</v>
+        <v>9.798971054949002</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -870,13 +870,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>96.80800000000001</v>
+        <v>99.694</v>
       </c>
       <c r="V4" t="n">
-        <v>55.65</v>
+        <v>57.932</v>
       </c>
       <c r="W4" t="n">
-        <v>-25.451</v>
+        <v>-22.566</v>
       </c>
     </row>
     <row r="5">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.71% / +3.57% / -3.86% | BRSAN.IS: +9.12% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +4.21% / +4.70% / -3.86% | BRSAN.IS: +10.72% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>8.212562249251732</v>
+        <v>9.798971054949002</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1119,13 +1119,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>96.80800000000001</v>
+        <v>99.694</v>
       </c>
       <c r="V7" t="n">
-        <v>55.65</v>
+        <v>57.932</v>
       </c>
       <c r="W7" t="n">
-        <v>-25.451</v>
+        <v>-22.566</v>
       </c>
     </row>
     <row r="8">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +1.40% / +1.77% / 0.00% | RALYH.IS: -0.58% / +5.24% / -3.00%</t>
+          <t>BRSAN.IS: +2.88% / +3.12% / 0.00% | RALYH.IS: -1.24% / +5.24% / -3.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>5.880320398884153</v>
       </c>
       <c r="K12" t="n">
-        <v>10.89665867070169</v>
+        <v>11.3650975673631</v>
       </c>
       <c r="L12" t="n">
         <v>17.97495932189197</v>
@@ -1542,13 +1542,13 @@
         <v>21.61</v>
       </c>
       <c r="U12" t="n">
-        <v>91.074</v>
+        <v>91.881</v>
       </c>
       <c r="V12" t="n">
-        <v>73.56</v>
+        <v>74.29300000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>-22.333</v>
+        <v>-21.526</v>
       </c>
     </row>
     <row r="13">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.71% / +3.57% / -3.86% | ASTOR.IS: +18.80% / +21.93% / 0.00% | BIMAS.IS: +2.44% / +3.87% / -0.86% | BRSAN.IS: +37.27% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +4.21% / +4.70% / -3.86% | ASTOR.IS: +22.00% / +23.58% / 0.00% | BIMAS.IS: +1.70% / +3.87% / -0.86% | BRSAN.IS: +39.28% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K13" t="n">
-        <v>8.616858291213214</v>
+        <v>9.813309577268669</v>
       </c>
       <c r="L13" t="n">
         <v>23.4189376077676</v>
@@ -1629,13 +1629,13 @@
         <v>22.513</v>
       </c>
       <c r="U13" t="n">
-        <v>51.916</v>
+        <v>53.589</v>
       </c>
       <c r="V13" t="n">
-        <v>43.918</v>
+        <v>45.504</v>
       </c>
       <c r="W13" t="n">
-        <v>-2.804</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="14">
@@ -1677,14 +1677,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.71% / +3.57% / -3.86% | ASTOR.IS: +18.80% / +21.93% / 0.00% | BIMAS.IS: +2.44% / +3.87% / -0.86% | BRSAN.IS: +37.27% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +4.21% / +4.70% / -3.86% | ASTOR.IS: +22.00% / +23.58% / 0.00% | BIMAS.IS: +1.70% / +3.87% / -0.86% | BRSAN.IS: +39.28% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>8.616858291213214</v>
+        <v>9.813309577268669</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1716,13 +1716,13 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>51.916</v>
+        <v>53.589</v>
       </c>
       <c r="V14" t="n">
-        <v>43.918</v>
+        <v>45.504</v>
       </c>
       <c r="W14" t="n">
-        <v>-2.804</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="16">
@@ -1967,14 +1967,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.71% / +3.57% / -3.86% | BRSAN.IS: +9.12% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +4.21% / +4.70% / -3.86% | BRSAN.IS: +10.72% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>8.212562249251732</v>
+        <v>9.798971054949002</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -2006,13 +2006,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>96.80800000000001</v>
+        <v>99.694</v>
       </c>
       <c r="V19" t="n">
-        <v>55.65</v>
+        <v>57.932</v>
       </c>
       <c r="W19" t="n">
-        <v>-25.451</v>
+        <v>-22.566</v>
       </c>
     </row>
     <row r="20">
@@ -2323,14 +2323,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +1.40% / +1.77% / 0.00% | RALYH.IS: -0.58% / +5.24% / -3.00%</t>
+          <t>BRSAN.IS: +2.88% / +3.12% / 0.00% | RALYH.IS: -1.24% / +5.24% / -3.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>5.880320398884153</v>
       </c>
       <c r="K23" t="n">
-        <v>10.89665867070169</v>
+        <v>11.3650975673631</v>
       </c>
       <c r="L23" t="n">
         <v>17.97495932189197</v>
@@ -2362,13 +2362,13 @@
         <v>21.61</v>
       </c>
       <c r="U23" t="n">
-        <v>91.074</v>
+        <v>91.881</v>
       </c>
       <c r="V23" t="n">
-        <v>73.56</v>
+        <v>74.29300000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>-22.333</v>
+        <v>-21.526</v>
       </c>
     </row>
     <row r="24">
@@ -2412,14 +2412,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.71% / +3.57% / -3.86% | ASTOR.IS: +18.80% / +21.93% / 0.00% | BIMAS.IS: +2.44% / +3.87% / -0.86% | BRSAN.IS: +37.27% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +4.21% / +4.70% / -3.86% | ASTOR.IS: +22.00% / +23.58% / 0.00% | BIMAS.IS: +1.70% / +3.87% / -0.86% | BRSAN.IS: +39.28% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K24" t="n">
-        <v>8.616858291213214</v>
+        <v>9.813309577268669</v>
       </c>
       <c r="L24" t="n">
         <v>23.4189376077676</v>
@@ -2451,13 +2451,13 @@
         <v>22.513</v>
       </c>
       <c r="U24" t="n">
-        <v>51.916</v>
+        <v>53.589</v>
       </c>
       <c r="V24" t="n">
-        <v>43.918</v>
+        <v>45.504</v>
       </c>
       <c r="W24" t="n">
-        <v>-2.804</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="25">
@@ -2501,14 +2501,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.71% / +3.57% / -3.86% | ASTOR.IS: +18.80% / +21.93% / 0.00% | BIMAS.IS: +2.44% / +3.87% / -0.86% | BRSAN.IS: +37.27% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +4.21% / +4.70% / -3.86% | ASTOR.IS: +22.00% / +23.58% / 0.00% | BIMAS.IS: +1.70% / +3.87% / -0.86% | BRSAN.IS: +39.28% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K25" t="n">
-        <v>8.616858291213214</v>
+        <v>9.813309577268669</v>
       </c>
       <c r="L25" t="n">
         <v>23.4189376077676</v>
@@ -2540,13 +2540,13 @@
         <v>22.513</v>
       </c>
       <c r="U25" t="n">
-        <v>51.916</v>
+        <v>53.589</v>
       </c>
       <c r="V25" t="n">
-        <v>43.918</v>
+        <v>45.504</v>
       </c>
       <c r="W25" t="n">
-        <v>-2.804</v>
+        <v>-1.13</v>
       </c>
     </row>
   </sheetData>
@@ -3446,14 +3446,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.99% / +3.81% / -0.90% | ASTOR.IS: +0.79% / +2.56% / -2.12%</t>
+          <t>AKBNK.IS: +1.51% / +3.81% / -0.90% | ASTOR.IS: +3.50% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>22.6289940339258</v>
+        <v>23.97433914763116</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3485,10 +3485,10 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>49.613</v>
+        <v>51.254</v>
       </c>
       <c r="V12" t="n">
-        <v>29.664</v>
+        <v>31.086</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -3533,14 +3533,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.53% / +1.57% / 0.00% | ASTOR.IS: +0.79% / +2.56% / -2.12%</t>
+          <t>AKBNK.IS: +0.05% / +1.57% / -0.07% | ASTOR.IS: +3.50% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>21.88221956835365</v>
+        <v>23.2232424710131</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3572,10 +3572,10 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>56.368</v>
+        <v>58.089</v>
       </c>
       <c r="V13" t="n">
-        <v>42.316</v>
+        <v>43.882</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +5.74% / +7.63% / -0.81% | BRSAN.IS: +7.75% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +5.23% / +7.63% / -0.81% | BRSAN.IS: +9.33% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>15.84675500775874</v>
+        <v>16.43107972063114</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3659,13 +3659,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>52.249</v>
+        <v>53.017</v>
       </c>
       <c r="V14" t="n">
-        <v>37.308</v>
+        <v>38.001</v>
       </c>
       <c r="W14" t="n">
-        <v>-12.444</v>
+        <v>-11.676</v>
       </c>
     </row>
     <row r="16">
@@ -4384,14 +4384,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +5.74% / +7.63% / -0.81% | BRSAN.IS: +7.75% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +5.23% / +7.63% / -0.81% | BRSAN.IS: +9.33% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>15.84675500775874</v>
+        <v>16.43107972063114</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4423,13 +4423,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>52.249</v>
+        <v>53.017</v>
       </c>
       <c r="V25" t="n">
-        <v>37.308</v>
+        <v>38.001</v>
       </c>
       <c r="W25" t="n">
-        <v>-12.444</v>
+        <v>-11.676</v>
       </c>
     </row>
     <row r="26">
@@ -4473,14 +4473,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.99% / +3.81% / -0.90% | ASTOR.IS: +0.79% / +2.56% / -2.12%</t>
+          <t>AKBNK.IS: +1.51% / +3.81% / -0.90% | ASTOR.IS: +3.50% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>22.6289940339258</v>
+        <v>23.97433914763116</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4512,10 +4512,10 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>49.613</v>
+        <v>51.254</v>
       </c>
       <c r="V26" t="n">
-        <v>29.664</v>
+        <v>31.086</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4562,14 +4562,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.53% / +1.57% / 0.00% | ASTOR.IS: +0.79% / +2.56% / -2.12%</t>
+          <t>AKBNK.IS: +0.05% / +1.57% / -0.07% | ASTOR.IS: +3.50% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>21.88221956835365</v>
+        <v>23.2232424710131</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4601,10 +4601,10 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>56.368</v>
+        <v>58.089</v>
       </c>
       <c r="V27" t="n">
-        <v>42.316</v>
+        <v>43.882</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -831,14 +831,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +4.21% / +4.70% / -3.86% | BRSAN.IS: +10.72% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.90% / +4.70% / -3.86% | BRSAN.IS: +12.33% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>9.798971054949002</v>
+        <v>9.974577446654909</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -870,13 +870,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>99.694</v>
+        <v>100.013</v>
       </c>
       <c r="V4" t="n">
-        <v>57.932</v>
+        <v>58.185</v>
       </c>
       <c r="W4" t="n">
-        <v>-22.566</v>
+        <v>-22.246</v>
       </c>
     </row>
     <row r="5">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +4.21% / +4.70% / -3.86% | BRSAN.IS: +10.72% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.90% / +4.70% / -3.86% | BRSAN.IS: +12.33% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>9.798971054949002</v>
+        <v>9.974577446654909</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1119,13 +1119,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>99.694</v>
+        <v>100.013</v>
       </c>
       <c r="V7" t="n">
-        <v>57.932</v>
+        <v>58.185</v>
       </c>
       <c r="W7" t="n">
-        <v>-22.566</v>
+        <v>-22.246</v>
       </c>
     </row>
     <row r="8">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +2.88% / +3.12% / 0.00% | RALYH.IS: -1.24% / +5.24% / -3.00%</t>
+          <t>BRSAN.IS: +4.37% / +4.60% / 0.00% | RALYH.IS: -1.89% / +5.24% / -3.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>5.880320398884153</v>
       </c>
       <c r="K12" t="n">
-        <v>11.3650975673631</v>
+        <v>11.8335364640245</v>
       </c>
       <c r="L12" t="n">
         <v>17.97495932189197</v>
@@ -1542,13 +1542,13 @@
         <v>21.61</v>
       </c>
       <c r="U12" t="n">
-        <v>91.881</v>
+        <v>92.68899999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>74.29300000000001</v>
+        <v>75.026</v>
       </c>
       <c r="W12" t="n">
-        <v>-21.526</v>
+        <v>-20.719</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T3_kademeli_slot|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
+          <t>ALARK.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
+          <t>ALARK.IS: 2026-08-21 | BRSAN.IS: 2026-08-17</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>22.83095636113686</v>
+        <v>122.3614568902708</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALARK.IS: +4.21% / +4.70% / -3.86% | ASTOR.IS: +22.00% / +23.58% / 0.00% | BIMAS.IS: +1.70% / +3.87% / -0.86% | BRSAN.IS: +39.28% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +2.90% / +4.70% / -3.86% | BRSAN.IS: +12.33% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-5.037231846603429</v>
+        <v>42.36862230756586</v>
       </c>
       <c r="K13" t="n">
-        <v>9.813309577268669</v>
+        <v>9.974578414255507</v>
       </c>
       <c r="L13" t="n">
-        <v>23.4189376077676</v>
+        <v>18.35191516155641</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>180.8</v>
+        <v>121.3</v>
       </c>
       <c r="O13" t="n">
-        <v>45.9</v>
+        <v>42.9</v>
       </c>
       <c r="P13" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1620,22 +1620,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>22.513</v>
+        <v>27.525</v>
       </c>
       <c r="T13" t="n">
-        <v>22.513</v>
+        <v>27.525</v>
       </c>
       <c r="U13" t="n">
-        <v>53.589</v>
+        <v>90.711</v>
       </c>
       <c r="V13" t="n">
-        <v>45.504</v>
+        <v>51.408</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.13</v>
+        <v>-21.212</v>
       </c>
     </row>
     <row r="14">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
+          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1677,14 +1677,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: +4.21% / +4.70% / -3.86% | ASTOR.IS: +22.00% / +23.58% / 0.00% | BIMAS.IS: +1.70% / +3.87% / -0.86% | BRSAN.IS: +39.28% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +2.90% / +4.70% / -3.86% | ASTOR.IS: +21.22% / +23.58% / 0.00% | BIMAS.IS: +1.76% / +3.87% / -0.86% | BRSAN.IS: +41.29% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>9.813309577268669</v>
+        <v>9.787424677056823</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1716,13 +1716,13 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>53.589</v>
+        <v>53.553</v>
       </c>
       <c r="V14" t="n">
-        <v>45.504</v>
+        <v>45.469</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.13</v>
+        <v>-1.167</v>
       </c>
     </row>
     <row r="16">
@@ -1967,14 +1967,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +4.21% / +4.70% / -3.86% | BRSAN.IS: +10.72% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.90% / +4.70% / -3.86% | BRSAN.IS: +12.33% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>9.798971054949002</v>
+        <v>9.974577446654909</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -2006,29 +2006,29 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>99.694</v>
+        <v>100.013</v>
       </c>
       <c r="V19" t="n">
-        <v>57.932</v>
+        <v>58.185</v>
       </c>
       <c r="W19" t="n">
-        <v>-22.566</v>
+        <v>-22.246</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2043,42 +2043,42 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ALARK.IS, DOHOL.IS</t>
+          <t>ALARK.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27</t>
+          <t>ALARK.IS: 2026-08-21 | BRSAN.IS: 2026-08-17</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>115.6477996753693</v>
+        <v>122.3614568902708</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +2.90% / +4.70% / -3.86% | BRSAN.IS: +12.33% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>20.71036906913848</v>
+        <v>42.36862230756586</v>
       </c>
       <c r="K20" t="n">
-        <v>-28.67642172789157</v>
+        <v>9.974578414255507</v>
       </c>
       <c r="L20" t="n">
-        <v>25.50508358988237</v>
+        <v>18.35191516155641</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>94.3</v>
+        <v>121.3</v>
       </c>
       <c r="O20" t="n">
-        <v>37</v>
+        <v>42.9</v>
       </c>
       <c r="P20" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2089,35 +2089,35 @@
         <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>35.713</v>
+        <v>27.525</v>
       </c>
       <c r="T20" t="n">
-        <v>35.713</v>
+        <v>27.525</v>
       </c>
       <c r="U20" t="n">
-        <v>21.504</v>
+        <v>90.711</v>
       </c>
       <c r="V20" t="n">
-        <v>12.278</v>
+        <v>51.408</v>
       </c>
       <c r="W20" t="n">
-        <v>-67.498</v>
+        <v>-21.212</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
+          <t>KAR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3 | 2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T2_rotasyon|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2132,42 +2132,42 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TAVHL.IS</t>
+          <t>ALARK.IS, DOHOL.IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
+          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>96.86982435918456</v>
+        <v>115.6477996753693</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TAVHL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>42.40716574291981</v>
+        <v>20.71036906913848</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2676917652018496</v>
+        <v>-28.67642172789157</v>
       </c>
       <c r="L21" t="n">
-        <v>13.72502171397572</v>
+        <v>25.50508358988237</v>
       </c>
       <c r="M21" t="n">
-        <v>94.44444444444444</v>
+        <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>47.2</v>
+        <v>94.3</v>
       </c>
       <c r="O21" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="P21" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -2178,35 +2178,35 @@
         <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>29.993</v>
+        <v>35.713</v>
       </c>
       <c r="T21" t="n">
-        <v>29.993</v>
+        <v>35.713</v>
       </c>
       <c r="U21" t="n">
-        <v>3.94</v>
+        <v>21.504</v>
       </c>
       <c r="V21" t="n">
-        <v>-6.806</v>
+        <v>12.278</v>
       </c>
       <c r="W21" t="n">
-        <v>-44.104</v>
+        <v>-67.498</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 | 2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2221,39 +2221,39 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ALARK.IS, DOHOL.IS, TAVHL.IS</t>
+          <t>BRSAN.IS, TAVHL.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
+          <t>BRSAN.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>87.24519408485627</v>
+        <v>96.86982435918456</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00% | TAVHL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TAVHL.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>29.19814518717994</v>
+        <v>42.40716574291981</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.774623035017985</v>
+        <v>0.2676917652018496</v>
       </c>
       <c r="L22" t="n">
-        <v>10.56563994340933</v>
+        <v>13.72502171397572</v>
       </c>
       <c r="M22" t="n">
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>73.2</v>
+        <v>47.2</v>
       </c>
       <c r="O22" t="n">
-        <v>37.6</v>
+        <v>50</v>
       </c>
       <c r="P22" t="n">
         <v>4.6</v>
@@ -2264,38 +2264,38 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>29.287</v>
+        <v>29.993</v>
       </c>
       <c r="T22" t="n">
-        <v>29.287</v>
+        <v>29.993</v>
       </c>
       <c r="U22" t="n">
-        <v>37.054</v>
+        <v>3.94</v>
       </c>
       <c r="V22" t="n">
-        <v>14.328</v>
+        <v>-6.806</v>
       </c>
       <c r="W22" t="n">
-        <v>-48.788</v>
+        <v>-44.104</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T1_genislik_skor|E50|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2310,42 +2310,42 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BRSAN.IS, RALYH.IS</t>
+          <t>ALARK.IS, DOHOL.IS, TAVHL.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-26 | RALYH.IS: 2026-08-14</t>
+          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>35.05565740671337</v>
+        <v>87.24519408485627</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +2.88% / +3.12% / 0.00% | RALYH.IS: -1.24% / +5.24% / -3.00%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00% | TAVHL.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>5.880320398884153</v>
+        <v>29.19814518717994</v>
       </c>
       <c r="K23" t="n">
-        <v>11.3650975673631</v>
+        <v>-0.774623035017985</v>
       </c>
       <c r="L23" t="n">
-        <v>17.97495932189197</v>
+        <v>10.56563994340933</v>
       </c>
       <c r="M23" t="n">
-        <v>100</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N23" t="n">
-        <v>140.5</v>
+        <v>73.2</v>
       </c>
       <c r="O23" t="n">
-        <v>46.5</v>
+        <v>37.6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2353,22 +2353,22 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S23" t="n">
-        <v>21.61</v>
+        <v>29.287</v>
       </c>
       <c r="T23" t="n">
-        <v>21.61</v>
+        <v>29.287</v>
       </c>
       <c r="U23" t="n">
-        <v>91.881</v>
+        <v>37.054</v>
       </c>
       <c r="V23" t="n">
-        <v>74.29300000000001</v>
+        <v>14.328</v>
       </c>
       <c r="W23" t="n">
-        <v>-21.526</v>
+        <v>-48.788</v>
       </c>
     </row>
     <row r="24">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2399,42 +2399,42 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
+          <t>BRSAN.IS, RALYH.IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
+          <t>BRSAN.IS: 2026-08-26 | RALYH.IS: 2026-08-14</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>22.83095636113686</v>
+        <v>35.05565740671337</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +4.21% / +4.70% / -3.86% | ASTOR.IS: +22.00% / +23.58% / 0.00% | BIMAS.IS: +1.70% / +3.87% / -0.86% | BRSAN.IS: +39.28% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>BRSAN.IS: +4.37% / +4.60% / 0.00% | RALYH.IS: -1.89% / +5.24% / -3.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>-5.037231846603429</v>
+        <v>5.880320398884153</v>
       </c>
       <c r="K24" t="n">
-        <v>9.813309577268669</v>
+        <v>11.8335364640245</v>
       </c>
       <c r="L24" t="n">
-        <v>23.4189376077676</v>
+        <v>17.97495932189197</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>180.8</v>
+        <v>140.5</v>
       </c>
       <c r="O24" t="n">
-        <v>45.9</v>
+        <v>46.5</v>
       </c>
       <c r="P24" t="n">
-        <v>5.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2442,22 +2442,22 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>22.513</v>
+        <v>21.61</v>
       </c>
       <c r="T24" t="n">
-        <v>22.513</v>
+        <v>21.61</v>
       </c>
       <c r="U24" t="n">
-        <v>53.589</v>
+        <v>92.68899999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>45.504</v>
+        <v>75.026</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.13</v>
+        <v>-20.719</v>
       </c>
     </row>
     <row r="25">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
+          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2501,14 +2501,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ALARK.IS: +4.21% / +4.70% / -3.86% | ASTOR.IS: +22.00% / +23.58% / 0.00% | BIMAS.IS: +1.70% / +3.87% / -0.86% | BRSAN.IS: +39.28% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +2.90% / +4.70% / -3.86% | ASTOR.IS: +21.22% / +23.58% / 0.00% | BIMAS.IS: +1.76% / +3.87% / -0.86% | BRSAN.IS: +41.29% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K25" t="n">
-        <v>9.813309577268669</v>
+        <v>9.787424677056823</v>
       </c>
       <c r="L25" t="n">
         <v>23.4189376077676</v>
@@ -2540,13 +2540,13 @@
         <v>22.513</v>
       </c>
       <c r="U25" t="n">
-        <v>53.589</v>
+        <v>53.553</v>
       </c>
       <c r="V25" t="n">
-        <v>45.504</v>
+        <v>45.469</v>
       </c>
       <c r="W25" t="n">
-        <v>-1.13</v>
+        <v>-1.167</v>
       </c>
     </row>
   </sheetData>
@@ -3446,14 +3446,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.51% / +3.81% / -0.90% | ASTOR.IS: +3.50% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +0.74% / +3.81% / -0.90% | ASTOR.IS: +2.84% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>23.97433914763116</v>
+        <v>23.11436732229753</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3485,10 +3485,10 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>51.254</v>
+        <v>50.205</v>
       </c>
       <c r="V12" t="n">
-        <v>31.086</v>
+        <v>30.177</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -3533,14 +3533,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.05% / +1.57% / -0.07% | ASTOR.IS: +3.50% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: -0.70% / +1.57% / -0.95% | ASTOR.IS: +2.84% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>23.2232424710131</v>
+        <v>22.37331608251767</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3552,7 +3552,7 @@
         <v>128.2</v>
       </c>
       <c r="O13" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="P13" t="n">
         <v>3.9</v>
@@ -3572,10 +3572,10 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>58.089</v>
+        <v>56.998</v>
       </c>
       <c r="V13" t="n">
-        <v>43.882</v>
+        <v>42.89</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +5.23% / +7.63% / -0.81% | BRSAN.IS: +9.33% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +4.44% / +7.63% / -0.81% | BRSAN.IS: +10.91% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>16.43107972063114</v>
+        <v>16.85935753873742</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3659,13 +3659,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>53.017</v>
+        <v>53.58</v>
       </c>
       <c r="V14" t="n">
-        <v>38.001</v>
+        <v>38.509</v>
       </c>
       <c r="W14" t="n">
-        <v>-11.676</v>
+        <v>-11.113</v>
       </c>
     </row>
     <row r="16">
@@ -4384,14 +4384,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +5.23% / +7.63% / -0.81% | BRSAN.IS: +9.33% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +4.44% / +7.63% / -0.81% | BRSAN.IS: +10.91% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>16.43107972063114</v>
+        <v>16.85935753873742</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4423,13 +4423,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>53.017</v>
+        <v>53.58</v>
       </c>
       <c r="V25" t="n">
-        <v>38.001</v>
+        <v>38.509</v>
       </c>
       <c r="W25" t="n">
-        <v>-11.676</v>
+        <v>-11.113</v>
       </c>
     </row>
     <row r="26">
@@ -4473,14 +4473,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.51% / +3.81% / -0.90% | ASTOR.IS: +3.50% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +0.74% / +3.81% / -0.90% | ASTOR.IS: +2.84% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>23.97433914763116</v>
+        <v>23.11436732229753</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4512,10 +4512,10 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>51.254</v>
+        <v>50.205</v>
       </c>
       <c r="V26" t="n">
-        <v>31.086</v>
+        <v>30.177</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4562,14 +4562,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.05% / +1.57% / -0.07% | ASTOR.IS: +3.50% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: -0.70% / +1.57% / -0.95% | ASTOR.IS: +2.84% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>23.2232424710131</v>
+        <v>22.37331608251767</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4581,7 +4581,7 @@
         <v>128.2</v>
       </c>
       <c r="O27" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="P27" t="n">
         <v>3.9</v>
@@ -4601,10 +4601,10 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>58.089</v>
+        <v>56.998</v>
       </c>
       <c r="V27" t="n">
-        <v>43.882</v>
+        <v>42.89</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -831,14 +831,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.90% / +4.70% / -3.86% | BRSAN.IS: +12.33% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +11.56% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>9.974577446654909</v>
+        <v>9.671495980103106</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -870,13 +870,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>100.013</v>
+        <v>99.462</v>
       </c>
       <c r="V4" t="n">
-        <v>58.185</v>
+        <v>57.749</v>
       </c>
       <c r="W4" t="n">
-        <v>-22.246</v>
+        <v>-22.798</v>
       </c>
     </row>
     <row r="5">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.90% / +4.70% / -3.86% | BRSAN.IS: +12.33% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +11.56% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>9.974577446654909</v>
+        <v>9.671495980103106</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1119,13 +1119,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>100.013</v>
+        <v>99.462</v>
       </c>
       <c r="V7" t="n">
-        <v>58.185</v>
+        <v>57.749</v>
       </c>
       <c r="W7" t="n">
-        <v>-22.246</v>
+        <v>-22.798</v>
       </c>
     </row>
     <row r="8">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +4.37% / +4.60% / 0.00% | RALYH.IS: -1.89% / +5.24% / -3.00%</t>
+          <t>BRSAN.IS: +3.66% / +4.75% / 0.00% | RALYH.IS: -1.99% / +5.24% / -3.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>5.880320398884153</v>
       </c>
       <c r="K12" t="n">
-        <v>11.8335364640245</v>
+        <v>11.39531254094917</v>
       </c>
       <c r="L12" t="n">
         <v>17.97495932189197</v>
@@ -1542,13 +1542,13 @@
         <v>21.61</v>
       </c>
       <c r="U12" t="n">
-        <v>92.68899999999999</v>
+        <v>91.934</v>
       </c>
       <c r="V12" t="n">
-        <v>75.026</v>
+        <v>74.34099999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>-20.719</v>
+        <v>-21.474</v>
       </c>
     </row>
     <row r="13">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.90% / +4.70% / -3.86% | BRSAN.IS: +12.33% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +11.56% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>42.36862230756586</v>
       </c>
       <c r="K13" t="n">
-        <v>9.974578414255507</v>
+        <v>9.671496945037106</v>
       </c>
       <c r="L13" t="n">
         <v>18.35191516155641</v>
@@ -1629,13 +1629,13 @@
         <v>27.525</v>
       </c>
       <c r="U13" t="n">
-        <v>90.711</v>
+        <v>90.18600000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>51.408</v>
+        <v>50.991</v>
       </c>
       <c r="W13" t="n">
-        <v>-21.212</v>
+        <v>-21.737</v>
       </c>
     </row>
     <row r="14">
@@ -1677,14 +1677,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.90% / +4.70% / -3.86% | ASTOR.IS: +21.22% / +23.58% / 0.00% | BIMAS.IS: +1.76% / +3.87% / -0.86% | BRSAN.IS: +41.29% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +20.53% / +23.58% / 0.00% | BIMAS.IS: +1.64% / +3.87% / -0.86% | BRSAN.IS: +40.34% / +45.64% / -0.48% | CANTE.IS: -0.02% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>9.787424677056823</v>
+        <v>9.320943279978454</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1696,7 +1696,7 @@
         <v>180.8</v>
       </c>
       <c r="O14" t="n">
-        <v>45.9</v>
+        <v>45.7</v>
       </c>
       <c r="P14" t="n">
         <v>5.6</v>
@@ -1716,13 +1716,13 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>53.553</v>
+        <v>52.901</v>
       </c>
       <c r="V14" t="n">
-        <v>45.469</v>
+        <v>44.851</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.167</v>
+        <v>-1.819</v>
       </c>
     </row>
     <row r="16">
@@ -1967,14 +1967,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.90% / +4.70% / -3.86% | BRSAN.IS: +12.33% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +11.56% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>9.974577446654909</v>
+        <v>9.671495980103106</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -2006,13 +2006,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>100.013</v>
+        <v>99.462</v>
       </c>
       <c r="V19" t="n">
-        <v>58.185</v>
+        <v>57.749</v>
       </c>
       <c r="W19" t="n">
-        <v>-22.246</v>
+        <v>-22.798</v>
       </c>
     </row>
     <row r="20">
@@ -2056,14 +2056,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.90% / +4.70% / -3.86% | BRSAN.IS: +12.33% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +11.56% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>42.36862230756586</v>
       </c>
       <c r="K20" t="n">
-        <v>9.974578414255507</v>
+        <v>9.671496945037106</v>
       </c>
       <c r="L20" t="n">
         <v>18.35191516155641</v>
@@ -2095,13 +2095,13 @@
         <v>27.525</v>
       </c>
       <c r="U20" t="n">
-        <v>90.711</v>
+        <v>90.18600000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>51.408</v>
+        <v>50.991</v>
       </c>
       <c r="W20" t="n">
-        <v>-21.212</v>
+        <v>-21.737</v>
       </c>
     </row>
     <row r="21">
@@ -2412,14 +2412,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +4.37% / +4.60% / 0.00% | RALYH.IS: -1.89% / +5.24% / -3.00%</t>
+          <t>BRSAN.IS: +3.66% / +4.75% / 0.00% | RALYH.IS: -1.99% / +5.24% / -3.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>5.880320398884153</v>
       </c>
       <c r="K24" t="n">
-        <v>11.8335364640245</v>
+        <v>11.39531254094917</v>
       </c>
       <c r="L24" t="n">
         <v>17.97495932189197</v>
@@ -2451,13 +2451,13 @@
         <v>21.61</v>
       </c>
       <c r="U24" t="n">
-        <v>92.68899999999999</v>
+        <v>91.934</v>
       </c>
       <c r="V24" t="n">
-        <v>75.026</v>
+        <v>74.34099999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>-20.719</v>
+        <v>-21.474</v>
       </c>
     </row>
     <row r="25">
@@ -2501,14 +2501,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.90% / +4.70% / -3.86% | ASTOR.IS: +21.22% / +23.58% / 0.00% | BIMAS.IS: +1.76% / +3.87% / -0.86% | BRSAN.IS: +41.29% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +20.53% / +23.58% / 0.00% | BIMAS.IS: +1.64% / +3.87% / -0.86% | BRSAN.IS: +40.34% / +45.64% / -0.48% | CANTE.IS: -0.02% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K25" t="n">
-        <v>9.787424677056823</v>
+        <v>9.320943279978454</v>
       </c>
       <c r="L25" t="n">
         <v>23.4189376077676</v>
@@ -2520,7 +2520,7 @@
         <v>180.8</v>
       </c>
       <c r="O25" t="n">
-        <v>45.9</v>
+        <v>45.7</v>
       </c>
       <c r="P25" t="n">
         <v>5.6</v>
@@ -2540,13 +2540,13 @@
         <v>22.513</v>
       </c>
       <c r="U25" t="n">
-        <v>53.553</v>
+        <v>52.901</v>
       </c>
       <c r="V25" t="n">
-        <v>45.469</v>
+        <v>44.851</v>
       </c>
       <c r="W25" t="n">
-        <v>-1.167</v>
+        <v>-1.819</v>
       </c>
     </row>
   </sheetData>
@@ -3446,14 +3446,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.74% / +3.81% / -0.90% | ASTOR.IS: +2.84% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +1.02% / +3.81% / -0.90% | ASTOR.IS: +2.25% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>23.11436732229753</v>
+        <v>22.92775695315248</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3485,10 +3485,10 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>50.205</v>
+        <v>49.977</v>
       </c>
       <c r="V12" t="n">
-        <v>30.177</v>
+        <v>29.98</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -3533,14 +3533,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.70% / +1.57% / -0.95% | ASTOR.IS: +2.84% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: -0.43% / +1.57% / -0.95% | ASTOR.IS: +2.25% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>22.37331608251767</v>
+        <v>22.18587975399264</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3572,10 +3572,10 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>56.998</v>
+        <v>56.758</v>
       </c>
       <c r="V13" t="n">
-        <v>42.89</v>
+        <v>42.671</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.44% / +7.63% / -0.81% | BRSAN.IS: +10.91% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +4.73% / +7.63% / -0.81% | BRSAN.IS: +10.15% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>16.85935753873742</v>
+        <v>16.60711222598934</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3659,13 +3659,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>53.58</v>
+        <v>53.249</v>
       </c>
       <c r="V14" t="n">
-        <v>38.509</v>
+        <v>38.21</v>
       </c>
       <c r="W14" t="n">
-        <v>-11.113</v>
+        <v>-11.445</v>
       </c>
     </row>
     <row r="16">
@@ -4384,14 +4384,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.44% / +7.63% / -0.81% | BRSAN.IS: +10.91% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +4.73% / +7.63% / -0.81% | BRSAN.IS: +10.15% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>16.85935753873742</v>
+        <v>16.60711222598934</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4423,13 +4423,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>53.58</v>
+        <v>53.249</v>
       </c>
       <c r="V25" t="n">
-        <v>38.509</v>
+        <v>38.21</v>
       </c>
       <c r="W25" t="n">
-        <v>-11.113</v>
+        <v>-11.445</v>
       </c>
     </row>
     <row r="26">
@@ -4473,14 +4473,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.74% / +3.81% / -0.90% | ASTOR.IS: +2.84% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +1.02% / +3.81% / -0.90% | ASTOR.IS: +2.25% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>23.11436732229753</v>
+        <v>22.92775695315248</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4512,10 +4512,10 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>50.205</v>
+        <v>49.977</v>
       </c>
       <c r="V26" t="n">
-        <v>30.177</v>
+        <v>29.98</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4562,14 +4562,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.70% / +1.57% / -0.95% | ASTOR.IS: +2.84% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: -0.43% / +1.57% / -0.95% | ASTOR.IS: +2.25% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>22.37331608251767</v>
+        <v>22.18587975399264</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4601,10 +4601,10 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>56.998</v>
+        <v>56.758</v>
       </c>
       <c r="V27" t="n">
-        <v>42.89</v>
+        <v>42.671</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -578,13 +578,13 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
     <col width="21" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
@@ -733,25 +733,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ALTNY.IS, DOHOL.IS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-08-28 | ALTNY.IS: 2026-08-28 | DOHOL.IS: 2026-08-28</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>141.8141741847757</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J3" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K3" t="n">
-        <v>-25.7895858596781</v>
+        <v>-25.81926606744547</v>
       </c>
       <c r="L3" t="n">
         <v>14.20226218585835</v>
@@ -760,36 +772,36 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>116.9</v>
+        <v>118.2</v>
       </c>
       <c r="O3" t="n">
-        <v>39.9</v>
+        <v>39.4</v>
       </c>
       <c r="P3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>28.567</v>
+        <v>28.595</v>
       </c>
       <c r="T3" t="n">
-        <v>28.567</v>
+        <v>28.595</v>
       </c>
       <c r="U3" t="n">
-        <v>75.807</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>41.769</v>
+        <v>41.712</v>
       </c>
       <c r="W3" t="n">
-        <v>-70.307</v>
+        <v>-71.48</v>
       </c>
     </row>
     <row r="4">
@@ -808,12 +820,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -831,14 +843,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +11.56% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.55% / +4.70% / -3.86% | BRSAN.IS: +11.87% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>9.671495980103106</v>
+        <v>10.0654824316933</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -847,7 +859,7 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>120.8</v>
+        <v>120.6</v>
       </c>
       <c r="O4" t="n">
         <v>43.5</v>
@@ -870,13 +882,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>99.462</v>
+        <v>96.018</v>
       </c>
       <c r="V4" t="n">
-        <v>57.749</v>
+        <v>58.316</v>
       </c>
       <c r="W4" t="n">
-        <v>-22.798</v>
+        <v>-21.622</v>
       </c>
     </row>
     <row r="5">
@@ -895,12 +907,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -918,14 +930,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +0.44% / +0.55% / -0.18% | DOHOL.IS: +0.88% / +1.07% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K5" t="n">
-        <v>-28.67642172789157</v>
+        <v>-28.19443330708214</v>
       </c>
       <c r="L5" t="n">
         <v>25.50508358988237</v>
@@ -934,10 +946,10 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>94.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P5" t="n">
         <v>3.9</v>
@@ -951,19 +963,19 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>35.713</v>
+        <v>35.7</v>
       </c>
       <c r="T5" t="n">
-        <v>35.713</v>
+        <v>35.7</v>
       </c>
       <c r="U5" t="n">
-        <v>21.504</v>
+        <v>18.157</v>
       </c>
       <c r="V5" t="n">
-        <v>12.278</v>
+        <v>13.037</v>
       </c>
       <c r="W5" t="n">
-        <v>-67.498</v>
+        <v>-64.405</v>
       </c>
     </row>
     <row r="6">
@@ -982,25 +994,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ALTNY.IS, DOHOL.IS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-08-28 | ALTNY.IS: 2026-08-28 | DOHOL.IS: 2026-08-28</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>141.8141741847757</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J6" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K6" t="n">
-        <v>-25.7895858596781</v>
+        <v>-25.81926606744547</v>
       </c>
       <c r="L6" t="n">
         <v>14.20226218585835</v>
@@ -1009,36 +1033,36 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>116.9</v>
+        <v>118.2</v>
       </c>
       <c r="O6" t="n">
-        <v>39.9</v>
+        <v>39.4</v>
       </c>
       <c r="P6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>28.567</v>
+        <v>28.595</v>
       </c>
       <c r="T6" t="n">
-        <v>28.567</v>
+        <v>28.595</v>
       </c>
       <c r="U6" t="n">
-        <v>75.807</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>41.769</v>
+        <v>41.712</v>
       </c>
       <c r="W6" t="n">
-        <v>-70.307</v>
+        <v>-71.48</v>
       </c>
     </row>
     <row r="7">
@@ -1057,12 +1081,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1080,14 +1104,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +11.56% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.55% / +4.70% / -3.86% | BRSAN.IS: +11.87% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>9.671495980103106</v>
+        <v>10.0654824316933</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1096,7 +1120,7 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>120.8</v>
+        <v>120.6</v>
       </c>
       <c r="O7" t="n">
         <v>43.5</v>
@@ -1119,13 +1143,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>99.462</v>
+        <v>96.018</v>
       </c>
       <c r="V7" t="n">
-        <v>57.749</v>
+        <v>58.316</v>
       </c>
       <c r="W7" t="n">
-        <v>-22.798</v>
+        <v>-21.622</v>
       </c>
     </row>
     <row r="8">
@@ -1144,12 +1168,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1167,14 +1191,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TAVHL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +0.25% / +0.96% / -0.20% | TAVHL.IS: +0.86% / +0.88% / -0.09%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2676917652018496</v>
+        <v>0.8476365768067984</v>
       </c>
       <c r="L8" t="n">
         <v>13.72502171397572</v>
@@ -1183,10 +1207,10 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N8" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="O8" t="n">
-        <v>50</v>
+        <v>52.1</v>
       </c>
       <c r="P8" t="n">
         <v>4.6</v>
@@ -1206,13 +1230,13 @@
         <v>29.993</v>
       </c>
       <c r="U8" t="n">
-        <v>3.94</v>
+        <v>-0.839</v>
       </c>
       <c r="V8" t="n">
-        <v>-6.806</v>
+        <v>-6.267</v>
       </c>
       <c r="W8" t="n">
-        <v>-44.104</v>
+        <v>-41.264</v>
       </c>
     </row>
     <row r="9">
@@ -1231,25 +1255,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ALTNY.IS, DOHOL.IS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-08-28 | ALTNY.IS: 2026-08-28 | DOHOL.IS: 2026-08-28</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>141.8141741847757</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J9" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K9" t="n">
-        <v>-25.7895858596781</v>
+        <v>-25.81926606744547</v>
       </c>
       <c r="L9" t="n">
         <v>14.20226218585835</v>
@@ -1258,36 +1294,36 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>116.9</v>
+        <v>118.2</v>
       </c>
       <c r="O9" t="n">
-        <v>39.9</v>
+        <v>39.4</v>
       </c>
       <c r="P9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>28.567</v>
+        <v>28.595</v>
       </c>
       <c r="T9" t="n">
-        <v>28.567</v>
+        <v>28.595</v>
       </c>
       <c r="U9" t="n">
-        <v>75.807</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>41.769</v>
+        <v>41.712</v>
       </c>
       <c r="W9" t="n">
-        <v>-70.307</v>
+        <v>-71.48</v>
       </c>
     </row>
     <row r="10">
@@ -1306,12 +1342,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1329,14 +1365,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TAVHL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +0.25% / +0.96% / -0.20% | TAVHL.IS: +0.86% / +0.88% / -0.09%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2676917652018496</v>
+        <v>0.8476365768067984</v>
       </c>
       <c r="L10" t="n">
         <v>13.72502171397572</v>
@@ -1345,10 +1381,10 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="O10" t="n">
-        <v>50</v>
+        <v>52.1</v>
       </c>
       <c r="P10" t="n">
         <v>4.6</v>
@@ -1368,13 +1404,13 @@
         <v>29.993</v>
       </c>
       <c r="U10" t="n">
-        <v>3.94</v>
+        <v>-0.839</v>
       </c>
       <c r="V10" t="n">
-        <v>-6.806</v>
+        <v>-6.267</v>
       </c>
       <c r="W10" t="n">
-        <v>-44.104</v>
+        <v>-41.264</v>
       </c>
     </row>
     <row r="11">
@@ -1393,12 +1429,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1416,14 +1452,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00% | TAVHL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +0.44% / +0.55% / -0.18% | DOHOL.IS: +0.88% / +1.07% / 0.00% | TAVHL.IS: +0.86% / +0.88% / -0.09%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.774623035017985</v>
+        <v>-0.03541090990838436</v>
       </c>
       <c r="L11" t="n">
         <v>10.56563994340933</v>
@@ -1432,10 +1468,10 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>73.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>37.6</v>
+        <v>39.6</v>
       </c>
       <c r="P11" t="n">
         <v>4.6</v>
@@ -1455,13 +1491,13 @@
         <v>29.287</v>
       </c>
       <c r="U11" t="n">
-        <v>37.054</v>
+        <v>35.183</v>
       </c>
       <c r="V11" t="n">
-        <v>14.328</v>
+        <v>15.18</v>
       </c>
       <c r="W11" t="n">
-        <v>-48.788</v>
+        <v>-46.766</v>
       </c>
     </row>
     <row r="12">
@@ -1480,12 +1516,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1503,14 +1539,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +3.66% / +4.75% / 0.00% | RALYH.IS: -1.99% / +5.24% / -3.00%</t>
+          <t>BRSAN.IS: +3.95% / +4.75% / 0.00% | RALYH.IS: -2.36% / +5.24% / -3.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>5.880320398884153</v>
       </c>
       <c r="K12" t="n">
-        <v>11.39531254094917</v>
+        <v>11.35213420865118</v>
       </c>
       <c r="L12" t="n">
         <v>17.97495932189197</v>
@@ -1519,7 +1555,7 @@
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>140.5</v>
+        <v>140.2</v>
       </c>
       <c r="O12" t="n">
         <v>46.5</v>
@@ -1542,13 +1578,13 @@
         <v>21.61</v>
       </c>
       <c r="U12" t="n">
-        <v>91.934</v>
+        <v>83.11799999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>74.34099999999999</v>
+        <v>74.273</v>
       </c>
       <c r="W12" t="n">
-        <v>-21.474</v>
+        <v>-20.566</v>
       </c>
     </row>
     <row r="13">
@@ -1567,12 +1603,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1590,14 +1626,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +11.56% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.55% / +4.70% / -3.86% | BRSAN.IS: +11.87% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>42.36862230756586</v>
       </c>
       <c r="K13" t="n">
-        <v>9.671496945037106</v>
+        <v>10.06548340009372</v>
       </c>
       <c r="L13" t="n">
         <v>18.35191516155641</v>
@@ -1606,7 +1642,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>121.3</v>
+        <v>121.1</v>
       </c>
       <c r="O13" t="n">
         <v>42.9</v>
@@ -1629,13 +1665,13 @@
         <v>27.525</v>
       </c>
       <c r="U13" t="n">
-        <v>90.18600000000001</v>
+        <v>86.902</v>
       </c>
       <c r="V13" t="n">
-        <v>50.991</v>
+        <v>51.534</v>
       </c>
       <c r="W13" t="n">
-        <v>-21.737</v>
+        <v>-20.617</v>
       </c>
     </row>
     <row r="14">
@@ -1654,12 +1690,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1677,14 +1713,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +20.53% / +23.58% / 0.00% | BIMAS.IS: +1.64% / +3.87% / -0.86% | BRSAN.IS: +40.34% / +45.64% / -0.48% | CANTE.IS: -0.02% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +3.55% / +4.70% / -3.86% | ASTOR.IS: +20.36% / +23.58% / 0.00% | BIMAS.IS: +2.19% / +3.87% / -0.86% | BRSAN.IS: +40.72% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>9.320943279978454</v>
+        <v>9.71735405328209</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1693,10 +1729,10 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>180.8</v>
+        <v>180.4</v>
       </c>
       <c r="O14" t="n">
-        <v>45.7</v>
+        <v>45.9</v>
       </c>
       <c r="P14" t="n">
         <v>5.6</v>
@@ -1716,13 +1752,13 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>52.901</v>
+        <v>50.432</v>
       </c>
       <c r="V14" t="n">
-        <v>44.851</v>
+        <v>45.376</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.819</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="16">
@@ -1867,25 +1903,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ALTNY.IS, DOHOL.IS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-08-28 | ALTNY.IS: 2026-08-28 | DOHOL.IS: 2026-08-28</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>141.8141741847757</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J18" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K18" t="n">
-        <v>-25.7895858596781</v>
+        <v>-25.81926606744547</v>
       </c>
       <c r="L18" t="n">
         <v>14.20226218585835</v>
@@ -1894,36 +1942,36 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>116.9</v>
+        <v>118.2</v>
       </c>
       <c r="O18" t="n">
-        <v>39.9</v>
+        <v>39.4</v>
       </c>
       <c r="P18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>28.567</v>
+        <v>28.595</v>
       </c>
       <c r="T18" t="n">
-        <v>28.567</v>
+        <v>28.595</v>
       </c>
       <c r="U18" t="n">
-        <v>75.807</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>41.769</v>
+        <v>41.712</v>
       </c>
       <c r="W18" t="n">
-        <v>-70.307</v>
+        <v>-71.48</v>
       </c>
     </row>
     <row r="19">
@@ -1944,12 +1992,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1967,14 +2015,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +11.56% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.55% / +4.70% / -3.86% | BRSAN.IS: +11.87% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>9.671495980103106</v>
+        <v>10.0654824316933</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -1983,7 +2031,7 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>120.8</v>
+        <v>120.6</v>
       </c>
       <c r="O19" t="n">
         <v>43.5</v>
@@ -2006,13 +2054,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>99.462</v>
+        <v>96.018</v>
       </c>
       <c r="V19" t="n">
-        <v>57.749</v>
+        <v>58.316</v>
       </c>
       <c r="W19" t="n">
-        <v>-22.798</v>
+        <v>-21.622</v>
       </c>
     </row>
     <row r="20">
@@ -2033,12 +2081,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2056,14 +2104,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +11.56% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.55% / +4.70% / -3.86% | BRSAN.IS: +11.87% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>42.36862230756586</v>
       </c>
       <c r="K20" t="n">
-        <v>9.671496945037106</v>
+        <v>10.06548340009372</v>
       </c>
       <c r="L20" t="n">
         <v>18.35191516155641</v>
@@ -2072,7 +2120,7 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>121.3</v>
+        <v>121.1</v>
       </c>
       <c r="O20" t="n">
         <v>42.9</v>
@@ -2095,13 +2143,13 @@
         <v>27.525</v>
       </c>
       <c r="U20" t="n">
-        <v>90.18600000000001</v>
+        <v>86.902</v>
       </c>
       <c r="V20" t="n">
-        <v>50.991</v>
+        <v>51.534</v>
       </c>
       <c r="W20" t="n">
-        <v>-21.737</v>
+        <v>-20.617</v>
       </c>
     </row>
     <row r="21">
@@ -2122,12 +2170,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2145,14 +2193,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +0.44% / +0.55% / -0.18% | DOHOL.IS: +0.88% / +1.07% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K21" t="n">
-        <v>-28.67642172789157</v>
+        <v>-28.19443330708214</v>
       </c>
       <c r="L21" t="n">
         <v>25.50508358988237</v>
@@ -2161,10 +2209,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>94.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P21" t="n">
         <v>3.9</v>
@@ -2178,19 +2226,19 @@
         <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>35.713</v>
+        <v>35.7</v>
       </c>
       <c r="T21" t="n">
-        <v>35.713</v>
+        <v>35.7</v>
       </c>
       <c r="U21" t="n">
-        <v>21.504</v>
+        <v>18.157</v>
       </c>
       <c r="V21" t="n">
-        <v>12.278</v>
+        <v>13.037</v>
       </c>
       <c r="W21" t="n">
-        <v>-67.498</v>
+        <v>-64.405</v>
       </c>
     </row>
     <row r="22">
@@ -2211,12 +2259,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2234,14 +2282,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | TAVHL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +0.25% / +0.96% / -0.20% | TAVHL.IS: +0.86% / +0.88% / -0.09%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2676917652018496</v>
+        <v>0.8476365768067984</v>
       </c>
       <c r="L22" t="n">
         <v>13.72502171397572</v>
@@ -2250,10 +2298,10 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="O22" t="n">
-        <v>50</v>
+        <v>52.1</v>
       </c>
       <c r="P22" t="n">
         <v>4.6</v>
@@ -2273,13 +2321,13 @@
         <v>29.993</v>
       </c>
       <c r="U22" t="n">
-        <v>3.94</v>
+        <v>-0.839</v>
       </c>
       <c r="V22" t="n">
-        <v>-6.806</v>
+        <v>-6.267</v>
       </c>
       <c r="W22" t="n">
-        <v>-44.104</v>
+        <v>-41.264</v>
       </c>
     </row>
     <row r="23">
@@ -2300,12 +2348,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2323,14 +2371,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00% | TAVHL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +0.44% / +0.55% / -0.18% | DOHOL.IS: +0.88% / +1.07% / 0.00% | TAVHL.IS: +0.86% / +0.88% / -0.09%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.774623035017985</v>
+        <v>-0.03541090990838436</v>
       </c>
       <c r="L23" t="n">
         <v>10.56563994340933</v>
@@ -2339,10 +2387,10 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N23" t="n">
-        <v>73.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>37.6</v>
+        <v>39.6</v>
       </c>
       <c r="P23" t="n">
         <v>4.6</v>
@@ -2362,13 +2410,13 @@
         <v>29.287</v>
       </c>
       <c r="U23" t="n">
-        <v>37.054</v>
+        <v>35.183</v>
       </c>
       <c r="V23" t="n">
-        <v>14.328</v>
+        <v>15.18</v>
       </c>
       <c r="W23" t="n">
-        <v>-48.788</v>
+        <v>-46.766</v>
       </c>
     </row>
     <row r="24">
@@ -2389,12 +2437,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2412,14 +2460,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +3.66% / +4.75% / 0.00% | RALYH.IS: -1.99% / +5.24% / -3.00%</t>
+          <t>BRSAN.IS: +3.95% / +4.75% / 0.00% | RALYH.IS: -2.36% / +5.24% / -3.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>5.880320398884153</v>
       </c>
       <c r="K24" t="n">
-        <v>11.39531254094917</v>
+        <v>11.35213420865118</v>
       </c>
       <c r="L24" t="n">
         <v>17.97495932189197</v>
@@ -2428,7 +2476,7 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>140.5</v>
+        <v>140.2</v>
       </c>
       <c r="O24" t="n">
         <v>46.5</v>
@@ -2451,13 +2499,13 @@
         <v>21.61</v>
       </c>
       <c r="U24" t="n">
-        <v>91.934</v>
+        <v>83.11799999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>74.34099999999999</v>
+        <v>74.273</v>
       </c>
       <c r="W24" t="n">
-        <v>-21.474</v>
+        <v>-20.566</v>
       </c>
     </row>
     <row r="25">
@@ -2478,12 +2526,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2501,14 +2549,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +20.53% / +23.58% / 0.00% | BIMAS.IS: +1.64% / +3.87% / -0.86% | BRSAN.IS: +40.34% / +45.64% / -0.48% | CANTE.IS: -0.02% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +3.55% / +4.70% / -3.86% | ASTOR.IS: +20.36% / +23.58% / 0.00% | BIMAS.IS: +2.19% / +3.87% / -0.86% | BRSAN.IS: +40.72% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K25" t="n">
-        <v>9.320943279978454</v>
+        <v>9.71735405328209</v>
       </c>
       <c r="L25" t="n">
         <v>23.4189376077676</v>
@@ -2517,10 +2565,10 @@
         <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>180.8</v>
+        <v>180.4</v>
       </c>
       <c r="O25" t="n">
-        <v>45.7</v>
+        <v>45.9</v>
       </c>
       <c r="P25" t="n">
         <v>5.6</v>
@@ -2540,13 +2588,13 @@
         <v>22.513</v>
       </c>
       <c r="U25" t="n">
-        <v>52.901</v>
+        <v>50.432</v>
       </c>
       <c r="V25" t="n">
-        <v>44.851</v>
+        <v>45.376</v>
       </c>
       <c r="W25" t="n">
-        <v>-1.819</v>
+        <v>-1.24</v>
       </c>
     </row>
   </sheetData>
@@ -2736,12 +2784,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2763,7 +2811,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>65.59999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="O3" t="n">
         <v>45.9</v>
@@ -2786,13 +2834,13 @@
         <v>31.839</v>
       </c>
       <c r="U3" t="n">
-        <v>15.209</v>
+        <v>10.689</v>
       </c>
       <c r="V3" t="n">
         <v>27.773</v>
       </c>
       <c r="W3" t="n">
-        <v>-53.815</v>
+        <v>-51.704</v>
       </c>
     </row>
     <row r="4">
@@ -2811,12 +2859,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2838,7 +2886,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N4" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="O4" t="n">
         <v>46.7</v>
@@ -2861,13 +2909,13 @@
         <v>30.704</v>
       </c>
       <c r="U4" t="n">
-        <v>2.192</v>
+        <v>-1.756</v>
       </c>
       <c r="V4" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>-45.28</v>
+        <v>-43.531</v>
       </c>
     </row>
     <row r="5">
@@ -2886,12 +2934,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -2913,7 +2961,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="O5" t="n">
         <v>46.7</v>
@@ -2936,13 +2984,13 @@
         <v>30.704</v>
       </c>
       <c r="U5" t="n">
-        <v>2.192</v>
+        <v>-1.756</v>
       </c>
       <c r="V5" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-45.28</v>
+        <v>-43.531</v>
       </c>
     </row>
     <row r="6">
@@ -2961,12 +3009,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -2988,7 +3036,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="O6" t="n">
         <v>46.7</v>
@@ -3011,13 +3059,13 @@
         <v>30.704</v>
       </c>
       <c r="U6" t="n">
-        <v>2.192</v>
+        <v>-1.756</v>
       </c>
       <c r="V6" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>-45.28</v>
+        <v>-43.531</v>
       </c>
     </row>
     <row r="7">
@@ -3036,12 +3084,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3063,7 +3111,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N7" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="O7" t="n">
         <v>46.7</v>
@@ -3086,13 +3134,13 @@
         <v>30.704</v>
       </c>
       <c r="U7" t="n">
-        <v>2.192</v>
+        <v>-1.756</v>
       </c>
       <c r="V7" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>-45.28</v>
+        <v>-43.531</v>
       </c>
     </row>
     <row r="8">
@@ -3111,12 +3159,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3134,14 +3182,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: -0.16% / +1.22% / -0.57% | BRSAN.IS: +0.25% / +0.96% / -0.20% | TRALT.IS: +1.64% / +1.84% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K8" t="n">
-        <v>-21.725984589795</v>
+        <v>-21.25970279201362</v>
       </c>
       <c r="L8" t="n">
         <v>16.84258916554939</v>
@@ -3150,10 +3198,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>111.9</v>
+        <v>111.7</v>
       </c>
       <c r="O8" t="n">
-        <v>37.9</v>
+        <v>38.8</v>
       </c>
       <c r="P8" t="n">
         <v>4.9</v>
@@ -3167,19 +3215,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>28.916</v>
+        <v>28.902</v>
       </c>
       <c r="T8" t="n">
-        <v>28.916</v>
+        <v>28.902</v>
       </c>
       <c r="U8" t="n">
-        <v>44.043</v>
+        <v>45.183</v>
       </c>
       <c r="V8" t="n">
-        <v>14.312</v>
+        <v>14.993</v>
       </c>
       <c r="W8" t="n">
-        <v>-58.596</v>
+        <v>-57.85</v>
       </c>
     </row>
     <row r="9">
@@ -3198,12 +3246,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3225,7 +3273,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="N9" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="O9" t="n">
         <v>57.4</v>
@@ -3273,12 +3321,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3300,7 +3348,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>68.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>45.7</v>
@@ -3323,13 +3371,13 @@
         <v>13.513</v>
       </c>
       <c r="U10" t="n">
-        <v>14.45</v>
+        <v>12.064</v>
       </c>
       <c r="V10" t="n">
         <v>13.389</v>
       </c>
       <c r="W10" t="n">
-        <v>-17.156</v>
+        <v>-16.799</v>
       </c>
     </row>
     <row r="11">
@@ -3348,12 +3396,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3375,7 +3423,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="O11" t="n">
         <v>44.2</v>
@@ -3398,13 +3446,13 @@
         <v>13.42</v>
       </c>
       <c r="U11" t="n">
-        <v>18.52</v>
+        <v>16.049</v>
       </c>
       <c r="V11" t="n">
         <v>12.908</v>
       </c>
       <c r="W11" t="n">
-        <v>-18.371</v>
+        <v>-17.988</v>
       </c>
     </row>
     <row r="12">
@@ -3423,12 +3471,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3446,14 +3494,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.02% / +3.81% / -0.90% | ASTOR.IS: +2.25% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +1.23% / +3.81% / -0.90% | ASTOR.IS: +2.10% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>22.92775695315248</v>
+        <v>22.96498265860674</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3462,7 +3510,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N12" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="O12" t="n">
         <v>49.4</v>
@@ -3485,10 +3533,10 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>49.977</v>
+        <v>43.375</v>
       </c>
       <c r="V12" t="n">
-        <v>29.98</v>
+        <v>30.019</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -3510,12 +3558,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3533,14 +3581,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.43% / +1.57% / -0.95% | ASTOR.IS: +2.25% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: -0.23% / +1.57% / -0.95% | ASTOR.IS: +2.10% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>22.18587975399264</v>
+        <v>22.22148283971572</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3549,7 +3597,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N13" t="n">
-        <v>128.2</v>
+        <v>128</v>
       </c>
       <c r="O13" t="n">
         <v>50</v>
@@ -3572,10 +3620,10 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>56.758</v>
+        <v>56.271</v>
       </c>
       <c r="V13" t="n">
-        <v>42.671</v>
+        <v>42.712</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -3597,12 +3645,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3620,14 +3668,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.73% / +7.63% / -0.81% | BRSAN.IS: +10.15% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +4.95% / +7.63% / -0.81% | BRSAN.IS: +10.45% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>16.60711222598934</v>
+        <v>16.88747410218565</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3636,7 +3684,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N14" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="O14" t="n">
         <v>57.1</v>
@@ -3659,13 +3707,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>53.249</v>
+        <v>53.333</v>
       </c>
       <c r="V14" t="n">
-        <v>38.21</v>
+        <v>38.542</v>
       </c>
       <c r="W14" t="n">
-        <v>-11.445</v>
+        <v>-11.056</v>
       </c>
     </row>
     <row r="16">
@@ -3810,12 +3858,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -3837,7 +3885,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>65.59999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="O18" t="n">
         <v>45.9</v>
@@ -3860,13 +3908,13 @@
         <v>31.839</v>
       </c>
       <c r="U18" t="n">
-        <v>15.209</v>
+        <v>10.689</v>
       </c>
       <c r="V18" t="n">
         <v>27.773</v>
       </c>
       <c r="W18" t="n">
-        <v>-53.815</v>
+        <v>-51.704</v>
       </c>
     </row>
     <row r="19">
@@ -3887,12 +3935,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -3914,7 +3962,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="O19" t="n">
         <v>46.7</v>
@@ -3937,13 +3985,13 @@
         <v>30.704</v>
       </c>
       <c r="U19" t="n">
-        <v>2.192</v>
+        <v>-1.756</v>
       </c>
       <c r="V19" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>-45.28</v>
+        <v>-43.531</v>
       </c>
     </row>
     <row r="20">
@@ -3964,12 +4012,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -3991,7 +4039,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="O20" t="n">
         <v>46.7</v>
@@ -4014,13 +4062,13 @@
         <v>30.704</v>
       </c>
       <c r="U20" t="n">
-        <v>2.192</v>
+        <v>-1.756</v>
       </c>
       <c r="V20" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-45.28</v>
+        <v>-43.531</v>
       </c>
     </row>
     <row r="21">
@@ -4041,12 +4089,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4064,14 +4112,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: -0.16% / +1.22% / -0.57% | BRSAN.IS: +0.25% / +0.96% / -0.20% | TRALT.IS: +1.64% / +1.84% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K21" t="n">
-        <v>-21.725984589795</v>
+        <v>-21.25970279201362</v>
       </c>
       <c r="L21" t="n">
         <v>16.84258916554939</v>
@@ -4080,10 +4128,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>111.9</v>
+        <v>111.7</v>
       </c>
       <c r="O21" t="n">
-        <v>37.9</v>
+        <v>38.8</v>
       </c>
       <c r="P21" t="n">
         <v>4.9</v>
@@ -4097,19 +4145,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>28.916</v>
+        <v>28.902</v>
       </c>
       <c r="T21" t="n">
-        <v>28.916</v>
+        <v>28.902</v>
       </c>
       <c r="U21" t="n">
-        <v>44.043</v>
+        <v>45.183</v>
       </c>
       <c r="V21" t="n">
-        <v>14.312</v>
+        <v>14.993</v>
       </c>
       <c r="W21" t="n">
-        <v>-58.596</v>
+        <v>-57.85</v>
       </c>
     </row>
     <row r="22">
@@ -4130,12 +4178,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4157,7 +4205,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="O22" t="n">
         <v>44.2</v>
@@ -4180,13 +4228,13 @@
         <v>13.42</v>
       </c>
       <c r="U22" t="n">
-        <v>18.52</v>
+        <v>16.049</v>
       </c>
       <c r="V22" t="n">
         <v>12.908</v>
       </c>
       <c r="W22" t="n">
-        <v>-18.371</v>
+        <v>-17.988</v>
       </c>
     </row>
     <row r="23">
@@ -4207,12 +4255,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -4234,7 +4282,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N23" t="n">
-        <v>68.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="O23" t="n">
         <v>45.7</v>
@@ -4257,13 +4305,13 @@
         <v>13.513</v>
       </c>
       <c r="U23" t="n">
-        <v>14.45</v>
+        <v>12.064</v>
       </c>
       <c r="V23" t="n">
         <v>13.389</v>
       </c>
       <c r="W23" t="n">
-        <v>-17.156</v>
+        <v>-16.799</v>
       </c>
     </row>
     <row r="24">
@@ -4284,12 +4332,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4311,7 +4359,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="N24" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="O24" t="n">
         <v>57.4</v>
@@ -4361,12 +4409,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4384,14 +4432,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.73% / +7.63% / -0.81% | BRSAN.IS: +10.15% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +4.95% / +7.63% / -0.81% | BRSAN.IS: +10.45% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>16.60711222598934</v>
+        <v>16.88747410218565</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4400,7 +4448,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N25" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="O25" t="n">
         <v>57.1</v>
@@ -4423,13 +4471,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>53.249</v>
+        <v>53.333</v>
       </c>
       <c r="V25" t="n">
-        <v>38.21</v>
+        <v>38.542</v>
       </c>
       <c r="W25" t="n">
-        <v>-11.445</v>
+        <v>-11.056</v>
       </c>
     </row>
     <row r="26">
@@ -4450,12 +4498,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4473,14 +4521,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.02% / +3.81% / -0.90% | ASTOR.IS: +2.25% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +1.23% / +3.81% / -0.90% | ASTOR.IS: +2.10% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>22.92775695315248</v>
+        <v>22.96498265860674</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4489,7 +4537,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N26" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="O26" t="n">
         <v>49.4</v>
@@ -4512,10 +4560,10 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>49.977</v>
+        <v>43.375</v>
       </c>
       <c r="V26" t="n">
-        <v>29.98</v>
+        <v>30.019</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4539,12 +4587,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4562,14 +4610,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.43% / +1.57% / -0.95% | ASTOR.IS: +2.25% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: -0.23% / +1.57% / -0.95% | ASTOR.IS: +2.10% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>22.18587975399264</v>
+        <v>22.22148283971572</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4578,7 +4626,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N27" t="n">
-        <v>128.2</v>
+        <v>128</v>
       </c>
       <c r="O27" t="n">
         <v>50</v>
@@ -4601,10 +4649,10 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>56.758</v>
+        <v>56.271</v>
       </c>
       <c r="V27" t="n">
-        <v>42.671</v>
+        <v>42.712</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -578,7 +578,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -843,14 +843,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.55% / +4.70% / -3.86% | BRSAN.IS: +11.87% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +12.02% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>10.0654824316933</v>
+        <v>9.909775949847788</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -882,13 +882,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>96.018</v>
+        <v>95.741</v>
       </c>
       <c r="V4" t="n">
-        <v>58.316</v>
+        <v>58.092</v>
       </c>
       <c r="W4" t="n">
-        <v>-21.622</v>
+        <v>-21.899</v>
       </c>
     </row>
     <row r="5">
@@ -930,14 +930,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.44% / +0.55% / -0.18% | DOHOL.IS: +0.88% / +1.07% / 0.00%</t>
+          <t>ALARK.IS: -0.02% / +1.46% / -0.36% | DOHOL.IS: +0.61% / +1.16% / -1.07%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K5" t="n">
-        <v>-28.19443330708214</v>
+        <v>-28.45293790104135</v>
       </c>
       <c r="L5" t="n">
         <v>25.50508358988237</v>
@@ -949,7 +949,7 @@
         <v>94.09999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="P5" t="n">
         <v>3.9</v>
@@ -969,13 +969,13 @@
         <v>35.7</v>
       </c>
       <c r="U5" t="n">
-        <v>18.157</v>
+        <v>17.732</v>
       </c>
       <c r="V5" t="n">
-        <v>13.037</v>
+        <v>12.63</v>
       </c>
       <c r="W5" t="n">
-        <v>-64.405</v>
+        <v>-64.831</v>
       </c>
     </row>
     <row r="6">
@@ -1104,14 +1104,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.55% / +4.70% / -3.86% | BRSAN.IS: +11.87% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +12.02% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>10.0654824316933</v>
+        <v>9.909775949847788</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1143,13 +1143,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>96.018</v>
+        <v>95.741</v>
       </c>
       <c r="V7" t="n">
-        <v>58.316</v>
+        <v>58.092</v>
       </c>
       <c r="W7" t="n">
-        <v>-21.622</v>
+        <v>-21.899</v>
       </c>
     </row>
     <row r="8">
@@ -1191,14 +1191,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +0.25% / +0.96% / -0.20% | TAVHL.IS: +0.86% / +0.88% / -0.09%</t>
+          <t>BRSAN.IS: +0.39% / +2.39% / -0.89% | TAVHL.IS: +0.60% / +1.41% / -0.09%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8476365768067984</v>
+        <v>0.7832353101179024</v>
       </c>
       <c r="L8" t="n">
         <v>13.72502171397572</v>
@@ -1230,13 +1230,13 @@
         <v>29.993</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.839</v>
+        <v>-0.902</v>
       </c>
       <c r="V8" t="n">
-        <v>-6.267</v>
+        <v>-6.327</v>
       </c>
       <c r="W8" t="n">
-        <v>-41.264</v>
+        <v>-41.328</v>
       </c>
     </row>
     <row r="9">
@@ -1365,14 +1365,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +0.25% / +0.96% / -0.20% | TAVHL.IS: +0.86% / +0.88% / -0.09%</t>
+          <t>BRSAN.IS: +0.39% / +2.39% / -0.89% | TAVHL.IS: +0.60% / +1.41% / -0.09%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8476365768067984</v>
+        <v>0.7832353101179024</v>
       </c>
       <c r="L10" t="n">
         <v>13.72502171397572</v>
@@ -1404,13 +1404,13 @@
         <v>29.993</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.839</v>
+        <v>-0.902</v>
       </c>
       <c r="V10" t="n">
-        <v>-6.267</v>
+        <v>-6.327</v>
       </c>
       <c r="W10" t="n">
-        <v>-41.264</v>
+        <v>-41.328</v>
       </c>
     </row>
     <row r="11">
@@ -1452,14 +1452,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.44% / +0.55% / -0.18% | DOHOL.IS: +0.88% / +1.07% / 0.00% | TAVHL.IS: +0.86% / +0.88% / -0.09%</t>
+          <t>ALARK.IS: -0.02% / +1.46% / -0.36% | DOHOL.IS: +0.61% / +1.16% / -1.07% | TAVHL.IS: +0.60% / +1.41% / -0.09%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.03541090990838436</v>
+        <v>-0.3628204980789307</v>
       </c>
       <c r="L11" t="n">
         <v>10.56563994340933</v>
@@ -1471,7 +1471,7 @@
         <v>73.09999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>39.6</v>
+        <v>38.9</v>
       </c>
       <c r="P11" t="n">
         <v>4.6</v>
@@ -1491,13 +1491,13 @@
         <v>29.287</v>
       </c>
       <c r="U11" t="n">
-        <v>35.183</v>
+        <v>34.74</v>
       </c>
       <c r="V11" t="n">
-        <v>15.18</v>
+        <v>14.802</v>
       </c>
       <c r="W11" t="n">
-        <v>-46.766</v>
+        <v>-47.209</v>
       </c>
     </row>
     <row r="12">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1526,42 +1526,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BRSAN.IS, RALYH.IS</t>
+          <t>AKBNK.IS, BRSAN.IS, CANTE.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-26 | RALYH.IS: 2026-08-14</t>
+          <t>AKBNK.IS: 2026-08-26 | BRSAN.IS: 2026-08-26 | CANTE.IS: 2026-08-21</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>35.05565740671337</v>
+        <v>3.443912532931592</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +3.95% / +4.75% / 0.00% | RALYH.IS: -2.36% / +5.24% / -3.00%</t>
+          <t>AKBNK.IS: -0.36% / +1.57% / -0.96% | BRSAN.IS: +4.09% / +6.16% / 0.00% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>5.880320398884153</v>
+        <v>-1.862436885442242</v>
       </c>
       <c r="K12" t="n">
-        <v>11.35213420865118</v>
+        <v>14.03235101239271</v>
       </c>
       <c r="L12" t="n">
-        <v>17.97495932189197</v>
+        <v>7.902828022135555</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="N12" t="n">
-        <v>140.2</v>
+        <v>34.3</v>
       </c>
       <c r="O12" t="n">
-        <v>46.5</v>
+        <v>47.1</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1569,22 +1569,22 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>21.61</v>
+        <v>8.954000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>21.61</v>
+        <v>8.954000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>83.11799999999999</v>
+        <v>14.292</v>
       </c>
       <c r="V12" t="n">
-        <v>74.273</v>
+        <v>13.287</v>
       </c>
       <c r="W12" t="n">
-        <v>-20.566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1613,42 +1613,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ALARK.IS, BRSAN.IS</t>
+          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-21 | BRSAN.IS: 2026-08-17</t>
+          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>122.3614568902708</v>
+        <v>22.83095636113686</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.55% / +4.70% / -3.86% | BRSAN.IS: +11.87% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +19.84% / +23.58% / 0.00% | BIMAS.IS: +1.95% / +3.87% / -0.86% | BRSAN.IS: +40.91% / +45.64% / -0.48% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>42.36862230756586</v>
+        <v>-5.037231846603429</v>
       </c>
       <c r="K13" t="n">
-        <v>10.06548340009372</v>
+        <v>11.31703599030387</v>
       </c>
       <c r="L13" t="n">
-        <v>18.35191516155641</v>
+        <v>23.4189376077676</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>121.1</v>
+        <v>180.4</v>
       </c>
       <c r="O13" t="n">
-        <v>42.9</v>
+        <v>45.9</v>
       </c>
       <c r="P13" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1656,22 +1656,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S13" t="n">
-        <v>27.525</v>
+        <v>22.513</v>
       </c>
       <c r="T13" t="n">
-        <v>27.525</v>
+        <v>22.513</v>
       </c>
       <c r="U13" t="n">
-        <v>86.902</v>
+        <v>52.625</v>
       </c>
       <c r="V13" t="n">
-        <v>51.534</v>
+        <v>47.496</v>
       </c>
       <c r="W13" t="n">
-        <v>-20.617</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1713,14 +1713,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.55% / +4.70% / -3.86% | ASTOR.IS: +20.36% / +23.58% / 0.00% | BIMAS.IS: +2.19% / +3.87% / -0.86% | BRSAN.IS: +40.72% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +19.84% / +23.58% / 0.00% | BIMAS.IS: +1.95% / +3.87% / -0.86% | BRSAN.IS: +40.91% / +45.64% / -0.48% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>9.71735405328209</v>
+        <v>11.31703599030387</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1752,13 +1752,13 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>50.432</v>
+        <v>52.625</v>
       </c>
       <c r="V14" t="n">
-        <v>45.376</v>
+        <v>47.496</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2015,14 +2015,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.55% / +4.70% / -3.86% | BRSAN.IS: +11.87% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +12.02% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>10.0654824316933</v>
+        <v>9.909775949847788</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -2054,29 +2054,29 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>96.018</v>
+        <v>95.741</v>
       </c>
       <c r="V19" t="n">
-        <v>58.316</v>
+        <v>58.092</v>
       </c>
       <c r="W19" t="n">
-        <v>-21.622</v>
+        <v>-21.899</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>KAR_TOP3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2091,42 +2091,42 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ALARK.IS, BRSAN.IS</t>
+          <t>ALARK.IS, DOHOL.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-21 | BRSAN.IS: 2026-08-17</t>
+          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>122.3614568902708</v>
+        <v>115.6477996753693</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.55% / +4.70% / -3.86% | BRSAN.IS: +11.87% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: -0.02% / +1.46% / -0.36% | DOHOL.IS: +0.61% / +1.16% / -1.07%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>42.36862230756586</v>
+        <v>20.71036906913848</v>
       </c>
       <c r="K20" t="n">
-        <v>10.06548340009372</v>
+        <v>-28.45293790104135</v>
       </c>
       <c r="L20" t="n">
-        <v>18.35191516155641</v>
+        <v>25.50508358988237</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>121.1</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>42.9</v>
+        <v>37.5</v>
       </c>
       <c r="P20" t="n">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2137,35 +2137,35 @@
         <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>27.525</v>
+        <v>35.7</v>
       </c>
       <c r="T20" t="n">
-        <v>27.525</v>
+        <v>35.7</v>
       </c>
       <c r="U20" t="n">
-        <v>86.902</v>
+        <v>17.732</v>
       </c>
       <c r="V20" t="n">
-        <v>51.534</v>
+        <v>12.63</v>
       </c>
       <c r="W20" t="n">
-        <v>-20.617</v>
+        <v>-64.831</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KAR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 | 2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2180,42 +2180,42 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ALARK.IS, DOHOL.IS</t>
+          <t>BRSAN.IS, TAVHL.IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27</t>
+          <t>BRSAN.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>115.6477996753693</v>
+        <v>96.86982435918456</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.44% / +0.55% / -0.18% | DOHOL.IS: +0.88% / +1.07% / 0.00%</t>
+          <t>BRSAN.IS: +0.39% / +2.39% / -0.89% | TAVHL.IS: +0.60% / +1.41% / -0.09%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>20.71036906913848</v>
+        <v>42.40716574291981</v>
       </c>
       <c r="K21" t="n">
-        <v>-28.19443330708214</v>
+        <v>0.7832353101179024</v>
       </c>
       <c r="L21" t="n">
-        <v>25.50508358988237</v>
+        <v>13.72502171397572</v>
       </c>
       <c r="M21" t="n">
-        <v>100</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N21" t="n">
-        <v>94.09999999999999</v>
+        <v>47.1</v>
       </c>
       <c r="O21" t="n">
-        <v>38</v>
+        <v>52.1</v>
       </c>
       <c r="P21" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -2226,35 +2226,35 @@
         <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>35.7</v>
+        <v>29.993</v>
       </c>
       <c r="T21" t="n">
-        <v>35.7</v>
+        <v>29.993</v>
       </c>
       <c r="U21" t="n">
-        <v>18.157</v>
+        <v>-0.902</v>
       </c>
       <c r="V21" t="n">
-        <v>13.037</v>
+        <v>-6.327</v>
       </c>
       <c r="W21" t="n">
-        <v>-64.405</v>
+        <v>-41.328</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3 | 2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T1_genislik_skor|E50|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2269,39 +2269,39 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TAVHL.IS</t>
+          <t>ALARK.IS, DOHOL.IS, TAVHL.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
+          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>96.86982435918456</v>
+        <v>87.24519408485627</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +0.25% / +0.96% / -0.20% | TAVHL.IS: +0.86% / +0.88% / -0.09%</t>
+          <t>ALARK.IS: -0.02% / +1.46% / -0.36% | DOHOL.IS: +0.61% / +1.16% / -1.07% | TAVHL.IS: +0.60% / +1.41% / -0.09%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>42.40716574291981</v>
+        <v>29.19814518717994</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8476365768067984</v>
+        <v>-0.3628204980789307</v>
       </c>
       <c r="L22" t="n">
-        <v>13.72502171397572</v>
+        <v>10.56563994340933</v>
       </c>
       <c r="M22" t="n">
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>47.1</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>52.1</v>
+        <v>38.9</v>
       </c>
       <c r="P22" t="n">
         <v>4.6</v>
@@ -2312,38 +2312,38 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S22" t="n">
-        <v>29.993</v>
+        <v>29.287</v>
       </c>
       <c r="T22" t="n">
-        <v>29.993</v>
+        <v>29.287</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.839</v>
+        <v>34.74</v>
       </c>
       <c r="V22" t="n">
-        <v>-6.267</v>
+        <v>14.802</v>
       </c>
       <c r="W22" t="n">
-        <v>-41.264</v>
+        <v>-47.209</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S3|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2358,42 +2358,42 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ALARK.IS, DOHOL.IS, TAVHL.IS</t>
+          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
+          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>87.24519408485627</v>
+        <v>22.83095636113686</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.44% / +0.55% / -0.18% | DOHOL.IS: +0.88% / +1.07% / 0.00% | TAVHL.IS: +0.86% / +0.88% / -0.09%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +19.84% / +23.58% / 0.00% | BIMAS.IS: +1.95% / +3.87% / -0.86% | BRSAN.IS: +40.91% / +45.64% / -0.48% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>29.19814518717994</v>
+        <v>-5.037231846603429</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.03541090990838436</v>
+        <v>11.31703599030387</v>
       </c>
       <c r="L23" t="n">
-        <v>10.56563994340933</v>
+        <v>23.4189376077676</v>
       </c>
       <c r="M23" t="n">
-        <v>94.44444444444444</v>
+        <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>73.09999999999999</v>
+        <v>180.4</v>
       </c>
       <c r="O23" t="n">
-        <v>39.6</v>
+        <v>45.9</v>
       </c>
       <c r="P23" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2401,22 +2401,22 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S23" t="n">
-        <v>29.287</v>
+        <v>22.513</v>
       </c>
       <c r="T23" t="n">
-        <v>29.287</v>
+        <v>22.513</v>
       </c>
       <c r="U23" t="n">
-        <v>35.183</v>
+        <v>52.625</v>
       </c>
       <c r="V23" t="n">
-        <v>15.18</v>
+        <v>47.496</v>
       </c>
       <c r="W23" t="n">
-        <v>-46.766</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|vidya_trend</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2447,42 +2447,42 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BRSAN.IS, RALYH.IS</t>
+          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-26 | RALYH.IS: 2026-08-14</t>
+          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>35.05565740671337</v>
+        <v>22.83095636113686</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +3.95% / +4.75% / 0.00% | RALYH.IS: -2.36% / +5.24% / -3.00%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +19.84% / +23.58% / 0.00% | BIMAS.IS: +1.95% / +3.87% / -0.86% | BRSAN.IS: +40.91% / +45.64% / -0.48% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>5.880320398884153</v>
+        <v>-5.037231846603429</v>
       </c>
       <c r="K24" t="n">
-        <v>11.35213420865118</v>
+        <v>11.31703599030387</v>
       </c>
       <c r="L24" t="n">
-        <v>17.97495932189197</v>
+        <v>23.4189376077676</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>140.2</v>
+        <v>180.4</v>
       </c>
       <c r="O24" t="n">
-        <v>46.5</v>
+        <v>45.9</v>
       </c>
       <c r="P24" t="n">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2490,22 +2490,22 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S24" t="n">
-        <v>21.61</v>
+        <v>22.513</v>
       </c>
       <c r="T24" t="n">
-        <v>21.61</v>
+        <v>22.513</v>
       </c>
       <c r="U24" t="n">
-        <v>83.11799999999999</v>
+        <v>52.625</v>
       </c>
       <c r="V24" t="n">
-        <v>74.273</v>
+        <v>47.496</v>
       </c>
       <c r="W24" t="n">
-        <v>-20.566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S5|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E50|S3|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2536,42 +2536,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
+          <t>AKBNK.IS, BRSAN.IS, CANTE.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
+          <t>AKBNK.IS: 2026-08-26 | BRSAN.IS: 2026-08-26 | CANTE.IS: 2026-08-21</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>22.83095636113686</v>
+        <v>3.443912532931592</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.55% / +4.70% / -3.86% | ASTOR.IS: +20.36% / +23.58% / 0.00% | BIMAS.IS: +2.19% / +3.87% / -0.86% | BRSAN.IS: +40.72% / +45.64% / -0.48% | CANTE.IS: +0.81% / +2.48% / -0.83%</t>
+          <t>AKBNK.IS: -0.36% / +1.57% / -0.96% | BRSAN.IS: +4.09% / +6.16% / 0.00% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>-5.037231846603429</v>
+        <v>-1.862436885442242</v>
       </c>
       <c r="K25" t="n">
-        <v>9.71735405328209</v>
+        <v>14.03235101239271</v>
       </c>
       <c r="L25" t="n">
-        <v>23.4189376077676</v>
+        <v>7.902828022135555</v>
       </c>
       <c r="M25" t="n">
-        <v>100</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="N25" t="n">
-        <v>180.4</v>
+        <v>34.3</v>
       </c>
       <c r="O25" t="n">
-        <v>45.9</v>
+        <v>47.1</v>
       </c>
       <c r="P25" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2579,22 +2579,22 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S25" t="n">
-        <v>22.513</v>
+        <v>8.954000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>22.513</v>
+        <v>8.954000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>50.432</v>
+        <v>14.292</v>
       </c>
       <c r="V25" t="n">
-        <v>45.376</v>
+        <v>13.287</v>
       </c>
       <c r="W25" t="n">
-        <v>-1.24</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3182,14 +3182,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.16% / +1.22% / -0.57% | BRSAN.IS: +0.25% / +0.96% / -0.20% | TRALT.IS: +1.64% / +1.84% / 0.00%</t>
+          <t>ASTOR.IS: -0.59% / +1.22% / -1.29% | BRSAN.IS: +0.39% / +2.39% / -0.89% | TRALT.IS: +2.01% / +2.58% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K8" t="n">
-        <v>-21.25970279201362</v>
+        <v>-21.24013277139327</v>
       </c>
       <c r="L8" t="n">
         <v>16.84258916554939</v>
@@ -3221,13 +3221,13 @@
         <v>28.902</v>
       </c>
       <c r="U8" t="n">
-        <v>45.183</v>
+        <v>45.219</v>
       </c>
       <c r="V8" t="n">
-        <v>14.993</v>
+        <v>15.021</v>
       </c>
       <c r="W8" t="n">
-        <v>-57.85</v>
+        <v>-57.814</v>
       </c>
     </row>
     <row r="9">
@@ -3494,14 +3494,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.23% / +3.81% / -0.90% | ASTOR.IS: +2.10% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +1.09% / +3.81% / -0.90% | ASTOR.IS: +1.66% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>22.96498265860674</v>
+        <v>22.61533715807487</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3533,13 +3533,13 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>43.375</v>
+        <v>42.967</v>
       </c>
       <c r="V12" t="n">
-        <v>30.019</v>
+        <v>29.649</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.393</v>
       </c>
     </row>
     <row r="13">
@@ -3581,14 +3581,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.23% / +1.57% / -0.95% | ASTOR.IS: +2.10% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: -0.36% / +1.57% / -0.95% | ASTOR.IS: +1.66% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>22.22148283971572</v>
+        <v>21.87475805894989</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3620,13 +3620,13 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>56.271</v>
+        <v>55.828</v>
       </c>
       <c r="V13" t="n">
-        <v>42.712</v>
+        <v>42.308</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.429</v>
       </c>
     </row>
     <row r="14">
@@ -3668,14 +3668,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.95% / +7.63% / -0.81% | BRSAN.IS: +10.45% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +4.80% / +7.63% / -0.81% | BRSAN.IS: +10.60% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>16.88747410218565</v>
+        <v>16.8911073125942</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3707,13 +3707,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>53.333</v>
+        <v>53.338</v>
       </c>
       <c r="V14" t="n">
-        <v>38.542</v>
+        <v>38.546</v>
       </c>
       <c r="W14" t="n">
-        <v>-11.056</v>
+        <v>-11.051</v>
       </c>
     </row>
     <row r="16">
@@ -4112,14 +4112,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.16% / +1.22% / -0.57% | BRSAN.IS: +0.25% / +0.96% / -0.20% | TRALT.IS: +1.64% / +1.84% / 0.00%</t>
+          <t>ASTOR.IS: -0.59% / +1.22% / -1.29% | BRSAN.IS: +0.39% / +2.39% / -0.89% | TRALT.IS: +2.01% / +2.58% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K21" t="n">
-        <v>-21.25970279201362</v>
+        <v>-21.24013277139327</v>
       </c>
       <c r="L21" t="n">
         <v>16.84258916554939</v>
@@ -4151,13 +4151,13 @@
         <v>28.902</v>
       </c>
       <c r="U21" t="n">
-        <v>45.183</v>
+        <v>45.219</v>
       </c>
       <c r="V21" t="n">
-        <v>14.993</v>
+        <v>15.021</v>
       </c>
       <c r="W21" t="n">
-        <v>-57.85</v>
+        <v>-57.814</v>
       </c>
     </row>
     <row r="22">
@@ -4432,14 +4432,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.95% / +7.63% / -0.81% | BRSAN.IS: +10.45% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +4.80% / +7.63% / -0.81% | BRSAN.IS: +10.60% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>16.88747410218565</v>
+        <v>16.8911073125942</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4471,13 +4471,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>53.333</v>
+        <v>53.338</v>
       </c>
       <c r="V25" t="n">
-        <v>38.542</v>
+        <v>38.546</v>
       </c>
       <c r="W25" t="n">
-        <v>-11.056</v>
+        <v>-11.051</v>
       </c>
     </row>
     <row r="26">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.23% / +3.81% / -0.90% | ASTOR.IS: +2.10% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +1.09% / +3.81% / -0.90% | ASTOR.IS: +1.66% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>22.96498265860674</v>
+        <v>22.61533715807487</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4560,13 +4560,13 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>43.375</v>
+        <v>42.967</v>
       </c>
       <c r="V26" t="n">
-        <v>30.019</v>
+        <v>29.649</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>-0.393</v>
       </c>
     </row>
     <row r="27">
@@ -4610,14 +4610,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.23% / +1.57% / -0.95% | ASTOR.IS: +2.10% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: -0.36% / +1.57% / -0.95% | ASTOR.IS: +1.66% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>22.22148283971572</v>
+        <v>21.87475805894989</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4649,13 +4649,13 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>56.271</v>
+        <v>55.828</v>
       </c>
       <c r="V27" t="n">
-        <v>42.712</v>
+        <v>42.308</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>-0.429</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -578,7 +578,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -843,14 +843,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +12.02% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +10.95% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>9.909775949847788</v>
+        <v>9.353789353776865</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -882,13 +882,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>95.741</v>
+        <v>94.751</v>
       </c>
       <c r="V4" t="n">
-        <v>58.092</v>
+        <v>57.292</v>
       </c>
       <c r="W4" t="n">
-        <v>-21.899</v>
+        <v>-22.89</v>
       </c>
     </row>
     <row r="5">
@@ -930,14 +930,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +1.46% / -0.36% | DOHOL.IS: +0.61% / +1.16% / -1.07%</t>
+          <t>ALARK.IS: -0.02% / +1.46% / -0.73% | DOHOL.IS: +1.41% / +2.33% / -1.07%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K5" t="n">
-        <v>-28.45293790104135</v>
+        <v>-28.16559980540377</v>
       </c>
       <c r="L5" t="n">
         <v>25.50508358988237</v>
@@ -969,13 +969,13 @@
         <v>35.7</v>
       </c>
       <c r="U5" t="n">
-        <v>17.732</v>
+        <v>18.205</v>
       </c>
       <c r="V5" t="n">
-        <v>12.63</v>
+        <v>13.082</v>
       </c>
       <c r="W5" t="n">
-        <v>-64.831</v>
+        <v>-64.358</v>
       </c>
     </row>
     <row r="6">
@@ -1104,14 +1104,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +12.02% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +10.95% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>9.909775949847788</v>
+        <v>9.353789353776865</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1143,13 +1143,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>95.741</v>
+        <v>94.751</v>
       </c>
       <c r="V7" t="n">
-        <v>58.092</v>
+        <v>57.292</v>
       </c>
       <c r="W7" t="n">
-        <v>-21.899</v>
+        <v>-22.89</v>
       </c>
     </row>
     <row r="8">
@@ -1191,14 +1191,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +0.39% / +2.39% / -0.89% | TAVHL.IS: +0.60% / +1.41% / -0.09%</t>
+          <t>BRSAN.IS: -0.57% / +2.39% / -1.02% | TAVHL.IS: +0.51% / +1.41% / -0.09%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7832353101179024</v>
+        <v>0.2595165775889585</v>
       </c>
       <c r="L8" t="n">
         <v>13.72502171397572</v>
@@ -1210,7 +1210,7 @@
         <v>47.1</v>
       </c>
       <c r="O8" t="n">
-        <v>52.1</v>
+        <v>51</v>
       </c>
       <c r="P8" t="n">
         <v>4.6</v>
@@ -1230,13 +1230,13 @@
         <v>29.993</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.902</v>
+        <v>-1.417</v>
       </c>
       <c r="V8" t="n">
-        <v>-6.327</v>
+        <v>-6.814</v>
       </c>
       <c r="W8" t="n">
-        <v>-41.328</v>
+        <v>-41.843</v>
       </c>
     </row>
     <row r="9">
@@ -1365,14 +1365,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +0.39% / +2.39% / -0.89% | TAVHL.IS: +0.60% / +1.41% / -0.09%</t>
+          <t>BRSAN.IS: -0.57% / +2.39% / -1.02% | TAVHL.IS: +0.51% / +1.41% / -0.09%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7832353101179024</v>
+        <v>0.2595165775889585</v>
       </c>
       <c r="L10" t="n">
         <v>13.72502171397572</v>
@@ -1384,7 +1384,7 @@
         <v>47.1</v>
       </c>
       <c r="O10" t="n">
-        <v>52.1</v>
+        <v>51</v>
       </c>
       <c r="P10" t="n">
         <v>4.6</v>
@@ -1404,13 +1404,13 @@
         <v>29.993</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.902</v>
+        <v>-1.417</v>
       </c>
       <c r="V10" t="n">
-        <v>-6.327</v>
+        <v>-6.814</v>
       </c>
       <c r="W10" t="n">
-        <v>-41.328</v>
+        <v>-41.843</v>
       </c>
     </row>
     <row r="11">
@@ -1452,14 +1452,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +1.46% / -0.36% | DOHOL.IS: +0.61% / +1.16% / -1.07% | TAVHL.IS: +0.60% / +1.41% / -0.09%</t>
+          <t>ALARK.IS: -0.02% / +1.46% / -0.73% | DOHOL.IS: +1.41% / +2.33% / -1.07% | TAVHL.IS: +0.51% / +1.41% / -0.09%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3628204980789307</v>
+        <v>-0.1254831096130227</v>
       </c>
       <c r="L11" t="n">
         <v>10.56563994340933</v>
@@ -1491,13 +1491,13 @@
         <v>29.287</v>
       </c>
       <c r="U11" t="n">
-        <v>34.74</v>
+        <v>35.061</v>
       </c>
       <c r="V11" t="n">
-        <v>14.802</v>
+        <v>15.076</v>
       </c>
       <c r="W11" t="n">
-        <v>-47.209</v>
+        <v>-46.888</v>
       </c>
     </row>
     <row r="12">
@@ -1539,14 +1539,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.36% / +1.57% / -0.96% | BRSAN.IS: +4.09% / +6.16% / 0.00% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
+          <t>AKBNK.IS: +0.12% / +1.57% / -0.96% | BRSAN.IS: +3.10% / +6.16% / 0.00% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K12" t="n">
-        <v>14.03235101239271</v>
+        <v>13.84801443885533</v>
       </c>
       <c r="L12" t="n">
         <v>7.902828022135555</v>
@@ -1558,7 +1558,7 @@
         <v>34.3</v>
       </c>
       <c r="O12" t="n">
-        <v>47.1</v>
+        <v>48.6</v>
       </c>
       <c r="P12" t="n">
         <v>4.4</v>
@@ -1578,10 +1578,10 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>14.292</v>
+        <v>14.107</v>
       </c>
       <c r="V12" t="n">
-        <v>13.287</v>
+        <v>13.104</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1626,14 +1626,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +19.84% / +23.58% / 0.00% | BIMAS.IS: +1.95% / +3.87% / -0.86% | BRSAN.IS: +40.91% / +45.64% / -0.48% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +18.63% / +23.58% / 0.00% | BIMAS.IS: +1.95% / +3.87% / -0.86% | BRSAN.IS: +39.57% / +45.64% / -0.48% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K13" t="n">
-        <v>11.31703599030387</v>
+        <v>10.82165450285963</v>
       </c>
       <c r="L13" t="n">
         <v>23.4189376077676</v>
@@ -1665,10 +1665,10 @@
         <v>22.513</v>
       </c>
       <c r="U13" t="n">
-        <v>52.625</v>
+        <v>51.946</v>
       </c>
       <c r="V13" t="n">
-        <v>47.496</v>
+        <v>46.84</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1713,14 +1713,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +19.84% / +23.58% / 0.00% | BIMAS.IS: +1.95% / +3.87% / -0.86% | BRSAN.IS: +40.91% / +45.64% / -0.48% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +18.63% / +23.58% / 0.00% | BIMAS.IS: +1.95% / +3.87% / -0.86% | BRSAN.IS: +39.57% / +45.64% / -0.48% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>11.31703599030387</v>
+        <v>10.82165450285963</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1752,10 +1752,10 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>52.625</v>
+        <v>51.946</v>
       </c>
       <c r="V14" t="n">
-        <v>47.496</v>
+        <v>46.84</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2015,14 +2015,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +12.02% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +10.95% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>9.909775949847788</v>
+        <v>9.353789353776865</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -2054,13 +2054,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>95.741</v>
+        <v>94.751</v>
       </c>
       <c r="V19" t="n">
-        <v>58.092</v>
+        <v>57.292</v>
       </c>
       <c r="W19" t="n">
-        <v>-21.899</v>
+        <v>-22.89</v>
       </c>
     </row>
     <row r="20">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +1.46% / -0.36% | DOHOL.IS: +0.61% / +1.16% / -1.07%</t>
+          <t>ALARK.IS: -0.02% / +1.46% / -0.73% | DOHOL.IS: +1.41% / +2.33% / -1.07%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K20" t="n">
-        <v>-28.45293790104135</v>
+        <v>-28.16559980540377</v>
       </c>
       <c r="L20" t="n">
         <v>25.50508358988237</v>
@@ -2143,13 +2143,13 @@
         <v>35.7</v>
       </c>
       <c r="U20" t="n">
-        <v>17.732</v>
+        <v>18.205</v>
       </c>
       <c r="V20" t="n">
-        <v>12.63</v>
+        <v>13.082</v>
       </c>
       <c r="W20" t="n">
-        <v>-64.831</v>
+        <v>-64.358</v>
       </c>
     </row>
     <row r="21">
@@ -2193,14 +2193,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +0.39% / +2.39% / -0.89% | TAVHL.IS: +0.60% / +1.41% / -0.09%</t>
+          <t>BRSAN.IS: -0.57% / +2.39% / -1.02% | TAVHL.IS: +0.51% / +1.41% / -0.09%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7832353101179024</v>
+        <v>0.2595165775889585</v>
       </c>
       <c r="L21" t="n">
         <v>13.72502171397572</v>
@@ -2212,7 +2212,7 @@
         <v>47.1</v>
       </c>
       <c r="O21" t="n">
-        <v>52.1</v>
+        <v>51</v>
       </c>
       <c r="P21" t="n">
         <v>4.6</v>
@@ -2232,13 +2232,13 @@
         <v>29.993</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.902</v>
+        <v>-1.417</v>
       </c>
       <c r="V21" t="n">
-        <v>-6.327</v>
+        <v>-6.814</v>
       </c>
       <c r="W21" t="n">
-        <v>-41.328</v>
+        <v>-41.843</v>
       </c>
     </row>
     <row r="22">
@@ -2282,14 +2282,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +1.46% / -0.36% | DOHOL.IS: +0.61% / +1.16% / -1.07% | TAVHL.IS: +0.60% / +1.41% / -0.09%</t>
+          <t>ALARK.IS: -0.02% / +1.46% / -0.73% | DOHOL.IS: +1.41% / +2.33% / -1.07% | TAVHL.IS: +0.51% / +1.41% / -0.09%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3628204980789307</v>
+        <v>-0.1254831096130227</v>
       </c>
       <c r="L22" t="n">
         <v>10.56563994340933</v>
@@ -2321,13 +2321,13 @@
         <v>29.287</v>
       </c>
       <c r="U22" t="n">
-        <v>34.74</v>
+        <v>35.061</v>
       </c>
       <c r="V22" t="n">
-        <v>14.802</v>
+        <v>15.076</v>
       </c>
       <c r="W22" t="n">
-        <v>-47.209</v>
+        <v>-46.888</v>
       </c>
     </row>
     <row r="23">
@@ -2371,14 +2371,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +19.84% / +23.58% / 0.00% | BIMAS.IS: +1.95% / +3.87% / -0.86% | BRSAN.IS: +40.91% / +45.64% / -0.48% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +18.63% / +23.58% / 0.00% | BIMAS.IS: +1.95% / +3.87% / -0.86% | BRSAN.IS: +39.57% / +45.64% / -0.48% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K23" t="n">
-        <v>11.31703599030387</v>
+        <v>10.82165450285963</v>
       </c>
       <c r="L23" t="n">
         <v>23.4189376077676</v>
@@ -2410,10 +2410,10 @@
         <v>22.513</v>
       </c>
       <c r="U23" t="n">
-        <v>52.625</v>
+        <v>51.946</v>
       </c>
       <c r="V23" t="n">
-        <v>47.496</v>
+        <v>46.84</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -2460,14 +2460,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +19.84% / +23.58% / 0.00% | BIMAS.IS: +1.95% / +3.87% / -0.86% | BRSAN.IS: +40.91% / +45.64% / -0.48% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
+          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +18.63% / +23.58% / 0.00% | BIMAS.IS: +1.95% / +3.87% / -0.86% | BRSAN.IS: +39.57% / +45.64% / -0.48% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K24" t="n">
-        <v>11.31703599030387</v>
+        <v>10.82165450285963</v>
       </c>
       <c r="L24" t="n">
         <v>23.4189376077676</v>
@@ -2499,10 +2499,10 @@
         <v>22.513</v>
       </c>
       <c r="U24" t="n">
-        <v>52.625</v>
+        <v>51.946</v>
       </c>
       <c r="V24" t="n">
-        <v>47.496</v>
+        <v>46.84</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -2549,14 +2549,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.36% / +1.57% / -0.96% | BRSAN.IS: +4.09% / +6.16% / 0.00% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
+          <t>AKBNK.IS: +0.12% / +1.57% / -0.96% | BRSAN.IS: +3.10% / +6.16% / 0.00% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K25" t="n">
-        <v>14.03235101239271</v>
+        <v>13.84801443885533</v>
       </c>
       <c r="L25" t="n">
         <v>7.902828022135555</v>
@@ -2568,7 +2568,7 @@
         <v>34.3</v>
       </c>
       <c r="O25" t="n">
-        <v>47.1</v>
+        <v>48.6</v>
       </c>
       <c r="P25" t="n">
         <v>4.4</v>
@@ -2588,10 +2588,10 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>14.292</v>
+        <v>14.107</v>
       </c>
       <c r="V25" t="n">
-        <v>13.287</v>
+        <v>13.104</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -3182,14 +3182,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.59% / +1.22% / -1.29% | BRSAN.IS: +0.39% / +2.39% / -0.89% | TRALT.IS: +2.01% / +2.58% / 0.00%</t>
+          <t>ASTOR.IS: -1.60% / +1.22% / -2.08% | BRSAN.IS: -0.57% / +2.39% / -1.02% | TRALT.IS: +0.53% / +2.76% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K8" t="n">
-        <v>-21.24013277139327</v>
+        <v>-22.13573069239504</v>
       </c>
       <c r="L8" t="n">
         <v>16.84258916554939</v>
@@ -3201,7 +3201,7 @@
         <v>111.7</v>
       </c>
       <c r="O8" t="n">
-        <v>38.8</v>
+        <v>38.3</v>
       </c>
       <c r="P8" t="n">
         <v>4.9</v>
@@ -3215,19 +3215,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>28.902</v>
+        <v>29.288</v>
       </c>
       <c r="T8" t="n">
-        <v>28.902</v>
+        <v>29.288</v>
       </c>
       <c r="U8" t="n">
-        <v>45.219</v>
+        <v>43.567</v>
       </c>
       <c r="V8" t="n">
-        <v>15.021</v>
+        <v>13.713</v>
       </c>
       <c r="W8" t="n">
-        <v>-57.814</v>
+        <v>-59.465</v>
       </c>
     </row>
     <row r="9">
@@ -3494,14 +3494,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.09% / +3.81% / -0.90% | ASTOR.IS: +1.66% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +1.57% / +3.81% / -0.90% | ASTOR.IS: +0.64% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>22.61533715807487</v>
+        <v>22.28877222034233</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3533,13 +3533,13 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>42.967</v>
+        <v>42.587</v>
       </c>
       <c r="V12" t="n">
-        <v>29.649</v>
+        <v>29.304</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.393</v>
+        <v>-0.774</v>
       </c>
     </row>
     <row r="13">
@@ -3581,14 +3581,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.36% / +1.57% / -0.95% | ASTOR.IS: +1.66% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +0.12% / +1.57% / -0.95% | ASTOR.IS: +0.64% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>21.87475805894989</v>
+        <v>21.54674763813658</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3600,7 +3600,7 @@
         <v>128</v>
       </c>
       <c r="O13" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="P13" t="n">
         <v>3.9</v>
@@ -3620,13 +3620,13 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>55.828</v>
+        <v>55.409</v>
       </c>
       <c r="V13" t="n">
-        <v>42.308</v>
+        <v>41.925</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.429</v>
+        <v>-0.848</v>
       </c>
     </row>
     <row r="14">
@@ -3668,14 +3668,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.80% / +7.63% / -0.81% | BRSAN.IS: +10.60% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +5.30% / +7.63% / -0.81% | BRSAN.IS: +9.55% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>16.8911073125942</v>
+        <v>16.5925853534677</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3707,13 +3707,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>53.338</v>
+        <v>52.946</v>
       </c>
       <c r="V14" t="n">
-        <v>38.546</v>
+        <v>38.192</v>
       </c>
       <c r="W14" t="n">
-        <v>-11.051</v>
+        <v>-11.443</v>
       </c>
     </row>
     <row r="16">
@@ -4112,14 +4112,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.59% / +1.22% / -1.29% | BRSAN.IS: +0.39% / +2.39% / -0.89% | TRALT.IS: +2.01% / +2.58% / 0.00%</t>
+          <t>ASTOR.IS: -1.60% / +1.22% / -2.08% | BRSAN.IS: -0.57% / +2.39% / -1.02% | TRALT.IS: +0.53% / +2.76% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K21" t="n">
-        <v>-21.24013277139327</v>
+        <v>-22.13573069239504</v>
       </c>
       <c r="L21" t="n">
         <v>16.84258916554939</v>
@@ -4131,7 +4131,7 @@
         <v>111.7</v>
       </c>
       <c r="O21" t="n">
-        <v>38.8</v>
+        <v>38.3</v>
       </c>
       <c r="P21" t="n">
         <v>4.9</v>
@@ -4145,19 +4145,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>28.902</v>
+        <v>29.288</v>
       </c>
       <c r="T21" t="n">
-        <v>28.902</v>
+        <v>29.288</v>
       </c>
       <c r="U21" t="n">
-        <v>45.219</v>
+        <v>43.567</v>
       </c>
       <c r="V21" t="n">
-        <v>15.021</v>
+        <v>13.713</v>
       </c>
       <c r="W21" t="n">
-        <v>-57.814</v>
+        <v>-59.465</v>
       </c>
     </row>
     <row r="22">
@@ -4432,14 +4432,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +4.80% / +7.63% / -0.81% | BRSAN.IS: +10.60% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +5.30% / +7.63% / -0.81% | BRSAN.IS: +9.55% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>16.8911073125942</v>
+        <v>16.5925853534677</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4471,13 +4471,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>53.338</v>
+        <v>52.946</v>
       </c>
       <c r="V25" t="n">
-        <v>38.546</v>
+        <v>38.192</v>
       </c>
       <c r="W25" t="n">
-        <v>-11.051</v>
+        <v>-11.443</v>
       </c>
     </row>
     <row r="26">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.09% / +3.81% / -0.90% | ASTOR.IS: +1.66% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +1.57% / +3.81% / -0.90% | ASTOR.IS: +0.64% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>22.61533715807487</v>
+        <v>22.28877222034233</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4560,13 +4560,13 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>42.967</v>
+        <v>42.587</v>
       </c>
       <c r="V26" t="n">
-        <v>29.649</v>
+        <v>29.304</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.393</v>
+        <v>-0.774</v>
       </c>
     </row>
     <row r="27">
@@ -4610,14 +4610,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.36% / +1.57% / -0.95% | ASTOR.IS: +1.66% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +0.12% / +1.57% / -0.95% | ASTOR.IS: +0.64% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>21.87475805894989</v>
+        <v>21.54674763813658</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4629,7 +4629,7 @@
         <v>128</v>
       </c>
       <c r="O27" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="P27" t="n">
         <v>3.9</v>
@@ -4649,13 +4649,13 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>55.828</v>
+        <v>55.409</v>
       </c>
       <c r="V27" t="n">
-        <v>42.308</v>
+        <v>41.925</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.429</v>
+        <v>-0.848</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -843,14 +843,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +10.95% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.65% / +4.70% / -3.86% | BRSAN.IS: +10.72% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>9.353789353776865</v>
+        <v>9.516808420212275</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -882,13 +882,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>94.751</v>
+        <v>95.041</v>
       </c>
       <c r="V4" t="n">
-        <v>57.292</v>
+        <v>57.526</v>
       </c>
       <c r="W4" t="n">
-        <v>-22.89</v>
+        <v>-22.599</v>
       </c>
     </row>
     <row r="5">
@@ -930,14 +930,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +1.46% / -0.73% | DOHOL.IS: +1.41% / +2.33% / -1.07%</t>
+          <t>ALARK.IS: +0.53% / +1.46% / -0.73% | DOHOL.IS: +1.41% / +2.33% / -1.07%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K5" t="n">
-        <v>-28.16559980540377</v>
+        <v>-27.97033247114848</v>
       </c>
       <c r="L5" t="n">
         <v>25.50508358988237</v>
@@ -949,7 +949,7 @@
         <v>94.09999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="P5" t="n">
         <v>3.9</v>
@@ -969,13 +969,13 @@
         <v>35.7</v>
       </c>
       <c r="U5" t="n">
-        <v>18.205</v>
+        <v>18.526</v>
       </c>
       <c r="V5" t="n">
-        <v>13.082</v>
+        <v>13.39</v>
       </c>
       <c r="W5" t="n">
-        <v>-64.358</v>
+        <v>-64.036</v>
       </c>
     </row>
     <row r="6">
@@ -1104,14 +1104,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +10.95% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.65% / +4.70% / -3.86% | BRSAN.IS: +10.72% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>9.353789353776865</v>
+        <v>9.516808420212275</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1143,13 +1143,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>94.751</v>
+        <v>95.041</v>
       </c>
       <c r="V7" t="n">
-        <v>57.292</v>
+        <v>57.526</v>
       </c>
       <c r="W7" t="n">
-        <v>-22.89</v>
+        <v>-22.599</v>
       </c>
     </row>
     <row r="8">
@@ -1191,14 +1191,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.57% / +2.39% / -1.02% | TAVHL.IS: +0.51% / +1.41% / -0.09%</t>
+          <t>BRSAN.IS: -0.77% / +2.39% / -1.30% | TAVHL.IS: -0.02% / +1.41% / -0.18%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2595165775889585</v>
+        <v>-0.1089969675226232</v>
       </c>
       <c r="L8" t="n">
         <v>13.72502171397572</v>
@@ -1210,7 +1210,7 @@
         <v>47.1</v>
       </c>
       <c r="O8" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P8" t="n">
         <v>4.6</v>
@@ -1224,19 +1224,19 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>29.993</v>
+        <v>30.055</v>
       </c>
       <c r="T8" t="n">
-        <v>29.993</v>
+        <v>30.055</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.417</v>
+        <v>-1.78</v>
       </c>
       <c r="V8" t="n">
-        <v>-6.814</v>
+        <v>-7.156</v>
       </c>
       <c r="W8" t="n">
-        <v>-41.843</v>
+        <v>-42.205</v>
       </c>
     </row>
     <row r="9">
@@ -1365,14 +1365,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.57% / +2.39% / -1.02% | TAVHL.IS: +0.51% / +1.41% / -0.09%</t>
+          <t>BRSAN.IS: -0.77% / +2.39% / -1.30% | TAVHL.IS: -0.02% / +1.41% / -0.18%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2595165775889585</v>
+        <v>-0.1089969675226232</v>
       </c>
       <c r="L10" t="n">
         <v>13.72502171397572</v>
@@ -1384,7 +1384,7 @@
         <v>47.1</v>
       </c>
       <c r="O10" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P10" t="n">
         <v>4.6</v>
@@ -1398,19 +1398,19 @@
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>29.993</v>
+        <v>30.055</v>
       </c>
       <c r="T10" t="n">
-        <v>29.993</v>
+        <v>30.055</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.417</v>
+        <v>-1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>-6.814</v>
+        <v>-7.156</v>
       </c>
       <c r="W10" t="n">
-        <v>-41.843</v>
+        <v>-42.205</v>
       </c>
     </row>
     <row r="11">
@@ -1452,14 +1452,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +1.46% / -0.73% | DOHOL.IS: +1.41% / +2.33% / -1.07% | TAVHL.IS: +0.51% / +1.41% / -0.09%</t>
+          <t>ALARK.IS: +0.53% / +1.46% / -0.73% | DOHOL.IS: +1.41% / +2.33% / -1.07% | TAVHL.IS: -0.02% / +1.41% / -0.18%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1254831096130227</v>
+        <v>-0.1196539232451554</v>
       </c>
       <c r="L11" t="n">
         <v>10.56563994340933</v>
@@ -1491,13 +1491,13 @@
         <v>29.287</v>
       </c>
       <c r="U11" t="n">
-        <v>35.061</v>
+        <v>35.069</v>
       </c>
       <c r="V11" t="n">
-        <v>15.076</v>
+        <v>15.082</v>
       </c>
       <c r="W11" t="n">
-        <v>-46.888</v>
+        <v>-46.88</v>
       </c>
     </row>
     <row r="12">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-26 | BRSAN.IS: 2026-08-26 | CANTE.IS: 2026-08-21</t>
+          <t>AKBNK.IS: 2026-08-26 | BRSAN.IS: 2026-08-28 | CANTE.IS: 2026-08-21</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1539,14 +1539,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.12% / +1.57% / -0.96% | BRSAN.IS: +3.10% / +6.16% / 0.00% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
+          <t>AKBNK.IS: +0.05% / +1.57% / -0.96% | BRSAN.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: +7.42% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K12" t="n">
-        <v>13.84801443885533</v>
+        <v>12.82494611781235</v>
       </c>
       <c r="L12" t="n">
         <v>7.902828022135555</v>
@@ -1555,10 +1555,10 @@
         <v>33.33333333333333</v>
       </c>
       <c r="N12" t="n">
-        <v>34.3</v>
+        <v>34.8</v>
       </c>
       <c r="O12" t="n">
-        <v>48.6</v>
+        <v>47.9</v>
       </c>
       <c r="P12" t="n">
         <v>4.4</v>
@@ -1578,13 +1578,13 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>14.107</v>
+        <v>13.082</v>
       </c>
       <c r="V12" t="n">
-        <v>13.104</v>
+        <v>12.087</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.745</v>
       </c>
     </row>
     <row r="13">
@@ -1626,14 +1626,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +18.63% / +23.58% / 0.00% | BIMAS.IS: +1.95% / +3.87% / -0.86% | BRSAN.IS: +39.57% / +45.64% / -0.48% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
+          <t>ALARK.IS: +3.65% / +4.70% / -3.86% | ASTOR.IS: +20.61% / +23.58% / 0.00% | BIMAS.IS: +2.07% / +3.87% / -0.86% | BRSAN.IS: +39.28% / +45.64% / -0.48% | CANTE.IS: +7.42% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K13" t="n">
-        <v>10.82165450285963</v>
+        <v>10.8016778336085</v>
       </c>
       <c r="L13" t="n">
         <v>23.4189376077676</v>
@@ -1665,10 +1665,10 @@
         <v>22.513</v>
       </c>
       <c r="U13" t="n">
-        <v>51.946</v>
+        <v>51.918</v>
       </c>
       <c r="V13" t="n">
-        <v>46.84</v>
+        <v>46.813</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1713,14 +1713,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +18.63% / +23.58% / 0.00% | BIMAS.IS: +1.95% / +3.87% / -0.86% | BRSAN.IS: +39.57% / +45.64% / -0.48% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
+          <t>ALARK.IS: +3.65% / +4.70% / -3.86% | ASTOR.IS: +20.61% / +23.58% / 0.00% | BIMAS.IS: +2.07% / +3.87% / -0.86% | BRSAN.IS: +39.28% / +45.64% / -0.48% | CANTE.IS: +7.42% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>10.82165450285963</v>
+        <v>10.8016778336085</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1752,10 +1752,10 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>51.946</v>
+        <v>51.918</v>
       </c>
       <c r="V14" t="n">
-        <v>46.84</v>
+        <v>46.813</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2015,14 +2015,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | BRSAN.IS: +10.95% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +3.65% / +4.70% / -3.86% | BRSAN.IS: +10.72% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>9.353789353776865</v>
+        <v>9.516808420212275</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -2054,13 +2054,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>94.751</v>
+        <v>95.041</v>
       </c>
       <c r="V19" t="n">
-        <v>57.292</v>
+        <v>57.526</v>
       </c>
       <c r="W19" t="n">
-        <v>-22.89</v>
+        <v>-22.599</v>
       </c>
     </row>
     <row r="20">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +1.46% / -0.73% | DOHOL.IS: +1.41% / +2.33% / -1.07%</t>
+          <t>ALARK.IS: +0.53% / +1.46% / -0.73% | DOHOL.IS: +1.41% / +2.33% / -1.07%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K20" t="n">
-        <v>-28.16559980540377</v>
+        <v>-27.97033247114848</v>
       </c>
       <c r="L20" t="n">
         <v>25.50508358988237</v>
@@ -2123,7 +2123,7 @@
         <v>94.09999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="P20" t="n">
         <v>3.9</v>
@@ -2143,13 +2143,13 @@
         <v>35.7</v>
       </c>
       <c r="U20" t="n">
-        <v>18.205</v>
+        <v>18.526</v>
       </c>
       <c r="V20" t="n">
-        <v>13.082</v>
+        <v>13.39</v>
       </c>
       <c r="W20" t="n">
-        <v>-64.358</v>
+        <v>-64.036</v>
       </c>
     </row>
     <row r="21">
@@ -2193,14 +2193,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.57% / +2.39% / -1.02% | TAVHL.IS: +0.51% / +1.41% / -0.09%</t>
+          <t>BRSAN.IS: -0.77% / +2.39% / -1.30% | TAVHL.IS: -0.02% / +1.41% / -0.18%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2595165775889585</v>
+        <v>-0.1089969675226232</v>
       </c>
       <c r="L21" t="n">
         <v>13.72502171397572</v>
@@ -2212,7 +2212,7 @@
         <v>47.1</v>
       </c>
       <c r="O21" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P21" t="n">
         <v>4.6</v>
@@ -2226,19 +2226,19 @@
         <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>29.993</v>
+        <v>30.055</v>
       </c>
       <c r="T21" t="n">
-        <v>29.993</v>
+        <v>30.055</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.417</v>
+        <v>-1.78</v>
       </c>
       <c r="V21" t="n">
-        <v>-6.814</v>
+        <v>-7.156</v>
       </c>
       <c r="W21" t="n">
-        <v>-41.843</v>
+        <v>-42.205</v>
       </c>
     </row>
     <row r="22">
@@ -2282,14 +2282,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +1.46% / -0.73% | DOHOL.IS: +1.41% / +2.33% / -1.07% | TAVHL.IS: +0.51% / +1.41% / -0.09%</t>
+          <t>ALARK.IS: +0.53% / +1.46% / -0.73% | DOHOL.IS: +1.41% / +2.33% / -1.07% | TAVHL.IS: -0.02% / +1.41% / -0.18%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1254831096130227</v>
+        <v>-0.1196539232451554</v>
       </c>
       <c r="L22" t="n">
         <v>10.56563994340933</v>
@@ -2321,13 +2321,13 @@
         <v>29.287</v>
       </c>
       <c r="U22" t="n">
-        <v>35.061</v>
+        <v>35.069</v>
       </c>
       <c r="V22" t="n">
-        <v>15.076</v>
+        <v>15.082</v>
       </c>
       <c r="W22" t="n">
-        <v>-46.888</v>
+        <v>-46.88</v>
       </c>
     </row>
     <row r="23">
@@ -2371,14 +2371,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +18.63% / +23.58% / 0.00% | BIMAS.IS: +1.95% / +3.87% / -0.86% | BRSAN.IS: +39.57% / +45.64% / -0.48% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
+          <t>ALARK.IS: +3.65% / +4.70% / -3.86% | ASTOR.IS: +20.61% / +23.58% / 0.00% | BIMAS.IS: +2.07% / +3.87% / -0.86% | BRSAN.IS: +39.28% / +45.64% / -0.48% | CANTE.IS: +7.42% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K23" t="n">
-        <v>10.82165450285963</v>
+        <v>10.8016778336085</v>
       </c>
       <c r="L23" t="n">
         <v>23.4189376077676</v>
@@ -2410,10 +2410,10 @@
         <v>22.513</v>
       </c>
       <c r="U23" t="n">
-        <v>51.946</v>
+        <v>51.918</v>
       </c>
       <c r="V23" t="n">
-        <v>46.84</v>
+        <v>46.813</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -2460,14 +2460,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.08% / +4.70% / -3.86% | ASTOR.IS: +18.63% / +23.58% / 0.00% | BIMAS.IS: +1.95% / +3.87% / -0.86% | BRSAN.IS: +39.57% / +45.64% / -0.48% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
+          <t>ALARK.IS: +3.65% / +4.70% / -3.86% | ASTOR.IS: +20.61% / +23.58% / 0.00% | BIMAS.IS: +2.07% / +3.87% / -0.86% | BRSAN.IS: +39.28% / +45.64% / -0.48% | CANTE.IS: +7.42% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K24" t="n">
-        <v>10.82165450285963</v>
+        <v>10.8016778336085</v>
       </c>
       <c r="L24" t="n">
         <v>23.4189376077676</v>
@@ -2499,10 +2499,10 @@
         <v>22.513</v>
       </c>
       <c r="U24" t="n">
-        <v>51.946</v>
+        <v>51.918</v>
       </c>
       <c r="V24" t="n">
-        <v>46.84</v>
+        <v>46.813</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-26 | BRSAN.IS: 2026-08-26 | CANTE.IS: 2026-08-21</t>
+          <t>AKBNK.IS: 2026-08-26 | BRSAN.IS: 2026-08-28 | CANTE.IS: 2026-08-21</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -2549,14 +2549,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.12% / +1.57% / -0.96% | BRSAN.IS: +3.10% / +6.16% / 0.00% | CANTE.IS: +9.90% / +9.92% / -0.83%</t>
+          <t>AKBNK.IS: +0.05% / +1.57% / -0.96% | BRSAN.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: +7.42% / +9.92% / -0.83%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K25" t="n">
-        <v>13.84801443885533</v>
+        <v>12.82494611781235</v>
       </c>
       <c r="L25" t="n">
         <v>7.902828022135555</v>
@@ -2565,10 +2565,10 @@
         <v>33.33333333333333</v>
       </c>
       <c r="N25" t="n">
-        <v>34.3</v>
+        <v>34.8</v>
       </c>
       <c r="O25" t="n">
-        <v>48.6</v>
+        <v>47.9</v>
       </c>
       <c r="P25" t="n">
         <v>4.4</v>
@@ -2588,13 +2588,13 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>14.107</v>
+        <v>13.082</v>
       </c>
       <c r="V25" t="n">
-        <v>13.104</v>
+        <v>12.087</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.745</v>
       </c>
     </row>
   </sheetData>
@@ -3182,14 +3182,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -1.60% / +1.22% / -2.08% | BRSAN.IS: -0.57% / +2.39% / -1.02% | TRALT.IS: +0.53% / +2.76% / 0.00%</t>
+          <t>ASTOR.IS: +0.05% / +1.22% / -2.08% | BRSAN.IS: -0.77% / +2.39% / -1.30% | TRALT.IS: -0.66% / +2.76% / -1.66%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K8" t="n">
-        <v>-22.13573069239504</v>
+        <v>-22.07151331458045</v>
       </c>
       <c r="L8" t="n">
         <v>16.84258916554939</v>
@@ -3215,19 +3215,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>29.288</v>
+        <v>29.23</v>
       </c>
       <c r="T8" t="n">
-        <v>29.288</v>
+        <v>29.23</v>
       </c>
       <c r="U8" t="n">
-        <v>43.567</v>
+        <v>43.686</v>
       </c>
       <c r="V8" t="n">
-        <v>13.713</v>
+        <v>13.807</v>
       </c>
       <c r="W8" t="n">
-        <v>-59.465</v>
+        <v>-59.347</v>
       </c>
     </row>
     <row r="9">
@@ -3494,14 +3494,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.57% / +3.81% / -0.90% | ASTOR.IS: +0.64% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +1.51% / +3.81% / -0.90% | ASTOR.IS: +2.32% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>22.28877222034233</v>
+        <v>23.26561805146417</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3533,13 +3533,13 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>42.587</v>
+        <v>43.726</v>
       </c>
       <c r="V12" t="n">
-        <v>29.304</v>
+        <v>30.337</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.774</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3581,14 +3581,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.12% / +1.57% / -0.95% | ASTOR.IS: +0.64% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +0.05% / +1.57% / -0.95% | ASTOR.IS: +2.32% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>21.54674763813658</v>
+        <v>22.51853375896779</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3620,13 +3620,13 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>55.409</v>
+        <v>56.651</v>
       </c>
       <c r="V13" t="n">
-        <v>41.925</v>
+        <v>43.059</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3668,14 +3668,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +5.30% / +7.63% / -0.81% | BRSAN.IS: +9.55% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +5.23% / +7.63% / -0.81% | BRSAN.IS: +9.33% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>16.5925853534677</v>
+        <v>16.43107972063114</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3707,13 +3707,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>52.946</v>
+        <v>52.734</v>
       </c>
       <c r="V14" t="n">
-        <v>38.192</v>
+        <v>38.001</v>
       </c>
       <c r="W14" t="n">
-        <v>-11.443</v>
+        <v>-11.655</v>
       </c>
     </row>
     <row r="16">
@@ -4112,14 +4112,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -1.60% / +1.22% / -2.08% | BRSAN.IS: -0.57% / +2.39% / -1.02% | TRALT.IS: +0.53% / +2.76% / 0.00%</t>
+          <t>ASTOR.IS: +0.05% / +1.22% / -2.08% | BRSAN.IS: -0.77% / +2.39% / -1.30% | TRALT.IS: -0.66% / +2.76% / -1.66%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K21" t="n">
-        <v>-22.13573069239504</v>
+        <v>-22.07151331458045</v>
       </c>
       <c r="L21" t="n">
         <v>16.84258916554939</v>
@@ -4145,19 +4145,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>29.288</v>
+        <v>29.23</v>
       </c>
       <c r="T21" t="n">
-        <v>29.288</v>
+        <v>29.23</v>
       </c>
       <c r="U21" t="n">
-        <v>43.567</v>
+        <v>43.686</v>
       </c>
       <c r="V21" t="n">
-        <v>13.713</v>
+        <v>13.807</v>
       </c>
       <c r="W21" t="n">
-        <v>-59.465</v>
+        <v>-59.347</v>
       </c>
     </row>
     <row r="22">
@@ -4432,14 +4432,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +5.30% / +7.63% / -0.81% | BRSAN.IS: +9.55% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +5.23% / +7.63% / -0.81% | BRSAN.IS: +9.33% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>16.5925853534677</v>
+        <v>16.43107972063114</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4471,13 +4471,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>52.946</v>
+        <v>52.734</v>
       </c>
       <c r="V25" t="n">
-        <v>38.192</v>
+        <v>38.001</v>
       </c>
       <c r="W25" t="n">
-        <v>-11.443</v>
+        <v>-11.655</v>
       </c>
     </row>
     <row r="26">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.57% / +3.81% / -0.90% | ASTOR.IS: +0.64% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +1.51% / +3.81% / -0.90% | ASTOR.IS: +2.32% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>22.28877222034233</v>
+        <v>23.26561805146417</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4560,13 +4560,13 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>42.587</v>
+        <v>43.726</v>
       </c>
       <c r="V26" t="n">
-        <v>29.304</v>
+        <v>30.337</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.774</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -4610,14 +4610,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.12% / +1.57% / -0.95% | ASTOR.IS: +0.64% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +0.05% / +1.57% / -0.95% | ASTOR.IS: +2.32% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>21.54674763813658</v>
+        <v>22.51853375896779</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4649,13 +4649,13 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>55.409</v>
+        <v>56.651</v>
       </c>
       <c r="V27" t="n">
-        <v>41.925</v>
+        <v>43.059</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.848</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -578,7 +578,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -0.66% / +0.09% / -1.09% | ALTNY.IS: -0.13% / +0.38% / -1.73% | DOHOL.IS: -0.73% / +0.00% / -0.79%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K3" t="n">
-        <v>-25.81926606744547</v>
+        <v>-26.17768269500018</v>
       </c>
       <c r="L3" t="n">
         <v>14.20226218585835</v>
@@ -772,7 +772,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>118.2</v>
+        <v>117.9</v>
       </c>
       <c r="O3" t="n">
         <v>39.4</v>
@@ -789,19 +789,19 @@
         <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>28.595</v>
+        <v>28.94</v>
       </c>
       <c r="T3" t="n">
-        <v>28.595</v>
+        <v>28.94</v>
       </c>
       <c r="U3" t="n">
-        <v>78.48999999999999</v>
+        <v>81.00700000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>41.712</v>
+        <v>41.027</v>
       </c>
       <c r="W3" t="n">
-        <v>-71.48</v>
+        <v>-73.71899999999999</v>
       </c>
     </row>
     <row r="4">
@@ -820,12 +820,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -843,14 +843,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.65% / +4.70% / -3.86% | BRSAN.IS: +10.72% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.99% / +4.70% / -3.86% | BRSAN.IS: +11.11% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>9.516808420212275</v>
+        <v>9.386190102180404</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -859,7 +859,7 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>120.6</v>
+        <v>120.4</v>
       </c>
       <c r="O4" t="n">
         <v>43.5</v>
@@ -882,10 +882,10 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>95.041</v>
+        <v>92.824</v>
       </c>
       <c r="V4" t="n">
-        <v>57.526</v>
+        <v>57.339</v>
       </c>
       <c r="W4" t="n">
         <v>-22.599</v>
@@ -907,12 +907,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -930,14 +930,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.53% / +1.46% / -0.73% | DOHOL.IS: +1.41% / +2.33% / -1.07%</t>
+          <t>ALARK.IS: -0.11% / +1.46% / -0.73% | DOHOL.IS: +0.70% / +2.33% / -1.07%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K5" t="n">
-        <v>-27.97033247114848</v>
+        <v>-28.45355490687034</v>
       </c>
       <c r="L5" t="n">
         <v>25.50508358988237</v>
@@ -946,10 +946,10 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>94.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="P5" t="n">
         <v>3.9</v>
@@ -969,13 +969,13 @@
         <v>35.7</v>
       </c>
       <c r="U5" t="n">
-        <v>18.526</v>
+        <v>19.096</v>
       </c>
       <c r="V5" t="n">
-        <v>13.39</v>
+        <v>12.629</v>
       </c>
       <c r="W5" t="n">
-        <v>-64.036</v>
+        <v>-65.583</v>
       </c>
     </row>
     <row r="6">
@@ -994,12 +994,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1017,14 +1017,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -0.66% / +0.09% / -1.09% | ALTNY.IS: -0.13% / +0.38% / -1.73% | DOHOL.IS: -0.73% / +0.00% / -0.79%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K6" t="n">
-        <v>-25.81926606744547</v>
+        <v>-26.17768269500018</v>
       </c>
       <c r="L6" t="n">
         <v>14.20226218585835</v>
@@ -1033,7 +1033,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>118.2</v>
+        <v>117.9</v>
       </c>
       <c r="O6" t="n">
         <v>39.4</v>
@@ -1050,19 +1050,19 @@
         <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>28.595</v>
+        <v>28.94</v>
       </c>
       <c r="T6" t="n">
-        <v>28.595</v>
+        <v>28.94</v>
       </c>
       <c r="U6" t="n">
-        <v>78.48999999999999</v>
+        <v>81.00700000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>41.712</v>
+        <v>41.027</v>
       </c>
       <c r="W6" t="n">
-        <v>-71.48</v>
+        <v>-73.71899999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1104,14 +1104,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.65% / +4.70% / -3.86% | BRSAN.IS: +10.72% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.99% / +4.70% / -3.86% | BRSAN.IS: +11.11% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>9.516808420212275</v>
+        <v>9.386190102180404</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1120,7 +1120,7 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>120.6</v>
+        <v>120.4</v>
       </c>
       <c r="O7" t="n">
         <v>43.5</v>
@@ -1143,10 +1143,10 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>95.041</v>
+        <v>92.824</v>
       </c>
       <c r="V7" t="n">
-        <v>57.526</v>
+        <v>57.339</v>
       </c>
       <c r="W7" t="n">
         <v>-22.599</v>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1191,14 +1191,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.77% / +2.39% / -1.30% | TAVHL.IS: -0.02% / +1.41% / -0.18%</t>
+          <t>BRSAN.IS: -0.43% / +2.39% / -1.30% | TAVHL.IS: -1.26% / +1.41% / -1.41%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1089969675226232</v>
+        <v>-0.557928743144176</v>
       </c>
       <c r="L8" t="n">
         <v>13.72502171397572</v>
@@ -1207,7 +1207,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N8" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="O8" t="n">
         <v>50</v>
@@ -1224,19 +1224,19 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>30.055</v>
+        <v>30.369</v>
       </c>
       <c r="T8" t="n">
-        <v>30.055</v>
+        <v>30.369</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.78</v>
+        <v>-3.65</v>
       </c>
       <c r="V8" t="n">
-        <v>-7.156</v>
+        <v>-7.573</v>
       </c>
       <c r="W8" t="n">
-        <v>-42.205</v>
+        <v>-42.023</v>
       </c>
     </row>
     <row r="9">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1278,14 +1278,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -0.66% / +0.09% / -1.09% | ALTNY.IS: -0.13% / +0.38% / -1.73% | DOHOL.IS: -0.73% / +0.00% / -0.79%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K9" t="n">
-        <v>-25.81926606744547</v>
+        <v>-26.17768269500018</v>
       </c>
       <c r="L9" t="n">
         <v>14.20226218585835</v>
@@ -1294,7 +1294,7 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>118.2</v>
+        <v>117.9</v>
       </c>
       <c r="O9" t="n">
         <v>39.4</v>
@@ -1311,19 +1311,19 @@
         <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>28.595</v>
+        <v>28.94</v>
       </c>
       <c r="T9" t="n">
-        <v>28.595</v>
+        <v>28.94</v>
       </c>
       <c r="U9" t="n">
-        <v>78.48999999999999</v>
+        <v>81.00700000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>41.712</v>
+        <v>41.027</v>
       </c>
       <c r="W9" t="n">
-        <v>-71.48</v>
+        <v>-73.71899999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1365,14 +1365,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.77% / +2.39% / -1.30% | TAVHL.IS: -0.02% / +1.41% / -0.18%</t>
+          <t>BRSAN.IS: -0.43% / +2.39% / -1.30% | TAVHL.IS: -1.26% / +1.41% / -1.41%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1089969675226232</v>
+        <v>-0.557928743144176</v>
       </c>
       <c r="L10" t="n">
         <v>13.72502171397572</v>
@@ -1381,7 +1381,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="O10" t="n">
         <v>50</v>
@@ -1398,19 +1398,19 @@
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>30.055</v>
+        <v>30.369</v>
       </c>
       <c r="T10" t="n">
-        <v>30.055</v>
+        <v>30.369</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.78</v>
+        <v>-3.65</v>
       </c>
       <c r="V10" t="n">
-        <v>-7.156</v>
+        <v>-7.573</v>
       </c>
       <c r="W10" t="n">
-        <v>-42.205</v>
+        <v>-42.023</v>
       </c>
     </row>
     <row r="11">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1452,14 +1452,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.53% / +1.46% / -0.73% | DOHOL.IS: +1.41% / +2.33% / -1.07% | TAVHL.IS: -0.02% / +1.41% / -0.18%</t>
+          <t>ALARK.IS: -0.11% / +1.46% / -0.73% | DOHOL.IS: +0.70% / +2.33% / -1.07% | TAVHL.IS: -1.26% / +1.41% / -1.41%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1196539232451554</v>
+        <v>-0.9768485639447322</v>
       </c>
       <c r="L11" t="n">
         <v>10.56563994340933</v>
@@ -1468,13 +1468,13 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>73.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>38.9</v>
+        <v>38.3</v>
       </c>
       <c r="P11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1491,13 +1491,13 @@
         <v>29.287</v>
       </c>
       <c r="U11" t="n">
-        <v>35.069</v>
+        <v>34.178</v>
       </c>
       <c r="V11" t="n">
-        <v>15.082</v>
+        <v>14.095</v>
       </c>
       <c r="W11" t="n">
-        <v>-46.88</v>
+        <v>-48.135</v>
       </c>
     </row>
     <row r="12">
@@ -1516,12 +1516,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1539,14 +1539,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.05% / +1.57% / -0.96% | BRSAN.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: +7.42% / +9.92% / -0.83%</t>
+          <t>AKBNK.IS: -0.16% / +1.57% / -0.96% | BRSAN.IS: +0.32% / +1.10% / 0.00% | CANTE.IS: +14.03% / +15.70% / -0.83%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K12" t="n">
-        <v>12.82494611781235</v>
+        <v>15.29583375526287</v>
       </c>
       <c r="L12" t="n">
         <v>7.902828022135555</v>
@@ -1555,7 +1555,7 @@
         <v>33.33333333333333</v>
       </c>
       <c r="N12" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="O12" t="n">
         <v>47.9</v>
@@ -1578,13 +1578,13 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>13.082</v>
+        <v>15.558</v>
       </c>
       <c r="V12" t="n">
-        <v>12.087</v>
+        <v>14.542</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1626,14 +1626,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.65% / +4.70% / -3.86% | ASTOR.IS: +20.61% / +23.58% / 0.00% | BIMAS.IS: +2.07% / +3.87% / -0.86% | BRSAN.IS: +39.28% / +45.64% / -0.48% | CANTE.IS: +7.42% / +9.92% / -0.83%</t>
+          <t>ALARK.IS: +2.99% / +4.70% / -3.86% | ASTOR.IS: +21.82% / +23.58% / 0.00% | BIMAS.IS: +2.19% / +3.87% / -0.86% | BRSAN.IS: +39.76% / +45.64% / -0.48% | CANTE.IS: +14.03% / +15.70% / -0.83%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K13" t="n">
-        <v>10.8016778336085</v>
+        <v>12.32877730267639</v>
       </c>
       <c r="L13" t="n">
         <v>23.4189376077676</v>
@@ -1642,7 +1642,7 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>180.4</v>
+        <v>180.1</v>
       </c>
       <c r="O13" t="n">
         <v>45.9</v>
@@ -1665,10 +1665,10 @@
         <v>22.513</v>
       </c>
       <c r="U13" t="n">
-        <v>51.918</v>
+        <v>52.596</v>
       </c>
       <c r="V13" t="n">
-        <v>46.813</v>
+        <v>48.837</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1713,14 +1713,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.65% / +4.70% / -3.86% | ASTOR.IS: +20.61% / +23.58% / 0.00% | BIMAS.IS: +2.07% / +3.87% / -0.86% | BRSAN.IS: +39.28% / +45.64% / -0.48% | CANTE.IS: +7.42% / +9.92% / -0.83%</t>
+          <t>ALARK.IS: +2.99% / +4.70% / -3.86% | ASTOR.IS: +21.82% / +23.58% / 0.00% | BIMAS.IS: +2.19% / +3.87% / -0.86% | BRSAN.IS: +39.76% / +45.64% / -0.48% | CANTE.IS: +14.03% / +15.70% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>10.8016778336085</v>
+        <v>12.32877730267639</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1729,7 +1729,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>180.4</v>
+        <v>180.1</v>
       </c>
       <c r="O14" t="n">
         <v>45.9</v>
@@ -1752,10 +1752,10 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>51.918</v>
+        <v>52.596</v>
       </c>
       <c r="V14" t="n">
-        <v>46.813</v>
+        <v>48.837</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1926,14 +1926,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -0.66% / +0.09% / -1.09% | ALTNY.IS: -0.13% / +0.38% / -1.73% | DOHOL.IS: -0.73% / +0.00% / -0.79%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K18" t="n">
-        <v>-25.81926606744547</v>
+        <v>-26.17768269500018</v>
       </c>
       <c r="L18" t="n">
         <v>14.20226218585835</v>
@@ -1942,7 +1942,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>118.2</v>
+        <v>117.9</v>
       </c>
       <c r="O18" t="n">
         <v>39.4</v>
@@ -1959,19 +1959,19 @@
         <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>28.595</v>
+        <v>28.94</v>
       </c>
       <c r="T18" t="n">
-        <v>28.595</v>
+        <v>28.94</v>
       </c>
       <c r="U18" t="n">
-        <v>78.48999999999999</v>
+        <v>81.00700000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>41.712</v>
+        <v>41.027</v>
       </c>
       <c r="W18" t="n">
-        <v>-71.48</v>
+        <v>-73.71899999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2015,14 +2015,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.65% / +4.70% / -3.86% | BRSAN.IS: +10.72% / +15.78% / -3.96%</t>
+          <t>ALARK.IS: +2.99% / +4.70% / -3.86% | BRSAN.IS: +11.11% / +15.78% / -3.96%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>9.516808420212275</v>
+        <v>9.386190102180404</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -2031,7 +2031,7 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>120.6</v>
+        <v>120.4</v>
       </c>
       <c r="O19" t="n">
         <v>43.5</v>
@@ -2054,10 +2054,10 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>95.041</v>
+        <v>92.824</v>
       </c>
       <c r="V19" t="n">
-        <v>57.526</v>
+        <v>57.339</v>
       </c>
       <c r="W19" t="n">
         <v>-22.599</v>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.53% / +1.46% / -0.73% | DOHOL.IS: +1.41% / +2.33% / -1.07%</t>
+          <t>ALARK.IS: -0.11% / +1.46% / -0.73% | DOHOL.IS: +0.70% / +2.33% / -1.07%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K20" t="n">
-        <v>-27.97033247114848</v>
+        <v>-28.45355490687034</v>
       </c>
       <c r="L20" t="n">
         <v>25.50508358988237</v>
@@ -2120,10 +2120,10 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>94.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="P20" t="n">
         <v>3.9</v>
@@ -2143,13 +2143,13 @@
         <v>35.7</v>
       </c>
       <c r="U20" t="n">
-        <v>18.526</v>
+        <v>19.096</v>
       </c>
       <c r="V20" t="n">
-        <v>13.39</v>
+        <v>12.629</v>
       </c>
       <c r="W20" t="n">
-        <v>-64.036</v>
+        <v>-65.583</v>
       </c>
     </row>
     <row r="21">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2193,14 +2193,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.77% / +2.39% / -1.30% | TAVHL.IS: -0.02% / +1.41% / -0.18%</t>
+          <t>BRSAN.IS: -0.43% / +2.39% / -1.30% | TAVHL.IS: -1.26% / +1.41% / -1.41%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1089969675226232</v>
+        <v>-0.557928743144176</v>
       </c>
       <c r="L21" t="n">
         <v>13.72502171397572</v>
@@ -2209,7 +2209,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N21" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="O21" t="n">
         <v>50</v>
@@ -2226,19 +2226,19 @@
         <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>30.055</v>
+        <v>30.369</v>
       </c>
       <c r="T21" t="n">
-        <v>30.055</v>
+        <v>30.369</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.78</v>
+        <v>-3.65</v>
       </c>
       <c r="V21" t="n">
-        <v>-7.156</v>
+        <v>-7.573</v>
       </c>
       <c r="W21" t="n">
-        <v>-42.205</v>
+        <v>-42.023</v>
       </c>
     </row>
     <row r="22">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2282,14 +2282,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.53% / +1.46% / -0.73% | DOHOL.IS: +1.41% / +2.33% / -1.07% | TAVHL.IS: -0.02% / +1.41% / -0.18%</t>
+          <t>ALARK.IS: -0.11% / +1.46% / -0.73% | DOHOL.IS: +0.70% / +2.33% / -1.07% | TAVHL.IS: -1.26% / +1.41% / -1.41%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1196539232451554</v>
+        <v>-0.9768485639447322</v>
       </c>
       <c r="L22" t="n">
         <v>10.56563994340933</v>
@@ -2298,13 +2298,13 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>73.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>38.9</v>
+        <v>38.3</v>
       </c>
       <c r="P22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>29.287</v>
       </c>
       <c r="U22" t="n">
-        <v>35.069</v>
+        <v>34.178</v>
       </c>
       <c r="V22" t="n">
-        <v>15.082</v>
+        <v>14.095</v>
       </c>
       <c r="W22" t="n">
-        <v>-46.88</v>
+        <v>-48.135</v>
       </c>
     </row>
     <row r="23">
@@ -2348,12 +2348,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2371,14 +2371,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.65% / +4.70% / -3.86% | ASTOR.IS: +20.61% / +23.58% / 0.00% | BIMAS.IS: +2.07% / +3.87% / -0.86% | BRSAN.IS: +39.28% / +45.64% / -0.48% | CANTE.IS: +7.42% / +9.92% / -0.83%</t>
+          <t>ALARK.IS: +2.99% / +4.70% / -3.86% | ASTOR.IS: +21.82% / +23.58% / 0.00% | BIMAS.IS: +2.19% / +3.87% / -0.86% | BRSAN.IS: +39.76% / +45.64% / -0.48% | CANTE.IS: +14.03% / +15.70% / -0.83%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K23" t="n">
-        <v>10.8016778336085</v>
+        <v>12.32877730267639</v>
       </c>
       <c r="L23" t="n">
         <v>23.4189376077676</v>
@@ -2387,7 +2387,7 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>180.4</v>
+        <v>180.1</v>
       </c>
       <c r="O23" t="n">
         <v>45.9</v>
@@ -2410,10 +2410,10 @@
         <v>22.513</v>
       </c>
       <c r="U23" t="n">
-        <v>51.918</v>
+        <v>52.596</v>
       </c>
       <c r="V23" t="n">
-        <v>46.813</v>
+        <v>48.837</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2460,14 +2460,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.65% / +4.70% / -3.86% | ASTOR.IS: +20.61% / +23.58% / 0.00% | BIMAS.IS: +2.07% / +3.87% / -0.86% | BRSAN.IS: +39.28% / +45.64% / -0.48% | CANTE.IS: +7.42% / +9.92% / -0.83%</t>
+          <t>ALARK.IS: +2.99% / +4.70% / -3.86% | ASTOR.IS: +21.82% / +23.58% / 0.00% | BIMAS.IS: +2.19% / +3.87% / -0.86% | BRSAN.IS: +39.76% / +45.64% / -0.48% | CANTE.IS: +14.03% / +15.70% / -0.83%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K24" t="n">
-        <v>10.8016778336085</v>
+        <v>12.32877730267639</v>
       </c>
       <c r="L24" t="n">
         <v>23.4189376077676</v>
@@ -2476,7 +2476,7 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>180.4</v>
+        <v>180.1</v>
       </c>
       <c r="O24" t="n">
         <v>45.9</v>
@@ -2499,10 +2499,10 @@
         <v>22.513</v>
       </c>
       <c r="U24" t="n">
-        <v>51.918</v>
+        <v>52.596</v>
       </c>
       <c r="V24" t="n">
-        <v>46.813</v>
+        <v>48.837</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2549,14 +2549,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.05% / +1.57% / -0.96% | BRSAN.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: +7.42% / +9.92% / -0.83%</t>
+          <t>AKBNK.IS: -0.16% / +1.57% / -0.96% | BRSAN.IS: +0.32% / +1.10% / 0.00% | CANTE.IS: +14.03% / +15.70% / -0.83%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K25" t="n">
-        <v>12.82494611781235</v>
+        <v>15.29583375526287</v>
       </c>
       <c r="L25" t="n">
         <v>7.902828022135555</v>
@@ -2565,7 +2565,7 @@
         <v>33.33333333333333</v>
       </c>
       <c r="N25" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="O25" t="n">
         <v>47.9</v>
@@ -2588,13 +2588,13 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>13.082</v>
+        <v>15.558</v>
       </c>
       <c r="V25" t="n">
-        <v>12.087</v>
+        <v>14.542</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.745</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2784,12 +2784,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2811,7 +2811,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>65.5</v>
+        <v>65.3</v>
       </c>
       <c r="O3" t="n">
         <v>45.9</v>
@@ -2834,13 +2834,13 @@
         <v>31.839</v>
       </c>
       <c r="U3" t="n">
-        <v>10.689</v>
+        <v>10.536</v>
       </c>
       <c r="V3" t="n">
         <v>27.773</v>
       </c>
       <c r="W3" t="n">
-        <v>-51.704</v>
+        <v>-51.632</v>
       </c>
     </row>
     <row r="4">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2886,7 +2886,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N4" t="n">
-        <v>59.1</v>
+        <v>58.9</v>
       </c>
       <c r="O4" t="n">
         <v>46.7</v>
@@ -2909,13 +2909,13 @@
         <v>30.704</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.756</v>
+        <v>-1.871</v>
       </c>
       <c r="V4" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>-43.531</v>
+        <v>-43.48</v>
       </c>
     </row>
     <row r="5">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -2961,7 +2961,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>59.1</v>
+        <v>58.9</v>
       </c>
       <c r="O5" t="n">
         <v>46.7</v>
@@ -2984,13 +2984,13 @@
         <v>30.704</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.756</v>
+        <v>-1.871</v>
       </c>
       <c r="V5" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-43.531</v>
+        <v>-43.48</v>
       </c>
     </row>
     <row r="6">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -3036,7 +3036,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>59.1</v>
+        <v>58.9</v>
       </c>
       <c r="O6" t="n">
         <v>46.7</v>
@@ -3059,13 +3059,13 @@
         <v>30.704</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.756</v>
+        <v>-1.871</v>
       </c>
       <c r="V6" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>-43.531</v>
+        <v>-43.48</v>
       </c>
     </row>
     <row r="7">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3111,7 +3111,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N7" t="n">
-        <v>59.1</v>
+        <v>58.9</v>
       </c>
       <c r="O7" t="n">
         <v>46.7</v>
@@ -3134,13 +3134,13 @@
         <v>30.704</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.756</v>
+        <v>-1.871</v>
       </c>
       <c r="V7" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>-43.531</v>
+        <v>-43.48</v>
       </c>
     </row>
     <row r="8">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3182,14 +3182,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +0.05% / +1.22% / -2.08% | BRSAN.IS: -0.77% / +2.39% / -1.30% | TRALT.IS: -0.66% / +2.76% / -1.66%</t>
+          <t>ASTOR.IS: +1.05% / +1.58% / -2.08% | BRSAN.IS: -0.43% / +2.39% / -1.30% | TRALT.IS: -2.51% / +2.76% / -3.68%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K8" t="n">
-        <v>-22.07151331458045</v>
+        <v>-22.20107975232143</v>
       </c>
       <c r="L8" t="n">
         <v>16.84258916554939</v>
@@ -3198,7 +3198,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>111.7</v>
+        <v>111.5</v>
       </c>
       <c r="O8" t="n">
         <v>38.3</v>
@@ -3215,19 +3215,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>29.23</v>
+        <v>29.348</v>
       </c>
       <c r="T8" t="n">
-        <v>29.23</v>
+        <v>29.348</v>
       </c>
       <c r="U8" t="n">
-        <v>43.686</v>
+        <v>44.264</v>
       </c>
       <c r="V8" t="n">
-        <v>13.807</v>
+        <v>13.618</v>
       </c>
       <c r="W8" t="n">
-        <v>-59.347</v>
+        <v>-59.925</v>
       </c>
     </row>
     <row r="9">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3273,7 +3273,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="N9" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="O9" t="n">
         <v>57.4</v>
@@ -3321,12 +3321,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3348,7 +3348,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>67.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="O10" t="n">
         <v>45.7</v>
@@ -3371,13 +3371,13 @@
         <v>13.513</v>
       </c>
       <c r="U10" t="n">
-        <v>12.064</v>
+        <v>11.847</v>
       </c>
       <c r="V10" t="n">
         <v>13.389</v>
       </c>
       <c r="W10" t="n">
-        <v>-16.799</v>
+        <v>-16.766</v>
       </c>
     </row>
     <row r="11">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3423,7 +3423,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>59.1</v>
+        <v>58.9</v>
       </c>
       <c r="O11" t="n">
         <v>44.2</v>
@@ -3446,13 +3446,13 @@
         <v>13.42</v>
       </c>
       <c r="U11" t="n">
-        <v>16.049</v>
+        <v>15.824</v>
       </c>
       <c r="V11" t="n">
         <v>12.908</v>
       </c>
       <c r="W11" t="n">
-        <v>-17.988</v>
+        <v>-17.953</v>
       </c>
     </row>
     <row r="12">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3494,14 +3494,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.51% / +3.81% / -0.90% | ASTOR.IS: +2.32% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +1.30% / +3.81% / -0.90% | ASTOR.IS: +3.35% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>23.26561805146417</v>
+        <v>23.75993956790246</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3510,7 +3510,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N12" t="n">
-        <v>81.7</v>
+        <v>81.5</v>
       </c>
       <c r="O12" t="n">
         <v>49.4</v>
@@ -3533,10 +3533,10 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>43.726</v>
+        <v>44.023</v>
       </c>
       <c r="V12" t="n">
-        <v>30.337</v>
+        <v>30.86</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3581,14 +3581,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.05% / +1.57% / -0.95% | ASTOR.IS: +2.32% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: -0.16% / +1.57% / -0.95% | ASTOR.IS: +3.35% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>22.51853375896779</v>
+        <v>23.01146849899773</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3597,10 +3597,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N13" t="n">
-        <v>128</v>
+        <v>127.7</v>
       </c>
       <c r="O13" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="P13" t="n">
         <v>3.9</v>
@@ -3620,10 +3620,10 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>56.651</v>
+        <v>59.017</v>
       </c>
       <c r="V13" t="n">
-        <v>43.059</v>
+        <v>43.635</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -3645,12 +3645,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3668,14 +3668,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +5.23% / +7.63% / -0.81% | BRSAN.IS: +9.33% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +5.02% / +7.63% / -0.81% | BRSAN.IS: +9.70% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>16.43107972063114</v>
+        <v>16.51819213583832</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3684,13 +3684,13 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N14" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="O14" t="n">
         <v>57.1</v>
       </c>
       <c r="P14" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3707,13 +3707,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>52.734</v>
+        <v>55.209</v>
       </c>
       <c r="V14" t="n">
-        <v>38.001</v>
+        <v>38.104</v>
       </c>
       <c r="W14" t="n">
-        <v>-11.655</v>
+        <v>-11.719</v>
       </c>
     </row>
     <row r="16">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -3885,7 +3885,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>65.5</v>
+        <v>65.3</v>
       </c>
       <c r="O18" t="n">
         <v>45.9</v>
@@ -3908,13 +3908,13 @@
         <v>31.839</v>
       </c>
       <c r="U18" t="n">
-        <v>10.689</v>
+        <v>10.536</v>
       </c>
       <c r="V18" t="n">
         <v>27.773</v>
       </c>
       <c r="W18" t="n">
-        <v>-51.704</v>
+        <v>-51.632</v>
       </c>
     </row>
     <row r="19">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -3962,7 +3962,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>59.1</v>
+        <v>58.9</v>
       </c>
       <c r="O19" t="n">
         <v>46.7</v>
@@ -3985,13 +3985,13 @@
         <v>30.704</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.756</v>
+        <v>-1.871</v>
       </c>
       <c r="V19" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>-43.531</v>
+        <v>-43.48</v>
       </c>
     </row>
     <row r="20">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -4039,7 +4039,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>59.1</v>
+        <v>58.9</v>
       </c>
       <c r="O20" t="n">
         <v>46.7</v>
@@ -4062,13 +4062,13 @@
         <v>30.704</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.756</v>
+        <v>-1.871</v>
       </c>
       <c r="V20" t="n">
         <v>8.694000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-43.531</v>
+        <v>-43.48</v>
       </c>
     </row>
     <row r="21">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4112,14 +4112,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +0.05% / +1.22% / -2.08% | BRSAN.IS: -0.77% / +2.39% / -1.30% | TRALT.IS: -0.66% / +2.76% / -1.66%</t>
+          <t>ASTOR.IS: +1.05% / +1.58% / -2.08% | BRSAN.IS: -0.43% / +2.39% / -1.30% | TRALT.IS: -2.51% / +2.76% / -3.68%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K21" t="n">
-        <v>-22.07151331458045</v>
+        <v>-22.20107975232143</v>
       </c>
       <c r="L21" t="n">
         <v>16.84258916554939</v>
@@ -4128,7 +4128,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>111.7</v>
+        <v>111.5</v>
       </c>
       <c r="O21" t="n">
         <v>38.3</v>
@@ -4145,19 +4145,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>29.23</v>
+        <v>29.348</v>
       </c>
       <c r="T21" t="n">
-        <v>29.23</v>
+        <v>29.348</v>
       </c>
       <c r="U21" t="n">
-        <v>43.686</v>
+        <v>44.264</v>
       </c>
       <c r="V21" t="n">
-        <v>13.807</v>
+        <v>13.618</v>
       </c>
       <c r="W21" t="n">
-        <v>-59.347</v>
+        <v>-59.925</v>
       </c>
     </row>
     <row r="22">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4205,7 +4205,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>59.1</v>
+        <v>58.9</v>
       </c>
       <c r="O22" t="n">
         <v>44.2</v>
@@ -4228,13 +4228,13 @@
         <v>13.42</v>
       </c>
       <c r="U22" t="n">
-        <v>16.049</v>
+        <v>15.824</v>
       </c>
       <c r="V22" t="n">
         <v>12.908</v>
       </c>
       <c r="W22" t="n">
-        <v>-17.988</v>
+        <v>-17.953</v>
       </c>
     </row>
     <row r="23">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -4282,7 +4282,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N23" t="n">
-        <v>67.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="O23" t="n">
         <v>45.7</v>
@@ -4305,13 +4305,13 @@
         <v>13.513</v>
       </c>
       <c r="U23" t="n">
-        <v>12.064</v>
+        <v>11.847</v>
       </c>
       <c r="V23" t="n">
         <v>13.389</v>
       </c>
       <c r="W23" t="n">
-        <v>-16.799</v>
+        <v>-16.766</v>
       </c>
     </row>
     <row r="24">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4359,7 +4359,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="N24" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="O24" t="n">
         <v>57.4</v>
@@ -4409,12 +4409,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4432,14 +4432,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +5.23% / +7.63% / -0.81% | BRSAN.IS: +9.33% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +5.02% / +7.63% / -0.81% | BRSAN.IS: +9.70% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>16.43107972063114</v>
+        <v>16.51819213583832</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4448,13 +4448,13 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N25" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="O25" t="n">
         <v>57.1</v>
       </c>
       <c r="P25" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4471,13 +4471,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>52.734</v>
+        <v>55.209</v>
       </c>
       <c r="V25" t="n">
-        <v>38.001</v>
+        <v>38.104</v>
       </c>
       <c r="W25" t="n">
-        <v>-11.655</v>
+        <v>-11.719</v>
       </c>
     </row>
     <row r="26">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.51% / +3.81% / -0.90% | ASTOR.IS: +2.32% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +1.30% / +3.81% / -0.90% | ASTOR.IS: +3.35% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>23.26561805146417</v>
+        <v>23.75993956790246</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4537,7 +4537,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N26" t="n">
-        <v>81.7</v>
+        <v>81.5</v>
       </c>
       <c r="O26" t="n">
         <v>49.4</v>
@@ -4560,10 +4560,10 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>43.726</v>
+        <v>44.023</v>
       </c>
       <c r="V26" t="n">
-        <v>30.337</v>
+        <v>30.86</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4610,14 +4610,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +0.05% / +1.57% / -0.95% | ASTOR.IS: +2.32% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: -0.16% / +1.57% / -0.95% | ASTOR.IS: +3.35% / +4.84% / -2.12%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>22.51853375896779</v>
+        <v>23.01146849899773</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4626,10 +4626,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N27" t="n">
-        <v>128</v>
+        <v>127.7</v>
       </c>
       <c r="O27" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="P27" t="n">
         <v>3.9</v>
@@ -4649,10 +4649,10 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>56.651</v>
+        <v>59.017</v>
       </c>
       <c r="V27" t="n">
-        <v>43.059</v>
+        <v>43.635</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.66% / +0.09% / -1.09% | ALTNY.IS: -0.13% / +0.38% / -1.73% | DOHOL.IS: -0.73% / +0.00% / -0.79%</t>
+          <t>ALARK.IS: -1.02% / +0.09% / -1.18% | ALTNY.IS: -2.99% / +0.38% / -3.25% | DOHOL.IS: -1.78% / +0.00% / -2.12%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K3" t="n">
-        <v>-26.17768269500018</v>
+        <v>-27.23827732471599</v>
       </c>
       <c r="L3" t="n">
         <v>14.20226218585835</v>
@@ -789,19 +789,19 @@
         <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>28.94</v>
+        <v>29.961</v>
       </c>
       <c r="T3" t="n">
-        <v>28.94</v>
+        <v>29.961</v>
       </c>
       <c r="U3" t="n">
-        <v>81.00700000000001</v>
+        <v>78.407</v>
       </c>
       <c r="V3" t="n">
-        <v>41.027</v>
+        <v>39.001</v>
       </c>
       <c r="W3" t="n">
-        <v>-73.71899999999999</v>
+        <v>-76.319</v>
       </c>
     </row>
     <row r="4">
@@ -830,12 +830,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ALARK.IS, BRSAN.IS</t>
+          <t>BRSAN.IS, DOHOL.IS, ECILC.IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-21 | BRSAN.IS: 2026-08-17</t>
+          <t>BRSAN.IS: 2026-08-17 | DOHOL.IS: 2026-08-31 | ECILC.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -843,14 +843,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.99% / +4.70% / -3.86% | BRSAN.IS: +11.11% / +15.78% / -3.96%</t>
+          <t>BRSAN.IS: +11.26% / +15.78% / -3.96% | DOHOL.IS: -0.02% / +0.00% / 0.00% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>9.386190102180404</v>
+        <v>9.256993294205484</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -859,13 +859,13 @@
         <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>120.4</v>
+        <v>121.4</v>
       </c>
       <c r="O4" t="n">
-        <v>43.5</v>
+        <v>43.1</v>
       </c>
       <c r="P4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
         <v>28.662</v>
@@ -882,13 +882,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>92.824</v>
+        <v>92.59699999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>57.339</v>
+        <v>57.153</v>
       </c>
       <c r="W4" t="n">
-        <v>-22.599</v>
+        <v>-22.827</v>
       </c>
     </row>
     <row r="5">
@@ -930,14 +930,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.11% / +1.46% / -0.73% | DOHOL.IS: +0.70% / +2.33% / -1.07%</t>
+          <t>ALARK.IS: -0.48% / +1.46% / -0.73% | DOHOL.IS: -0.38% / +2.33% / -1.07%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K5" t="n">
-        <v>-28.45355490687034</v>
+        <v>-28.96685039131007</v>
       </c>
       <c r="L5" t="n">
         <v>25.50508358988237</v>
@@ -949,7 +949,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="P5" t="n">
         <v>3.9</v>
@@ -963,19 +963,19 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>35.7</v>
+        <v>35.975</v>
       </c>
       <c r="T5" t="n">
-        <v>35.7</v>
+        <v>35.975</v>
       </c>
       <c r="U5" t="n">
-        <v>19.096</v>
+        <v>18.241</v>
       </c>
       <c r="V5" t="n">
-        <v>12.629</v>
+        <v>11.821</v>
       </c>
       <c r="W5" t="n">
-        <v>-65.583</v>
+        <v>-66.438</v>
       </c>
     </row>
     <row r="6">
@@ -1017,14 +1017,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.66% / +0.09% / -1.09% | ALTNY.IS: -0.13% / +0.38% / -1.73% | DOHOL.IS: -0.73% / +0.00% / -0.79%</t>
+          <t>ALARK.IS: -1.02% / +0.09% / -1.18% | ALTNY.IS: -2.99% / +0.38% / -3.25% | DOHOL.IS: -1.78% / +0.00% / -2.12%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K6" t="n">
-        <v>-26.17768269500018</v>
+        <v>-27.23827732471599</v>
       </c>
       <c r="L6" t="n">
         <v>14.20226218585835</v>
@@ -1050,19 +1050,19 @@
         <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>28.94</v>
+        <v>29.961</v>
       </c>
       <c r="T6" t="n">
-        <v>28.94</v>
+        <v>29.961</v>
       </c>
       <c r="U6" t="n">
-        <v>81.00700000000001</v>
+        <v>78.407</v>
       </c>
       <c r="V6" t="n">
-        <v>41.027</v>
+        <v>39.001</v>
       </c>
       <c r="W6" t="n">
-        <v>-73.71899999999999</v>
+        <v>-76.319</v>
       </c>
     </row>
     <row r="7">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ALARK.IS, BRSAN.IS</t>
+          <t>BRSAN.IS, DOHOL.IS, ECILC.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-21 | BRSAN.IS: 2026-08-17</t>
+          <t>BRSAN.IS: 2026-08-17 | DOHOL.IS: 2026-08-31 | ECILC.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1104,14 +1104,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.99% / +4.70% / -3.86% | BRSAN.IS: +11.11% / +15.78% / -3.96%</t>
+          <t>BRSAN.IS: +11.26% / +15.78% / -3.96% | DOHOL.IS: -0.02% / +0.00% / 0.00% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>9.386190102180404</v>
+        <v>9.256993294205484</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1120,13 +1120,13 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>120.4</v>
+        <v>121.4</v>
       </c>
       <c r="O7" t="n">
-        <v>43.5</v>
+        <v>43.1</v>
       </c>
       <c r="P7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
         <v>28.662</v>
@@ -1143,13 +1143,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>92.824</v>
+        <v>92.59699999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>57.339</v>
+        <v>57.153</v>
       </c>
       <c r="W7" t="n">
-        <v>-22.599</v>
+        <v>-22.827</v>
       </c>
     </row>
     <row r="8">
@@ -1191,14 +1191,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.43% / +2.39% / -1.30% | TAVHL.IS: -1.26% / +1.41% / -1.41%</t>
+          <t>BRSAN.IS: -0.29% / +2.39% / -1.71% | TAVHL.IS: -3.38% / +1.41% / -3.71%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.557928743144176</v>
+        <v>-1.552560900123012</v>
       </c>
       <c r="L8" t="n">
         <v>13.72502171397572</v>
@@ -1224,19 +1224,19 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>30.369</v>
+        <v>31.066</v>
       </c>
       <c r="T8" t="n">
-        <v>30.369</v>
+        <v>31.066</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.65</v>
+        <v>-4.614</v>
       </c>
       <c r="V8" t="n">
-        <v>-7.573</v>
+        <v>-8.497999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>-42.023</v>
+        <v>-42.987</v>
       </c>
     </row>
     <row r="9">
@@ -1278,14 +1278,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.66% / +0.09% / -1.09% | ALTNY.IS: -0.13% / +0.38% / -1.73% | DOHOL.IS: -0.73% / +0.00% / -0.79%</t>
+          <t>ALARK.IS: -1.02% / +0.09% / -1.18% | ALTNY.IS: -2.99% / +0.38% / -3.25% | DOHOL.IS: -1.78% / +0.00% / -2.12%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K9" t="n">
-        <v>-26.17768269500018</v>
+        <v>-27.23827732471599</v>
       </c>
       <c r="L9" t="n">
         <v>14.20226218585835</v>
@@ -1311,19 +1311,19 @@
         <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>28.94</v>
+        <v>29.961</v>
       </c>
       <c r="T9" t="n">
-        <v>28.94</v>
+        <v>29.961</v>
       </c>
       <c r="U9" t="n">
-        <v>81.00700000000001</v>
+        <v>78.407</v>
       </c>
       <c r="V9" t="n">
-        <v>41.027</v>
+        <v>39.001</v>
       </c>
       <c r="W9" t="n">
-        <v>-73.71899999999999</v>
+        <v>-76.319</v>
       </c>
     </row>
     <row r="10">
@@ -1365,14 +1365,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.43% / +2.39% / -1.30% | TAVHL.IS: -1.26% / +1.41% / -1.41%</t>
+          <t>BRSAN.IS: -0.29% / +2.39% / -1.71% | TAVHL.IS: -3.38% / +1.41% / -3.71%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.557928743144176</v>
+        <v>-1.552560900123012</v>
       </c>
       <c r="L10" t="n">
         <v>13.72502171397572</v>
@@ -1398,19 +1398,19 @@
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>30.369</v>
+        <v>31.066</v>
       </c>
       <c r="T10" t="n">
-        <v>30.369</v>
+        <v>31.066</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.65</v>
+        <v>-4.614</v>
       </c>
       <c r="V10" t="n">
-        <v>-7.573</v>
+        <v>-8.497999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>-42.023</v>
+        <v>-42.987</v>
       </c>
     </row>
     <row r="11">
@@ -1452,14 +1452,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.11% / +1.46% / -0.73% | DOHOL.IS: +0.70% / +2.33% / -1.07% | TAVHL.IS: -1.26% / +1.41% / -1.41%</t>
+          <t>ALARK.IS: -0.48% / +1.46% / -0.73% | DOHOL.IS: -0.38% / +2.33% / -1.07% | TAVHL.IS: -3.38% / +1.41% / -3.71%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9768485639447322</v>
+        <v>-2.154083288580599</v>
       </c>
       <c r="L11" t="n">
         <v>10.56563994340933</v>
@@ -1471,7 +1471,7 @@
         <v>72.90000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>38.3</v>
+        <v>37.6</v>
       </c>
       <c r="P11" t="n">
         <v>4.7</v>
@@ -1491,13 +1491,13 @@
         <v>29.287</v>
       </c>
       <c r="U11" t="n">
-        <v>34.178</v>
+        <v>32.583</v>
       </c>
       <c r="V11" t="n">
-        <v>14.095</v>
+        <v>12.738</v>
       </c>
       <c r="W11" t="n">
-        <v>-48.135</v>
+        <v>-49.73</v>
       </c>
     </row>
     <row r="12">
@@ -1539,14 +1539,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.16% / +1.57% / -0.96% | BRSAN.IS: +0.32% / +1.10% / 0.00% | CANTE.IS: +14.03% / +15.70% / -0.83%</t>
+          <t>AKBNK.IS: -0.09% / +1.57% / -0.96% | BRSAN.IS: +0.46% / +1.10% / -0.96% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K12" t="n">
-        <v>15.29583375526287</v>
+        <v>15.37184218883045</v>
       </c>
       <c r="L12" t="n">
         <v>7.902828022135555</v>
@@ -1578,10 +1578,10 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>15.558</v>
+        <v>15.634</v>
       </c>
       <c r="V12" t="n">
-        <v>14.542</v>
+        <v>14.617</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
+          <t>AKBNK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
+          <t>AKBNK.IS: 2026-08-31 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1626,14 +1626,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.99% / +4.70% / -3.86% | ASTOR.IS: +21.82% / +23.58% / 0.00% | BIMAS.IS: +2.19% / +3.87% / -0.86% | BRSAN.IS: +39.76% / +45.64% / -0.48% | CANTE.IS: +14.03% / +15.70% / -0.83%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +16.13% / +23.58% / 0.00% | BIMAS.IS: +0.72% / +3.87% / -0.86% | BRSAN.IS: +39.95% / +45.64% / -0.48% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K13" t="n">
-        <v>12.32877730267639</v>
+        <v>10.90577143667923</v>
       </c>
       <c r="L13" t="n">
         <v>23.4189376077676</v>
@@ -1642,10 +1642,10 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>180.1</v>
+        <v>180.6</v>
       </c>
       <c r="O13" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="P13" t="n">
         <v>5.6</v>
@@ -1665,10 +1665,10 @@
         <v>22.513</v>
       </c>
       <c r="U13" t="n">
-        <v>52.596</v>
+        <v>50.663</v>
       </c>
       <c r="V13" t="n">
-        <v>48.837</v>
+        <v>46.951</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
+          <t>AKBNK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
+          <t>AKBNK.IS: 2026-08-31 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1713,14 +1713,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.99% / +4.70% / -3.86% | ASTOR.IS: +21.82% / +23.58% / 0.00% | BIMAS.IS: +2.19% / +3.87% / -0.86% | BRSAN.IS: +39.76% / +45.64% / -0.48% | CANTE.IS: +14.03% / +15.70% / -0.83%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +16.13% / +23.58% / 0.00% | BIMAS.IS: +0.72% / +3.87% / -0.86% | BRSAN.IS: +39.95% / +45.64% / -0.48% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>12.32877730267639</v>
+        <v>10.90577143667923</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1729,10 +1729,10 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>180.1</v>
+        <v>180.6</v>
       </c>
       <c r="O14" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="P14" t="n">
         <v>5.6</v>
@@ -1752,10 +1752,10 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>52.596</v>
+        <v>50.663</v>
       </c>
       <c r="V14" t="n">
-        <v>48.837</v>
+        <v>46.951</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -1926,14 +1926,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.66% / +0.09% / -1.09% | ALTNY.IS: -0.13% / +0.38% / -1.73% | DOHOL.IS: -0.73% / +0.00% / -0.79%</t>
+          <t>ALARK.IS: -1.02% / +0.09% / -1.18% | ALTNY.IS: -2.99% / +0.38% / -3.25% | DOHOL.IS: -1.78% / +0.00% / -2.12%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K18" t="n">
-        <v>-26.17768269500018</v>
+        <v>-27.23827732471599</v>
       </c>
       <c r="L18" t="n">
         <v>14.20226218585835</v>
@@ -1959,19 +1959,19 @@
         <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>28.94</v>
+        <v>29.961</v>
       </c>
       <c r="T18" t="n">
-        <v>28.94</v>
+        <v>29.961</v>
       </c>
       <c r="U18" t="n">
-        <v>81.00700000000001</v>
+        <v>78.407</v>
       </c>
       <c r="V18" t="n">
-        <v>41.027</v>
+        <v>39.001</v>
       </c>
       <c r="W18" t="n">
-        <v>-73.71899999999999</v>
+        <v>-76.319</v>
       </c>
     </row>
     <row r="19">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ALARK.IS, BRSAN.IS</t>
+          <t>BRSAN.IS, DOHOL.IS, ECILC.IS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-21 | BRSAN.IS: 2026-08-17</t>
+          <t>BRSAN.IS: 2026-08-17 | DOHOL.IS: 2026-08-31 | ECILC.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2015,14 +2015,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.99% / +4.70% / -3.86% | BRSAN.IS: +11.11% / +15.78% / -3.96%</t>
+          <t>BRSAN.IS: +11.26% / +15.78% / -3.96% | DOHOL.IS: -0.02% / +0.00% / 0.00% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>9.386190102180404</v>
+        <v>9.256993294205484</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -2031,13 +2031,13 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>120.4</v>
+        <v>121.4</v>
       </c>
       <c r="O19" t="n">
-        <v>43.5</v>
+        <v>43.1</v>
       </c>
       <c r="P19" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S19" t="n">
         <v>28.662</v>
@@ -2054,13 +2054,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>92.824</v>
+        <v>92.59699999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>57.339</v>
+        <v>57.153</v>
       </c>
       <c r="W19" t="n">
-        <v>-22.599</v>
+        <v>-22.827</v>
       </c>
     </row>
     <row r="20">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.11% / +1.46% / -0.73% | DOHOL.IS: +0.70% / +2.33% / -1.07%</t>
+          <t>ALARK.IS: -0.48% / +1.46% / -0.73% | DOHOL.IS: -0.38% / +2.33% / -1.07%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K20" t="n">
-        <v>-28.45355490687034</v>
+        <v>-28.96685039131007</v>
       </c>
       <c r="L20" t="n">
         <v>25.50508358988237</v>
@@ -2123,7 +2123,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="P20" t="n">
         <v>3.9</v>
@@ -2137,19 +2137,19 @@
         <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>35.7</v>
+        <v>35.975</v>
       </c>
       <c r="T20" t="n">
-        <v>35.7</v>
+        <v>35.975</v>
       </c>
       <c r="U20" t="n">
-        <v>19.096</v>
+        <v>18.241</v>
       </c>
       <c r="V20" t="n">
-        <v>12.629</v>
+        <v>11.821</v>
       </c>
       <c r="W20" t="n">
-        <v>-65.583</v>
+        <v>-66.438</v>
       </c>
     </row>
     <row r="21">
@@ -2193,14 +2193,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.43% / +2.39% / -1.30% | TAVHL.IS: -1.26% / +1.41% / -1.41%</t>
+          <t>BRSAN.IS: -0.29% / +2.39% / -1.71% | TAVHL.IS: -3.38% / +1.41% / -3.71%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.557928743144176</v>
+        <v>-1.552560900123012</v>
       </c>
       <c r="L21" t="n">
         <v>13.72502171397572</v>
@@ -2226,19 +2226,19 @@
         <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>30.369</v>
+        <v>31.066</v>
       </c>
       <c r="T21" t="n">
-        <v>30.369</v>
+        <v>31.066</v>
       </c>
       <c r="U21" t="n">
-        <v>-3.65</v>
+        <v>-4.614</v>
       </c>
       <c r="V21" t="n">
-        <v>-7.573</v>
+        <v>-8.497999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>-42.023</v>
+        <v>-42.987</v>
       </c>
     </row>
     <row r="22">
@@ -2282,14 +2282,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.11% / +1.46% / -0.73% | DOHOL.IS: +0.70% / +2.33% / -1.07% | TAVHL.IS: -1.26% / +1.41% / -1.41%</t>
+          <t>ALARK.IS: -0.48% / +1.46% / -0.73% | DOHOL.IS: -0.38% / +2.33% / -1.07% | TAVHL.IS: -3.38% / +1.41% / -3.71%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9768485639447322</v>
+        <v>-2.154083288580599</v>
       </c>
       <c r="L22" t="n">
         <v>10.56563994340933</v>
@@ -2301,7 +2301,7 @@
         <v>72.90000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>38.3</v>
+        <v>37.6</v>
       </c>
       <c r="P22" t="n">
         <v>4.7</v>
@@ -2321,13 +2321,13 @@
         <v>29.287</v>
       </c>
       <c r="U22" t="n">
-        <v>34.178</v>
+        <v>32.583</v>
       </c>
       <c r="V22" t="n">
-        <v>14.095</v>
+        <v>12.738</v>
       </c>
       <c r="W22" t="n">
-        <v>-48.135</v>
+        <v>-49.73</v>
       </c>
     </row>
     <row r="23">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
+          <t>AKBNK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
+          <t>AKBNK.IS: 2026-08-31 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2371,14 +2371,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.99% / +4.70% / -3.86% | ASTOR.IS: +21.82% / +23.58% / 0.00% | BIMAS.IS: +2.19% / +3.87% / -0.86% | BRSAN.IS: +39.76% / +45.64% / -0.48% | CANTE.IS: +14.03% / +15.70% / -0.83%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +16.13% / +23.58% / 0.00% | BIMAS.IS: +0.72% / +3.87% / -0.86% | BRSAN.IS: +39.95% / +45.64% / -0.48% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K23" t="n">
-        <v>12.32877730267639</v>
+        <v>10.90577143667923</v>
       </c>
       <c r="L23" t="n">
         <v>23.4189376077676</v>
@@ -2387,10 +2387,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>180.1</v>
+        <v>180.6</v>
       </c>
       <c r="O23" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="P23" t="n">
         <v>5.6</v>
@@ -2410,10 +2410,10 @@
         <v>22.513</v>
       </c>
       <c r="U23" t="n">
-        <v>52.596</v>
+        <v>50.663</v>
       </c>
       <c r="V23" t="n">
-        <v>48.837</v>
+        <v>46.951</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ALARK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
+          <t>AKBNK.IS, ASTOR.IS, BIMAS.IS, BRSAN.IS, CANTE.IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-21 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
+          <t>AKBNK.IS: 2026-08-31 | ASTOR.IS: 2026-08-03 | BIMAS.IS: 2026-08-19 | BRSAN.IS: 2026-07-31 | CANTE.IS: 2026-08-18</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2460,14 +2460,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.99% / +4.70% / -3.86% | ASTOR.IS: +21.82% / +23.58% / 0.00% | BIMAS.IS: +2.19% / +3.87% / -0.86% | BRSAN.IS: +39.76% / +45.64% / -0.48% | CANTE.IS: +14.03% / +15.70% / -0.83%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +16.13% / +23.58% / 0.00% | BIMAS.IS: +0.72% / +3.87% / -0.86% | BRSAN.IS: +39.95% / +45.64% / -0.48% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K24" t="n">
-        <v>12.32877730267639</v>
+        <v>10.90577143667923</v>
       </c>
       <c r="L24" t="n">
         <v>23.4189376077676</v>
@@ -2476,10 +2476,10 @@
         <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>180.1</v>
+        <v>180.6</v>
       </c>
       <c r="O24" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="P24" t="n">
         <v>5.6</v>
@@ -2499,10 +2499,10 @@
         <v>22.513</v>
       </c>
       <c r="U24" t="n">
-        <v>52.596</v>
+        <v>50.663</v>
       </c>
       <c r="V24" t="n">
-        <v>48.837</v>
+        <v>46.951</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -2549,14 +2549,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.16% / +1.57% / -0.96% | BRSAN.IS: +0.32% / +1.10% / 0.00% | CANTE.IS: +14.03% / +15.70% / -0.83%</t>
+          <t>AKBNK.IS: -0.09% / +1.57% / -0.96% | BRSAN.IS: +0.46% / +1.10% / -0.96% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K25" t="n">
-        <v>15.29583375526287</v>
+        <v>15.37184218883045</v>
       </c>
       <c r="L25" t="n">
         <v>7.902828022135555</v>
@@ -2588,10 +2588,10 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>15.558</v>
+        <v>15.634</v>
       </c>
       <c r="V25" t="n">
-        <v>14.542</v>
+        <v>14.617</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASTOR.IS, BRSAN.IS, TRALT.IS</t>
+          <t>ALARK.IS, BRSAN.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-08-27 | BRSAN.IS: 2026-08-27 | TRALT.IS: 2026-08-27</t>
+          <t>ALARK.IS: 2026-08-31 | BRSAN.IS: 2026-08-27 | TRALT.IS: 2026-08-27</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -3182,14 +3182,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +1.05% / +1.58% / -2.08% | BRSAN.IS: -0.43% / +2.39% / -1.30% | TRALT.IS: -2.51% / +2.76% / -3.68%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.29% / +2.39% / -1.71% | TRALT.IS: -2.69% / +2.76% / -3.68%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K8" t="n">
-        <v>-22.20107975232143</v>
+        <v>-23.54775897667501</v>
       </c>
       <c r="L8" t="n">
         <v>16.84258916554939</v>
@@ -3198,10 +3198,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>111.5</v>
+        <v>112</v>
       </c>
       <c r="O8" t="n">
-        <v>38.3</v>
+        <v>37.7</v>
       </c>
       <c r="P8" t="n">
         <v>4.9</v>
@@ -3215,19 +3215,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>29.348</v>
+        <v>30.571</v>
       </c>
       <c r="T8" t="n">
-        <v>29.348</v>
+        <v>30.571</v>
       </c>
       <c r="U8" t="n">
-        <v>44.264</v>
+        <v>41.767</v>
       </c>
       <c r="V8" t="n">
-        <v>13.618</v>
+        <v>11.651</v>
       </c>
       <c r="W8" t="n">
-        <v>-59.925</v>
+        <v>-62.422</v>
       </c>
     </row>
     <row r="9">
@@ -3494,14 +3494,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.30% / +3.81% / -0.90% | ASTOR.IS: +3.35% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +1.37% / +3.81% / -0.90% | ASTOR.IS: -1.48% / +4.84% / -2.42%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K12" t="n">
-        <v>23.75993956790246</v>
+        <v>20.87839939106448</v>
       </c>
       <c r="L12" t="n">
         <v>28.49280591027672</v>
@@ -3513,7 +3513,7 @@
         <v>81.5</v>
       </c>
       <c r="O12" t="n">
-        <v>49.4</v>
+        <v>48.8</v>
       </c>
       <c r="P12" t="n">
         <v>3.6</v>
@@ -3533,13 +3533,13 @@
         <v>13.617</v>
       </c>
       <c r="U12" t="n">
-        <v>44.023</v>
+        <v>40.67</v>
       </c>
       <c r="V12" t="n">
-        <v>30.86</v>
+        <v>27.813</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-2.807</v>
       </c>
     </row>
     <row r="13">
@@ -3581,14 +3581,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.16% / +1.57% / -0.95% | ASTOR.IS: +3.35% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: -0.09% / +1.57% / -0.95% | ASTOR.IS: -1.48% / +4.84% / -2.42%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K13" t="n">
-        <v>23.01146849899773</v>
+        <v>20.14577142282576</v>
       </c>
       <c r="L13" t="n">
         <v>28.84422545304696</v>
@@ -3600,7 +3600,7 @@
         <v>127.7</v>
       </c>
       <c r="O13" t="n">
-        <v>50</v>
+        <v>49.6</v>
       </c>
       <c r="P13" t="n">
         <v>3.9</v>
@@ -3620,13 +3620,13 @@
         <v>10.914</v>
       </c>
       <c r="U13" t="n">
-        <v>59.017</v>
+        <v>55.312</v>
       </c>
       <c r="V13" t="n">
-        <v>43.635</v>
+        <v>40.289</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-3.099</v>
       </c>
     </row>
     <row r="14">
@@ -3668,14 +3668,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +5.02% / +7.63% / -0.81% | BRSAN.IS: +9.70% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +5.09% / +7.63% / -0.81% | BRSAN.IS: +9.85% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>16.51819213583832</v>
+        <v>16.63886199984612</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3707,13 +3707,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>55.209</v>
+        <v>55.37</v>
       </c>
       <c r="V14" t="n">
-        <v>38.104</v>
+        <v>38.247</v>
       </c>
       <c r="W14" t="n">
-        <v>-11.719</v>
+        <v>-11.558</v>
       </c>
     </row>
     <row r="16">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ASTOR.IS, BRSAN.IS, TRALT.IS</t>
+          <t>ALARK.IS, BRSAN.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-08-27 | BRSAN.IS: 2026-08-27 | TRALT.IS: 2026-08-27</t>
+          <t>ALARK.IS: 2026-08-31 | BRSAN.IS: 2026-08-27 | TRALT.IS: 2026-08-27</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -4112,14 +4112,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +1.05% / +1.58% / -2.08% | BRSAN.IS: -0.43% / +2.39% / -1.30% | TRALT.IS: -2.51% / +2.76% / -3.68%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.29% / +2.39% / -1.71% | TRALT.IS: -2.69% / +2.76% / -3.68%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K21" t="n">
-        <v>-22.20107975232143</v>
+        <v>-23.54775897667501</v>
       </c>
       <c r="L21" t="n">
         <v>16.84258916554939</v>
@@ -4128,10 +4128,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>111.5</v>
+        <v>112</v>
       </c>
       <c r="O21" t="n">
-        <v>38.3</v>
+        <v>37.7</v>
       </c>
       <c r="P21" t="n">
         <v>4.9</v>
@@ -4145,19 +4145,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>29.348</v>
+        <v>30.571</v>
       </c>
       <c r="T21" t="n">
-        <v>29.348</v>
+        <v>30.571</v>
       </c>
       <c r="U21" t="n">
-        <v>44.264</v>
+        <v>41.767</v>
       </c>
       <c r="V21" t="n">
-        <v>13.618</v>
+        <v>11.651</v>
       </c>
       <c r="W21" t="n">
-        <v>-59.925</v>
+        <v>-62.422</v>
       </c>
     </row>
     <row r="22">
@@ -4432,14 +4432,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +5.02% / +7.63% / -0.81% | BRSAN.IS: +9.70% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +5.09% / +7.63% / -0.81% | BRSAN.IS: +9.85% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>16.51819213583832</v>
+        <v>16.63886199984612</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4471,13 +4471,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>55.209</v>
+        <v>55.37</v>
       </c>
       <c r="V25" t="n">
-        <v>38.104</v>
+        <v>38.247</v>
       </c>
       <c r="W25" t="n">
-        <v>-11.719</v>
+        <v>-11.558</v>
       </c>
     </row>
     <row r="26">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.30% / +3.81% / -0.90% | ASTOR.IS: +3.35% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: +1.37% / +3.81% / -0.90% | ASTOR.IS: -1.48% / +4.84% / -2.42%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>23.75993956790246</v>
+        <v>20.87839939106448</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4540,7 +4540,7 @@
         <v>81.5</v>
       </c>
       <c r="O26" t="n">
-        <v>49.4</v>
+        <v>48.8</v>
       </c>
       <c r="P26" t="n">
         <v>3.6</v>
@@ -4560,13 +4560,13 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>44.023</v>
+        <v>40.67</v>
       </c>
       <c r="V26" t="n">
-        <v>30.86</v>
+        <v>27.813</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>-2.807</v>
       </c>
     </row>
     <row r="27">
@@ -4610,14 +4610,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.16% / +1.57% / -0.95% | ASTOR.IS: +3.35% / +4.84% / -2.12%</t>
+          <t>AKBNK.IS: -0.09% / +1.57% / -0.95% | ASTOR.IS: -1.48% / +4.84% / -2.42%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-1.715971707851549</v>
       </c>
       <c r="K27" t="n">
-        <v>23.01146849899773</v>
+        <v>20.14577142282576</v>
       </c>
       <c r="L27" t="n">
         <v>28.84422545304696</v>
@@ -4629,7 +4629,7 @@
         <v>127.7</v>
       </c>
       <c r="O27" t="n">
-        <v>50</v>
+        <v>49.6</v>
       </c>
       <c r="P27" t="n">
         <v>3.9</v>
@@ -4649,13 +4649,13 @@
         <v>10.914</v>
       </c>
       <c r="U27" t="n">
-        <v>59.017</v>
+        <v>55.312</v>
       </c>
       <c r="V27" t="n">
-        <v>43.635</v>
+        <v>40.289</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>-3.099</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -743,12 +743,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, DOHOL.IS</t>
+          <t>ALARK.IS, DOHOL.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-28 | ALTNY.IS: 2026-08-28 | DOHOL.IS: 2026-08-28</t>
+          <t>ALARK.IS: 2026-08-28 | DOHOL.IS: 2026-08-28 | VAKBN.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.02% / +0.09% / -1.18% | ALTNY.IS: -2.99% / +0.38% / -3.25% | DOHOL.IS: -1.78% / +0.00% / -2.12%</t>
+          <t>ALARK.IS: -2.47% / +0.09% / -3.54% | DOHOL.IS: -3.11% / +0.00% / -3.53% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K3" t="n">
-        <v>-27.23827732471599</v>
+        <v>-28.1877488155844</v>
       </c>
       <c r="L3" t="n">
         <v>14.20226218585835</v>
@@ -772,10 +772,10 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>117.9</v>
+        <v>118.4</v>
       </c>
       <c r="O3" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
@@ -789,19 +789,19 @@
         <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>29.961</v>
+        <v>30.875</v>
       </c>
       <c r="T3" t="n">
-        <v>29.961</v>
+        <v>30.875</v>
       </c>
       <c r="U3" t="n">
-        <v>78.407</v>
+        <v>76.07899999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>39.001</v>
+        <v>37.187</v>
       </c>
       <c r="W3" t="n">
-        <v>-76.319</v>
+        <v>-78.64700000000001</v>
       </c>
     </row>
     <row r="4">
@@ -843,14 +843,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.26% / +15.78% / -3.96% | DOHOL.IS: -0.02% / +0.00% / 0.00% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +9.96% / +15.78% / -3.96% | DOHOL.IS: -0.02% / +0.00% / 0.00% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>9.256993294205484</v>
+        <v>7.829742331378675</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -882,13 +882,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>92.59699999999999</v>
+        <v>90.081</v>
       </c>
       <c r="V4" t="n">
-        <v>57.153</v>
+        <v>55.1</v>
       </c>
       <c r="W4" t="n">
-        <v>-22.827</v>
+        <v>-25.343</v>
       </c>
     </row>
     <row r="5">
@@ -930,14 +930,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.48% / +1.46% / -0.73% | DOHOL.IS: -0.38% / +2.33% / -1.07%</t>
+          <t>ALARK.IS: -1.94% / +1.46% / -3.01% | DOHOL.IS: -1.72% / +2.33% / -2.15%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K5" t="n">
-        <v>-28.96685039131007</v>
+        <v>-29.96646194093252</v>
       </c>
       <c r="L5" t="n">
         <v>25.50508358988237</v>
@@ -963,19 +963,19 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>35.975</v>
+        <v>36.876</v>
       </c>
       <c r="T5" t="n">
-        <v>35.975</v>
+        <v>36.876</v>
       </c>
       <c r="U5" t="n">
-        <v>18.241</v>
+        <v>16.577</v>
       </c>
       <c r="V5" t="n">
-        <v>11.821</v>
+        <v>10.247</v>
       </c>
       <c r="W5" t="n">
-        <v>-66.438</v>
+        <v>-68.102</v>
       </c>
     </row>
     <row r="6">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, DOHOL.IS</t>
+          <t>ALARK.IS, DOHOL.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-28 | ALTNY.IS: 2026-08-28 | DOHOL.IS: 2026-08-28</t>
+          <t>ALARK.IS: 2026-08-28 | DOHOL.IS: 2026-08-28 | VAKBN.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1017,14 +1017,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.02% / +0.09% / -1.18% | ALTNY.IS: -2.99% / +0.38% / -3.25% | DOHOL.IS: -1.78% / +0.00% / -2.12%</t>
+          <t>ALARK.IS: -2.47% / +0.09% / -3.54% | DOHOL.IS: -3.11% / +0.00% / -3.53% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K6" t="n">
-        <v>-27.23827732471599</v>
+        <v>-28.1877488155844</v>
       </c>
       <c r="L6" t="n">
         <v>14.20226218585835</v>
@@ -1033,10 +1033,10 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>117.9</v>
+        <v>118.4</v>
       </c>
       <c r="O6" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="P6" t="n">
         <v>5</v>
@@ -1050,19 +1050,19 @@
         <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>29.961</v>
+        <v>30.875</v>
       </c>
       <c r="T6" t="n">
-        <v>29.961</v>
+        <v>30.875</v>
       </c>
       <c r="U6" t="n">
-        <v>78.407</v>
+        <v>76.07899999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>39.001</v>
+        <v>37.187</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.319</v>
+        <v>-78.64700000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1104,14 +1104,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.26% / +15.78% / -3.96% | DOHOL.IS: -0.02% / +0.00% / 0.00% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +9.96% / +15.78% / -3.96% | DOHOL.IS: -0.02% / +0.00% / 0.00% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>9.256993294205484</v>
+        <v>7.829742331378675</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1143,13 +1143,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>92.59699999999999</v>
+        <v>90.081</v>
       </c>
       <c r="V7" t="n">
-        <v>57.153</v>
+        <v>55.1</v>
       </c>
       <c r="W7" t="n">
-        <v>-22.827</v>
+        <v>-25.343</v>
       </c>
     </row>
     <row r="8">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TAVHL.IS</t>
+          <t>BRSAN.IS, ECILC.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
+          <t>BRSAN.IS: 2026-08-27 | ECILC.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1191,14 +1191,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.29% / +2.39% / -1.71% | TAVHL.IS: -3.38% / +1.41% / -3.71%</t>
+          <t>BRSAN.IS: -1.45% / +2.39% / -1.98% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.552560900123012</v>
+        <v>-2.476447492659206</v>
       </c>
       <c r="L8" t="n">
         <v>13.72502171397572</v>
@@ -1207,13 +1207,13 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N8" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="O8" t="n">
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="P8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1224,19 +1224,19 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>31.066</v>
+        <v>31.713</v>
       </c>
       <c r="T8" t="n">
-        <v>31.066</v>
+        <v>31.713</v>
       </c>
       <c r="U8" t="n">
-        <v>-4.614</v>
+        <v>-5.509</v>
       </c>
       <c r="V8" t="n">
-        <v>-8.497999999999999</v>
+        <v>-9.356999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>-42.987</v>
+        <v>-43.882</v>
       </c>
     </row>
     <row r="9">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, DOHOL.IS</t>
+          <t>ALARK.IS, DOHOL.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-28 | ALTNY.IS: 2026-08-28 | DOHOL.IS: 2026-08-28</t>
+          <t>ALARK.IS: 2026-08-28 | DOHOL.IS: 2026-08-28 | VAKBN.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1278,14 +1278,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.02% / +0.09% / -1.18% | ALTNY.IS: -2.99% / +0.38% / -3.25% | DOHOL.IS: -1.78% / +0.00% / -2.12%</t>
+          <t>ALARK.IS: -2.47% / +0.09% / -3.54% | DOHOL.IS: -3.11% / +0.00% / -3.53% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K9" t="n">
-        <v>-27.23827732471599</v>
+        <v>-28.1877488155844</v>
       </c>
       <c r="L9" t="n">
         <v>14.20226218585835</v>
@@ -1294,10 +1294,10 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>117.9</v>
+        <v>118.4</v>
       </c>
       <c r="O9" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="P9" t="n">
         <v>5</v>
@@ -1311,19 +1311,19 @@
         <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>29.961</v>
+        <v>30.875</v>
       </c>
       <c r="T9" t="n">
-        <v>29.961</v>
+        <v>30.875</v>
       </c>
       <c r="U9" t="n">
-        <v>78.407</v>
+        <v>76.07899999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>39.001</v>
+        <v>37.187</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.319</v>
+        <v>-78.64700000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TAVHL.IS</t>
+          <t>BRSAN.IS, ECILC.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
+          <t>BRSAN.IS: 2026-08-27 | ECILC.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1365,14 +1365,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.29% / +2.39% / -1.71% | TAVHL.IS: -3.38% / +1.41% / -3.71%</t>
+          <t>BRSAN.IS: -1.45% / +2.39% / -1.98% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.552560900123012</v>
+        <v>-2.476447492659206</v>
       </c>
       <c r="L10" t="n">
         <v>13.72502171397572</v>
@@ -1381,13 +1381,13 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="O10" t="n">
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="P10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1398,19 +1398,19 @@
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>31.066</v>
+        <v>31.713</v>
       </c>
       <c r="T10" t="n">
-        <v>31.066</v>
+        <v>31.713</v>
       </c>
       <c r="U10" t="n">
-        <v>-4.614</v>
+        <v>-5.509</v>
       </c>
       <c r="V10" t="n">
-        <v>-8.497999999999999</v>
+        <v>-9.356999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>-42.987</v>
+        <v>-43.882</v>
       </c>
     </row>
     <row r="11">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ALARK.IS, DOHOL.IS, TAVHL.IS</t>
+          <t>ALARK.IS, DOHOL.IS, ECILC.IS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
+          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27 | ECILC.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1452,14 +1452,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.48% / +1.46% / -0.73% | DOHOL.IS: -0.38% / +2.33% / -1.07% | TAVHL.IS: -3.38% / +1.41% / -3.71%</t>
+          <t>ALARK.IS: -1.94% / +1.46% / -3.01% | DOHOL.IS: -1.72% / +2.33% / -2.15% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.154083288580599</v>
+        <v>-3.306641054060266</v>
       </c>
       <c r="L11" t="n">
         <v>10.56563994340933</v>
@@ -1468,13 +1468,13 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N11" t="n">
-        <v>72.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="P11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1491,13 +1491,13 @@
         <v>29.287</v>
       </c>
       <c r="U11" t="n">
-        <v>32.583</v>
+        <v>31.021</v>
       </c>
       <c r="V11" t="n">
-        <v>12.738</v>
+        <v>11.41</v>
       </c>
       <c r="W11" t="n">
-        <v>-49.73</v>
+        <v>-51.292</v>
       </c>
     </row>
     <row r="12">
@@ -1539,14 +1539,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.09% / +1.57% / -0.96% | BRSAN.IS: +0.46% / +1.10% / -0.96% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
+          <t>AKBNK.IS: -2.14% / +1.57% / -2.19% | BRSAN.IS: -0.71% / +1.10% / -1.24% | CANTE.IS: +15.68% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K12" t="n">
-        <v>15.37184218883045</v>
+        <v>14.79588649506534</v>
       </c>
       <c r="L12" t="n">
         <v>7.902828022135555</v>
@@ -1558,7 +1558,7 @@
         <v>34.7</v>
       </c>
       <c r="O12" t="n">
-        <v>47.9</v>
+        <v>46.5</v>
       </c>
       <c r="P12" t="n">
         <v>4.4</v>
@@ -1578,10 +1578,10 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>15.634</v>
+        <v>15.057</v>
       </c>
       <c r="V12" t="n">
-        <v>14.617</v>
+        <v>14.045</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1626,14 +1626,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +16.13% / +23.58% / 0.00% | BIMAS.IS: +0.72% / +3.87% / -0.86% | BRSAN.IS: +39.95% / +45.64% / -0.48% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +11.64% / +23.58% / 0.00% | BIMAS.IS: -0.94% / +3.87% / -1.04% | BRSAN.IS: +38.32% / +45.64% / -0.48% | CANTE.IS: +15.68% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K13" t="n">
-        <v>10.90577143667923</v>
+        <v>9.442025796428899</v>
       </c>
       <c r="L13" t="n">
         <v>23.4189376077676</v>
@@ -1645,7 +1645,7 @@
         <v>180.6</v>
       </c>
       <c r="O13" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="P13" t="n">
         <v>5.6</v>
@@ -1665,13 +1665,13 @@
         <v>22.513</v>
       </c>
       <c r="U13" t="n">
-        <v>50.663</v>
+        <v>48.674</v>
       </c>
       <c r="V13" t="n">
-        <v>46.951</v>
+        <v>45.012</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-1.877</v>
       </c>
     </row>
     <row r="14">
@@ -1713,14 +1713,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +16.13% / +23.58% / 0.00% | BIMAS.IS: +0.72% / +3.87% / -0.86% | BRSAN.IS: +39.95% / +45.64% / -0.48% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +11.64% / +23.58% / 0.00% | BIMAS.IS: -0.94% / +3.87% / -1.04% | BRSAN.IS: +38.32% / +45.64% / -0.48% | CANTE.IS: +15.68% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>10.90577143667923</v>
+        <v>9.442025796428899</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1732,7 +1732,7 @@
         <v>180.6</v>
       </c>
       <c r="O14" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="P14" t="n">
         <v>5.6</v>
@@ -1752,13 +1752,13 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>50.663</v>
+        <v>48.674</v>
       </c>
       <c r="V14" t="n">
-        <v>46.951</v>
+        <v>45.012</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-1.877</v>
       </c>
     </row>
     <row r="16">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, DOHOL.IS</t>
+          <t>ALARK.IS, DOHOL.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-28 | ALTNY.IS: 2026-08-28 | DOHOL.IS: 2026-08-28</t>
+          <t>ALARK.IS: 2026-08-28 | DOHOL.IS: 2026-08-28 | VAKBN.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1926,14 +1926,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.02% / +0.09% / -1.18% | ALTNY.IS: -2.99% / +0.38% / -3.25% | DOHOL.IS: -1.78% / +0.00% / -2.12%</t>
+          <t>ALARK.IS: -2.47% / +0.09% / -3.54% | DOHOL.IS: -3.11% / +0.00% / -3.53% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K18" t="n">
-        <v>-27.23827732471599</v>
+        <v>-28.1877488155844</v>
       </c>
       <c r="L18" t="n">
         <v>14.20226218585835</v>
@@ -1942,10 +1942,10 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>117.9</v>
+        <v>118.4</v>
       </c>
       <c r="O18" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="P18" t="n">
         <v>5</v>
@@ -1959,19 +1959,19 @@
         <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>29.961</v>
+        <v>30.875</v>
       </c>
       <c r="T18" t="n">
-        <v>29.961</v>
+        <v>30.875</v>
       </c>
       <c r="U18" t="n">
-        <v>78.407</v>
+        <v>76.07899999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>39.001</v>
+        <v>37.187</v>
       </c>
       <c r="W18" t="n">
-        <v>-76.319</v>
+        <v>-78.64700000000001</v>
       </c>
     </row>
     <row r="19">
@@ -2015,14 +2015,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.26% / +15.78% / -3.96% | DOHOL.IS: -0.02% / +0.00% / 0.00% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +9.96% / +15.78% / -3.96% | DOHOL.IS: -0.02% / +0.00% / 0.00% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>9.256993294205484</v>
+        <v>7.829742331378675</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -2054,13 +2054,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>92.59699999999999</v>
+        <v>90.081</v>
       </c>
       <c r="V19" t="n">
-        <v>57.153</v>
+        <v>55.1</v>
       </c>
       <c r="W19" t="n">
-        <v>-22.827</v>
+        <v>-25.343</v>
       </c>
     </row>
     <row r="20">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.48% / +1.46% / -0.73% | DOHOL.IS: -0.38% / +2.33% / -1.07%</t>
+          <t>ALARK.IS: -1.94% / +1.46% / -3.01% | DOHOL.IS: -1.72% / +2.33% / -2.15%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K20" t="n">
-        <v>-28.96685039131007</v>
+        <v>-29.96646194093252</v>
       </c>
       <c r="L20" t="n">
         <v>25.50508358988237</v>
@@ -2137,19 +2137,19 @@
         <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>35.975</v>
+        <v>36.876</v>
       </c>
       <c r="T20" t="n">
-        <v>35.975</v>
+        <v>36.876</v>
       </c>
       <c r="U20" t="n">
-        <v>18.241</v>
+        <v>16.577</v>
       </c>
       <c r="V20" t="n">
-        <v>11.821</v>
+        <v>10.247</v>
       </c>
       <c r="W20" t="n">
-        <v>-66.438</v>
+        <v>-68.102</v>
       </c>
     </row>
     <row r="21">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TAVHL.IS</t>
+          <t>BRSAN.IS, ECILC.IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
+          <t>BRSAN.IS: 2026-08-27 | ECILC.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2193,14 +2193,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.29% / +2.39% / -1.71% | TAVHL.IS: -3.38% / +1.41% / -3.71%</t>
+          <t>BRSAN.IS: -1.45% / +2.39% / -1.98% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.552560900123012</v>
+        <v>-2.476447492659206</v>
       </c>
       <c r="L21" t="n">
         <v>13.72502171397572</v>
@@ -2209,13 +2209,13 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N21" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="O21" t="n">
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="P21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -2226,19 +2226,19 @@
         <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>31.066</v>
+        <v>31.713</v>
       </c>
       <c r="T21" t="n">
-        <v>31.066</v>
+        <v>31.713</v>
       </c>
       <c r="U21" t="n">
-        <v>-4.614</v>
+        <v>-5.509</v>
       </c>
       <c r="V21" t="n">
-        <v>-8.497999999999999</v>
+        <v>-9.356999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>-42.987</v>
+        <v>-43.882</v>
       </c>
     </row>
     <row r="22">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ALARK.IS, DOHOL.IS, TAVHL.IS</t>
+          <t>ALARK.IS, DOHOL.IS, ECILC.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27 | TAVHL.IS: 2026-08-27</t>
+          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27 | ECILC.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2282,14 +2282,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.48% / +1.46% / -0.73% | DOHOL.IS: -0.38% / +2.33% / -1.07% | TAVHL.IS: -3.38% / +1.41% / -3.71%</t>
+          <t>ALARK.IS: -1.94% / +1.46% / -3.01% | DOHOL.IS: -1.72% / +2.33% / -2.15% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.154083288580599</v>
+        <v>-3.306641054060266</v>
       </c>
       <c r="L22" t="n">
         <v>10.56563994340933</v>
@@ -2298,13 +2298,13 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>72.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="P22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>29.287</v>
       </c>
       <c r="U22" t="n">
-        <v>32.583</v>
+        <v>31.021</v>
       </c>
       <c r="V22" t="n">
-        <v>12.738</v>
+        <v>11.41</v>
       </c>
       <c r="W22" t="n">
-        <v>-49.73</v>
+        <v>-51.292</v>
       </c>
     </row>
     <row r="23">
@@ -2371,14 +2371,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +16.13% / +23.58% / 0.00% | BIMAS.IS: +0.72% / +3.87% / -0.86% | BRSAN.IS: +39.95% / +45.64% / -0.48% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +11.64% / +23.58% / 0.00% | BIMAS.IS: -0.94% / +3.87% / -1.04% | BRSAN.IS: +38.32% / +45.64% / -0.48% | CANTE.IS: +15.68% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K23" t="n">
-        <v>10.90577143667923</v>
+        <v>9.442025796428899</v>
       </c>
       <c r="L23" t="n">
         <v>23.4189376077676</v>
@@ -2390,7 +2390,7 @@
         <v>180.6</v>
       </c>
       <c r="O23" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="P23" t="n">
         <v>5.6</v>
@@ -2410,13 +2410,13 @@
         <v>22.513</v>
       </c>
       <c r="U23" t="n">
-        <v>50.663</v>
+        <v>48.674</v>
       </c>
       <c r="V23" t="n">
-        <v>46.951</v>
+        <v>45.012</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-1.877</v>
       </c>
     </row>
     <row r="24">
@@ -2460,14 +2460,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +16.13% / +23.58% / 0.00% | BIMAS.IS: +0.72% / +3.87% / -0.86% | BRSAN.IS: +39.95% / +45.64% / -0.48% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +11.64% / +23.58% / 0.00% | BIMAS.IS: -0.94% / +3.87% / -1.04% | BRSAN.IS: +38.32% / +45.64% / -0.48% | CANTE.IS: +15.68% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K24" t="n">
-        <v>10.90577143667923</v>
+        <v>9.442025796428899</v>
       </c>
       <c r="L24" t="n">
         <v>23.4189376077676</v>
@@ -2479,7 +2479,7 @@
         <v>180.6</v>
       </c>
       <c r="O24" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="P24" t="n">
         <v>5.6</v>
@@ -2499,13 +2499,13 @@
         <v>22.513</v>
       </c>
       <c r="U24" t="n">
-        <v>50.663</v>
+        <v>48.674</v>
       </c>
       <c r="V24" t="n">
-        <v>46.951</v>
+        <v>45.012</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-1.877</v>
       </c>
     </row>
     <row r="25">
@@ -2549,14 +2549,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.09% / +1.57% / -0.96% | BRSAN.IS: +0.46% / +1.10% / -0.96% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
+          <t>AKBNK.IS: -2.14% / +1.57% / -2.19% | BRSAN.IS: -0.71% / +1.10% / -1.24% | CANTE.IS: +15.68% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K25" t="n">
-        <v>15.37184218883045</v>
+        <v>14.79588649506534</v>
       </c>
       <c r="L25" t="n">
         <v>7.902828022135555</v>
@@ -2568,7 +2568,7 @@
         <v>34.7</v>
       </c>
       <c r="O25" t="n">
-        <v>47.9</v>
+        <v>46.5</v>
       </c>
       <c r="P25" t="n">
         <v>4.4</v>
@@ -2588,10 +2588,10 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>15.634</v>
+        <v>15.057</v>
       </c>
       <c r="V25" t="n">
-        <v>14.617</v>
+        <v>14.045</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -3182,14 +3182,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.29% / +2.39% / -1.71% | TRALT.IS: -2.69% / +2.76% / -3.68%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -1.45% / +2.39% / -1.98% | TRALT.IS: -3.15% / +2.76% / -3.68%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K8" t="n">
-        <v>-23.54775897667501</v>
+        <v>-23.97089460983509</v>
       </c>
       <c r="L8" t="n">
         <v>16.84258916554939</v>
@@ -3215,19 +3215,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>30.571</v>
+        <v>30.955</v>
       </c>
       <c r="T8" t="n">
-        <v>30.571</v>
+        <v>30.955</v>
       </c>
       <c r="U8" t="n">
-        <v>41.767</v>
+        <v>40.982</v>
       </c>
       <c r="V8" t="n">
-        <v>11.651</v>
+        <v>11.033</v>
       </c>
       <c r="W8" t="n">
-        <v>-62.422</v>
+        <v>-63.207</v>
       </c>
     </row>
     <row r="9">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
+          <t>T3_kademeli_slot|E30|S2|M20|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3479,67 +3479,55 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>AKBNK.IS, ASTOR.IS</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>AKBNK.IS: 2026-08-24 | ASTOR.IS: 2026-08-24</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>18.78300085000422</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>AKBNK.IS: +1.37% / +3.81% / -0.90% | ASTOR.IS: -1.48% / +4.84% / -2.42%</t>
-        </is>
-      </c>
+        <v>-31.68030208588772</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>-0.2995012191682078</v>
+        <v>-42.73273215208214</v>
       </c>
       <c r="K12" t="n">
-        <v>20.87839939106448</v>
+        <v>18.91282273316368</v>
       </c>
       <c r="L12" t="n">
-        <v>28.49280591027672</v>
+        <v>55.03591015625</v>
       </c>
       <c r="M12" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>81.5</v>
+        <v>229.9</v>
       </c>
       <c r="O12" t="n">
-        <v>48.8</v>
+        <v>41.9</v>
       </c>
       <c r="P12" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>13.617</v>
+        <v>30.327</v>
       </c>
       <c r="T12" t="n">
-        <v>13.617</v>
+        <v>15.334</v>
       </c>
       <c r="U12" t="n">
-        <v>40.67</v>
+        <v>11.695</v>
       </c>
       <c r="V12" t="n">
-        <v>27.813</v>
+        <v>55.16</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.807</v>
+        <v>-13.227</v>
       </c>
     </row>
     <row r="13">
@@ -3553,7 +3541,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3568,42 +3556,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AKBNK.IS, ASTOR.IS</t>
+          <t>AKBNK.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-26 | ASTOR.IS: 2026-08-24</t>
+          <t>AKBNK.IS: 2026-08-24 | BRSAN.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>13.9199517857125</v>
+        <v>18.78300085000422</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.09% / +1.57% / -0.95% | ASTOR.IS: -1.48% / +4.84% / -2.42%</t>
+          <t>AKBNK.IS: -0.71% / +3.81% / -0.90% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-1.715971707851549</v>
+        <v>-0.2995012191682078</v>
       </c>
       <c r="K13" t="n">
-        <v>20.14577142282576</v>
+        <v>18.06443156381583</v>
       </c>
       <c r="L13" t="n">
-        <v>28.84422545304696</v>
+        <v>28.49280591027672</v>
       </c>
       <c r="M13" t="n">
         <v>88.88888888888889</v>
       </c>
       <c r="N13" t="n">
-        <v>127.7</v>
+        <v>82</v>
       </c>
       <c r="O13" t="n">
-        <v>49.6</v>
+        <v>47.9</v>
       </c>
       <c r="P13" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3614,19 +3602,19 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>10.914</v>
+        <v>13.617</v>
       </c>
       <c r="T13" t="n">
-        <v>10.914</v>
+        <v>13.617</v>
       </c>
       <c r="U13" t="n">
-        <v>55.312</v>
+        <v>37.395</v>
       </c>
       <c r="V13" t="n">
-        <v>40.289</v>
+        <v>24.837</v>
       </c>
       <c r="W13" t="n">
-        <v>-3.099</v>
+        <v>-6.081</v>
       </c>
     </row>
     <row r="14">
@@ -3660,7 +3648,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-19 | BRSAN.IS: 2026-08-19</t>
+          <t>AKBNK.IS: 2026-08-31 | BRSAN.IS: 2026-08-19</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -3668,14 +3656,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +5.09% / +7.63% / -0.81% | BRSAN.IS: +9.85% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +8.57% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>16.63886199984612</v>
+        <v>14.75199816154253</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3684,13 +3672,13 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N14" t="n">
-        <v>37.8</v>
+        <v>38.3</v>
       </c>
       <c r="O14" t="n">
-        <v>57.1</v>
+        <v>56.4</v>
       </c>
       <c r="P14" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3707,13 +3695,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>55.37</v>
+        <v>52.856</v>
       </c>
       <c r="V14" t="n">
-        <v>38.247</v>
+        <v>36.011</v>
       </c>
       <c r="W14" t="n">
-        <v>-11.558</v>
+        <v>-14.071</v>
       </c>
     </row>
     <row r="16">
@@ -4112,14 +4100,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -0.29% / +2.39% / -1.71% | TRALT.IS: -2.69% / +2.76% / -3.68%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -1.45% / +2.39% / -1.98% | TRALT.IS: -3.15% / +2.76% / -3.68%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K21" t="n">
-        <v>-23.54775897667501</v>
+        <v>-23.97089460983509</v>
       </c>
       <c r="L21" t="n">
         <v>16.84258916554939</v>
@@ -4145,19 +4133,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>30.571</v>
+        <v>30.955</v>
       </c>
       <c r="T21" t="n">
-        <v>30.571</v>
+        <v>30.955</v>
       </c>
       <c r="U21" t="n">
-        <v>41.767</v>
+        <v>40.982</v>
       </c>
       <c r="V21" t="n">
-        <v>11.651</v>
+        <v>11.033</v>
       </c>
       <c r="W21" t="n">
-        <v>-62.422</v>
+        <v>-63.207</v>
       </c>
     </row>
     <row r="22">
@@ -4424,7 +4412,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-19 | BRSAN.IS: 2026-08-19</t>
+          <t>AKBNK.IS: 2026-08-31 | BRSAN.IS: 2026-08-19</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -4432,14 +4420,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +5.09% / +7.63% / -0.81% | BRSAN.IS: +9.85% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +8.57% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>16.63886199984612</v>
+        <v>14.75199816154253</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4448,13 +4436,13 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N25" t="n">
-        <v>37.8</v>
+        <v>38.3</v>
       </c>
       <c r="O25" t="n">
-        <v>57.1</v>
+        <v>56.4</v>
       </c>
       <c r="P25" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4471,13 +4459,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>55.37</v>
+        <v>52.856</v>
       </c>
       <c r="V25" t="n">
-        <v>38.247</v>
+        <v>36.011</v>
       </c>
       <c r="W25" t="n">
-        <v>-11.558</v>
+        <v>-14.071</v>
       </c>
     </row>
     <row r="26">
@@ -4488,7 +4476,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4508,12 +4496,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AKBNK.IS, ASTOR.IS</t>
+          <t>AKBNK.IS, BRSAN.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-24 | ASTOR.IS: 2026-08-24</t>
+          <t>AKBNK.IS: 2026-08-24 | BRSAN.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -4521,14 +4509,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: +1.37% / +3.81% / -0.90% | ASTOR.IS: -1.48% / +4.84% / -2.42%</t>
+          <t>AKBNK.IS: -0.71% / +3.81% / -0.90% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>20.87839939106448</v>
+        <v>18.06443156381583</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4537,10 +4525,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N26" t="n">
-        <v>81.5</v>
+        <v>82</v>
       </c>
       <c r="O26" t="n">
-        <v>48.8</v>
+        <v>47.9</v>
       </c>
       <c r="P26" t="n">
         <v>3.6</v>
@@ -4560,13 +4548,13 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>40.67</v>
+        <v>37.395</v>
       </c>
       <c r="V26" t="n">
-        <v>27.813</v>
+        <v>24.837</v>
       </c>
       <c r="W26" t="n">
-        <v>-2.807</v>
+        <v>-6.081</v>
       </c>
     </row>
     <row r="27">
@@ -4577,12 +4565,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T3_kademeli_slot|E30|S2|M20|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Pskor</t>
+          <t>T3_kademeli_slot|E30|S2|M20|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4595,67 +4583,55 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>AKBNK.IS, ASTOR.IS</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>AKBNK.IS: 2026-08-26 | ASTOR.IS: 2026-08-24</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>13.9199517857125</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>AKBNK.IS: -0.09% / +1.57% / -0.95% | ASTOR.IS: -1.48% / +4.84% / -2.42%</t>
-        </is>
-      </c>
+        <v>-31.68030208588772</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>-1.715971707851549</v>
+        <v>-42.73273215208214</v>
       </c>
       <c r="K27" t="n">
-        <v>20.14577142282576</v>
+        <v>18.91282273316368</v>
       </c>
       <c r="L27" t="n">
-        <v>28.84422545304696</v>
+        <v>55.03591015625</v>
       </c>
       <c r="M27" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="N27" t="n">
-        <v>127.7</v>
+        <v>229.9</v>
       </c>
       <c r="O27" t="n">
-        <v>49.6</v>
+        <v>41.9</v>
       </c>
       <c r="P27" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>10.914</v>
+        <v>30.327</v>
       </c>
       <c r="T27" t="n">
-        <v>10.914</v>
+        <v>15.334</v>
       </c>
       <c r="U27" t="n">
-        <v>55.312</v>
+        <v>11.695</v>
       </c>
       <c r="V27" t="n">
-        <v>40.289</v>
+        <v>55.16</v>
       </c>
       <c r="W27" t="n">
-        <v>-3.099</v>
+        <v>-13.227</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.47% / +0.09% / -3.54% | DOHOL.IS: -3.11% / +0.00% / -3.53% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -1.74% / +0.09% / -3.54% | DOHOL.IS: -2.40% / +0.00% / -3.53% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K3" t="n">
-        <v>-28.1877488155844</v>
+        <v>-27.83364722865428</v>
       </c>
       <c r="L3" t="n">
         <v>14.20226218585835</v>
@@ -789,19 +789,19 @@
         <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>30.875</v>
+        <v>30.534</v>
       </c>
       <c r="T3" t="n">
-        <v>30.875</v>
+        <v>30.534</v>
       </c>
       <c r="U3" t="n">
-        <v>76.07899999999999</v>
+        <v>76.947</v>
       </c>
       <c r="V3" t="n">
-        <v>37.187</v>
+        <v>37.864</v>
       </c>
       <c r="W3" t="n">
-        <v>-78.64700000000001</v>
+        <v>-77.779</v>
       </c>
     </row>
     <row r="4">
@@ -843,14 +843,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.96% / +15.78% / -3.96% | DOHOL.IS: -0.02% / +0.00% / 0.00% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +10.34% / +15.78% / -3.96% | DOHOL.IS: -0.02% / +0.00% / 0.00% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K4" t="n">
-        <v>7.829742331378675</v>
+        <v>8.40437295434211</v>
       </c>
       <c r="L4" t="n">
         <v>18.35191836499257</v>
@@ -882,13 +882,13 @@
         <v>28.662</v>
       </c>
       <c r="U4" t="n">
-        <v>90.081</v>
+        <v>91.09399999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>55.1</v>
+        <v>55.926</v>
       </c>
       <c r="W4" t="n">
-        <v>-25.343</v>
+        <v>-24.33</v>
       </c>
     </row>
     <row r="5">
@@ -930,14 +930,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.94% / +1.46% / -3.01% | DOHOL.IS: -1.72% / +2.33% / -2.15%</t>
+          <t>ALARK.IS: -1.21% / +1.46% / -3.01% | DOHOL.IS: -1.00% / +2.33% / -2.15%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K5" t="n">
-        <v>-29.96646194093252</v>
+        <v>-29.4506898328609</v>
       </c>
       <c r="L5" t="n">
         <v>25.50508358988237</v>
@@ -963,19 +963,19 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>36.876</v>
+        <v>36.411</v>
       </c>
       <c r="T5" t="n">
-        <v>36.876</v>
+        <v>36.411</v>
       </c>
       <c r="U5" t="n">
-        <v>16.577</v>
+        <v>17.436</v>
       </c>
       <c r="V5" t="n">
-        <v>10.247</v>
+        <v>11.059</v>
       </c>
       <c r="W5" t="n">
-        <v>-68.102</v>
+        <v>-67.24299999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1017,14 +1017,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.47% / +0.09% / -3.54% | DOHOL.IS: -3.11% / +0.00% / -3.53% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -1.74% / +0.09% / -3.54% | DOHOL.IS: -2.40% / +0.00% / -3.53% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K6" t="n">
-        <v>-28.1877488155844</v>
+        <v>-27.83364722865428</v>
       </c>
       <c r="L6" t="n">
         <v>14.20226218585835</v>
@@ -1050,19 +1050,19 @@
         <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>30.875</v>
+        <v>30.534</v>
       </c>
       <c r="T6" t="n">
-        <v>30.875</v>
+        <v>30.534</v>
       </c>
       <c r="U6" t="n">
-        <v>76.07899999999999</v>
+        <v>76.947</v>
       </c>
       <c r="V6" t="n">
-        <v>37.187</v>
+        <v>37.864</v>
       </c>
       <c r="W6" t="n">
-        <v>-78.64700000000001</v>
+        <v>-77.779</v>
       </c>
     </row>
     <row r="7">
@@ -1104,14 +1104,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.96% / +15.78% / -3.96% | DOHOL.IS: -0.02% / +0.00% / 0.00% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +10.34% / +15.78% / -3.96% | DOHOL.IS: -0.02% / +0.00% / 0.00% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K7" t="n">
-        <v>7.829742331378675</v>
+        <v>8.40437295434211</v>
       </c>
       <c r="L7" t="n">
         <v>18.35191836499257</v>
@@ -1143,13 +1143,13 @@
         <v>28.662</v>
       </c>
       <c r="U7" t="n">
-        <v>90.081</v>
+        <v>91.09399999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>55.1</v>
+        <v>55.926</v>
       </c>
       <c r="W7" t="n">
-        <v>-25.343</v>
+        <v>-24.33</v>
       </c>
     </row>
     <row r="8">
@@ -1191,14 +1191,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -1.45% / +2.39% / -1.98% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: -1.11% / +2.39% / -1.98% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.476447492659206</v>
+        <v>-2.305225341420825</v>
       </c>
       <c r="L8" t="n">
         <v>13.72502171397572</v>
@@ -1224,19 +1224,19 @@
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>31.713</v>
+        <v>31.593</v>
       </c>
       <c r="T8" t="n">
-        <v>31.713</v>
+        <v>31.593</v>
       </c>
       <c r="U8" t="n">
-        <v>-5.509</v>
+        <v>-5.343</v>
       </c>
       <c r="V8" t="n">
-        <v>-9.356999999999999</v>
+        <v>-9.196999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>-43.882</v>
+        <v>-43.716</v>
       </c>
     </row>
     <row r="9">
@@ -1278,14 +1278,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.47% / +0.09% / -3.54% | DOHOL.IS: -3.11% / +0.00% / -3.53% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -1.74% / +0.09% / -3.54% | DOHOL.IS: -2.40% / +0.00% / -3.53% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K9" t="n">
-        <v>-28.1877488155844</v>
+        <v>-27.83364722865428</v>
       </c>
       <c r="L9" t="n">
         <v>14.20226218585835</v>
@@ -1311,19 +1311,19 @@
         <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>30.875</v>
+        <v>30.534</v>
       </c>
       <c r="T9" t="n">
-        <v>30.875</v>
+        <v>30.534</v>
       </c>
       <c r="U9" t="n">
-        <v>76.07899999999999</v>
+        <v>76.947</v>
       </c>
       <c r="V9" t="n">
-        <v>37.187</v>
+        <v>37.864</v>
       </c>
       <c r="W9" t="n">
-        <v>-78.64700000000001</v>
+        <v>-77.779</v>
       </c>
     </row>
     <row r="10">
@@ -1365,14 +1365,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -1.45% / +2.39% / -1.98% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: -1.11% / +2.39% / -1.98% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.476447492659206</v>
+        <v>-2.305225341420825</v>
       </c>
       <c r="L10" t="n">
         <v>13.72502171397572</v>
@@ -1398,19 +1398,19 @@
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>31.713</v>
+        <v>31.593</v>
       </c>
       <c r="T10" t="n">
-        <v>31.713</v>
+        <v>31.593</v>
       </c>
       <c r="U10" t="n">
-        <v>-5.509</v>
+        <v>-5.343</v>
       </c>
       <c r="V10" t="n">
-        <v>-9.356999999999999</v>
+        <v>-9.196999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>-43.882</v>
+        <v>-43.716</v>
       </c>
     </row>
     <row r="11">
@@ -1452,14 +1452,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.94% / +1.46% / -3.01% | DOHOL.IS: -1.72% / +2.33% / -2.15% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -1.21% / +1.46% / -3.01% | DOHOL.IS: -1.00% / +2.33% / -2.15% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.306641054060266</v>
+        <v>-2.828232163826871</v>
       </c>
       <c r="L11" t="n">
         <v>10.56563994340933</v>
@@ -1491,13 +1491,13 @@
         <v>29.287</v>
       </c>
       <c r="U11" t="n">
-        <v>31.021</v>
+        <v>31.669</v>
       </c>
       <c r="V11" t="n">
-        <v>11.41</v>
+        <v>11.962</v>
       </c>
       <c r="W11" t="n">
-        <v>-51.292</v>
+        <v>-50.644</v>
       </c>
     </row>
     <row r="12">
@@ -1539,14 +1539,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -2.14% / +1.57% / -2.19% | BRSAN.IS: -0.71% / +1.10% / -1.24% | CANTE.IS: +15.68% / +18.18% / -0.83%</t>
+          <t>AKBNK.IS: -1.80% / +1.57% / -2.60% | BRSAN.IS: -0.36% / +1.10% / -1.24% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K12" t="n">
-        <v>14.79588649506534</v>
+        <v>14.44365447198786</v>
       </c>
       <c r="L12" t="n">
         <v>7.902828022135555</v>
@@ -1578,10 +1578,10 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>15.057</v>
+        <v>14.704</v>
       </c>
       <c r="V12" t="n">
-        <v>14.045</v>
+        <v>13.695</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1626,14 +1626,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +11.64% / +23.58% / 0.00% | BIMAS.IS: -0.94% / +3.87% / -1.04% | BRSAN.IS: +38.32% / +45.64% / -0.48% | CANTE.IS: +15.68% / +18.18% / -0.83%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +12.50% / +23.58% / 0.00% | BIMAS.IS: -0.39% / +3.87% / -1.35% | BRSAN.IS: +38.80% / +45.64% / -0.48% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K13" t="n">
-        <v>9.442025796428899</v>
+        <v>9.626327574085526</v>
       </c>
       <c r="L13" t="n">
         <v>23.4189376077676</v>
@@ -1665,13 +1665,13 @@
         <v>22.513</v>
       </c>
       <c r="U13" t="n">
-        <v>48.674</v>
+        <v>48.925</v>
       </c>
       <c r="V13" t="n">
-        <v>45.012</v>
+        <v>45.256</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.877</v>
+        <v>-1.627</v>
       </c>
     </row>
     <row r="14">
@@ -1713,14 +1713,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +11.64% / +23.58% / 0.00% | BIMAS.IS: -0.94% / +3.87% / -1.04% | BRSAN.IS: +38.32% / +45.64% / -0.48% | CANTE.IS: +15.68% / +18.18% / -0.83%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +12.50% / +23.58% / 0.00% | BIMAS.IS: -0.39% / +3.87% / -1.35% | BRSAN.IS: +38.80% / +45.64% / -0.48% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K14" t="n">
-        <v>9.442025796428899</v>
+        <v>9.626327574085526</v>
       </c>
       <c r="L14" t="n">
         <v>23.4189376077676</v>
@@ -1752,13 +1752,13 @@
         <v>22.513</v>
       </c>
       <c r="U14" t="n">
-        <v>48.674</v>
+        <v>48.925</v>
       </c>
       <c r="V14" t="n">
-        <v>45.012</v>
+        <v>45.256</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.877</v>
+        <v>-1.627</v>
       </c>
     </row>
     <row r="16">
@@ -1926,14 +1926,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.47% / +0.09% / -3.54% | DOHOL.IS: -3.11% / +0.00% / -3.53% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -1.74% / +0.09% / -3.54% | DOHOL.IS: -2.40% / +0.00% / -3.53% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>48.52701462824125</v>
       </c>
       <c r="K18" t="n">
-        <v>-28.1877488155844</v>
+        <v>-27.83364722865428</v>
       </c>
       <c r="L18" t="n">
         <v>14.20226218585835</v>
@@ -1959,19 +1959,19 @@
         <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>30.875</v>
+        <v>30.534</v>
       </c>
       <c r="T18" t="n">
-        <v>30.875</v>
+        <v>30.534</v>
       </c>
       <c r="U18" t="n">
-        <v>76.07899999999999</v>
+        <v>76.947</v>
       </c>
       <c r="V18" t="n">
-        <v>37.187</v>
+        <v>37.864</v>
       </c>
       <c r="W18" t="n">
-        <v>-78.64700000000001</v>
+        <v>-77.779</v>
       </c>
     </row>
     <row r="19">
@@ -2015,14 +2015,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.96% / +15.78% / -3.96% | DOHOL.IS: -0.02% / +0.00% / 0.00% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +10.34% / +15.78% / -3.96% | DOHOL.IS: -0.02% / +0.00% / 0.00% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>42.67896088967316</v>
       </c>
       <c r="K19" t="n">
-        <v>7.829742331378675</v>
+        <v>8.40437295434211</v>
       </c>
       <c r="L19" t="n">
         <v>18.35191836499257</v>
@@ -2054,13 +2054,13 @@
         <v>28.662</v>
       </c>
       <c r="U19" t="n">
-        <v>90.081</v>
+        <v>91.09399999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>55.1</v>
+        <v>55.926</v>
       </c>
       <c r="W19" t="n">
-        <v>-25.343</v>
+        <v>-24.33</v>
       </c>
     </row>
     <row r="20">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.94% / +1.46% / -3.01% | DOHOL.IS: -1.72% / +2.33% / -2.15%</t>
+          <t>ALARK.IS: -1.21% / +1.46% / -3.01% | DOHOL.IS: -1.00% / +2.33% / -2.15%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>20.71036906913848</v>
       </c>
       <c r="K20" t="n">
-        <v>-29.96646194093252</v>
+        <v>-29.4506898328609</v>
       </c>
       <c r="L20" t="n">
         <v>25.50508358988237</v>
@@ -2137,19 +2137,19 @@
         <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>36.876</v>
+        <v>36.411</v>
       </c>
       <c r="T20" t="n">
-        <v>36.876</v>
+        <v>36.411</v>
       </c>
       <c r="U20" t="n">
-        <v>16.577</v>
+        <v>17.436</v>
       </c>
       <c r="V20" t="n">
-        <v>10.247</v>
+        <v>11.059</v>
       </c>
       <c r="W20" t="n">
-        <v>-68.102</v>
+        <v>-67.24299999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2193,14 +2193,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -1.45% / +2.39% / -1.98% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: -1.11% / +2.39% / -1.98% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>42.40716574291981</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.476447492659206</v>
+        <v>-2.305225341420825</v>
       </c>
       <c r="L21" t="n">
         <v>13.72502171397572</v>
@@ -2226,19 +2226,19 @@
         <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>31.713</v>
+        <v>31.593</v>
       </c>
       <c r="T21" t="n">
-        <v>31.713</v>
+        <v>31.593</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.509</v>
+        <v>-5.343</v>
       </c>
       <c r="V21" t="n">
-        <v>-9.356999999999999</v>
+        <v>-9.196999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>-43.882</v>
+        <v>-43.716</v>
       </c>
     </row>
     <row r="22">
@@ -2282,14 +2282,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.94% / +1.46% / -3.01% | DOHOL.IS: -1.72% / +2.33% / -2.15% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -1.21% / +1.46% / -3.01% | DOHOL.IS: -1.00% / +2.33% / -2.15% | ECILC.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.19814518717994</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.306641054060266</v>
+        <v>-2.828232163826871</v>
       </c>
       <c r="L22" t="n">
         <v>10.56563994340933</v>
@@ -2321,13 +2321,13 @@
         <v>29.287</v>
       </c>
       <c r="U22" t="n">
-        <v>31.021</v>
+        <v>31.669</v>
       </c>
       <c r="V22" t="n">
-        <v>11.41</v>
+        <v>11.962</v>
       </c>
       <c r="W22" t="n">
-        <v>-51.292</v>
+        <v>-50.644</v>
       </c>
     </row>
     <row r="23">
@@ -2371,14 +2371,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +11.64% / +23.58% / 0.00% | BIMAS.IS: -0.94% / +3.87% / -1.04% | BRSAN.IS: +38.32% / +45.64% / -0.48% | CANTE.IS: +15.68% / +18.18% / -0.83%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +12.50% / +23.58% / 0.00% | BIMAS.IS: -0.39% / +3.87% / -1.35% | BRSAN.IS: +38.80% / +45.64% / -0.48% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K23" t="n">
-        <v>9.442025796428899</v>
+        <v>9.626327574085526</v>
       </c>
       <c r="L23" t="n">
         <v>23.4189376077676</v>
@@ -2410,13 +2410,13 @@
         <v>22.513</v>
       </c>
       <c r="U23" t="n">
-        <v>48.674</v>
+        <v>48.925</v>
       </c>
       <c r="V23" t="n">
-        <v>45.012</v>
+        <v>45.256</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.877</v>
+        <v>-1.627</v>
       </c>
     </row>
     <row r="24">
@@ -2460,14 +2460,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +11.64% / +23.58% / 0.00% | BIMAS.IS: -0.94% / +3.87% / -1.04% | BRSAN.IS: +38.32% / +45.64% / -0.48% | CANTE.IS: +15.68% / +18.18% / -0.83%</t>
+          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | ASTOR.IS: +12.50% / +23.58% / 0.00% | BIMAS.IS: -0.39% / +3.87% / -1.35% | BRSAN.IS: +38.80% / +45.64% / -0.48% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-5.037231846603429</v>
       </c>
       <c r="K24" t="n">
-        <v>9.442025796428899</v>
+        <v>9.626327574085526</v>
       </c>
       <c r="L24" t="n">
         <v>23.4189376077676</v>
@@ -2499,13 +2499,13 @@
         <v>22.513</v>
       </c>
       <c r="U24" t="n">
-        <v>48.674</v>
+        <v>48.925</v>
       </c>
       <c r="V24" t="n">
-        <v>45.012</v>
+        <v>45.256</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.877</v>
+        <v>-1.627</v>
       </c>
     </row>
     <row r="25">
@@ -2549,14 +2549,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -2.14% / +1.57% / -2.19% | BRSAN.IS: -0.71% / +1.10% / -1.24% | CANTE.IS: +15.68% / +18.18% / -0.83%</t>
+          <t>AKBNK.IS: -1.80% / +1.57% / -2.60% | BRSAN.IS: -0.36% / +1.10% / -1.24% | CANTE.IS: +14.03% / +18.18% / -0.83%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-1.862436885442242</v>
       </c>
       <c r="K25" t="n">
-        <v>14.79588649506534</v>
+        <v>14.44365447198786</v>
       </c>
       <c r="L25" t="n">
         <v>7.902828022135555</v>
@@ -2588,10 +2588,10 @@
         <v>8.954000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>15.057</v>
+        <v>14.704</v>
       </c>
       <c r="V25" t="n">
-        <v>14.045</v>
+        <v>13.695</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -3182,14 +3182,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -1.45% / +2.39% / -1.98% | TRALT.IS: -3.15% / +2.76% / -3.68%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -1.11% / +2.39% / -1.98% | TRALT.IS: -2.60% / +2.76% / -3.68%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K8" t="n">
-        <v>-23.97089460983509</v>
+        <v>-23.73764334753501</v>
       </c>
       <c r="L8" t="n">
         <v>16.84258916554939</v>
@@ -3215,19 +3215,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>30.955</v>
+        <v>30.743</v>
       </c>
       <c r="T8" t="n">
-        <v>30.955</v>
+        <v>30.743</v>
       </c>
       <c r="U8" t="n">
-        <v>40.982</v>
+        <v>41.414</v>
       </c>
       <c r="V8" t="n">
-        <v>11.033</v>
+        <v>11.374</v>
       </c>
       <c r="W8" t="n">
-        <v>-63.207</v>
+        <v>-62.774</v>
       </c>
     </row>
     <row r="9">
@@ -3569,14 +3569,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.71% / +3.81% / -0.90% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AKBNK.IS: -0.37% / +3.81% / -1.18% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K13" t="n">
-        <v>18.06443156381583</v>
+        <v>18.27412249576019</v>
       </c>
       <c r="L13" t="n">
         <v>28.49280591027672</v>
@@ -3608,13 +3608,13 @@
         <v>13.617</v>
       </c>
       <c r="U13" t="n">
-        <v>37.395</v>
+        <v>37.639</v>
       </c>
       <c r="V13" t="n">
-        <v>24.837</v>
+        <v>25.059</v>
       </c>
       <c r="W13" t="n">
-        <v>-6.081</v>
+        <v>-5.837</v>
       </c>
     </row>
     <row r="14">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-31 | BRSAN.IS: 2026-08-19</t>
+          <t>AKBNK.IS: 2026-08-19 | BRSAN.IS: 2026-08-19</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -3656,14 +3656,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +8.57% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +3.29% / +7.63% / -0.81% | BRSAN.IS: +8.95% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K14" t="n">
-        <v>14.75199816154253</v>
+        <v>15.17355904026347</v>
       </c>
       <c r="L14" t="n">
         <v>26.02919881379223</v>
@@ -3672,13 +3672,13 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N14" t="n">
-        <v>38.3</v>
+        <v>37.8</v>
       </c>
       <c r="O14" t="n">
-        <v>56.4</v>
+        <v>57.1</v>
       </c>
       <c r="P14" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3695,13 +3695,13 @@
         <v>13.394</v>
       </c>
       <c r="U14" t="n">
-        <v>52.856</v>
+        <v>53.418</v>
       </c>
       <c r="V14" t="n">
-        <v>36.011</v>
+        <v>36.51</v>
       </c>
       <c r="W14" t="n">
-        <v>-14.071</v>
+        <v>-13.51</v>
       </c>
     </row>
     <row r="16">
@@ -4100,14 +4100,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -1.45% / +2.39% / -1.98% | TRALT.IS: -3.15% / +2.76% / -3.68%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: -1.11% / +2.39% / -1.98% | TRALT.IS: -2.60% / +2.76% / -3.68%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>24.46792464739556</v>
       </c>
       <c r="K21" t="n">
-        <v>-23.97089460983509</v>
+        <v>-23.73764334753501</v>
       </c>
       <c r="L21" t="n">
         <v>16.84258916554939</v>
@@ -4133,19 +4133,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>30.955</v>
+        <v>30.743</v>
       </c>
       <c r="T21" t="n">
-        <v>30.955</v>
+        <v>30.743</v>
       </c>
       <c r="U21" t="n">
-        <v>40.982</v>
+        <v>41.414</v>
       </c>
       <c r="V21" t="n">
-        <v>11.033</v>
+        <v>11.374</v>
       </c>
       <c r="W21" t="n">
-        <v>-63.207</v>
+        <v>-62.774</v>
       </c>
     </row>
     <row r="22">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: 2026-08-31 | BRSAN.IS: 2026-08-19</t>
+          <t>AKBNK.IS: 2026-08-19 | BRSAN.IS: 2026-08-19</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -4420,14 +4420,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +8.57% / +14.31% / 0.00%</t>
+          <t>AKBNK.IS: +3.29% / +7.63% / -0.81% | BRSAN.IS: +8.95% / +14.31% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>4.259526299565808</v>
       </c>
       <c r="K25" t="n">
-        <v>14.75199816154253</v>
+        <v>15.17355904026347</v>
       </c>
       <c r="L25" t="n">
         <v>26.02919881379223</v>
@@ -4436,13 +4436,13 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N25" t="n">
-        <v>38.3</v>
+        <v>37.8</v>
       </c>
       <c r="O25" t="n">
-        <v>56.4</v>
+        <v>57.1</v>
       </c>
       <c r="P25" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4459,13 +4459,13 @@
         <v>13.394</v>
       </c>
       <c r="U25" t="n">
-        <v>52.856</v>
+        <v>53.418</v>
       </c>
       <c r="V25" t="n">
-        <v>36.011</v>
+        <v>36.51</v>
       </c>
       <c r="W25" t="n">
-        <v>-14.071</v>
+        <v>-13.51</v>
       </c>
     </row>
     <row r="26">
@@ -4509,14 +4509,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AKBNK.IS: -0.71% / +3.81% / -0.90% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AKBNK.IS: -0.37% / +3.81% / -1.18% | BRSAN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-0.2995012191682078</v>
       </c>
       <c r="K26" t="n">
-        <v>18.06443156381583</v>
+        <v>18.27412249576019</v>
       </c>
       <c r="L26" t="n">
         <v>28.49280591027672</v>
@@ -4548,13 +4548,13 @@
         <v>13.617</v>
       </c>
       <c r="U26" t="n">
-        <v>37.395</v>
+        <v>37.639</v>
       </c>
       <c r="V26" t="n">
-        <v>24.837</v>
+        <v>25.059</v>
       </c>
       <c r="W26" t="n">
-        <v>-6.081</v>
+        <v>-5.837</v>
       </c>
     </row>
     <row r="27">

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -578,7 +578,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -733,49 +733,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ALARK.IS, DOHOL.IS</t>
+          <t>ALARK.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27</t>
+          <t>ALARK.IS: 2026-08-27 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>111.9220792811126</v>
+        <v>111.9220744729613</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.57% / +1.46% / -3.01% | DOHOL.IS: -3.15% / +2.33% / -3.31%</t>
+          <t>ALARK.IS: -3.67% / +1.46% / -3.65% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>49.01214391258802</v>
+        <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-14.04476589499197</v>
+        <v>-15.36676101799904</v>
       </c>
       <c r="L3" t="n">
-        <v>18.08648334700127</v>
+        <v>18.08648750869864</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>102.1</v>
+        <v>102.4</v>
       </c>
       <c r="O3" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="P3" t="n">
         <v>6.8</v>
@@ -789,19 +789,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>20.292</v>
+        <v>21.518</v>
       </c>
       <c r="T3" t="n">
-        <v>20.292</v>
+        <v>21.518</v>
       </c>
       <c r="U3" t="n">
-        <v>58.499</v>
+        <v>58.533</v>
       </c>
       <c r="V3" t="n">
-        <v>16.777</v>
+        <v>14.981</v>
       </c>
       <c r="W3" t="n">
-        <v>-40.351</v>
+        <v>-43.467</v>
       </c>
     </row>
     <row r="4">
@@ -820,34 +820,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>93.76910018359669</v>
+        <v>93.76910111606556</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>15.94339796743394</v>
+        <v>15.94339964154305</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-3.898349643094434e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>11.6131504338196</v>
+        <v>11.61314751566397</v>
       </c>
       <c r="M4" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>64.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="O4" t="n">
         <v>48.8</v>
@@ -895,34 +895,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>66.7556852606542</v>
+        <v>66.75568133038392</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>1.223082499642225</v>
+        <v>1.223081376779578</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-1.901404478310553e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>12.97177432578954</v>
+        <v>12.97177163659006</v>
       </c>
       <c r="M5" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N5" t="n">
-        <v>65.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>46.6</v>
@@ -970,49 +970,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ALARK.IS, DOHOL.IS</t>
+          <t>ALARK.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27</t>
+          <t>ALARK.IS: 2026-08-27 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>111.9220792811126</v>
+        <v>111.9220744729613</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.57% / +1.46% / -3.01% | DOHOL.IS: -3.15% / +2.33% / -3.31%</t>
+          <t>ALARK.IS: -3.67% / +1.46% / -3.65% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>49.01214391258802</v>
+        <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-14.04476589499197</v>
+        <v>-15.36676101799904</v>
       </c>
       <c r="L6" t="n">
-        <v>18.08648334700127</v>
+        <v>18.08648750869864</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>102.1</v>
+        <v>102.4</v>
       </c>
       <c r="O6" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="P6" t="n">
         <v>6.8</v>
@@ -1026,19 +1026,19 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>20.292</v>
+        <v>21.518</v>
       </c>
       <c r="T6" t="n">
-        <v>20.292</v>
+        <v>21.518</v>
       </c>
       <c r="U6" t="n">
-        <v>58.499</v>
+        <v>58.533</v>
       </c>
       <c r="V6" t="n">
-        <v>16.777</v>
+        <v>14.981</v>
       </c>
       <c r="W6" t="n">
-        <v>-40.351</v>
+        <v>-43.467</v>
       </c>
     </row>
     <row r="7">
@@ -1057,52 +1057,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DOHOL.IS, ECILC.IS</t>
+          <t>DOHOL.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DOHOL.IS: 2026-08-31 | ECILC.IS: 2026-08-31</t>
+          <t>DOHOL.IS: 2026-08-31 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>59.20106793151596</v>
+        <v>59.2010679593864</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DOHOL.IS: -2.19% / +0.99% / -2.35% | ECILC.IS: -3.49% / +1.22% / -3.47%</t>
+          <t>DOHOL.IS: -3.18% / +0.99% / -3.25% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>29.78173813328349</v>
+        <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.772999274853817</v>
+        <v>-4.602895459827383</v>
       </c>
       <c r="L7" t="n">
-        <v>15.27952058925568</v>
+        <v>15.27952105135885</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>134.5</v>
+        <v>134.7</v>
       </c>
       <c r="O7" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="P7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>16.853</v>
+        <v>17.08</v>
       </c>
       <c r="T7" t="n">
-        <v>16.853</v>
+        <v>17.08</v>
       </c>
       <c r="U7" t="n">
-        <v>66.68000000000001</v>
+        <v>72.139</v>
       </c>
       <c r="V7" t="n">
-        <v>31.673</v>
+        <v>30.537</v>
       </c>
       <c r="W7" t="n">
-        <v>-32.598</v>
+        <v>-35.456</v>
       </c>
     </row>
     <row r="8">
@@ -1144,49 +1144,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, KRDMD.IS</t>
+          <t>ALTNY.IS, ENERY.IS, KRDMD.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-28 | ALTNY.IS: 2026-08-31 | KRDMD.IS: 2026-09-01</t>
+          <t>ALTNY.IS: 2026-08-31 | ENERY.IS: 2026-09-02 | KRDMD.IS: 2026-09-01</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>60.64600183674172</v>
+        <v>60.64599942530686</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.11% / +0.09% / -3.54% | ALTNY.IS: -1.94% / +0.00% / -3.44% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALTNY.IS: -1.43% / +0.00% / -3.44% | ENERY.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: -2.05% / +0.00% / -2.12%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>27.97836742584838</v>
+        <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-14.11063427229013</v>
+        <v>-15.12733085728632</v>
       </c>
       <c r="L8" t="n">
-        <v>14.40134655953992</v>
+        <v>14.40134401582471</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>191.7</v>
+        <v>191.9</v>
       </c>
       <c r="O8" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1200,19 +1200,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>15.457</v>
+        <v>16.458</v>
       </c>
       <c r="T8" t="n">
-        <v>15.457</v>
+        <v>16.458</v>
       </c>
       <c r="U8" t="n">
-        <v>40.362</v>
+        <v>41.935</v>
       </c>
       <c r="V8" t="n">
-        <v>14.035</v>
+        <v>12.685</v>
       </c>
       <c r="W8" t="n">
-        <v>-25.663</v>
+        <v>-27.962</v>
       </c>
     </row>
     <row r="9">
@@ -1231,49 +1231,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ALARK.IS, DOHOL.IS</t>
+          <t>ALARK.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27</t>
+          <t>ALARK.IS: 2026-08-27 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>111.9220792811126</v>
+        <v>111.9220744729613</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.57% / +1.46% / -3.01% | DOHOL.IS: -3.15% / +2.33% / -3.31%</t>
+          <t>ALARK.IS: -3.67% / +1.46% / -3.65% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>49.01214391258802</v>
+        <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-14.04476589499197</v>
+        <v>-15.36676101799904</v>
       </c>
       <c r="L9" t="n">
-        <v>18.08648334700127</v>
+        <v>18.08648750869864</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>102.1</v>
+        <v>102.4</v>
       </c>
       <c r="O9" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="P9" t="n">
         <v>6.8</v>
@@ -1287,19 +1287,19 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>20.292</v>
+        <v>21.518</v>
       </c>
       <c r="T9" t="n">
-        <v>20.292</v>
+        <v>21.518</v>
       </c>
       <c r="U9" t="n">
-        <v>58.499</v>
+        <v>58.533</v>
       </c>
       <c r="V9" t="n">
-        <v>16.777</v>
+        <v>14.981</v>
       </c>
       <c r="W9" t="n">
-        <v>-40.351</v>
+        <v>-43.467</v>
       </c>
     </row>
     <row r="10">
@@ -1318,49 +1318,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FENER.IS</t>
+          <t>FENER.IS, PETKM.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>FENER.IS: 2026-09-01</t>
+          <t>FENER.IS: 2026-09-01 | PETKM.IS: 2026-09-02 | TRALT.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>23.02092119806101</v>
+        <v>23.02092795860866</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FENER.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>FENER.IS: -0.99% / +0.00% / -1.29% | PETKM.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>12.8601447340497</v>
+        <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.105746774645302</v>
+        <v>-4.307242823430224</v>
       </c>
       <c r="L10" t="n">
-        <v>4.543445525149103</v>
+        <v>4.543450519200398</v>
       </c>
       <c r="M10" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>174.8</v>
+        <v>175.5</v>
       </c>
       <c r="O10" t="n">
-        <v>48.7</v>
+        <v>48.4</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
         <v>10.072</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>16.121</v>
+        <v>15.877</v>
       </c>
       <c r="V10" t="n">
-        <v>7.969</v>
+        <v>7.742</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.266999999999999</v>
+        <v>-9.510999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1405,34 +1405,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>50.58108258302254</v>
+        <v>50.58108284302749</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>13.32150388021296</v>
+        <v>13.3215021172385</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-4.400004582905126e-07</v>
       </c>
       <c r="L11" t="n">
-        <v>5.668148668007911</v>
+        <v>5.668150937989602</v>
       </c>
       <c r="M11" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>67.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="O11" t="n">
         <v>51.9</v>
@@ -1480,14 +1480,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>ASTOR.IS, FENER.IS</t>
@@ -1499,27 +1499,27 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>20.48700317587983</v>
+        <v>20.48700524499634</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: -2.23% / +0.00% / -2.60% | FENER.IS: -0.99% / +0.00% / -1.29%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-3.767341961802895</v>
+        <v>-3.767340978838807</v>
       </c>
       <c r="K12" t="n">
-        <v>12.58738424712718</v>
+        <v>10.79666974366784</v>
       </c>
       <c r="L12" t="n">
-        <v>16.57596065472375</v>
+        <v>16.57596537747867</v>
       </c>
       <c r="M12" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>88.2</v>
+        <v>88</v>
       </c>
       <c r="O12" t="n">
         <v>47.5</v>
@@ -1542,13 +1542,13 @@
         <v>17.404</v>
       </c>
       <c r="U12" t="n">
-        <v>52.281</v>
+        <v>49.859</v>
       </c>
       <c r="V12" t="n">
-        <v>44.736</v>
+        <v>42.434</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.421</v>
+        <v>-4.843</v>
       </c>
     </row>
     <row r="13">
@@ -1567,14 +1567,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>BRSAN.IS, DOHOL.IS, RALYH.IS</t>
@@ -1586,27 +1586,27 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>13.58351794435175</v>
+        <v>13.58351811074014</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.56% / +20.94% / 0.00% | DOHOL.IS: -2.19% / +0.99% / -2.35% | RALYH.IS: +24.25% / +35.10% / -0.91%</t>
+          <t>BRSAN.IS: +10.17% / +20.94% / 0.00% | DOHOL.IS: -3.18% / +0.99% / -3.25% | RALYH.IS: +21.61% / +35.10% / -0.91%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-10.39434470102466</v>
+        <v>-10.39434387728287</v>
       </c>
       <c r="K13" t="n">
-        <v>12.06483083746406</v>
+        <v>10.09821327502263</v>
       </c>
       <c r="L13" t="n">
-        <v>34.56349605759726</v>
+        <v>34.56349599547857</v>
       </c>
       <c r="M13" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>69.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>44.3</v>
@@ -1629,13 +1629,13 @@
         <v>23.777</v>
       </c>
       <c r="U13" t="n">
-        <v>48.218</v>
+        <v>45.617</v>
       </c>
       <c r="V13" t="n">
-        <v>42.017</v>
+        <v>39.525</v>
       </c>
       <c r="W13" t="n">
-        <v>-11.82</v>
+        <v>-14.421</v>
       </c>
     </row>
     <row r="14">
@@ -1654,34 +1654,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>55.72500185278999</v>
+        <v>55.72500398673659</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>-8.265158532570904</v>
+        <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>4.847592419675562</v>
+        <v>4.847595630925805</v>
       </c>
       <c r="L14" t="n">
-        <v>22.7318913992404</v>
+        <v>22.73189287884475</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>59.3</v>
+        <v>59.1</v>
       </c>
       <c r="O14" t="n">
         <v>44.5</v>
@@ -1704,13 +1704,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>75.491</v>
+        <v>78.53400000000001</v>
       </c>
       <c r="V14" t="n">
         <v>93.19</v>
       </c>
       <c r="W14" t="n">
-        <v>-29.274</v>
+        <v>-29.782</v>
       </c>
     </row>
     <row r="16">
@@ -1855,49 +1855,49 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ALARK.IS, DOHOL.IS</t>
+          <t>ALARK.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-27 | DOHOL.IS: 2026-08-27</t>
+          <t>ALARK.IS: 2026-08-27 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>111.9220792811126</v>
+        <v>111.9220744729613</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: -1.57% / +1.46% / -3.01% | DOHOL.IS: -3.15% / +2.33% / -3.31%</t>
+          <t>ALARK.IS: -3.67% / +1.46% / -3.65% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>49.01214391258802</v>
+        <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-14.04476589499197</v>
+        <v>-15.36676101799904</v>
       </c>
       <c r="L18" t="n">
-        <v>18.08648334700127</v>
+        <v>18.08648750869864</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>102.1</v>
+        <v>102.4</v>
       </c>
       <c r="O18" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="P18" t="n">
         <v>6.8</v>
@@ -1911,19 +1911,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>20.292</v>
+        <v>21.518</v>
       </c>
       <c r="T18" t="n">
-        <v>20.292</v>
+        <v>21.518</v>
       </c>
       <c r="U18" t="n">
-        <v>58.499</v>
+        <v>58.533</v>
       </c>
       <c r="V18" t="n">
-        <v>16.777</v>
+        <v>14.981</v>
       </c>
       <c r="W18" t="n">
-        <v>-40.351</v>
+        <v>-43.467</v>
       </c>
     </row>
     <row r="19">
@@ -1944,34 +1944,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>93.76910018359669</v>
+        <v>93.76910111606556</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>15.94339796743394</v>
+        <v>15.94339964154305</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-3.898349643094434e-07</v>
       </c>
       <c r="L19" t="n">
-        <v>11.6131504338196</v>
+        <v>11.61314751566397</v>
       </c>
       <c r="M19" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>64.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="O19" t="n">
         <v>48.8</v>
@@ -2021,34 +2021,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>66.7556852606542</v>
+        <v>66.75568133038392</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>1.223082499642225</v>
+        <v>1.223081376779578</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-1.901404478310553e-06</v>
       </c>
       <c r="L20" t="n">
-        <v>12.97177432578954</v>
+        <v>12.97177163659006</v>
       </c>
       <c r="M20" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>65.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="O20" t="n">
         <v>46.6</v>
@@ -2098,49 +2098,49 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, KRDMD.IS</t>
+          <t>ALTNY.IS, ENERY.IS, KRDMD.IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-28 | ALTNY.IS: 2026-08-31 | KRDMD.IS: 2026-09-01</t>
+          <t>ALTNY.IS: 2026-08-31 | ENERY.IS: 2026-09-02 | KRDMD.IS: 2026-09-01</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>60.64600183674172</v>
+        <v>60.64599942530686</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.11% / +0.09% / -3.54% | ALTNY.IS: -1.94% / +0.00% / -3.44% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALTNY.IS: -1.43% / +0.00% / -3.44% | ENERY.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: -2.05% / +0.00% / -2.12%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>27.97836742584838</v>
+        <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-14.11063427229013</v>
+        <v>-15.12733085728632</v>
       </c>
       <c r="L21" t="n">
-        <v>14.40134655953992</v>
+        <v>14.40134401582471</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>191.7</v>
+        <v>191.9</v>
       </c>
       <c r="O21" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2154,19 +2154,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>15.457</v>
+        <v>16.458</v>
       </c>
       <c r="T21" t="n">
-        <v>15.457</v>
+        <v>16.458</v>
       </c>
       <c r="U21" t="n">
-        <v>40.362</v>
+        <v>41.935</v>
       </c>
       <c r="V21" t="n">
-        <v>14.035</v>
+        <v>12.685</v>
       </c>
       <c r="W21" t="n">
-        <v>-25.663</v>
+        <v>-27.962</v>
       </c>
     </row>
     <row r="22">
@@ -2187,52 +2187,52 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DOHOL.IS, ECILC.IS</t>
+          <t>DOHOL.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DOHOL.IS: 2026-08-31 | ECILC.IS: 2026-08-31</t>
+          <t>DOHOL.IS: 2026-08-31 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>59.20106793151596</v>
+        <v>59.2010679593864</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DOHOL.IS: -2.19% / +0.99% / -2.35% | ECILC.IS: -3.49% / +1.22% / -3.47%</t>
+          <t>DOHOL.IS: -3.18% / +0.99% / -3.25% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>29.78173813328349</v>
+        <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.772999274853817</v>
+        <v>-4.602895459827383</v>
       </c>
       <c r="L22" t="n">
-        <v>15.27952058925568</v>
+        <v>15.27952105135885</v>
       </c>
       <c r="M22" t="n">
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>134.5</v>
+        <v>134.7</v>
       </c>
       <c r="O22" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="P22" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2243,19 +2243,19 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>16.853</v>
+        <v>17.08</v>
       </c>
       <c r="T22" t="n">
-        <v>16.853</v>
+        <v>17.08</v>
       </c>
       <c r="U22" t="n">
-        <v>66.68000000000001</v>
+        <v>72.139</v>
       </c>
       <c r="V22" t="n">
-        <v>31.673</v>
+        <v>30.537</v>
       </c>
       <c r="W22" t="n">
-        <v>-32.598</v>
+        <v>-35.456</v>
       </c>
     </row>
     <row r="23">
@@ -2276,34 +2276,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>55.72500185278999</v>
+        <v>55.72500398673659</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>-8.265158532570904</v>
+        <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>4.847592419675562</v>
+        <v>4.847595630925805</v>
       </c>
       <c r="L23" t="n">
-        <v>22.7318913992404</v>
+        <v>22.73189287884475</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>59.3</v>
+        <v>59.1</v>
       </c>
       <c r="O23" t="n">
         <v>44.5</v>
@@ -2326,13 +2326,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>75.491</v>
+        <v>78.53400000000001</v>
       </c>
       <c r="V23" t="n">
         <v>93.19</v>
       </c>
       <c r="W23" t="n">
-        <v>-29.274</v>
+        <v>-29.782</v>
       </c>
     </row>
     <row r="24">
@@ -2353,34 +2353,34 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>50.58108258302254</v>
+        <v>50.58108284302749</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>13.32150388021296</v>
+        <v>13.3215021172385</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>-4.400004582905126e-07</v>
       </c>
       <c r="L24" t="n">
-        <v>5.668148668007911</v>
+        <v>5.668150937989602</v>
       </c>
       <c r="M24" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>67.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="O24" t="n">
         <v>51.9</v>
@@ -2430,49 +2430,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FENER.IS</t>
+          <t>FENER.IS, PETKM.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>FENER.IS: 2026-09-01</t>
+          <t>FENER.IS: 2026-09-01 | PETKM.IS: 2026-09-02 | TRALT.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>23.02092119806101</v>
+        <v>23.02092795860866</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FENER.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>FENER.IS: -0.99% / +0.00% / -1.29% | PETKM.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>12.8601447340497</v>
+        <v>12.86015270141232</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.105746774645302</v>
+        <v>-4.307242823430224</v>
       </c>
       <c r="L25" t="n">
-        <v>4.543445525149103</v>
+        <v>4.543450519200398</v>
       </c>
       <c r="M25" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N25" t="n">
-        <v>174.8</v>
+        <v>175.5</v>
       </c>
       <c r="O25" t="n">
-        <v>48.7</v>
+        <v>48.4</v>
       </c>
       <c r="P25" t="n">
         <v>1.9</v>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S25" t="n">
         <v>10.072</v>
@@ -2492,13 +2492,13 @@
         <v>10.072</v>
       </c>
       <c r="U25" t="n">
-        <v>16.121</v>
+        <v>15.877</v>
       </c>
       <c r="V25" t="n">
-        <v>7.969</v>
+        <v>7.742</v>
       </c>
       <c r="W25" t="n">
-        <v>-9.266999999999999</v>
+        <v>-9.510999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -2519,14 +2519,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>ASTOR.IS, FENER.IS</t>
@@ -2538,27 +2538,27 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>20.48700317587983</v>
+        <v>20.48700524499634</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: -2.23% / +0.00% / -2.60% | FENER.IS: -0.99% / +0.00% / -1.29%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-3.767341961802895</v>
+        <v>-3.767340978838807</v>
       </c>
       <c r="K26" t="n">
-        <v>12.58738424712718</v>
+        <v>10.79666974366784</v>
       </c>
       <c r="L26" t="n">
-        <v>16.57596065472375</v>
+        <v>16.57596537747867</v>
       </c>
       <c r="M26" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>88.2</v>
+        <v>88</v>
       </c>
       <c r="O26" t="n">
         <v>47.5</v>
@@ -2581,13 +2581,13 @@
         <v>17.404</v>
       </c>
       <c r="U26" t="n">
-        <v>52.281</v>
+        <v>49.859</v>
       </c>
       <c r="V26" t="n">
-        <v>44.736</v>
+        <v>42.434</v>
       </c>
       <c r="W26" t="n">
-        <v>-2.421</v>
+        <v>-4.843</v>
       </c>
     </row>
     <row r="27">
@@ -2608,14 +2608,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>BRSAN.IS, DOHOL.IS, RALYH.IS</t>
@@ -2627,27 +2627,27 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>13.58351794435175</v>
+        <v>13.58351811074014</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.56% / +20.94% / 0.00% | DOHOL.IS: -2.19% / +0.99% / -2.35% | RALYH.IS: +24.25% / +35.10% / -0.91%</t>
+          <t>BRSAN.IS: +10.17% / +20.94% / 0.00% | DOHOL.IS: -3.18% / +0.99% / -3.25% | RALYH.IS: +21.61% / +35.10% / -0.91%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>-10.39434470102466</v>
+        <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>12.06483083746406</v>
+        <v>10.09821327502263</v>
       </c>
       <c r="L27" t="n">
-        <v>34.56349605759726</v>
+        <v>34.56349599547857</v>
       </c>
       <c r="M27" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N27" t="n">
-        <v>69.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="O27" t="n">
         <v>44.3</v>
@@ -2670,13 +2670,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>48.218</v>
+        <v>45.617</v>
       </c>
       <c r="V27" t="n">
-        <v>42.017</v>
+        <v>39.525</v>
       </c>
       <c r="W27" t="n">
-        <v>-11.82</v>
+        <v>-14.421</v>
       </c>
     </row>
   </sheetData>
@@ -2717,7 +2717,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
     <col width="21" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
@@ -2866,14 +2866,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>ALARK.IS, TKFEN.IS</t>
@@ -2885,27 +2885,27 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>86.93022195417733</v>
+        <v>86.93022416585528</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.39% / +1.57% / -1.39% | TKFEN.IS: +14.63% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | TKFEN.IS: +12.70% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.05810894902989</v>
+        <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2719929856001668</v>
+        <v>-1.61366876561112</v>
       </c>
       <c r="L3" t="n">
-        <v>28.40818688752193</v>
+        <v>28.4081875</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>93</v>
+        <v>92.8</v>
       </c>
       <c r="O3" t="n">
         <v>44.1</v>
@@ -2928,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>276.788</v>
+        <v>277.418</v>
       </c>
       <c r="V3" t="n">
-        <v>101.995</v>
+        <v>98.196</v>
       </c>
       <c r="W3" t="n">
-        <v>-40.913</v>
+        <v>-49.001</v>
       </c>
     </row>
     <row r="4">
@@ -2953,49 +2953,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, BRSAN.IS, DOHOL.IS, ENJSA.IS</t>
+          <t>ALARK.IS, ALTNY.IS, DOHOL.IS, ENERY.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | BRSAN.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ENJSA.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>85.65134753292634</v>
+        <v>85.65134732223945</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.39% / +1.57% / -1.39% | ALTNY.IS: -1.94% / +0.00% / -3.44% | BRSAN.IS: -2.37% / +0.90% / -2.69% | DOHOL.IS: -2.19% / +0.99% / -2.35% | ENJSA.IS: +0.62% / +2.09% / -0.09%</t>
+          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | ALTNY.IS: -1.43% / +0.00% / -3.44% | DOHOL.IS: -3.18% / +0.99% / -3.26% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.52% / +2.09% / -0.09%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>23.84260390924482</v>
+        <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-9.78159267893618</v>
+        <v>-10.40172566965912</v>
       </c>
       <c r="L4" t="n">
-        <v>13.10602632780896</v>
+        <v>13.10602576687011</v>
       </c>
       <c r="M4" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>117</v>
+        <v>117.3</v>
       </c>
       <c r="O4" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="P4" t="n">
         <v>3.9</v>
@@ -3009,19 +3009,19 @@
         <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>24.703</v>
+        <v>25.221</v>
       </c>
       <c r="T4" t="n">
-        <v>24.703</v>
+        <v>25.221</v>
       </c>
       <c r="U4" t="n">
-        <v>56.529</v>
+        <v>58.564</v>
       </c>
       <c r="V4" t="n">
-        <v>21.382</v>
+        <v>20.547</v>
       </c>
       <c r="W4" t="n">
-        <v>-51.354</v>
+        <v>-53.479</v>
       </c>
     </row>
     <row r="5">
@@ -3040,14 +3040,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>ALARK.IS, TKFEN.IS</t>
@@ -3059,27 +3059,27 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>83.80706095677104</v>
+        <v>83.80706321463933</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.39% / +1.57% / -1.39% | TKFEN.IS: +14.63% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | TKFEN.IS: +12.70% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>-0.4421646049801775</v>
+        <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2519171994405767</v>
+        <v>-1.633364774066537</v>
       </c>
       <c r="L5" t="n">
-        <v>32.32163079109998</v>
+        <v>32.3216328125</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="O5" t="n">
         <v>42.1</v>
@@ -3102,13 +3102,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>279</v>
+        <v>274.713</v>
       </c>
       <c r="V5" t="n">
-        <v>83.949</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-41.105</v>
+        <v>-48.601</v>
       </c>
     </row>
     <row r="6">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>BRSAN.IS, CANTE.IS, DOHOL.IS, ECILC.IS, TKFEN.IS</t>
@@ -3146,27 +3146,27 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>60.21036272243545</v>
+        <v>60.21035987359713</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.71% / +20.03% / -1.13% | CANTE.IS: +5.39% / +15.84% / -2.80% | DOHOL.IS: -2.19% / +0.99% / -2.35% | ECILC.IS: -1.44% / +6.20% / -2.94% | TKFEN.IS: +14.63% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +9.34% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | DOHOL.IS: -3.18% / +0.99% / -3.26% | ECILC.IS: -2.89% / +6.20% / -3.06% | TKFEN.IS: +12.70% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>33.48059234987395</v>
+        <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.984606183727273</v>
+        <v>-9.714799709635013</v>
       </c>
       <c r="L6" t="n">
-        <v>19.41140971066007</v>
+        <v>19.41140710190506</v>
       </c>
       <c r="M6" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>138.5</v>
+        <v>138.2</v>
       </c>
       <c r="O6" t="n">
         <v>42.6</v>
@@ -3189,13 +3189,13 @@
         <v>26.15</v>
       </c>
       <c r="U6" t="n">
-        <v>23.939</v>
+        <v>25.28</v>
       </c>
       <c r="V6" t="n">
-        <v>13.156</v>
+        <v>12.249</v>
       </c>
       <c r="W6" t="n">
-        <v>-41.312</v>
+        <v>-43.11</v>
       </c>
     </row>
     <row r="7">
@@ -3214,49 +3214,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, BRSAN.IS, DOHOL.IS, ENJSA.IS</t>
+          <t>ALARK.IS, ALTNY.IS, DOHOL.IS, ENERY.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | BRSAN.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ENJSA.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>85.65134753292634</v>
+        <v>85.65134732223945</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.39% / +1.57% / -1.39% | ALTNY.IS: -1.94% / +0.00% / -3.44% | BRSAN.IS: -2.37% / +0.90% / -2.69% | DOHOL.IS: -2.19% / +0.99% / -2.35% | ENJSA.IS: +0.62% / +2.09% / -0.09%</t>
+          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | ALTNY.IS: -1.43% / +0.00% / -3.44% | DOHOL.IS: -3.18% / +0.99% / -3.26% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.52% / +2.09% / -0.09%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>23.84260390924482</v>
+        <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.78159267893618</v>
+        <v>-10.40172566965912</v>
       </c>
       <c r="L7" t="n">
-        <v>13.10602632780896</v>
+        <v>13.10602576687011</v>
       </c>
       <c r="M7" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>117</v>
+        <v>117.3</v>
       </c>
       <c r="O7" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="P7" t="n">
         <v>3.9</v>
@@ -3270,19 +3270,19 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>24.703</v>
+        <v>25.221</v>
       </c>
       <c r="T7" t="n">
-        <v>24.703</v>
+        <v>25.221</v>
       </c>
       <c r="U7" t="n">
-        <v>56.529</v>
+        <v>58.564</v>
       </c>
       <c r="V7" t="n">
-        <v>21.382</v>
+        <v>20.547</v>
       </c>
       <c r="W7" t="n">
-        <v>-51.354</v>
+        <v>-53.479</v>
       </c>
     </row>
     <row r="8">
@@ -3301,49 +3301,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BRSAN.IS, DOHOL.IS, ECILC.IS</t>
+          <t>BRSAN.IS, CANTE.IS, DOHOL.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | DOHOL.IS: 2026-08-31 | ECILC.IS: 2026-08-31</t>
+          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-09-02 | DOHOL.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>48.21914486587673</v>
+        <v>48.21914524341393</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.71% / +20.03% / -1.13% | DOHOL.IS: -2.19% / +0.99% / -2.35% | ECILC.IS: -3.49% / +1.22% / -3.47%</t>
+          <t>BRSAN.IS: +9.34% / +20.03% / -1.13% | CANTE.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -3.18% / +0.99% / -3.26%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>21.40028975775241</v>
+        <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.19616237122725</v>
+        <v>-3.286575364070232</v>
       </c>
       <c r="L8" t="n">
-        <v>16.16102122336589</v>
+        <v>16.16102048107813</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>153.5</v>
+        <v>153.7</v>
       </c>
       <c r="O8" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="P8" t="n">
         <v>4.2</v>
@@ -3363,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>19.56</v>
+        <v>21.195</v>
       </c>
       <c r="V8" t="n">
-        <v>2.508</v>
+        <v>1.365</v>
       </c>
       <c r="W8" t="n">
-        <v>-29.905</v>
+        <v>-32.022</v>
       </c>
     </row>
     <row r="9">
@@ -3388,46 +3388,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ALTNY.IS, DOHOL.IS, ECILC.IS</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ALTNY.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ECILC.IS: 2026-08-31</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>28.40087202006096</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ALTNY.IS: -1.94% / +0.00% / -3.44% | DOHOL.IS: -2.19% / +0.99% / -2.35% | ECILC.IS: -3.49% / +1.22% / -3.47%</t>
-        </is>
-      </c>
+        <v>28.40086810394897</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>15.38513800674384</v>
+        <v>15.38514121842653</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.713342161610269</v>
+        <v>-6.297380057931356</v>
       </c>
       <c r="L9" t="n">
-        <v>5.127815013494629</v>
+        <v>5.127814043936619</v>
       </c>
       <c r="M9" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N9" t="n">
-        <v>76</v>
+        <v>75.8</v>
       </c>
       <c r="O9" t="n">
         <v>49.3</v>
@@ -3437,26 +3425,26 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>12.442</v>
+        <v>12.984</v>
       </c>
       <c r="T9" t="n">
-        <v>12.442</v>
+        <v>12.984</v>
       </c>
       <c r="U9" t="n">
-        <v>7.959</v>
+        <v>8.936</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.004</v>
+        <v>-0.623</v>
       </c>
       <c r="W9" t="n">
-        <v>-15.341</v>
+        <v>-16.255</v>
       </c>
     </row>
     <row r="10">
@@ -3475,49 +3463,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ALARK.IS, DOHOL.IS, ECILC.IS</t>
+          <t>ALARK.IS, CANTE.IS, DOHOL.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ECILC.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | CANTE.IS: 2026-09-02 | DOHOL.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>38.04089892782267</v>
+        <v>38.04089454478734</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.39% / +1.57% / -1.39% | DOHOL.IS: -2.19% / +0.99% / -2.35% | ECILC.IS: -3.49% / +1.22% / -3.47%</t>
+          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | CANTE.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -3.18% / +0.99% / -3.26%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13.75066770777271</v>
+        <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.450756566937097</v>
+        <v>-4.513188934672541</v>
       </c>
       <c r="L10" t="n">
-        <v>5.808643018798421</v>
+        <v>5.808640829284117</v>
       </c>
       <c r="M10" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>113.5</v>
+        <v>113.8</v>
       </c>
       <c r="O10" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="P10" t="n">
         <v>2.4</v>
@@ -3531,19 +3519,19 @@
         <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>20.062</v>
+        <v>20.942</v>
       </c>
       <c r="T10" t="n">
-        <v>20.062</v>
+        <v>20.942</v>
       </c>
       <c r="U10" t="n">
-        <v>6.314</v>
+        <v>8.651999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.873</v>
+        <v>-3.942</v>
       </c>
       <c r="W10" t="n">
-        <v>-26.682</v>
+        <v>-28.781</v>
       </c>
     </row>
     <row r="11">
@@ -3562,49 +3550,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, BRSAN.IS, DOHOL.IS, ENJSA.IS</t>
+          <t>ALARK.IS, ALTNY.IS, DOHOL.IS, ENERY.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | BRSAN.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ENJSA.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>63.58450671500058</v>
+        <v>63.58450648919234</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.39% / +1.57% / -1.39% | ALTNY.IS: -1.94% / +0.00% / -3.44% | BRSAN.IS: -2.37% / +0.90% / -2.69% | DOHOL.IS: -2.19% / +0.99% / -2.35% | ENJSA.IS: +0.62% / +2.09% / -0.09%</t>
+          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | ALTNY.IS: -1.43% / +0.00% / -3.44% | DOHOL.IS: -3.18% / +0.99% / -3.26% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.52% / +2.09% / -0.09%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>22.7235340197322</v>
+        <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.697341378772473</v>
+        <v>-10.31805449116768</v>
       </c>
       <c r="L11" t="n">
-        <v>9.664713924402102</v>
+        <v>9.664716767669679</v>
       </c>
       <c r="M11" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>178</v>
+        <v>178.1</v>
       </c>
       <c r="O11" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
@@ -3618,19 +3606,19 @@
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>23.371</v>
+        <v>23.897</v>
       </c>
       <c r="T11" t="n">
-        <v>23.371</v>
+        <v>23.897</v>
       </c>
       <c r="U11" t="n">
-        <v>32.406</v>
+        <v>34.485</v>
       </c>
       <c r="V11" t="n">
-        <v>8.288</v>
+        <v>7.544</v>
       </c>
       <c r="W11" t="n">
-        <v>-40.382</v>
+        <v>-42.23</v>
       </c>
     </row>
     <row r="12">
@@ -3644,19 +3632,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>BRSAN.IS, TKFEN.IS</t>
@@ -3668,33 +3656,33 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>23.21519247003325</v>
+        <v>6.880672511445463</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.71% / +20.03% / -1.13% | TKFEN.IS: +14.63% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +9.34% / +20.03% / -1.13% | TKFEN.IS: +12.70% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-6.505634231645974</v>
+        <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>11.10457161788687</v>
+        <v>9.004198403489783</v>
       </c>
       <c r="L12" t="n">
-        <v>23.2021083711861</v>
+        <v>31.31195090134997</v>
       </c>
       <c r="M12" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>47.5</v>
+        <v>48.4</v>
       </c>
       <c r="O12" t="n">
-        <v>44.2</v>
+        <v>43.3</v>
       </c>
       <c r="P12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3705,19 +3693,19 @@
         <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>27.528</v>
+        <v>28.439</v>
       </c>
       <c r="T12" t="n">
-        <v>27.528</v>
+        <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>44.489</v>
+        <v>37.828</v>
       </c>
       <c r="V12" t="n">
-        <v>61.345</v>
+        <v>51.887</v>
       </c>
       <c r="W12" t="n">
-        <v>-13.805</v>
+        <v>-18.037</v>
       </c>
     </row>
     <row r="13">
@@ -3736,14 +3724,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>ASTOR.IS, FENER.IS</t>
@@ -3755,27 +3743,27 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-0.4938844333224335</v>
+        <v>-0.49388395046156</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: -2.23% / +0.00% / -2.60% | FENER.IS: -0.99% / +0.04% / -1.25%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-19.60938072014315</v>
+        <v>-19.60937535624424</v>
       </c>
       <c r="K13" t="n">
-        <v>9.404806102137364</v>
+        <v>7.664581132672121</v>
       </c>
       <c r="L13" t="n">
-        <v>19.61961180062131</v>
+        <v>19.61961325199098</v>
       </c>
       <c r="M13" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N13" t="n">
-        <v>88</v>
+        <v>87.8</v>
       </c>
       <c r="O13" t="n">
         <v>46</v>
@@ -3798,13 +3786,13 @@
         <v>18.132</v>
       </c>
       <c r="U13" t="n">
-        <v>8.077999999999999</v>
+        <v>9.458</v>
       </c>
       <c r="V13" t="n">
-        <v>14.241</v>
+        <v>12.424</v>
       </c>
       <c r="W13" t="n">
-        <v>-5.181</v>
+        <v>-7.101</v>
       </c>
     </row>
     <row r="14">
@@ -3823,52 +3811,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASTOR.IS</t>
+          <t>ASTOR.IS, KRDMD.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-01</t>
+          <t>ASTOR.IS: 2026-09-01 | KRDMD.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8.530011799530879</v>
+        <v>8.530010255723974</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: -2.23% / +0.00% / -2.60% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.8142534255296985</v>
+        <v>0.8142516931666233</v>
       </c>
       <c r="K14" t="n">
-        <v>8.192968654145272</v>
+        <v>6.97606599636289</v>
       </c>
       <c r="L14" t="n">
-        <v>9.181211877431517</v>
+        <v>9.181211458048665</v>
       </c>
       <c r="M14" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N14" t="n">
-        <v>35.5</v>
+        <v>35.9</v>
       </c>
       <c r="O14" t="n">
-        <v>50.7</v>
+        <v>50</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3876,7 +3864,7 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
         <v>8.083</v>
@@ -3885,13 +3873,13 @@
         <v>7.916</v>
       </c>
       <c r="U14" t="n">
-        <v>14.678</v>
+        <v>13.388</v>
       </c>
       <c r="V14" t="n">
-        <v>9.308</v>
+        <v>8.077999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.417</v>
+        <v>-1.707</v>
       </c>
     </row>
     <row r="16">
@@ -4036,14 +4024,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>ALARK.IS, TKFEN.IS</t>
@@ -4055,27 +4043,27 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>86.93022195417733</v>
+        <v>86.93022416585528</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.39% / +1.57% / -1.39% | TKFEN.IS: +14.63% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | TKFEN.IS: +12.70% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1.05810894902989</v>
+        <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2719929856001668</v>
+        <v>-1.61366876561112</v>
       </c>
       <c r="L18" t="n">
-        <v>28.40818688752193</v>
+        <v>28.4081875</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>93</v>
+        <v>92.8</v>
       </c>
       <c r="O18" t="n">
         <v>44.1</v>
@@ -4098,13 +4086,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>276.788</v>
+        <v>277.418</v>
       </c>
       <c r="V18" t="n">
-        <v>101.995</v>
+        <v>98.196</v>
       </c>
       <c r="W18" t="n">
-        <v>-40.913</v>
+        <v>-49.001</v>
       </c>
     </row>
     <row r="19">
@@ -4125,49 +4113,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, BRSAN.IS, DOHOL.IS, ENJSA.IS</t>
+          <t>ALARK.IS, ALTNY.IS, DOHOL.IS, ENERY.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | BRSAN.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ENJSA.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>85.65134753292634</v>
+        <v>85.65134732223945</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.39% / +1.57% / -1.39% | ALTNY.IS: -1.94% / +0.00% / -3.44% | BRSAN.IS: -2.37% / +0.90% / -2.69% | DOHOL.IS: -2.19% / +0.99% / -2.35% | ENJSA.IS: +0.62% / +2.09% / -0.09%</t>
+          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | ALTNY.IS: -1.43% / +0.00% / -3.44% | DOHOL.IS: -3.18% / +0.99% / -3.26% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.52% / +2.09% / -0.09%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>23.84260390924482</v>
+        <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-9.78159267893618</v>
+        <v>-10.40172566965912</v>
       </c>
       <c r="L19" t="n">
-        <v>13.10602632780896</v>
+        <v>13.10602576687011</v>
       </c>
       <c r="M19" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>117</v>
+        <v>117.3</v>
       </c>
       <c r="O19" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="P19" t="n">
         <v>3.9</v>
@@ -4181,19 +4169,19 @@
         <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>24.703</v>
+        <v>25.221</v>
       </c>
       <c r="T19" t="n">
-        <v>24.703</v>
+        <v>25.221</v>
       </c>
       <c r="U19" t="n">
-        <v>56.529</v>
+        <v>58.564</v>
       </c>
       <c r="V19" t="n">
-        <v>21.382</v>
+        <v>20.547</v>
       </c>
       <c r="W19" t="n">
-        <v>-51.354</v>
+        <v>-53.479</v>
       </c>
     </row>
     <row r="20">
@@ -4214,14 +4202,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>ALARK.IS, TKFEN.IS</t>
@@ -4233,27 +4221,27 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>83.80706095677104</v>
+        <v>83.80706321463933</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.39% / +1.57% / -1.39% | TKFEN.IS: +14.63% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | TKFEN.IS: +12.70% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>-0.4421646049801775</v>
+        <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2519171994405767</v>
+        <v>-1.633364774066537</v>
       </c>
       <c r="L20" t="n">
-        <v>32.32163079109998</v>
+        <v>32.3216328125</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="O20" t="n">
         <v>42.1</v>
@@ -4276,13 +4264,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>279</v>
+        <v>274.713</v>
       </c>
       <c r="V20" t="n">
-        <v>83.949</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>-41.105</v>
+        <v>-48.601</v>
       </c>
     </row>
     <row r="21">
@@ -4303,49 +4291,49 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, BRSAN.IS, DOHOL.IS, ENJSA.IS</t>
+          <t>ALARK.IS, ALTNY.IS, DOHOL.IS, ENERY.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | BRSAN.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ENJSA.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>63.58450671500058</v>
+        <v>63.58450648919234</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.39% / +1.57% / -1.39% | ALTNY.IS: -1.94% / +0.00% / -3.44% | BRSAN.IS: -2.37% / +0.90% / -2.69% | DOHOL.IS: -2.19% / +0.99% / -2.35% | ENJSA.IS: +0.62% / +2.09% / -0.09%</t>
+          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | ALTNY.IS: -1.43% / +0.00% / -3.44% | DOHOL.IS: -3.18% / +0.99% / -3.26% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.52% / +2.09% / -0.09%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>22.7235340197322</v>
+        <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.697341378772473</v>
+        <v>-10.31805449116768</v>
       </c>
       <c r="L21" t="n">
-        <v>9.664713924402102</v>
+        <v>9.664716767669679</v>
       </c>
       <c r="M21" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>178</v>
+        <v>178.1</v>
       </c>
       <c r="O21" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
@@ -4359,19 +4347,19 @@
         <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>23.371</v>
+        <v>23.897</v>
       </c>
       <c r="T21" t="n">
-        <v>23.371</v>
+        <v>23.897</v>
       </c>
       <c r="U21" t="n">
-        <v>32.406</v>
+        <v>34.485</v>
       </c>
       <c r="V21" t="n">
-        <v>8.288</v>
+        <v>7.544</v>
       </c>
       <c r="W21" t="n">
-        <v>-40.382</v>
+        <v>-42.23</v>
       </c>
     </row>
     <row r="22">
@@ -4392,14 +4380,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>BRSAN.IS, CANTE.IS, DOHOL.IS, ECILC.IS, TKFEN.IS</t>
@@ -4411,27 +4399,27 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>60.21036272243545</v>
+        <v>60.21035987359713</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.71% / +20.03% / -1.13% | CANTE.IS: +5.39% / +15.84% / -2.80% | DOHOL.IS: -2.19% / +0.99% / -2.35% | ECILC.IS: -1.44% / +6.20% / -2.94% | TKFEN.IS: +14.63% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +9.34% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | DOHOL.IS: -3.18% / +0.99% / -3.26% | ECILC.IS: -2.89% / +6.20% / -3.06% | TKFEN.IS: +12.70% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>33.48059234987395</v>
+        <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-8.984606183727273</v>
+        <v>-9.714799709635013</v>
       </c>
       <c r="L22" t="n">
-        <v>19.41140971066007</v>
+        <v>19.41140710190506</v>
       </c>
       <c r="M22" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>138.5</v>
+        <v>138.2</v>
       </c>
       <c r="O22" t="n">
         <v>42.6</v>
@@ -4454,13 +4442,13 @@
         <v>26.15</v>
       </c>
       <c r="U22" t="n">
-        <v>23.939</v>
+        <v>25.28</v>
       </c>
       <c r="V22" t="n">
-        <v>13.156</v>
+        <v>12.249</v>
       </c>
       <c r="W22" t="n">
-        <v>-41.312</v>
+        <v>-43.11</v>
       </c>
     </row>
     <row r="23">
@@ -4481,49 +4469,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BRSAN.IS, DOHOL.IS, ECILC.IS</t>
+          <t>BRSAN.IS, CANTE.IS, DOHOL.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | DOHOL.IS: 2026-08-31 | ECILC.IS: 2026-08-31</t>
+          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-09-02 | DOHOL.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>48.21914486587673</v>
+        <v>48.21914524341393</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.71% / +20.03% / -1.13% | DOHOL.IS: -2.19% / +0.99% / -2.35% | ECILC.IS: -3.49% / +1.22% / -3.47%</t>
+          <t>BRSAN.IS: +9.34% / +20.03% / -1.13% | CANTE.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -3.18% / +0.99% / -3.26%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>21.40028975775241</v>
+        <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.19616237122725</v>
+        <v>-3.286575364070232</v>
       </c>
       <c r="L23" t="n">
-        <v>16.16102122336589</v>
+        <v>16.16102048107813</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>153.5</v>
+        <v>153.7</v>
       </c>
       <c r="O23" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="P23" t="n">
         <v>4.2</v>
@@ -4543,13 +4531,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>19.56</v>
+        <v>21.195</v>
       </c>
       <c r="V23" t="n">
-        <v>2.508</v>
+        <v>1.365</v>
       </c>
       <c r="W23" t="n">
-        <v>-29.905</v>
+        <v>-32.022</v>
       </c>
     </row>
     <row r="24">
@@ -4570,49 +4558,49 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ALARK.IS, DOHOL.IS, ECILC.IS</t>
+          <t>ALARK.IS, CANTE.IS, DOHOL.IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ECILC.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | CANTE.IS: 2026-09-02 | DOHOL.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>38.04089892782267</v>
+        <v>38.04089454478734</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.39% / +1.57% / -1.39% | DOHOL.IS: -2.19% / +0.99% / -2.35% | ECILC.IS: -3.49% / +1.22% / -3.47%</t>
+          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | CANTE.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -3.18% / +0.99% / -3.26%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>13.75066770777271</v>
+        <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.450756566937097</v>
+        <v>-4.513188934672541</v>
       </c>
       <c r="L24" t="n">
-        <v>5.808643018798421</v>
+        <v>5.808640829284117</v>
       </c>
       <c r="M24" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>113.5</v>
+        <v>113.8</v>
       </c>
       <c r="O24" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="P24" t="n">
         <v>2.4</v>
@@ -4626,19 +4614,19 @@
         <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>20.062</v>
+        <v>20.942</v>
       </c>
       <c r="T24" t="n">
-        <v>20.062</v>
+        <v>20.942</v>
       </c>
       <c r="U24" t="n">
-        <v>6.314</v>
+        <v>8.651999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.873</v>
+        <v>-3.942</v>
       </c>
       <c r="W24" t="n">
-        <v>-26.682</v>
+        <v>-28.781</v>
       </c>
     </row>
     <row r="25">
@@ -4659,46 +4647,34 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ALTNY.IS, DOHOL.IS, ECILC.IS</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ALTNY.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ECILC.IS: 2026-08-31</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>28.40087202006096</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>ALTNY.IS: -1.94% / +0.00% / -3.44% | DOHOL.IS: -2.19% / +0.99% / -2.35% | ECILC.IS: -3.49% / +1.22% / -3.47%</t>
-        </is>
-      </c>
+        <v>28.40086810394897</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>15.38513800674384</v>
+        <v>15.38514121842653</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.713342161610269</v>
+        <v>-6.297380057931356</v>
       </c>
       <c r="L25" t="n">
-        <v>5.127815013494629</v>
+        <v>5.127814043936619</v>
       </c>
       <c r="M25" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>76</v>
+        <v>75.8</v>
       </c>
       <c r="O25" t="n">
         <v>49.3</v>
@@ -4708,26 +4684,26 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>12.442</v>
+        <v>12.984</v>
       </c>
       <c r="T25" t="n">
-        <v>12.442</v>
+        <v>12.984</v>
       </c>
       <c r="U25" t="n">
-        <v>7.959</v>
+        <v>8.936</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.004</v>
+        <v>-0.623</v>
       </c>
       <c r="W25" t="n">
-        <v>-15.341</v>
+        <v>-16.255</v>
       </c>
     </row>
     <row r="26">
@@ -4738,62 +4714,62 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
+          <t>ASTOR.IS, KRDMD.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
+          <t>ASTOR.IS: 2026-09-01 | KRDMD.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>23.21519247003325</v>
+        <v>8.530010255723974</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.71% / +20.03% / -1.13% | TKFEN.IS: +14.63% / +31.83% / -0.56%</t>
+          <t>ASTOR.IS: -2.23% / +0.00% / -2.60% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-6.505634231645974</v>
+        <v>0.8142516931666233</v>
       </c>
       <c r="K26" t="n">
-        <v>11.10457161788687</v>
+        <v>6.97606599636289</v>
       </c>
       <c r="L26" t="n">
-        <v>23.2021083711861</v>
+        <v>9.181211458048665</v>
       </c>
       <c r="M26" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>47.5</v>
+        <v>35.9</v>
       </c>
       <c r="O26" t="n">
-        <v>44.2</v>
+        <v>50</v>
       </c>
       <c r="P26" t="n">
-        <v>6.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4804,19 +4780,19 @@
         <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>27.528</v>
+        <v>8.083</v>
       </c>
       <c r="T26" t="n">
-        <v>27.528</v>
+        <v>7.916</v>
       </c>
       <c r="U26" t="n">
-        <v>44.489</v>
+        <v>13.388</v>
       </c>
       <c r="V26" t="n">
-        <v>61.345</v>
+        <v>8.077999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>-13.805</v>
+        <v>-1.707</v>
       </c>
     </row>
     <row r="27">
@@ -4827,62 +4803,62 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ASTOR.IS</t>
+          <t>BRSAN.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-01</t>
+          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>8.530011799530879</v>
+        <v>6.880672511445463</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +9.34% / +20.03% / -1.13% | TKFEN.IS: +12.70% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0.8142534255296985</v>
+        <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>8.192968654145272</v>
+        <v>9.004198403489783</v>
       </c>
       <c r="L27" t="n">
-        <v>9.181211877431517</v>
+        <v>31.31195090134997</v>
       </c>
       <c r="M27" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N27" t="n">
-        <v>35.5</v>
+        <v>48.4</v>
       </c>
       <c r="O27" t="n">
-        <v>50.7</v>
+        <v>43.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4890,22 +4866,22 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
-        <v>8.083</v>
+        <v>28.439</v>
       </c>
       <c r="T27" t="n">
-        <v>7.916</v>
+        <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>14.678</v>
+        <v>37.828</v>
       </c>
       <c r="V27" t="n">
-        <v>9.308</v>
+        <v>51.887</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.417</v>
+        <v>-18.037</v>
       </c>
     </row>
     <row r="28">
@@ -4926,14 +4902,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>ASTOR.IS, FENER.IS</t>
@@ -4945,27 +4921,27 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>-0.4938844333224335</v>
+        <v>-0.49388395046156</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: -2.23% / +0.00% / -2.60% | FENER.IS: -0.99% / +0.04% / -1.25%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>-19.60938072014315</v>
+        <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>9.404806102137364</v>
+        <v>7.664581132672121</v>
       </c>
       <c r="L28" t="n">
-        <v>19.61961180062131</v>
+        <v>19.61961325199098</v>
       </c>
       <c r="M28" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N28" t="n">
-        <v>88</v>
+        <v>87.8</v>
       </c>
       <c r="O28" t="n">
         <v>46</v>
@@ -4988,13 +4964,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>8.077999999999999</v>
+        <v>9.458</v>
       </c>
       <c r="V28" t="n">
-        <v>14.241</v>
+        <v>12.424</v>
       </c>
       <c r="W28" t="n">
-        <v>-5.181</v>
+        <v>-7.101</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -743,12 +743,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ALARK.IS, VAKBN.IS</t>
+          <t>CANTE.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-27 | VAKBN.IS: 2026-09-02</t>
+          <t>CANTE.IS: 2026-09-02 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: -3.67% / +1.46% / -3.65% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-15.36676101799904</v>
+        <v>-15.53788135963107</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -772,13 +772,13 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>102.4</v>
+        <v>102.9</v>
       </c>
       <c r="O3" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="P3" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -789,19 +789,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>21.518</v>
+        <v>21.677</v>
       </c>
       <c r="T3" t="n">
-        <v>21.518</v>
+        <v>21.677</v>
       </c>
       <c r="U3" t="n">
-        <v>58.533</v>
+        <v>58.213</v>
       </c>
       <c r="V3" t="n">
-        <v>14.981</v>
+        <v>14.748</v>
       </c>
       <c r="W3" t="n">
-        <v>-43.467</v>
+        <v>-43.787</v>
       </c>
     </row>
     <row r="4">
@@ -980,12 +980,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ALARK.IS, VAKBN.IS</t>
+          <t>CANTE.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-27 | VAKBN.IS: 2026-09-02</t>
+          <t>CANTE.IS: 2026-09-02 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ALARK.IS: -3.67% / +1.46% / -3.65% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-15.36676101799904</v>
+        <v>-15.53788135963107</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1009,13 +1009,13 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>102.4</v>
+        <v>102.9</v>
       </c>
       <c r="O6" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="P6" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>21.518</v>
+        <v>21.677</v>
       </c>
       <c r="T6" t="n">
-        <v>21.518</v>
+        <v>21.677</v>
       </c>
       <c r="U6" t="n">
-        <v>58.533</v>
+        <v>58.213</v>
       </c>
       <c r="V6" t="n">
-        <v>14.981</v>
+        <v>14.748</v>
       </c>
       <c r="W6" t="n">
-        <v>-43.467</v>
+        <v>-43.787</v>
       </c>
     </row>
     <row r="7">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DOHOL.IS, VAKBN.IS</t>
+          <t>CANTE.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DOHOL.IS: 2026-08-31 | VAKBN.IS: 2026-09-02</t>
+          <t>CANTE.IS: 2026-09-02 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DOHOL.IS: -3.18% / +0.99% / -3.25% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.602895459827383</v>
+        <v>-5.035620267310758</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1096,10 +1096,10 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>134.7</v>
+        <v>135.2</v>
       </c>
       <c r="O7" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>17.08</v>
+        <v>17.456</v>
       </c>
       <c r="T7" t="n">
-        <v>17.08</v>
+        <v>17.456</v>
       </c>
       <c r="U7" t="n">
-        <v>72.139</v>
+        <v>71.358</v>
       </c>
       <c r="V7" t="n">
-        <v>30.537</v>
+        <v>29.945</v>
       </c>
       <c r="W7" t="n">
-        <v>-35.456</v>
+        <v>-36.237</v>
       </c>
     </row>
     <row r="8">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -1.43% / +0.00% / -3.44% | ENERY.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: -2.05% / +0.00% / -2.12%</t>
+          <t>ALTNY.IS: -2.56% / +0.00% / -3.49% | ENERY.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: -2.90% / +0.00% / -3.24%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-15.12733085728632</v>
+        <v>-15.69494759543275</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1200,19 +1200,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>16.458</v>
+        <v>17.017</v>
       </c>
       <c r="T8" t="n">
-        <v>16.458</v>
+        <v>17.017</v>
       </c>
       <c r="U8" t="n">
-        <v>41.935</v>
+        <v>40.986</v>
       </c>
       <c r="V8" t="n">
-        <v>12.685</v>
+        <v>11.931</v>
       </c>
       <c r="W8" t="n">
-        <v>-27.962</v>
+        <v>-28.911</v>
       </c>
     </row>
     <row r="9">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ALARK.IS, VAKBN.IS</t>
+          <t>CANTE.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-27 | VAKBN.IS: 2026-09-02</t>
+          <t>CANTE.IS: 2026-09-02 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ALARK.IS: -3.67% / +1.46% / -3.65% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-15.36676101799904</v>
+        <v>-15.53788135963107</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1270,13 +1270,13 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>102.4</v>
+        <v>102.9</v>
       </c>
       <c r="O9" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="P9" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1287,19 +1287,19 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>21.518</v>
+        <v>21.677</v>
       </c>
       <c r="T9" t="n">
-        <v>21.518</v>
+        <v>21.677</v>
       </c>
       <c r="U9" t="n">
-        <v>58.533</v>
+        <v>58.213</v>
       </c>
       <c r="V9" t="n">
-        <v>14.981</v>
+        <v>14.748</v>
       </c>
       <c r="W9" t="n">
-        <v>-43.467</v>
+        <v>-43.787</v>
       </c>
     </row>
     <row r="10">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FENER.IS: -0.99% / +0.00% / -1.29% | PETKM.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>FENER.IS: -1.31% / +0.65% / -1.62% | PETKM.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.307242823430224</v>
+        <v>-4.369292859264751</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>15.877</v>
+        <v>15.802</v>
       </c>
       <c r="V10" t="n">
-        <v>7.742</v>
+        <v>7.672</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.510999999999999</v>
+        <v>-9.586</v>
       </c>
     </row>
     <row r="11">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -2.23% / +0.00% / -2.60% | FENER.IS: -0.99% / +0.00% / -1.29%</t>
+          <t>ASTOR.IS: -2.94% / +0.00% / -3.31% | FENER.IS: -1.31% / +0.65% / -1.62%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-3.767340978838807</v>
       </c>
       <c r="K12" t="n">
-        <v>10.79666974366784</v>
+        <v>10.21457700670652</v>
       </c>
       <c r="L12" t="n">
         <v>16.57596537747867</v>
@@ -1542,13 +1542,13 @@
         <v>17.404</v>
       </c>
       <c r="U12" t="n">
-        <v>49.859</v>
+        <v>49.071</v>
       </c>
       <c r="V12" t="n">
-        <v>42.434</v>
+        <v>41.686</v>
       </c>
       <c r="W12" t="n">
-        <v>-4.843</v>
+        <v>-5.63</v>
       </c>
     </row>
     <row r="13">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BRSAN.IS, DOHOL.IS, RALYH.IS</t>
+          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-13 | DOHOL.IS: 2026-08-31 | RALYH.IS: 2026-07-13</t>
+          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +10.17% / +20.94% / 0.00% | DOHOL.IS: -3.18% / +0.99% / -3.25% | RALYH.IS: +21.61% / +35.10% / -0.91%</t>
+          <t>BRSAN.IS: +8.42% / +20.94% / 0.00% | RALYH.IS: +21.85% / +35.10% / -0.91% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K13" t="n">
-        <v>10.09821327502263</v>
+        <v>9.275812959084906</v>
       </c>
       <c r="L13" t="n">
         <v>34.56349599547857</v>
@@ -1606,10 +1606,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>69.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>44.3</v>
+        <v>44</v>
       </c>
       <c r="P13" t="n">
         <v>6.1</v>
@@ -1629,13 +1629,13 @@
         <v>23.777</v>
       </c>
       <c r="U13" t="n">
-        <v>45.617</v>
+        <v>44.529</v>
       </c>
       <c r="V13" t="n">
-        <v>39.525</v>
+        <v>38.483</v>
       </c>
       <c r="W13" t="n">
-        <v>-14.421</v>
+        <v>-15.509</v>
       </c>
     </row>
     <row r="14">
@@ -1865,12 +1865,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ALARK.IS, VAKBN.IS</t>
+          <t>CANTE.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-27 | VAKBN.IS: 2026-09-02</t>
+          <t>CANTE.IS: 2026-09-02 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1878,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: -3.67% / +1.46% / -3.65% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-15.36676101799904</v>
+        <v>-15.53788135963107</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1894,13 +1894,13 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>102.4</v>
+        <v>102.9</v>
       </c>
       <c r="O18" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="P18" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1911,19 +1911,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>21.518</v>
+        <v>21.677</v>
       </c>
       <c r="T18" t="n">
-        <v>21.518</v>
+        <v>21.677</v>
       </c>
       <c r="U18" t="n">
-        <v>58.533</v>
+        <v>58.213</v>
       </c>
       <c r="V18" t="n">
-        <v>14.981</v>
+        <v>14.748</v>
       </c>
       <c r="W18" t="n">
-        <v>-43.467</v>
+        <v>-43.787</v>
       </c>
     </row>
     <row r="19">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -1.43% / +0.00% / -3.44% | ENERY.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: -2.05% / +0.00% / -2.12%</t>
+          <t>ALTNY.IS: -2.56% / +0.00% / -3.49% | ENERY.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: -2.90% / +0.00% / -3.24%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-15.12733085728632</v>
+        <v>-15.69494759543275</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2154,19 +2154,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>16.458</v>
+        <v>17.017</v>
       </c>
       <c r="T21" t="n">
-        <v>16.458</v>
+        <v>17.017</v>
       </c>
       <c r="U21" t="n">
-        <v>41.935</v>
+        <v>40.986</v>
       </c>
       <c r="V21" t="n">
-        <v>12.685</v>
+        <v>11.931</v>
       </c>
       <c r="W21" t="n">
-        <v>-27.962</v>
+        <v>-28.911</v>
       </c>
     </row>
     <row r="22">
@@ -2197,12 +2197,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DOHOL.IS, VAKBN.IS</t>
+          <t>CANTE.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DOHOL.IS: 2026-08-31 | VAKBN.IS: 2026-09-02</t>
+          <t>CANTE.IS: 2026-09-02 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2210,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DOHOL.IS: -3.18% / +0.99% / -3.25% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.602895459827383</v>
+        <v>-5.035620267310758</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2226,10 +2226,10 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>134.7</v>
+        <v>135.2</v>
       </c>
       <c r="O22" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
@@ -2243,19 +2243,19 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>17.08</v>
+        <v>17.456</v>
       </c>
       <c r="T22" t="n">
-        <v>17.08</v>
+        <v>17.456</v>
       </c>
       <c r="U22" t="n">
-        <v>72.139</v>
+        <v>71.358</v>
       </c>
       <c r="V22" t="n">
-        <v>30.537</v>
+        <v>29.945</v>
       </c>
       <c r="W22" t="n">
-        <v>-35.456</v>
+        <v>-36.237</v>
       </c>
     </row>
     <row r="23">
@@ -2453,14 +2453,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FENER.IS: -0.99% / +0.00% / -1.29% | PETKM.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>FENER.IS: -1.31% / +0.65% / -1.62% | PETKM.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.307242823430224</v>
+        <v>-4.369292859264751</v>
       </c>
       <c r="L25" t="n">
         <v>4.543450519200398</v>
@@ -2492,13 +2492,13 @@
         <v>10.072</v>
       </c>
       <c r="U25" t="n">
-        <v>15.877</v>
+        <v>15.802</v>
       </c>
       <c r="V25" t="n">
-        <v>7.742</v>
+        <v>7.672</v>
       </c>
       <c r="W25" t="n">
-        <v>-9.510999999999999</v>
+        <v>-9.586</v>
       </c>
     </row>
     <row r="26">
@@ -2542,14 +2542,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -2.23% / +0.00% / -2.60% | FENER.IS: -0.99% / +0.00% / -1.29%</t>
+          <t>ASTOR.IS: -2.94% / +0.00% / -3.31% | FENER.IS: -1.31% / +0.65% / -1.62%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-3.767340978838807</v>
       </c>
       <c r="K26" t="n">
-        <v>10.79666974366784</v>
+        <v>10.21457700670652</v>
       </c>
       <c r="L26" t="n">
         <v>16.57596537747867</v>
@@ -2581,13 +2581,13 @@
         <v>17.404</v>
       </c>
       <c r="U26" t="n">
-        <v>49.859</v>
+        <v>49.071</v>
       </c>
       <c r="V26" t="n">
-        <v>42.434</v>
+        <v>41.686</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.843</v>
+        <v>-5.63</v>
       </c>
     </row>
     <row r="27">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BRSAN.IS, DOHOL.IS, RALYH.IS</t>
+          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-13 | DOHOL.IS: 2026-08-31 | RALYH.IS: 2026-07-13</t>
+          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +10.17% / +20.94% / 0.00% | DOHOL.IS: -3.18% / +0.99% / -3.25% | RALYH.IS: +21.61% / +35.10% / -0.91%</t>
+          <t>BRSAN.IS: +8.42% / +20.94% / 0.00% | RALYH.IS: +21.85% / +35.10% / -0.91% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>10.09821327502263</v>
+        <v>9.275812959084906</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2647,10 +2647,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N27" t="n">
-        <v>69.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>44.3</v>
+        <v>44</v>
       </c>
       <c r="P27" t="n">
         <v>6.1</v>
@@ -2670,13 +2670,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>45.617</v>
+        <v>44.529</v>
       </c>
       <c r="V27" t="n">
-        <v>39.525</v>
+        <v>38.483</v>
       </c>
       <c r="W27" t="n">
-        <v>-14.421</v>
+        <v>-15.509</v>
       </c>
     </row>
   </sheetData>
@@ -2889,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | TKFEN.IS: +12.70% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | TKFEN.IS: +14.36% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.61366876561112</v>
+        <v>-0.6831203050018497</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2928,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>277.418</v>
+        <v>280.988</v>
       </c>
       <c r="V3" t="n">
-        <v>98.196</v>
+        <v>100.071</v>
       </c>
       <c r="W3" t="n">
-        <v>-49.001</v>
+        <v>-45.431</v>
       </c>
     </row>
     <row r="4">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, DOHOL.IS, ENERY.IS, ENJSA.IS</t>
+          <t>ALARK.IS, ALTNY.IS, ASTOR.IS, ENERY.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | ASTOR.IS: 2026-09-02 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2976,14 +2976,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | ALTNY.IS: -1.43% / +0.00% / -3.44% | DOHOL.IS: -3.18% / +0.99% / -3.26% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.52% / +2.09% / -0.09%</t>
+          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.07% / +2.81% / -0.09%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.40172566965912</v>
+        <v>-10.79970291561334</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2992,10 +2992,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>117.3</v>
+        <v>117.8</v>
       </c>
       <c r="O4" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
       <c r="P4" t="n">
         <v>3.9</v>
@@ -3009,19 +3009,19 @@
         <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>25.221</v>
+        <v>25.553</v>
       </c>
       <c r="T4" t="n">
-        <v>25.221</v>
+        <v>25.553</v>
       </c>
       <c r="U4" t="n">
-        <v>58.564</v>
+        <v>57.86</v>
       </c>
       <c r="V4" t="n">
-        <v>20.547</v>
+        <v>20.012</v>
       </c>
       <c r="W4" t="n">
-        <v>-53.479</v>
+        <v>-54.184</v>
       </c>
     </row>
     <row r="5">
@@ -3063,14 +3063,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | TKFEN.IS: +12.70% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | TKFEN.IS: +14.36% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.633364774066537</v>
+        <v>-0.7030026004151702</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3102,13 +3102,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>274.713</v>
+        <v>278.257</v>
       </c>
       <c r="V5" t="n">
-        <v>80.48999999999999</v>
+        <v>82.197</v>
       </c>
       <c r="W5" t="n">
-        <v>-48.601</v>
+        <v>-45.057</v>
       </c>
     </row>
     <row r="6">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BRSAN.IS, CANTE.IS, DOHOL.IS, ECILC.IS, TKFEN.IS</t>
+          <t>ALTNY.IS, BRSAN.IS, CANTE.IS, ENERY.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | DOHOL.IS: 2026-08-31 | ECILC.IS: 2026-08-17 | TKFEN.IS: 2026-08-05</t>
+          <t>ALTNY.IS: 2026-09-02 | BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-02 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3150,14 +3150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.34% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | DOHOL.IS: -3.18% / +0.99% / -3.26% | ECILC.IS: -2.89% / +6.20% / -3.06% | TKFEN.IS: +12.70% / +31.83% / -0.56%</t>
+          <t>ALTNY.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +7.60% / +20.03% / -1.13% | CANTE.IS: +9.45% / +15.84% / -2.80% | ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +14.36% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.714799709635013</v>
+        <v>-9.74469155141071</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3166,10 +3166,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>138.2</v>
+        <v>139.2</v>
       </c>
       <c r="O6" t="n">
-        <v>42.6</v>
+        <v>42.3</v>
       </c>
       <c r="P6" t="n">
         <v>5.7</v>
@@ -3189,13 +3189,13 @@
         <v>26.15</v>
       </c>
       <c r="U6" t="n">
-        <v>25.28</v>
+        <v>25.238</v>
       </c>
       <c r="V6" t="n">
-        <v>12.249</v>
+        <v>12.211</v>
       </c>
       <c r="W6" t="n">
-        <v>-43.11</v>
+        <v>-43.152</v>
       </c>
     </row>
     <row r="7">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, DOHOL.IS, ENERY.IS, ENJSA.IS</t>
+          <t>ALARK.IS, ALTNY.IS, ASTOR.IS, ENERY.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | ASTOR.IS: 2026-09-02 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3237,14 +3237,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | ALTNY.IS: -1.43% / +0.00% / -3.44% | DOHOL.IS: -3.18% / +0.99% / -3.26% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.52% / +2.09% / -0.09%</t>
+          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.07% / +2.81% / -0.09%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.40172566965912</v>
+        <v>-10.79970291561334</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3253,10 +3253,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>117.3</v>
+        <v>117.8</v>
       </c>
       <c r="O7" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
       <c r="P7" t="n">
         <v>3.9</v>
@@ -3270,19 +3270,19 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>25.221</v>
+        <v>25.553</v>
       </c>
       <c r="T7" t="n">
-        <v>25.221</v>
+        <v>25.553</v>
       </c>
       <c r="U7" t="n">
-        <v>58.564</v>
+        <v>57.86</v>
       </c>
       <c r="V7" t="n">
-        <v>20.547</v>
+        <v>20.012</v>
       </c>
       <c r="W7" t="n">
-        <v>-53.479</v>
+        <v>-54.184</v>
       </c>
     </row>
     <row r="8">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BRSAN.IS, CANTE.IS, DOHOL.IS</t>
+          <t>BRSAN.IS, CANTE.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-09-02 | DOHOL.IS: 2026-08-31</t>
+          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -3324,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.34% / +20.03% / -1.13% | CANTE.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -3.18% / +0.99% / -3.26%</t>
+          <t>BRSAN.IS: +7.60% / +20.03% / -1.13% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.286575364070232</v>
+        <v>-3.992878533709088</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3340,10 +3340,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>153.7</v>
+        <v>154.2</v>
       </c>
       <c r="O8" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="P8" t="n">
         <v>4.2</v>
@@ -3363,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>21.195</v>
+        <v>20.309</v>
       </c>
       <c r="V8" t="n">
-        <v>1.365</v>
+        <v>0.625</v>
       </c>
       <c r="W8" t="n">
-        <v>-32.022</v>
+        <v>-32.907</v>
       </c>
     </row>
     <row r="9">
@@ -3406,7 +3406,7 @@
         <v>15.38514121842653</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.297380057931356</v>
+        <v>-7.45137257857702</v>
       </c>
       <c r="L9" t="n">
         <v>5.127814043936619</v>
@@ -3432,19 +3432,19 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>12.984</v>
+        <v>14.056</v>
       </c>
       <c r="T9" t="n">
-        <v>12.984</v>
+        <v>14.056</v>
       </c>
       <c r="U9" t="n">
-        <v>8.936</v>
+        <v>7.594</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.623</v>
+        <v>-1.847</v>
       </c>
       <c r="W9" t="n">
-        <v>-16.255</v>
+        <v>-17.597</v>
       </c>
     </row>
     <row r="10">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ALARK.IS, CANTE.IS, DOHOL.IS</t>
+          <t>ALARK.IS, CANTE.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | CANTE.IS: 2026-09-02 | DOHOL.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -3486,14 +3486,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | CANTE.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -3.18% / +0.99% / -3.26%</t>
+          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.513188934672541</v>
+        <v>-4.713765708883644</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3502,10 +3502,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>113.8</v>
+        <v>114.3</v>
       </c>
       <c r="O10" t="n">
-        <v>49.6</v>
+        <v>49.3</v>
       </c>
       <c r="P10" t="n">
         <v>2.4</v>
@@ -3519,19 +3519,19 @@
         <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>20.942</v>
+        <v>21.108</v>
       </c>
       <c r="T10" t="n">
-        <v>20.942</v>
+        <v>21.108</v>
       </c>
       <c r="U10" t="n">
-        <v>8.651999999999999</v>
+        <v>8.423999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.942</v>
+        <v>-4.144</v>
       </c>
       <c r="W10" t="n">
-        <v>-28.781</v>
+        <v>-29.009</v>
       </c>
     </row>
     <row r="11">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, DOHOL.IS, ENERY.IS, ENJSA.IS</t>
+          <t>ALARK.IS, ALTNY.IS, ASTOR.IS, ENERY.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | ASTOR.IS: 2026-09-02 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -3573,14 +3573,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | ALTNY.IS: -1.43% / +0.00% / -3.44% | DOHOL.IS: -3.18% / +0.99% / -3.26% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.52% / +2.09% / -0.09%</t>
+          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.07% / +2.81% / -0.09%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.31805449116768</v>
+        <v>-10.71640338741797</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3589,10 +3589,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>178.1</v>
+        <v>178.6</v>
       </c>
       <c r="O11" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
@@ -3606,19 +3606,19 @@
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>23.897</v>
+        <v>24.235</v>
       </c>
       <c r="T11" t="n">
-        <v>23.897</v>
+        <v>24.235</v>
       </c>
       <c r="U11" t="n">
-        <v>34.485</v>
+        <v>33.887</v>
       </c>
       <c r="V11" t="n">
-        <v>7.544</v>
+        <v>7.066</v>
       </c>
       <c r="W11" t="n">
-        <v>-42.23</v>
+        <v>-42.828</v>
       </c>
     </row>
     <row r="12">
@@ -3660,14 +3660,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.34% / +20.03% / -1.13% | TKFEN.IS: +12.70% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +7.60% / +20.03% / -1.13% | TKFEN.IS: +14.36% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>9.004198403489783</v>
+        <v>9.022636561173147</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3699,13 +3699,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>37.828</v>
+        <v>37.851</v>
       </c>
       <c r="V12" t="n">
-        <v>51.887</v>
+        <v>51.913</v>
       </c>
       <c r="W12" t="n">
-        <v>-18.037</v>
+        <v>-18.014</v>
       </c>
     </row>
     <row r="13">
@@ -3747,14 +3747,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -2.23% / +0.00% / -2.60% | FENER.IS: -0.99% / +0.04% / -1.25%</t>
+          <t>ASTOR.IS: -2.94% / +0.00% / -3.32% | FENER.IS: -1.31% / +0.69% / -1.58%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K13" t="n">
-        <v>7.664581132672121</v>
+        <v>7.098900428076393</v>
       </c>
       <c r="L13" t="n">
         <v>19.61961325199098</v>
@@ -3786,13 +3786,13 @@
         <v>18.132</v>
       </c>
       <c r="U13" t="n">
-        <v>9.458</v>
+        <v>8.882999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>12.424</v>
+        <v>11.833</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.101</v>
+        <v>-7.677</v>
       </c>
     </row>
     <row r="14">
@@ -3834,14 +3834,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -2.23% / +0.00% / -2.60% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: -2.94% / +0.00% / -3.32% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>0.8142516931666233</v>
       </c>
       <c r="K14" t="n">
-        <v>6.97606599636289</v>
+        <v>6.591874226814332</v>
       </c>
       <c r="L14" t="n">
         <v>9.181211458048665</v>
@@ -3873,13 +3873,13 @@
         <v>7.916</v>
       </c>
       <c r="U14" t="n">
-        <v>13.388</v>
+        <v>12.981</v>
       </c>
       <c r="V14" t="n">
-        <v>8.077999999999999</v>
+        <v>7.69</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.707</v>
+        <v>-2.114</v>
       </c>
     </row>
     <row r="16">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | TKFEN.IS: +12.70% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | TKFEN.IS: +14.36% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.61366876561112</v>
+        <v>-0.6831203050018497</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4086,13 +4086,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>277.418</v>
+        <v>280.988</v>
       </c>
       <c r="V18" t="n">
-        <v>98.196</v>
+        <v>100.071</v>
       </c>
       <c r="W18" t="n">
-        <v>-49.001</v>
+        <v>-45.431</v>
       </c>
     </row>
     <row r="19">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, DOHOL.IS, ENERY.IS, ENJSA.IS</t>
+          <t>ALARK.IS, ALTNY.IS, ASTOR.IS, ENERY.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | ASTOR.IS: 2026-09-02 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -4136,14 +4136,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | ALTNY.IS: -1.43% / +0.00% / -3.44% | DOHOL.IS: -3.18% / +0.99% / -3.26% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.52% / +2.09% / -0.09%</t>
+          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.07% / +2.81% / -0.09%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.40172566965912</v>
+        <v>-10.79970291561334</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4152,10 +4152,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>117.3</v>
+        <v>117.8</v>
       </c>
       <c r="O19" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
       <c r="P19" t="n">
         <v>3.9</v>
@@ -4169,19 +4169,19 @@
         <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>25.221</v>
+        <v>25.553</v>
       </c>
       <c r="T19" t="n">
-        <v>25.221</v>
+        <v>25.553</v>
       </c>
       <c r="U19" t="n">
-        <v>58.564</v>
+        <v>57.86</v>
       </c>
       <c r="V19" t="n">
-        <v>20.547</v>
+        <v>20.012</v>
       </c>
       <c r="W19" t="n">
-        <v>-53.479</v>
+        <v>-54.184</v>
       </c>
     </row>
     <row r="20">
@@ -4225,14 +4225,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | TKFEN.IS: +12.70% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | TKFEN.IS: +14.36% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.633364774066537</v>
+        <v>-0.7030026004151702</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4264,13 +4264,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>274.713</v>
+        <v>278.257</v>
       </c>
       <c r="V20" t="n">
-        <v>80.48999999999999</v>
+        <v>82.197</v>
       </c>
       <c r="W20" t="n">
-        <v>-48.601</v>
+        <v>-45.057</v>
       </c>
     </row>
     <row r="21">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, DOHOL.IS, ENERY.IS, ENJSA.IS</t>
+          <t>ALARK.IS, ALTNY.IS, ASTOR.IS, ENERY.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | DOHOL.IS: 2026-08-31 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | ASTOR.IS: 2026-09-02 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -4314,14 +4314,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | ALTNY.IS: -1.43% / +0.00% / -3.44% | DOHOL.IS: -3.18% / +0.99% / -3.26% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.52% / +2.09% / -0.09%</t>
+          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.07% / +2.81% / -0.09%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.31805449116768</v>
+        <v>-10.71640338741797</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4330,10 +4330,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>178.1</v>
+        <v>178.6</v>
       </c>
       <c r="O21" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
@@ -4347,19 +4347,19 @@
         <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>23.897</v>
+        <v>24.235</v>
       </c>
       <c r="T21" t="n">
-        <v>23.897</v>
+        <v>24.235</v>
       </c>
       <c r="U21" t="n">
-        <v>34.485</v>
+        <v>33.887</v>
       </c>
       <c r="V21" t="n">
-        <v>7.544</v>
+        <v>7.066</v>
       </c>
       <c r="W21" t="n">
-        <v>-42.23</v>
+        <v>-42.828</v>
       </c>
     </row>
     <row r="22">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BRSAN.IS, CANTE.IS, DOHOL.IS, ECILC.IS, TKFEN.IS</t>
+          <t>ALTNY.IS, BRSAN.IS, CANTE.IS, ENERY.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | DOHOL.IS: 2026-08-31 | ECILC.IS: 2026-08-17 | TKFEN.IS: 2026-08-05</t>
+          <t>ALTNY.IS: 2026-09-02 | BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-02 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -4403,14 +4403,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.34% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | DOHOL.IS: -3.18% / +0.99% / -3.26% | ECILC.IS: -2.89% / +6.20% / -3.06% | TKFEN.IS: +12.70% / +31.83% / -0.56%</t>
+          <t>ALTNY.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +7.60% / +20.03% / -1.13% | CANTE.IS: +9.45% / +15.84% / -2.80% | ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +14.36% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-9.714799709635013</v>
+        <v>-9.74469155141071</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4419,10 +4419,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>138.2</v>
+        <v>139.2</v>
       </c>
       <c r="O22" t="n">
-        <v>42.6</v>
+        <v>42.3</v>
       </c>
       <c r="P22" t="n">
         <v>5.7</v>
@@ -4442,13 +4442,13 @@
         <v>26.15</v>
       </c>
       <c r="U22" t="n">
-        <v>25.28</v>
+        <v>25.238</v>
       </c>
       <c r="V22" t="n">
-        <v>12.249</v>
+        <v>12.211</v>
       </c>
       <c r="W22" t="n">
-        <v>-43.11</v>
+        <v>-43.152</v>
       </c>
     </row>
     <row r="23">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BRSAN.IS, CANTE.IS, DOHOL.IS</t>
+          <t>BRSAN.IS, CANTE.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-09-02 | DOHOL.IS: 2026-08-31</t>
+          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -4492,14 +4492,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.34% / +20.03% / -1.13% | CANTE.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -3.18% / +0.99% / -3.26%</t>
+          <t>BRSAN.IS: +7.60% / +20.03% / -1.13% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.286575364070232</v>
+        <v>-3.992878533709088</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4508,10 +4508,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>153.7</v>
+        <v>154.2</v>
       </c>
       <c r="O23" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="P23" t="n">
         <v>4.2</v>
@@ -4531,13 +4531,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>21.195</v>
+        <v>20.309</v>
       </c>
       <c r="V23" t="n">
-        <v>1.365</v>
+        <v>0.625</v>
       </c>
       <c r="W23" t="n">
-        <v>-32.022</v>
+        <v>-32.907</v>
       </c>
     </row>
     <row r="24">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ALARK.IS, CANTE.IS, DOHOL.IS</t>
+          <t>ALARK.IS, CANTE.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | CANTE.IS: 2026-09-02 | DOHOL.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -4581,14 +4581,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.51% / +1.57% / -2.49% | CANTE.IS: -0.02% / +0.00% / 0.00% | DOHOL.IS: -3.18% / +0.99% / -3.26%</t>
+          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.513188934672541</v>
+        <v>-4.713765708883644</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4597,10 +4597,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>113.8</v>
+        <v>114.3</v>
       </c>
       <c r="O24" t="n">
-        <v>49.6</v>
+        <v>49.3</v>
       </c>
       <c r="P24" t="n">
         <v>2.4</v>
@@ -4614,19 +4614,19 @@
         <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>20.942</v>
+        <v>21.108</v>
       </c>
       <c r="T24" t="n">
-        <v>20.942</v>
+        <v>21.108</v>
       </c>
       <c r="U24" t="n">
-        <v>8.651999999999999</v>
+        <v>8.423999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.942</v>
+        <v>-4.144</v>
       </c>
       <c r="W24" t="n">
-        <v>-28.781</v>
+        <v>-29.009</v>
       </c>
     </row>
     <row r="25">
@@ -4665,7 +4665,7 @@
         <v>15.38514121842653</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.297380057931356</v>
+        <v>-7.45137257857702</v>
       </c>
       <c r="L25" t="n">
         <v>5.127814043936619</v>
@@ -4691,19 +4691,19 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>12.984</v>
+        <v>14.056</v>
       </c>
       <c r="T25" t="n">
-        <v>12.984</v>
+        <v>14.056</v>
       </c>
       <c r="U25" t="n">
-        <v>8.936</v>
+        <v>7.594</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.623</v>
+        <v>-1.847</v>
       </c>
       <c r="W25" t="n">
-        <v>-16.255</v>
+        <v>-17.597</v>
       </c>
     </row>
     <row r="26">
@@ -4747,14 +4747,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -2.23% / +0.00% / -2.60% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: -2.94% / +0.00% / -3.32% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>0.8142516931666233</v>
       </c>
       <c r="K26" t="n">
-        <v>6.97606599636289</v>
+        <v>6.591874226814332</v>
       </c>
       <c r="L26" t="n">
         <v>9.181211458048665</v>
@@ -4786,13 +4786,13 @@
         <v>7.916</v>
       </c>
       <c r="U26" t="n">
-        <v>13.388</v>
+        <v>12.981</v>
       </c>
       <c r="V26" t="n">
-        <v>8.077999999999999</v>
+        <v>7.69</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.707</v>
+        <v>-2.114</v>
       </c>
     </row>
     <row r="27">
@@ -4836,14 +4836,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.34% / +20.03% / -1.13% | TKFEN.IS: +12.70% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +7.60% / +20.03% / -1.13% | TKFEN.IS: +14.36% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>9.004198403489783</v>
+        <v>9.022636561173147</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4875,13 +4875,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>37.828</v>
+        <v>37.851</v>
       </c>
       <c r="V27" t="n">
-        <v>51.887</v>
+        <v>51.913</v>
       </c>
       <c r="W27" t="n">
-        <v>-18.037</v>
+        <v>-18.014</v>
       </c>
     </row>
     <row r="28">
@@ -4925,14 +4925,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -2.23% / +0.00% / -2.60% | FENER.IS: -0.99% / +0.04% / -1.25%</t>
+          <t>ASTOR.IS: -2.94% / +0.00% / -3.32% | FENER.IS: -1.31% / +0.69% / -1.58%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>7.664581132672121</v>
+        <v>7.098900428076393</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4964,13 +4964,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>9.458</v>
+        <v>8.882999999999999</v>
       </c>
       <c r="V28" t="n">
-        <v>12.424</v>
+        <v>11.833</v>
       </c>
       <c r="W28" t="n">
-        <v>-7.101</v>
+        <v>-7.677</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -2.56% / +0.00% / -3.49% | ENERY.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: -2.90% / +0.00% / -3.24%</t>
+          <t>ALTNY.IS: -3.23% / +0.00% / -3.49% | ENERY.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: -0.56% / +0.09% / -3.24%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-15.69494759543275</v>
+        <v>-15.21815302569316</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1200,19 +1200,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>17.017</v>
+        <v>16.547</v>
       </c>
       <c r="T8" t="n">
-        <v>17.017</v>
+        <v>16.547</v>
       </c>
       <c r="U8" t="n">
-        <v>40.986</v>
+        <v>41.783</v>
       </c>
       <c r="V8" t="n">
-        <v>11.931</v>
+        <v>12.564</v>
       </c>
       <c r="W8" t="n">
-        <v>-28.911</v>
+        <v>-28.113</v>
       </c>
     </row>
     <row r="9">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FENER.IS: -1.31% / +0.65% / -1.62% | PETKM.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>FENER.IS: -0.34% / +0.65% / -1.62% | PETKM.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.369292859264751</v>
+        <v>-4.183142751761104</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>15.802</v>
+        <v>16.027</v>
       </c>
       <c r="V10" t="n">
-        <v>7.672</v>
+        <v>7.882</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.586</v>
+        <v>-9.361000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -2.94% / +0.00% / -3.31% | FENER.IS: -1.31% / +0.65% / -1.62%</t>
+          <t>ASTOR.IS: +0.14% / +0.39% / -3.31% | FENER.IS: -0.34% / +0.65% / -1.62%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-3.767340978838807</v>
       </c>
       <c r="K12" t="n">
-        <v>10.21457700670652</v>
+        <v>12.49402354583942</v>
       </c>
       <c r="L12" t="n">
         <v>16.57596537747867</v>
@@ -1522,7 +1522,7 @@
         <v>88</v>
       </c>
       <c r="O12" t="n">
-        <v>47.5</v>
+        <v>48</v>
       </c>
       <c r="P12" t="n">
         <v>2.5</v>
@@ -1542,13 +1542,13 @@
         <v>17.404</v>
       </c>
       <c r="U12" t="n">
-        <v>49.071</v>
+        <v>52.155</v>
       </c>
       <c r="V12" t="n">
-        <v>41.686</v>
+        <v>44.616</v>
       </c>
       <c r="W12" t="n">
-        <v>-5.63</v>
+        <v>-2.547</v>
       </c>
     </row>
     <row r="13">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.42% / +20.94% / 0.00% | RALYH.IS: +21.85% / +35.10% / -0.91% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +9.53% / +20.94% / 0.00% | RALYH.IS: +25.22% / +35.10% / -0.91% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K13" t="n">
-        <v>9.275812959084906</v>
+        <v>10.67598218073205</v>
       </c>
       <c r="L13" t="n">
         <v>34.56349599547857</v>
@@ -1629,13 +1629,13 @@
         <v>23.777</v>
       </c>
       <c r="U13" t="n">
-        <v>44.529</v>
+        <v>46.381</v>
       </c>
       <c r="V13" t="n">
-        <v>38.483</v>
+        <v>40.257</v>
       </c>
       <c r="W13" t="n">
-        <v>-15.509</v>
+        <v>-13.657</v>
       </c>
     </row>
     <row r="14">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -2.56% / +0.00% / -3.49% | ENERY.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: -2.90% / +0.00% / -3.24%</t>
+          <t>ALTNY.IS: -3.23% / +0.00% / -3.49% | ENERY.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: -0.56% / +0.09% / -3.24%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-15.69494759543275</v>
+        <v>-15.21815302569316</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2154,19 +2154,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>17.017</v>
+        <v>16.547</v>
       </c>
       <c r="T21" t="n">
-        <v>17.017</v>
+        <v>16.547</v>
       </c>
       <c r="U21" t="n">
-        <v>40.986</v>
+        <v>41.783</v>
       </c>
       <c r="V21" t="n">
-        <v>11.931</v>
+        <v>12.564</v>
       </c>
       <c r="W21" t="n">
-        <v>-28.911</v>
+        <v>-28.113</v>
       </c>
     </row>
     <row r="22">
@@ -2453,14 +2453,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FENER.IS: -1.31% / +0.65% / -1.62% | PETKM.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>FENER.IS: -0.34% / +0.65% / -1.62% | PETKM.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.369292859264751</v>
+        <v>-4.183142751761104</v>
       </c>
       <c r="L25" t="n">
         <v>4.543450519200398</v>
@@ -2492,13 +2492,13 @@
         <v>10.072</v>
       </c>
       <c r="U25" t="n">
-        <v>15.802</v>
+        <v>16.027</v>
       </c>
       <c r="V25" t="n">
-        <v>7.672</v>
+        <v>7.882</v>
       </c>
       <c r="W25" t="n">
-        <v>-9.586</v>
+        <v>-9.361000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2542,14 +2542,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -2.94% / +0.00% / -3.31% | FENER.IS: -1.31% / +0.65% / -1.62%</t>
+          <t>ASTOR.IS: +0.14% / +0.39% / -3.31% | FENER.IS: -0.34% / +0.65% / -1.62%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-3.767340978838807</v>
       </c>
       <c r="K26" t="n">
-        <v>10.21457700670652</v>
+        <v>12.49402354583942</v>
       </c>
       <c r="L26" t="n">
         <v>16.57596537747867</v>
@@ -2561,7 +2561,7 @@
         <v>88</v>
       </c>
       <c r="O26" t="n">
-        <v>47.5</v>
+        <v>48</v>
       </c>
       <c r="P26" t="n">
         <v>2.5</v>
@@ -2581,13 +2581,13 @@
         <v>17.404</v>
       </c>
       <c r="U26" t="n">
-        <v>49.071</v>
+        <v>52.155</v>
       </c>
       <c r="V26" t="n">
-        <v>41.686</v>
+        <v>44.616</v>
       </c>
       <c r="W26" t="n">
-        <v>-5.63</v>
+        <v>-2.547</v>
       </c>
     </row>
     <row r="27">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.42% / +20.94% / 0.00% | RALYH.IS: +21.85% / +35.10% / -0.91% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +9.53% / +20.94% / 0.00% | RALYH.IS: +25.22% / +35.10% / -0.91% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>9.275812959084906</v>
+        <v>10.67598218073205</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2670,13 +2670,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>44.529</v>
+        <v>46.381</v>
       </c>
       <c r="V27" t="n">
-        <v>38.483</v>
+        <v>40.257</v>
       </c>
       <c r="W27" t="n">
-        <v>-15.509</v>
+        <v>-13.657</v>
       </c>
     </row>
   </sheetData>
@@ -2711,7 +2711,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2889,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | TKFEN.IS: +14.36% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | TKFEN.IS: +11.58% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6831203050018497</v>
+        <v>-0.2627514567618672</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2908,7 +2908,7 @@
         <v>92.8</v>
       </c>
       <c r="O3" t="n">
-        <v>44.1</v>
+        <v>44.6</v>
       </c>
       <c r="P3" t="n">
         <v>4.3</v>
@@ -2928,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>280.988</v>
+        <v>282.601</v>
       </c>
       <c r="V3" t="n">
-        <v>100.071</v>
+        <v>100.918</v>
       </c>
       <c r="W3" t="n">
-        <v>-45.431</v>
+        <v>-43.819</v>
       </c>
     </row>
     <row r="4">
@@ -2976,14 +2976,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.07% / +2.81% / -0.09%</t>
+          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | ALTNY.IS: -3.23% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.34% / +3.27% / -0.09%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.79970291561334</v>
+        <v>-9.965632173979866</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2995,7 +2995,7 @@
         <v>117.8</v>
       </c>
       <c r="O4" t="n">
-        <v>46.6</v>
+        <v>47</v>
       </c>
       <c r="P4" t="n">
         <v>3.9</v>
@@ -3009,19 +3009,19 @@
         <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>25.553</v>
+        <v>24.857</v>
       </c>
       <c r="T4" t="n">
-        <v>25.553</v>
+        <v>24.857</v>
       </c>
       <c r="U4" t="n">
-        <v>57.86</v>
+        <v>59.336</v>
       </c>
       <c r="V4" t="n">
-        <v>20.012</v>
+        <v>21.134</v>
       </c>
       <c r="W4" t="n">
-        <v>-54.184</v>
+        <v>-52.707</v>
       </c>
     </row>
     <row r="5">
@@ -3063,14 +3063,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | TKFEN.IS: +14.36% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | TKFEN.IS: +11.58% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7030026004151702</v>
+        <v>-0.2827179060234664</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3082,7 +3082,7 @@
         <v>81.8</v>
       </c>
       <c r="O5" t="n">
-        <v>42.1</v>
+        <v>42.7</v>
       </c>
       <c r="P5" t="n">
         <v>4.7</v>
@@ -3102,13 +3102,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>278.257</v>
+        <v>279.858</v>
       </c>
       <c r="V5" t="n">
-        <v>82.197</v>
+        <v>82.968</v>
       </c>
       <c r="W5" t="n">
-        <v>-45.057</v>
+        <v>-43.456</v>
       </c>
     </row>
     <row r="6">
@@ -3150,14 +3150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +7.60% / +20.03% / -1.13% | CANTE.IS: +9.45% / +15.84% / -2.80% | ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +14.36% / +31.83% / -0.56%</t>
+          <t>ALTNY.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +8.71% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +11.58% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.74469155141071</v>
+        <v>-10.35517153976994</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3189,13 +3189,13 @@
         <v>26.15</v>
       </c>
       <c r="U6" t="n">
-        <v>25.238</v>
+        <v>24.391</v>
       </c>
       <c r="V6" t="n">
-        <v>12.211</v>
+        <v>11.452</v>
       </c>
       <c r="W6" t="n">
-        <v>-43.152</v>
+        <v>-43.999</v>
       </c>
     </row>
     <row r="7">
@@ -3237,14 +3237,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.07% / +2.81% / -0.09%</t>
+          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | ALTNY.IS: -3.23% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.34% / +3.27% / -0.09%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.79970291561334</v>
+        <v>-9.965632173979866</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3256,7 +3256,7 @@
         <v>117.8</v>
       </c>
       <c r="O7" t="n">
-        <v>46.6</v>
+        <v>47</v>
       </c>
       <c r="P7" t="n">
         <v>3.9</v>
@@ -3270,19 +3270,19 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>25.553</v>
+        <v>24.857</v>
       </c>
       <c r="T7" t="n">
-        <v>25.553</v>
+        <v>24.857</v>
       </c>
       <c r="U7" t="n">
-        <v>57.86</v>
+        <v>59.336</v>
       </c>
       <c r="V7" t="n">
-        <v>20.012</v>
+        <v>21.134</v>
       </c>
       <c r="W7" t="n">
-        <v>-54.184</v>
+        <v>-52.707</v>
       </c>
     </row>
     <row r="8">
@@ -3324,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +7.60% / +20.03% / -1.13% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.992878533709088</v>
+        <v>-3.721058835851221</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3363,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>20.309</v>
+        <v>20.65</v>
       </c>
       <c r="V8" t="n">
-        <v>0.625</v>
+        <v>0.91</v>
       </c>
       <c r="W8" t="n">
-        <v>-32.907</v>
+        <v>-32.566</v>
       </c>
     </row>
     <row r="9">
@@ -3406,7 +3406,7 @@
         <v>15.38514121842653</v>
       </c>
       <c r="K9" t="n">
-        <v>-7.45137257857702</v>
+        <v>-6.632543801829504</v>
       </c>
       <c r="L9" t="n">
         <v>5.127814043936619</v>
@@ -3432,19 +3432,19 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>14.056</v>
+        <v>13.295</v>
       </c>
       <c r="T9" t="n">
-        <v>14.056</v>
+        <v>13.295</v>
       </c>
       <c r="U9" t="n">
-        <v>7.594</v>
+        <v>8.545999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.847</v>
+        <v>-0.979</v>
       </c>
       <c r="W9" t="n">
-        <v>-17.597</v>
+        <v>-16.645</v>
       </c>
     </row>
     <row r="10">
@@ -3486,14 +3486,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.713765708883644</v>
+        <v>-3.659799766004945</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3505,7 +3505,7 @@
         <v>114.3</v>
       </c>
       <c r="O10" t="n">
-        <v>49.3</v>
+        <v>49.8</v>
       </c>
       <c r="P10" t="n">
         <v>2.4</v>
@@ -3519,19 +3519,19 @@
         <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>21.108</v>
+        <v>20.235</v>
       </c>
       <c r="T10" t="n">
-        <v>21.108</v>
+        <v>20.235</v>
       </c>
       <c r="U10" t="n">
-        <v>8.423999999999999</v>
+        <v>9.624000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.144</v>
+        <v>-3.083</v>
       </c>
       <c r="W10" t="n">
-        <v>-29.009</v>
+        <v>-27.81</v>
       </c>
     </row>
     <row r="11">
@@ -3573,14 +3573,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.07% / +2.81% / -0.09%</t>
+          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | ALTNY.IS: -3.23% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.34% / +3.27% / -0.09%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.71640338741797</v>
+        <v>-9.881553750404859</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3592,7 +3592,7 @@
         <v>178.6</v>
       </c>
       <c r="O11" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
@@ -3606,19 +3606,19 @@
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>24.235</v>
+        <v>23.527</v>
       </c>
       <c r="T11" t="n">
-        <v>24.235</v>
+        <v>23.527</v>
       </c>
       <c r="U11" t="n">
-        <v>33.887</v>
+        <v>35.139</v>
       </c>
       <c r="V11" t="n">
-        <v>7.066</v>
+        <v>8.067</v>
       </c>
       <c r="W11" t="n">
-        <v>-42.828</v>
+        <v>-41.576</v>
       </c>
     </row>
     <row r="12">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3647,42 +3647,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
+          <t>ASTOR.IS, FENER.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
+          <t>ASTOR.IS: 2026-09-01 | FENER.IS: 2026-09-01</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6.880672511445463</v>
+        <v>-0.49388395046156</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +7.60% / +20.03% / -1.13% | TKFEN.IS: +14.36% / +31.83% / -0.56%</t>
+          <t>ASTOR.IS: +0.14% / +0.39% / -3.32% | FENER.IS: -0.34% / +0.69% / -1.58%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-18.9000927288166</v>
+        <v>-19.60937535624424</v>
       </c>
       <c r="K12" t="n">
-        <v>9.022636561173147</v>
+        <v>9.314143135238373</v>
       </c>
       <c r="L12" t="n">
-        <v>31.31195090134997</v>
+        <v>19.61961325199098</v>
       </c>
       <c r="M12" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N12" t="n">
-        <v>48.4</v>
+        <v>87.8</v>
       </c>
       <c r="O12" t="n">
-        <v>43.3</v>
+        <v>46.6</v>
       </c>
       <c r="P12" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3693,19 +3693,19 @@
         <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>28.439</v>
+        <v>18.132</v>
       </c>
       <c r="T12" t="n">
-        <v>28.439</v>
+        <v>18.132</v>
       </c>
       <c r="U12" t="n">
-        <v>37.851</v>
+        <v>11.135</v>
       </c>
       <c r="V12" t="n">
-        <v>51.913</v>
+        <v>14.146</v>
       </c>
       <c r="W12" t="n">
-        <v>-18.014</v>
+        <v>-5.424</v>
       </c>
     </row>
     <row r="13">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
+          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3734,39 +3734,39 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASTOR.IS, FENER.IS</t>
+          <t>ASTOR.IS, KRDMD.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-01 | FENER.IS: 2026-09-01</t>
+          <t>ASTOR.IS: 2026-09-01 | KRDMD.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-0.49388395046156</v>
+        <v>8.530010255723974</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -2.94% / +0.00% / -3.32% | FENER.IS: -1.31% / +0.69% / -1.58%</t>
+          <t>ASTOR.IS: +0.14% / +0.39% / -3.32% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-19.60937535624424</v>
+        <v>0.8142516931666233</v>
       </c>
       <c r="K13" t="n">
-        <v>7.098900428076393</v>
+        <v>8.256724474506161</v>
       </c>
       <c r="L13" t="n">
-        <v>19.61961325199098</v>
+        <v>9.181211458048665</v>
       </c>
       <c r="M13" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N13" t="n">
-        <v>87.8</v>
+        <v>35.9</v>
       </c>
       <c r="O13" t="n">
-        <v>46</v>
+        <v>51.4</v>
       </c>
       <c r="P13" t="n">
         <v>2.2</v>
@@ -3780,19 +3780,19 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>18.132</v>
+        <v>8.083</v>
       </c>
       <c r="T13" t="n">
-        <v>18.132</v>
+        <v>7.916</v>
       </c>
       <c r="U13" t="n">
-        <v>8.882999999999999</v>
+        <v>14.745</v>
       </c>
       <c r="V13" t="n">
-        <v>11.833</v>
+        <v>9.372</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.677</v>
+        <v>-0.349</v>
       </c>
     </row>
     <row r="14">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3821,42 +3821,42 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASTOR.IS, KRDMD.IS</t>
+          <t>BRSAN.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-01 | KRDMD.IS: 2026-09-02</t>
+          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8.530010255723974</v>
+        <v>6.880672511445463</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -2.94% / +0.00% / -3.32% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | TKFEN.IS: +11.58% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.8142516931666233</v>
+        <v>-18.9000927288166</v>
       </c>
       <c r="K14" t="n">
-        <v>6.591874226814332</v>
+        <v>8.134533393956911</v>
       </c>
       <c r="L14" t="n">
-        <v>9.181211458048665</v>
+        <v>31.31195090134997</v>
       </c>
       <c r="M14" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N14" t="n">
-        <v>35.9</v>
+        <v>48.4</v>
       </c>
       <c r="O14" t="n">
-        <v>50</v>
+        <v>43.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3867,19 +3867,19 @@
         <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>8.083</v>
+        <v>28.439</v>
       </c>
       <c r="T14" t="n">
-        <v>7.916</v>
+        <v>28.439</v>
       </c>
       <c r="U14" t="n">
-        <v>12.981</v>
+        <v>36.728</v>
       </c>
       <c r="V14" t="n">
-        <v>7.69</v>
+        <v>50.675</v>
       </c>
       <c r="W14" t="n">
-        <v>-2.114</v>
+        <v>-19.137</v>
       </c>
     </row>
     <row r="16">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | TKFEN.IS: +14.36% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | TKFEN.IS: +11.58% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6831203050018497</v>
+        <v>-0.2627514567618672</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4066,7 +4066,7 @@
         <v>92.8</v>
       </c>
       <c r="O18" t="n">
-        <v>44.1</v>
+        <v>44.6</v>
       </c>
       <c r="P18" t="n">
         <v>4.3</v>
@@ -4086,13 +4086,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>280.988</v>
+        <v>282.601</v>
       </c>
       <c r="V18" t="n">
-        <v>100.071</v>
+        <v>100.918</v>
       </c>
       <c r="W18" t="n">
-        <v>-45.431</v>
+        <v>-43.819</v>
       </c>
     </row>
     <row r="19">
@@ -4136,14 +4136,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.07% / +2.81% / -0.09%</t>
+          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | ALTNY.IS: -3.23% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.34% / +3.27% / -0.09%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.79970291561334</v>
+        <v>-9.965632173979866</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4155,7 +4155,7 @@
         <v>117.8</v>
       </c>
       <c r="O19" t="n">
-        <v>46.6</v>
+        <v>47</v>
       </c>
       <c r="P19" t="n">
         <v>3.9</v>
@@ -4169,19 +4169,19 @@
         <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>25.553</v>
+        <v>24.857</v>
       </c>
       <c r="T19" t="n">
-        <v>25.553</v>
+        <v>24.857</v>
       </c>
       <c r="U19" t="n">
-        <v>57.86</v>
+        <v>59.336</v>
       </c>
       <c r="V19" t="n">
-        <v>20.012</v>
+        <v>21.134</v>
       </c>
       <c r="W19" t="n">
-        <v>-54.184</v>
+        <v>-52.707</v>
       </c>
     </row>
     <row r="20">
@@ -4225,14 +4225,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | TKFEN.IS: +14.36% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | TKFEN.IS: +11.58% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7030026004151702</v>
+        <v>-0.2827179060234664</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4244,7 +4244,7 @@
         <v>81.8</v>
       </c>
       <c r="O20" t="n">
-        <v>42.1</v>
+        <v>42.7</v>
       </c>
       <c r="P20" t="n">
         <v>4.7</v>
@@ -4264,13 +4264,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>278.257</v>
+        <v>279.858</v>
       </c>
       <c r="V20" t="n">
-        <v>82.197</v>
+        <v>82.968</v>
       </c>
       <c r="W20" t="n">
-        <v>-45.057</v>
+        <v>-43.456</v>
       </c>
     </row>
     <row r="21">
@@ -4314,14 +4314,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +1.07% / +2.81% / -0.09%</t>
+          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | ALTNY.IS: -3.23% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.34% / +3.27% / -0.09%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.71640338741797</v>
+        <v>-9.881553750404859</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4333,7 +4333,7 @@
         <v>178.6</v>
       </c>
       <c r="O21" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
@@ -4347,19 +4347,19 @@
         <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>24.235</v>
+        <v>23.527</v>
       </c>
       <c r="T21" t="n">
-        <v>24.235</v>
+        <v>23.527</v>
       </c>
       <c r="U21" t="n">
-        <v>33.887</v>
+        <v>35.139</v>
       </c>
       <c r="V21" t="n">
-        <v>7.066</v>
+        <v>8.067</v>
       </c>
       <c r="W21" t="n">
-        <v>-42.828</v>
+        <v>-41.576</v>
       </c>
     </row>
     <row r="22">
@@ -4403,14 +4403,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +7.60% / +20.03% / -1.13% | CANTE.IS: +9.45% / +15.84% / -2.80% | ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +14.36% / +31.83% / -0.56%</t>
+          <t>ALTNY.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +8.71% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +11.58% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-9.74469155141071</v>
+        <v>-10.35517153976994</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4442,13 +4442,13 @@
         <v>26.15</v>
       </c>
       <c r="U22" t="n">
-        <v>25.238</v>
+        <v>24.391</v>
       </c>
       <c r="V22" t="n">
-        <v>12.211</v>
+        <v>11.452</v>
       </c>
       <c r="W22" t="n">
-        <v>-43.152</v>
+        <v>-43.999</v>
       </c>
     </row>
     <row r="23">
@@ -4492,14 +4492,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +7.60% / +20.03% / -1.13% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.992878533709088</v>
+        <v>-3.721058835851221</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4531,13 +4531,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>20.309</v>
+        <v>20.65</v>
       </c>
       <c r="V23" t="n">
-        <v>0.625</v>
+        <v>0.91</v>
       </c>
       <c r="W23" t="n">
-        <v>-32.907</v>
+        <v>-32.566</v>
       </c>
     </row>
     <row r="24">
@@ -4581,14 +4581,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: -2.24% / +1.57% / -3.23% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.713765708883644</v>
+        <v>-3.659799766004945</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4600,7 +4600,7 @@
         <v>114.3</v>
       </c>
       <c r="O24" t="n">
-        <v>49.3</v>
+        <v>49.8</v>
       </c>
       <c r="P24" t="n">
         <v>2.4</v>
@@ -4614,19 +4614,19 @@
         <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>21.108</v>
+        <v>20.235</v>
       </c>
       <c r="T24" t="n">
-        <v>21.108</v>
+        <v>20.235</v>
       </c>
       <c r="U24" t="n">
-        <v>8.423999999999999</v>
+        <v>9.624000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>-4.144</v>
+        <v>-3.083</v>
       </c>
       <c r="W24" t="n">
-        <v>-29.009</v>
+        <v>-27.81</v>
       </c>
     </row>
     <row r="25">
@@ -4665,7 +4665,7 @@
         <v>15.38514121842653</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.45137257857702</v>
+        <v>-6.632543801829504</v>
       </c>
       <c r="L25" t="n">
         <v>5.127814043936619</v>
@@ -4691,19 +4691,19 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>14.056</v>
+        <v>13.295</v>
       </c>
       <c r="T25" t="n">
-        <v>14.056</v>
+        <v>13.295</v>
       </c>
       <c r="U25" t="n">
-        <v>7.594</v>
+        <v>8.545999999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.847</v>
+        <v>-0.979</v>
       </c>
       <c r="W25" t="n">
-        <v>-17.597</v>
+        <v>-16.645</v>
       </c>
     </row>
     <row r="26">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4747,14 +4747,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -2.94% / +0.00% / -3.32% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: +0.14% / +0.39% / -3.32% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>0.8142516931666233</v>
       </c>
       <c r="K26" t="n">
-        <v>6.591874226814332</v>
+        <v>8.256724474506161</v>
       </c>
       <c r="L26" t="n">
         <v>9.181211458048665</v>
@@ -4766,7 +4766,7 @@
         <v>35.9</v>
       </c>
       <c r="O26" t="n">
-        <v>50</v>
+        <v>51.4</v>
       </c>
       <c r="P26" t="n">
         <v>2.2</v>
@@ -4786,13 +4786,13 @@
         <v>7.916</v>
       </c>
       <c r="U26" t="n">
-        <v>12.981</v>
+        <v>14.745</v>
       </c>
       <c r="V26" t="n">
-        <v>7.69</v>
+        <v>9.372</v>
       </c>
       <c r="W26" t="n">
-        <v>-2.114</v>
+        <v>-0.349</v>
       </c>
     </row>
     <row r="27">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4836,14 +4836,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +7.60% / +20.03% / -1.13% | TKFEN.IS: +14.36% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | TKFEN.IS: +11.58% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>9.022636561173147</v>
+        <v>8.134533393956911</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4875,13 +4875,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>37.851</v>
+        <v>36.728</v>
       </c>
       <c r="V27" t="n">
-        <v>51.913</v>
+        <v>50.675</v>
       </c>
       <c r="W27" t="n">
-        <v>-18.014</v>
+        <v>-19.137</v>
       </c>
     </row>
     <row r="28">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4925,14 +4925,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -2.94% / +0.00% / -3.32% | FENER.IS: -1.31% / +0.69% / -1.58%</t>
+          <t>ASTOR.IS: +0.14% / +0.39% / -3.32% | FENER.IS: -0.34% / +0.69% / -1.58%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>7.098900428076393</v>
+        <v>9.314143135238373</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4944,7 +4944,7 @@
         <v>87.8</v>
       </c>
       <c r="O28" t="n">
-        <v>46</v>
+        <v>46.6</v>
       </c>
       <c r="P28" t="n">
         <v>2.2</v>
@@ -4964,13 +4964,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>8.882999999999999</v>
+        <v>11.135</v>
       </c>
       <c r="V28" t="n">
-        <v>11.833</v>
+        <v>14.146</v>
       </c>
       <c r="W28" t="n">
-        <v>-7.677</v>
+        <v>-5.424</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -3.23% / +0.00% / -3.49% | ENERY.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: -0.56% / +0.09% / -3.24%</t>
+          <t>ALTNY.IS: -1.65% / +0.00% / -3.49% | ENERY.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: +0.43% / +0.68% / -3.24%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-15.21815302569316</v>
+        <v>-14.4827919160602</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1186,7 +1186,7 @@
         <v>191.9</v>
       </c>
       <c r="O8" t="n">
-        <v>46.6</v>
+        <v>46.9</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1200,19 +1200,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>16.547</v>
+        <v>15.824</v>
       </c>
       <c r="T8" t="n">
-        <v>16.547</v>
+        <v>15.824</v>
       </c>
       <c r="U8" t="n">
-        <v>41.783</v>
+        <v>43.013</v>
       </c>
       <c r="V8" t="n">
-        <v>12.564</v>
+        <v>13.541</v>
       </c>
       <c r="W8" t="n">
-        <v>-28.113</v>
+        <v>-26.884</v>
       </c>
     </row>
     <row r="9">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FENER.IS: -0.34% / +0.65% / -1.62% | PETKM.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>FENER.IS: -1.31% / +0.65% / -1.62% | PETKM.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.183142751761104</v>
+        <v>-4.369292859264751</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>16.027</v>
+        <v>15.802</v>
       </c>
       <c r="V10" t="n">
-        <v>7.882</v>
+        <v>7.672</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.361000000000001</v>
+        <v>-9.586</v>
       </c>
     </row>
     <row r="11">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +0.14% / +0.39% / -3.31% | FENER.IS: -0.34% / +0.65% / -1.62%</t>
+          <t>ASTOR.IS: -0.26% / +1.03% / -3.31% | FENER.IS: -1.31% / +0.65% / -1.62%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-3.767340978838807</v>
       </c>
       <c r="K12" t="n">
-        <v>12.49402354583942</v>
+        <v>11.72522060341192</v>
       </c>
       <c r="L12" t="n">
         <v>16.57596537747867</v>
@@ -1522,7 +1522,7 @@
         <v>88</v>
       </c>
       <c r="O12" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
       <c r="P12" t="n">
         <v>2.5</v>
@@ -1542,13 +1542,13 @@
         <v>17.404</v>
       </c>
       <c r="U12" t="n">
-        <v>52.155</v>
+        <v>51.115</v>
       </c>
       <c r="V12" t="n">
-        <v>44.616</v>
+        <v>43.628</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.547</v>
+        <v>-3.587</v>
       </c>
     </row>
     <row r="13">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.53% / +20.94% / 0.00% | RALYH.IS: +25.22% / +35.10% / -0.91% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +10.57% / +20.94% / 0.00% | RALYH.IS: +24.13% / +35.10% / -0.91% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K13" t="n">
-        <v>10.67598218073205</v>
+        <v>10.67351598326982</v>
       </c>
       <c r="L13" t="n">
         <v>34.56349599547857</v>
@@ -1629,13 +1629,13 @@
         <v>23.777</v>
       </c>
       <c r="U13" t="n">
-        <v>46.381</v>
+        <v>46.378</v>
       </c>
       <c r="V13" t="n">
-        <v>40.257</v>
+        <v>40.254</v>
       </c>
       <c r="W13" t="n">
-        <v>-13.657</v>
+        <v>-13.66</v>
       </c>
     </row>
     <row r="14">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -3.23% / +0.00% / -3.49% | ENERY.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: -0.56% / +0.09% / -3.24%</t>
+          <t>ALTNY.IS: -1.65% / +0.00% / -3.49% | ENERY.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: +0.43% / +0.68% / -3.24%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-15.21815302569316</v>
+        <v>-14.4827919160602</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2140,7 +2140,7 @@
         <v>191.9</v>
       </c>
       <c r="O21" t="n">
-        <v>46.6</v>
+        <v>46.9</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2154,19 +2154,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>16.547</v>
+        <v>15.824</v>
       </c>
       <c r="T21" t="n">
-        <v>16.547</v>
+        <v>15.824</v>
       </c>
       <c r="U21" t="n">
-        <v>41.783</v>
+        <v>43.013</v>
       </c>
       <c r="V21" t="n">
-        <v>12.564</v>
+        <v>13.541</v>
       </c>
       <c r="W21" t="n">
-        <v>-28.113</v>
+        <v>-26.884</v>
       </c>
     </row>
     <row r="22">
@@ -2453,14 +2453,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FENER.IS: -0.34% / +0.65% / -1.62% | PETKM.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>FENER.IS: -1.31% / +0.65% / -1.62% | PETKM.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.183142751761104</v>
+        <v>-4.369292859264751</v>
       </c>
       <c r="L25" t="n">
         <v>4.543450519200398</v>
@@ -2492,13 +2492,13 @@
         <v>10.072</v>
       </c>
       <c r="U25" t="n">
-        <v>16.027</v>
+        <v>15.802</v>
       </c>
       <c r="V25" t="n">
-        <v>7.882</v>
+        <v>7.672</v>
       </c>
       <c r="W25" t="n">
-        <v>-9.361000000000001</v>
+        <v>-9.586</v>
       </c>
     </row>
     <row r="26">
@@ -2542,14 +2542,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +0.14% / +0.39% / -3.31% | FENER.IS: -0.34% / +0.65% / -1.62%</t>
+          <t>ASTOR.IS: -0.26% / +1.03% / -3.31% | FENER.IS: -1.31% / +0.65% / -1.62%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-3.767340978838807</v>
       </c>
       <c r="K26" t="n">
-        <v>12.49402354583942</v>
+        <v>11.72522060341192</v>
       </c>
       <c r="L26" t="n">
         <v>16.57596537747867</v>
@@ -2561,7 +2561,7 @@
         <v>88</v>
       </c>
       <c r="O26" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
       <c r="P26" t="n">
         <v>2.5</v>
@@ -2581,13 +2581,13 @@
         <v>17.404</v>
       </c>
       <c r="U26" t="n">
-        <v>52.155</v>
+        <v>51.115</v>
       </c>
       <c r="V26" t="n">
-        <v>44.616</v>
+        <v>43.628</v>
       </c>
       <c r="W26" t="n">
-        <v>-2.547</v>
+        <v>-3.587</v>
       </c>
     </row>
     <row r="27">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.53% / +20.94% / 0.00% | RALYH.IS: +25.22% / +35.10% / -0.91% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +10.57% / +20.94% / 0.00% | RALYH.IS: +24.13% / +35.10% / -0.91% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>10.67598218073205</v>
+        <v>10.67351598326982</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2670,13 +2670,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>46.381</v>
+        <v>46.378</v>
       </c>
       <c r="V27" t="n">
-        <v>40.257</v>
+        <v>40.254</v>
       </c>
       <c r="W27" t="n">
-        <v>-13.657</v>
+        <v>-13.66</v>
       </c>
     </row>
   </sheetData>
@@ -2711,7 +2711,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2889,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | TKFEN.IS: +11.58% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | TKFEN.IS: +11.95% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2627514567618672</v>
+        <v>0.001928040318710522</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2928,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>282.601</v>
+        <v>283.616</v>
       </c>
       <c r="V3" t="n">
-        <v>100.918</v>
+        <v>101.451</v>
       </c>
       <c r="W3" t="n">
-        <v>-43.819</v>
+        <v>-42.803</v>
       </c>
     </row>
     <row r="4">
@@ -2976,14 +2976,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | ALTNY.IS: -3.23% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.34% / +3.27% / -0.09%</t>
+          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | ALTNY.IS: -1.65% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.80% / +3.27% / -0.09%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-9.965632173979866</v>
+        <v>-9.560560652765593</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -3009,19 +3009,19 @@
         <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>24.857</v>
+        <v>24.688</v>
       </c>
       <c r="T4" t="n">
-        <v>24.857</v>
+        <v>24.688</v>
       </c>
       <c r="U4" t="n">
-        <v>59.336</v>
+        <v>60.052</v>
       </c>
       <c r="V4" t="n">
-        <v>21.134</v>
+        <v>21.679</v>
       </c>
       <c r="W4" t="n">
-        <v>-52.707</v>
+        <v>-51.991</v>
       </c>
     </row>
     <row r="5">
@@ -3063,14 +3063,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | TKFEN.IS: +11.58% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | TKFEN.IS: +11.95% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2827179060234664</v>
+        <v>-0.01809139526269821</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3102,13 +3102,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>279.858</v>
+        <v>280.866</v>
       </c>
       <c r="V5" t="n">
-        <v>82.968</v>
+        <v>83.45399999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-43.456</v>
+        <v>-42.448</v>
       </c>
     </row>
     <row r="6">
@@ -3150,14 +3150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +8.71% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +11.58% / +31.83% / -0.56%</t>
+          <t>ALTNY.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +9.74% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +11.95% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.35517153976994</v>
+        <v>-10.09242331958823</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3189,13 +3189,13 @@
         <v>26.15</v>
       </c>
       <c r="U6" t="n">
-        <v>24.391</v>
+        <v>24.756</v>
       </c>
       <c r="V6" t="n">
-        <v>11.452</v>
+        <v>11.779</v>
       </c>
       <c r="W6" t="n">
-        <v>-43.999</v>
+        <v>-43.634</v>
       </c>
     </row>
     <row r="7">
@@ -3237,14 +3237,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | ALTNY.IS: -3.23% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.34% / +3.27% / -0.09%</t>
+          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | ALTNY.IS: -1.65% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.80% / +3.27% / -0.09%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.965632173979866</v>
+        <v>-9.560560652765593</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3270,19 +3270,19 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>24.857</v>
+        <v>24.688</v>
       </c>
       <c r="T7" t="n">
-        <v>24.857</v>
+        <v>24.688</v>
       </c>
       <c r="U7" t="n">
-        <v>59.336</v>
+        <v>60.052</v>
       </c>
       <c r="V7" t="n">
-        <v>21.134</v>
+        <v>21.679</v>
       </c>
       <c r="W7" t="n">
-        <v>-52.707</v>
+        <v>-51.991</v>
       </c>
     </row>
     <row r="8">
@@ -3324,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +9.74% / +20.03% / -1.13% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.721058835851221</v>
+        <v>-3.468690306550293</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3363,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>20.65</v>
+        <v>20.966</v>
       </c>
       <c r="V8" t="n">
-        <v>0.91</v>
+        <v>1.175</v>
       </c>
       <c r="W8" t="n">
-        <v>-32.566</v>
+        <v>-32.25</v>
       </c>
     </row>
     <row r="9">
@@ -3406,7 +3406,7 @@
         <v>15.38514121842653</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.632543801829504</v>
+        <v>-6.616392554049999</v>
       </c>
       <c r="L9" t="n">
         <v>5.127814043936619</v>
@@ -3432,19 +3432,19 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>13.295</v>
+        <v>13.28</v>
       </c>
       <c r="T9" t="n">
-        <v>13.295</v>
+        <v>13.28</v>
       </c>
       <c r="U9" t="n">
-        <v>8.545999999999999</v>
+        <v>8.565</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.979</v>
+        <v>-0.962</v>
       </c>
       <c r="W9" t="n">
-        <v>-16.645</v>
+        <v>-16.626</v>
       </c>
     </row>
     <row r="10">
@@ -3486,14 +3486,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.659799766004945</v>
+        <v>-3.610798768024204</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3519,19 +3519,19 @@
         <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>20.235</v>
+        <v>20.194</v>
       </c>
       <c r="T10" t="n">
-        <v>20.235</v>
+        <v>20.194</v>
       </c>
       <c r="U10" t="n">
-        <v>9.624000000000001</v>
+        <v>9.679</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.083</v>
+        <v>-3.034</v>
       </c>
       <c r="W10" t="n">
-        <v>-27.81</v>
+        <v>-27.754</v>
       </c>
     </row>
     <row r="11">
@@ -3573,14 +3573,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | ALTNY.IS: -3.23% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.34% / +3.27% / -0.09%</t>
+          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | ALTNY.IS: -1.65% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.80% / +3.27% / -0.09%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.881553750404859</v>
+        <v>-9.476103953919047</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3606,19 +3606,19 @@
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>23.527</v>
+        <v>23.355</v>
       </c>
       <c r="T11" t="n">
-        <v>23.527</v>
+        <v>23.355</v>
       </c>
       <c r="U11" t="n">
-        <v>35.139</v>
+        <v>35.747</v>
       </c>
       <c r="V11" t="n">
-        <v>8.067</v>
+        <v>8.553000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>-41.576</v>
+        <v>-40.968</v>
       </c>
     </row>
     <row r="12">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3647,42 +3647,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASTOR.IS, FENER.IS</t>
+          <t>BRSAN.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-01 | FENER.IS: 2026-09-01</t>
+          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-0.49388395046156</v>
+        <v>6.880672511445463</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +0.14% / +0.39% / -3.32% | FENER.IS: -0.34% / +0.69% / -1.58%</t>
+          <t>BRSAN.IS: +9.74% / +20.03% / -1.13% | TKFEN.IS: +11.95% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-19.60937535624424</v>
+        <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>9.314143135238373</v>
+        <v>8.811158021390009</v>
       </c>
       <c r="L12" t="n">
-        <v>19.61961325199098</v>
+        <v>31.31195090134997</v>
       </c>
       <c r="M12" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>87.8</v>
+        <v>48.4</v>
       </c>
       <c r="O12" t="n">
-        <v>46.6</v>
+        <v>43.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3693,19 +3693,19 @@
         <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>18.132</v>
+        <v>28.439</v>
       </c>
       <c r="T12" t="n">
-        <v>18.132</v>
+        <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>11.135</v>
+        <v>37.584</v>
       </c>
       <c r="V12" t="n">
-        <v>14.146</v>
+        <v>51.618</v>
       </c>
       <c r="W12" t="n">
-        <v>-5.424</v>
+        <v>-18.282</v>
       </c>
     </row>
     <row r="13">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3734,39 +3734,39 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASTOR.IS, KRDMD.IS</t>
+          <t>ASTOR.IS, FENER.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-01 | KRDMD.IS: 2026-09-02</t>
+          <t>ASTOR.IS: 2026-09-01 | FENER.IS: 2026-09-01</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>8.530010255723974</v>
+        <v>-0.49388395046156</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +0.14% / +0.39% / -3.32% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: -0.26% / +1.03% / -3.32% | FENER.IS: -1.31% / +0.69% / -1.58%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.8142516931666233</v>
+        <v>-19.60937535624424</v>
       </c>
       <c r="K13" t="n">
-        <v>8.256724474506161</v>
+        <v>8.567135442638163</v>
       </c>
       <c r="L13" t="n">
-        <v>9.181211458048665</v>
+        <v>19.61961325199098</v>
       </c>
       <c r="M13" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N13" t="n">
-        <v>35.9</v>
+        <v>87.8</v>
       </c>
       <c r="O13" t="n">
-        <v>51.4</v>
+        <v>46</v>
       </c>
       <c r="P13" t="n">
         <v>2.2</v>
@@ -3780,19 +3780,19 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>8.083</v>
+        <v>18.132</v>
       </c>
       <c r="T13" t="n">
-        <v>7.916</v>
+        <v>18.132</v>
       </c>
       <c r="U13" t="n">
-        <v>14.745</v>
+        <v>10.376</v>
       </c>
       <c r="V13" t="n">
-        <v>9.372</v>
+        <v>13.366</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.349</v>
+        <v>-6.184</v>
       </c>
     </row>
     <row r="14">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3821,42 +3821,42 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
+          <t>ASTOR.IS, KRDMD.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
+          <t>ASTOR.IS: 2026-09-01 | KRDMD.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6.880672511445463</v>
+        <v>8.530010255723974</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | TKFEN.IS: +11.58% / +31.83% / -0.56%</t>
+          <t>ASTOR.IS: -0.26% / +1.03% / -3.32% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-18.9000927288166</v>
+        <v>0.8142516931666233</v>
       </c>
       <c r="K14" t="n">
-        <v>8.134533393956911</v>
+        <v>8.043265356219909</v>
       </c>
       <c r="L14" t="n">
-        <v>31.31195090134997</v>
+        <v>9.181211458048665</v>
       </c>
       <c r="M14" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N14" t="n">
-        <v>48.4</v>
+        <v>35.9</v>
       </c>
       <c r="O14" t="n">
-        <v>43.3</v>
+        <v>50</v>
       </c>
       <c r="P14" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3867,19 +3867,19 @@
         <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>28.439</v>
+        <v>8.083</v>
       </c>
       <c r="T14" t="n">
-        <v>28.439</v>
+        <v>7.916</v>
       </c>
       <c r="U14" t="n">
-        <v>36.728</v>
+        <v>14.519</v>
       </c>
       <c r="V14" t="n">
-        <v>50.675</v>
+        <v>9.157</v>
       </c>
       <c r="W14" t="n">
-        <v>-19.137</v>
+        <v>-0.576</v>
       </c>
     </row>
     <row r="16">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | TKFEN.IS: +11.58% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | TKFEN.IS: +11.95% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2627514567618672</v>
+        <v>0.001928040318710522</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4086,13 +4086,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>282.601</v>
+        <v>283.616</v>
       </c>
       <c r="V18" t="n">
-        <v>100.918</v>
+        <v>101.451</v>
       </c>
       <c r="W18" t="n">
-        <v>-43.819</v>
+        <v>-42.803</v>
       </c>
     </row>
     <row r="19">
@@ -4136,14 +4136,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | ALTNY.IS: -3.23% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.34% / +3.27% / -0.09%</t>
+          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | ALTNY.IS: -1.65% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.80% / +3.27% / -0.09%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-9.965632173979866</v>
+        <v>-9.560560652765593</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4169,19 +4169,19 @@
         <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>24.857</v>
+        <v>24.688</v>
       </c>
       <c r="T19" t="n">
-        <v>24.857</v>
+        <v>24.688</v>
       </c>
       <c r="U19" t="n">
-        <v>59.336</v>
+        <v>60.052</v>
       </c>
       <c r="V19" t="n">
-        <v>21.134</v>
+        <v>21.679</v>
       </c>
       <c r="W19" t="n">
-        <v>-52.707</v>
+        <v>-51.991</v>
       </c>
     </row>
     <row r="20">
@@ -4225,14 +4225,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | TKFEN.IS: +11.58% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | TKFEN.IS: +11.95% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2827179060234664</v>
+        <v>-0.01809139526269821</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4264,13 +4264,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>279.858</v>
+        <v>280.866</v>
       </c>
       <c r="V20" t="n">
-        <v>82.968</v>
+        <v>83.45399999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>-43.456</v>
+        <v>-42.448</v>
       </c>
     </row>
     <row r="21">
@@ -4314,14 +4314,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | ALTNY.IS: -3.23% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.34% / +3.27% / -0.09%</t>
+          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | ALTNY.IS: -1.65% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.80% / +3.27% / -0.09%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.881553750404859</v>
+        <v>-9.476103953919047</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4347,19 +4347,19 @@
         <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>23.527</v>
+        <v>23.355</v>
       </c>
       <c r="T21" t="n">
-        <v>23.527</v>
+        <v>23.355</v>
       </c>
       <c r="U21" t="n">
-        <v>35.139</v>
+        <v>35.747</v>
       </c>
       <c r="V21" t="n">
-        <v>8.067</v>
+        <v>8.553000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>-41.576</v>
+        <v>-40.968</v>
       </c>
     </row>
     <row r="22">
@@ -4403,14 +4403,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +8.71% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +11.58% / +31.83% / -0.56%</t>
+          <t>ALTNY.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +9.74% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +11.95% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.35517153976994</v>
+        <v>-10.09242331958823</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4442,13 +4442,13 @@
         <v>26.15</v>
       </c>
       <c r="U22" t="n">
-        <v>24.391</v>
+        <v>24.756</v>
       </c>
       <c r="V22" t="n">
-        <v>11.452</v>
+        <v>11.779</v>
       </c>
       <c r="W22" t="n">
-        <v>-43.999</v>
+        <v>-43.634</v>
       </c>
     </row>
     <row r="23">
@@ -4492,14 +4492,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +9.74% / +20.03% / -1.13% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.721058835851221</v>
+        <v>-3.468690306550293</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4531,13 +4531,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>20.65</v>
+        <v>20.966</v>
       </c>
       <c r="V23" t="n">
-        <v>0.91</v>
+        <v>1.175</v>
       </c>
       <c r="W23" t="n">
-        <v>-32.566</v>
+        <v>-32.25</v>
       </c>
     </row>
     <row r="24">
@@ -4581,14 +4581,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.73% / +2.49% / -3.23% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.659799766004945</v>
+        <v>-3.610798768024204</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4614,19 +4614,19 @@
         <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>20.235</v>
+        <v>20.194</v>
       </c>
       <c r="T24" t="n">
-        <v>20.235</v>
+        <v>20.194</v>
       </c>
       <c r="U24" t="n">
-        <v>9.624000000000001</v>
+        <v>9.679</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.083</v>
+        <v>-3.034</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.81</v>
+        <v>-27.754</v>
       </c>
     </row>
     <row r="25">
@@ -4665,7 +4665,7 @@
         <v>15.38514121842653</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.632543801829504</v>
+        <v>-6.616392554049999</v>
       </c>
       <c r="L25" t="n">
         <v>5.127814043936619</v>
@@ -4691,19 +4691,19 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>13.295</v>
+        <v>13.28</v>
       </c>
       <c r="T25" t="n">
-        <v>13.295</v>
+        <v>13.28</v>
       </c>
       <c r="U25" t="n">
-        <v>8.545999999999999</v>
+        <v>8.565</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.979</v>
+        <v>-0.962</v>
       </c>
       <c r="W25" t="n">
-        <v>-16.645</v>
+        <v>-16.626</v>
       </c>
     </row>
     <row r="26">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4747,14 +4747,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +0.14% / +0.39% / -3.32% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: -0.26% / +1.03% / -3.32% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>0.8142516931666233</v>
       </c>
       <c r="K26" t="n">
-        <v>8.256724474506161</v>
+        <v>8.043265356219909</v>
       </c>
       <c r="L26" t="n">
         <v>9.181211458048665</v>
@@ -4766,7 +4766,7 @@
         <v>35.9</v>
       </c>
       <c r="O26" t="n">
-        <v>51.4</v>
+        <v>50</v>
       </c>
       <c r="P26" t="n">
         <v>2.2</v>
@@ -4786,13 +4786,13 @@
         <v>7.916</v>
       </c>
       <c r="U26" t="n">
-        <v>14.745</v>
+        <v>14.519</v>
       </c>
       <c r="V26" t="n">
-        <v>9.372</v>
+        <v>9.157</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.349</v>
+        <v>-0.576</v>
       </c>
     </row>
     <row r="27">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4836,14 +4836,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | TKFEN.IS: +11.58% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +9.74% / +20.03% / -1.13% | TKFEN.IS: +11.95% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>8.134533393956911</v>
+        <v>8.811158021390009</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4875,13 +4875,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>36.728</v>
+        <v>37.584</v>
       </c>
       <c r="V27" t="n">
-        <v>50.675</v>
+        <v>51.618</v>
       </c>
       <c r="W27" t="n">
-        <v>-19.137</v>
+        <v>-18.282</v>
       </c>
     </row>
     <row r="28">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4925,14 +4925,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +0.14% / +0.39% / -3.32% | FENER.IS: -0.34% / +0.69% / -1.58%</t>
+          <t>ASTOR.IS: -0.26% / +1.03% / -3.32% | FENER.IS: -1.31% / +0.69% / -1.58%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>9.314143135238373</v>
+        <v>8.567135442638163</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4944,7 +4944,7 @@
         <v>87.8</v>
       </c>
       <c r="O28" t="n">
-        <v>46.6</v>
+        <v>46</v>
       </c>
       <c r="P28" t="n">
         <v>2.2</v>
@@ -4964,13 +4964,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>11.135</v>
+        <v>10.376</v>
       </c>
       <c r="V28" t="n">
-        <v>14.146</v>
+        <v>13.366</v>
       </c>
       <c r="W28" t="n">
-        <v>-5.424</v>
+        <v>-6.184</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.77% / +1.50% / -0.75% | VAKBN.IS: +1.15% / +2.23% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-15.53788135963107</v>
+        <v>-15.35964179515489</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -772,10 +772,10 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>102.9</v>
+        <v>102.7</v>
       </c>
       <c r="O3" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="P3" t="n">
         <v>6.7</v>
@@ -789,19 +789,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>21.677</v>
+        <v>21.661</v>
       </c>
       <c r="T3" t="n">
-        <v>21.677</v>
+        <v>21.661</v>
       </c>
       <c r="U3" t="n">
-        <v>58.213</v>
+        <v>60.827</v>
       </c>
       <c r="V3" t="n">
-        <v>14.748</v>
+        <v>14.99</v>
       </c>
       <c r="W3" t="n">
-        <v>-43.787</v>
+        <v>-44.078</v>
       </c>
     </row>
     <row r="4">
@@ -820,12 +820,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -847,7 +847,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>64.09999999999999</v>
+        <v>64</v>
       </c>
       <c r="O4" t="n">
         <v>48.8</v>
@@ -895,12 +895,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N5" t="n">
-        <v>65.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="O5" t="n">
         <v>46.6</v>
@@ -970,12 +970,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.77% / +1.50% / -0.75% | VAKBN.IS: +1.15% / +2.23% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-15.53788135963107</v>
+        <v>-15.35964179515489</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1009,10 +1009,10 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>102.9</v>
+        <v>102.7</v>
       </c>
       <c r="O6" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="P6" t="n">
         <v>6.7</v>
@@ -1026,19 +1026,19 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>21.677</v>
+        <v>21.661</v>
       </c>
       <c r="T6" t="n">
-        <v>21.677</v>
+        <v>21.661</v>
       </c>
       <c r="U6" t="n">
-        <v>58.213</v>
+        <v>60.827</v>
       </c>
       <c r="V6" t="n">
-        <v>14.748</v>
+        <v>14.99</v>
       </c>
       <c r="W6" t="n">
-        <v>-43.787</v>
+        <v>-44.078</v>
       </c>
     </row>
     <row r="7">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.77% / +1.50% / -0.75% | VAKBN.IS: +1.15% / +2.23% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.035620267310758</v>
+        <v>-4.835217886257837</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1096,10 +1096,10 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>135.2</v>
+        <v>134.9</v>
       </c>
       <c r="O7" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>17.456</v>
+        <v>17.439</v>
       </c>
       <c r="T7" t="n">
-        <v>17.456</v>
+        <v>17.439</v>
       </c>
       <c r="U7" t="n">
-        <v>71.358</v>
+        <v>71.90300000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>29.945</v>
+        <v>30.219</v>
       </c>
       <c r="W7" t="n">
-        <v>-36.237</v>
+        <v>-35.914</v>
       </c>
     </row>
     <row r="8">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -1.65% / +0.00% / -3.49% | ENERY.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: +0.43% / +0.68% / -3.24%</t>
+          <t>ALTNY.IS: -2.56% / +0.00% / -3.49% | ENERY.IS: +0.27% / +1.24% / -0.10% | KRDMD.IS: +0.07% / +1.08% / -3.24%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-14.4827919160602</v>
+        <v>-14.76266051766313</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1183,10 +1183,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>191.9</v>
+        <v>191.5</v>
       </c>
       <c r="O8" t="n">
-        <v>46.9</v>
+        <v>47.2</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1200,19 +1200,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>15.824</v>
+        <v>16.099</v>
       </c>
       <c r="T8" t="n">
-        <v>15.824</v>
+        <v>16.099</v>
       </c>
       <c r="U8" t="n">
-        <v>43.013</v>
+        <v>42.893</v>
       </c>
       <c r="V8" t="n">
-        <v>13.541</v>
+        <v>13.169</v>
       </c>
       <c r="W8" t="n">
-        <v>-26.884</v>
+        <v>-27.418</v>
       </c>
     </row>
     <row r="9">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.77% / +1.50% / -0.75% | VAKBN.IS: +1.15% / +2.23% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-15.53788135963107</v>
+        <v>-15.35964179515489</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1270,10 +1270,10 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>102.9</v>
+        <v>102.7</v>
       </c>
       <c r="O9" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="P9" t="n">
         <v>6.7</v>
@@ -1287,19 +1287,19 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>21.677</v>
+        <v>21.661</v>
       </c>
       <c r="T9" t="n">
-        <v>21.677</v>
+        <v>21.661</v>
       </c>
       <c r="U9" t="n">
-        <v>58.213</v>
+        <v>60.827</v>
       </c>
       <c r="V9" t="n">
-        <v>14.748</v>
+        <v>14.99</v>
       </c>
       <c r="W9" t="n">
-        <v>-43.787</v>
+        <v>-44.078</v>
       </c>
     </row>
     <row r="10">
@@ -1318,22 +1318,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FENER.IS, PETKM.IS, TRALT.IS</t>
+          <t>KUYAS.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>FENER.IS: 2026-09-01 | PETKM.IS: 2026-09-02 | TRALT.IS: 2026-09-02</t>
+          <t>KUYAS.IS: 2026-09-03 | TRALT.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FENER.IS: -1.31% / +0.65% / -1.62% | PETKM.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>KUYAS.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: +0.08% / +1.89% / -0.40%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.369292859264751</v>
+        <v>-4.444209921439257</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1357,10 +1357,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>175.5</v>
+        <v>175.6</v>
       </c>
       <c r="O10" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
         <v>10.072</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>15.802</v>
+        <v>15.711</v>
       </c>
       <c r="V10" t="n">
-        <v>7.672</v>
+        <v>7.588</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.586</v>
+        <v>-9.677</v>
       </c>
     </row>
     <row r="11">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>67.09999999999999</v>
+        <v>67</v>
       </c>
       <c r="O11" t="n">
         <v>51.9</v>
@@ -1475,57 +1475,57 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASTOR.IS, FENER.IS</t>
+          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-01 | FENER.IS: 2026-09-01</t>
+          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>20.48700524499634</v>
+        <v>13.58351811074014</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.26% / +1.03% / -3.31% | FENER.IS: -1.31% / +0.65% / -1.62%</t>
+          <t>BRSAN.IS: +9.69% / +20.94% / 0.00% | RALYH.IS: +23.89% / +35.10% / -0.91% | VAKBN.IS: +1.15% / +2.23% / 0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-3.767340978838807</v>
+        <v>-10.39434387728287</v>
       </c>
       <c r="K12" t="n">
-        <v>11.72522060341192</v>
+        <v>10.74849862712506</v>
       </c>
       <c r="L12" t="n">
-        <v>16.57596537747867</v>
+        <v>34.56349599547857</v>
       </c>
       <c r="M12" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>88</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>47.5</v>
+        <v>44.7</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>17.404</v>
+        <v>23.777</v>
       </c>
       <c r="T12" t="n">
-        <v>17.404</v>
+        <v>23.777</v>
       </c>
       <c r="U12" t="n">
-        <v>51.115</v>
+        <v>46.477</v>
       </c>
       <c r="V12" t="n">
-        <v>43.628</v>
+        <v>40.349</v>
       </c>
       <c r="W12" t="n">
-        <v>-3.587</v>
+        <v>-13.561</v>
       </c>
     </row>
     <row r="13">
@@ -1562,57 +1562,57 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
+          <t>ASTOR.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
+          <t>ASTOR.IS: 2026-09-01 | TRALT.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>13.58351811074014</v>
+        <v>20.48700524499634</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +10.57% / +20.94% / 0.00% | RALYH.IS: +24.13% / +35.10% / -0.91% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: -2.78% / +1.03% / -3.31% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-10.39434387728287</v>
+        <v>-3.767340978838807</v>
       </c>
       <c r="K13" t="n">
-        <v>10.67351598326982</v>
+        <v>10.28137551708646</v>
       </c>
       <c r="L13" t="n">
-        <v>34.56349599547857</v>
+        <v>16.57596537747867</v>
       </c>
       <c r="M13" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>70.09999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="O13" t="n">
-        <v>44</v>
+        <v>47.2</v>
       </c>
       <c r="P13" t="n">
-        <v>6.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1620,22 +1620,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>23.777</v>
+        <v>17.404</v>
       </c>
       <c r="T13" t="n">
-        <v>23.777</v>
+        <v>17.404</v>
       </c>
       <c r="U13" t="n">
-        <v>46.378</v>
+        <v>49.162</v>
       </c>
       <c r="V13" t="n">
-        <v>40.254</v>
+        <v>41.772</v>
       </c>
       <c r="W13" t="n">
-        <v>-13.66</v>
+        <v>-5.54</v>
       </c>
     </row>
     <row r="14">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1681,7 +1681,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>59.1</v>
+        <v>59</v>
       </c>
       <c r="O14" t="n">
         <v>44.5</v>
@@ -1704,13 +1704,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>78.53400000000001</v>
+        <v>82.66800000000001</v>
       </c>
       <c r="V14" t="n">
         <v>93.19</v>
       </c>
       <c r="W14" t="n">
-        <v>-29.782</v>
+        <v>-30.472</v>
       </c>
     </row>
     <row r="16">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1878,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.77% / +1.50% / -0.75% | VAKBN.IS: +1.15% / +2.23% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-15.53788135963107</v>
+        <v>-15.35964179515489</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1894,10 +1894,10 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>102.9</v>
+        <v>102.7</v>
       </c>
       <c r="O18" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="P18" t="n">
         <v>6.7</v>
@@ -1911,19 +1911,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>21.677</v>
+        <v>21.661</v>
       </c>
       <c r="T18" t="n">
-        <v>21.677</v>
+        <v>21.661</v>
       </c>
       <c r="U18" t="n">
-        <v>58.213</v>
+        <v>60.827</v>
       </c>
       <c r="V18" t="n">
-        <v>14.748</v>
+        <v>14.99</v>
       </c>
       <c r="W18" t="n">
-        <v>-43.787</v>
+        <v>-44.078</v>
       </c>
     </row>
     <row r="19">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1971,7 +1971,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>64.09999999999999</v>
+        <v>64</v>
       </c>
       <c r="O19" t="n">
         <v>48.8</v>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2048,7 +2048,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>65.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="O20" t="n">
         <v>46.6</v>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -1.65% / +0.00% / -3.49% | ENERY.IS: -0.02% / +0.00% / 0.00% | KRDMD.IS: +0.43% / +0.68% / -3.24%</t>
+          <t>ALTNY.IS: -2.56% / +0.00% / -3.49% | ENERY.IS: +0.27% / +1.24% / -0.10% | KRDMD.IS: +0.07% / +1.08% / -3.24%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-14.4827919160602</v>
+        <v>-14.76266051766313</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2137,10 +2137,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>191.9</v>
+        <v>191.5</v>
       </c>
       <c r="O21" t="n">
-        <v>46.9</v>
+        <v>47.2</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2154,19 +2154,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>15.824</v>
+        <v>16.099</v>
       </c>
       <c r="T21" t="n">
-        <v>15.824</v>
+        <v>16.099</v>
       </c>
       <c r="U21" t="n">
-        <v>43.013</v>
+        <v>42.893</v>
       </c>
       <c r="V21" t="n">
-        <v>13.541</v>
+        <v>13.169</v>
       </c>
       <c r="W21" t="n">
-        <v>-26.884</v>
+        <v>-27.418</v>
       </c>
     </row>
     <row r="22">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2210,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.77% / +1.50% / -0.75% | VAKBN.IS: +1.15% / +2.23% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.035620267310758</v>
+        <v>-4.835217886257837</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2226,10 +2226,10 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>135.2</v>
+        <v>134.9</v>
       </c>
       <c r="O22" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
@@ -2243,19 +2243,19 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>17.456</v>
+        <v>17.439</v>
       </c>
       <c r="T22" t="n">
-        <v>17.456</v>
+        <v>17.439</v>
       </c>
       <c r="U22" t="n">
-        <v>71.358</v>
+        <v>71.90300000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>29.945</v>
+        <v>30.219</v>
       </c>
       <c r="W22" t="n">
-        <v>-36.237</v>
+        <v>-35.914</v>
       </c>
     </row>
     <row r="23">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -2303,7 +2303,7 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>59.1</v>
+        <v>59</v>
       </c>
       <c r="O23" t="n">
         <v>44.5</v>
@@ -2326,13 +2326,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>78.53400000000001</v>
+        <v>82.66800000000001</v>
       </c>
       <c r="V23" t="n">
         <v>93.19</v>
       </c>
       <c r="W23" t="n">
-        <v>-29.782</v>
+        <v>-30.472</v>
       </c>
     </row>
     <row r="24">
@@ -2353,12 +2353,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2380,7 +2380,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>67.09999999999999</v>
+        <v>67</v>
       </c>
       <c r="O24" t="n">
         <v>51.9</v>
@@ -2430,22 +2430,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FENER.IS, PETKM.IS, TRALT.IS</t>
+          <t>KUYAS.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>FENER.IS: 2026-09-01 | PETKM.IS: 2026-09-02 | TRALT.IS: 2026-09-02</t>
+          <t>KUYAS.IS: 2026-09-03 | TRALT.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -2453,14 +2453,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FENER.IS: -1.31% / +0.65% / -1.62% | PETKM.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>KUYAS.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: +0.08% / +1.89% / -0.40%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.369292859264751</v>
+        <v>-4.444209921439257</v>
       </c>
       <c r="L25" t="n">
         <v>4.543450519200398</v>
@@ -2469,10 +2469,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N25" t="n">
-        <v>175.5</v>
+        <v>175.6</v>
       </c>
       <c r="O25" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
       <c r="P25" t="n">
         <v>1.9</v>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
         <v>10.072</v>
@@ -2492,13 +2492,13 @@
         <v>10.072</v>
       </c>
       <c r="U25" t="n">
-        <v>15.802</v>
+        <v>15.711</v>
       </c>
       <c r="V25" t="n">
-        <v>7.672</v>
+        <v>7.588</v>
       </c>
       <c r="W25" t="n">
-        <v>-9.586</v>
+        <v>-9.677</v>
       </c>
     </row>
     <row r="26">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2519,22 +2519,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ASTOR.IS, FENER.IS</t>
+          <t>ASTOR.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-01 | FENER.IS: 2026-09-01</t>
+          <t>ASTOR.IS: 2026-09-01 | TRALT.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2542,14 +2542,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.26% / +1.03% / -3.31% | FENER.IS: -1.31% / +0.65% / -1.62%</t>
+          <t>ASTOR.IS: -2.78% / +1.03% / -3.31% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-3.767340978838807</v>
       </c>
       <c r="K26" t="n">
-        <v>11.72522060341192</v>
+        <v>10.28137551708646</v>
       </c>
       <c r="L26" t="n">
         <v>16.57596537747867</v>
@@ -2558,10 +2558,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>88</v>
+        <v>88.3</v>
       </c>
       <c r="O26" t="n">
-        <v>47.5</v>
+        <v>47.2</v>
       </c>
       <c r="P26" t="n">
         <v>2.5</v>
@@ -2581,13 +2581,13 @@
         <v>17.404</v>
       </c>
       <c r="U26" t="n">
-        <v>51.115</v>
+        <v>49.162</v>
       </c>
       <c r="V26" t="n">
-        <v>43.628</v>
+        <v>41.772</v>
       </c>
       <c r="W26" t="n">
-        <v>-3.587</v>
+        <v>-5.54</v>
       </c>
     </row>
     <row r="27">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +10.57% / +20.94% / 0.00% | RALYH.IS: +24.13% / +35.10% / -0.91% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +9.69% / +20.94% / 0.00% | RALYH.IS: +23.89% / +35.10% / -0.91% | VAKBN.IS: +1.15% / +2.23% / 0.00%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>10.67351598326982</v>
+        <v>10.74849862712506</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2647,10 +2647,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N27" t="n">
-        <v>70.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>44</v>
+        <v>44.7</v>
       </c>
       <c r="P27" t="n">
         <v>6.1</v>
@@ -2670,13 +2670,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>46.378</v>
+        <v>46.477</v>
       </c>
       <c r="V27" t="n">
-        <v>40.254</v>
+        <v>40.349</v>
       </c>
       <c r="W27" t="n">
-        <v>-13.66</v>
+        <v>-13.561</v>
       </c>
     </row>
   </sheetData>
@@ -2711,7 +2711,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2866,22 +2866,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ALARK.IS, TKFEN.IS</t>
+          <t>ALARK.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | TKFEN.IS: 2026-08-05</t>
+          <t>ALARK.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2889,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | TKFEN.IS: +11.95% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: +2.20% / +2.95% / -3.23%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001928040318710522</v>
+        <v>0.28182546797757</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2905,7 +2905,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>92.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O3" t="n">
         <v>44.6</v>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>18.106</v>
@@ -2928,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>283.616</v>
+        <v>277.454</v>
       </c>
       <c r="V3" t="n">
-        <v>101.451</v>
+        <v>102.015</v>
       </c>
       <c r="W3" t="n">
-        <v>-42.803</v>
+        <v>-40.945</v>
       </c>
     </row>
     <row r="4">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2976,14 +2976,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | ALTNY.IS: -1.65% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.80% / +3.27% / -0.09%</t>
+          <t>ALARK.IS: +2.20% / +2.95% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -2.55% / +1.19% / -2.61% | ENERY.IS: +0.27% / +1.23% / -0.10% | ENJSA.IS: +2.07% / +3.36% / -0.09%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-9.560560652765593</v>
+        <v>-10.18560854326407</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2992,10 +2992,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>117.8</v>
+        <v>117.5</v>
       </c>
       <c r="O4" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="P4" t="n">
         <v>3.9</v>
@@ -3009,19 +3009,19 @@
         <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>24.688</v>
+        <v>25.041</v>
       </c>
       <c r="T4" t="n">
-        <v>24.688</v>
+        <v>25.041</v>
       </c>
       <c r="U4" t="n">
-        <v>60.052</v>
+        <v>56.999</v>
       </c>
       <c r="V4" t="n">
-        <v>21.679</v>
+        <v>20.838</v>
       </c>
       <c r="W4" t="n">
-        <v>-51.991</v>
+        <v>-52.446</v>
       </c>
     </row>
     <row r="5">
@@ -3040,22 +3040,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ALARK.IS, TKFEN.IS</t>
+          <t>ALARK.IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | TKFEN.IS: 2026-08-05</t>
+          <t>ALARK.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3063,14 +3063,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | TKFEN.IS: +11.95% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: +2.20% / +2.95% / -3.23%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.01809139526269821</v>
+        <v>0.261749999591232</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3079,7 +3079,7 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="O5" t="n">
         <v>42.7</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>21.096</v>
@@ -3102,13 +3102,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>280.866</v>
+        <v>274.663</v>
       </c>
       <c r="V5" t="n">
-        <v>83.45399999999999</v>
+        <v>83.968</v>
       </c>
       <c r="W5" t="n">
-        <v>-42.448</v>
+        <v>-40.594</v>
       </c>
     </row>
     <row r="6">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3150,14 +3150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +9.74% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +11.95% / +31.83% / -0.56%</t>
+          <t>ALTNY.IS: -0.94% / +0.85% / -1.04% | BRSAN.IS: +8.87% / +20.03% / -1.13% | CANTE.IS: +7.02% / +15.84% / -2.80% | ENERY.IS: +0.27% / +1.23% / -0.10% | TKFEN.IS: +12.27% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.09242331958823</v>
+        <v>-10.39056794739956</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3166,10 +3166,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>139.2</v>
+        <v>138.9</v>
       </c>
       <c r="O6" t="n">
-        <v>42.3</v>
+        <v>42.7</v>
       </c>
       <c r="P6" t="n">
         <v>5.7</v>
@@ -3183,19 +3183,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>26.15</v>
+        <v>26.158</v>
       </c>
       <c r="T6" t="n">
-        <v>26.15</v>
+        <v>26.158</v>
       </c>
       <c r="U6" t="n">
-        <v>24.756</v>
+        <v>24.526</v>
       </c>
       <c r="V6" t="n">
-        <v>11.779</v>
+        <v>11.408</v>
       </c>
       <c r="W6" t="n">
-        <v>-43.634</v>
+        <v>-44.113</v>
       </c>
     </row>
     <row r="7">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3237,14 +3237,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | ALTNY.IS: -1.65% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.80% / +3.27% / -0.09%</t>
+          <t>ALARK.IS: +2.20% / +2.95% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -2.55% / +1.19% / -2.61% | ENERY.IS: +0.27% / +1.23% / -0.10% | ENJSA.IS: +2.07% / +3.36% / -0.09%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.560560652765593</v>
+        <v>-10.18560854326407</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3253,10 +3253,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>117.8</v>
+        <v>117.5</v>
       </c>
       <c r="O7" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="P7" t="n">
         <v>3.9</v>
@@ -3270,19 +3270,19 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>24.688</v>
+        <v>25.041</v>
       </c>
       <c r="T7" t="n">
-        <v>24.688</v>
+        <v>25.041</v>
       </c>
       <c r="U7" t="n">
-        <v>60.052</v>
+        <v>56.999</v>
       </c>
       <c r="V7" t="n">
-        <v>21.679</v>
+        <v>20.838</v>
       </c>
       <c r="W7" t="n">
-        <v>-51.991</v>
+        <v>-52.446</v>
       </c>
     </row>
     <row r="8">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3324,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.74% / +20.03% / -1.13% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +8.87% / +20.03% / -1.13% | CANTE.IS: -0.77% / +1.46% / -0.80% | ENERY.IS: +0.27% / +1.23% / -0.10%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.468690306550293</v>
+        <v>-3.794250119283926</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3340,10 +3340,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>154.2</v>
+        <v>153.9</v>
       </c>
       <c r="O8" t="n">
-        <v>41.7</v>
+        <v>42.1</v>
       </c>
       <c r="P8" t="n">
         <v>4.2</v>
@@ -3363,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>20.966</v>
+        <v>21.282</v>
       </c>
       <c r="V8" t="n">
-        <v>1.175</v>
+        <v>0.833</v>
       </c>
       <c r="W8" t="n">
-        <v>-32.25</v>
+        <v>-32.854</v>
       </c>
     </row>
     <row r="9">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3415,7 +3415,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N9" t="n">
-        <v>75.8</v>
+        <v>75.7</v>
       </c>
       <c r="O9" t="n">
         <v>49.3</v>
@@ -3438,13 +3438,13 @@
         <v>13.28</v>
       </c>
       <c r="U9" t="n">
-        <v>8.565</v>
+        <v>9.128</v>
       </c>
       <c r="V9" t="n">
         <v>-0.962</v>
       </c>
       <c r="W9" t="n">
-        <v>-16.626</v>
+        <v>-16.712</v>
       </c>
     </row>
     <row r="10">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3486,14 +3486,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +2.20% / +2.95% / -3.23% | CANTE.IS: -0.77% / +1.46% / -0.80% | ENERY.IS: +0.27% / +1.23% / -0.10%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.610798768024204</v>
+        <v>-3.649039617463301</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3502,10 +3502,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>114.3</v>
+        <v>114</v>
       </c>
       <c r="O10" t="n">
-        <v>49.8</v>
+        <v>50.2</v>
       </c>
       <c r="P10" t="n">
         <v>2.4</v>
@@ -3519,19 +3519,19 @@
         <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>20.194</v>
+        <v>20.226</v>
       </c>
       <c r="T10" t="n">
-        <v>20.194</v>
+        <v>20.226</v>
       </c>
       <c r="U10" t="n">
-        <v>9.679</v>
+        <v>10.21</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.034</v>
+        <v>-3.073</v>
       </c>
       <c r="W10" t="n">
-        <v>-27.754</v>
+        <v>-27.943</v>
       </c>
     </row>
     <row r="11">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3573,14 +3573,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | ALTNY.IS: -1.65% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.80% / +3.27% / -0.09%</t>
+          <t>ALARK.IS: +2.20% / +2.95% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -2.55% / +1.19% / -2.61% | ENERY.IS: +0.27% / +1.23% / -0.10% | ENJSA.IS: +2.07% / +3.36% / -0.09%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.476103953919047</v>
+        <v>-10.10173554420417</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3589,10 +3589,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>178.6</v>
+        <v>178.3</v>
       </c>
       <c r="O11" t="n">
-        <v>52.2</v>
+        <v>52.5</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
@@ -3606,19 +3606,19 @@
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>23.355</v>
+        <v>23.714</v>
       </c>
       <c r="T11" t="n">
-        <v>23.355</v>
+        <v>23.714</v>
       </c>
       <c r="U11" t="n">
-        <v>35.747</v>
+        <v>33.037</v>
       </c>
       <c r="V11" t="n">
-        <v>8.553000000000001</v>
+        <v>7.803</v>
       </c>
       <c r="W11" t="n">
-        <v>-40.968</v>
+        <v>-41.355</v>
       </c>
     </row>
     <row r="12">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3660,14 +3660,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.74% / +20.03% / -1.13% | TKFEN.IS: +11.95% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +8.87% / +20.03% / -1.13% | TKFEN.IS: +12.27% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>8.811158021390009</v>
+        <v>8.562399589571768</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3676,7 +3676,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="O12" t="n">
         <v>43.3</v>
@@ -3699,13 +3699,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>37.584</v>
+        <v>38.295</v>
       </c>
       <c r="V12" t="n">
-        <v>51.618</v>
+        <v>51.271</v>
       </c>
       <c r="W12" t="n">
-        <v>-18.282</v>
+        <v>-18.735</v>
       </c>
     </row>
     <row r="13">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3747,14 +3747,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.26% / +1.03% / -3.32% | FENER.IS: -1.31% / +0.69% / -1.58%</t>
+          <t>ASTOR.IS: -2.78% / +1.03% / -3.32% | FENER.IS: -1.31% / +0.69% / -1.90%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K13" t="n">
-        <v>8.567135442638163</v>
+        <v>7.185267193638833</v>
       </c>
       <c r="L13" t="n">
         <v>19.61961325199098</v>
@@ -3763,7 +3763,7 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N13" t="n">
-        <v>87.8</v>
+        <v>87.7</v>
       </c>
       <c r="O13" t="n">
         <v>46</v>
@@ -3786,13 +3786,13 @@
         <v>18.132</v>
       </c>
       <c r="U13" t="n">
-        <v>10.376</v>
+        <v>6.726</v>
       </c>
       <c r="V13" t="n">
-        <v>13.366</v>
+        <v>11.923</v>
       </c>
       <c r="W13" t="n">
-        <v>-6.184</v>
+        <v>-7.432</v>
       </c>
     </row>
     <row r="14">
@@ -3811,37 +3811,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ASTOR.IS, KRDMD.IS</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ASTOR.IS: 2026-09-01 | KRDMD.IS: 2026-09-02</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>8.530010255723974</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>ASTOR.IS: -0.26% / +1.03% / -3.32% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
         <v>0.8142516931666233</v>
       </c>
       <c r="K14" t="n">
-        <v>8.043265356219909</v>
+        <v>6.48315810656519</v>
       </c>
       <c r="L14" t="n">
         <v>9.181211458048665</v>
@@ -3856,15 +3844,15 @@
         <v>50</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>8.083</v>
@@ -3873,13 +3861,13 @@
         <v>7.916</v>
       </c>
       <c r="U14" t="n">
-        <v>14.519</v>
+        <v>12.877</v>
       </c>
       <c r="V14" t="n">
-        <v>9.157</v>
+        <v>7.58</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.576</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="16">
@@ -4024,22 +4012,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ALARK.IS, TKFEN.IS</t>
+          <t>ALARK.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | TKFEN.IS: 2026-08-05</t>
+          <t>ALARK.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -4047,14 +4035,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | TKFEN.IS: +11.95% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: +2.20% / +2.95% / -3.23%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001928040318710522</v>
+        <v>0.28182546797757</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4063,7 +4051,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>92.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O18" t="n">
         <v>44.6</v>
@@ -4077,7 +4065,7 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>18.106</v>
@@ -4086,13 +4074,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>283.616</v>
+        <v>277.454</v>
       </c>
       <c r="V18" t="n">
-        <v>101.451</v>
+        <v>102.015</v>
       </c>
       <c r="W18" t="n">
-        <v>-42.803</v>
+        <v>-40.945</v>
       </c>
     </row>
     <row r="19">
@@ -4113,12 +4101,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4136,14 +4124,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | ALTNY.IS: -1.65% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.80% / +3.27% / -0.09%</t>
+          <t>ALARK.IS: +2.20% / +2.95% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -2.55% / +1.19% / -2.61% | ENERY.IS: +0.27% / +1.23% / -0.10% | ENJSA.IS: +2.07% / +3.36% / -0.09%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-9.560560652765593</v>
+        <v>-10.18560854326407</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4152,10 +4140,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>117.8</v>
+        <v>117.5</v>
       </c>
       <c r="O19" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="P19" t="n">
         <v>3.9</v>
@@ -4169,19 +4157,19 @@
         <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>24.688</v>
+        <v>25.041</v>
       </c>
       <c r="T19" t="n">
-        <v>24.688</v>
+        <v>25.041</v>
       </c>
       <c r="U19" t="n">
-        <v>60.052</v>
+        <v>56.999</v>
       </c>
       <c r="V19" t="n">
-        <v>21.679</v>
+        <v>20.838</v>
       </c>
       <c r="W19" t="n">
-        <v>-51.991</v>
+        <v>-52.446</v>
       </c>
     </row>
     <row r="20">
@@ -4202,22 +4190,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ALARK.IS, TKFEN.IS</t>
+          <t>ALARK.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | TKFEN.IS: 2026-08-05</t>
+          <t>ALARK.IS: 2026-08-31</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -4225,14 +4213,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | TKFEN.IS: +11.95% / +31.83% / -0.56%</t>
+          <t>ALARK.IS: +2.20% / +2.95% / -3.23%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.01809139526269821</v>
+        <v>0.261749999591232</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4241,7 +4229,7 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="O20" t="n">
         <v>42.7</v>
@@ -4255,7 +4243,7 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>21.096</v>
@@ -4264,13 +4252,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>280.866</v>
+        <v>274.663</v>
       </c>
       <c r="V20" t="n">
-        <v>83.45399999999999</v>
+        <v>83.968</v>
       </c>
       <c r="W20" t="n">
-        <v>-42.448</v>
+        <v>-40.594</v>
       </c>
     </row>
     <row r="21">
@@ -4291,12 +4279,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4314,14 +4302,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | ALTNY.IS: -1.65% / +0.00% / -3.49% | ASTOR.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +2.80% / +3.27% / -0.09%</t>
+          <t>ALARK.IS: +2.20% / +2.95% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -2.55% / +1.19% / -2.61% | ENERY.IS: +0.27% / +1.23% / -0.10% | ENJSA.IS: +2.07% / +3.36% / -0.09%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.476103953919047</v>
+        <v>-10.10173554420417</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4330,10 +4318,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>178.6</v>
+        <v>178.3</v>
       </c>
       <c r="O21" t="n">
-        <v>52.2</v>
+        <v>52.5</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
@@ -4347,19 +4335,19 @@
         <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>23.355</v>
+        <v>23.714</v>
       </c>
       <c r="T21" t="n">
-        <v>23.355</v>
+        <v>23.714</v>
       </c>
       <c r="U21" t="n">
-        <v>35.747</v>
+        <v>33.037</v>
       </c>
       <c r="V21" t="n">
-        <v>8.553000000000001</v>
+        <v>7.803</v>
       </c>
       <c r="W21" t="n">
-        <v>-40.968</v>
+        <v>-41.355</v>
       </c>
     </row>
     <row r="22">
@@ -4380,12 +4368,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4403,14 +4391,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -0.02% / +0.00% / 0.00% | BRSAN.IS: +9.74% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | ENERY.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +11.95% / +31.83% / -0.56%</t>
+          <t>ALTNY.IS: -0.94% / +0.85% / -1.04% | BRSAN.IS: +8.87% / +20.03% / -1.13% | CANTE.IS: +7.02% / +15.84% / -2.80% | ENERY.IS: +0.27% / +1.23% / -0.10% | TKFEN.IS: +12.27% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.09242331958823</v>
+        <v>-10.39056794739956</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4419,10 +4407,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>139.2</v>
+        <v>138.9</v>
       </c>
       <c r="O22" t="n">
-        <v>42.3</v>
+        <v>42.7</v>
       </c>
       <c r="P22" t="n">
         <v>5.7</v>
@@ -4436,19 +4424,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>26.15</v>
+        <v>26.158</v>
       </c>
       <c r="T22" t="n">
-        <v>26.15</v>
+        <v>26.158</v>
       </c>
       <c r="U22" t="n">
-        <v>24.756</v>
+        <v>24.526</v>
       </c>
       <c r="V22" t="n">
-        <v>11.779</v>
+        <v>11.408</v>
       </c>
       <c r="W22" t="n">
-        <v>-43.634</v>
+        <v>-44.113</v>
       </c>
     </row>
     <row r="23">
@@ -4469,12 +4457,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4492,14 +4480,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.74% / +20.03% / -1.13% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +8.87% / +20.03% / -1.13% | CANTE.IS: -0.77% / +1.46% / -0.80% | ENERY.IS: +0.27% / +1.23% / -0.10%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.468690306550293</v>
+        <v>-3.794250119283926</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4508,10 +4496,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>154.2</v>
+        <v>153.9</v>
       </c>
       <c r="O23" t="n">
-        <v>41.7</v>
+        <v>42.1</v>
       </c>
       <c r="P23" t="n">
         <v>4.2</v>
@@ -4531,13 +4519,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>20.966</v>
+        <v>21.282</v>
       </c>
       <c r="V23" t="n">
-        <v>1.175</v>
+        <v>0.833</v>
       </c>
       <c r="W23" t="n">
-        <v>-32.25</v>
+        <v>-32.854</v>
       </c>
     </row>
     <row r="24">
@@ -4558,12 +4546,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4581,14 +4569,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.92% / +2.49% / -3.23% | CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +2.20% / +2.95% / -3.23% | CANTE.IS: -0.77% / +1.46% / -0.80% | ENERY.IS: +0.27% / +1.23% / -0.10%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.610798768024204</v>
+        <v>-3.649039617463301</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4597,10 +4585,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>114.3</v>
+        <v>114</v>
       </c>
       <c r="O24" t="n">
-        <v>49.8</v>
+        <v>50.2</v>
       </c>
       <c r="P24" t="n">
         <v>2.4</v>
@@ -4614,19 +4602,19 @@
         <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>20.194</v>
+        <v>20.226</v>
       </c>
       <c r="T24" t="n">
-        <v>20.194</v>
+        <v>20.226</v>
       </c>
       <c r="U24" t="n">
-        <v>9.679</v>
+        <v>10.21</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.034</v>
+        <v>-3.073</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.754</v>
+        <v>-27.943</v>
       </c>
     </row>
     <row r="25">
@@ -4647,12 +4635,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -4674,7 +4662,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>75.8</v>
+        <v>75.7</v>
       </c>
       <c r="O25" t="n">
         <v>49.3</v>
@@ -4697,13 +4685,13 @@
         <v>13.28</v>
       </c>
       <c r="U25" t="n">
-        <v>8.565</v>
+        <v>9.128</v>
       </c>
       <c r="V25" t="n">
         <v>-0.962</v>
       </c>
       <c r="W25" t="n">
-        <v>-16.626</v>
+        <v>-16.712</v>
       </c>
     </row>
     <row r="26">
@@ -4724,37 +4712,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ASTOR.IS, KRDMD.IS</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ASTOR.IS: 2026-09-01 | KRDMD.IS: 2026-09-02</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>8.530010255723974</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>ASTOR.IS: -0.26% / +1.03% / -3.32% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
         <v>0.8142516931666233</v>
       </c>
       <c r="K26" t="n">
-        <v>8.043265356219909</v>
+        <v>6.48315810656519</v>
       </c>
       <c r="L26" t="n">
         <v>9.181211458048665</v>
@@ -4769,15 +4745,15 @@
         <v>50</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>8.083</v>
@@ -4786,13 +4762,13 @@
         <v>7.916</v>
       </c>
       <c r="U26" t="n">
-        <v>14.519</v>
+        <v>12.877</v>
       </c>
       <c r="V26" t="n">
-        <v>9.157</v>
+        <v>7.58</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.576</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="27">
@@ -4813,12 +4789,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4836,14 +4812,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.74% / +20.03% / -1.13% | TKFEN.IS: +11.95% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +8.87% / +20.03% / -1.13% | TKFEN.IS: +12.27% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>8.811158021390009</v>
+        <v>8.562399589571768</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4852,7 +4828,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N27" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="O27" t="n">
         <v>43.3</v>
@@ -4875,13 +4851,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>37.584</v>
+        <v>38.295</v>
       </c>
       <c r="V27" t="n">
-        <v>51.618</v>
+        <v>51.271</v>
       </c>
       <c r="W27" t="n">
-        <v>-18.282</v>
+        <v>-18.735</v>
       </c>
     </row>
     <row r="28">
@@ -4902,12 +4878,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4925,14 +4901,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.26% / +1.03% / -3.32% | FENER.IS: -1.31% / +0.69% / -1.58%</t>
+          <t>ASTOR.IS: -2.78% / +1.03% / -3.32% | FENER.IS: -1.31% / +0.69% / -1.90%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>8.567135442638163</v>
+        <v>7.185267193638833</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4941,7 +4917,7 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N28" t="n">
-        <v>87.8</v>
+        <v>87.7</v>
       </c>
       <c r="O28" t="n">
         <v>46</v>
@@ -4964,13 +4940,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>10.376</v>
+        <v>6.726</v>
       </c>
       <c r="V28" t="n">
-        <v>13.366</v>
+        <v>11.923</v>
       </c>
       <c r="W28" t="n">
-        <v>-6.184</v>
+        <v>-7.432</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +1.50% / -0.75% | VAKBN.IS: +1.15% / +2.23% / 0.00%</t>
+          <t>CANTE.IS: +1.48% / +2.26% / -2.26% | VAKBN.IS: +0.10% / +2.23% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-15.35964179515489</v>
+        <v>-14.85325520074797</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -775,7 +775,7 @@
         <v>102.7</v>
       </c>
       <c r="O3" t="n">
-        <v>43.5</v>
+        <v>44</v>
       </c>
       <c r="P3" t="n">
         <v>6.7</v>
@@ -795,13 +795,13 @@
         <v>21.661</v>
       </c>
       <c r="U3" t="n">
-        <v>60.827</v>
+        <v>61.789</v>
       </c>
       <c r="V3" t="n">
-        <v>14.99</v>
+        <v>15.678</v>
       </c>
       <c r="W3" t="n">
-        <v>-44.078</v>
+        <v>-43.116</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +1.50% / -0.75% | VAKBN.IS: +1.15% / +2.23% / 0.00%</t>
+          <t>CANTE.IS: +1.48% / +2.26% / -2.26% | VAKBN.IS: +0.10% / +2.23% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-15.35964179515489</v>
+        <v>-14.85325520074797</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1012,7 +1012,7 @@
         <v>102.7</v>
       </c>
       <c r="O6" t="n">
-        <v>43.5</v>
+        <v>44</v>
       </c>
       <c r="P6" t="n">
         <v>6.7</v>
@@ -1032,13 +1032,13 @@
         <v>21.661</v>
       </c>
       <c r="U6" t="n">
-        <v>60.827</v>
+        <v>61.789</v>
       </c>
       <c r="V6" t="n">
-        <v>14.99</v>
+        <v>15.678</v>
       </c>
       <c r="W6" t="n">
-        <v>-44.078</v>
+        <v>-43.116</v>
       </c>
     </row>
     <row r="7">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +1.50% / -0.75% | VAKBN.IS: +1.15% / +2.23% / 0.00%</t>
+          <t>CANTE.IS: +1.48% / +2.26% / -2.26% | VAKBN.IS: +0.10% / +2.23% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.835217886257837</v>
+        <v>-4.265865736241825</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1099,7 +1099,7 @@
         <v>134.9</v>
       </c>
       <c r="O7" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1119,13 +1119,13 @@
         <v>17.439</v>
       </c>
       <c r="U7" t="n">
-        <v>71.90300000000001</v>
+        <v>72.932</v>
       </c>
       <c r="V7" t="n">
-        <v>30.219</v>
+        <v>30.998</v>
       </c>
       <c r="W7" t="n">
-        <v>-35.914</v>
+        <v>-34.885</v>
       </c>
     </row>
     <row r="8">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ALTNY.IS, ENERY.IS, KRDMD.IS</t>
+          <t>ALARK.IS, ENERY.IS, KRDMD.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ALTNY.IS: 2026-08-31 | ENERY.IS: 2026-09-02 | KRDMD.IS: 2026-09-01</t>
+          <t>ALARK.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | KRDMD.IS: 2026-09-01</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -2.56% / +0.00% / -3.49% | ENERY.IS: +0.27% / +1.24% / -0.10% | KRDMD.IS: +0.07% / +1.08% / -3.24%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.54% / +2.48% / -1.62% | KRDMD.IS: -1.10% / +1.08% / -3.24%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-14.76266051766313</v>
+        <v>-16.04366387849218</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1183,10 +1183,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>191.5</v>
+        <v>192</v>
       </c>
       <c r="O8" t="n">
-        <v>47.2</v>
+        <v>46.5</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1200,19 +1200,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>16.099</v>
+        <v>17.36</v>
       </c>
       <c r="T8" t="n">
-        <v>16.099</v>
+        <v>17.36</v>
       </c>
       <c r="U8" t="n">
-        <v>42.893</v>
+        <v>40.745</v>
       </c>
       <c r="V8" t="n">
-        <v>13.169</v>
+        <v>11.468</v>
       </c>
       <c r="W8" t="n">
-        <v>-27.418</v>
+        <v>-29.566</v>
       </c>
     </row>
     <row r="9">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +1.50% / -0.75% | VAKBN.IS: +1.15% / +2.23% / 0.00%</t>
+          <t>CANTE.IS: +1.48% / +2.26% / -2.26% | VAKBN.IS: +0.10% / +2.23% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-15.35964179515489</v>
+        <v>-14.85325520074797</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1273,7 +1273,7 @@
         <v>102.7</v>
       </c>
       <c r="O9" t="n">
-        <v>43.5</v>
+        <v>44</v>
       </c>
       <c r="P9" t="n">
         <v>6.7</v>
@@ -1293,13 +1293,13 @@
         <v>21.661</v>
       </c>
       <c r="U9" t="n">
-        <v>60.827</v>
+        <v>61.789</v>
       </c>
       <c r="V9" t="n">
-        <v>14.99</v>
+        <v>15.678</v>
       </c>
       <c r="W9" t="n">
-        <v>-44.078</v>
+        <v>-43.116</v>
       </c>
     </row>
     <row r="10">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>KUYAS.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: +0.08% / +1.89% / -0.40%</t>
+          <t>KUYAS.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -1.65% / +1.89% / -1.71%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.444209921439257</v>
+        <v>-3.995503466783423</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1360,7 +1360,7 @@
         <v>175.6</v>
       </c>
       <c r="O10" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>15.711</v>
+        <v>16.254</v>
       </c>
       <c r="V10" t="n">
-        <v>7.588</v>
+        <v>8.093</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.677</v>
+        <v>-9.134</v>
       </c>
     </row>
     <row r="11">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1490,42 +1490,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
+          <t>ASTOR.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
+          <t>ASTOR.IS: 2026-09-03 | TRALT.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>13.58351811074014</v>
+        <v>20.48700524499634</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.69% / +20.94% / 0.00% | RALYH.IS: +23.89% / +35.10% / -0.91% | VAKBN.IS: +1.15% / +2.23% / 0.00%</t>
+          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-10.39434387728287</v>
+        <v>-3.767340978838807</v>
       </c>
       <c r="K12" t="n">
-        <v>10.74849862712506</v>
+        <v>10.83793225314063</v>
       </c>
       <c r="L12" t="n">
-        <v>34.56349599547857</v>
+        <v>16.57596537747867</v>
       </c>
       <c r="M12" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>69.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="O12" t="n">
-        <v>44.7</v>
+        <v>47.5</v>
       </c>
       <c r="P12" t="n">
-        <v>6.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>23.777</v>
+        <v>17.404</v>
       </c>
       <c r="T12" t="n">
-        <v>23.777</v>
+        <v>17.404</v>
       </c>
       <c r="U12" t="n">
-        <v>46.477</v>
+        <v>49.915</v>
       </c>
       <c r="V12" t="n">
-        <v>40.349</v>
+        <v>42.487</v>
       </c>
       <c r="W12" t="n">
-        <v>-13.561</v>
+        <v>-4.787</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASTOR.IS, TRALT.IS</t>
+          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-01 | TRALT.IS: 2026-09-03</t>
+          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>20.48700524499634</v>
+        <v>13.58351811074014</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -2.78% / +1.03% / -3.31% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +9.61% / +20.94% / 0.00% | RALYH.IS: +22.81% / +35.10% / -0.91% | VAKBN.IS: +0.10% / +2.23% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-3.767340978838807</v>
+        <v>-10.39434387728287</v>
       </c>
       <c r="K13" t="n">
-        <v>10.28137551708646</v>
+        <v>10.0002218501311</v>
       </c>
       <c r="L13" t="n">
-        <v>16.57596537747867</v>
+        <v>34.56349599547857</v>
       </c>
       <c r="M13" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>88.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>47.2</v>
+        <v>44.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1620,22 +1620,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
-        <v>17.404</v>
+        <v>23.777</v>
       </c>
       <c r="T13" t="n">
-        <v>17.404</v>
+        <v>23.777</v>
       </c>
       <c r="U13" t="n">
-        <v>49.162</v>
+        <v>45.487</v>
       </c>
       <c r="V13" t="n">
-        <v>41.772</v>
+        <v>39.401</v>
       </c>
       <c r="W13" t="n">
-        <v>-5.54</v>
+        <v>-14.551</v>
       </c>
     </row>
     <row r="14">
@@ -1878,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +1.50% / -0.75% | VAKBN.IS: +1.15% / +2.23% / 0.00%</t>
+          <t>CANTE.IS: +1.48% / +2.26% / -2.26% | VAKBN.IS: +0.10% / +2.23% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-15.35964179515489</v>
+        <v>-14.85325520074797</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1897,7 +1897,7 @@
         <v>102.7</v>
       </c>
       <c r="O18" t="n">
-        <v>43.5</v>
+        <v>44</v>
       </c>
       <c r="P18" t="n">
         <v>6.7</v>
@@ -1917,13 +1917,13 @@
         <v>21.661</v>
       </c>
       <c r="U18" t="n">
-        <v>60.827</v>
+        <v>61.789</v>
       </c>
       <c r="V18" t="n">
-        <v>14.99</v>
+        <v>15.678</v>
       </c>
       <c r="W18" t="n">
-        <v>-44.078</v>
+        <v>-43.116</v>
       </c>
     </row>
     <row r="19">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ALTNY.IS, ENERY.IS, KRDMD.IS</t>
+          <t>ALARK.IS, ENERY.IS, KRDMD.IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ALTNY.IS: 2026-08-31 | ENERY.IS: 2026-09-02 | KRDMD.IS: 2026-09-01</t>
+          <t>ALARK.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | KRDMD.IS: 2026-09-01</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -2.56% / +0.00% / -3.49% | ENERY.IS: +0.27% / +1.24% / -0.10% | KRDMD.IS: +0.07% / +1.08% / -3.24%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.54% / +2.48% / -1.62% | KRDMD.IS: -1.10% / +1.08% / -3.24%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-14.76266051766313</v>
+        <v>-16.04366387849218</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2137,10 +2137,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>191.5</v>
+        <v>192</v>
       </c>
       <c r="O21" t="n">
-        <v>47.2</v>
+        <v>46.5</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2154,19 +2154,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>16.099</v>
+        <v>17.36</v>
       </c>
       <c r="T21" t="n">
-        <v>16.099</v>
+        <v>17.36</v>
       </c>
       <c r="U21" t="n">
-        <v>42.893</v>
+        <v>40.745</v>
       </c>
       <c r="V21" t="n">
-        <v>13.169</v>
+        <v>11.468</v>
       </c>
       <c r="W21" t="n">
-        <v>-27.418</v>
+        <v>-29.566</v>
       </c>
     </row>
     <row r="22">
@@ -2210,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +1.50% / -0.75% | VAKBN.IS: +1.15% / +2.23% / 0.00%</t>
+          <t>CANTE.IS: +1.48% / +2.26% / -2.26% | VAKBN.IS: +0.10% / +2.23% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.835217886257837</v>
+        <v>-4.265865736241825</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2229,7 +2229,7 @@
         <v>134.9</v>
       </c>
       <c r="O22" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
@@ -2249,13 +2249,13 @@
         <v>17.439</v>
       </c>
       <c r="U22" t="n">
-        <v>71.90300000000001</v>
+        <v>72.932</v>
       </c>
       <c r="V22" t="n">
-        <v>30.219</v>
+        <v>30.998</v>
       </c>
       <c r="W22" t="n">
-        <v>-35.914</v>
+        <v>-34.885</v>
       </c>
     </row>
     <row r="23">
@@ -2453,14 +2453,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>KUYAS.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: +0.08% / +1.89% / -0.40%</t>
+          <t>KUYAS.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -1.65% / +1.89% / -1.71%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.444209921439257</v>
+        <v>-3.995503466783423</v>
       </c>
       <c r="L25" t="n">
         <v>4.543450519200398</v>
@@ -2472,7 +2472,7 @@
         <v>175.6</v>
       </c>
       <c r="O25" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="P25" t="n">
         <v>1.9</v>
@@ -2492,13 +2492,13 @@
         <v>10.072</v>
       </c>
       <c r="U25" t="n">
-        <v>15.711</v>
+        <v>16.254</v>
       </c>
       <c r="V25" t="n">
-        <v>7.588</v>
+        <v>8.093</v>
       </c>
       <c r="W25" t="n">
-        <v>-9.677</v>
+        <v>-9.134</v>
       </c>
     </row>
     <row r="26">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-01 | TRALT.IS: 2026-09-03</t>
+          <t>ASTOR.IS: 2026-09-03 | TRALT.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2542,14 +2542,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -2.78% / +1.03% / -3.31% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-3.767340978838807</v>
       </c>
       <c r="K26" t="n">
-        <v>10.28137551708646</v>
+        <v>10.83793225314063</v>
       </c>
       <c r="L26" t="n">
         <v>16.57596537747867</v>
@@ -2558,10 +2558,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>88.3</v>
+        <v>88.8</v>
       </c>
       <c r="O26" t="n">
-        <v>47.2</v>
+        <v>47.5</v>
       </c>
       <c r="P26" t="n">
         <v>2.5</v>
@@ -2581,13 +2581,13 @@
         <v>17.404</v>
       </c>
       <c r="U26" t="n">
-        <v>49.162</v>
+        <v>49.915</v>
       </c>
       <c r="V26" t="n">
-        <v>41.772</v>
+        <v>42.487</v>
       </c>
       <c r="W26" t="n">
-        <v>-5.54</v>
+        <v>-4.787</v>
       </c>
     </row>
     <row r="27">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.69% / +20.94% / 0.00% | RALYH.IS: +23.89% / +35.10% / -0.91% | VAKBN.IS: +1.15% / +2.23% / 0.00%</t>
+          <t>BRSAN.IS: +9.61% / +20.94% / 0.00% | RALYH.IS: +22.81% / +35.10% / -0.91% | VAKBN.IS: +0.10% / +2.23% / 0.00%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>10.74849862712506</v>
+        <v>10.0002218501311</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2670,13 +2670,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>46.477</v>
+        <v>45.487</v>
       </c>
       <c r="V27" t="n">
-        <v>40.349</v>
+        <v>39.401</v>
       </c>
       <c r="W27" t="n">
-        <v>-13.561</v>
+        <v>-14.551</v>
       </c>
     </row>
   </sheetData>
@@ -2889,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.20% / +2.95% / -3.23%</t>
+          <t>ALARK.IS: +2.47% / +3.97% / -3.23%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>0.28182546797757</v>
+        <v>-0.7135304692478472</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2928,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>277.454</v>
+        <v>273.708</v>
       </c>
       <c r="V3" t="n">
-        <v>102.015</v>
+        <v>100.01</v>
       </c>
       <c r="W3" t="n">
-        <v>-40.945</v>
+        <v>-44.691</v>
       </c>
     </row>
     <row r="4">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, ASTOR.IS, ENERY.IS, ENJSA.IS</t>
+          <t>ALARK.IS, ALTNY.IS, ENERY.IS, ENJSA.IS, SOKM.IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | ASTOR.IS: 2026-09-02 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2976,14 +2976,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.20% / +2.95% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -2.55% / +1.19% / -2.61% | ENERY.IS: +0.27% / +1.23% / -0.10% | ENJSA.IS: +2.07% / +3.36% / -0.09%</t>
+          <t>ALARK.IS: +2.47% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.54% / +2.47% / -1.62% | ENJSA.IS: +2.70% / +3.36% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.18560854326407</v>
+        <v>-10.87649869230984</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2992,13 +2992,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>117.5</v>
+        <v>118.5</v>
       </c>
       <c r="O4" t="n">
-        <v>47.5</v>
+        <v>46.6</v>
       </c>
       <c r="P4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>25.041</v>
+        <v>25.617</v>
       </c>
       <c r="T4" t="n">
-        <v>25.041</v>
+        <v>25.617</v>
       </c>
       <c r="U4" t="n">
-        <v>56.999</v>
+        <v>55.792</v>
       </c>
       <c r="V4" t="n">
-        <v>20.838</v>
+        <v>19.909</v>
       </c>
       <c r="W4" t="n">
-        <v>-52.446</v>
+        <v>-53.654</v>
       </c>
     </row>
     <row r="5">
@@ -3063,14 +3063,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.20% / +2.95% / -3.23%</t>
+          <t>ALARK.IS: +2.47% / +3.97% / -3.23%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.261749999591232</v>
+        <v>-0.7334066768353353</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3102,13 +3102,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>274.663</v>
+        <v>270.944</v>
       </c>
       <c r="V5" t="n">
-        <v>83.968</v>
+        <v>82.142</v>
       </c>
       <c r="W5" t="n">
-        <v>-40.594</v>
+        <v>-44.313</v>
       </c>
     </row>
     <row r="6">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ALTNY.IS, BRSAN.IS, CANTE.IS, ENERY.IS, TKFEN.IS</t>
+          <t>BRSAN.IS, CANTE.IS, ENERY.IS, SOKM.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ALTNY.IS: 2026-09-02 | BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-02 | TKFEN.IS: 2026-08-05</t>
+          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-02 | SOKM.IS: 2026-09-03 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3150,14 +3150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -0.94% / +0.85% / -1.04% | BRSAN.IS: +8.87% / +20.03% / -1.13% | CANTE.IS: +7.02% / +15.84% / -2.80% | ENERY.IS: +0.27% / +1.23% / -0.10% | TKFEN.IS: +12.27% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +8.79% / +20.03% / -1.13% | CANTE.IS: +9.45% / +15.84% / -2.80% | ENERY.IS: -1.54% / +2.47% / -1.62% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +9.97% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.39056794739956</v>
+        <v>-11.03951962468362</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3166,10 +3166,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>138.9</v>
+        <v>139.4</v>
       </c>
       <c r="O6" t="n">
-        <v>42.7</v>
+        <v>42.1</v>
       </c>
       <c r="P6" t="n">
         <v>5.7</v>
@@ -3183,19 +3183,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>26.158</v>
+        <v>26.693</v>
       </c>
       <c r="T6" t="n">
-        <v>26.158</v>
+        <v>26.693</v>
       </c>
       <c r="U6" t="n">
-        <v>24.526</v>
+        <v>23.624</v>
       </c>
       <c r="V6" t="n">
-        <v>11.408</v>
+        <v>10.602</v>
       </c>
       <c r="W6" t="n">
-        <v>-44.113</v>
+        <v>-45.015</v>
       </c>
     </row>
     <row r="7">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, ASTOR.IS, ENERY.IS, ENJSA.IS</t>
+          <t>ALARK.IS, ALTNY.IS, ENERY.IS, ENJSA.IS, SOKM.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | ASTOR.IS: 2026-09-02 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3237,14 +3237,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.20% / +2.95% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -2.55% / +1.19% / -2.61% | ENERY.IS: +0.27% / +1.23% / -0.10% | ENJSA.IS: +2.07% / +3.36% / -0.09%</t>
+          <t>ALARK.IS: +2.47% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.54% / +2.47% / -1.62% | ENJSA.IS: +2.70% / +3.36% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.18560854326407</v>
+        <v>-10.87649869230984</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3253,13 +3253,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>117.5</v>
+        <v>118.5</v>
       </c>
       <c r="O7" t="n">
-        <v>47.5</v>
+        <v>46.6</v>
       </c>
       <c r="P7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -3270,19 +3270,19 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>25.041</v>
+        <v>25.617</v>
       </c>
       <c r="T7" t="n">
-        <v>25.041</v>
+        <v>25.617</v>
       </c>
       <c r="U7" t="n">
-        <v>56.999</v>
+        <v>55.792</v>
       </c>
       <c r="V7" t="n">
-        <v>20.838</v>
+        <v>19.909</v>
       </c>
       <c r="W7" t="n">
-        <v>-52.446</v>
+        <v>-53.654</v>
       </c>
     </row>
     <row r="8">
@@ -3324,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.87% / +20.03% / -1.13% | CANTE.IS: -0.77% / +1.46% / -0.80% | ENERY.IS: +0.27% / +1.23% / -0.10%</t>
+          <t>BRSAN.IS: +8.79% / +20.03% / -1.13% | CANTE.IS: +1.48% / +2.21% / -2.30% | ENERY.IS: -1.54% / +2.47% / -1.62%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.794250119283926</v>
+        <v>-3.742360135314404</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3363,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>21.282</v>
+        <v>21.347</v>
       </c>
       <c r="V8" t="n">
-        <v>0.833</v>
+        <v>0.888</v>
       </c>
       <c r="W8" t="n">
-        <v>-32.854</v>
+        <v>-32.789</v>
       </c>
     </row>
     <row r="9">
@@ -3486,14 +3486,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.20% / +2.95% / -3.23% | CANTE.IS: -0.77% / +1.46% / -0.80% | ENERY.IS: +0.27% / +1.23% / -0.10%</t>
+          <t>ALARK.IS: +2.47% / +3.97% / -3.23% | CANTE.IS: +1.48% / +2.21% / -2.30% | ENERY.IS: -1.54% / +2.47% / -1.62%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.649039617463301</v>
+        <v>-3.50428724728844</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3519,19 +3519,19 @@
         <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>20.226</v>
+        <v>20.181</v>
       </c>
       <c r="T10" t="n">
-        <v>20.226</v>
+        <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>10.21</v>
+        <v>10.375</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.073</v>
+        <v>-2.927</v>
       </c>
       <c r="W10" t="n">
-        <v>-27.943</v>
+        <v>-27.777</v>
       </c>
     </row>
     <row r="11">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, ASTOR.IS, ENERY.IS, ENJSA.IS</t>
+          <t>ALARK.IS, ALTNY.IS, ENERY.IS, ENJSA.IS, SOKM.IS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | ASTOR.IS: 2026-09-02 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -3573,14 +3573,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.20% / +2.95% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -2.55% / +1.19% / -2.61% | ENERY.IS: +0.27% / +1.23% / -0.10% | ENJSA.IS: +2.07% / +3.36% / -0.09%</t>
+          <t>ALARK.IS: +2.47% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.54% / +2.47% / -1.62% | ENJSA.IS: +2.70% / +3.36% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.10173554420417</v>
+        <v>-10.79327087970484</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3589,10 +3589,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>178.3</v>
+        <v>179.3</v>
       </c>
       <c r="O11" t="n">
-        <v>52.5</v>
+        <v>51.9</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
@@ -3606,19 +3606,19 @@
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>23.714</v>
+        <v>24.301</v>
       </c>
       <c r="T11" t="n">
-        <v>23.714</v>
+        <v>24.301</v>
       </c>
       <c r="U11" t="n">
-        <v>33.037</v>
+        <v>32.013</v>
       </c>
       <c r="V11" t="n">
-        <v>7.803</v>
+        <v>6.974</v>
       </c>
       <c r="W11" t="n">
-        <v>-41.355</v>
+        <v>-42.378</v>
       </c>
     </row>
     <row r="12">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3647,42 +3647,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
+          <t>ASTOR.IS, FENER.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
+          <t>ASTOR.IS: 2026-09-03 | FENER.IS: 2026-09-01</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6.880672511445463</v>
+        <v>-0.49388395046156</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.87% / +20.03% / -1.13% | TKFEN.IS: +12.27% / +31.83% / -0.56%</t>
+          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | FENER.IS: +0.95% / +1.01% / -1.90%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-18.9000927288166</v>
+        <v>-19.60937535624424</v>
       </c>
       <c r="K12" t="n">
-        <v>8.562399589571768</v>
+        <v>7.726358197822303</v>
       </c>
       <c r="L12" t="n">
-        <v>31.31195090134997</v>
+        <v>19.61961325199098</v>
       </c>
       <c r="M12" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N12" t="n">
-        <v>48.3</v>
+        <v>88.2</v>
       </c>
       <c r="O12" t="n">
-        <v>43.3</v>
+        <v>46.3</v>
       </c>
       <c r="P12" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3693,19 +3693,19 @@
         <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>28.439</v>
+        <v>18.132</v>
       </c>
       <c r="T12" t="n">
-        <v>28.439</v>
+        <v>18.132</v>
       </c>
       <c r="U12" t="n">
-        <v>38.295</v>
+        <v>7.265</v>
       </c>
       <c r="V12" t="n">
-        <v>51.271</v>
+        <v>12.488</v>
       </c>
       <c r="W12" t="n">
-        <v>-18.735</v>
+        <v>-6.894</v>
       </c>
     </row>
     <row r="13">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3734,42 +3734,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASTOR.IS, FENER.IS</t>
+          <t>BRSAN.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-01 | FENER.IS: 2026-09-01</t>
+          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-0.49388395046156</v>
+        <v>6.880672511445463</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -2.78% / +1.03% / -3.32% | FENER.IS: -1.31% / +0.69% / -1.90%</t>
+          <t>BRSAN.IS: +8.79% / +20.03% / -1.13% | TKFEN.IS: +9.97% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-19.60937535624424</v>
+        <v>-18.9000927288166</v>
       </c>
       <c r="K13" t="n">
-        <v>7.185267193638833</v>
+        <v>7.357304125380115</v>
       </c>
       <c r="L13" t="n">
-        <v>19.61961325199098</v>
+        <v>31.31195090134997</v>
       </c>
       <c r="M13" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>87.7</v>
+        <v>48.3</v>
       </c>
       <c r="O13" t="n">
-        <v>46</v>
+        <v>43.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3780,19 +3780,19 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>18.132</v>
+        <v>28.439</v>
       </c>
       <c r="T13" t="n">
-        <v>18.132</v>
+        <v>28.439</v>
       </c>
       <c r="U13" t="n">
-        <v>6.726</v>
+        <v>36.76</v>
       </c>
       <c r="V13" t="n">
-        <v>11.923</v>
+        <v>49.592</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.432</v>
+        <v>-20.27</v>
       </c>
     </row>
     <row r="14">
@@ -3829,7 +3829,7 @@
         <v>0.8142516931666233</v>
       </c>
       <c r="K14" t="n">
-        <v>6.48315810656519</v>
+        <v>5.183764598665919</v>
       </c>
       <c r="L14" t="n">
         <v>9.181211458048665</v>
@@ -3861,13 +3861,13 @@
         <v>7.916</v>
       </c>
       <c r="U14" t="n">
-        <v>12.877</v>
+        <v>11.499</v>
       </c>
       <c r="V14" t="n">
-        <v>7.58</v>
+        <v>6.268</v>
       </c>
       <c r="W14" t="n">
-        <v>-2.23</v>
+        <v>-3.607</v>
       </c>
     </row>
     <row r="16">
@@ -4035,14 +4035,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.20% / +2.95% / -3.23%</t>
+          <t>ALARK.IS: +2.47% / +3.97% / -3.23%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>0.28182546797757</v>
+        <v>-0.7135304692478472</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4074,13 +4074,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>277.454</v>
+        <v>273.708</v>
       </c>
       <c r="V18" t="n">
-        <v>102.015</v>
+        <v>100.01</v>
       </c>
       <c r="W18" t="n">
-        <v>-40.945</v>
+        <v>-44.691</v>
       </c>
     </row>
     <row r="19">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, ASTOR.IS, ENERY.IS, ENJSA.IS</t>
+          <t>ALARK.IS, ALTNY.IS, ENERY.IS, ENJSA.IS, SOKM.IS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | ASTOR.IS: 2026-09-02 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -4124,14 +4124,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.20% / +2.95% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -2.55% / +1.19% / -2.61% | ENERY.IS: +0.27% / +1.23% / -0.10% | ENJSA.IS: +2.07% / +3.36% / -0.09%</t>
+          <t>ALARK.IS: +2.47% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.54% / +2.47% / -1.62% | ENJSA.IS: +2.70% / +3.36% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.18560854326407</v>
+        <v>-10.87649869230984</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4140,13 +4140,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>117.5</v>
+        <v>118.5</v>
       </c>
       <c r="O19" t="n">
-        <v>47.5</v>
+        <v>46.6</v>
       </c>
       <c r="P19" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -4157,19 +4157,19 @@
         <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>25.041</v>
+        <v>25.617</v>
       </c>
       <c r="T19" t="n">
-        <v>25.041</v>
+        <v>25.617</v>
       </c>
       <c r="U19" t="n">
-        <v>56.999</v>
+        <v>55.792</v>
       </c>
       <c r="V19" t="n">
-        <v>20.838</v>
+        <v>19.909</v>
       </c>
       <c r="W19" t="n">
-        <v>-52.446</v>
+        <v>-53.654</v>
       </c>
     </row>
     <row r="20">
@@ -4213,14 +4213,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.20% / +2.95% / -3.23%</t>
+          <t>ALARK.IS: +2.47% / +3.97% / -3.23%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>0.261749999591232</v>
+        <v>-0.7334066768353353</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4252,13 +4252,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>274.663</v>
+        <v>270.944</v>
       </c>
       <c r="V20" t="n">
-        <v>83.968</v>
+        <v>82.142</v>
       </c>
       <c r="W20" t="n">
-        <v>-40.594</v>
+        <v>-44.313</v>
       </c>
     </row>
     <row r="21">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, ASTOR.IS, ENERY.IS, ENJSA.IS</t>
+          <t>ALARK.IS, ALTNY.IS, ENERY.IS, ENJSA.IS, SOKM.IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-08-31 | ASTOR.IS: 2026-09-02 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -4302,14 +4302,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.20% / +2.95% / -3.23% | ALTNY.IS: -2.56% / +0.00% / -3.49% | ASTOR.IS: -2.55% / +1.19% / -2.61% | ENERY.IS: +0.27% / +1.23% / -0.10% | ENJSA.IS: +2.07% / +3.36% / -0.09%</t>
+          <t>ALARK.IS: +2.47% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.54% / +2.47% / -1.62% | ENJSA.IS: +2.70% / +3.36% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.10173554420417</v>
+        <v>-10.79327087970484</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4318,10 +4318,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>178.3</v>
+        <v>179.3</v>
       </c>
       <c r="O21" t="n">
-        <v>52.5</v>
+        <v>51.9</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
@@ -4335,19 +4335,19 @@
         <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>23.714</v>
+        <v>24.301</v>
       </c>
       <c r="T21" t="n">
-        <v>23.714</v>
+        <v>24.301</v>
       </c>
       <c r="U21" t="n">
-        <v>33.037</v>
+        <v>32.013</v>
       </c>
       <c r="V21" t="n">
-        <v>7.803</v>
+        <v>6.974</v>
       </c>
       <c r="W21" t="n">
-        <v>-41.355</v>
+        <v>-42.378</v>
       </c>
     </row>
     <row r="22">
@@ -4378,12 +4378,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ALTNY.IS, BRSAN.IS, CANTE.IS, ENERY.IS, TKFEN.IS</t>
+          <t>BRSAN.IS, CANTE.IS, ENERY.IS, SOKM.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ALTNY.IS: 2026-09-02 | BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-02 | TKFEN.IS: 2026-08-05</t>
+          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-02 | SOKM.IS: 2026-09-03 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -4391,14 +4391,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ALTNY.IS: -0.94% / +0.85% / -1.04% | BRSAN.IS: +8.87% / +20.03% / -1.13% | CANTE.IS: +7.02% / +15.84% / -2.80% | ENERY.IS: +0.27% / +1.23% / -0.10% | TKFEN.IS: +12.27% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +8.79% / +20.03% / -1.13% | CANTE.IS: +9.45% / +15.84% / -2.80% | ENERY.IS: -1.54% / +2.47% / -1.62% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +9.97% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.39056794739956</v>
+        <v>-11.03951962468362</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4407,10 +4407,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>138.9</v>
+        <v>139.4</v>
       </c>
       <c r="O22" t="n">
-        <v>42.7</v>
+        <v>42.1</v>
       </c>
       <c r="P22" t="n">
         <v>5.7</v>
@@ -4424,19 +4424,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>26.158</v>
+        <v>26.693</v>
       </c>
       <c r="T22" t="n">
-        <v>26.158</v>
+        <v>26.693</v>
       </c>
       <c r="U22" t="n">
-        <v>24.526</v>
+        <v>23.624</v>
       </c>
       <c r="V22" t="n">
-        <v>11.408</v>
+        <v>10.602</v>
       </c>
       <c r="W22" t="n">
-        <v>-44.113</v>
+        <v>-45.015</v>
       </c>
     </row>
     <row r="23">
@@ -4480,14 +4480,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.87% / +20.03% / -1.13% | CANTE.IS: -0.77% / +1.46% / -0.80% | ENERY.IS: +0.27% / +1.23% / -0.10%</t>
+          <t>BRSAN.IS: +8.79% / +20.03% / -1.13% | CANTE.IS: +1.48% / +2.21% / -2.30% | ENERY.IS: -1.54% / +2.47% / -1.62%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.794250119283926</v>
+        <v>-3.742360135314404</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4519,13 +4519,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>21.282</v>
+        <v>21.347</v>
       </c>
       <c r="V23" t="n">
-        <v>0.833</v>
+        <v>0.888</v>
       </c>
       <c r="W23" t="n">
-        <v>-32.854</v>
+        <v>-32.789</v>
       </c>
     </row>
     <row r="24">
@@ -4569,14 +4569,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.20% / +2.95% / -3.23% | CANTE.IS: -0.77% / +1.46% / -0.80% | ENERY.IS: +0.27% / +1.23% / -0.10%</t>
+          <t>ALARK.IS: +2.47% / +3.97% / -3.23% | CANTE.IS: +1.48% / +2.21% / -2.30% | ENERY.IS: -1.54% / +2.47% / -1.62%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.649039617463301</v>
+        <v>-3.50428724728844</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4602,19 +4602,19 @@
         <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>20.226</v>
+        <v>20.181</v>
       </c>
       <c r="T24" t="n">
-        <v>20.226</v>
+        <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>10.21</v>
+        <v>10.375</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.073</v>
+        <v>-2.927</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.943</v>
+        <v>-27.777</v>
       </c>
     </row>
     <row r="25">
@@ -4730,7 +4730,7 @@
         <v>0.8142516931666233</v>
       </c>
       <c r="K26" t="n">
-        <v>6.48315810656519</v>
+        <v>5.183764598665919</v>
       </c>
       <c r="L26" t="n">
         <v>9.181211458048665</v>
@@ -4762,13 +4762,13 @@
         <v>7.916</v>
       </c>
       <c r="U26" t="n">
-        <v>12.877</v>
+        <v>11.499</v>
       </c>
       <c r="V26" t="n">
-        <v>7.58</v>
+        <v>6.268</v>
       </c>
       <c r="W26" t="n">
-        <v>-2.23</v>
+        <v>-3.607</v>
       </c>
     </row>
     <row r="27">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4812,14 +4812,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.87% / +20.03% / -1.13% | TKFEN.IS: +12.27% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +8.79% / +20.03% / -1.13% | TKFEN.IS: +9.97% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>8.562399589571768</v>
+        <v>7.357304125380115</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4851,13 +4851,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>38.295</v>
+        <v>36.76</v>
       </c>
       <c r="V27" t="n">
-        <v>51.271</v>
+        <v>49.592</v>
       </c>
       <c r="W27" t="n">
-        <v>-18.735</v>
+        <v>-20.27</v>
       </c>
     </row>
     <row r="28">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-01 | FENER.IS: 2026-09-01</t>
+          <t>ASTOR.IS: 2026-09-03 | FENER.IS: 2026-09-01</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4901,14 +4901,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -2.78% / +1.03% / -3.32% | FENER.IS: -1.31% / +0.69% / -1.90%</t>
+          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | FENER.IS: +0.95% / +1.01% / -1.90%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>7.185267193638833</v>
+        <v>7.726358197822303</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4917,10 +4917,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N28" t="n">
-        <v>87.7</v>
+        <v>88.2</v>
       </c>
       <c r="O28" t="n">
-        <v>46</v>
+        <v>46.3</v>
       </c>
       <c r="P28" t="n">
         <v>2.2</v>
@@ -4940,13 +4940,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>6.726</v>
+        <v>7.265</v>
       </c>
       <c r="V28" t="n">
-        <v>11.923</v>
+        <v>12.488</v>
       </c>
       <c r="W28" t="n">
-        <v>-7.432</v>
+        <v>-6.894</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.48% / +2.26% / -2.26% | VAKBN.IS: +0.10% / +2.23% / 0.00%</t>
+          <t>CANTE.IS: +1.48% / +3.76% / -2.26% | VAKBN.IS: -1.19% / +2.23% / -1.35%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-14.85325520074797</v>
+        <v>-15.39859921157596</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -775,7 +775,7 @@
         <v>102.7</v>
       </c>
       <c r="O3" t="n">
-        <v>44</v>
+        <v>43.5</v>
       </c>
       <c r="P3" t="n">
         <v>6.7</v>
@@ -795,13 +795,13 @@
         <v>21.661</v>
       </c>
       <c r="U3" t="n">
-        <v>61.789</v>
+        <v>60.753</v>
       </c>
       <c r="V3" t="n">
-        <v>15.678</v>
+        <v>14.937</v>
       </c>
       <c r="W3" t="n">
-        <v>-43.116</v>
+        <v>-44.152</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.48% / +2.26% / -2.26% | VAKBN.IS: +0.10% / +2.23% / 0.00%</t>
+          <t>CANTE.IS: +1.48% / +3.76% / -2.26% | VAKBN.IS: -1.19% / +2.23% / -1.35%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-14.85325520074797</v>
+        <v>-15.39859921157596</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1012,7 +1012,7 @@
         <v>102.7</v>
       </c>
       <c r="O6" t="n">
-        <v>44</v>
+        <v>43.5</v>
       </c>
       <c r="P6" t="n">
         <v>6.7</v>
@@ -1032,13 +1032,13 @@
         <v>21.661</v>
       </c>
       <c r="U6" t="n">
-        <v>61.789</v>
+        <v>60.753</v>
       </c>
       <c r="V6" t="n">
-        <v>15.678</v>
+        <v>14.937</v>
       </c>
       <c r="W6" t="n">
-        <v>-43.116</v>
+        <v>-44.152</v>
       </c>
     </row>
     <row r="7">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.48% / +2.26% / -2.26% | VAKBN.IS: +0.10% / +2.23% / 0.00%</t>
+          <t>CANTE.IS: +1.48% / +3.76% / -2.26% | VAKBN.IS: -1.19% / +2.23% / -1.35%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.265865736241825</v>
+        <v>-4.879019379116012</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1099,7 +1099,7 @@
         <v>134.9</v>
       </c>
       <c r="O7" t="n">
-        <v>47.8</v>
+        <v>47.4</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1119,13 +1119,13 @@
         <v>17.439</v>
       </c>
       <c r="U7" t="n">
-        <v>72.932</v>
+        <v>71.824</v>
       </c>
       <c r="V7" t="n">
-        <v>30.998</v>
+        <v>30.159</v>
       </c>
       <c r="W7" t="n">
-        <v>-34.885</v>
+        <v>-35.993</v>
       </c>
     </row>
     <row r="8">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ALARK.IS, ENERY.IS, KRDMD.IS</t>
+          <t>ALARK.IS, ENERY.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | KRDMD.IS: 2026-09-01</t>
+          <t>ALARK.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.54% / +2.48% / -1.62% | KRDMD.IS: -1.10% / +1.08% / -3.24%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.31% / +2.48% / -2.76% | ENJSA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-16.04366387849218</v>
+        <v>-16.53722600142411</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1183,10 +1183,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>192</v>
+        <v>192.5</v>
       </c>
       <c r="O8" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1200,19 +1200,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>17.36</v>
+        <v>17.846</v>
       </c>
       <c r="T8" t="n">
-        <v>17.36</v>
+        <v>17.846</v>
       </c>
       <c r="U8" t="n">
-        <v>40.745</v>
+        <v>39.918</v>
       </c>
       <c r="V8" t="n">
-        <v>11.468</v>
+        <v>10.813</v>
       </c>
       <c r="W8" t="n">
-        <v>-29.566</v>
+        <v>-30.393</v>
       </c>
     </row>
     <row r="9">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.48% / +2.26% / -2.26% | VAKBN.IS: +0.10% / +2.23% / 0.00%</t>
+          <t>CANTE.IS: +1.48% / +3.76% / -2.26% | VAKBN.IS: -1.19% / +2.23% / -1.35%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-14.85325520074797</v>
+        <v>-15.39859921157596</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1273,7 +1273,7 @@
         <v>102.7</v>
       </c>
       <c r="O9" t="n">
-        <v>44</v>
+        <v>43.5</v>
       </c>
       <c r="P9" t="n">
         <v>6.7</v>
@@ -1293,13 +1293,13 @@
         <v>21.661</v>
       </c>
       <c r="U9" t="n">
-        <v>61.789</v>
+        <v>60.753</v>
       </c>
       <c r="V9" t="n">
-        <v>15.678</v>
+        <v>14.937</v>
       </c>
       <c r="W9" t="n">
-        <v>-43.116</v>
+        <v>-44.152</v>
       </c>
     </row>
     <row r="10">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>KUYAS.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -1.65% / +1.89% / -1.71%</t>
+          <t>KUYAS.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: +2.46% / +2.68% / -2.03%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.995503466783423</v>
+        <v>-3.370921394748372</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1360,7 +1360,7 @@
         <v>175.6</v>
       </c>
       <c r="O10" t="n">
-        <v>48.9</v>
+        <v>49.2</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>16.254</v>
+        <v>17.011</v>
       </c>
       <c r="V10" t="n">
-        <v>8.093</v>
+        <v>8.795999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.134</v>
+        <v>-8.377000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1490,42 +1490,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASTOR.IS, TRALT.IS</t>
+          <t>TRALT.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-03 | TRALT.IS: 2026-09-03</t>
+          <t>TRALT.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>20.48700524499634</v>
+        <v>25.65141339163128</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>TRALT.IS: +2.46% / +2.68% / -2.03%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-3.767340978838807</v>
+        <v>-5.044425134583063</v>
       </c>
       <c r="K12" t="n">
-        <v>10.83793225314063</v>
+        <v>11.62957530431525</v>
       </c>
       <c r="L12" t="n">
-        <v>16.57596537747867</v>
+        <v>9.344627019167174</v>
       </c>
       <c r="M12" t="n">
-        <v>77.77777777777779</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N12" t="n">
-        <v>88.8</v>
+        <v>59</v>
       </c>
       <c r="O12" t="n">
-        <v>47.5</v>
+        <v>52.1</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>17.404</v>
+        <v>12.101</v>
       </c>
       <c r="T12" t="n">
-        <v>17.404</v>
+        <v>12.101</v>
       </c>
       <c r="U12" t="n">
-        <v>49.915</v>
+        <v>30.241</v>
       </c>
       <c r="V12" t="n">
-        <v>42.487</v>
+        <v>35.678</v>
       </c>
       <c r="W12" t="n">
-        <v>-4.787</v>
+        <v>-7.538</v>
       </c>
     </row>
     <row r="13">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.61% / +20.94% / 0.00% | RALYH.IS: +22.81% / +35.10% / -0.91% | VAKBN.IS: +0.10% / +2.23% / 0.00%</t>
+          <t>BRSAN.IS: +9.13% / +20.94% / 0.00% | RALYH.IS: +23.05% / +35.10% / -0.91% | VAKBN.IS: -1.19% / +2.23% / -1.35%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K13" t="n">
-        <v>10.0002218501311</v>
+        <v>9.44732483159536</v>
       </c>
       <c r="L13" t="n">
         <v>34.56349599547857</v>
@@ -1609,7 +1609,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>44.7</v>
+        <v>44</v>
       </c>
       <c r="P13" t="n">
         <v>6.1</v>
@@ -1629,13 +1629,13 @@
         <v>23.777</v>
       </c>
       <c r="U13" t="n">
-        <v>45.487</v>
+        <v>44.756</v>
       </c>
       <c r="V13" t="n">
-        <v>39.401</v>
+        <v>38.7</v>
       </c>
       <c r="W13" t="n">
-        <v>-14.551</v>
+        <v>-15.282</v>
       </c>
     </row>
     <row r="14">
@@ -1878,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.48% / +2.26% / -2.26% | VAKBN.IS: +0.10% / +2.23% / 0.00%</t>
+          <t>CANTE.IS: +1.48% / +3.76% / -2.26% | VAKBN.IS: -1.19% / +2.23% / -1.35%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-14.85325520074797</v>
+        <v>-15.39859921157596</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1897,7 +1897,7 @@
         <v>102.7</v>
       </c>
       <c r="O18" t="n">
-        <v>44</v>
+        <v>43.5</v>
       </c>
       <c r="P18" t="n">
         <v>6.7</v>
@@ -1917,13 +1917,13 @@
         <v>21.661</v>
       </c>
       <c r="U18" t="n">
-        <v>61.789</v>
+        <v>60.753</v>
       </c>
       <c r="V18" t="n">
-        <v>15.678</v>
+        <v>14.937</v>
       </c>
       <c r="W18" t="n">
-        <v>-43.116</v>
+        <v>-44.152</v>
       </c>
     </row>
     <row r="19">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ALARK.IS, ENERY.IS, KRDMD.IS</t>
+          <t>ALARK.IS, ENERY.IS, ENJSA.IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | KRDMD.IS: 2026-09-01</t>
+          <t>ALARK.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.54% / +2.48% / -1.62% | KRDMD.IS: -1.10% / +1.08% / -3.24%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.31% / +2.48% / -2.76% | ENJSA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-16.04366387849218</v>
+        <v>-16.53722600142411</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2137,10 +2137,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>192</v>
+        <v>192.5</v>
       </c>
       <c r="O21" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2154,19 +2154,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>17.36</v>
+        <v>17.846</v>
       </c>
       <c r="T21" t="n">
-        <v>17.36</v>
+        <v>17.846</v>
       </c>
       <c r="U21" t="n">
-        <v>40.745</v>
+        <v>39.918</v>
       </c>
       <c r="V21" t="n">
-        <v>11.468</v>
+        <v>10.813</v>
       </c>
       <c r="W21" t="n">
-        <v>-29.566</v>
+        <v>-30.393</v>
       </c>
     </row>
     <row r="22">
@@ -2210,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.48% / +2.26% / -2.26% | VAKBN.IS: +0.10% / +2.23% / 0.00%</t>
+          <t>CANTE.IS: +1.48% / +3.76% / -2.26% | VAKBN.IS: -1.19% / +2.23% / -1.35%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.265865736241825</v>
+        <v>-4.879019379116012</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2229,7 +2229,7 @@
         <v>134.9</v>
       </c>
       <c r="O22" t="n">
-        <v>47.8</v>
+        <v>47.4</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
@@ -2249,13 +2249,13 @@
         <v>17.439</v>
       </c>
       <c r="U22" t="n">
-        <v>72.932</v>
+        <v>71.824</v>
       </c>
       <c r="V22" t="n">
-        <v>30.998</v>
+        <v>30.159</v>
       </c>
       <c r="W22" t="n">
-        <v>-34.885</v>
+        <v>-35.993</v>
       </c>
     </row>
     <row r="23">
@@ -2415,17 +2415,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2440,42 +2440,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KUYAS.IS, TRALT.IS</t>
+          <t>TRALT.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>KUYAS.IS: 2026-09-03 | TRALT.IS: 2026-09-02</t>
+          <t>TRALT.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>23.02092795860866</v>
+        <v>25.65141339163128</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>KUYAS.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -1.65% / +1.89% / -1.71%</t>
+          <t>TRALT.IS: +2.46% / +2.68% / -2.03%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>12.86015270141232</v>
+        <v>-5.044425134583063</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.995503466783423</v>
+        <v>11.62957530431525</v>
       </c>
       <c r="L25" t="n">
-        <v>4.543450519200398</v>
+        <v>9.344627019167174</v>
       </c>
       <c r="M25" t="n">
-        <v>72.22222222222221</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N25" t="n">
-        <v>175.6</v>
+        <v>59</v>
       </c>
       <c r="O25" t="n">
-        <v>48.9</v>
+        <v>52.1</v>
       </c>
       <c r="P25" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2483,38 +2483,38 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>10.072</v>
+        <v>12.101</v>
       </c>
       <c r="T25" t="n">
-        <v>10.072</v>
+        <v>12.101</v>
       </c>
       <c r="U25" t="n">
-        <v>16.254</v>
+        <v>30.241</v>
       </c>
       <c r="V25" t="n">
-        <v>8.093</v>
+        <v>35.678</v>
       </c>
       <c r="W25" t="n">
-        <v>-9.134</v>
+        <v>-7.538</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
+          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2529,42 +2529,42 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ASTOR.IS, TRALT.IS</t>
+          <t>KUYAS.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-03 | TRALT.IS: 2026-09-03</t>
+          <t>KUYAS.IS: 2026-09-03 | TRALT.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>20.48700524499634</v>
+        <v>23.02092795860866</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>KUYAS.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: +2.46% / +2.68% / -2.03%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-3.767340978838807</v>
+        <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>10.83793225314063</v>
+        <v>-3.370921394748372</v>
       </c>
       <c r="L26" t="n">
-        <v>16.57596537747867</v>
+        <v>4.543450519200398</v>
       </c>
       <c r="M26" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>88.8</v>
+        <v>175.6</v>
       </c>
       <c r="O26" t="n">
-        <v>47.5</v>
+        <v>49.2</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2575,19 +2575,19 @@
         <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>17.404</v>
+        <v>10.072</v>
       </c>
       <c r="T26" t="n">
-        <v>17.404</v>
+        <v>10.072</v>
       </c>
       <c r="U26" t="n">
-        <v>49.915</v>
+        <v>17.011</v>
       </c>
       <c r="V26" t="n">
-        <v>42.487</v>
+        <v>8.795999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.787</v>
+        <v>-8.377000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.61% / +20.94% / 0.00% | RALYH.IS: +22.81% / +35.10% / -0.91% | VAKBN.IS: +0.10% / +2.23% / 0.00%</t>
+          <t>BRSAN.IS: +9.13% / +20.94% / 0.00% | RALYH.IS: +23.05% / +35.10% / -0.91% | VAKBN.IS: -1.19% / +2.23% / -1.35%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>10.0002218501311</v>
+        <v>9.44732483159536</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2650,7 +2650,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>44.7</v>
+        <v>44</v>
       </c>
       <c r="P27" t="n">
         <v>6.1</v>
@@ -2670,13 +2670,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>45.487</v>
+        <v>44.756</v>
       </c>
       <c r="V27" t="n">
-        <v>39.401</v>
+        <v>38.7</v>
       </c>
       <c r="W27" t="n">
-        <v>-14.551</v>
+        <v>-15.282</v>
       </c>
     </row>
   </sheetData>
@@ -2889,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.47% / +3.97% / -3.23%</t>
+          <t>ALARK.IS: +2.66% / +3.97% / -3.23%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7135304692478472</v>
+        <v>0.2017897931249069</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2928,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>273.708</v>
+        <v>277.153</v>
       </c>
       <c r="V3" t="n">
-        <v>100.01</v>
+        <v>101.854</v>
       </c>
       <c r="W3" t="n">
-        <v>-44.691</v>
+        <v>-41.246</v>
       </c>
     </row>
     <row r="4">
@@ -2976,14 +2976,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.47% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.54% / +2.47% / -1.62% | ENJSA.IS: +2.70% / +3.36% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +2.66% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.31% / +2.47% / -2.77% | ENJSA.IS: +4.16% / +4.18% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.87649869230984</v>
+        <v>-10.35345989122698</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -3009,19 +3009,19 @@
         <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>25.617</v>
+        <v>25.181</v>
       </c>
       <c r="T4" t="n">
-        <v>25.617</v>
+        <v>25.181</v>
       </c>
       <c r="U4" t="n">
-        <v>55.792</v>
+        <v>56.706</v>
       </c>
       <c r="V4" t="n">
-        <v>19.909</v>
+        <v>20.612</v>
       </c>
       <c r="W4" t="n">
-        <v>-53.654</v>
+        <v>-52.74</v>
       </c>
     </row>
     <row r="5">
@@ -3063,14 +3063,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.47% / +3.97% / -3.23%</t>
+          <t>ALARK.IS: +2.66% / +3.97% / -3.23%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7334066768353353</v>
+        <v>0.1817303471200349</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3102,13 +3102,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>270.944</v>
+        <v>274.364</v>
       </c>
       <c r="V5" t="n">
-        <v>82.142</v>
+        <v>83.821</v>
       </c>
       <c r="W5" t="n">
-        <v>-44.313</v>
+        <v>-40.893</v>
       </c>
     </row>
     <row r="6">
@@ -3150,14 +3150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.79% / +20.03% / -1.13% | CANTE.IS: +9.45% / +15.84% / -2.80% | ENERY.IS: -1.54% / +2.47% / -1.62% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +9.97% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +8.31% / +20.03% / -1.13% | CANTE.IS: +9.45% / +15.84% / -2.80% | ENERY.IS: -0.31% / +2.47% / -2.77% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +11.68% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.03951962468362</v>
+        <v>-10.58658151009358</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3183,19 +3183,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>26.693</v>
+        <v>26.32</v>
       </c>
       <c r="T6" t="n">
-        <v>26.693</v>
+        <v>26.32</v>
       </c>
       <c r="U6" t="n">
-        <v>23.624</v>
+        <v>24.253</v>
       </c>
       <c r="V6" t="n">
-        <v>10.602</v>
+        <v>11.165</v>
       </c>
       <c r="W6" t="n">
-        <v>-45.015</v>
+        <v>-44.386</v>
       </c>
     </row>
     <row r="7">
@@ -3237,14 +3237,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.47% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.54% / +2.47% / -1.62% | ENJSA.IS: +2.70% / +3.36% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +2.66% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.31% / +2.47% / -2.77% | ENJSA.IS: +4.16% / +4.18% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.87649869230984</v>
+        <v>-10.35345989122698</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3270,19 +3270,19 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>25.617</v>
+        <v>25.181</v>
       </c>
       <c r="T7" t="n">
-        <v>25.617</v>
+        <v>25.181</v>
       </c>
       <c r="U7" t="n">
-        <v>55.792</v>
+        <v>56.706</v>
       </c>
       <c r="V7" t="n">
-        <v>19.909</v>
+        <v>20.612</v>
       </c>
       <c r="W7" t="n">
-        <v>-53.654</v>
+        <v>-52.74</v>
       </c>
     </row>
     <row r="8">
@@ -3324,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.79% / +20.03% / -1.13% | CANTE.IS: +1.48% / +2.21% / -2.30% | ENERY.IS: -1.54% / +2.47% / -1.62%</t>
+          <t>BRSAN.IS: +8.31% / +20.03% / -1.13% | CANTE.IS: +1.48% / +3.71% / -2.30% | ENERY.IS: -0.31% / +2.47% / -2.77%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.742360135314404</v>
+        <v>-3.514962194552895</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3363,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>21.347</v>
+        <v>21.634</v>
       </c>
       <c r="V8" t="n">
-        <v>0.888</v>
+        <v>1.126</v>
       </c>
       <c r="W8" t="n">
-        <v>-32.789</v>
+        <v>-32.502</v>
       </c>
     </row>
     <row r="9">
@@ -3486,14 +3486,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.47% / +3.97% / -3.23% | CANTE.IS: +1.48% / +2.21% / -2.30% | ENERY.IS: -1.54% / +2.47% / -1.62%</t>
+          <t>ALARK.IS: +2.66% / +3.97% / -3.23% | CANTE.IS: +1.48% / +3.71% / -2.30% | ENERY.IS: -0.31% / +2.47% / -2.77%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.50428724728844</v>
+        <v>-3.11185120536086</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3525,13 +3525,13 @@
         <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>10.375</v>
+        <v>10.824</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.927</v>
+        <v>-2.532</v>
       </c>
       <c r="W10" t="n">
-        <v>-27.777</v>
+        <v>-27.328</v>
       </c>
     </row>
     <row r="11">
@@ -3573,14 +3573,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.47% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.54% / +2.47% / -1.62% | ENJSA.IS: +2.70% / +3.36% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +2.66% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.31% / +2.47% / -2.77% | ENJSA.IS: +4.16% / +4.18% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.79327087970484</v>
+        <v>-10.26974363982992</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3606,19 +3606,19 @@
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>24.301</v>
+        <v>23.856</v>
       </c>
       <c r="T11" t="n">
-        <v>24.301</v>
+        <v>23.856</v>
       </c>
       <c r="U11" t="n">
-        <v>32.013</v>
+        <v>32.788</v>
       </c>
       <c r="V11" t="n">
-        <v>6.974</v>
+        <v>7.602</v>
       </c>
       <c r="W11" t="n">
-        <v>-42.378</v>
+        <v>-41.604</v>
       </c>
     </row>
     <row r="12">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3647,42 +3647,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASTOR.IS, FENER.IS</t>
+          <t>BRSAN.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-03 | FENER.IS: 2026-09-01</t>
+          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-0.49388395046156</v>
+        <v>6.880672511445463</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | FENER.IS: +0.95% / +1.01% / -1.90%</t>
+          <t>BRSAN.IS: +8.31% / +20.03% / -1.13% | TKFEN.IS: +11.68% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-19.60937535624424</v>
+        <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>7.726358197822303</v>
+        <v>8.001712459790999</v>
       </c>
       <c r="L12" t="n">
-        <v>19.61961325199098</v>
+        <v>31.31195090134997</v>
       </c>
       <c r="M12" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>88.2</v>
+        <v>48.3</v>
       </c>
       <c r="O12" t="n">
-        <v>46.3</v>
+        <v>43.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3693,19 +3693,19 @@
         <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>18.132</v>
+        <v>28.439</v>
       </c>
       <c r="T12" t="n">
-        <v>18.132</v>
+        <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>7.265</v>
+        <v>37.581</v>
       </c>
       <c r="V12" t="n">
-        <v>12.488</v>
+        <v>50.49</v>
       </c>
       <c r="W12" t="n">
-        <v>-6.894</v>
+        <v>-19.449</v>
       </c>
     </row>
     <row r="13">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3734,42 +3734,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
+          <t>ASTOR.IS, FENER.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
+          <t>ASTOR.IS: 2026-09-03 | FENER.IS: 2026-09-01</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.880672511445463</v>
+        <v>-0.49388395046156</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.79% / +20.03% / -1.13% | TKFEN.IS: +9.97% / +31.83% / -0.56%</t>
+          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | FENER.IS: +0.30% / +1.66% / -1.90%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-18.9000927288166</v>
+        <v>-19.60937535624424</v>
       </c>
       <c r="K13" t="n">
-        <v>7.357304125380115</v>
+        <v>7.372297501662484</v>
       </c>
       <c r="L13" t="n">
-        <v>31.31195090134997</v>
+        <v>19.61961325199098</v>
       </c>
       <c r="M13" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N13" t="n">
-        <v>48.3</v>
+        <v>88.2</v>
       </c>
       <c r="O13" t="n">
-        <v>43.3</v>
+        <v>46.3</v>
       </c>
       <c r="P13" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3780,19 +3780,19 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>28.439</v>
+        <v>18.132</v>
       </c>
       <c r="T13" t="n">
-        <v>28.439</v>
+        <v>18.132</v>
       </c>
       <c r="U13" t="n">
-        <v>36.76</v>
+        <v>6.912</v>
       </c>
       <c r="V13" t="n">
-        <v>49.592</v>
+        <v>12.119</v>
       </c>
       <c r="W13" t="n">
-        <v>-20.27</v>
+        <v>-7.246</v>
       </c>
     </row>
     <row r="14">
@@ -3829,7 +3829,7 @@
         <v>0.8142516931666233</v>
       </c>
       <c r="K14" t="n">
-        <v>5.183764598665919</v>
+        <v>3.846414277792909</v>
       </c>
       <c r="L14" t="n">
         <v>9.181211458048665</v>
@@ -3861,13 +3861,13 @@
         <v>7.916</v>
       </c>
       <c r="U14" t="n">
-        <v>11.499</v>
+        <v>10.082</v>
       </c>
       <c r="V14" t="n">
-        <v>6.268</v>
+        <v>4.916</v>
       </c>
       <c r="W14" t="n">
-        <v>-3.607</v>
+        <v>-5.025</v>
       </c>
     </row>
     <row r="16">
@@ -4035,14 +4035,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.47% / +3.97% / -3.23%</t>
+          <t>ALARK.IS: +2.66% / +3.97% / -3.23%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7135304692478472</v>
+        <v>0.2017897931249069</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4074,13 +4074,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>273.708</v>
+        <v>277.153</v>
       </c>
       <c r="V18" t="n">
-        <v>100.01</v>
+        <v>101.854</v>
       </c>
       <c r="W18" t="n">
-        <v>-44.691</v>
+        <v>-41.246</v>
       </c>
     </row>
     <row r="19">
@@ -4124,14 +4124,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.47% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.54% / +2.47% / -1.62% | ENJSA.IS: +2.70% / +3.36% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +2.66% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.31% / +2.47% / -2.77% | ENJSA.IS: +4.16% / +4.18% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.87649869230984</v>
+        <v>-10.35345989122698</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4157,19 +4157,19 @@
         <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>25.617</v>
+        <v>25.181</v>
       </c>
       <c r="T19" t="n">
-        <v>25.617</v>
+        <v>25.181</v>
       </c>
       <c r="U19" t="n">
-        <v>55.792</v>
+        <v>56.706</v>
       </c>
       <c r="V19" t="n">
-        <v>19.909</v>
+        <v>20.612</v>
       </c>
       <c r="W19" t="n">
-        <v>-53.654</v>
+        <v>-52.74</v>
       </c>
     </row>
     <row r="20">
@@ -4213,14 +4213,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.47% / +3.97% / -3.23%</t>
+          <t>ALARK.IS: +2.66% / +3.97% / -3.23%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7334066768353353</v>
+        <v>0.1817303471200349</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4252,13 +4252,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>270.944</v>
+        <v>274.364</v>
       </c>
       <c r="V20" t="n">
-        <v>82.142</v>
+        <v>83.821</v>
       </c>
       <c r="W20" t="n">
-        <v>-44.313</v>
+        <v>-40.893</v>
       </c>
     </row>
     <row r="21">
@@ -4302,14 +4302,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.47% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.54% / +2.47% / -1.62% | ENJSA.IS: +2.70% / +3.36% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +2.66% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.31% / +2.47% / -2.77% | ENJSA.IS: +4.16% / +4.18% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.79327087970484</v>
+        <v>-10.26974363982992</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4335,19 +4335,19 @@
         <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>24.301</v>
+        <v>23.856</v>
       </c>
       <c r="T21" t="n">
-        <v>24.301</v>
+        <v>23.856</v>
       </c>
       <c r="U21" t="n">
-        <v>32.013</v>
+        <v>32.788</v>
       </c>
       <c r="V21" t="n">
-        <v>6.974</v>
+        <v>7.602</v>
       </c>
       <c r="W21" t="n">
-        <v>-42.378</v>
+        <v>-41.604</v>
       </c>
     </row>
     <row r="22">
@@ -4391,14 +4391,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.79% / +20.03% / -1.13% | CANTE.IS: +9.45% / +15.84% / -2.80% | ENERY.IS: -1.54% / +2.47% / -1.62% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +9.97% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +8.31% / +20.03% / -1.13% | CANTE.IS: +9.45% / +15.84% / -2.80% | ENERY.IS: -0.31% / +2.47% / -2.77% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +11.68% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.03951962468362</v>
+        <v>-10.58658151009358</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4424,19 +4424,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>26.693</v>
+        <v>26.32</v>
       </c>
       <c r="T22" t="n">
-        <v>26.693</v>
+        <v>26.32</v>
       </c>
       <c r="U22" t="n">
-        <v>23.624</v>
+        <v>24.253</v>
       </c>
       <c r="V22" t="n">
-        <v>10.602</v>
+        <v>11.165</v>
       </c>
       <c r="W22" t="n">
-        <v>-45.015</v>
+        <v>-44.386</v>
       </c>
     </row>
     <row r="23">
@@ -4480,14 +4480,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.79% / +20.03% / -1.13% | CANTE.IS: +1.48% / +2.21% / -2.30% | ENERY.IS: -1.54% / +2.47% / -1.62%</t>
+          <t>BRSAN.IS: +8.31% / +20.03% / -1.13% | CANTE.IS: +1.48% / +3.71% / -2.30% | ENERY.IS: -0.31% / +2.47% / -2.77%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.742360135314404</v>
+        <v>-3.514962194552895</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4519,13 +4519,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>21.347</v>
+        <v>21.634</v>
       </c>
       <c r="V23" t="n">
-        <v>0.888</v>
+        <v>1.126</v>
       </c>
       <c r="W23" t="n">
-        <v>-32.789</v>
+        <v>-32.502</v>
       </c>
     </row>
     <row r="24">
@@ -4569,14 +4569,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.47% / +3.97% / -3.23% | CANTE.IS: +1.48% / +2.21% / -2.30% | ENERY.IS: -1.54% / +2.47% / -1.62%</t>
+          <t>ALARK.IS: +2.66% / +3.97% / -3.23% | CANTE.IS: +1.48% / +3.71% / -2.30% | ENERY.IS: -0.31% / +2.47% / -2.77%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.50428724728844</v>
+        <v>-3.11185120536086</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4608,13 +4608,13 @@
         <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>10.375</v>
+        <v>10.824</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.927</v>
+        <v>-2.532</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.777</v>
+        <v>-27.328</v>
       </c>
     </row>
     <row r="25">
@@ -4730,7 +4730,7 @@
         <v>0.8142516931666233</v>
       </c>
       <c r="K26" t="n">
-        <v>5.183764598665919</v>
+        <v>3.846414277792909</v>
       </c>
       <c r="L26" t="n">
         <v>9.181211458048665</v>
@@ -4762,13 +4762,13 @@
         <v>7.916</v>
       </c>
       <c r="U26" t="n">
-        <v>11.499</v>
+        <v>10.082</v>
       </c>
       <c r="V26" t="n">
-        <v>6.268</v>
+        <v>4.916</v>
       </c>
       <c r="W26" t="n">
-        <v>-3.607</v>
+        <v>-5.025</v>
       </c>
     </row>
     <row r="27">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4812,14 +4812,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.79% / +20.03% / -1.13% | TKFEN.IS: +9.97% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +8.31% / +20.03% / -1.13% | TKFEN.IS: +11.68% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>7.357304125380115</v>
+        <v>8.001712459790999</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4851,13 +4851,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>36.76</v>
+        <v>37.581</v>
       </c>
       <c r="V27" t="n">
-        <v>49.592</v>
+        <v>50.49</v>
       </c>
       <c r="W27" t="n">
-        <v>-20.27</v>
+        <v>-19.449</v>
       </c>
     </row>
     <row r="28">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4901,14 +4901,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | FENER.IS: +0.95% / +1.01% / -1.90%</t>
+          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | FENER.IS: +0.30% / +1.66% / -1.90%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>7.726358197822303</v>
+        <v>7.372297501662484</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4940,13 +4940,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>7.265</v>
+        <v>6.912</v>
       </c>
       <c r="V28" t="n">
-        <v>12.488</v>
+        <v>12.119</v>
       </c>
       <c r="W28" t="n">
-        <v>-6.894</v>
+        <v>-7.246</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.48% / +3.76% / -2.26% | VAKBN.IS: -1.19% / +2.23% / -1.35%</t>
+          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.02% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-15.39859921157596</v>
+        <v>-15.64175862267482</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -789,19 +789,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>21.661</v>
+        <v>21.773</v>
       </c>
       <c r="T3" t="n">
-        <v>21.661</v>
+        <v>21.773</v>
       </c>
       <c r="U3" t="n">
-        <v>60.753</v>
+        <v>60.291</v>
       </c>
       <c r="V3" t="n">
-        <v>14.937</v>
+        <v>14.607</v>
       </c>
       <c r="W3" t="n">
-        <v>-44.152</v>
+        <v>-44.614</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.48% / +3.76% / -2.26% | VAKBN.IS: -1.19% / +2.23% / -1.35%</t>
+          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.02% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-15.39859921157596</v>
+        <v>-15.64175862267482</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1026,19 +1026,19 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>21.661</v>
+        <v>21.773</v>
       </c>
       <c r="T6" t="n">
-        <v>21.661</v>
+        <v>21.773</v>
       </c>
       <c r="U6" t="n">
-        <v>60.753</v>
+        <v>60.291</v>
       </c>
       <c r="V6" t="n">
-        <v>14.937</v>
+        <v>14.607</v>
       </c>
       <c r="W6" t="n">
-        <v>-44.152</v>
+        <v>-44.614</v>
       </c>
     </row>
     <row r="7">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.48% / +3.76% / -2.26% | VAKBN.IS: -1.19% / +2.23% / -1.35%</t>
+          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.02% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.879019379116012</v>
+        <v>-5.152413925960042</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>17.439</v>
+        <v>17.557</v>
       </c>
       <c r="T7" t="n">
-        <v>17.439</v>
+        <v>17.557</v>
       </c>
       <c r="U7" t="n">
-        <v>71.824</v>
+        <v>71.33</v>
       </c>
       <c r="V7" t="n">
-        <v>30.159</v>
+        <v>29.785</v>
       </c>
       <c r="W7" t="n">
-        <v>-35.993</v>
+        <v>-36.487</v>
       </c>
     </row>
     <row r="8">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.31% / +2.48% / -2.76% | ENJSA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +2.48% / -2.76% | ENJSA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-16.53722600142411</v>
+        <v>-16.45577636120216</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1200,19 +1200,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>17.846</v>
+        <v>17.766</v>
       </c>
       <c r="T8" t="n">
-        <v>17.846</v>
+        <v>17.766</v>
       </c>
       <c r="U8" t="n">
-        <v>39.918</v>
+        <v>40.054</v>
       </c>
       <c r="V8" t="n">
-        <v>10.813</v>
+        <v>10.921</v>
       </c>
       <c r="W8" t="n">
-        <v>-30.393</v>
+        <v>-30.257</v>
       </c>
     </row>
     <row r="9">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.48% / +3.76% / -2.26% | VAKBN.IS: -1.19% / +2.23% / -1.35%</t>
+          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.02% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-15.39859921157596</v>
+        <v>-15.64175862267482</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1287,19 +1287,19 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>21.661</v>
+        <v>21.773</v>
       </c>
       <c r="T9" t="n">
-        <v>21.661</v>
+        <v>21.773</v>
       </c>
       <c r="U9" t="n">
-        <v>60.753</v>
+        <v>60.291</v>
       </c>
       <c r="V9" t="n">
-        <v>14.937</v>
+        <v>14.607</v>
       </c>
       <c r="W9" t="n">
-        <v>-44.152</v>
+        <v>-44.614</v>
       </c>
     </row>
     <row r="10">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>KUYAS.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: +2.46% / +2.68% / -2.03%</t>
+          <t>KUYAS.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: +2.76% / +2.88% / -2.03%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.370921394748372</v>
+        <v>-3.461710094756265</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1360,7 +1360,7 @@
         <v>175.6</v>
       </c>
       <c r="O10" t="n">
-        <v>49.2</v>
+        <v>48.9</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>17.011</v>
+        <v>16.901</v>
       </c>
       <c r="V10" t="n">
-        <v>8.795999999999999</v>
+        <v>8.694000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>-8.377000000000001</v>
+        <v>-8.487</v>
       </c>
     </row>
     <row r="11">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TRALT.IS: +2.46% / +2.68% / -2.03%</t>
+          <t>TRALT.IS: +2.76% / +2.88% / -2.03%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-5.044425134583063</v>
       </c>
       <c r="K12" t="n">
-        <v>11.62957530431525</v>
+        <v>11.25815008441988</v>
       </c>
       <c r="L12" t="n">
         <v>9.344627019167174</v>
@@ -1522,7 +1522,7 @@
         <v>59</v>
       </c>
       <c r="O12" t="n">
-        <v>52.1</v>
+        <v>51.3</v>
       </c>
       <c r="P12" t="n">
         <v>2.1</v>
@@ -1542,13 +1542,13 @@
         <v>12.101</v>
       </c>
       <c r="U12" t="n">
-        <v>30.241</v>
+        <v>29.807</v>
       </c>
       <c r="V12" t="n">
-        <v>35.678</v>
+        <v>35.227</v>
       </c>
       <c r="W12" t="n">
-        <v>-7.538</v>
+        <v>-7.972</v>
       </c>
     </row>
     <row r="13">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.13% / +20.94% / 0.00% | RALYH.IS: +23.05% / +35.10% / -0.91% | VAKBN.IS: -1.19% / +2.23% / -1.35%</t>
+          <t>BRSAN.IS: +9.53% / +20.94% / 0.00% | RALYH.IS: +23.17% / +35.10% / -0.91% | VAKBN.IS: -1.02% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K13" t="n">
-        <v>9.44732483159536</v>
+        <v>9.677058012552408</v>
       </c>
       <c r="L13" t="n">
         <v>34.56349599547857</v>
@@ -1629,13 +1629,13 @@
         <v>23.777</v>
       </c>
       <c r="U13" t="n">
-        <v>44.756</v>
+        <v>45.06</v>
       </c>
       <c r="V13" t="n">
-        <v>38.7</v>
+        <v>38.991</v>
       </c>
       <c r="W13" t="n">
-        <v>-15.282</v>
+        <v>-14.978</v>
       </c>
     </row>
     <row r="14">
@@ -1878,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.48% / +3.76% / -2.26% | VAKBN.IS: -1.19% / +2.23% / -1.35%</t>
+          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.02% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-15.39859921157596</v>
+        <v>-15.64175862267482</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1911,19 +1911,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>21.661</v>
+        <v>21.773</v>
       </c>
       <c r="T18" t="n">
-        <v>21.661</v>
+        <v>21.773</v>
       </c>
       <c r="U18" t="n">
-        <v>60.753</v>
+        <v>60.291</v>
       </c>
       <c r="V18" t="n">
-        <v>14.937</v>
+        <v>14.607</v>
       </c>
       <c r="W18" t="n">
-        <v>-44.152</v>
+        <v>-44.614</v>
       </c>
     </row>
     <row r="19">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.31% / +2.48% / -2.76% | ENJSA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +2.48% / -2.76% | ENJSA.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-16.53722600142411</v>
+        <v>-16.45577636120216</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2154,19 +2154,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>17.846</v>
+        <v>17.766</v>
       </c>
       <c r="T21" t="n">
-        <v>17.846</v>
+        <v>17.766</v>
       </c>
       <c r="U21" t="n">
-        <v>39.918</v>
+        <v>40.054</v>
       </c>
       <c r="V21" t="n">
-        <v>10.813</v>
+        <v>10.921</v>
       </c>
       <c r="W21" t="n">
-        <v>-30.393</v>
+        <v>-30.257</v>
       </c>
     </row>
     <row r="22">
@@ -2210,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.48% / +3.76% / -2.26% | VAKBN.IS: -1.19% / +2.23% / -1.35%</t>
+          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.02% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.879019379116012</v>
+        <v>-5.152413925960042</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2243,19 +2243,19 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>17.439</v>
+        <v>17.557</v>
       </c>
       <c r="T22" t="n">
-        <v>17.439</v>
+        <v>17.557</v>
       </c>
       <c r="U22" t="n">
-        <v>71.824</v>
+        <v>71.33</v>
       </c>
       <c r="V22" t="n">
-        <v>30.159</v>
+        <v>29.785</v>
       </c>
       <c r="W22" t="n">
-        <v>-35.993</v>
+        <v>-36.487</v>
       </c>
     </row>
     <row r="23">
@@ -2453,14 +2453,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TRALT.IS: +2.46% / +2.68% / -2.03%</t>
+          <t>TRALT.IS: +2.76% / +2.88% / -2.03%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-5.044425134583063</v>
       </c>
       <c r="K25" t="n">
-        <v>11.62957530431525</v>
+        <v>11.25815008441988</v>
       </c>
       <c r="L25" t="n">
         <v>9.344627019167174</v>
@@ -2472,7 +2472,7 @@
         <v>59</v>
       </c>
       <c r="O25" t="n">
-        <v>52.1</v>
+        <v>51.3</v>
       </c>
       <c r="P25" t="n">
         <v>2.1</v>
@@ -2492,13 +2492,13 @@
         <v>12.101</v>
       </c>
       <c r="U25" t="n">
-        <v>30.241</v>
+        <v>29.807</v>
       </c>
       <c r="V25" t="n">
-        <v>35.678</v>
+        <v>35.227</v>
       </c>
       <c r="W25" t="n">
-        <v>-7.538</v>
+        <v>-7.972</v>
       </c>
     </row>
     <row r="26">
@@ -2542,14 +2542,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>KUYAS.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: +2.46% / +2.68% / -2.03%</t>
+          <t>KUYAS.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: +2.76% / +2.88% / -2.03%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.370921394748372</v>
+        <v>-3.461710094756265</v>
       </c>
       <c r="L26" t="n">
         <v>4.543450519200398</v>
@@ -2561,7 +2561,7 @@
         <v>175.6</v>
       </c>
       <c r="O26" t="n">
-        <v>49.2</v>
+        <v>48.9</v>
       </c>
       <c r="P26" t="n">
         <v>1.9</v>
@@ -2581,13 +2581,13 @@
         <v>10.072</v>
       </c>
       <c r="U26" t="n">
-        <v>17.011</v>
+        <v>16.901</v>
       </c>
       <c r="V26" t="n">
-        <v>8.795999999999999</v>
+        <v>8.694000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>-8.377000000000001</v>
+        <v>-8.487</v>
       </c>
     </row>
     <row r="27">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.13% / +20.94% / 0.00% | RALYH.IS: +23.05% / +35.10% / -0.91% | VAKBN.IS: -1.19% / +2.23% / -1.35%</t>
+          <t>BRSAN.IS: +9.53% / +20.94% / 0.00% | RALYH.IS: +23.17% / +35.10% / -0.91% | VAKBN.IS: -1.02% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>9.44732483159536</v>
+        <v>9.677058012552408</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2670,13 +2670,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>44.756</v>
+        <v>45.06</v>
       </c>
       <c r="V27" t="n">
-        <v>38.7</v>
+        <v>38.991</v>
       </c>
       <c r="W27" t="n">
-        <v>-15.282</v>
+        <v>-14.978</v>
       </c>
     </row>
   </sheetData>
@@ -2889,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.66% / +3.97% / -3.23%</t>
+          <t>ALARK.IS: +3.12% / +3.97% / -3.23%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2017897931249069</v>
+        <v>0.3299569951602965</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2928,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>277.153</v>
+        <v>277.635</v>
       </c>
       <c r="V3" t="n">
-        <v>101.854</v>
+        <v>102.112</v>
       </c>
       <c r="W3" t="n">
-        <v>-41.246</v>
+        <v>-40.763</v>
       </c>
     </row>
     <row r="4">
@@ -2976,14 +2976,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.66% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.31% / +2.47% / -2.77% | ENJSA.IS: +4.16% / +4.18% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.12% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +2.47% / -2.77% | ENJSA.IS: +3.98% / +4.45% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.35345989122698</v>
+        <v>-10.25058082134072</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -3009,19 +3009,19 @@
         <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>25.181</v>
+        <v>25.095</v>
       </c>
       <c r="T4" t="n">
-        <v>25.181</v>
+        <v>25.095</v>
       </c>
       <c r="U4" t="n">
-        <v>56.706</v>
+        <v>56.886</v>
       </c>
       <c r="V4" t="n">
-        <v>20.612</v>
+        <v>20.751</v>
       </c>
       <c r="W4" t="n">
-        <v>-52.74</v>
+        <v>-52.56</v>
       </c>
     </row>
     <row r="5">
@@ -3063,14 +3063,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.66% / +3.97% / -3.23%</t>
+          <t>ALARK.IS: +3.12% / +3.97% / -3.23%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1817303471200349</v>
+        <v>0.3098718912996734</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3102,13 +3102,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>274.364</v>
+        <v>274.842</v>
       </c>
       <c r="V5" t="n">
-        <v>83.821</v>
+        <v>84.056</v>
       </c>
       <c r="W5" t="n">
-        <v>-40.893</v>
+        <v>-40.414</v>
       </c>
     </row>
     <row r="6">
@@ -3150,14 +3150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.31% / +20.03% / -1.13% | CANTE.IS: +9.45% / +15.84% / -2.80% | ENERY.IS: -0.31% / +2.47% / -2.77% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +11.68% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | CANTE.IS: +8.64% / +15.84% / -2.80% | ENERY.IS: -0.02% / +2.47% / -2.77% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +11.52% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.58658151009358</v>
+        <v>-10.64060502073337</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3183,19 +3183,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>26.32</v>
+        <v>26.364</v>
       </c>
       <c r="T6" t="n">
-        <v>26.32</v>
+        <v>26.364</v>
       </c>
       <c r="U6" t="n">
-        <v>24.253</v>
+        <v>24.178</v>
       </c>
       <c r="V6" t="n">
-        <v>11.165</v>
+        <v>11.098</v>
       </c>
       <c r="W6" t="n">
-        <v>-44.386</v>
+        <v>-44.461</v>
       </c>
     </row>
     <row r="7">
@@ -3237,14 +3237,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.66% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.31% / +2.47% / -2.77% | ENJSA.IS: +4.16% / +4.18% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.12% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +2.47% / -2.77% | ENJSA.IS: +3.98% / +4.45% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.35345989122698</v>
+        <v>-10.25058082134072</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3270,19 +3270,19 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>25.181</v>
+        <v>25.095</v>
       </c>
       <c r="T7" t="n">
-        <v>25.181</v>
+        <v>25.095</v>
       </c>
       <c r="U7" t="n">
-        <v>56.706</v>
+        <v>56.886</v>
       </c>
       <c r="V7" t="n">
-        <v>20.612</v>
+        <v>20.751</v>
       </c>
       <c r="W7" t="n">
-        <v>-52.74</v>
+        <v>-52.56</v>
       </c>
     </row>
     <row r="8">
@@ -3324,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.31% / +20.03% / -1.13% | CANTE.IS: +1.48% / +3.71% / -2.30% | ENERY.IS: -0.31% / +2.47% / -2.77%</t>
+          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | CANTE.IS: +0.73% / +3.71% / -2.30% | ENERY.IS: -0.02% / +2.47% / -2.77%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.514962194552895</v>
+        <v>-3.529820070730949</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3363,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>21.634</v>
+        <v>21.615</v>
       </c>
       <c r="V8" t="n">
-        <v>1.126</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>-32.502</v>
+        <v>-32.521</v>
       </c>
     </row>
     <row r="9">
@@ -3486,14 +3486,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.66% / +3.97% / -3.23% | CANTE.IS: +1.48% / +3.71% / -2.30% | ENERY.IS: -0.31% / +2.47% / -2.77%</t>
+          <t>ALARK.IS: +3.12% / +3.97% / -3.23% | CANTE.IS: +0.73% / +3.71% / -2.30% | ENERY.IS: -0.02% / +2.47% / -2.77%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.11185120536086</v>
+        <v>-3.101059115227844</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3525,13 +3525,13 @@
         <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>10.824</v>
+        <v>10.836</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.532</v>
+        <v>-2.521</v>
       </c>
       <c r="W10" t="n">
-        <v>-27.328</v>
+        <v>-27.316</v>
       </c>
     </row>
     <row r="11">
@@ -3573,14 +3573,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.66% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.31% / +2.47% / -2.77% | ENJSA.IS: +4.16% / +4.18% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.12% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +2.47% / -2.77% | ENJSA.IS: +3.98% / +4.45% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.26974363982992</v>
+        <v>-10.16676849651943</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3606,19 +3606,19 @@
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>23.856</v>
+        <v>23.769</v>
       </c>
       <c r="T11" t="n">
-        <v>23.856</v>
+        <v>23.769</v>
       </c>
       <c r="U11" t="n">
-        <v>32.788</v>
+        <v>32.94</v>
       </c>
       <c r="V11" t="n">
-        <v>7.602</v>
+        <v>7.725</v>
       </c>
       <c r="W11" t="n">
-        <v>-41.604</v>
+        <v>-41.451</v>
       </c>
     </row>
     <row r="12">
@@ -3660,14 +3660,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.31% / +20.03% / -1.13% | TKFEN.IS: +11.68% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | TKFEN.IS: +11.52% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>8.001712459790999</v>
+        <v>8.107376558782775</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3699,13 +3699,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>37.581</v>
+        <v>37.715</v>
       </c>
       <c r="V12" t="n">
-        <v>50.49</v>
+        <v>50.637</v>
       </c>
       <c r="W12" t="n">
-        <v>-19.449</v>
+        <v>-19.315</v>
       </c>
     </row>
     <row r="13">
@@ -3747,14 +3747,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | FENER.IS: +0.30% / +1.66% / -1.90%</t>
+          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.67% / +1.66% / -1.90%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K13" t="n">
-        <v>7.372297501662484</v>
+        <v>6.841206722968418</v>
       </c>
       <c r="L13" t="n">
         <v>19.61961325199098</v>
@@ -3766,7 +3766,7 @@
         <v>88.2</v>
       </c>
       <c r="O13" t="n">
-        <v>46.3</v>
+        <v>45.8</v>
       </c>
       <c r="P13" t="n">
         <v>2.2</v>
@@ -3786,13 +3786,13 @@
         <v>18.132</v>
       </c>
       <c r="U13" t="n">
-        <v>6.912</v>
+        <v>6.383</v>
       </c>
       <c r="V13" t="n">
-        <v>12.119</v>
+        <v>11.564</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.246</v>
+        <v>-7.775</v>
       </c>
     </row>
     <row r="14">
@@ -4035,14 +4035,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.66% / +3.97% / -3.23%</t>
+          <t>ALARK.IS: +3.12% / +3.97% / -3.23%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2017897931249069</v>
+        <v>0.3299569951602965</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4074,13 +4074,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>277.153</v>
+        <v>277.635</v>
       </c>
       <c r="V18" t="n">
-        <v>101.854</v>
+        <v>102.112</v>
       </c>
       <c r="W18" t="n">
-        <v>-41.246</v>
+        <v>-40.763</v>
       </c>
     </row>
     <row r="19">
@@ -4124,14 +4124,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.66% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.31% / +2.47% / -2.77% | ENJSA.IS: +4.16% / +4.18% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.12% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +2.47% / -2.77% | ENJSA.IS: +3.98% / +4.45% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.35345989122698</v>
+        <v>-10.25058082134072</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4157,19 +4157,19 @@
         <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>25.181</v>
+        <v>25.095</v>
       </c>
       <c r="T19" t="n">
-        <v>25.181</v>
+        <v>25.095</v>
       </c>
       <c r="U19" t="n">
-        <v>56.706</v>
+        <v>56.886</v>
       </c>
       <c r="V19" t="n">
-        <v>20.612</v>
+        <v>20.751</v>
       </c>
       <c r="W19" t="n">
-        <v>-52.74</v>
+        <v>-52.56</v>
       </c>
     </row>
     <row r="20">
@@ -4213,14 +4213,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.66% / +3.97% / -3.23%</t>
+          <t>ALARK.IS: +3.12% / +3.97% / -3.23%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1817303471200349</v>
+        <v>0.3098718912996734</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4252,13 +4252,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>274.364</v>
+        <v>274.842</v>
       </c>
       <c r="V20" t="n">
-        <v>83.821</v>
+        <v>84.056</v>
       </c>
       <c r="W20" t="n">
-        <v>-40.893</v>
+        <v>-40.414</v>
       </c>
     </row>
     <row r="21">
@@ -4302,14 +4302,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.66% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.31% / +2.47% / -2.77% | ENJSA.IS: +4.16% / +4.18% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.12% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +2.47% / -2.77% | ENJSA.IS: +3.98% / +4.45% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.26974363982992</v>
+        <v>-10.16676849651943</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4335,19 +4335,19 @@
         <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>23.856</v>
+        <v>23.769</v>
       </c>
       <c r="T21" t="n">
-        <v>23.856</v>
+        <v>23.769</v>
       </c>
       <c r="U21" t="n">
-        <v>32.788</v>
+        <v>32.94</v>
       </c>
       <c r="V21" t="n">
-        <v>7.602</v>
+        <v>7.725</v>
       </c>
       <c r="W21" t="n">
-        <v>-41.604</v>
+        <v>-41.451</v>
       </c>
     </row>
     <row r="22">
@@ -4391,14 +4391,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.31% / +20.03% / -1.13% | CANTE.IS: +9.45% / +15.84% / -2.80% | ENERY.IS: -0.31% / +2.47% / -2.77% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +11.68% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | CANTE.IS: +8.64% / +15.84% / -2.80% | ENERY.IS: -0.02% / +2.47% / -2.77% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +11.52% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.58658151009358</v>
+        <v>-10.64060502073337</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4424,19 +4424,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>26.32</v>
+        <v>26.364</v>
       </c>
       <c r="T22" t="n">
-        <v>26.32</v>
+        <v>26.364</v>
       </c>
       <c r="U22" t="n">
-        <v>24.253</v>
+        <v>24.178</v>
       </c>
       <c r="V22" t="n">
-        <v>11.165</v>
+        <v>11.098</v>
       </c>
       <c r="W22" t="n">
-        <v>-44.386</v>
+        <v>-44.461</v>
       </c>
     </row>
     <row r="23">
@@ -4480,14 +4480,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.31% / +20.03% / -1.13% | CANTE.IS: +1.48% / +3.71% / -2.30% | ENERY.IS: -0.31% / +2.47% / -2.77%</t>
+          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | CANTE.IS: +0.73% / +3.71% / -2.30% | ENERY.IS: -0.02% / +2.47% / -2.77%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.514962194552895</v>
+        <v>-3.529820070730949</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4519,13 +4519,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>21.634</v>
+        <v>21.615</v>
       </c>
       <c r="V23" t="n">
-        <v>1.126</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>-32.502</v>
+        <v>-32.521</v>
       </c>
     </row>
     <row r="24">
@@ -4569,14 +4569,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.66% / +3.97% / -3.23% | CANTE.IS: +1.48% / +3.71% / -2.30% | ENERY.IS: -0.31% / +2.47% / -2.77%</t>
+          <t>ALARK.IS: +3.12% / +3.97% / -3.23% | CANTE.IS: +0.73% / +3.71% / -2.30% | ENERY.IS: -0.02% / +2.47% / -2.77%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.11185120536086</v>
+        <v>-3.101059115227844</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4608,13 +4608,13 @@
         <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>10.824</v>
+        <v>10.836</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.532</v>
+        <v>-2.521</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.328</v>
+        <v>-27.316</v>
       </c>
     </row>
     <row r="25">
@@ -4812,14 +4812,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.31% / +20.03% / -1.13% | TKFEN.IS: +11.68% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | TKFEN.IS: +11.52% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>8.001712459790999</v>
+        <v>8.107376558782775</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4851,13 +4851,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>37.581</v>
+        <v>37.715</v>
       </c>
       <c r="V27" t="n">
-        <v>50.49</v>
+        <v>50.637</v>
       </c>
       <c r="W27" t="n">
-        <v>-19.449</v>
+        <v>-19.315</v>
       </c>
     </row>
     <row r="28">
@@ -4901,14 +4901,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | FENER.IS: +0.30% / +1.66% / -1.90%</t>
+          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.67% / +1.66% / -1.90%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>7.372297501662484</v>
+        <v>6.841206722968418</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4920,7 +4920,7 @@
         <v>88.2</v>
       </c>
       <c r="O28" t="n">
-        <v>46.3</v>
+        <v>45.8</v>
       </c>
       <c r="P28" t="n">
         <v>2.2</v>
@@ -4940,13 +4940,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>6.912</v>
+        <v>6.383</v>
       </c>
       <c r="V28" t="n">
-        <v>12.119</v>
+        <v>11.564</v>
       </c>
       <c r="W28" t="n">
-        <v>-7.246</v>
+        <v>-7.775</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.02% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -0.90% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-15.64175862267482</v>
+        <v>-15.90971176798014</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -772,13 +772,13 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>102.7</v>
+        <v>102.5</v>
       </c>
       <c r="O3" t="n">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="P3" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -789,19 +789,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>21.773</v>
+        <v>22.022</v>
       </c>
       <c r="T3" t="n">
-        <v>21.773</v>
+        <v>22.022</v>
       </c>
       <c r="U3" t="n">
-        <v>60.291</v>
+        <v>59.373</v>
       </c>
       <c r="V3" t="n">
-        <v>14.607</v>
+        <v>14.243</v>
       </c>
       <c r="W3" t="n">
-        <v>-44.614</v>
+        <v>-45.008</v>
       </c>
     </row>
     <row r="4">
@@ -820,12 +820,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -847,7 +847,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
       <c r="O4" t="n">
         <v>48.8</v>
@@ -895,12 +895,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N5" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>46.6</v>
@@ -970,12 +970,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.02% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -0.90% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-15.64175862267482</v>
+        <v>-15.90971176798014</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1009,13 +1009,13 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>102.7</v>
+        <v>102.5</v>
       </c>
       <c r="O6" t="n">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="P6" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>21.773</v>
+        <v>22.022</v>
       </c>
       <c r="T6" t="n">
-        <v>21.773</v>
+        <v>22.022</v>
       </c>
       <c r="U6" t="n">
-        <v>60.291</v>
+        <v>59.373</v>
       </c>
       <c r="V6" t="n">
-        <v>14.607</v>
+        <v>14.243</v>
       </c>
       <c r="W6" t="n">
-        <v>-44.614</v>
+        <v>-45.008</v>
       </c>
     </row>
     <row r="7">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.02% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -0.90% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.152413925960042</v>
+        <v>-5.453685130743446</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1096,13 +1096,13 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>134.9</v>
+        <v>134.7</v>
       </c>
       <c r="O7" t="n">
-        <v>47.4</v>
+        <v>47.1</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>17.557</v>
+        <v>17.819</v>
       </c>
       <c r="T7" t="n">
-        <v>17.557</v>
+        <v>17.819</v>
       </c>
       <c r="U7" t="n">
-        <v>71.33</v>
+        <v>65.256</v>
       </c>
       <c r="V7" t="n">
-        <v>29.785</v>
+        <v>29.373</v>
       </c>
       <c r="W7" t="n">
-        <v>-36.487</v>
+        <v>-35.832</v>
       </c>
     </row>
     <row r="8">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +2.48% / -2.76% | ENJSA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +0.79% / +1.61% / -0.36% | ENERY.IS: +0.84% / +2.48% / -2.76% | ENJSA.IS: -0.37% / +0.61% / -0.44%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-16.45577636120216</v>
+        <v>-16.08200296859165</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1183,10 +1183,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>192.5</v>
+        <v>192.1</v>
       </c>
       <c r="O8" t="n">
-        <v>46.4</v>
+        <v>46.9</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1200,19 +1200,19 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>17.766</v>
+        <v>17.749</v>
       </c>
       <c r="T8" t="n">
-        <v>17.766</v>
+        <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>40.054</v>
+        <v>40.568</v>
       </c>
       <c r="V8" t="n">
-        <v>10.921</v>
+        <v>11.417</v>
       </c>
       <c r="W8" t="n">
-        <v>-30.257</v>
+        <v>-29.607</v>
       </c>
     </row>
     <row r="9">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.02% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -0.90% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-15.64175862267482</v>
+        <v>-15.90971176798014</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1270,13 +1270,13 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>102.7</v>
+        <v>102.5</v>
       </c>
       <c r="O9" t="n">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="P9" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1287,19 +1287,19 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>21.773</v>
+        <v>22.022</v>
       </c>
       <c r="T9" t="n">
-        <v>21.773</v>
+        <v>22.022</v>
       </c>
       <c r="U9" t="n">
-        <v>60.291</v>
+        <v>59.373</v>
       </c>
       <c r="V9" t="n">
-        <v>14.607</v>
+        <v>14.243</v>
       </c>
       <c r="W9" t="n">
-        <v>-44.614</v>
+        <v>-45.008</v>
       </c>
     </row>
     <row r="10">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>KUYAS.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: +2.76% / +2.88% / -2.03%</t>
+          <t>KUYAS.IS: -0.73% / +0.00% / -0.78% | TRALT.IS: +0.38% / +2.88% / -2.03%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.461710094756265</v>
+        <v>-4.055214696096021</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1357,7 +1357,7 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>175.6</v>
+        <v>175.3</v>
       </c>
       <c r="O10" t="n">
         <v>48.9</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>16.901</v>
+        <v>16.182</v>
       </c>
       <c r="V10" t="n">
-        <v>8.694000000000001</v>
+        <v>8.026</v>
       </c>
       <c r="W10" t="n">
-        <v>-8.487</v>
+        <v>-9.206</v>
       </c>
     </row>
     <row r="11">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>67</v>
+        <v>66.8</v>
       </c>
       <c r="O11" t="n">
         <v>51.9</v>
@@ -1475,80 +1475,68 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>TRALT.IS</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>TRALT.IS: 2026-09-02</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>25.65141339163128</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>TRALT.IS: +2.76% / +2.88% / -2.03%</t>
-        </is>
-      </c>
+        <v>7.610984631351814</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>-5.044425134583063</v>
+        <v>-16.01405991857144</v>
       </c>
       <c r="K12" t="n">
-        <v>11.25815008441988</v>
+        <v>9.964713536822334</v>
       </c>
       <c r="L12" t="n">
-        <v>9.344627019167174</v>
+        <v>19.17000314054332</v>
       </c>
       <c r="M12" t="n">
-        <v>66.66666666666666</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N12" t="n">
-        <v>59</v>
+        <v>59.9</v>
       </c>
       <c r="O12" t="n">
-        <v>51.3</v>
+        <v>43.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>12.101</v>
+        <v>27.346</v>
       </c>
       <c r="T12" t="n">
-        <v>12.101</v>
+        <v>27.346</v>
       </c>
       <c r="U12" t="n">
-        <v>29.807</v>
+        <v>-5.223</v>
       </c>
       <c r="V12" t="n">
-        <v>35.227</v>
+        <v>7.691</v>
       </c>
       <c r="W12" t="n">
-        <v>-7.972</v>
+        <v>-23.852</v>
       </c>
     </row>
     <row r="13">
@@ -1567,12 +1555,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1590,14 +1578,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.53% / +20.94% / 0.00% | RALYH.IS: +23.17% / +35.10% / -0.91% | VAKBN.IS: -1.02% / +2.23% / -1.88%</t>
+          <t>BRSAN.IS: +10.01% / +20.94% / 0.00% | RALYH.IS: +22.09% / +35.10% / -0.91% | VAKBN.IS: -0.90% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K13" t="n">
-        <v>9.677058012552408</v>
+        <v>9.53861823686324</v>
       </c>
       <c r="L13" t="n">
         <v>34.56349599547857</v>
@@ -1606,7 +1594,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>69.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="O13" t="n">
         <v>44</v>
@@ -1629,13 +1617,13 @@
         <v>23.777</v>
       </c>
       <c r="U13" t="n">
-        <v>45.06</v>
+        <v>44.877</v>
       </c>
       <c r="V13" t="n">
-        <v>38.991</v>
+        <v>38.816</v>
       </c>
       <c r="W13" t="n">
-        <v>-14.978</v>
+        <v>-15.161</v>
       </c>
     </row>
     <row r="14">
@@ -1654,12 +1642,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1681,7 +1669,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>59</v>
+        <v>58.9</v>
       </c>
       <c r="O14" t="n">
         <v>44.5</v>
@@ -1704,13 +1692,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>82.66800000000001</v>
+        <v>77.732</v>
       </c>
       <c r="V14" t="n">
         <v>93.19</v>
       </c>
       <c r="W14" t="n">
-        <v>-30.472</v>
+        <v>-29.648</v>
       </c>
     </row>
     <row r="16">
@@ -1855,12 +1843,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1878,14 +1866,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.02% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -0.90% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-15.64175862267482</v>
+        <v>-15.90971176798014</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1894,13 +1882,13 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>102.7</v>
+        <v>102.5</v>
       </c>
       <c r="O18" t="n">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="P18" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1911,19 +1899,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>21.773</v>
+        <v>22.022</v>
       </c>
       <c r="T18" t="n">
-        <v>21.773</v>
+        <v>22.022</v>
       </c>
       <c r="U18" t="n">
-        <v>60.291</v>
+        <v>59.373</v>
       </c>
       <c r="V18" t="n">
-        <v>14.607</v>
+        <v>14.243</v>
       </c>
       <c r="W18" t="n">
-        <v>-44.614</v>
+        <v>-45.008</v>
       </c>
     </row>
     <row r="19">
@@ -1944,12 +1932,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1971,7 +1959,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
       <c r="O19" t="n">
         <v>48.8</v>
@@ -2021,12 +2009,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2048,7 +2036,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>46.6</v>
@@ -2098,12 +2086,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2121,14 +2109,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +2.48% / -2.76% | ENJSA.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +0.79% / +1.61% / -0.36% | ENERY.IS: +0.84% / +2.48% / -2.76% | ENJSA.IS: -0.37% / +0.61% / -0.44%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-16.45577636120216</v>
+        <v>-16.08200296859165</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2137,10 +2125,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>192.5</v>
+        <v>192.1</v>
       </c>
       <c r="O21" t="n">
-        <v>46.4</v>
+        <v>46.9</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2154,19 +2142,19 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>17.766</v>
+        <v>17.749</v>
       </c>
       <c r="T21" t="n">
-        <v>17.766</v>
+        <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>40.054</v>
+        <v>40.568</v>
       </c>
       <c r="V21" t="n">
-        <v>10.921</v>
+        <v>11.417</v>
       </c>
       <c r="W21" t="n">
-        <v>-30.257</v>
+        <v>-29.607</v>
       </c>
     </row>
     <row r="22">
@@ -2187,12 +2175,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2210,14 +2198,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.02% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -0.90% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.152413925960042</v>
+        <v>-5.453685130743446</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2226,13 +2214,13 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>134.9</v>
+        <v>134.7</v>
       </c>
       <c r="O22" t="n">
-        <v>47.4</v>
+        <v>47.1</v>
       </c>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2243,19 +2231,19 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>17.557</v>
+        <v>17.819</v>
       </c>
       <c r="T22" t="n">
-        <v>17.557</v>
+        <v>17.819</v>
       </c>
       <c r="U22" t="n">
-        <v>71.33</v>
+        <v>65.256</v>
       </c>
       <c r="V22" t="n">
-        <v>29.785</v>
+        <v>29.373</v>
       </c>
       <c r="W22" t="n">
-        <v>-36.487</v>
+        <v>-35.832</v>
       </c>
     </row>
     <row r="23">
@@ -2276,12 +2264,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -2303,7 +2291,7 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>59</v>
+        <v>58.9</v>
       </c>
       <c r="O23" t="n">
         <v>44.5</v>
@@ -2326,13 +2314,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>82.66800000000001</v>
+        <v>77.732</v>
       </c>
       <c r="V23" t="n">
         <v>93.19</v>
       </c>
       <c r="W23" t="n">
-        <v>-30.472</v>
+        <v>-29.648</v>
       </c>
     </row>
     <row r="24">
@@ -2353,12 +2341,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2380,7 +2368,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>67</v>
+        <v>66.8</v>
       </c>
       <c r="O24" t="n">
         <v>51.9</v>
@@ -2415,67 +2403,67 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
+          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TRALT.IS</t>
+          <t>KUYAS.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TRALT.IS: 2026-09-02</t>
+          <t>KUYAS.IS: 2026-09-03 | TRALT.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>25.65141339163128</v>
+        <v>23.02092795860866</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TRALT.IS: +2.76% / +2.88% / -2.03%</t>
+          <t>KUYAS.IS: -0.73% / +0.00% / -0.78% | TRALT.IS: +0.38% / +2.88% / -2.03%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>-5.044425134583063</v>
+        <v>12.86015270141232</v>
       </c>
       <c r="K25" t="n">
-        <v>11.25815008441988</v>
+        <v>-4.055214696096021</v>
       </c>
       <c r="L25" t="n">
-        <v>9.344627019167174</v>
+        <v>4.543450519200398</v>
       </c>
       <c r="M25" t="n">
-        <v>66.66666666666666</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N25" t="n">
-        <v>59</v>
+        <v>175.3</v>
       </c>
       <c r="O25" t="n">
-        <v>51.3</v>
+        <v>48.9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2483,28 +2471,28 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>12.101</v>
+        <v>10.072</v>
       </c>
       <c r="T25" t="n">
-        <v>12.101</v>
+        <v>10.072</v>
       </c>
       <c r="U25" t="n">
-        <v>29.807</v>
+        <v>16.182</v>
       </c>
       <c r="V25" t="n">
-        <v>35.227</v>
+        <v>8.026</v>
       </c>
       <c r="W25" t="n">
-        <v>-7.972</v>
+        <v>-9.206</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2514,57 +2502,57 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KUYAS.IS, TRALT.IS</t>
+          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>KUYAS.IS: 2026-09-03 | TRALT.IS: 2026-09-02</t>
+          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>23.02092795860866</v>
+        <v>13.58351811074014</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>KUYAS.IS: -0.02% / +0.00% / 0.00% | TRALT.IS: +2.76% / +2.88% / -2.03%</t>
+          <t>BRSAN.IS: +10.01% / +20.94% / 0.00% | RALYH.IS: +22.09% / +35.10% / -0.91% | VAKBN.IS: -0.90% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>12.86015270141232</v>
+        <v>-10.39434387728287</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.461710094756265</v>
+        <v>9.53861823686324</v>
       </c>
       <c r="L26" t="n">
-        <v>4.543450519200398</v>
+        <v>34.56349599547857</v>
       </c>
       <c r="M26" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>175.6</v>
+        <v>69.8</v>
       </c>
       <c r="O26" t="n">
-        <v>48.9</v>
+        <v>44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.9</v>
+        <v>6.1</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2572,22 +2560,22 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>10.072</v>
+        <v>23.777</v>
       </c>
       <c r="T26" t="n">
-        <v>10.072</v>
+        <v>23.777</v>
       </c>
       <c r="U26" t="n">
-        <v>16.901</v>
+        <v>44.877</v>
       </c>
       <c r="V26" t="n">
-        <v>8.694000000000001</v>
+        <v>38.816</v>
       </c>
       <c r="W26" t="n">
-        <v>-8.487</v>
+        <v>-15.161</v>
       </c>
     </row>
     <row r="27">
@@ -2598,85 +2586,73 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>13.58351811074014</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +9.53% / +20.94% / 0.00% | RALYH.IS: +23.17% / +35.10% / -0.91% | VAKBN.IS: -1.02% / +2.23% / -1.88%</t>
-        </is>
-      </c>
+        <v>7.610984631351814</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>-10.39434387728287</v>
+        <v>-16.01405991857144</v>
       </c>
       <c r="K27" t="n">
-        <v>9.677058012552408</v>
+        <v>9.964713536822334</v>
       </c>
       <c r="L27" t="n">
-        <v>34.56349599547857</v>
+        <v>19.17000314054332</v>
       </c>
       <c r="M27" t="n">
-        <v>77.77777777777779</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N27" t="n">
-        <v>69.90000000000001</v>
+        <v>59.9</v>
       </c>
       <c r="O27" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="P27" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>23.777</v>
+        <v>27.346</v>
       </c>
       <c r="T27" t="n">
-        <v>23.777</v>
+        <v>27.346</v>
       </c>
       <c r="U27" t="n">
-        <v>45.06</v>
+        <v>-5.223</v>
       </c>
       <c r="V27" t="n">
-        <v>38.991</v>
+        <v>7.691</v>
       </c>
       <c r="W27" t="n">
-        <v>-14.978</v>
+        <v>-23.852</v>
       </c>
     </row>
   </sheetData>
@@ -2866,22 +2842,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ALARK.IS</t>
+          <t>ALARK.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2889,14 +2865,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.12% / +3.97% / -3.23%</t>
+          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3299569951602965</v>
+        <v>0.6810570016952733</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2905,10 +2881,10 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>92.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>44.6</v>
+        <v>44.4</v>
       </c>
       <c r="P3" t="n">
         <v>4.3</v>
@@ -2919,7 +2895,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>18.106</v>
@@ -2928,13 +2904,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>277.635</v>
+        <v>256.361</v>
       </c>
       <c r="V3" t="n">
-        <v>102.112</v>
+        <v>102.819</v>
       </c>
       <c r="W3" t="n">
-        <v>-40.763</v>
+        <v>-37.09</v>
       </c>
     </row>
     <row r="4">
@@ -2953,14 +2929,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>ALARK.IS, ALTNY.IS, ENERY.IS, ENJSA.IS, SOKM.IS</t>
@@ -2968,7 +2944,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2976,14 +2952,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.12% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +2.47% / -2.77% | ENJSA.IS: +3.98% / +4.45% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +0.84% / +2.47% / -2.77% | ENJSA.IS: +3.61% / +4.63% / -0.09% | SOKM.IS: -0.54% / +0.69% / -0.69%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.25058082134072</v>
+        <v>-10.74407057356332</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2992,10 +2968,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>118.5</v>
+        <v>118.8</v>
       </c>
       <c r="O4" t="n">
-        <v>46.6</v>
+        <v>46.9</v>
       </c>
       <c r="P4" t="n">
         <v>3.8</v>
@@ -3009,19 +2985,19 @@
         <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>25.095</v>
+        <v>25.507</v>
       </c>
       <c r="T4" t="n">
-        <v>25.095</v>
+        <v>25.507</v>
       </c>
       <c r="U4" t="n">
-        <v>56.886</v>
+        <v>56.023</v>
       </c>
       <c r="V4" t="n">
-        <v>20.751</v>
+        <v>20.087</v>
       </c>
       <c r="W4" t="n">
-        <v>-52.56</v>
+        <v>-53.423</v>
       </c>
     </row>
     <row r="5">
@@ -3040,22 +3016,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ALARK.IS</t>
+          <t>ALARK.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3063,14 +3039,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.12% / +3.97% / -3.23%</t>
+          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3098718912996734</v>
+        <v>0.660901610950182</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3079,10 +3055,10 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>81.7</v>
+        <v>82</v>
       </c>
       <c r="O5" t="n">
-        <v>42.7</v>
+        <v>42.4</v>
       </c>
       <c r="P5" t="n">
         <v>4.7</v>
@@ -3093,7 +3069,7 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>21.096</v>
@@ -3102,13 +3078,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>274.842</v>
+        <v>253.618</v>
       </c>
       <c r="V5" t="n">
-        <v>84.056</v>
+        <v>84.7</v>
       </c>
       <c r="W5" t="n">
-        <v>-40.414</v>
+        <v>-36.76</v>
       </c>
     </row>
     <row r="6">
@@ -3127,12 +3103,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3150,14 +3126,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | CANTE.IS: +8.64% / +15.84% / -2.80% | ENERY.IS: -0.02% / +2.47% / -2.77% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +11.52% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +9.18% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | ENERY.IS: +0.84% / +2.47% / -2.77% | SOKM.IS: -0.54% / +0.69% / -0.69% | TKFEN.IS: +8.53% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.64060502073337</v>
+        <v>-11.15816275529833</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3166,10 +3142,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>139.4</v>
+        <v>139.2</v>
       </c>
       <c r="O6" t="n">
-        <v>42.1</v>
+        <v>42.5</v>
       </c>
       <c r="P6" t="n">
         <v>5.7</v>
@@ -3183,19 +3159,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>26.364</v>
+        <v>26.791</v>
       </c>
       <c r="T6" t="n">
-        <v>26.364</v>
+        <v>26.791</v>
       </c>
       <c r="U6" t="n">
-        <v>24.178</v>
+        <v>20.886</v>
       </c>
       <c r="V6" t="n">
-        <v>11.098</v>
+        <v>10.454</v>
       </c>
       <c r="W6" t="n">
-        <v>-44.461</v>
+        <v>-44.238</v>
       </c>
     </row>
     <row r="7">
@@ -3214,14 +3190,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>ALARK.IS, ALTNY.IS, ENERY.IS, ENJSA.IS, SOKM.IS</t>
@@ -3229,7 +3205,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3237,14 +3213,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.12% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +2.47% / -2.77% | ENJSA.IS: +3.98% / +4.45% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +0.84% / +2.47% / -2.77% | ENJSA.IS: +3.61% / +4.63% / -0.09% | SOKM.IS: -0.54% / +0.69% / -0.69%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.25058082134072</v>
+        <v>-10.74407057356332</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3253,10 +3229,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>118.5</v>
+        <v>118.8</v>
       </c>
       <c r="O7" t="n">
-        <v>46.6</v>
+        <v>46.9</v>
       </c>
       <c r="P7" t="n">
         <v>3.8</v>
@@ -3270,19 +3246,19 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>25.095</v>
+        <v>25.507</v>
       </c>
       <c r="T7" t="n">
-        <v>25.095</v>
+        <v>25.507</v>
       </c>
       <c r="U7" t="n">
-        <v>56.886</v>
+        <v>56.023</v>
       </c>
       <c r="V7" t="n">
-        <v>20.751</v>
+        <v>20.087</v>
       </c>
       <c r="W7" t="n">
-        <v>-52.56</v>
+        <v>-53.423</v>
       </c>
     </row>
     <row r="8">
@@ -3301,12 +3277,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3324,14 +3300,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | CANTE.IS: +0.73% / +3.71% / -2.30% | ENERY.IS: -0.02% / +2.47% / -2.77%</t>
+          <t>BRSAN.IS: +9.18% / +20.03% / -1.13% | CANTE.IS: -0.02% / +3.71% / -2.30% | ENERY.IS: +0.84% / +2.47% / -2.77%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.529820070730949</v>
+        <v>-3.366529880386737</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3340,7 +3316,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>153.9</v>
+        <v>153.6</v>
       </c>
       <c r="O8" t="n">
         <v>42.1</v>
@@ -3363,13 +3339,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>21.615</v>
+        <v>21.048</v>
       </c>
       <c r="V8" t="n">
-        <v>1.11</v>
+        <v>1.282</v>
       </c>
       <c r="W8" t="n">
-        <v>-32.521</v>
+        <v>-32.11</v>
       </c>
     </row>
     <row r="9">
@@ -3388,12 +3364,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3415,7 +3391,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N9" t="n">
-        <v>75.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="O9" t="n">
         <v>49.3</v>
@@ -3463,12 +3439,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3486,14 +3462,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.12% / +3.97% / -3.23% | CANTE.IS: +0.73% / +3.71% / -2.30% | ENERY.IS: -0.02% / +2.47% / -2.77%</t>
+          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | CANTE.IS: -0.02% / +3.71% / -2.30% | ENERY.IS: +0.84% / +2.47% / -2.77%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.101059115227844</v>
+        <v>-2.833707452921619</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3502,7 +3478,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>114</v>
+        <v>113.8</v>
       </c>
       <c r="O10" t="n">
         <v>50.2</v>
@@ -3525,13 +3501,13 @@
         <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>10.836</v>
+        <v>11.142</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.521</v>
+        <v>-2.252</v>
       </c>
       <c r="W10" t="n">
-        <v>-27.316</v>
+        <v>-27.01</v>
       </c>
     </row>
     <row r="11">
@@ -3550,14 +3526,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>ALARK.IS, ALTNY.IS, ENERY.IS, ENJSA.IS, SOKM.IS</t>
@@ -3565,7 +3541,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -3573,14 +3549,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.12% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +2.47% / -2.77% | ENJSA.IS: +3.98% / +4.45% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +0.84% / +2.47% / -2.77% | ENJSA.IS: +3.61% / +4.63% / -0.09% | SOKM.IS: -0.54% / +0.69% / -0.69%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.16676849651943</v>
+        <v>-10.66071909321087</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3589,10 +3565,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>179.3</v>
+        <v>179.4</v>
       </c>
       <c r="O11" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
@@ -3606,19 +3582,19 @@
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>23.769</v>
+        <v>24.188</v>
       </c>
       <c r="T11" t="n">
-        <v>23.769</v>
+        <v>24.188</v>
       </c>
       <c r="U11" t="n">
-        <v>32.94</v>
+        <v>32.209</v>
       </c>
       <c r="V11" t="n">
-        <v>7.725</v>
+        <v>7.133</v>
       </c>
       <c r="W11" t="n">
-        <v>-41.451</v>
+        <v>-42.182</v>
       </c>
     </row>
     <row r="12">
@@ -3637,12 +3613,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3660,14 +3636,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | TKFEN.IS: +11.52% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +9.18% / +20.03% / -1.13% | TKFEN.IS: +8.53% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>8.107376558782775</v>
+        <v>6.811241450675753</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3676,13 +3652,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="O12" t="n">
         <v>43.3</v>
       </c>
       <c r="P12" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3699,13 +3675,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>37.715</v>
+        <v>38.887</v>
       </c>
       <c r="V12" t="n">
-        <v>50.637</v>
+        <v>48.831</v>
       </c>
       <c r="W12" t="n">
-        <v>-19.315</v>
+        <v>-21.401</v>
       </c>
     </row>
     <row r="13">
@@ -3724,22 +3700,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASTOR.IS, FENER.IS</t>
+          <t>CVKMD.IS, FENER.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-03 | FENER.IS: 2026-09-01</t>
+          <t>CVKMD.IS: 2026-09-04 | FENER.IS: 2026-09-01</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -3747,14 +3723,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.67% / +1.66% / -1.90%</t>
+          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.34% / +1.66% / -1.90%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K13" t="n">
-        <v>6.841206722968418</v>
+        <v>6.639608727219781</v>
       </c>
       <c r="L13" t="n">
         <v>19.61961325199098</v>
@@ -3763,10 +3739,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N13" t="n">
-        <v>88.2</v>
+        <v>88.5</v>
       </c>
       <c r="O13" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="P13" t="n">
         <v>2.2</v>
@@ -3786,13 +3762,13 @@
         <v>18.132</v>
       </c>
       <c r="U13" t="n">
-        <v>6.383</v>
+        <v>3.981</v>
       </c>
       <c r="V13" t="n">
-        <v>11.564</v>
+        <v>11.354</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.775</v>
+        <v>-7.81</v>
       </c>
     </row>
     <row r="14">
@@ -3811,12 +3787,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -3838,7 +3814,7 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N14" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="O14" t="n">
         <v>50</v>
@@ -3861,13 +3837,13 @@
         <v>7.916</v>
       </c>
       <c r="U14" t="n">
-        <v>10.082</v>
+        <v>8.898</v>
       </c>
       <c r="V14" t="n">
         <v>4.916</v>
       </c>
       <c r="W14" t="n">
-        <v>-5.025</v>
+        <v>-4.971</v>
       </c>
     </row>
     <row r="16">
@@ -4012,22 +3988,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ALARK.IS</t>
+          <t>ALARK.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -4035,14 +4011,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.12% / +3.97% / -3.23%</t>
+          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3299569951602965</v>
+        <v>0.6810570016952733</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4051,10 +4027,10 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>92.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>44.6</v>
+        <v>44.4</v>
       </c>
       <c r="P18" t="n">
         <v>4.3</v>
@@ -4065,7 +4041,7 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
         <v>18.106</v>
@@ -4074,13 +4050,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>277.635</v>
+        <v>256.361</v>
       </c>
       <c r="V18" t="n">
-        <v>102.112</v>
+        <v>102.819</v>
       </c>
       <c r="W18" t="n">
-        <v>-40.763</v>
+        <v>-37.09</v>
       </c>
     </row>
     <row r="19">
@@ -4101,14 +4077,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>ALARK.IS, ALTNY.IS, ENERY.IS, ENJSA.IS, SOKM.IS</t>
@@ -4116,7 +4092,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -4124,14 +4100,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.12% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +2.47% / -2.77% | ENJSA.IS: +3.98% / +4.45% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +0.84% / +2.47% / -2.77% | ENJSA.IS: +3.61% / +4.63% / -0.09% | SOKM.IS: -0.54% / +0.69% / -0.69%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.25058082134072</v>
+        <v>-10.74407057356332</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4140,10 +4116,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>118.5</v>
+        <v>118.8</v>
       </c>
       <c r="O19" t="n">
-        <v>46.6</v>
+        <v>46.9</v>
       </c>
       <c r="P19" t="n">
         <v>3.8</v>
@@ -4157,19 +4133,19 @@
         <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>25.095</v>
+        <v>25.507</v>
       </c>
       <c r="T19" t="n">
-        <v>25.095</v>
+        <v>25.507</v>
       </c>
       <c r="U19" t="n">
-        <v>56.886</v>
+        <v>56.023</v>
       </c>
       <c r="V19" t="n">
-        <v>20.751</v>
+        <v>20.087</v>
       </c>
       <c r="W19" t="n">
-        <v>-52.56</v>
+        <v>-53.423</v>
       </c>
     </row>
     <row r="20">
@@ -4190,22 +4166,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ALARK.IS</t>
+          <t>ALARK.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31</t>
+          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -4213,14 +4189,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.12% / +3.97% / -3.23%</t>
+          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3098718912996734</v>
+        <v>0.660901610950182</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4229,10 +4205,10 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>81.7</v>
+        <v>82</v>
       </c>
       <c r="O20" t="n">
-        <v>42.7</v>
+        <v>42.4</v>
       </c>
       <c r="P20" t="n">
         <v>4.7</v>
@@ -4243,7 +4219,7 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
         <v>21.096</v>
@@ -4252,13 +4228,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>274.842</v>
+        <v>253.618</v>
       </c>
       <c r="V20" t="n">
-        <v>84.056</v>
+        <v>84.7</v>
       </c>
       <c r="W20" t="n">
-        <v>-40.414</v>
+        <v>-36.76</v>
       </c>
     </row>
     <row r="21">
@@ -4279,14 +4255,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>ALARK.IS, ALTNY.IS, ENERY.IS, ENJSA.IS, SOKM.IS</t>
@@ -4294,7 +4270,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -4302,14 +4278,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.12% / +3.97% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +2.47% / -2.77% | ENJSA.IS: +3.98% / +4.45% / -0.09% | SOKM.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +0.84% / +2.47% / -2.77% | ENJSA.IS: +3.61% / +4.63% / -0.09% | SOKM.IS: -0.54% / +0.69% / -0.69%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.16676849651943</v>
+        <v>-10.66071909321087</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4318,10 +4294,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>179.3</v>
+        <v>179.4</v>
       </c>
       <c r="O21" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
@@ -4335,19 +4311,19 @@
         <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>23.769</v>
+        <v>24.188</v>
       </c>
       <c r="T21" t="n">
-        <v>23.769</v>
+        <v>24.188</v>
       </c>
       <c r="U21" t="n">
-        <v>32.94</v>
+        <v>32.209</v>
       </c>
       <c r="V21" t="n">
-        <v>7.725</v>
+        <v>7.133</v>
       </c>
       <c r="W21" t="n">
-        <v>-41.451</v>
+        <v>-42.182</v>
       </c>
     </row>
     <row r="22">
@@ -4368,12 +4344,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4391,14 +4367,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | CANTE.IS: +8.64% / +15.84% / -2.80% | ENERY.IS: -0.02% / +2.47% / -2.77% | SOKM.IS: -0.02% / +0.00% / 0.00% | TKFEN.IS: +11.52% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +9.18% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | ENERY.IS: +0.84% / +2.47% / -2.77% | SOKM.IS: -0.54% / +0.69% / -0.69% | TKFEN.IS: +8.53% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.64060502073337</v>
+        <v>-11.15816275529833</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4407,10 +4383,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>139.4</v>
+        <v>139.2</v>
       </c>
       <c r="O22" t="n">
-        <v>42.1</v>
+        <v>42.5</v>
       </c>
       <c r="P22" t="n">
         <v>5.7</v>
@@ -4424,19 +4400,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>26.364</v>
+        <v>26.791</v>
       </c>
       <c r="T22" t="n">
-        <v>26.364</v>
+        <v>26.791</v>
       </c>
       <c r="U22" t="n">
-        <v>24.178</v>
+        <v>20.886</v>
       </c>
       <c r="V22" t="n">
-        <v>11.098</v>
+        <v>10.454</v>
       </c>
       <c r="W22" t="n">
-        <v>-44.461</v>
+        <v>-44.238</v>
       </c>
     </row>
     <row r="23">
@@ -4457,12 +4433,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4480,14 +4456,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | CANTE.IS: +0.73% / +3.71% / -2.30% | ENERY.IS: -0.02% / +2.47% / -2.77%</t>
+          <t>BRSAN.IS: +9.18% / +20.03% / -1.13% | CANTE.IS: -0.02% / +3.71% / -2.30% | ENERY.IS: +0.84% / +2.47% / -2.77%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.529820070730949</v>
+        <v>-3.366529880386737</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4496,7 +4472,7 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>153.9</v>
+        <v>153.6</v>
       </c>
       <c r="O23" t="n">
         <v>42.1</v>
@@ -4519,13 +4495,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>21.615</v>
+        <v>21.048</v>
       </c>
       <c r="V23" t="n">
-        <v>1.11</v>
+        <v>1.282</v>
       </c>
       <c r="W23" t="n">
-        <v>-32.521</v>
+        <v>-32.11</v>
       </c>
     </row>
     <row r="24">
@@ -4546,12 +4522,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4569,14 +4545,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.12% / +3.97% / -3.23% | CANTE.IS: +0.73% / +3.71% / -2.30% | ENERY.IS: -0.02% / +2.47% / -2.77%</t>
+          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | CANTE.IS: -0.02% / +3.71% / -2.30% | ENERY.IS: +0.84% / +2.47% / -2.77%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.101059115227844</v>
+        <v>-2.833707452921619</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4585,7 +4561,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>114</v>
+        <v>113.8</v>
       </c>
       <c r="O24" t="n">
         <v>50.2</v>
@@ -4608,13 +4584,13 @@
         <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>10.836</v>
+        <v>11.142</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.521</v>
+        <v>-2.252</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.316</v>
+        <v>-27.01</v>
       </c>
     </row>
     <row r="25">
@@ -4635,12 +4611,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -4662,7 +4638,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>75.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="O25" t="n">
         <v>49.3</v>
@@ -4712,12 +4688,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -4739,7 +4715,7 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="O26" t="n">
         <v>50</v>
@@ -4762,13 +4738,13 @@
         <v>7.916</v>
       </c>
       <c r="U26" t="n">
-        <v>10.082</v>
+        <v>8.898</v>
       </c>
       <c r="V26" t="n">
         <v>4.916</v>
       </c>
       <c r="W26" t="n">
-        <v>-5.025</v>
+        <v>-4.971</v>
       </c>
     </row>
     <row r="27">
@@ -4789,12 +4765,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4812,14 +4788,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +8.71% / +20.03% / -1.13% | TKFEN.IS: +11.52% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +9.18% / +20.03% / -1.13% | TKFEN.IS: +8.53% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>8.107376558782775</v>
+        <v>6.811241450675753</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4828,13 +4804,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N27" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="O27" t="n">
         <v>43.3</v>
       </c>
       <c r="P27" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4851,13 +4827,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>37.715</v>
+        <v>38.887</v>
       </c>
       <c r="V27" t="n">
-        <v>50.637</v>
+        <v>48.831</v>
       </c>
       <c r="W27" t="n">
-        <v>-19.315</v>
+        <v>-21.401</v>
       </c>
     </row>
     <row r="28">
@@ -4878,22 +4854,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ASTOR.IS, FENER.IS</t>
+          <t>CVKMD.IS, FENER.IS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-03 | FENER.IS: 2026-09-01</t>
+          <t>CVKMD.IS: 2026-09-04 | FENER.IS: 2026-09-01</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4901,14 +4877,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ASTOR.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.67% / +1.66% / -1.90%</t>
+          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.34% / +1.66% / -1.90%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>6.841206722968418</v>
+        <v>6.639608727219781</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4917,10 +4893,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N28" t="n">
-        <v>88.2</v>
+        <v>88.5</v>
       </c>
       <c r="O28" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="P28" t="n">
         <v>2.2</v>
@@ -4940,13 +4916,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>6.383</v>
+        <v>3.981</v>
       </c>
       <c r="V28" t="n">
-        <v>11.564</v>
+        <v>11.354</v>
       </c>
       <c r="W28" t="n">
-        <v>-7.775</v>
+        <v>-7.81</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -0.90% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.84% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-15.90971176798014</v>
+        <v>-16.20244919070133</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -789,19 +789,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>22.022</v>
+        <v>22.293</v>
       </c>
       <c r="T3" t="n">
-        <v>22.022</v>
+        <v>22.293</v>
       </c>
       <c r="U3" t="n">
-        <v>59.373</v>
+        <v>58.818</v>
       </c>
       <c r="V3" t="n">
-        <v>14.243</v>
+        <v>13.845</v>
       </c>
       <c r="W3" t="n">
-        <v>-45.008</v>
+        <v>-45.563</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -0.90% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.84% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-15.90971176798014</v>
+        <v>-16.20244919070133</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1026,19 +1026,19 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>22.022</v>
+        <v>22.293</v>
       </c>
       <c r="T6" t="n">
-        <v>22.022</v>
+        <v>22.293</v>
       </c>
       <c r="U6" t="n">
-        <v>59.373</v>
+        <v>58.818</v>
       </c>
       <c r="V6" t="n">
-        <v>14.243</v>
+        <v>13.845</v>
       </c>
       <c r="W6" t="n">
-        <v>-45.008</v>
+        <v>-45.563</v>
       </c>
     </row>
     <row r="7">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -0.90% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.84% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.453685130743446</v>
+        <v>-5.782822360791307</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>17.819</v>
+        <v>18.105</v>
       </c>
       <c r="T7" t="n">
-        <v>17.819</v>
+        <v>18.105</v>
       </c>
       <c r="U7" t="n">
-        <v>65.256</v>
+        <v>64.681</v>
       </c>
       <c r="V7" t="n">
-        <v>29.373</v>
+        <v>28.923</v>
       </c>
       <c r="W7" t="n">
-        <v>-35.832</v>
+        <v>-36.407</v>
       </c>
     </row>
     <row r="8">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.79% / +1.61% / -0.36% | ENERY.IS: +0.84% / +2.48% / -2.76% | ENJSA.IS: -0.37% / +0.61% / -0.44%</t>
+          <t>ALARK.IS: -0.56% / +1.61% / -0.81% | ENERY.IS: +2.65% / +3.05% / -2.76% | ENJSA.IS: -0.89% / +0.61% / -1.31%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-16.08200296859165</v>
+        <v>-16.08264952961187</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1186,7 +1186,7 @@
         <v>192.1</v>
       </c>
       <c r="O8" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>40.568</v>
+        <v>40.567</v>
       </c>
       <c r="V8" t="n">
         <v>11.417</v>
       </c>
       <c r="W8" t="n">
-        <v>-29.607</v>
+        <v>-29.608</v>
       </c>
     </row>
     <row r="9">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -0.90% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.84% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-15.90971176798014</v>
+        <v>-16.20244919070133</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1287,19 +1287,19 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>22.022</v>
+        <v>22.293</v>
       </c>
       <c r="T9" t="n">
-        <v>22.022</v>
+        <v>22.293</v>
       </c>
       <c r="U9" t="n">
-        <v>59.373</v>
+        <v>58.818</v>
       </c>
       <c r="V9" t="n">
-        <v>14.243</v>
+        <v>13.845</v>
       </c>
       <c r="W9" t="n">
-        <v>-45.008</v>
+        <v>-45.563</v>
       </c>
     </row>
     <row r="10">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>KUYAS.IS: -0.73% / +0.00% / -0.78% | TRALT.IS: +0.38% / +2.88% / -2.03%</t>
+          <t>KUYAS.IS: +0.05% / +0.50% / -1.07% | TRALT.IS: +4.05% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.055214696096021</v>
+        <v>-3.200831843318375</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1360,7 +1360,7 @@
         <v>175.3</v>
       </c>
       <c r="O10" t="n">
-        <v>48.9</v>
+        <v>49.2</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>16.182</v>
+        <v>17.217</v>
       </c>
       <c r="V10" t="n">
-        <v>8.026</v>
+        <v>8.988</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.206</v>
+        <v>-8.170999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1488,55 +1488,67 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
+        </is>
+      </c>
       <c r="H12" t="n">
-        <v>7.610984631351814</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>13.58351811074014</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: +11.84% / +20.94% / 0.00% | RALYH.IS: +28.34% / +35.10% / -0.91% | VAKBN.IS: -0.84% / +2.23% / -1.88%</t>
+        </is>
+      </c>
       <c r="J12" t="n">
-        <v>-16.01405991857144</v>
+        <v>-10.39434387728287</v>
       </c>
       <c r="K12" t="n">
-        <v>9.964713536822334</v>
+        <v>12.08394181459536</v>
       </c>
       <c r="L12" t="n">
-        <v>19.17000314054332</v>
+        <v>34.56349599547857</v>
       </c>
       <c r="M12" t="n">
-        <v>88.88888888888889</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>59.9</v>
+        <v>69.8</v>
       </c>
       <c r="O12" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>27.346</v>
+        <v>23.777</v>
       </c>
       <c r="T12" t="n">
-        <v>27.346</v>
+        <v>23.777</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.223</v>
+        <v>48.243</v>
       </c>
       <c r="V12" t="n">
-        <v>7.691</v>
+        <v>42.042</v>
       </c>
       <c r="W12" t="n">
-        <v>-23.852</v>
+        <v>-11.795</v>
       </c>
     </row>
     <row r="13">
@@ -1550,7 +1562,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1565,42 +1577,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
+          <t>TRALT.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
+          <t>TRALT.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>13.58351811074014</v>
+        <v>25.65141339163128</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +10.01% / +20.94% / 0.00% | RALYH.IS: +22.09% / +35.10% / -0.91% | VAKBN.IS: -0.90% / +2.23% / -1.88%</t>
+          <t>TRALT.IS: +4.05% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-10.39434387728287</v>
+        <v>-5.044425134583063</v>
       </c>
       <c r="K13" t="n">
-        <v>9.53861823686324</v>
+        <v>11.96494399083883</v>
       </c>
       <c r="L13" t="n">
-        <v>34.56349599547857</v>
+        <v>9.344627019167174</v>
       </c>
       <c r="M13" t="n">
-        <v>77.77777777777779</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N13" t="n">
-        <v>69.8</v>
+        <v>58.9</v>
       </c>
       <c r="O13" t="n">
-        <v>44</v>
+        <v>51.3</v>
       </c>
       <c r="P13" t="n">
-        <v>6.1</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1608,22 +1620,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>23.777</v>
+        <v>12.101</v>
       </c>
       <c r="T13" t="n">
-        <v>23.777</v>
+        <v>12.101</v>
       </c>
       <c r="U13" t="n">
-        <v>44.877</v>
+        <v>30.632</v>
       </c>
       <c r="V13" t="n">
-        <v>38.816</v>
+        <v>36.086</v>
       </c>
       <c r="W13" t="n">
-        <v>-15.161</v>
+        <v>-7.147</v>
       </c>
     </row>
     <row r="14">
@@ -1866,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -0.90% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.84% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-15.90971176798014</v>
+        <v>-16.20244919070133</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1899,19 +1911,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>22.022</v>
+        <v>22.293</v>
       </c>
       <c r="T18" t="n">
-        <v>22.022</v>
+        <v>22.293</v>
       </c>
       <c r="U18" t="n">
-        <v>59.373</v>
+        <v>58.818</v>
       </c>
       <c r="V18" t="n">
-        <v>14.243</v>
+        <v>13.845</v>
       </c>
       <c r="W18" t="n">
-        <v>-45.008</v>
+        <v>-45.563</v>
       </c>
     </row>
     <row r="19">
@@ -2109,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.79% / +1.61% / -0.36% | ENERY.IS: +0.84% / +2.48% / -2.76% | ENJSA.IS: -0.37% / +0.61% / -0.44%</t>
+          <t>ALARK.IS: -0.56% / +1.61% / -0.81% | ENERY.IS: +2.65% / +3.05% / -2.76% | ENJSA.IS: -0.89% / +0.61% / -1.31%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-16.08200296859165</v>
+        <v>-16.08264952961187</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2128,7 +2140,7 @@
         <v>192.1</v>
       </c>
       <c r="O21" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2148,13 +2160,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>40.568</v>
+        <v>40.567</v>
       </c>
       <c r="V21" t="n">
         <v>11.417</v>
       </c>
       <c r="W21" t="n">
-        <v>-29.607</v>
+        <v>-29.608</v>
       </c>
     </row>
     <row r="22">
@@ -2198,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -0.90% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.84% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.453685130743446</v>
+        <v>-5.782822360791307</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2231,19 +2243,19 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>17.819</v>
+        <v>18.105</v>
       </c>
       <c r="T22" t="n">
-        <v>17.819</v>
+        <v>18.105</v>
       </c>
       <c r="U22" t="n">
-        <v>65.256</v>
+        <v>64.681</v>
       </c>
       <c r="V22" t="n">
-        <v>29.373</v>
+        <v>28.923</v>
       </c>
       <c r="W22" t="n">
-        <v>-35.832</v>
+        <v>-36.407</v>
       </c>
     </row>
     <row r="23">
@@ -2403,7 +2415,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2413,7 +2425,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2428,42 +2440,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KUYAS.IS, TRALT.IS</t>
+          <t>TRALT.IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>KUYAS.IS: 2026-09-03 | TRALT.IS: 2026-09-02</t>
+          <t>TRALT.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>23.02092795860866</v>
+        <v>25.65141339163128</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>KUYAS.IS: -0.73% / +0.00% / -0.78% | TRALT.IS: +0.38% / +2.88% / -2.03%</t>
+          <t>TRALT.IS: +4.05% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>12.86015270141232</v>
+        <v>-5.044425134583063</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.055214696096021</v>
+        <v>11.96494399083883</v>
       </c>
       <c r="L25" t="n">
-        <v>4.543450519200398</v>
+        <v>9.344627019167174</v>
       </c>
       <c r="M25" t="n">
-        <v>72.22222222222221</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N25" t="n">
-        <v>175.3</v>
+        <v>58.9</v>
       </c>
       <c r="O25" t="n">
-        <v>48.9</v>
+        <v>51.3</v>
       </c>
       <c r="P25" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2471,28 +2483,28 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>10.072</v>
+        <v>12.101</v>
       </c>
       <c r="T25" t="n">
-        <v>10.072</v>
+        <v>12.101</v>
       </c>
       <c r="U25" t="n">
-        <v>16.182</v>
+        <v>30.632</v>
       </c>
       <c r="V25" t="n">
-        <v>8.026</v>
+        <v>36.086</v>
       </c>
       <c r="W25" t="n">
-        <v>-9.206</v>
+        <v>-7.147</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2502,7 +2514,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2517,42 +2529,42 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
+          <t>KUYAS.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
+          <t>KUYAS.IS: 2026-09-03 | TRALT.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>13.58351811074014</v>
+        <v>23.02092795860866</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +10.01% / +20.94% / 0.00% | RALYH.IS: +22.09% / +35.10% / -0.91% | VAKBN.IS: -0.90% / +2.23% / -1.88%</t>
+          <t>KUYAS.IS: +0.05% / +0.50% / -1.07% | TRALT.IS: +4.05% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-10.39434387728287</v>
+        <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>9.53861823686324</v>
+        <v>-3.200831843318375</v>
       </c>
       <c r="L26" t="n">
-        <v>34.56349599547857</v>
+        <v>4.543450519200398</v>
       </c>
       <c r="M26" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>69.8</v>
+        <v>175.3</v>
       </c>
       <c r="O26" t="n">
-        <v>44</v>
+        <v>49.2</v>
       </c>
       <c r="P26" t="n">
-        <v>6.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2560,22 +2572,22 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>23.777</v>
+        <v>10.072</v>
       </c>
       <c r="T26" t="n">
-        <v>23.777</v>
+        <v>10.072</v>
       </c>
       <c r="U26" t="n">
-        <v>44.877</v>
+        <v>17.217</v>
       </c>
       <c r="V26" t="n">
-        <v>38.816</v>
+        <v>8.988</v>
       </c>
       <c r="W26" t="n">
-        <v>-15.161</v>
+        <v>-8.170999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -2591,7 +2603,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2604,55 +2616,67 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
+        </is>
+      </c>
       <c r="H27" t="n">
-        <v>7.610984631351814</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>13.58351811074014</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: +11.84% / +20.94% / 0.00% | RALYH.IS: +28.34% / +35.10% / -0.91% | VAKBN.IS: -0.84% / +2.23% / -1.88%</t>
+        </is>
+      </c>
       <c r="J27" t="n">
-        <v>-16.01405991857144</v>
+        <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>9.964713536822334</v>
+        <v>12.08394181459536</v>
       </c>
       <c r="L27" t="n">
-        <v>19.17000314054332</v>
+        <v>34.56349599547857</v>
       </c>
       <c r="M27" t="n">
-        <v>88.88888888888889</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N27" t="n">
-        <v>59.9</v>
+        <v>69.8</v>
       </c>
       <c r="O27" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S27" t="n">
-        <v>27.346</v>
+        <v>23.777</v>
       </c>
       <c r="T27" t="n">
-        <v>27.346</v>
+        <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>-5.223</v>
+        <v>48.243</v>
       </c>
       <c r="V27" t="n">
-        <v>7.691</v>
+        <v>42.042</v>
       </c>
       <c r="W27" t="n">
-        <v>-23.852</v>
+        <v>-11.795</v>
       </c>
     </row>
   </sheetData>
@@ -2852,12 +2876,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ALARK.IS, ENERY.IS</t>
+          <t>ENERY.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-04</t>
+          <t>ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2865,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6810570016952733</v>
+        <v>0.06244681108633632</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2895,7 +2919,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>18.106</v>
@@ -2904,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>256.361</v>
+        <v>254.172</v>
       </c>
       <c r="V3" t="n">
-        <v>102.819</v>
+        <v>101.573</v>
       </c>
       <c r="W3" t="n">
-        <v>-37.09</v>
+        <v>-39.28</v>
       </c>
     </row>
     <row r="4">
@@ -2944,7 +2968,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2952,14 +2976,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +0.84% / +2.47% / -2.77% | ENJSA.IS: +3.61% / +4.63% / -0.09% | SOKM.IS: -0.54% / +0.69% / -0.69%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.65% / +3.04% / -2.77% | ENJSA.IS: +3.07% / +4.63% / -0.09% | SOKM.IS: -1.31% / +0.69% / -1.89%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.74407057356332</v>
+        <v>-10.916099745662</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2968,10 +2992,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>118.8</v>
+        <v>119.3</v>
       </c>
       <c r="O4" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
       <c r="P4" t="n">
         <v>3.8</v>
@@ -2985,19 +3009,19 @@
         <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>25.507</v>
+        <v>25.65</v>
       </c>
       <c r="T4" t="n">
-        <v>25.507</v>
+        <v>25.65</v>
       </c>
       <c r="U4" t="n">
-        <v>56.023</v>
+        <v>55.722</v>
       </c>
       <c r="V4" t="n">
-        <v>20.087</v>
+        <v>19.855</v>
       </c>
       <c r="W4" t="n">
-        <v>-53.423</v>
+        <v>-53.723</v>
       </c>
     </row>
     <row r="5">
@@ -3026,12 +3050,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ALARK.IS, ENERY.IS</t>
+          <t>ENERY.IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-04</t>
+          <t>ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3039,14 +3063,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.660901610950182</v>
+        <v>0.04241526022217279</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3069,7 +3093,7 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>21.096</v>
@@ -3078,13 +3102,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>253.618</v>
+        <v>251.445</v>
       </c>
       <c r="V5" t="n">
-        <v>84.7</v>
+        <v>83.565</v>
       </c>
       <c r="W5" t="n">
-        <v>-36.76</v>
+        <v>-38.932</v>
       </c>
     </row>
     <row r="6">
@@ -3126,14 +3150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.18% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | ENERY.IS: +0.84% / +2.47% / -2.77% | SOKM.IS: -0.54% / +0.69% / -0.69% | TKFEN.IS: +8.53% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | CANTE.IS: +7.02% / +15.84% / -2.80% | ENERY.IS: +2.65% / +3.04% / -2.77% | SOKM.IS: -1.31% / +0.69% / -1.89% | TKFEN.IS: +8.47% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-11.15816275529833</v>
+        <v>-10.72949298628736</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3159,19 +3183,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>26.791</v>
+        <v>26.438</v>
       </c>
       <c r="T6" t="n">
-        <v>26.791</v>
+        <v>26.438</v>
       </c>
       <c r="U6" t="n">
-        <v>20.886</v>
+        <v>21.47</v>
       </c>
       <c r="V6" t="n">
-        <v>10.454</v>
+        <v>10.987</v>
       </c>
       <c r="W6" t="n">
-        <v>-44.238</v>
+        <v>-43.655</v>
       </c>
     </row>
     <row r="7">
@@ -3205,7 +3229,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3213,14 +3237,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +0.84% / +2.47% / -2.77% | ENJSA.IS: +3.61% / +4.63% / -0.09% | SOKM.IS: -0.54% / +0.69% / -0.69%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.65% / +3.04% / -2.77% | ENJSA.IS: +3.07% / +4.63% / -0.09% | SOKM.IS: -1.31% / +0.69% / -1.89%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.74407057356332</v>
+        <v>-10.916099745662</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3229,10 +3253,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>118.8</v>
+        <v>119.3</v>
       </c>
       <c r="O7" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
       <c r="P7" t="n">
         <v>3.8</v>
@@ -3246,19 +3270,19 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>25.507</v>
+        <v>25.65</v>
       </c>
       <c r="T7" t="n">
-        <v>25.507</v>
+        <v>25.65</v>
       </c>
       <c r="U7" t="n">
-        <v>56.023</v>
+        <v>55.722</v>
       </c>
       <c r="V7" t="n">
-        <v>20.087</v>
+        <v>19.855</v>
       </c>
       <c r="W7" t="n">
-        <v>-53.423</v>
+        <v>-53.723</v>
       </c>
     </row>
     <row r="8">
@@ -3300,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.18% / +20.03% / -1.13% | CANTE.IS: -0.02% / +3.71% / -2.30% | ENERY.IS: +0.84% / +2.47% / -2.77%</t>
+          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +2.65% / +3.04% / -2.77%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.366529880386737</v>
+        <v>-2.608573583050855</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3339,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>21.048</v>
+        <v>21.998</v>
       </c>
       <c r="V8" t="n">
-        <v>1.282</v>
+        <v>2.076</v>
       </c>
       <c r="W8" t="n">
-        <v>-32.11</v>
+        <v>-31.16</v>
       </c>
     </row>
     <row r="9">
@@ -3454,7 +3478,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-02</t>
+          <t>ALARK.IS: 2026-09-04 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -3462,14 +3486,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | CANTE.IS: -0.02% / +3.71% / -2.30% | ENERY.IS: +0.84% / +2.47% / -2.77%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +2.65% / +3.04% / -2.77%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.833707452921619</v>
+        <v>-2.901381784827162</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3478,10 +3502,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>113.8</v>
+        <v>114.3</v>
       </c>
       <c r="O10" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="P10" t="n">
         <v>2.4</v>
@@ -3501,13 +3525,13 @@
         <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>11.142</v>
+        <v>11.065</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.252</v>
+        <v>-2.32</v>
       </c>
       <c r="W10" t="n">
-        <v>-27.01</v>
+        <v>-27.088</v>
       </c>
     </row>
     <row r="11">
@@ -3541,7 +3565,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -3549,14 +3573,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +0.84% / +2.47% / -2.77% | ENJSA.IS: +3.61% / +4.63% / -0.09% | SOKM.IS: -0.54% / +0.69% / -0.69%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.65% / +3.04% / -2.77% | ENJSA.IS: +3.07% / +4.63% / -0.09% | SOKM.IS: -1.31% / +0.69% / -1.89%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.66071909321087</v>
+        <v>-10.83290891442549</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3565,10 +3589,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>179.4</v>
+        <v>179.9</v>
       </c>
       <c r="O11" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
@@ -3582,19 +3606,19 @@
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>24.188</v>
+        <v>24.334</v>
       </c>
       <c r="T11" t="n">
-        <v>24.188</v>
+        <v>24.334</v>
       </c>
       <c r="U11" t="n">
-        <v>32.209</v>
+        <v>31.955</v>
       </c>
       <c r="V11" t="n">
-        <v>7.133</v>
+        <v>6.926</v>
       </c>
       <c r="W11" t="n">
-        <v>-42.182</v>
+        <v>-42.437</v>
       </c>
     </row>
     <row r="12">
@@ -3636,14 +3660,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.18% / +20.03% / -1.13% | TKFEN.IS: +8.53% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | TKFEN.IS: +8.47% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>6.811241450675753</v>
+        <v>7.644888888073709</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3675,13 +3699,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>38.887</v>
+        <v>39.971</v>
       </c>
       <c r="V12" t="n">
-        <v>48.831</v>
+        <v>49.993</v>
       </c>
       <c r="W12" t="n">
-        <v>-21.401</v>
+        <v>-20.317</v>
       </c>
     </row>
     <row r="13">
@@ -3723,14 +3747,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.34% / +1.66% / -1.90%</t>
+          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.67% / +1.66% / -1.90%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K13" t="n">
-        <v>6.639608727219781</v>
+        <v>7.267248464575404</v>
       </c>
       <c r="L13" t="n">
         <v>19.61961325199098</v>
@@ -3742,7 +3766,7 @@
         <v>88.5</v>
       </c>
       <c r="O13" t="n">
-        <v>45.5</v>
+        <v>46.1</v>
       </c>
       <c r="P13" t="n">
         <v>2.2</v>
@@ -3762,13 +3786,13 @@
         <v>18.132</v>
       </c>
       <c r="U13" t="n">
-        <v>3.981</v>
+        <v>4.593</v>
       </c>
       <c r="V13" t="n">
-        <v>11.354</v>
+        <v>12.009</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.81</v>
+        <v>-7.198</v>
       </c>
     </row>
     <row r="14">
@@ -3998,12 +4022,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ALARK.IS, ENERY.IS</t>
+          <t>ENERY.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-04</t>
+          <t>ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -4011,14 +4035,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6810570016952733</v>
+        <v>0.06244681108633632</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4041,7 +4065,7 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>18.106</v>
@@ -4050,13 +4074,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>256.361</v>
+        <v>254.172</v>
       </c>
       <c r="V18" t="n">
-        <v>102.819</v>
+        <v>101.573</v>
       </c>
       <c r="W18" t="n">
-        <v>-37.09</v>
+        <v>-39.28</v>
       </c>
     </row>
     <row r="19">
@@ -4092,7 +4116,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -4100,14 +4124,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +0.84% / +2.47% / -2.77% | ENJSA.IS: +3.61% / +4.63% / -0.09% | SOKM.IS: -0.54% / +0.69% / -0.69%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.65% / +3.04% / -2.77% | ENJSA.IS: +3.07% / +4.63% / -0.09% | SOKM.IS: -1.31% / +0.69% / -1.89%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.74407057356332</v>
+        <v>-10.916099745662</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4116,10 +4140,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>118.8</v>
+        <v>119.3</v>
       </c>
       <c r="O19" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
       <c r="P19" t="n">
         <v>3.8</v>
@@ -4133,19 +4157,19 @@
         <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>25.507</v>
+        <v>25.65</v>
       </c>
       <c r="T19" t="n">
-        <v>25.507</v>
+        <v>25.65</v>
       </c>
       <c r="U19" t="n">
-        <v>56.023</v>
+        <v>55.722</v>
       </c>
       <c r="V19" t="n">
-        <v>20.087</v>
+        <v>19.855</v>
       </c>
       <c r="W19" t="n">
-        <v>-53.423</v>
+        <v>-53.723</v>
       </c>
     </row>
     <row r="20">
@@ -4176,12 +4200,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ALARK.IS, ENERY.IS</t>
+          <t>ENERY.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-04</t>
+          <t>ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -4189,14 +4213,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>0.660901610950182</v>
+        <v>0.04241526022217279</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4219,7 +4243,7 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>21.096</v>
@@ -4228,13 +4252,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>253.618</v>
+        <v>251.445</v>
       </c>
       <c r="V20" t="n">
-        <v>84.7</v>
+        <v>83.565</v>
       </c>
       <c r="W20" t="n">
-        <v>-36.76</v>
+        <v>-38.932</v>
       </c>
     </row>
     <row r="21">
@@ -4270,7 +4294,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -4278,14 +4302,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +0.84% / +2.47% / -2.77% | ENJSA.IS: +3.61% / +4.63% / -0.09% | SOKM.IS: -0.54% / +0.69% / -0.69%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.65% / +3.04% / -2.77% | ENJSA.IS: +3.07% / +4.63% / -0.09% | SOKM.IS: -1.31% / +0.69% / -1.89%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.66071909321087</v>
+        <v>-10.83290891442549</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4294,10 +4318,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>179.4</v>
+        <v>179.9</v>
       </c>
       <c r="O21" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
@@ -4311,19 +4335,19 @@
         <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>24.188</v>
+        <v>24.334</v>
       </c>
       <c r="T21" t="n">
-        <v>24.188</v>
+        <v>24.334</v>
       </c>
       <c r="U21" t="n">
-        <v>32.209</v>
+        <v>31.955</v>
       </c>
       <c r="V21" t="n">
-        <v>7.133</v>
+        <v>6.926</v>
       </c>
       <c r="W21" t="n">
-        <v>-42.182</v>
+        <v>-42.437</v>
       </c>
     </row>
     <row r="22">
@@ -4367,14 +4391,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.18% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | ENERY.IS: +0.84% / +2.47% / -2.77% | SOKM.IS: -0.54% / +0.69% / -0.69% | TKFEN.IS: +8.53% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | CANTE.IS: +7.02% / +15.84% / -2.80% | ENERY.IS: +2.65% / +3.04% / -2.77% | SOKM.IS: -1.31% / +0.69% / -1.89% | TKFEN.IS: +8.47% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.15816275529833</v>
+        <v>-10.72949298628736</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4400,19 +4424,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>26.791</v>
+        <v>26.438</v>
       </c>
       <c r="T22" t="n">
-        <v>26.791</v>
+        <v>26.438</v>
       </c>
       <c r="U22" t="n">
-        <v>20.886</v>
+        <v>21.47</v>
       </c>
       <c r="V22" t="n">
-        <v>10.454</v>
+        <v>10.987</v>
       </c>
       <c r="W22" t="n">
-        <v>-44.238</v>
+        <v>-43.655</v>
       </c>
     </row>
     <row r="23">
@@ -4456,14 +4480,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.18% / +20.03% / -1.13% | CANTE.IS: -0.02% / +3.71% / -2.30% | ENERY.IS: +0.84% / +2.47% / -2.77%</t>
+          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +2.65% / +3.04% / -2.77%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.366529880386737</v>
+        <v>-2.608573583050855</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4495,13 +4519,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>21.048</v>
+        <v>21.998</v>
       </c>
       <c r="V23" t="n">
-        <v>1.282</v>
+        <v>2.076</v>
       </c>
       <c r="W23" t="n">
-        <v>-32.11</v>
+        <v>-31.16</v>
       </c>
     </row>
     <row r="24">
@@ -4537,7 +4561,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-02</t>
+          <t>ALARK.IS: 2026-09-04 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -4545,14 +4569,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.95% / +4.80% / -3.23% | CANTE.IS: -0.02% / +3.71% / -2.30% | ENERY.IS: +0.84% / +2.47% / -2.77%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +2.65% / +3.04% / -2.77%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.833707452921619</v>
+        <v>-2.901381784827162</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4561,10 +4585,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>113.8</v>
+        <v>114.3</v>
       </c>
       <c r="O24" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="P24" t="n">
         <v>2.4</v>
@@ -4584,13 +4608,13 @@
         <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>11.142</v>
+        <v>11.065</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.252</v>
+        <v>-2.32</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.01</v>
+        <v>-27.088</v>
       </c>
     </row>
     <row r="25">
@@ -4788,14 +4812,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +9.18% / +20.03% / -1.13% | TKFEN.IS: +8.53% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | TKFEN.IS: +8.47% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>6.811241450675753</v>
+        <v>7.644888888073709</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4827,13 +4851,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>38.887</v>
+        <v>39.971</v>
       </c>
       <c r="V27" t="n">
-        <v>48.831</v>
+        <v>49.993</v>
       </c>
       <c r="W27" t="n">
-        <v>-21.401</v>
+        <v>-20.317</v>
       </c>
     </row>
     <row r="28">
@@ -4877,14 +4901,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.34% / +1.66% / -1.90%</t>
+          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.67% / +1.66% / -1.90%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>6.639608727219781</v>
+        <v>7.267248464575404</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4896,7 +4920,7 @@
         <v>88.5</v>
       </c>
       <c r="O28" t="n">
-        <v>45.5</v>
+        <v>46.1</v>
       </c>
       <c r="P28" t="n">
         <v>2.2</v>
@@ -4916,13 +4940,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>3.981</v>
+        <v>4.593</v>
       </c>
       <c r="V28" t="n">
-        <v>11.354</v>
+        <v>12.009</v>
       </c>
       <c r="W28" t="n">
-        <v>-7.81</v>
+        <v>-7.198</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.84% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.78% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-16.20244919070133</v>
+        <v>-16.17766019108726</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -789,19 +789,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>22.293</v>
+        <v>22.27</v>
       </c>
       <c r="T3" t="n">
-        <v>22.293</v>
+        <v>22.27</v>
       </c>
       <c r="U3" t="n">
-        <v>58.818</v>
+        <v>58.865</v>
       </c>
       <c r="V3" t="n">
-        <v>13.845</v>
+        <v>13.879</v>
       </c>
       <c r="W3" t="n">
-        <v>-45.563</v>
+        <v>-45.516</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.84% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.78% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-16.20244919070133</v>
+        <v>-16.17766019108726</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1026,19 +1026,19 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>22.293</v>
+        <v>22.27</v>
       </c>
       <c r="T6" t="n">
-        <v>22.293</v>
+        <v>22.27</v>
       </c>
       <c r="U6" t="n">
-        <v>58.818</v>
+        <v>58.865</v>
       </c>
       <c r="V6" t="n">
-        <v>13.845</v>
+        <v>13.879</v>
       </c>
       <c r="W6" t="n">
-        <v>-45.563</v>
+        <v>-45.516</v>
       </c>
     </row>
     <row r="7">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.84% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.78% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.782822360791307</v>
+        <v>-5.754951026157062</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>18.105</v>
+        <v>18.081</v>
       </c>
       <c r="T7" t="n">
-        <v>18.105</v>
+        <v>18.081</v>
       </c>
       <c r="U7" t="n">
-        <v>64.681</v>
+        <v>64.729</v>
       </c>
       <c r="V7" t="n">
-        <v>28.923</v>
+        <v>28.961</v>
       </c>
       <c r="W7" t="n">
-        <v>-36.407</v>
+        <v>-36.359</v>
       </c>
     </row>
     <row r="8">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.56% / +1.61% / -0.81% | ENERY.IS: +2.65% / +3.05% / -2.76% | ENJSA.IS: -0.89% / +0.61% / -1.31%</t>
+          <t>ALARK.IS: -0.83% / +1.61% / -1.61% | ENERY.IS: +4.26% / +4.86% / -2.76% | ENJSA.IS: -1.07% / +0.61% / -1.66%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-16.08264952961187</v>
+        <v>-15.74339255158701</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>40.567</v>
+        <v>41.136</v>
       </c>
       <c r="V8" t="n">
-        <v>11.417</v>
+        <v>11.867</v>
       </c>
       <c r="W8" t="n">
-        <v>-29.608</v>
+        <v>-29.039</v>
       </c>
     </row>
     <row r="9">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.84% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.78% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-16.20244919070133</v>
+        <v>-16.17766019108726</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1287,19 +1287,19 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>22.293</v>
+        <v>22.27</v>
       </c>
       <c r="T9" t="n">
-        <v>22.293</v>
+        <v>22.27</v>
       </c>
       <c r="U9" t="n">
-        <v>58.818</v>
+        <v>58.865</v>
       </c>
       <c r="V9" t="n">
-        <v>13.845</v>
+        <v>13.879</v>
       </c>
       <c r="W9" t="n">
-        <v>-45.563</v>
+        <v>-45.516</v>
       </c>
     </row>
     <row r="10">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>KUYAS.IS: +0.05% / +0.50% / -1.07% | TRALT.IS: +4.05% / +4.87% / -2.03%</t>
+          <t>KUYAS.IS: +0.12% / +0.50% / -1.07% | TRALT.IS: +1.57% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.200831843318375</v>
+        <v>-3.662413152260879</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>17.217</v>
+        <v>16.658</v>
       </c>
       <c r="V10" t="n">
-        <v>8.988</v>
+        <v>8.468</v>
       </c>
       <c r="W10" t="n">
-        <v>-8.170999999999999</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="11">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.84% / +20.94% / 0.00% | RALYH.IS: +28.34% / +35.10% / -0.91% | VAKBN.IS: -0.84% / +2.23% / -1.88%</t>
+          <t>BRSAN.IS: +11.68% / +20.94% / 0.00% | RALYH.IS: +29.54% / +35.10% / -0.91% | VAKBN.IS: -0.78% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K12" t="n">
-        <v>12.08394181459536</v>
+        <v>12.42653216346226</v>
       </c>
       <c r="L12" t="n">
         <v>34.56349599547857</v>
@@ -1542,13 +1542,13 @@
         <v>23.777</v>
       </c>
       <c r="U12" t="n">
-        <v>48.243</v>
+        <v>48.696</v>
       </c>
       <c r="V12" t="n">
-        <v>42.042</v>
+        <v>42.476</v>
       </c>
       <c r="W12" t="n">
-        <v>-11.795</v>
+        <v>-11.342</v>
       </c>
     </row>
     <row r="13">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TRALT.IS: +4.05% / +4.87% / -2.03%</t>
+          <t>TRALT.IS: +1.57% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-5.044425134583063</v>
       </c>
       <c r="K13" t="n">
-        <v>11.96494399083883</v>
+        <v>10.60572015138295</v>
       </c>
       <c r="L13" t="n">
         <v>9.344627019167174</v>
@@ -1629,13 +1629,13 @@
         <v>12.101</v>
       </c>
       <c r="U13" t="n">
-        <v>30.632</v>
+        <v>29.046</v>
       </c>
       <c r="V13" t="n">
-        <v>36.086</v>
+        <v>34.434</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.147</v>
+        <v>-8.733000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1878,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.84% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.78% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-16.20244919070133</v>
+        <v>-16.17766019108726</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1911,19 +1911,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>22.293</v>
+        <v>22.27</v>
       </c>
       <c r="T18" t="n">
-        <v>22.293</v>
+        <v>22.27</v>
       </c>
       <c r="U18" t="n">
-        <v>58.818</v>
+        <v>58.865</v>
       </c>
       <c r="V18" t="n">
-        <v>13.845</v>
+        <v>13.879</v>
       </c>
       <c r="W18" t="n">
-        <v>-45.563</v>
+        <v>-45.516</v>
       </c>
     </row>
     <row r="19">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.56% / +1.61% / -0.81% | ENERY.IS: +2.65% / +3.05% / -2.76% | ENJSA.IS: -0.89% / +0.61% / -1.31%</t>
+          <t>ALARK.IS: -0.83% / +1.61% / -1.61% | ENERY.IS: +4.26% / +4.86% / -2.76% | ENJSA.IS: -1.07% / +0.61% / -1.66%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-16.08264952961187</v>
+        <v>-15.74339255158701</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2160,13 +2160,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>40.567</v>
+        <v>41.136</v>
       </c>
       <c r="V21" t="n">
-        <v>11.417</v>
+        <v>11.867</v>
       </c>
       <c r="W21" t="n">
-        <v>-29.608</v>
+        <v>-29.039</v>
       </c>
     </row>
     <row r="22">
@@ -2210,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.84% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.78% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.782822360791307</v>
+        <v>-5.754951026157062</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2243,19 +2243,19 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>18.105</v>
+        <v>18.081</v>
       </c>
       <c r="T22" t="n">
-        <v>18.105</v>
+        <v>18.081</v>
       </c>
       <c r="U22" t="n">
-        <v>64.681</v>
+        <v>64.729</v>
       </c>
       <c r="V22" t="n">
-        <v>28.923</v>
+        <v>28.961</v>
       </c>
       <c r="W22" t="n">
-        <v>-36.407</v>
+        <v>-36.359</v>
       </c>
     </row>
     <row r="23">
@@ -2453,14 +2453,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TRALT.IS: +4.05% / +4.87% / -2.03%</t>
+          <t>TRALT.IS: +1.57% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-5.044425134583063</v>
       </c>
       <c r="K25" t="n">
-        <v>11.96494399083883</v>
+        <v>10.60572015138295</v>
       </c>
       <c r="L25" t="n">
         <v>9.344627019167174</v>
@@ -2492,13 +2492,13 @@
         <v>12.101</v>
       </c>
       <c r="U25" t="n">
-        <v>30.632</v>
+        <v>29.046</v>
       </c>
       <c r="V25" t="n">
-        <v>36.086</v>
+        <v>34.434</v>
       </c>
       <c r="W25" t="n">
-        <v>-7.147</v>
+        <v>-8.733000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2542,14 +2542,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>KUYAS.IS: +0.05% / +0.50% / -1.07% | TRALT.IS: +4.05% / +4.87% / -2.03%</t>
+          <t>KUYAS.IS: +0.12% / +0.50% / -1.07% | TRALT.IS: +1.57% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.200831843318375</v>
+        <v>-3.662413152260879</v>
       </c>
       <c r="L26" t="n">
         <v>4.543450519200398</v>
@@ -2581,13 +2581,13 @@
         <v>10.072</v>
       </c>
       <c r="U26" t="n">
-        <v>17.217</v>
+        <v>16.658</v>
       </c>
       <c r="V26" t="n">
-        <v>8.988</v>
+        <v>8.468</v>
       </c>
       <c r="W26" t="n">
-        <v>-8.170999999999999</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="27">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.84% / +20.94% / 0.00% | RALYH.IS: +28.34% / +35.10% / -0.91% | VAKBN.IS: -0.84% / +2.23% / -1.88%</t>
+          <t>BRSAN.IS: +11.68% / +20.94% / 0.00% | RALYH.IS: +29.54% / +35.10% / -0.91% | VAKBN.IS: -0.78% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>12.08394181459536</v>
+        <v>12.42653216346226</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2670,13 +2670,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>48.243</v>
+        <v>48.696</v>
       </c>
       <c r="V27" t="n">
-        <v>42.042</v>
+        <v>42.476</v>
       </c>
       <c r="W27" t="n">
-        <v>-11.795</v>
+        <v>-11.342</v>
       </c>
     </row>
   </sheetData>
@@ -2711,7 +2711,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2896,7 +2896,7 @@
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06244681108633632</v>
+        <v>-0.06127370985247182</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2928,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>254.172</v>
+        <v>253.734</v>
       </c>
       <c r="V3" t="n">
-        <v>101.573</v>
+        <v>101.324</v>
       </c>
       <c r="W3" t="n">
-        <v>-39.28</v>
+        <v>-39.718</v>
       </c>
     </row>
     <row r="4">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2976,14 +2976,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.65% / +3.04% / -2.77% | ENJSA.IS: +3.07% / +4.63% / -0.09% | SOKM.IS: -1.31% / +0.69% / -1.89%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +4.26% / +4.85% / -2.77% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.66% / +0.69% / -1.98%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.916099745662</v>
+        <v>-10.77640259976103</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2992,10 +2992,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>119.3</v>
+        <v>119.8</v>
       </c>
       <c r="O4" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
       <c r="P4" t="n">
         <v>3.8</v>
@@ -3009,19 +3009,19 @@
         <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>25.65</v>
+        <v>25.534</v>
       </c>
       <c r="T4" t="n">
-        <v>25.65</v>
+        <v>25.534</v>
       </c>
       <c r="U4" t="n">
-        <v>55.722</v>
+        <v>55.967</v>
       </c>
       <c r="V4" t="n">
-        <v>19.855</v>
+        <v>20.043</v>
       </c>
       <c r="W4" t="n">
-        <v>-53.723</v>
+        <v>-53.479</v>
       </c>
     </row>
     <row r="5">
@@ -3070,7 +3070,7 @@
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04241526022217279</v>
+        <v>-0.08128049304420015</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3102,13 +3102,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>251.445</v>
+        <v>251.01</v>
       </c>
       <c r="V5" t="n">
-        <v>83.565</v>
+        <v>83.33799999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-38.932</v>
+        <v>-39.367</v>
       </c>
     </row>
     <row r="6">
@@ -3150,14 +3150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | CANTE.IS: +7.02% / +15.84% / -2.80% | ENERY.IS: +2.65% / +3.04% / -2.77% | SOKM.IS: -1.31% / +0.69% / -1.89% | TKFEN.IS: +8.47% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +10.84% / +20.03% / -1.13% | CANTE.IS: +7.02% / +15.84% / -2.80% | ENERY.IS: +4.26% / +4.85% / -2.77% | SOKM.IS: -1.66% / +0.69% / -1.98% | TKFEN.IS: +10.77% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.72949298628736</v>
+        <v>-10.07376133349631</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3183,19 +3183,19 @@
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>26.438</v>
+        <v>26.35</v>
       </c>
       <c r="T6" t="n">
-        <v>26.438</v>
+        <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>21.47</v>
+        <v>22.362</v>
       </c>
       <c r="V6" t="n">
-        <v>10.987</v>
+        <v>11.802</v>
       </c>
       <c r="W6" t="n">
-        <v>-43.655</v>
+        <v>-42.763</v>
       </c>
     </row>
     <row r="7">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3237,14 +3237,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.65% / +3.04% / -2.77% | ENJSA.IS: +3.07% / +4.63% / -0.09% | SOKM.IS: -1.31% / +0.69% / -1.89%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +4.26% / +4.85% / -2.77% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.66% / +0.69% / -1.98%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.916099745662</v>
+        <v>-10.77640259976103</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3253,10 +3253,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>119.3</v>
+        <v>119.8</v>
       </c>
       <c r="O7" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
       <c r="P7" t="n">
         <v>3.8</v>
@@ -3270,19 +3270,19 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>25.65</v>
+        <v>25.534</v>
       </c>
       <c r="T7" t="n">
-        <v>25.65</v>
+        <v>25.534</v>
       </c>
       <c r="U7" t="n">
-        <v>55.722</v>
+        <v>55.967</v>
       </c>
       <c r="V7" t="n">
-        <v>19.855</v>
+        <v>20.043</v>
       </c>
       <c r="W7" t="n">
-        <v>-53.723</v>
+        <v>-53.479</v>
       </c>
     </row>
     <row r="8">
@@ -3324,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +2.65% / +3.04% / -2.77%</t>
+          <t>BRSAN.IS: +10.84% / +20.03% / -1.13% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +4.26% / +4.85% / -2.77%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.608573583050855</v>
+        <v>-2.197681541041863</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3363,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>21.998</v>
+        <v>22.512</v>
       </c>
       <c r="V8" t="n">
-        <v>2.076</v>
+        <v>2.507</v>
       </c>
       <c r="W8" t="n">
-        <v>-31.16</v>
+        <v>-30.646</v>
       </c>
     </row>
     <row r="9">
@@ -3486,14 +3486,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +2.65% / +3.04% / -2.77%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +4.26% / +4.85% / -2.77%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.901381784827162</v>
+        <v>-2.525873042119764</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3525,13 +3525,13 @@
         <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>11.065</v>
+        <v>11.494</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.32</v>
+        <v>-1.943</v>
       </c>
       <c r="W10" t="n">
-        <v>-27.088</v>
+        <v>-26.658</v>
       </c>
     </row>
     <row r="11">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -3573,14 +3573,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.65% / +3.04% / -2.77% | ENJSA.IS: +3.07% / +4.63% / -0.09% | SOKM.IS: -1.31% / +0.69% / -1.89%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +4.26% / +4.85% / -2.77% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.66% / +0.69% / -1.98%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.83290891442549</v>
+        <v>-10.69308131260991</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3589,10 +3589,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>179.9</v>
+        <v>180.4</v>
       </c>
       <c r="O11" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
@@ -3606,19 +3606,19 @@
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>24.334</v>
+        <v>24.216</v>
       </c>
       <c r="T11" t="n">
-        <v>24.334</v>
+        <v>24.216</v>
       </c>
       <c r="U11" t="n">
-        <v>31.955</v>
+        <v>32.162</v>
       </c>
       <c r="V11" t="n">
-        <v>6.926</v>
+        <v>7.094</v>
       </c>
       <c r="W11" t="n">
-        <v>-42.437</v>
+        <v>-42.23</v>
       </c>
     </row>
     <row r="12">
@@ -3660,14 +3660,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | TKFEN.IS: +8.47% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +10.84% / +20.03% / -1.13% | TKFEN.IS: +10.77% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>7.644888888073709</v>
+        <v>8.737710215420446</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3699,13 +3699,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>39.971</v>
+        <v>41.392</v>
       </c>
       <c r="V12" t="n">
-        <v>49.993</v>
+        <v>51.516</v>
       </c>
       <c r="W12" t="n">
-        <v>-20.317</v>
+        <v>-18.896</v>
       </c>
     </row>
     <row r="13">
@@ -3747,14 +3747,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.67% / +1.66% / -1.90%</t>
+          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.02% / +1.66% / -1.90%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K13" t="n">
-        <v>7.267248464575404</v>
+        <v>7.353085651398006</v>
       </c>
       <c r="L13" t="n">
         <v>19.61961325199098</v>
@@ -3786,13 +3786,13 @@
         <v>18.132</v>
       </c>
       <c r="U13" t="n">
-        <v>4.593</v>
+        <v>4.677</v>
       </c>
       <c r="V13" t="n">
-        <v>12.009</v>
+        <v>12.099</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.198</v>
+        <v>-7.115</v>
       </c>
     </row>
     <row r="14">
@@ -4042,7 +4042,7 @@
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>0.06244681108633632</v>
+        <v>-0.06127370985247182</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4074,13 +4074,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>254.172</v>
+        <v>253.734</v>
       </c>
       <c r="V18" t="n">
-        <v>101.573</v>
+        <v>101.324</v>
       </c>
       <c r="W18" t="n">
-        <v>-39.28</v>
+        <v>-39.718</v>
       </c>
     </row>
     <row r="19">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -4124,14 +4124,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.65% / +3.04% / -2.77% | ENJSA.IS: +3.07% / +4.63% / -0.09% | SOKM.IS: -1.31% / +0.69% / -1.89%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +4.26% / +4.85% / -2.77% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.66% / +0.69% / -1.98%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.916099745662</v>
+        <v>-10.77640259976103</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4140,10 +4140,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>119.3</v>
+        <v>119.8</v>
       </c>
       <c r="O19" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
       <c r="P19" t="n">
         <v>3.8</v>
@@ -4157,19 +4157,19 @@
         <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>25.65</v>
+        <v>25.534</v>
       </c>
       <c r="T19" t="n">
-        <v>25.65</v>
+        <v>25.534</v>
       </c>
       <c r="U19" t="n">
-        <v>55.722</v>
+        <v>55.967</v>
       </c>
       <c r="V19" t="n">
-        <v>19.855</v>
+        <v>20.043</v>
       </c>
       <c r="W19" t="n">
-        <v>-53.723</v>
+        <v>-53.479</v>
       </c>
     </row>
     <row r="20">
@@ -4220,7 +4220,7 @@
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>0.04241526022217279</v>
+        <v>-0.08128049304420015</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4252,13 +4252,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>251.445</v>
+        <v>251.01</v>
       </c>
       <c r="V20" t="n">
-        <v>83.565</v>
+        <v>83.33799999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>-38.932</v>
+        <v>-39.367</v>
       </c>
     </row>
     <row r="21">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -4302,14 +4302,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +2.65% / +3.04% / -2.77% | ENJSA.IS: +3.07% / +4.63% / -0.09% | SOKM.IS: -1.31% / +0.69% / -1.89%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +4.26% / +4.85% / -2.77% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.66% / +0.69% / -1.98%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.83290891442549</v>
+        <v>-10.69308131260991</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4318,10 +4318,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>179.9</v>
+        <v>180.4</v>
       </c>
       <c r="O21" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
@@ -4335,19 +4335,19 @@
         <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>24.334</v>
+        <v>24.216</v>
       </c>
       <c r="T21" t="n">
-        <v>24.334</v>
+        <v>24.216</v>
       </c>
       <c r="U21" t="n">
-        <v>31.955</v>
+        <v>32.162</v>
       </c>
       <c r="V21" t="n">
-        <v>6.926</v>
+        <v>7.094</v>
       </c>
       <c r="W21" t="n">
-        <v>-42.437</v>
+        <v>-42.23</v>
       </c>
     </row>
     <row r="22">
@@ -4391,14 +4391,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | CANTE.IS: +7.02% / +15.84% / -2.80% | ENERY.IS: +2.65% / +3.04% / -2.77% | SOKM.IS: -1.31% / +0.69% / -1.89% | TKFEN.IS: +8.47% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +10.84% / +20.03% / -1.13% | CANTE.IS: +7.02% / +15.84% / -2.80% | ENERY.IS: +4.26% / +4.85% / -2.77% | SOKM.IS: -1.66% / +0.69% / -1.98% | TKFEN.IS: +10.77% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.72949298628736</v>
+        <v>-10.07376133349631</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4424,19 +4424,19 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>26.438</v>
+        <v>26.35</v>
       </c>
       <c r="T22" t="n">
-        <v>26.438</v>
+        <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>21.47</v>
+        <v>22.362</v>
       </c>
       <c r="V22" t="n">
-        <v>10.987</v>
+        <v>11.802</v>
       </c>
       <c r="W22" t="n">
-        <v>-43.655</v>
+        <v>-42.763</v>
       </c>
     </row>
     <row r="23">
@@ -4480,14 +4480,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +2.65% / +3.04% / -2.77%</t>
+          <t>BRSAN.IS: +10.84% / +20.03% / -1.13% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +4.26% / +4.85% / -2.77%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.608573583050855</v>
+        <v>-2.197681541041863</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4519,13 +4519,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>21.998</v>
+        <v>22.512</v>
       </c>
       <c r="V23" t="n">
-        <v>2.076</v>
+        <v>2.507</v>
       </c>
       <c r="W23" t="n">
-        <v>-31.16</v>
+        <v>-30.646</v>
       </c>
     </row>
     <row r="24">
@@ -4569,14 +4569,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +2.65% / +3.04% / -2.77%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +4.26% / +4.85% / -2.77%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.901381784827162</v>
+        <v>-2.525873042119764</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4608,13 +4608,13 @@
         <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>11.065</v>
+        <v>11.494</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.32</v>
+        <v>-1.943</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.088</v>
+        <v>-26.658</v>
       </c>
     </row>
     <row r="25">
@@ -4812,14 +4812,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | TKFEN.IS: +8.47% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +10.84% / +20.03% / -1.13% | TKFEN.IS: +10.77% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>7.644888888073709</v>
+        <v>8.737710215420446</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4851,13 +4851,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>39.971</v>
+        <v>41.392</v>
       </c>
       <c r="V27" t="n">
-        <v>49.993</v>
+        <v>51.516</v>
       </c>
       <c r="W27" t="n">
-        <v>-20.317</v>
+        <v>-18.896</v>
       </c>
     </row>
     <row r="28">
@@ -4901,14 +4901,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.67% / +1.66% / -1.90%</t>
+          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.02% / +1.66% / -1.90%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>7.267248464575404</v>
+        <v>7.353085651398006</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4940,13 +4940,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>4.593</v>
+        <v>4.677</v>
       </c>
       <c r="V28" t="n">
-        <v>12.009</v>
+        <v>12.099</v>
       </c>
       <c r="W28" t="n">
-        <v>-7.198</v>
+        <v>-7.115</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.78% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.25% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-16.17766019108726</v>
+        <v>-15.95456382999942</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -789,19 +789,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>22.27</v>
+        <v>22.063</v>
       </c>
       <c r="T3" t="n">
-        <v>22.27</v>
+        <v>22.063</v>
       </c>
       <c r="U3" t="n">
-        <v>58.865</v>
+        <v>59.288</v>
       </c>
       <c r="V3" t="n">
-        <v>13.879</v>
+        <v>14.182</v>
       </c>
       <c r="W3" t="n">
-        <v>-45.516</v>
+        <v>-45.093</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.78% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.25% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-16.17766019108726</v>
+        <v>-15.95456382999942</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1026,19 +1026,19 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>22.27</v>
+        <v>22.063</v>
       </c>
       <c r="T6" t="n">
-        <v>22.27</v>
+        <v>22.063</v>
       </c>
       <c r="U6" t="n">
-        <v>58.865</v>
+        <v>59.288</v>
       </c>
       <c r="V6" t="n">
-        <v>13.879</v>
+        <v>14.182</v>
       </c>
       <c r="W6" t="n">
-        <v>-45.516</v>
+        <v>-45.093</v>
       </c>
     </row>
     <row r="7">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.78% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.25% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.754951026157062</v>
+        <v>-5.504114226271217</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>18.081</v>
+        <v>17.863</v>
       </c>
       <c r="T7" t="n">
-        <v>18.081</v>
+        <v>17.863</v>
       </c>
       <c r="U7" t="n">
-        <v>64.729</v>
+        <v>65.16800000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>28.961</v>
+        <v>29.304</v>
       </c>
       <c r="W7" t="n">
-        <v>-36.359</v>
+        <v>-35.92</v>
       </c>
     </row>
     <row r="8">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-09-03 | ENERY.IS: 2026-09-04 | ENJSA.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.83% / +1.61% / -1.61% | ENERY.IS: +4.26% / +4.86% / -2.76% | ENJSA.IS: -1.07% / +0.61% / -1.66%</t>
+          <t>ALARK.IS: -0.56% / +1.61% / -1.61% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -1.24% / +0.61% / -1.66%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-15.74339255158701</v>
+        <v>-15.48300585045406</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1183,10 +1183,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>192.1</v>
+        <v>192.6</v>
       </c>
       <c r="O8" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>41.136</v>
+        <v>41.572</v>
       </c>
       <c r="V8" t="n">
-        <v>11.867</v>
+        <v>12.213</v>
       </c>
       <c r="W8" t="n">
-        <v>-29.039</v>
+        <v>-28.603</v>
       </c>
     </row>
     <row r="9">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.78% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.25% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-16.17766019108726</v>
+        <v>-15.95456382999942</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1287,19 +1287,19 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>22.27</v>
+        <v>22.063</v>
       </c>
       <c r="T9" t="n">
-        <v>22.27</v>
+        <v>22.063</v>
       </c>
       <c r="U9" t="n">
-        <v>58.865</v>
+        <v>59.288</v>
       </c>
       <c r="V9" t="n">
-        <v>13.879</v>
+        <v>14.182</v>
       </c>
       <c r="W9" t="n">
-        <v>-45.516</v>
+        <v>-45.093</v>
       </c>
     </row>
     <row r="10">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>KUYAS.IS: +0.12% / +0.50% / -1.07% | TRALT.IS: +1.57% / +4.87% / -2.03%</t>
+          <t>KUYAS.IS: -1.58% / +0.50% / -1.71% | TRALT.IS: +1.87% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.662413152260879</v>
+        <v>-3.934691160239312</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1360,7 +1360,7 @@
         <v>175.3</v>
       </c>
       <c r="O10" t="n">
-        <v>49.2</v>
+        <v>48.9</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>16.658</v>
+        <v>16.328</v>
       </c>
       <c r="V10" t="n">
-        <v>8.468</v>
+        <v>8.161</v>
       </c>
       <c r="W10" t="n">
-        <v>-8.73</v>
+        <v>-9.06</v>
       </c>
     </row>
     <row r="11">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.68% / +20.94% / 0.00% | RALYH.IS: +29.54% / +35.10% / -0.91% | VAKBN.IS: -0.78% / +2.23% / -1.88%</t>
+          <t>BRSAN.IS: +11.84% / +20.94% / 0.00% | RALYH.IS: +29.54% / +35.10% / -0.91% | VAKBN.IS: -0.25% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K12" t="n">
-        <v>12.42653216346226</v>
+        <v>12.67154498993952</v>
       </c>
       <c r="L12" t="n">
         <v>34.56349599547857</v>
@@ -1542,13 +1542,13 @@
         <v>23.777</v>
       </c>
       <c r="U12" t="n">
-        <v>48.696</v>
+        <v>49.021</v>
       </c>
       <c r="V12" t="n">
-        <v>42.476</v>
+        <v>42.786</v>
       </c>
       <c r="W12" t="n">
-        <v>-11.342</v>
+        <v>-11.017</v>
       </c>
     </row>
     <row r="13">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TRALT.IS: +1.57% / +4.87% / -2.03%</t>
+          <t>TRALT.IS: +1.87% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-5.044425134583063</v>
       </c>
       <c r="K13" t="n">
-        <v>10.60572015138295</v>
+        <v>10.76882867580764</v>
       </c>
       <c r="L13" t="n">
         <v>9.344627019167174</v>
@@ -1629,13 +1629,13 @@
         <v>12.101</v>
       </c>
       <c r="U13" t="n">
-        <v>29.046</v>
+        <v>29.236</v>
       </c>
       <c r="V13" t="n">
-        <v>34.434</v>
+        <v>34.632</v>
       </c>
       <c r="W13" t="n">
-        <v>-8.733000000000001</v>
+        <v>-8.542999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1878,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.78% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.25% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-16.17766019108726</v>
+        <v>-15.95456382999942</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1911,19 +1911,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>22.27</v>
+        <v>22.063</v>
       </c>
       <c r="T18" t="n">
-        <v>22.27</v>
+        <v>22.063</v>
       </c>
       <c r="U18" t="n">
-        <v>58.865</v>
+        <v>59.288</v>
       </c>
       <c r="V18" t="n">
-        <v>13.879</v>
+        <v>14.182</v>
       </c>
       <c r="W18" t="n">
-        <v>-45.516</v>
+        <v>-45.093</v>
       </c>
     </row>
     <row r="19">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-03 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-09-03 | ENERY.IS: 2026-09-04 | ENJSA.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.83% / +1.61% / -1.61% | ENERY.IS: +4.26% / +4.86% / -2.76% | ENJSA.IS: -1.07% / +0.61% / -1.66%</t>
+          <t>ALARK.IS: -0.56% / +1.61% / -1.61% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -1.24% / +0.61% / -1.66%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-15.74339255158701</v>
+        <v>-15.48300585045406</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2137,10 +2137,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>192.1</v>
+        <v>192.6</v>
       </c>
       <c r="O21" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2160,13 +2160,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>41.136</v>
+        <v>41.572</v>
       </c>
       <c r="V21" t="n">
-        <v>11.867</v>
+        <v>12.213</v>
       </c>
       <c r="W21" t="n">
-        <v>-29.039</v>
+        <v>-28.603</v>
       </c>
     </row>
     <row r="22">
@@ -2210,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.78% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.25% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.754951026157062</v>
+        <v>-5.504114226271217</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2243,19 +2243,19 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>18.081</v>
+        <v>17.863</v>
       </c>
       <c r="T22" t="n">
-        <v>18.081</v>
+        <v>17.863</v>
       </c>
       <c r="U22" t="n">
-        <v>64.729</v>
+        <v>65.16800000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>28.961</v>
+        <v>29.304</v>
       </c>
       <c r="W22" t="n">
-        <v>-36.359</v>
+        <v>-35.92</v>
       </c>
     </row>
     <row r="23">
@@ -2453,14 +2453,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TRALT.IS: +1.57% / +4.87% / -2.03%</t>
+          <t>TRALT.IS: +1.87% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-5.044425134583063</v>
       </c>
       <c r="K25" t="n">
-        <v>10.60572015138295</v>
+        <v>10.76882867580764</v>
       </c>
       <c r="L25" t="n">
         <v>9.344627019167174</v>
@@ -2492,13 +2492,13 @@
         <v>12.101</v>
       </c>
       <c r="U25" t="n">
-        <v>29.046</v>
+        <v>29.236</v>
       </c>
       <c r="V25" t="n">
-        <v>34.434</v>
+        <v>34.632</v>
       </c>
       <c r="W25" t="n">
-        <v>-8.733000000000001</v>
+        <v>-8.542999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -2542,14 +2542,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>KUYAS.IS: +0.12% / +0.50% / -1.07% | TRALT.IS: +1.57% / +4.87% / -2.03%</t>
+          <t>KUYAS.IS: -1.58% / +0.50% / -1.71% | TRALT.IS: +1.87% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.662413152260879</v>
+        <v>-3.934691160239312</v>
       </c>
       <c r="L26" t="n">
         <v>4.543450519200398</v>
@@ -2561,7 +2561,7 @@
         <v>175.3</v>
       </c>
       <c r="O26" t="n">
-        <v>49.2</v>
+        <v>48.9</v>
       </c>
       <c r="P26" t="n">
         <v>1.9</v>
@@ -2581,13 +2581,13 @@
         <v>10.072</v>
       </c>
       <c r="U26" t="n">
-        <v>16.658</v>
+        <v>16.328</v>
       </c>
       <c r="V26" t="n">
-        <v>8.468</v>
+        <v>8.161</v>
       </c>
       <c r="W26" t="n">
-        <v>-8.73</v>
+        <v>-9.06</v>
       </c>
     </row>
     <row r="27">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.68% / +20.94% / 0.00% | RALYH.IS: +29.54% / +35.10% / -0.91% | VAKBN.IS: -0.78% / +2.23% / -1.88%</t>
+          <t>BRSAN.IS: +11.84% / +20.94% / 0.00% | RALYH.IS: +29.54% / +35.10% / -0.91% | VAKBN.IS: -0.25% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>12.42653216346226</v>
+        <v>12.67154498993952</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2670,13 +2670,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>48.696</v>
+        <v>49.021</v>
       </c>
       <c r="V27" t="n">
-        <v>42.476</v>
+        <v>42.786</v>
       </c>
       <c r="W27" t="n">
-        <v>-11.342</v>
+        <v>-11.017</v>
       </c>
     </row>
   </sheetData>
@@ -2711,7 +2711,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2896,7 +2896,7 @@
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.06127370985247182</v>
+        <v>0.06244681108633632</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2928,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>253.734</v>
+        <v>254.172</v>
       </c>
       <c r="V3" t="n">
-        <v>101.324</v>
+        <v>101.573</v>
       </c>
       <c r="W3" t="n">
-        <v>-39.718</v>
+        <v>-39.28</v>
       </c>
     </row>
     <row r="4">
@@ -2976,14 +2976,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +4.26% / +4.85% / -2.77% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.66% / +0.69% / -1.98%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.12% / +5.52% / -2.77% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.57% / +0.69% / -1.98%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.77640259976103</v>
+        <v>-10.5884342120014</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -3009,19 +3009,19 @@
         <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>25.534</v>
+        <v>25.377</v>
       </c>
       <c r="T4" t="n">
-        <v>25.534</v>
+        <v>25.377</v>
       </c>
       <c r="U4" t="n">
-        <v>55.967</v>
+        <v>56.295</v>
       </c>
       <c r="V4" t="n">
-        <v>20.043</v>
+        <v>20.296</v>
       </c>
       <c r="W4" t="n">
-        <v>-53.479</v>
+        <v>-53.15</v>
       </c>
     </row>
     <row r="5">
@@ -3070,7 +3070,7 @@
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.08128049304420015</v>
+        <v>0.04241526022217279</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3102,13 +3102,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>251.01</v>
+        <v>251.445</v>
       </c>
       <c r="V5" t="n">
-        <v>83.33799999999999</v>
+        <v>83.565</v>
       </c>
       <c r="W5" t="n">
-        <v>-39.367</v>
+        <v>-38.932</v>
       </c>
     </row>
     <row r="6">
@@ -3150,14 +3150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +10.84% / +20.03% / -1.13% | CANTE.IS: +7.02% / +15.84% / -2.80% | ENERY.IS: +4.26% / +4.85% / -2.77% | SOKM.IS: -1.66% / +0.69% / -1.98% | TKFEN.IS: +10.77% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | CANTE.IS: +7.02% / +15.84% / -2.80% | ENERY.IS: +5.12% / +5.52% / -2.77% | SOKM.IS: -1.57% / +0.69% / -1.98% | TKFEN.IS: +12.65% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.07376133349631</v>
+        <v>-9.53197808342029</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3189,13 +3189,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>22.362</v>
+        <v>23.099</v>
       </c>
       <c r="V6" t="n">
-        <v>11.802</v>
+        <v>12.476</v>
       </c>
       <c r="W6" t="n">
-        <v>-42.763</v>
+        <v>-42.026</v>
       </c>
     </row>
     <row r="7">
@@ -3237,14 +3237,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +4.26% / +4.85% / -2.77% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.66% / +0.69% / -1.98%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.12% / +5.52% / -2.77% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.57% / +0.69% / -1.98%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.77640259976103</v>
+        <v>-10.5884342120014</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3270,19 +3270,19 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>25.534</v>
+        <v>25.377</v>
       </c>
       <c r="T7" t="n">
-        <v>25.534</v>
+        <v>25.377</v>
       </c>
       <c r="U7" t="n">
-        <v>55.967</v>
+        <v>56.295</v>
       </c>
       <c r="V7" t="n">
-        <v>20.043</v>
+        <v>20.296</v>
       </c>
       <c r="W7" t="n">
-        <v>-53.479</v>
+        <v>-53.15</v>
       </c>
     </row>
     <row r="8">
@@ -3324,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +10.84% / +20.03% / -1.13% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +4.26% / +4.85% / -2.77%</t>
+          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +5.12% / +5.52% / -2.77%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.197681541041863</v>
+        <v>-1.920751275565813</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3363,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>22.512</v>
+        <v>22.859</v>
       </c>
       <c r="V8" t="n">
-        <v>2.507</v>
+        <v>2.797</v>
       </c>
       <c r="W8" t="n">
-        <v>-30.646</v>
+        <v>-30.299</v>
       </c>
     </row>
     <row r="9">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-02</t>
+          <t>ALARK.IS: 2026-09-04 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -3486,14 +3486,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +4.26% / +4.85% / -2.77%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.525873042119764</v>
+        <v>-2.225881668067542</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3502,10 +3502,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>114.3</v>
+        <v>114.8</v>
       </c>
       <c r="O10" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
       <c r="P10" t="n">
         <v>2.4</v>
@@ -3525,13 +3525,13 @@
         <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>11.494</v>
+        <v>11.837</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.943</v>
+        <v>-1.641</v>
       </c>
       <c r="W10" t="n">
-        <v>-26.658</v>
+        <v>-26.315</v>
       </c>
     </row>
     <row r="11">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-04 | ENJSA.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -3573,14 +3573,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +4.26% / +4.85% / -2.77% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.66% / +0.69% / -1.98%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.57% / +0.69% / -1.98%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.69308131260991</v>
+        <v>-10.5124707120014</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3589,10 +3589,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>180.4</v>
+        <v>180.9</v>
       </c>
       <c r="O11" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
@@ -3606,19 +3606,19 @@
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>24.216</v>
+        <v>24.062</v>
       </c>
       <c r="T11" t="n">
-        <v>24.216</v>
+        <v>24.062</v>
       </c>
       <c r="U11" t="n">
-        <v>32.162</v>
+        <v>32.429</v>
       </c>
       <c r="V11" t="n">
-        <v>7.094</v>
+        <v>7.31</v>
       </c>
       <c r="W11" t="n">
-        <v>-42.23</v>
+        <v>-41.963</v>
       </c>
     </row>
     <row r="12">
@@ -3660,14 +3660,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +10.84% / +20.03% / -1.13% | TKFEN.IS: +10.77% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | TKFEN.IS: +12.65% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>8.737710215420446</v>
+        <v>9.762993655547959</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3699,13 +3699,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>41.392</v>
+        <v>42.726</v>
       </c>
       <c r="V12" t="n">
-        <v>51.516</v>
+        <v>52.944</v>
       </c>
       <c r="W12" t="n">
-        <v>-18.896</v>
+        <v>-17.563</v>
       </c>
     </row>
     <row r="13">
@@ -3747,14 +3747,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.02% / +1.66% / -1.90%</t>
+          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.34% / +1.66% / -1.90%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K13" t="n">
-        <v>7.353085651398006</v>
+        <v>6.952535948244365</v>
       </c>
       <c r="L13" t="n">
         <v>19.61961325199098</v>
@@ -3766,7 +3766,7 @@
         <v>88.5</v>
       </c>
       <c r="O13" t="n">
-        <v>46.1</v>
+        <v>45.5</v>
       </c>
       <c r="P13" t="n">
         <v>2.2</v>
@@ -3786,13 +3786,13 @@
         <v>18.132</v>
       </c>
       <c r="U13" t="n">
-        <v>4.677</v>
+        <v>4.287</v>
       </c>
       <c r="V13" t="n">
-        <v>12.099</v>
+        <v>11.68</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.115</v>
+        <v>-7.505</v>
       </c>
     </row>
     <row r="14">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3819,55 +3819,67 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ENERY.IS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-09-04 | ENERY.IS: 2026-09-02</t>
+        </is>
+      </c>
       <c r="H14" t="n">
-        <v>8.530010255723974</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>32.90971238010212</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.12% / +5.52% / -2.77%</t>
+        </is>
+      </c>
       <c r="J14" t="n">
-        <v>0.8142516931666233</v>
+        <v>3.175499702073514</v>
       </c>
       <c r="K14" t="n">
-        <v>3.846414277792909</v>
+        <v>4.114018716336987</v>
       </c>
       <c r="L14" t="n">
-        <v>9.181211458048665</v>
+        <v>18.99889339779883</v>
       </c>
       <c r="M14" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N14" t="n">
-        <v>35.8</v>
+        <v>43.7</v>
       </c>
       <c r="O14" t="n">
         <v>50</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>8.083</v>
+        <v>18.999</v>
       </c>
       <c r="T14" t="n">
-        <v>7.916</v>
+        <v>16.472</v>
       </c>
       <c r="U14" t="n">
-        <v>8.898</v>
+        <v>21.201</v>
       </c>
       <c r="V14" t="n">
-        <v>4.916</v>
+        <v>19.346</v>
       </c>
       <c r="W14" t="n">
-        <v>-4.971</v>
+        <v>-12.646</v>
       </c>
     </row>
     <row r="16">
@@ -4042,7 +4054,7 @@
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.06127370985247182</v>
+        <v>0.06244681108633632</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4074,13 +4086,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>253.734</v>
+        <v>254.172</v>
       </c>
       <c r="V18" t="n">
-        <v>101.324</v>
+        <v>101.573</v>
       </c>
       <c r="W18" t="n">
-        <v>-39.718</v>
+        <v>-39.28</v>
       </c>
     </row>
     <row r="19">
@@ -4124,14 +4136,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +4.26% / +4.85% / -2.77% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.66% / +0.69% / -1.98%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.12% / +5.52% / -2.77% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.57% / +0.69% / -1.98%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.77640259976103</v>
+        <v>-10.5884342120014</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4157,19 +4169,19 @@
         <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>25.534</v>
+        <v>25.377</v>
       </c>
       <c r="T19" t="n">
-        <v>25.534</v>
+        <v>25.377</v>
       </c>
       <c r="U19" t="n">
-        <v>55.967</v>
+        <v>56.295</v>
       </c>
       <c r="V19" t="n">
-        <v>20.043</v>
+        <v>20.296</v>
       </c>
       <c r="W19" t="n">
-        <v>-53.479</v>
+        <v>-53.15</v>
       </c>
     </row>
     <row r="20">
@@ -4220,7 +4232,7 @@
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.08128049304420015</v>
+        <v>0.04241526022217279</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4252,13 +4264,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>251.01</v>
+        <v>251.445</v>
       </c>
       <c r="V20" t="n">
-        <v>83.33799999999999</v>
+        <v>83.565</v>
       </c>
       <c r="W20" t="n">
-        <v>-39.367</v>
+        <v>-38.932</v>
       </c>
     </row>
     <row r="21">
@@ -4294,7 +4306,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-04 | ENJSA.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -4302,14 +4314,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +4.26% / +4.85% / -2.77% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.66% / +0.69% / -1.98%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.57% / +0.69% / -1.98%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.69308131260991</v>
+        <v>-10.5124707120014</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4318,10 +4330,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>180.4</v>
+        <v>180.9</v>
       </c>
       <c r="O21" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
@@ -4335,19 +4347,19 @@
         <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>24.216</v>
+        <v>24.062</v>
       </c>
       <c r="T21" t="n">
-        <v>24.216</v>
+        <v>24.062</v>
       </c>
       <c r="U21" t="n">
-        <v>32.162</v>
+        <v>32.429</v>
       </c>
       <c r="V21" t="n">
-        <v>7.094</v>
+        <v>7.31</v>
       </c>
       <c r="W21" t="n">
-        <v>-42.23</v>
+        <v>-41.963</v>
       </c>
     </row>
     <row r="22">
@@ -4391,14 +4403,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +10.84% / +20.03% / -1.13% | CANTE.IS: +7.02% / +15.84% / -2.80% | ENERY.IS: +4.26% / +4.85% / -2.77% | SOKM.IS: -1.66% / +0.69% / -1.98% | TKFEN.IS: +10.77% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | CANTE.IS: +7.02% / +15.84% / -2.80% | ENERY.IS: +5.12% / +5.52% / -2.77% | SOKM.IS: -1.57% / +0.69% / -1.98% | TKFEN.IS: +12.65% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.07376133349631</v>
+        <v>-9.53197808342029</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4430,13 +4442,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>22.362</v>
+        <v>23.099</v>
       </c>
       <c r="V22" t="n">
-        <v>11.802</v>
+        <v>12.476</v>
       </c>
       <c r="W22" t="n">
-        <v>-42.763</v>
+        <v>-42.026</v>
       </c>
     </row>
     <row r="23">
@@ -4480,14 +4492,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +10.84% / +20.03% / -1.13% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +4.26% / +4.85% / -2.77%</t>
+          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +5.12% / +5.52% / -2.77%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.197681541041863</v>
+        <v>-1.920751275565813</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4519,13 +4531,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>22.512</v>
+        <v>22.859</v>
       </c>
       <c r="V23" t="n">
-        <v>2.507</v>
+        <v>2.797</v>
       </c>
       <c r="W23" t="n">
-        <v>-30.646</v>
+        <v>-30.299</v>
       </c>
     </row>
     <row r="24">
@@ -4561,7 +4573,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-02</t>
+          <t>ALARK.IS: 2026-09-04 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -4569,14 +4581,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +4.26% / +4.85% / -2.77%</t>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.525873042119764</v>
+        <v>-2.225881668067542</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4585,10 +4597,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>114.3</v>
+        <v>114.8</v>
       </c>
       <c r="O24" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
       <c r="P24" t="n">
         <v>2.4</v>
@@ -4608,29 +4620,29 @@
         <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>11.494</v>
+        <v>11.837</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.943</v>
+        <v>-1.641</v>
       </c>
       <c r="W24" t="n">
-        <v>-26.658</v>
+        <v>-26.315</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4643,71 +4655,83 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ALARK.IS, ENERY.IS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ALARK.IS: 2026-09-04 | ENERY.IS: 2026-09-02</t>
+        </is>
+      </c>
       <c r="H25" t="n">
-        <v>28.40086810394897</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>32.90971238010212</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.12% / +5.52% / -2.77%</t>
+        </is>
+      </c>
       <c r="J25" t="n">
-        <v>15.38514121842653</v>
+        <v>3.175499702073514</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.616392554049999</v>
+        <v>4.114018716336987</v>
       </c>
       <c r="L25" t="n">
-        <v>5.127814043936619</v>
+        <v>18.99889339779883</v>
       </c>
       <c r="M25" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>75.59999999999999</v>
+        <v>43.7</v>
       </c>
       <c r="O25" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="P25" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>13.28</v>
+        <v>18.999</v>
       </c>
       <c r="T25" t="n">
-        <v>13.28</v>
+        <v>16.472</v>
       </c>
       <c r="U25" t="n">
-        <v>9.128</v>
+        <v>21.201</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.962</v>
+        <v>19.346</v>
       </c>
       <c r="W25" t="n">
-        <v>-16.712</v>
+        <v>-12.646</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4723,29 +4747,29 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>8.530010255723974</v>
+        <v>28.40086810394897</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>0.8142516931666233</v>
+        <v>15.38514121842653</v>
       </c>
       <c r="K26" t="n">
-        <v>3.846414277792909</v>
+        <v>-6.616392554049999</v>
       </c>
       <c r="L26" t="n">
-        <v>9.181211458048665</v>
+        <v>5.127814043936619</v>
       </c>
       <c r="M26" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>35.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>50</v>
+        <v>49.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4756,19 +4780,19 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>8.083</v>
+        <v>13.28</v>
       </c>
       <c r="T26" t="n">
-        <v>7.916</v>
+        <v>13.28</v>
       </c>
       <c r="U26" t="n">
-        <v>8.898</v>
+        <v>9.128</v>
       </c>
       <c r="V26" t="n">
-        <v>4.916</v>
+        <v>-0.962</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.971</v>
+        <v>-16.712</v>
       </c>
     </row>
     <row r="27">
@@ -4812,14 +4836,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +10.84% / +20.03% / -1.13% | TKFEN.IS: +10.77% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | TKFEN.IS: +12.65% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>8.737710215420446</v>
+        <v>9.762993655547959</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4851,13 +4875,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>41.392</v>
+        <v>42.726</v>
       </c>
       <c r="V27" t="n">
-        <v>51.516</v>
+        <v>52.944</v>
       </c>
       <c r="W27" t="n">
-        <v>-18.896</v>
+        <v>-17.563</v>
       </c>
     </row>
     <row r="28">
@@ -4901,14 +4925,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.02% / +1.66% / -1.90%</t>
+          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.34% / +1.66% / -1.90%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>7.353085651398006</v>
+        <v>6.952535948244365</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4920,7 +4944,7 @@
         <v>88.5</v>
       </c>
       <c r="O28" t="n">
-        <v>46.1</v>
+        <v>45.5</v>
       </c>
       <c r="P28" t="n">
         <v>2.2</v>
@@ -4940,13 +4964,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>4.677</v>
+        <v>4.287</v>
       </c>
       <c r="V28" t="n">
-        <v>12.099</v>
+        <v>11.68</v>
       </c>
       <c r="W28" t="n">
-        <v>-7.115</v>
+        <v>-7.505</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.25% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -1.37% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-15.95456382999942</v>
+        <v>-16.10801911705971</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -789,19 +789,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>22.063</v>
+        <v>22.206</v>
       </c>
       <c r="T3" t="n">
-        <v>22.063</v>
+        <v>22.206</v>
       </c>
       <c r="U3" t="n">
-        <v>59.288</v>
+        <v>58.997</v>
       </c>
       <c r="V3" t="n">
-        <v>14.182</v>
+        <v>13.974</v>
       </c>
       <c r="W3" t="n">
-        <v>-45.093</v>
+        <v>-45.384</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.25% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -1.37% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-15.95456382999942</v>
+        <v>-16.10801911705971</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1026,19 +1026,19 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>22.063</v>
+        <v>22.206</v>
       </c>
       <c r="T6" t="n">
-        <v>22.063</v>
+        <v>22.206</v>
       </c>
       <c r="U6" t="n">
-        <v>59.288</v>
+        <v>58.997</v>
       </c>
       <c r="V6" t="n">
-        <v>14.182</v>
+        <v>13.974</v>
       </c>
       <c r="W6" t="n">
-        <v>-45.093</v>
+        <v>-45.384</v>
       </c>
     </row>
     <row r="7">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.25% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -1.37% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.504114226271217</v>
+        <v>-5.676650582059684</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>17.863</v>
+        <v>18.013</v>
       </c>
       <c r="T7" t="n">
-        <v>17.863</v>
+        <v>18.013</v>
       </c>
       <c r="U7" t="n">
-        <v>65.16800000000001</v>
+        <v>64.866</v>
       </c>
       <c r="V7" t="n">
-        <v>29.304</v>
+        <v>29.068</v>
       </c>
       <c r="W7" t="n">
-        <v>-35.92</v>
+        <v>-36.222</v>
       </c>
     </row>
     <row r="8">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.56% / +1.61% / -1.61% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -1.24% / +0.61% / -1.66%</t>
+          <t>ALARK.IS: +0.25% / +1.61% / -1.61% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.72% / +0.61% / -1.66%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-15.48300585045406</v>
+        <v>-15.11616313346885</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1186,7 +1186,7 @@
         <v>192.6</v>
       </c>
       <c r="O8" t="n">
-        <v>46.5</v>
+        <v>46.8</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>41.572</v>
+        <v>42.186</v>
       </c>
       <c r="V8" t="n">
-        <v>12.213</v>
+        <v>12.7</v>
       </c>
       <c r="W8" t="n">
-        <v>-28.603</v>
+        <v>-27.989</v>
       </c>
     </row>
     <row r="9">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.25% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -1.37% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-15.95456382999942</v>
+        <v>-16.10801911705971</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1287,19 +1287,19 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>22.063</v>
+        <v>22.206</v>
       </c>
       <c r="T9" t="n">
-        <v>22.063</v>
+        <v>22.206</v>
       </c>
       <c r="U9" t="n">
-        <v>59.288</v>
+        <v>58.997</v>
       </c>
       <c r="V9" t="n">
-        <v>14.182</v>
+        <v>13.974</v>
       </c>
       <c r="W9" t="n">
-        <v>-45.093</v>
+        <v>-45.384</v>
       </c>
     </row>
     <row r="10">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>KUYAS.IS: -1.58% / +0.50% / -1.71% | TRALT.IS: +1.87% / +4.87% / -2.03%</t>
+          <t>KUYAS.IS: -2.36% / +0.50% / -2.91% | TRALT.IS: +0.97% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.934691160239312</v>
+        <v>-4.256737160874479</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>16.328</v>
+        <v>15.938</v>
       </c>
       <c r="V10" t="n">
-        <v>8.161</v>
+        <v>7.799</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.06</v>
+        <v>-9.449999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.84% / +20.94% / 0.00% | RALYH.IS: +29.54% / +35.10% / -0.91% | VAKBN.IS: -0.25% / +2.23% / -1.88%</t>
+          <t>BRSAN.IS: +13.91% / +20.94% / 0.00% | RALYH.IS: +30.38% / +35.10% / -0.91% | VAKBN.IS: -1.37% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K12" t="n">
-        <v>12.67154498993952</v>
+        <v>13.18787930960317</v>
       </c>
       <c r="L12" t="n">
         <v>34.56349599547857</v>
@@ -1542,13 +1542,13 @@
         <v>23.777</v>
       </c>
       <c r="U12" t="n">
-        <v>49.021</v>
+        <v>49.703</v>
       </c>
       <c r="V12" t="n">
-        <v>42.786</v>
+        <v>43.44</v>
       </c>
       <c r="W12" t="n">
-        <v>-11.017</v>
+        <v>-10.335</v>
       </c>
     </row>
     <row r="13">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TRALT.IS: +1.87% / +4.87% / -2.03%</t>
+          <t>TRALT.IS: +0.97% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-5.044425134583063</v>
       </c>
       <c r="K13" t="n">
-        <v>10.76882867580764</v>
+        <v>10.27950726719542</v>
       </c>
       <c r="L13" t="n">
         <v>9.344627019167174</v>
@@ -1629,13 +1629,13 @@
         <v>12.101</v>
       </c>
       <c r="U13" t="n">
-        <v>29.236</v>
+        <v>28.665</v>
       </c>
       <c r="V13" t="n">
-        <v>34.632</v>
+        <v>34.037</v>
       </c>
       <c r="W13" t="n">
-        <v>-8.542999999999999</v>
+        <v>-9.113</v>
       </c>
     </row>
     <row r="14">
@@ -1878,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.25% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -1.37% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-15.95456382999942</v>
+        <v>-16.10801911705971</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1911,19 +1911,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>22.063</v>
+        <v>22.206</v>
       </c>
       <c r="T18" t="n">
-        <v>22.063</v>
+        <v>22.206</v>
       </c>
       <c r="U18" t="n">
-        <v>59.288</v>
+        <v>58.997</v>
       </c>
       <c r="V18" t="n">
-        <v>14.182</v>
+        <v>13.974</v>
       </c>
       <c r="W18" t="n">
-        <v>-45.093</v>
+        <v>-45.384</v>
       </c>
     </row>
     <row r="19">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.56% / +1.61% / -1.61% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -1.24% / +0.61% / -1.66%</t>
+          <t>ALARK.IS: +0.25% / +1.61% / -1.61% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.72% / +0.61% / -1.66%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-15.48300585045406</v>
+        <v>-15.11616313346885</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2140,7 +2140,7 @@
         <v>192.6</v>
       </c>
       <c r="O21" t="n">
-        <v>46.5</v>
+        <v>46.8</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2160,13 +2160,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>41.572</v>
+        <v>42.186</v>
       </c>
       <c r="V21" t="n">
-        <v>12.213</v>
+        <v>12.7</v>
       </c>
       <c r="W21" t="n">
-        <v>-28.603</v>
+        <v>-27.989</v>
       </c>
     </row>
     <row r="22">
@@ -2210,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -2.26% | VAKBN.IS: -0.25% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -1.37% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.504114226271217</v>
+        <v>-5.676650582059684</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2243,19 +2243,19 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>17.863</v>
+        <v>18.013</v>
       </c>
       <c r="T22" t="n">
-        <v>17.863</v>
+        <v>18.013</v>
       </c>
       <c r="U22" t="n">
-        <v>65.16800000000001</v>
+        <v>64.866</v>
       </c>
       <c r="V22" t="n">
-        <v>29.304</v>
+        <v>29.068</v>
       </c>
       <c r="W22" t="n">
-        <v>-35.92</v>
+        <v>-36.222</v>
       </c>
     </row>
     <row r="23">
@@ -2453,14 +2453,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TRALT.IS: +1.87% / +4.87% / -2.03%</t>
+          <t>TRALT.IS: +0.97% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-5.044425134583063</v>
       </c>
       <c r="K25" t="n">
-        <v>10.76882867580764</v>
+        <v>10.27950726719542</v>
       </c>
       <c r="L25" t="n">
         <v>9.344627019167174</v>
@@ -2492,13 +2492,13 @@
         <v>12.101</v>
       </c>
       <c r="U25" t="n">
-        <v>29.236</v>
+        <v>28.665</v>
       </c>
       <c r="V25" t="n">
-        <v>34.632</v>
+        <v>34.037</v>
       </c>
       <c r="W25" t="n">
-        <v>-8.542999999999999</v>
+        <v>-9.113</v>
       </c>
     </row>
     <row r="26">
@@ -2542,14 +2542,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>KUYAS.IS: -1.58% / +0.50% / -1.71% | TRALT.IS: +1.87% / +4.87% / -2.03%</t>
+          <t>KUYAS.IS: -2.36% / +0.50% / -2.91% | TRALT.IS: +0.97% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.934691160239312</v>
+        <v>-4.256737160874479</v>
       </c>
       <c r="L26" t="n">
         <v>4.543450519200398</v>
@@ -2581,13 +2581,13 @@
         <v>10.072</v>
       </c>
       <c r="U26" t="n">
-        <v>16.328</v>
+        <v>15.938</v>
       </c>
       <c r="V26" t="n">
-        <v>8.161</v>
+        <v>7.799</v>
       </c>
       <c r="W26" t="n">
-        <v>-9.06</v>
+        <v>-9.449999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.84% / +20.94% / 0.00% | RALYH.IS: +29.54% / +35.10% / -0.91% | VAKBN.IS: -0.25% / +2.23% / -1.88%</t>
+          <t>BRSAN.IS: +13.91% / +20.94% / 0.00% | RALYH.IS: +30.38% / +35.10% / -0.91% | VAKBN.IS: -1.37% / +2.23% / -1.88%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>12.67154498993952</v>
+        <v>13.18787930960317</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2670,13 +2670,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>49.021</v>
+        <v>49.703</v>
       </c>
       <c r="V27" t="n">
-        <v>42.786</v>
+        <v>43.44</v>
       </c>
       <c r="W27" t="n">
-        <v>-11.017</v>
+        <v>-10.335</v>
       </c>
     </row>
   </sheetData>
@@ -2876,12 +2876,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ENERY.IS</t>
+          <t>ALARK.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04</t>
+          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2889,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06244681108633632</v>
+        <v>0.4336128230461478</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>18.106</v>
@@ -2928,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>254.172</v>
+        <v>255.486</v>
       </c>
       <c r="V3" t="n">
-        <v>101.573</v>
+        <v>102.321</v>
       </c>
       <c r="W3" t="n">
-        <v>-39.28</v>
+        <v>-37.966</v>
       </c>
     </row>
     <row r="4">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2976,14 +2976,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.12% / +5.52% / -2.77% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.57% / +0.69% / -1.98%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.12% / +5.52% / -2.77% | ENJSA.IS: +3.25% / +4.63% / -0.09% | SOKM.IS: -0.02% / +0.69% / -1.98%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.5884342120014</v>
+        <v>-10.0435317800327</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2992,10 +2992,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>119.8</v>
+        <v>118.8</v>
       </c>
       <c r="O4" t="n">
-        <v>46.5</v>
+        <v>46.9</v>
       </c>
       <c r="P4" t="n">
         <v>3.8</v>
@@ -3009,19 +3009,19 @@
         <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>25.377</v>
+        <v>25.08</v>
       </c>
       <c r="T4" t="n">
-        <v>25.377</v>
+        <v>25.08</v>
       </c>
       <c r="U4" t="n">
-        <v>56.295</v>
+        <v>57.248</v>
       </c>
       <c r="V4" t="n">
-        <v>20.296</v>
+        <v>21.029</v>
       </c>
       <c r="W4" t="n">
-        <v>-53.15</v>
+        <v>-52.198</v>
       </c>
     </row>
     <row r="5">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ENERY.IS</t>
+          <t>ALARK.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04</t>
+          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3063,14 +3063,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04241526022217279</v>
+        <v>0.4135069682739134</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>21.096</v>
@@ -3102,13 +3102,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>251.445</v>
+        <v>252.749</v>
       </c>
       <c r="V5" t="n">
-        <v>83.565</v>
+        <v>84.246</v>
       </c>
       <c r="W5" t="n">
-        <v>-38.932</v>
+        <v>-37.629</v>
       </c>
     </row>
     <row r="6">
@@ -3150,14 +3150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | CANTE.IS: +7.02% / +15.84% / -2.80% | ENERY.IS: +5.12% / +5.52% / -2.77% | SOKM.IS: -1.57% / +0.69% / -1.98% | TKFEN.IS: +12.65% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +13.05% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | ENERY.IS: +5.12% / +5.52% / -2.77% | SOKM.IS: -0.02% / +0.69% / -1.98% | TKFEN.IS: +12.75% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.53197808342029</v>
+        <v>-8.819824308406277</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3189,13 +3189,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>23.099</v>
+        <v>24.068</v>
       </c>
       <c r="V6" t="n">
-        <v>12.476</v>
+        <v>13.361</v>
       </c>
       <c r="W6" t="n">
-        <v>-42.026</v>
+        <v>-41.057</v>
       </c>
     </row>
     <row r="7">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3237,14 +3237,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.12% / +5.52% / -2.77% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.57% / +0.69% / -1.98%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.12% / +5.52% / -2.77% | ENJSA.IS: +3.25% / +4.63% / -0.09% | SOKM.IS: -0.02% / +0.69% / -1.98%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.5884342120014</v>
+        <v>-10.0435317800327</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3253,10 +3253,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>119.8</v>
+        <v>118.8</v>
       </c>
       <c r="O7" t="n">
-        <v>46.5</v>
+        <v>46.9</v>
       </c>
       <c r="P7" t="n">
         <v>3.8</v>
@@ -3270,19 +3270,19 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>25.377</v>
+        <v>25.08</v>
       </c>
       <c r="T7" t="n">
-        <v>25.377</v>
+        <v>25.08</v>
       </c>
       <c r="U7" t="n">
-        <v>56.295</v>
+        <v>57.248</v>
       </c>
       <c r="V7" t="n">
-        <v>20.296</v>
+        <v>21.029</v>
       </c>
       <c r="W7" t="n">
-        <v>-53.15</v>
+        <v>-52.198</v>
       </c>
     </row>
     <row r="8">
@@ -3324,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +5.12% / +5.52% / -2.77%</t>
+          <t>BRSAN.IS: +13.05% / +20.03% / -1.13% | CANTE.IS: -0.02% / +3.71% / -2.30% | ENERY.IS: +5.12% / +5.52% / -2.77%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.920751275565813</v>
+        <v>-1.224545069392247</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3363,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>22.859</v>
+        <v>23.731</v>
       </c>
       <c r="V8" t="n">
-        <v>2.797</v>
+        <v>3.527</v>
       </c>
       <c r="W8" t="n">
-        <v>-30.299</v>
+        <v>-29.427</v>
       </c>
     </row>
     <row r="9">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-04</t>
+          <t>ALARK.IS: 2026-08-31 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -3486,14 +3486,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | CANTE.IS: -0.02% / +3.71% / -2.30% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.225881668067542</v>
+        <v>-1.803376591707262</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3502,10 +3502,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>114.8</v>
+        <v>114.3</v>
       </c>
       <c r="O10" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="P10" t="n">
         <v>2.4</v>
@@ -3525,13 +3525,13 @@
         <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>11.837</v>
+        <v>12.321</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.641</v>
+        <v>-1.216</v>
       </c>
       <c r="W10" t="n">
-        <v>-26.315</v>
+        <v>-25.832</v>
       </c>
     </row>
     <row r="11">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-04 | ENJSA.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-04 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -3573,14 +3573,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.57% / +0.69% / -1.98%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +3.25% / +4.63% / -0.09% | SOKM.IS: -0.02% / +0.69% / -1.98%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.5124707120014</v>
+        <v>-9.967139605338071</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3589,10 +3589,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>180.9</v>
+        <v>179.9</v>
       </c>
       <c r="O11" t="n">
-        <v>51.6</v>
+        <v>51.9</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
@@ -3606,19 +3606,19 @@
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>24.062</v>
+        <v>23.754</v>
       </c>
       <c r="T11" t="n">
-        <v>24.062</v>
+        <v>23.754</v>
       </c>
       <c r="U11" t="n">
-        <v>32.429</v>
+        <v>33.236</v>
       </c>
       <c r="V11" t="n">
-        <v>7.31</v>
+        <v>7.964</v>
       </c>
       <c r="W11" t="n">
-        <v>-41.963</v>
+        <v>-41.156</v>
       </c>
     </row>
     <row r="12">
@@ -3660,14 +3660,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | TKFEN.IS: +12.65% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +13.05% / +20.03% / -1.13% | TKFEN.IS: +12.75% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>9.762993655547959</v>
+        <v>10.79038159414842</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3699,13 +3699,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>42.726</v>
+        <v>44.061</v>
       </c>
       <c r="V12" t="n">
-        <v>52.944</v>
+        <v>54.376</v>
       </c>
       <c r="W12" t="n">
-        <v>-17.563</v>
+        <v>-16.227</v>
       </c>
     </row>
     <row r="13">
@@ -3747,14 +3747,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.34% / +1.66% / -1.90%</t>
+          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.02% / +1.66% / -1.90%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K13" t="n">
-        <v>6.952535948244365</v>
+        <v>7.442493428833585</v>
       </c>
       <c r="L13" t="n">
         <v>19.61961325199098</v>
@@ -3766,7 +3766,7 @@
         <v>88.5</v>
       </c>
       <c r="O13" t="n">
-        <v>45.5</v>
+        <v>46.1</v>
       </c>
       <c r="P13" t="n">
         <v>2.2</v>
@@ -3786,13 +3786,13 @@
         <v>18.132</v>
       </c>
       <c r="U13" t="n">
-        <v>4.287</v>
+        <v>4.764</v>
       </c>
       <c r="V13" t="n">
-        <v>11.68</v>
+        <v>12.192</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.505</v>
+        <v>-7.028</v>
       </c>
     </row>
     <row r="14">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | ENERY.IS: 2026-09-02</t>
+          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -3834,14 +3834,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.12% / +5.52% / -2.77%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: +5.12% / +5.52% / -2.77%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>3.175499702073514</v>
       </c>
       <c r="K14" t="n">
-        <v>4.114018716336987</v>
+        <v>4.560136784755486</v>
       </c>
       <c r="L14" t="n">
         <v>18.99889339779883</v>
@@ -3850,10 +3850,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N14" t="n">
-        <v>43.7</v>
+        <v>43.2</v>
       </c>
       <c r="O14" t="n">
-        <v>50</v>
+        <v>50.6</v>
       </c>
       <c r="P14" t="n">
         <v>3.9</v>
@@ -3873,13 +3873,13 @@
         <v>16.472</v>
       </c>
       <c r="U14" t="n">
-        <v>21.201</v>
+        <v>21.72</v>
       </c>
       <c r="V14" t="n">
-        <v>19.346</v>
+        <v>19.858</v>
       </c>
       <c r="W14" t="n">
-        <v>-12.646</v>
+        <v>-12.127</v>
       </c>
     </row>
     <row r="16">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ENERY.IS</t>
+          <t>ALARK.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04</t>
+          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>0.06244681108633632</v>
+        <v>0.4336128230461478</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
         <v>18.106</v>
@@ -4086,13 +4086,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>254.172</v>
+        <v>255.486</v>
       </c>
       <c r="V18" t="n">
-        <v>101.573</v>
+        <v>102.321</v>
       </c>
       <c r="W18" t="n">
-        <v>-39.28</v>
+        <v>-37.966</v>
       </c>
     </row>
     <row r="19">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -4136,14 +4136,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.12% / +5.52% / -2.77% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.57% / +0.69% / -1.98%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.12% / +5.52% / -2.77% | ENJSA.IS: +3.25% / +4.63% / -0.09% | SOKM.IS: -0.02% / +0.69% / -1.98%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.5884342120014</v>
+        <v>-10.0435317800327</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4152,10 +4152,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>119.8</v>
+        <v>118.8</v>
       </c>
       <c r="O19" t="n">
-        <v>46.5</v>
+        <v>46.9</v>
       </c>
       <c r="P19" t="n">
         <v>3.8</v>
@@ -4169,19 +4169,19 @@
         <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>25.377</v>
+        <v>25.08</v>
       </c>
       <c r="T19" t="n">
-        <v>25.377</v>
+        <v>25.08</v>
       </c>
       <c r="U19" t="n">
-        <v>56.295</v>
+        <v>57.248</v>
       </c>
       <c r="V19" t="n">
-        <v>20.296</v>
+        <v>21.029</v>
       </c>
       <c r="W19" t="n">
-        <v>-53.15</v>
+        <v>-52.198</v>
       </c>
     </row>
     <row r="20">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ENERY.IS</t>
+          <t>ALARK.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ENERY.IS: 2026-09-04</t>
+          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -4225,14 +4225,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>0.04241526022217279</v>
+        <v>0.4135069682739134</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
         <v>21.096</v>
@@ -4264,13 +4264,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>251.445</v>
+        <v>252.749</v>
       </c>
       <c r="V20" t="n">
-        <v>83.565</v>
+        <v>84.246</v>
       </c>
       <c r="W20" t="n">
-        <v>-38.932</v>
+        <v>-37.629</v>
       </c>
     </row>
     <row r="21">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-04 | ENJSA.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-04 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -4314,14 +4314,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.57% / +0.69% / -1.98%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +3.25% / +4.63% / -0.09% | SOKM.IS: -0.02% / +0.69% / -1.98%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.5124707120014</v>
+        <v>-9.967139605338071</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4330,10 +4330,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>180.9</v>
+        <v>179.9</v>
       </c>
       <c r="O21" t="n">
-        <v>51.6</v>
+        <v>51.9</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
@@ -4347,19 +4347,19 @@
         <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>24.062</v>
+        <v>23.754</v>
       </c>
       <c r="T21" t="n">
-        <v>24.062</v>
+        <v>23.754</v>
       </c>
       <c r="U21" t="n">
-        <v>32.429</v>
+        <v>33.236</v>
       </c>
       <c r="V21" t="n">
-        <v>7.31</v>
+        <v>7.964</v>
       </c>
       <c r="W21" t="n">
-        <v>-41.963</v>
+        <v>-41.156</v>
       </c>
     </row>
     <row r="22">
@@ -4403,14 +4403,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | CANTE.IS: +7.02% / +15.84% / -2.80% | ENERY.IS: +5.12% / +5.52% / -2.77% | SOKM.IS: -1.57% / +0.69% / -1.98% | TKFEN.IS: +12.65% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +13.05% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | ENERY.IS: +5.12% / +5.52% / -2.77% | SOKM.IS: -0.02% / +0.69% / -1.98% | TKFEN.IS: +12.75% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-9.53197808342029</v>
+        <v>-8.819824308406277</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4442,13 +4442,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>23.099</v>
+        <v>24.068</v>
       </c>
       <c r="V22" t="n">
-        <v>12.476</v>
+        <v>13.361</v>
       </c>
       <c r="W22" t="n">
-        <v>-42.026</v>
+        <v>-41.057</v>
       </c>
     </row>
     <row r="23">
@@ -4492,14 +4492,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: +5.12% / +5.52% / -2.77%</t>
+          <t>BRSAN.IS: +13.05% / +20.03% / -1.13% | CANTE.IS: -0.02% / +3.71% / -2.30% | ENERY.IS: +5.12% / +5.52% / -2.77%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.920751275565813</v>
+        <v>-1.224545069392247</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4531,13 +4531,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>22.859</v>
+        <v>23.731</v>
       </c>
       <c r="V23" t="n">
-        <v>2.797</v>
+        <v>3.527</v>
       </c>
       <c r="W23" t="n">
-        <v>-30.299</v>
+        <v>-29.427</v>
       </c>
     </row>
     <row r="24">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-04</t>
+          <t>ALARK.IS: 2026-08-31 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -4581,14 +4581,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.77% / +3.71% / -2.30% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | CANTE.IS: -0.02% / +3.71% / -2.30% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.225881668067542</v>
+        <v>-1.803376591707262</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4597,10 +4597,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>114.8</v>
+        <v>114.3</v>
       </c>
       <c r="O24" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="P24" t="n">
         <v>2.4</v>
@@ -4620,13 +4620,13 @@
         <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>11.837</v>
+        <v>12.321</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.641</v>
+        <v>-1.216</v>
       </c>
       <c r="W24" t="n">
-        <v>-26.315</v>
+        <v>-25.832</v>
       </c>
     </row>
     <row r="25">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-09-04 | ENERY.IS: 2026-09-02</t>
+          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -4670,14 +4670,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ALARK.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.12% / +5.52% / -2.77%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: +5.12% / +5.52% / -2.77%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>3.175499702073514</v>
       </c>
       <c r="K25" t="n">
-        <v>4.114018716336987</v>
+        <v>4.560136784755486</v>
       </c>
       <c r="L25" t="n">
         <v>18.99889339779883</v>
@@ -4686,10 +4686,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>43.7</v>
+        <v>43.2</v>
       </c>
       <c r="O25" t="n">
-        <v>50</v>
+        <v>50.6</v>
       </c>
       <c r="P25" t="n">
         <v>3.9</v>
@@ -4709,13 +4709,13 @@
         <v>16.472</v>
       </c>
       <c r="U25" t="n">
-        <v>21.201</v>
+        <v>21.72</v>
       </c>
       <c r="V25" t="n">
-        <v>19.346</v>
+        <v>19.858</v>
       </c>
       <c r="W25" t="n">
-        <v>-12.646</v>
+        <v>-12.127</v>
       </c>
     </row>
     <row r="26">
@@ -4836,14 +4836,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +11.00% / +20.03% / -1.13% | TKFEN.IS: +12.65% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +13.05% / +20.03% / -1.13% | TKFEN.IS: +12.75% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>9.762993655547959</v>
+        <v>10.79038159414842</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4875,13 +4875,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>42.726</v>
+        <v>44.061</v>
       </c>
       <c r="V27" t="n">
-        <v>52.944</v>
+        <v>54.376</v>
       </c>
       <c r="W27" t="n">
-        <v>-17.563</v>
+        <v>-16.227</v>
       </c>
     </row>
     <row r="28">
@@ -4925,14 +4925,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.34% / +1.66% / -1.90%</t>
+          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.02% / +1.66% / -1.90%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>6.952535948244365</v>
+        <v>7.442493428833585</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4944,7 +4944,7 @@
         <v>88.5</v>
       </c>
       <c r="O28" t="n">
-        <v>45.5</v>
+        <v>46.1</v>
       </c>
       <c r="P28" t="n">
         <v>2.2</v>
@@ -4964,13 +4964,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>4.287</v>
+        <v>4.764</v>
       </c>
       <c r="V28" t="n">
-        <v>11.68</v>
+        <v>12.192</v>
       </c>
       <c r="W28" t="n">
-        <v>-7.505</v>
+        <v>-7.028</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -1.37% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.72% / +2.23% / -3.17%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-16.10801911705971</v>
+        <v>-15.93922200739327</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -772,10 +772,10 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>102.5</v>
+        <v>102.3</v>
       </c>
       <c r="O3" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="P3" t="n">
         <v>6.8</v>
@@ -789,19 +789,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>22.206</v>
+        <v>22.19</v>
       </c>
       <c r="T3" t="n">
-        <v>22.206</v>
+        <v>22.19</v>
       </c>
       <c r="U3" t="n">
-        <v>58.997</v>
+        <v>65.123</v>
       </c>
       <c r="V3" t="n">
-        <v>13.974</v>
+        <v>14.203</v>
       </c>
       <c r="W3" t="n">
-        <v>-45.384</v>
+        <v>-46.706</v>
       </c>
     </row>
     <row r="4">
@@ -820,12 +820,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -847,7 +847,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>63.9</v>
+        <v>63.7</v>
       </c>
       <c r="O4" t="n">
         <v>48.8</v>
@@ -870,13 +870,13 @@
         <v>21.057</v>
       </c>
       <c r="U4" t="n">
-        <v>148.332</v>
+        <v>148.349</v>
       </c>
       <c r="V4" t="n">
         <v>111.543</v>
       </c>
       <c r="W4" t="n">
-        <v>-12.574</v>
+        <v>-12.575</v>
       </c>
     </row>
     <row r="5">
@@ -895,12 +895,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N5" t="n">
-        <v>64.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="O5" t="n">
         <v>46.6</v>
@@ -945,13 +945,13 @@
         <v>19.637</v>
       </c>
       <c r="U5" t="n">
-        <v>114.719</v>
+        <v>114.762</v>
       </c>
       <c r="V5" t="n">
         <v>117.535</v>
       </c>
       <c r="W5" t="n">
-        <v>-15.984</v>
+        <v>-15.987</v>
       </c>
     </row>
     <row r="6">
@@ -970,12 +970,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -1.37% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.72% / +2.23% / -3.17%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-16.10801911705971</v>
+        <v>-15.93922200739327</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1009,10 +1009,10 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>102.5</v>
+        <v>102.3</v>
       </c>
       <c r="O6" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="P6" t="n">
         <v>6.8</v>
@@ -1026,19 +1026,19 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>22.206</v>
+        <v>22.19</v>
       </c>
       <c r="T6" t="n">
-        <v>22.206</v>
+        <v>22.19</v>
       </c>
       <c r="U6" t="n">
-        <v>58.997</v>
+        <v>65.123</v>
       </c>
       <c r="V6" t="n">
-        <v>13.974</v>
+        <v>14.203</v>
       </c>
       <c r="W6" t="n">
-        <v>-45.384</v>
+        <v>-46.706</v>
       </c>
     </row>
     <row r="7">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -1.37% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.72% / +2.23% / -3.17%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.676650582059684</v>
+        <v>-5.486864757619314</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1096,10 +1096,10 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>134.7</v>
+        <v>134.4</v>
       </c>
       <c r="O7" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="P7" t="n">
         <v>3.1</v>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>18.013</v>
+        <v>17.996</v>
       </c>
       <c r="T7" t="n">
-        <v>18.013</v>
+        <v>17.996</v>
       </c>
       <c r="U7" t="n">
-        <v>64.866</v>
+        <v>71.455</v>
       </c>
       <c r="V7" t="n">
-        <v>29.068</v>
+        <v>29.328</v>
       </c>
       <c r="W7" t="n">
-        <v>-36.222</v>
+        <v>-37.249</v>
       </c>
     </row>
     <row r="8">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.25% / +1.61% / -1.61% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.72% / +0.61% / -1.66%</t>
+          <t>ALARK.IS: +0.25% / +1.61% / -1.61% | ENERY.IS: +0.43% / +1.27% / -0.27% | ENJSA.IS: -1.33% / +0.61% / -1.66%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-15.11616313346885</v>
+        <v>-15.15423682865462</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1183,10 +1183,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>192.6</v>
+        <v>192.2</v>
       </c>
       <c r="O8" t="n">
-        <v>46.8</v>
+        <v>47</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>42.186</v>
+        <v>46.07</v>
       </c>
       <c r="V8" t="n">
-        <v>12.7</v>
+        <v>12.649</v>
       </c>
       <c r="W8" t="n">
-        <v>-27.989</v>
+        <v>-28.832</v>
       </c>
     </row>
     <row r="9">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -1.37% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.72% / +2.23% / -3.17%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-16.10801911705971</v>
+        <v>-15.93922200739327</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1270,10 +1270,10 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>102.5</v>
+        <v>102.3</v>
       </c>
       <c r="O9" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="P9" t="n">
         <v>6.8</v>
@@ -1287,19 +1287,19 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>22.206</v>
+        <v>22.19</v>
       </c>
       <c r="T9" t="n">
-        <v>22.206</v>
+        <v>22.19</v>
       </c>
       <c r="U9" t="n">
-        <v>58.997</v>
+        <v>65.123</v>
       </c>
       <c r="V9" t="n">
-        <v>13.974</v>
+        <v>14.203</v>
       </c>
       <c r="W9" t="n">
-        <v>-45.384</v>
+        <v>-46.706</v>
       </c>
     </row>
     <row r="10">
@@ -1318,22 +1318,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KUYAS.IS, TRALT.IS</t>
+          <t>AGHOL.IS, KUYAS.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>KUYAS.IS: 2026-09-03 | TRALT.IS: 2026-09-02</t>
+          <t>AGHOL.IS: 2026-09-07 | KUYAS.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>KUYAS.IS: -2.36% / +0.50% / -2.91% | TRALT.IS: +0.97% / +4.87% / -2.03%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KUYAS.IS: -2.22% / +0.50% / -2.91%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.256737160874479</v>
+        <v>-4.465080385724218</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1357,10 +1357,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>175.3</v>
+        <v>175.4</v>
       </c>
       <c r="O10" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>15.938</v>
+        <v>15.686</v>
       </c>
       <c r="V10" t="n">
-        <v>7.799</v>
+        <v>7.564</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.702</v>
       </c>
     </row>
     <row r="11">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>66.8</v>
+        <v>66.7</v>
       </c>
       <c r="O11" t="n">
         <v>51.9</v>
@@ -1455,13 +1455,13 @@
         <v>7.033</v>
       </c>
       <c r="U11" t="n">
-        <v>84.06999999999999</v>
+        <v>84.07599999999999</v>
       </c>
       <c r="V11" t="n">
         <v>58.898</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.607</v>
+        <v>-1.608</v>
       </c>
     </row>
     <row r="12">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.91% / +20.94% / 0.00% | RALYH.IS: +30.38% / +35.10% / -0.91% | VAKBN.IS: -1.37% / +2.23% / -1.88%</t>
+          <t>BRSAN.IS: +14.23% / +20.94% / 0.00% | RALYH.IS: +31.58% / +35.10% / -0.91% | VAKBN.IS: -1.72% / +2.23% / -3.17%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K12" t="n">
-        <v>13.18787930960317</v>
+        <v>13.53316478460054</v>
       </c>
       <c r="L12" t="n">
         <v>34.56349599547857</v>
@@ -1519,7 +1519,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>69.8</v>
+        <v>69.7</v>
       </c>
       <c r="O12" t="n">
         <v>44</v>
@@ -1542,13 +1542,13 @@
         <v>23.777</v>
       </c>
       <c r="U12" t="n">
-        <v>49.703</v>
+        <v>50.16</v>
       </c>
       <c r="V12" t="n">
-        <v>43.44</v>
+        <v>43.878</v>
       </c>
       <c r="W12" t="n">
-        <v>-10.335</v>
+        <v>-9.878</v>
       </c>
     </row>
     <row r="13">
@@ -1562,80 +1562,68 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>TRALT.IS</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>TRALT.IS: 2026-09-02</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>25.65141339163128</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>TRALT.IS: +0.97% / +4.87% / -2.03%</t>
-        </is>
-      </c>
+        <v>7.610984631351814</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>-5.044425134583063</v>
+        <v>-16.01405991857144</v>
       </c>
       <c r="K13" t="n">
-        <v>10.27950726719542</v>
+        <v>9.964713536822334</v>
       </c>
       <c r="L13" t="n">
-        <v>9.344627019167174</v>
+        <v>19.17000314054332</v>
       </c>
       <c r="M13" t="n">
-        <v>66.66666666666666</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N13" t="n">
-        <v>58.9</v>
+        <v>59.8</v>
       </c>
       <c r="O13" t="n">
-        <v>51.3</v>
+        <v>43.8</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>12.101</v>
+        <v>27.346</v>
       </c>
       <c r="T13" t="n">
-        <v>12.101</v>
+        <v>27.346</v>
       </c>
       <c r="U13" t="n">
-        <v>28.665</v>
+        <v>-5.214</v>
       </c>
       <c r="V13" t="n">
-        <v>34.037</v>
+        <v>7.691</v>
       </c>
       <c r="W13" t="n">
-        <v>-9.113</v>
+        <v>-23.855</v>
       </c>
     </row>
     <row r="14">
@@ -1649,45 +1637,45 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>55.72500398673659</v>
+        <v>21.76975999384314</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>-8.265155599016705</v>
+        <v>-28.45194989279852</v>
       </c>
       <c r="K14" t="n">
-        <v>4.847595630925805</v>
+        <v>4.847592357308117</v>
       </c>
       <c r="L14" t="n">
-        <v>22.73189287884475</v>
+        <v>29.12044822069533</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>58.9</v>
+        <v>62.8</v>
       </c>
       <c r="O14" t="n">
-        <v>44.5</v>
+        <v>43.3</v>
       </c>
       <c r="P14" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1698,19 +1686,19 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>25.345</v>
+        <v>25.589</v>
       </c>
       <c r="T14" t="n">
-        <v>25.345</v>
+        <v>25.589</v>
       </c>
       <c r="U14" t="n">
-        <v>77.732</v>
+        <v>83.911</v>
       </c>
       <c r="V14" t="n">
-        <v>93.19</v>
+        <v>103.043</v>
       </c>
       <c r="W14" t="n">
-        <v>-29.648</v>
+        <v>-30.679</v>
       </c>
     </row>
     <row r="16">
@@ -1855,12 +1843,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1878,14 +1866,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -1.37% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.72% / +2.23% / -3.17%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-16.10801911705971</v>
+        <v>-15.93922200739327</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1894,10 +1882,10 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>102.5</v>
+        <v>102.3</v>
       </c>
       <c r="O18" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="P18" t="n">
         <v>6.8</v>
@@ -1911,19 +1899,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>22.206</v>
+        <v>22.19</v>
       </c>
       <c r="T18" t="n">
-        <v>22.206</v>
+        <v>22.19</v>
       </c>
       <c r="U18" t="n">
-        <v>58.997</v>
+        <v>65.123</v>
       </c>
       <c r="V18" t="n">
-        <v>13.974</v>
+        <v>14.203</v>
       </c>
       <c r="W18" t="n">
-        <v>-45.384</v>
+        <v>-46.706</v>
       </c>
     </row>
     <row r="19">
@@ -1944,12 +1932,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1971,7 +1959,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>63.9</v>
+        <v>63.7</v>
       </c>
       <c r="O19" t="n">
         <v>48.8</v>
@@ -1994,13 +1982,13 @@
         <v>21.057</v>
       </c>
       <c r="U19" t="n">
-        <v>148.332</v>
+        <v>148.349</v>
       </c>
       <c r="V19" t="n">
         <v>111.543</v>
       </c>
       <c r="W19" t="n">
-        <v>-12.574</v>
+        <v>-12.575</v>
       </c>
     </row>
     <row r="20">
@@ -2021,12 +2009,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2048,7 +2036,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>64.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="O20" t="n">
         <v>46.6</v>
@@ -2071,13 +2059,13 @@
         <v>19.637</v>
       </c>
       <c r="U20" t="n">
-        <v>114.719</v>
+        <v>114.762</v>
       </c>
       <c r="V20" t="n">
         <v>117.535</v>
       </c>
       <c r="W20" t="n">
-        <v>-15.984</v>
+        <v>-15.987</v>
       </c>
     </row>
     <row r="21">
@@ -2098,12 +2086,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2121,14 +2109,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.25% / +1.61% / -1.61% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: -0.72% / +0.61% / -1.66%</t>
+          <t>ALARK.IS: +0.25% / +1.61% / -1.61% | ENERY.IS: +0.43% / +1.27% / -0.27% | ENJSA.IS: -1.33% / +0.61% / -1.66%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-15.11616313346885</v>
+        <v>-15.15423682865462</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2137,10 +2125,10 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>192.6</v>
+        <v>192.2</v>
       </c>
       <c r="O21" t="n">
-        <v>46.8</v>
+        <v>47</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2160,13 +2148,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>42.186</v>
+        <v>46.07</v>
       </c>
       <c r="V21" t="n">
-        <v>12.7</v>
+        <v>12.649</v>
       </c>
       <c r="W21" t="n">
-        <v>-27.989</v>
+        <v>-28.832</v>
       </c>
     </row>
     <row r="22">
@@ -2187,12 +2175,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2210,14 +2198,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +3.76% / -2.26% | VAKBN.IS: -1.37% / +2.23% / -1.88%</t>
+          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.72% / +2.23% / -3.17%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.676650582059684</v>
+        <v>-5.486864757619314</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2226,10 +2214,10 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>134.7</v>
+        <v>134.4</v>
       </c>
       <c r="O22" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="P22" t="n">
         <v>3.1</v>
@@ -2243,25 +2231,25 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>18.013</v>
+        <v>17.996</v>
       </c>
       <c r="T22" t="n">
-        <v>18.013</v>
+        <v>17.996</v>
       </c>
       <c r="U22" t="n">
-        <v>64.866</v>
+        <v>71.455</v>
       </c>
       <c r="V22" t="n">
-        <v>29.068</v>
+        <v>29.328</v>
       </c>
       <c r="W22" t="n">
-        <v>-36.222</v>
+        <v>-37.249</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2271,45 +2259,45 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|coklu_zarf</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>55.72500398673659</v>
+        <v>50.58108284302749</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>-8.265155599016705</v>
+        <v>13.3215021172385</v>
       </c>
       <c r="K23" t="n">
-        <v>4.847595630925805</v>
+        <v>-4.400004582905126e-07</v>
       </c>
       <c r="L23" t="n">
-        <v>22.73189287884475</v>
+        <v>5.668150937989602</v>
       </c>
       <c r="M23" t="n">
-        <v>100</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N23" t="n">
-        <v>58.9</v>
+        <v>66.7</v>
       </c>
       <c r="O23" t="n">
-        <v>44.5</v>
+        <v>51.9</v>
       </c>
       <c r="P23" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2320,19 +2308,19 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>25.345</v>
+        <v>7.033</v>
       </c>
       <c r="T23" t="n">
-        <v>25.345</v>
+        <v>7.033</v>
       </c>
       <c r="U23" t="n">
-        <v>77.732</v>
+        <v>84.07599999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>93.19</v>
+        <v>58.898</v>
       </c>
       <c r="W23" t="n">
-        <v>-29.648</v>
+        <v>-1.608</v>
       </c>
     </row>
     <row r="24">
@@ -2343,73 +2331,85 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|coklu_zarf</t>
+          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, KUYAS.IS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-09-07 | KUYAS.IS: 2026-09-03</t>
+        </is>
+      </c>
       <c r="H24" t="n">
-        <v>50.58108284302749</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>23.02092795860866</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KUYAS.IS: -2.22% / +0.50% / -2.91%</t>
+        </is>
+      </c>
       <c r="J24" t="n">
-        <v>13.3215021172385</v>
+        <v>12.86015270141232</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.400004582905126e-07</v>
+        <v>-4.465080385724218</v>
       </c>
       <c r="L24" t="n">
-        <v>5.668150937989602</v>
+        <v>4.543450519200398</v>
       </c>
       <c r="M24" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N24" t="n">
-        <v>66.8</v>
+        <v>175.4</v>
       </c>
       <c r="O24" t="n">
-        <v>51.9</v>
+        <v>48.5</v>
       </c>
       <c r="P24" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>7.033</v>
+        <v>10.072</v>
       </c>
       <c r="T24" t="n">
-        <v>7.033</v>
+        <v>10.072</v>
       </c>
       <c r="U24" t="n">
-        <v>84.06999999999999</v>
+        <v>15.686</v>
       </c>
       <c r="V24" t="n">
-        <v>58.898</v>
+        <v>7.564</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.607</v>
+        <v>-9.702</v>
       </c>
     </row>
     <row r="25">
@@ -2420,151 +2420,139 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
+          <t>T1_genislik_skor|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>TRALT.IS</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>TRALT.IS: 2026-09-02</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>25.65141339163128</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>TRALT.IS: +0.97% / +4.87% / -2.03%</t>
-        </is>
-      </c>
+        <v>21.76975999384314</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>-5.044425134583063</v>
+        <v>-28.45194989279852</v>
       </c>
       <c r="K25" t="n">
-        <v>10.27950726719542</v>
+        <v>4.847592357308117</v>
       </c>
       <c r="L25" t="n">
-        <v>9.344627019167174</v>
+        <v>29.12044822069533</v>
       </c>
       <c r="M25" t="n">
-        <v>66.66666666666666</v>
+        <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>58.9</v>
+        <v>62.8</v>
       </c>
       <c r="O25" t="n">
-        <v>51.3</v>
+        <v>43.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>12.101</v>
+        <v>25.589</v>
       </c>
       <c r="T25" t="n">
-        <v>12.101</v>
+        <v>25.589</v>
       </c>
       <c r="U25" t="n">
-        <v>28.665</v>
+        <v>83.911</v>
       </c>
       <c r="V25" t="n">
-        <v>34.037</v>
+        <v>103.043</v>
       </c>
       <c r="W25" t="n">
-        <v>-9.113</v>
+        <v>-30.679</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KUYAS.IS, TRALT.IS</t>
+          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>KUYAS.IS: 2026-09-03 | TRALT.IS: 2026-09-02</t>
+          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>23.02092795860866</v>
+        <v>13.58351811074014</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>KUYAS.IS: -2.36% / +0.50% / -2.91% | TRALT.IS: +0.97% / +4.87% / -2.03%</t>
+          <t>BRSAN.IS: +14.23% / +20.94% / 0.00% | RALYH.IS: +31.58% / +35.10% / -0.91% | VAKBN.IS: -1.72% / +2.23% / -3.17%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>12.86015270141232</v>
+        <v>-10.39434387728287</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.256737160874479</v>
+        <v>13.53316478460054</v>
       </c>
       <c r="L26" t="n">
-        <v>4.543450519200398</v>
+        <v>34.56349599547857</v>
       </c>
       <c r="M26" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>175.3</v>
+        <v>69.7</v>
       </c>
       <c r="O26" t="n">
-        <v>48.9</v>
+        <v>44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.9</v>
+        <v>6.1</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2572,22 +2560,22 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>10.072</v>
+        <v>23.777</v>
       </c>
       <c r="T26" t="n">
-        <v>10.072</v>
+        <v>23.777</v>
       </c>
       <c r="U26" t="n">
-        <v>15.938</v>
+        <v>50.16</v>
       </c>
       <c r="V26" t="n">
-        <v>7.799</v>
+        <v>43.878</v>
       </c>
       <c r="W26" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.878</v>
       </c>
     </row>
     <row r="27">
@@ -2598,85 +2586,73 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>13.58351811074014</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +13.91% / +20.94% / 0.00% | RALYH.IS: +30.38% / +35.10% / -0.91% | VAKBN.IS: -1.37% / +2.23% / -1.88%</t>
-        </is>
-      </c>
+        <v>7.610984631351814</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>-10.39434387728287</v>
+        <v>-16.01405991857144</v>
       </c>
       <c r="K27" t="n">
-        <v>13.18787930960317</v>
+        <v>9.964713536822334</v>
       </c>
       <c r="L27" t="n">
-        <v>34.56349599547857</v>
+        <v>19.17000314054332</v>
       </c>
       <c r="M27" t="n">
-        <v>77.77777777777779</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N27" t="n">
-        <v>69.8</v>
+        <v>59.8</v>
       </c>
       <c r="O27" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="P27" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>23.777</v>
+        <v>27.346</v>
       </c>
       <c r="T27" t="n">
-        <v>23.777</v>
+        <v>27.346</v>
       </c>
       <c r="U27" t="n">
-        <v>49.703</v>
+        <v>-5.214</v>
       </c>
       <c r="V27" t="n">
-        <v>43.44</v>
+        <v>7.691</v>
       </c>
       <c r="W27" t="n">
-        <v>-10.335</v>
+        <v>-23.855</v>
       </c>
     </row>
   </sheetData>
@@ -2866,12 +2842,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2889,14 +2865,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: +0.43% / +1.28% / -0.26%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4336128230461478</v>
+        <v>0.6610658042645046</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2905,10 +2881,10 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="O3" t="n">
-        <v>44.4</v>
+        <v>44.9</v>
       </c>
       <c r="P3" t="n">
         <v>4.3</v>
@@ -2928,13 +2904,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>255.486</v>
+        <v>277.336</v>
       </c>
       <c r="V3" t="n">
-        <v>102.321</v>
+        <v>102.779</v>
       </c>
       <c r="W3" t="n">
-        <v>-37.966</v>
+        <v>-39.356</v>
       </c>
     </row>
     <row r="4">
@@ -2953,22 +2929,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, ENERY.IS, ENJSA.IS, SOKM.IS</t>
+          <t>ALARK.IS, ALTNY.IS, BRSAN.IS, ENERY.IS, SOKM.IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | BRSAN.IS: 2026-09-07 | ENERY.IS: 2026-09-02 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2976,14 +2952,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.12% / +5.52% / -2.77% | ENJSA.IS: +3.25% / +4.63% / -0.09% | SOKM.IS: -0.02% / +0.69% / -1.98%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.26% / +0.66% / -1.12% | BRSAN.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.60% / +6.47% / -2.77% | SOKM.IS: +0.50% / +1.21% / -1.98%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.0435317800327</v>
+        <v>-10.02390614601206</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2992,13 +2968,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>118.8</v>
+        <v>119.1</v>
       </c>
       <c r="O4" t="n">
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
       <c r="P4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -3015,13 +2991,13 @@
         <v>25.08</v>
       </c>
       <c r="U4" t="n">
-        <v>57.248</v>
+        <v>57.295</v>
       </c>
       <c r="V4" t="n">
-        <v>21.029</v>
+        <v>21.056</v>
       </c>
       <c r="W4" t="n">
-        <v>-52.198</v>
+        <v>-52.168</v>
       </c>
     </row>
     <row r="5">
@@ -3040,12 +3016,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3063,14 +3039,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: +0.43% / +1.28% / -0.26%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4135069682739134</v>
+        <v>0.6409144155671731</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3079,10 +3055,10 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>42.4</v>
+        <v>43</v>
       </c>
       <c r="P5" t="n">
         <v>4.7</v>
@@ -3102,13 +3078,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>252.749</v>
+        <v>274.465</v>
       </c>
       <c r="V5" t="n">
-        <v>84.246</v>
+        <v>84.663</v>
       </c>
       <c r="W5" t="n">
-        <v>-37.629</v>
+        <v>-39.009</v>
       </c>
     </row>
     <row r="6">
@@ -3127,12 +3103,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3150,14 +3126,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.05% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | ENERY.IS: +5.12% / +5.52% / -2.77% | SOKM.IS: -0.02% / +0.69% / -1.98% | TKFEN.IS: +12.75% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +13.37% / +20.03% / -1.13% | CANTE.IS: +8.64% / +15.84% / -2.80% | ENERY.IS: +5.60% / +6.47% / -2.77% | SOKM.IS: +0.50% / +1.21% / -1.98% | TKFEN.IS: +12.97% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.819824308406277</v>
+        <v>-8.433019611033687</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3166,10 +3142,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>139.2</v>
+        <v>138.9</v>
       </c>
       <c r="O6" t="n">
-        <v>42.5</v>
+        <v>42.9</v>
       </c>
       <c r="P6" t="n">
         <v>5.7</v>
@@ -3189,13 +3165,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>24.068</v>
+        <v>24.594</v>
       </c>
       <c r="V6" t="n">
-        <v>13.361</v>
+        <v>13.842</v>
       </c>
       <c r="W6" t="n">
-        <v>-41.057</v>
+        <v>-40.53</v>
       </c>
     </row>
     <row r="7">
@@ -3214,22 +3190,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, ENERY.IS, ENJSA.IS, SOKM.IS</t>
+          <t>ALARK.IS, ALTNY.IS, BRSAN.IS, ENERY.IS, SOKM.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | BRSAN.IS: 2026-09-07 | ENERY.IS: 2026-09-02 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3237,14 +3213,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.12% / +5.52% / -2.77% | ENJSA.IS: +3.25% / +4.63% / -0.09% | SOKM.IS: -0.02% / +0.69% / -1.98%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.26% / +0.66% / -1.12% | BRSAN.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.60% / +6.47% / -2.77% | SOKM.IS: +0.50% / +1.21% / -1.98%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.0435317800327</v>
+        <v>-10.02390614601206</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3253,13 +3229,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>118.8</v>
+        <v>119.1</v>
       </c>
       <c r="O7" t="n">
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
       <c r="P7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -3276,13 +3252,13 @@
         <v>25.08</v>
       </c>
       <c r="U7" t="n">
-        <v>57.248</v>
+        <v>57.295</v>
       </c>
       <c r="V7" t="n">
-        <v>21.029</v>
+        <v>21.056</v>
       </c>
       <c r="W7" t="n">
-        <v>-52.198</v>
+        <v>-52.168</v>
       </c>
     </row>
     <row r="8">
@@ -3301,12 +3277,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3324,14 +3300,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.05% / +20.03% / -1.13% | CANTE.IS: -0.02% / +3.71% / -2.30% | ENERY.IS: +5.12% / +5.52% / -2.77%</t>
+          <t>BRSAN.IS: +13.37% / +20.03% / -1.13% | CANTE.IS: +0.73% / +3.71% / -2.30% | ENERY.IS: +5.60% / +6.47% / -2.77%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.224545069392247</v>
+        <v>-0.8232801196845552</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3340,10 +3316,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>153.6</v>
+        <v>153.3</v>
       </c>
       <c r="O8" t="n">
-        <v>42.1</v>
+        <v>42.4</v>
       </c>
       <c r="P8" t="n">
         <v>4.2</v>
@@ -3363,13 +3339,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>23.731</v>
+        <v>26.262</v>
       </c>
       <c r="V8" t="n">
-        <v>3.527</v>
+        <v>3.947</v>
       </c>
       <c r="W8" t="n">
-        <v>-29.427</v>
+        <v>-29.396</v>
       </c>
     </row>
     <row r="9">
@@ -3388,12 +3364,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3415,7 +3391,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N9" t="n">
-        <v>75.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="O9" t="n">
         <v>49.3</v>
@@ -3438,13 +3414,13 @@
         <v>13.28</v>
       </c>
       <c r="U9" t="n">
-        <v>9.128</v>
+        <v>9.141</v>
       </c>
       <c r="V9" t="n">
         <v>-0.962</v>
       </c>
       <c r="W9" t="n">
-        <v>-16.712</v>
+        <v>-16.714</v>
       </c>
     </row>
     <row r="10">
@@ -3463,12 +3439,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3486,14 +3462,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | CANTE.IS: -0.02% / +3.71% / -2.30% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | CANTE.IS: +0.73% / +3.71% / -2.30% | ENERY.IS: +0.43% / +1.28% / -0.26%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.803376591707262</v>
+        <v>-1.484627807993466</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3502,10 +3478,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>114.3</v>
+        <v>114.1</v>
       </c>
       <c r="O10" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
       <c r="P10" t="n">
         <v>2.4</v>
@@ -3525,13 +3501,13 @@
         <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>12.321</v>
+        <v>12.7</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.216</v>
+        <v>-0.895</v>
       </c>
       <c r="W10" t="n">
-        <v>-25.832</v>
+        <v>-25.47</v>
       </c>
     </row>
     <row r="11">
@@ -3550,22 +3526,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, ENERY.IS, ENJSA.IS, SOKM.IS</t>
+          <t>ALARK.IS, ALTNY.IS, BRSAN.IS, ENERY.IS, SOKM.IS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-04 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | BRSAN.IS: 2026-09-07 | ENERY.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -3573,14 +3549,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +3.25% / +4.63% / -0.09% | SOKM.IS: -0.02% / +0.69% / -1.98%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.26% / +0.66% / -1.12% | BRSAN.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +0.43% / +1.28% / -0.26% | SOKM.IS: +0.50% / +1.21% / -1.98%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.967139605338071</v>
+        <v>-9.954577013247556</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3589,10 +3565,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>179.9</v>
+        <v>180.1</v>
       </c>
       <c r="O11" t="n">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
@@ -3612,13 +3588,13 @@
         <v>23.754</v>
       </c>
       <c r="U11" t="n">
-        <v>33.236</v>
+        <v>33.265</v>
       </c>
       <c r="V11" t="n">
-        <v>7.964</v>
+        <v>7.98</v>
       </c>
       <c r="W11" t="n">
-        <v>-41.156</v>
+        <v>-41.141</v>
       </c>
     </row>
     <row r="12">
@@ -3637,12 +3613,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3660,14 +3636,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.05% / +20.03% / -1.13% | TKFEN.IS: +12.75% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +13.37% / +20.03% / -1.13% | TKFEN.IS: +12.97% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>10.79038159414842</v>
+        <v>11.04870502319497</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3676,7 +3652,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="O12" t="n">
         <v>43.3</v>
@@ -3699,13 +3675,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>44.061</v>
+        <v>44.397</v>
       </c>
       <c r="V12" t="n">
-        <v>54.376</v>
+        <v>54.736</v>
       </c>
       <c r="W12" t="n">
-        <v>-16.227</v>
+        <v>-15.891</v>
       </c>
     </row>
     <row r="13">
@@ -3719,57 +3695,57 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CVKMD.IS, FENER.IS</t>
+          <t>ALARK.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CVKMD.IS: 2026-09-04 | FENER.IS: 2026-09-01</t>
+          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-0.49388395046156</v>
+        <v>32.90971238010212</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.02% / +1.66% / -1.90%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: +5.60% / +6.47% / -2.77%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-19.60937535624424</v>
+        <v>3.175499702073514</v>
       </c>
       <c r="K13" t="n">
-        <v>7.442493428833585</v>
+        <v>4.794038014733437</v>
       </c>
       <c r="L13" t="n">
-        <v>19.61961325199098</v>
+        <v>18.99889339779883</v>
       </c>
       <c r="M13" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>88.5</v>
+        <v>43.2</v>
       </c>
       <c r="O13" t="n">
-        <v>46.1</v>
+        <v>50.6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3780,19 +3756,19 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>18.132</v>
+        <v>18.999</v>
       </c>
       <c r="T13" t="n">
-        <v>18.132</v>
+        <v>16.472</v>
       </c>
       <c r="U13" t="n">
-        <v>4.764</v>
+        <v>22.017</v>
       </c>
       <c r="V13" t="n">
-        <v>12.192</v>
+        <v>20.126</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.028</v>
+        <v>-11.857</v>
       </c>
     </row>
     <row r="14">
@@ -3806,57 +3782,57 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ALARK.IS, ENERY.IS</t>
+          <t>CVKMD.IS, FENER.IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-02</t>
+          <t>CVKMD.IS: 2026-09-04 | FENER.IS: 2026-09-07</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>32.90971238010212</v>
+        <v>-0.49388395046156</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: +5.12% / +5.52% / -2.77%</t>
+          <t>CVKMD.IS: +0.11% / +0.64% / -0.19% | FENER.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3.175499702073514</v>
+        <v>-19.60937535624424</v>
       </c>
       <c r="K14" t="n">
-        <v>4.560136784755486</v>
+        <v>4.656680042638128</v>
       </c>
       <c r="L14" t="n">
-        <v>18.99889339779883</v>
+        <v>19.61961325199098</v>
       </c>
       <c r="M14" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N14" t="n">
-        <v>43.2</v>
+        <v>88.8</v>
       </c>
       <c r="O14" t="n">
-        <v>50.6</v>
+        <v>46.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3867,19 +3843,19 @@
         <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>18.999</v>
+        <v>18.132</v>
       </c>
       <c r="T14" t="n">
-        <v>16.472</v>
+        <v>18.132</v>
       </c>
       <c r="U14" t="n">
-        <v>21.72</v>
+        <v>2.048</v>
       </c>
       <c r="V14" t="n">
-        <v>19.858</v>
+        <v>9.282999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>-12.127</v>
+        <v>-9.744</v>
       </c>
     </row>
     <row r="16">
@@ -4024,12 +4000,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4047,14 +4023,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: +0.43% / +1.28% / -0.26%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4336128230461478</v>
+        <v>0.6610658042645046</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4063,10 +4039,10 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>92.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="O18" t="n">
-        <v>44.4</v>
+        <v>44.9</v>
       </c>
       <c r="P18" t="n">
         <v>4.3</v>
@@ -4086,13 +4062,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>255.486</v>
+        <v>277.336</v>
       </c>
       <c r="V18" t="n">
-        <v>102.321</v>
+        <v>102.779</v>
       </c>
       <c r="W18" t="n">
-        <v>-37.966</v>
+        <v>-39.356</v>
       </c>
     </row>
     <row r="19">
@@ -4113,22 +4089,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, ENERY.IS, ENJSA.IS, SOKM.IS</t>
+          <t>ALARK.IS, ALTNY.IS, BRSAN.IS, ENERY.IS, SOKM.IS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-02 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | BRSAN.IS: 2026-09-07 | ENERY.IS: 2026-09-02 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -4136,14 +4112,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.12% / +5.52% / -2.77% | ENJSA.IS: +3.25% / +4.63% / -0.09% | SOKM.IS: -0.02% / +0.69% / -1.98%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.26% / +0.66% / -1.12% | BRSAN.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.60% / +6.47% / -2.77% | SOKM.IS: +0.50% / +1.21% / -1.98%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.0435317800327</v>
+        <v>-10.02390614601206</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4152,13 +4128,13 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>118.8</v>
+        <v>119.1</v>
       </c>
       <c r="O19" t="n">
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
       <c r="P19" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -4175,13 +4151,13 @@
         <v>25.08</v>
       </c>
       <c r="U19" t="n">
-        <v>57.248</v>
+        <v>57.295</v>
       </c>
       <c r="V19" t="n">
-        <v>21.029</v>
+        <v>21.056</v>
       </c>
       <c r="W19" t="n">
-        <v>-52.198</v>
+        <v>-52.168</v>
       </c>
     </row>
     <row r="20">
@@ -4202,12 +4178,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4225,14 +4201,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: +0.43% / +1.28% / -0.26%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4135069682739134</v>
+        <v>0.6409144155671731</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4241,10 +4217,10 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>42.4</v>
+        <v>43</v>
       </c>
       <c r="P20" t="n">
         <v>4.7</v>
@@ -4264,13 +4240,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>252.749</v>
+        <v>274.465</v>
       </c>
       <c r="V20" t="n">
-        <v>84.246</v>
+        <v>84.663</v>
       </c>
       <c r="W20" t="n">
-        <v>-37.629</v>
+        <v>-39.009</v>
       </c>
     </row>
     <row r="21">
@@ -4291,22 +4267,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ALARK.IS, ALTNY.IS, ENERY.IS, ENJSA.IS, SOKM.IS</t>
+          <t>ALARK.IS, ALTNY.IS, BRSAN.IS, ENERY.IS, SOKM.IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | ENERY.IS: 2026-09-04 | ENJSA.IS: 2026-08-31 | SOKM.IS: 2026-09-03</t>
+          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | BRSAN.IS: 2026-09-07 | ENERY.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -4314,14 +4290,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.02% / +0.00% / 0.00% | ENJSA.IS: +3.25% / +4.63% / -0.09% | SOKM.IS: -0.02% / +0.69% / -1.98%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.26% / +0.66% / -1.12% | BRSAN.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +0.43% / +1.28% / -0.26% | SOKM.IS: +0.50% / +1.21% / -1.98%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.967139605338071</v>
+        <v>-9.954577013247556</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4330,10 +4306,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>179.9</v>
+        <v>180.1</v>
       </c>
       <c r="O21" t="n">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
@@ -4353,13 +4329,13 @@
         <v>23.754</v>
       </c>
       <c r="U21" t="n">
-        <v>33.236</v>
+        <v>33.265</v>
       </c>
       <c r="V21" t="n">
-        <v>7.964</v>
+        <v>7.98</v>
       </c>
       <c r="W21" t="n">
-        <v>-41.156</v>
+        <v>-41.141</v>
       </c>
     </row>
     <row r="22">
@@ -4380,12 +4356,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4403,14 +4379,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.05% / +20.03% / -1.13% | CANTE.IS: +7.83% / +15.84% / -2.80% | ENERY.IS: +5.12% / +5.52% / -2.77% | SOKM.IS: -0.02% / +0.69% / -1.98% | TKFEN.IS: +12.75% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +13.37% / +20.03% / -1.13% | CANTE.IS: +8.64% / +15.84% / -2.80% | ENERY.IS: +5.60% / +6.47% / -2.77% | SOKM.IS: +0.50% / +1.21% / -1.98% | TKFEN.IS: +12.97% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-8.819824308406277</v>
+        <v>-8.433019611033687</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4419,10 +4395,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>139.2</v>
+        <v>138.9</v>
       </c>
       <c r="O22" t="n">
-        <v>42.5</v>
+        <v>42.9</v>
       </c>
       <c r="P22" t="n">
         <v>5.7</v>
@@ -4442,13 +4418,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>24.068</v>
+        <v>24.594</v>
       </c>
       <c r="V22" t="n">
-        <v>13.361</v>
+        <v>13.842</v>
       </c>
       <c r="W22" t="n">
-        <v>-41.057</v>
+        <v>-40.53</v>
       </c>
     </row>
     <row r="23">
@@ -4469,12 +4445,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4492,14 +4468,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.05% / +20.03% / -1.13% | CANTE.IS: -0.02% / +3.71% / -2.30% | ENERY.IS: +5.12% / +5.52% / -2.77%</t>
+          <t>BRSAN.IS: +13.37% / +20.03% / -1.13% | CANTE.IS: +0.73% / +3.71% / -2.30% | ENERY.IS: +5.60% / +6.47% / -2.77%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.224545069392247</v>
+        <v>-0.8232801196845552</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4508,10 +4484,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>153.6</v>
+        <v>153.3</v>
       </c>
       <c r="O23" t="n">
-        <v>42.1</v>
+        <v>42.4</v>
       </c>
       <c r="P23" t="n">
         <v>4.2</v>
@@ -4531,13 +4507,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>23.731</v>
+        <v>26.262</v>
       </c>
       <c r="V23" t="n">
-        <v>3.527</v>
+        <v>3.947</v>
       </c>
       <c r="W23" t="n">
-        <v>-29.427</v>
+        <v>-29.396</v>
       </c>
     </row>
     <row r="24">
@@ -4558,12 +4534,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4581,14 +4557,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | CANTE.IS: -0.02% / +3.71% / -2.30% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | CANTE.IS: +0.73% / +3.71% / -2.30% | ENERY.IS: +0.43% / +1.28% / -0.26%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.803376591707262</v>
+        <v>-1.484627807993466</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4597,10 +4573,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>114.3</v>
+        <v>114.1</v>
       </c>
       <c r="O24" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
       <c r="P24" t="n">
         <v>2.4</v>
@@ -4620,13 +4596,13 @@
         <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>12.321</v>
+        <v>12.7</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.216</v>
+        <v>-0.895</v>
       </c>
       <c r="W24" t="n">
-        <v>-25.832</v>
+        <v>-25.47</v>
       </c>
     </row>
     <row r="25">
@@ -4637,7 +4613,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4647,12 +4623,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4670,14 +4646,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: +5.12% / +5.52% / -2.77%</t>
+          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: +5.60% / +6.47% / -2.77%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>3.175499702073514</v>
       </c>
       <c r="K25" t="n">
-        <v>4.560136784755486</v>
+        <v>4.794038014733437</v>
       </c>
       <c r="L25" t="n">
         <v>18.99889339779883</v>
@@ -4709,13 +4685,13 @@
         <v>16.472</v>
       </c>
       <c r="U25" t="n">
-        <v>21.72</v>
+        <v>22.017</v>
       </c>
       <c r="V25" t="n">
-        <v>19.858</v>
+        <v>20.126</v>
       </c>
       <c r="W25" t="n">
-        <v>-12.127</v>
+        <v>-11.857</v>
       </c>
     </row>
     <row r="26">
@@ -4736,12 +4712,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -4763,7 +4739,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>75.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="O26" t="n">
         <v>49.3</v>
@@ -4786,13 +4762,13 @@
         <v>13.28</v>
       </c>
       <c r="U26" t="n">
-        <v>9.128</v>
+        <v>9.141</v>
       </c>
       <c r="V26" t="n">
         <v>-0.962</v>
       </c>
       <c r="W26" t="n">
-        <v>-16.712</v>
+        <v>-16.714</v>
       </c>
     </row>
     <row r="27">
@@ -4813,12 +4789,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4836,14 +4812,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.05% / +20.03% / -1.13% | TKFEN.IS: +12.75% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +13.37% / +20.03% / -1.13% | TKFEN.IS: +12.97% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>10.79038159414842</v>
+        <v>11.04870502319497</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4852,7 +4828,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N27" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="O27" t="n">
         <v>43.3</v>
@@ -4875,13 +4851,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>44.061</v>
+        <v>44.397</v>
       </c>
       <c r="V27" t="n">
-        <v>54.376</v>
+        <v>54.736</v>
       </c>
       <c r="W27" t="n">
-        <v>-16.227</v>
+        <v>-15.891</v>
       </c>
     </row>
     <row r="28">
@@ -4892,7 +4868,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4902,14 +4878,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>CVKMD.IS, FENER.IS</t>
@@ -4917,7 +4893,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CVKMD.IS: 2026-09-04 | FENER.IS: 2026-09-01</t>
+          <t>CVKMD.IS: 2026-09-04 | FENER.IS: 2026-09-07</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4925,14 +4901,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CVKMD.IS: -0.02% / +0.00% / 0.00% | FENER.IS: -0.02% / +1.66% / -1.90%</t>
+          <t>CVKMD.IS: +0.11% / +0.64% / -0.19% | FENER.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>7.442493428833585</v>
+        <v>4.656680042638128</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4941,10 +4917,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N28" t="n">
-        <v>88.5</v>
+        <v>88.8</v>
       </c>
       <c r="O28" t="n">
-        <v>46.1</v>
+        <v>46.4</v>
       </c>
       <c r="P28" t="n">
         <v>2.2</v>
@@ -4964,13 +4940,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>4.764</v>
+        <v>2.048</v>
       </c>
       <c r="V28" t="n">
-        <v>12.192</v>
+        <v>9.282999999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>-7.028</v>
+        <v>-9.744</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.72% / +2.23% / -3.17%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -2.26% | VAKBN.IS: -1.90% / +2.23% / -3.17%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-15.93922200739327</v>
+        <v>-16.96617214553331</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -775,7 +775,7 @@
         <v>102.3</v>
       </c>
       <c r="O3" t="n">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="P3" t="n">
         <v>6.8</v>
@@ -789,19 +789,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>22.19</v>
+        <v>23.001</v>
       </c>
       <c r="T3" t="n">
-        <v>22.19</v>
+        <v>23.001</v>
       </c>
       <c r="U3" t="n">
-        <v>65.123</v>
+        <v>63.106</v>
       </c>
       <c r="V3" t="n">
-        <v>14.203</v>
+        <v>12.808</v>
       </c>
       <c r="W3" t="n">
-        <v>-46.706</v>
+        <v>-48.723</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.72% / +2.23% / -3.17%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -2.26% | VAKBN.IS: -1.90% / +2.23% / -3.17%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-15.93922200739327</v>
+        <v>-16.96617214553331</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1012,7 +1012,7 @@
         <v>102.3</v>
       </c>
       <c r="O6" t="n">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="P6" t="n">
         <v>6.8</v>
@@ -1026,19 +1026,19 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>22.19</v>
+        <v>23.001</v>
       </c>
       <c r="T6" t="n">
-        <v>22.19</v>
+        <v>23.001</v>
       </c>
       <c r="U6" t="n">
-        <v>65.123</v>
+        <v>63.106</v>
       </c>
       <c r="V6" t="n">
-        <v>14.203</v>
+        <v>12.808</v>
       </c>
       <c r="W6" t="n">
-        <v>-46.706</v>
+        <v>-48.723</v>
       </c>
     </row>
     <row r="7">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.72% / +2.23% / -3.17%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -2.26% | VAKBN.IS: -1.90% / +2.23% / -3.17%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.486864757619314</v>
+        <v>-6.641508809352303</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1099,7 +1099,7 @@
         <v>134.4</v>
       </c>
       <c r="O7" t="n">
-        <v>47.4</v>
+        <v>47.1</v>
       </c>
       <c r="P7" t="n">
         <v>3.1</v>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>17.996</v>
+        <v>18.852</v>
       </c>
       <c r="T7" t="n">
-        <v>17.996</v>
+        <v>18.852</v>
       </c>
       <c r="U7" t="n">
-        <v>71.455</v>
+        <v>69.36</v>
       </c>
       <c r="V7" t="n">
-        <v>29.328</v>
+        <v>27.748</v>
       </c>
       <c r="W7" t="n">
-        <v>-37.249</v>
+        <v>-39.344</v>
       </c>
     </row>
     <row r="8">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.25% / +1.61% / -1.61% | ENERY.IS: +0.43% / +1.27% / -0.27% | ENJSA.IS: -1.33% / +0.61% / -1.66%</t>
+          <t>ALARK.IS: +0.25% / +1.61% / -1.61% | ENERY.IS: -0.56% / +1.27% / -1.18% | ENJSA.IS: -1.50% / +0.61% / -1.66%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-15.15423682865462</v>
+        <v>-15.4836702712576</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1186,7 +1186,7 @@
         <v>192.2</v>
       </c>
       <c r="O8" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>46.07</v>
+        <v>45.503</v>
       </c>
       <c r="V8" t="n">
-        <v>12.649</v>
+        <v>12.212</v>
       </c>
       <c r="W8" t="n">
-        <v>-28.832</v>
+        <v>-29.399</v>
       </c>
     </row>
     <row r="9">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.72% / +2.23% / -3.17%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -2.26% | VAKBN.IS: -1.90% / +2.23% / -3.17%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-15.93922200739327</v>
+        <v>-16.96617214553331</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1273,7 +1273,7 @@
         <v>102.3</v>
       </c>
       <c r="O9" t="n">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="P9" t="n">
         <v>6.8</v>
@@ -1287,19 +1287,19 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>22.19</v>
+        <v>23.001</v>
       </c>
       <c r="T9" t="n">
-        <v>22.19</v>
+        <v>23.001</v>
       </c>
       <c r="U9" t="n">
-        <v>65.123</v>
+        <v>63.106</v>
       </c>
       <c r="V9" t="n">
-        <v>14.203</v>
+        <v>12.808</v>
       </c>
       <c r="W9" t="n">
-        <v>-46.706</v>
+        <v>-48.723</v>
       </c>
     </row>
     <row r="10">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KUYAS.IS: -2.22% / +0.50% / -2.91%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KUYAS.IS: -2.08% / +0.50% / -2.91%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.465080385724218</v>
+        <v>-4.380609280387859</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1360,7 +1360,7 @@
         <v>175.4</v>
       </c>
       <c r="O10" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>15.686</v>
+        <v>15.788</v>
       </c>
       <c r="V10" t="n">
-        <v>7.564</v>
+        <v>7.659</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.702</v>
+        <v>-9.6</v>
       </c>
     </row>
     <row r="11">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.23% / +20.94% / 0.00% | RALYH.IS: +31.58% / +35.10% / -0.91% | VAKBN.IS: -1.72% / +2.23% / -3.17%</t>
+          <t>BRSAN.IS: +13.91% / +20.94% / 0.00% | RALYH.IS: +31.22% / +35.10% / -0.91% | VAKBN.IS: -1.90% / +2.23% / -3.17%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K12" t="n">
-        <v>13.53316478460054</v>
+        <v>13.25456862715306</v>
       </c>
       <c r="L12" t="n">
         <v>34.56349599547857</v>
@@ -1542,13 +1542,13 @@
         <v>23.777</v>
       </c>
       <c r="U12" t="n">
-        <v>50.16</v>
+        <v>49.792</v>
       </c>
       <c r="V12" t="n">
-        <v>43.878</v>
+        <v>43.525</v>
       </c>
       <c r="W12" t="n">
-        <v>-9.878</v>
+        <v>-10.246</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1575,55 +1575,67 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ASTOR.IS, TRALT.IS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ASTOR.IS: 2026-09-03 | TRALT.IS: 2026-09-03</t>
+        </is>
+      </c>
       <c r="H13" t="n">
-        <v>7.610984631351814</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>20.48700524499634</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASTOR.IS: +3.39% / +3.92% / -1.28% | TRALT.IS: -2.63% / +2.03% / -3.29%</t>
+        </is>
+      </c>
       <c r="J13" t="n">
-        <v>-16.01405991857144</v>
+        <v>-3.767340978838807</v>
       </c>
       <c r="K13" t="n">
-        <v>9.964713536822334</v>
+        <v>10.36439988450466</v>
       </c>
       <c r="L13" t="n">
-        <v>19.17000314054332</v>
+        <v>16.57596537747867</v>
       </c>
       <c r="M13" t="n">
-        <v>88.88888888888889</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>59.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>43.8</v>
+        <v>47.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>27.346</v>
+        <v>17.404</v>
       </c>
       <c r="T13" t="n">
-        <v>27.346</v>
+        <v>17.404</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.214</v>
+        <v>49.274</v>
       </c>
       <c r="V13" t="n">
-        <v>7.691</v>
+        <v>41.879</v>
       </c>
       <c r="W13" t="n">
-        <v>-23.855</v>
+        <v>-5.428</v>
       </c>
     </row>
     <row r="14">
@@ -1866,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.72% / +2.23% / -3.17%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -2.26% | VAKBN.IS: -1.90% / +2.23% / -3.17%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-15.93922200739327</v>
+        <v>-16.96617214553331</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1885,7 +1897,7 @@
         <v>102.3</v>
       </c>
       <c r="O18" t="n">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="P18" t="n">
         <v>6.8</v>
@@ -1899,19 +1911,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>22.19</v>
+        <v>23.001</v>
       </c>
       <c r="T18" t="n">
-        <v>22.19</v>
+        <v>23.001</v>
       </c>
       <c r="U18" t="n">
-        <v>65.123</v>
+        <v>63.106</v>
       </c>
       <c r="V18" t="n">
-        <v>14.203</v>
+        <v>12.808</v>
       </c>
       <c r="W18" t="n">
-        <v>-46.706</v>
+        <v>-48.723</v>
       </c>
     </row>
     <row r="19">
@@ -2109,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.25% / +1.61% / -1.61% | ENERY.IS: +0.43% / +1.27% / -0.27% | ENJSA.IS: -1.33% / +0.61% / -1.66%</t>
+          <t>ALARK.IS: +0.25% / +1.61% / -1.61% | ENERY.IS: -0.56% / +1.27% / -1.18% | ENJSA.IS: -1.50% / +0.61% / -1.66%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-15.15423682865462</v>
+        <v>-15.4836702712576</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2128,7 +2140,7 @@
         <v>192.2</v>
       </c>
       <c r="O21" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2148,13 +2160,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>46.07</v>
+        <v>45.503</v>
       </c>
       <c r="V21" t="n">
-        <v>12.649</v>
+        <v>12.212</v>
       </c>
       <c r="W21" t="n">
-        <v>-28.832</v>
+        <v>-29.399</v>
       </c>
     </row>
     <row r="22">
@@ -2198,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.73% / +3.76% / -2.26% | VAKBN.IS: -1.72% / +2.23% / -3.17%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -2.26% | VAKBN.IS: -1.90% / +2.23% / -3.17%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.486864757619314</v>
+        <v>-6.641508809352303</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2217,7 +2229,7 @@
         <v>134.4</v>
       </c>
       <c r="O22" t="n">
-        <v>47.4</v>
+        <v>47.1</v>
       </c>
       <c r="P22" t="n">
         <v>3.1</v>
@@ -2231,19 +2243,19 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>17.996</v>
+        <v>18.852</v>
       </c>
       <c r="T22" t="n">
-        <v>17.996</v>
+        <v>18.852</v>
       </c>
       <c r="U22" t="n">
-        <v>71.455</v>
+        <v>69.36</v>
       </c>
       <c r="V22" t="n">
-        <v>29.328</v>
+        <v>27.748</v>
       </c>
       <c r="W22" t="n">
-        <v>-37.249</v>
+        <v>-39.344</v>
       </c>
     </row>
     <row r="23">
@@ -2364,14 +2376,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KUYAS.IS: -2.22% / +0.50% / -2.91%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KUYAS.IS: -2.08% / +0.50% / -2.91%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.465080385724218</v>
+        <v>-4.380609280387859</v>
       </c>
       <c r="L24" t="n">
         <v>4.543450519200398</v>
@@ -2383,7 +2395,7 @@
         <v>175.4</v>
       </c>
       <c r="O24" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="P24" t="n">
         <v>1.9</v>
@@ -2403,13 +2415,13 @@
         <v>10.072</v>
       </c>
       <c r="U24" t="n">
-        <v>15.686</v>
+        <v>15.788</v>
       </c>
       <c r="V24" t="n">
-        <v>7.564</v>
+        <v>7.659</v>
       </c>
       <c r="W24" t="n">
-        <v>-9.702</v>
+        <v>-9.6</v>
       </c>
     </row>
     <row r="25">
@@ -2497,12 +2509,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2517,42 +2529,42 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
+          <t>ASTOR.IS, TRALT.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
+          <t>ASTOR.IS: 2026-09-03 | TRALT.IS: 2026-09-03</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>13.58351811074014</v>
+        <v>20.48700524499634</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.23% / +20.94% / 0.00% | RALYH.IS: +31.58% / +35.10% / -0.91% | VAKBN.IS: -1.72% / +2.23% / -3.17%</t>
+          <t>ASTOR.IS: +3.39% / +3.92% / -1.28% | TRALT.IS: -2.63% / +2.03% / -3.29%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-10.39434387728287</v>
+        <v>-3.767340978838807</v>
       </c>
       <c r="K26" t="n">
-        <v>13.53316478460054</v>
+        <v>10.36439988450466</v>
       </c>
       <c r="L26" t="n">
-        <v>34.56349599547857</v>
+        <v>16.57596537747867</v>
       </c>
       <c r="M26" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>69.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>44</v>
+        <v>47.5</v>
       </c>
       <c r="P26" t="n">
-        <v>6.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2560,22 +2572,22 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>23.777</v>
+        <v>17.404</v>
       </c>
       <c r="T26" t="n">
-        <v>23.777</v>
+        <v>17.404</v>
       </c>
       <c r="U26" t="n">
-        <v>50.16</v>
+        <v>49.274</v>
       </c>
       <c r="V26" t="n">
-        <v>43.878</v>
+        <v>41.879</v>
       </c>
       <c r="W26" t="n">
-        <v>-9.878</v>
+        <v>-5.428</v>
       </c>
     </row>
     <row r="27">
@@ -2586,12 +2598,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2604,55 +2616,67 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
+        </is>
+      </c>
       <c r="H27" t="n">
-        <v>7.610984631351814</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>13.58351811074014</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: +13.91% / +20.94% / 0.00% | RALYH.IS: +31.22% / +35.10% / -0.91% | VAKBN.IS: -1.90% / +2.23% / -3.17%</t>
+        </is>
+      </c>
       <c r="J27" t="n">
-        <v>-16.01405991857144</v>
+        <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>9.964713536822334</v>
+        <v>13.25456862715306</v>
       </c>
       <c r="L27" t="n">
-        <v>19.17000314054332</v>
+        <v>34.56349599547857</v>
       </c>
       <c r="M27" t="n">
-        <v>88.88888888888889</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N27" t="n">
-        <v>59.8</v>
+        <v>69.7</v>
       </c>
       <c r="O27" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S27" t="n">
-        <v>27.346</v>
+        <v>23.777</v>
       </c>
       <c r="T27" t="n">
-        <v>27.346</v>
+        <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>-5.214</v>
+        <v>49.792</v>
       </c>
       <c r="V27" t="n">
-        <v>7.691</v>
+        <v>43.525</v>
       </c>
       <c r="W27" t="n">
-        <v>-23.855</v>
+        <v>-10.246</v>
       </c>
     </row>
   </sheetData>
@@ -2687,7 +2711,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2852,12 +2876,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ALARK.IS, ENERY.IS</t>
+          <t>CANTE.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-04</t>
+          <t>CANTE.IS: 2026-09-07 | ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2865,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: +0.43% / +1.28% / -0.26%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.56% / +1.25% / -1.20%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6610658042645046</v>
+        <v>-0.2348109215664529</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2881,10 +2905,10 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>92.8</v>
+        <v>93.3</v>
       </c>
       <c r="O3" t="n">
-        <v>44.9</v>
+        <v>44.1</v>
       </c>
       <c r="P3" t="n">
         <v>4.3</v>
@@ -2904,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>277.336</v>
+        <v>273.978</v>
       </c>
       <c r="V3" t="n">
-        <v>102.779</v>
+        <v>100.974</v>
       </c>
       <c r="W3" t="n">
-        <v>-39.356</v>
+        <v>-42.714</v>
       </c>
     </row>
     <row r="4">
@@ -2937,29 +2961,17 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ALTNY.IS, BRSAN.IS, ENERY.IS, SOKM.IS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | BRSAN.IS: 2026-09-07 | ENERY.IS: 2026-09-02 | SOKM.IS: 2026-09-03</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>85.65134732223945</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.26% / +0.66% / -1.12% | BRSAN.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.60% / +6.47% / -2.77% | SOKM.IS: +0.50% / +1.21% / -1.98%</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.02390614601206</v>
+        <v>-10.85755246824225</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2968,36 +2980,36 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>119.1</v>
+        <v>119.6</v>
       </c>
       <c r="O4" t="n">
-        <v>47.1</v>
+        <v>46.9</v>
       </c>
       <c r="P4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>25.08</v>
+        <v>25.601</v>
       </c>
       <c r="T4" t="n">
-        <v>25.08</v>
+        <v>25.601</v>
       </c>
       <c r="U4" t="n">
-        <v>57.295</v>
+        <v>55.837</v>
       </c>
       <c r="V4" t="n">
-        <v>21.056</v>
+        <v>19.934</v>
       </c>
       <c r="W4" t="n">
-        <v>-52.168</v>
+        <v>-53.625</v>
       </c>
     </row>
     <row r="5">
@@ -3026,12 +3038,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ALARK.IS, ENERY.IS</t>
+          <t>CANTE.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-04</t>
+          <t>CANTE.IS: 2026-09-07 | ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3039,14 +3051,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: +0.43% / +1.28% / -0.26%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.56% / +1.25% / -1.20%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6409144155671731</v>
+        <v>-0.2547829642576604</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3055,10 +3067,10 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>81.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="O5" t="n">
-        <v>43</v>
+        <v>42.2</v>
       </c>
       <c r="P5" t="n">
         <v>4.7</v>
@@ -3078,13 +3090,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>274.465</v>
+        <v>271.132</v>
       </c>
       <c r="V5" t="n">
-        <v>84.663</v>
+        <v>83.02</v>
       </c>
       <c r="W5" t="n">
-        <v>-39.009</v>
+        <v>-42.342</v>
       </c>
     </row>
     <row r="6">
@@ -3126,14 +3138,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.37% / +20.03% / -1.13% | CANTE.IS: +8.64% / +15.84% / -2.80% | ENERY.IS: +5.60% / +6.47% / -2.77% | SOKM.IS: +0.50% / +1.21% / -1.98% | TKFEN.IS: +12.97% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.13% / +20.01% / -1.13% | CANTE.IS: +5.34% / +15.33% / -2.99% | ENERY.IS: +3.70% / +5.60% / -3.33% | SOKM.IS: -1.09% / +0.81% / -2.78% | TKFEN.IS: +10.72% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.433019611033687</v>
+        <v>-10.19569415605796</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3145,7 +3157,7 @@
         <v>138.9</v>
       </c>
       <c r="O6" t="n">
-        <v>42.9</v>
+        <v>42.5</v>
       </c>
       <c r="P6" t="n">
         <v>5.7</v>
@@ -3165,13 +3177,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>24.594</v>
+        <v>22.196</v>
       </c>
       <c r="V6" t="n">
-        <v>13.842</v>
+        <v>11.651</v>
       </c>
       <c r="W6" t="n">
-        <v>-40.53</v>
+        <v>-42.929</v>
       </c>
     </row>
     <row r="7">
@@ -3198,29 +3210,17 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ALTNY.IS, BRSAN.IS, ENERY.IS, SOKM.IS</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | BRSAN.IS: 2026-09-07 | ENERY.IS: 2026-09-02 | SOKM.IS: 2026-09-03</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>85.65134732223945</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.26% / +0.66% / -1.12% | BRSAN.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.60% / +6.47% / -2.77% | SOKM.IS: +0.50% / +1.21% / -1.98%</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.02390614601206</v>
+        <v>-10.85755246824225</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3229,36 +3229,36 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>119.1</v>
+        <v>119.6</v>
       </c>
       <c r="O7" t="n">
-        <v>47.1</v>
+        <v>46.9</v>
       </c>
       <c r="P7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>25.08</v>
+        <v>25.601</v>
       </c>
       <c r="T7" t="n">
-        <v>25.08</v>
+        <v>25.601</v>
       </c>
       <c r="U7" t="n">
-        <v>57.295</v>
+        <v>55.837</v>
       </c>
       <c r="V7" t="n">
-        <v>21.056</v>
+        <v>19.934</v>
       </c>
       <c r="W7" t="n">
-        <v>-52.168</v>
+        <v>-53.625</v>
       </c>
     </row>
     <row r="8">
@@ -3300,14 +3300,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.37% / +20.03% / -1.13% | CANTE.IS: +0.73% / +3.71% / -2.30% | ENERY.IS: +5.60% / +6.47% / -2.77%</t>
+          <t>BRSAN.IS: +12.13% / +20.01% / -1.13% | CANTE.IS: -2.33% / +3.11% / -3.09% | ENERY.IS: +3.70% / +5.60% / -3.33%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8232801196845552</v>
+        <v>-2.433537307523903</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3319,7 +3319,7 @@
         <v>153.3</v>
       </c>
       <c r="O8" t="n">
-        <v>42.4</v>
+        <v>42.1</v>
       </c>
       <c r="P8" t="n">
         <v>4.2</v>
@@ -3339,13 +3339,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>26.262</v>
+        <v>24.211</v>
       </c>
       <c r="V8" t="n">
-        <v>3.947</v>
+        <v>2.259</v>
       </c>
       <c r="W8" t="n">
-        <v>-29.396</v>
+        <v>-31.446</v>
       </c>
     </row>
     <row r="9">
@@ -3447,29 +3447,17 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ALARK.IS, CANTE.IS, ENERY.IS</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-08-31 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-04</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>38.04089454478734</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | CANTE.IS: +0.73% / +3.71% / -2.30% | ENERY.IS: +0.43% / +1.28% / -0.26%</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.484627807993466</v>
+        <v>-3.00774107970363</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3481,18 +3469,18 @@
         <v>114.1</v>
       </c>
       <c r="O10" t="n">
-        <v>50.9</v>
+        <v>50</v>
       </c>
       <c r="P10" t="n">
         <v>2.4</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>20.181</v>
@@ -3501,13 +3489,13 @@
         <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>12.7</v>
+        <v>10.958</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.895</v>
+        <v>-2.427</v>
       </c>
       <c r="W10" t="n">
-        <v>-25.47</v>
+        <v>-27.213</v>
       </c>
     </row>
     <row r="11">
@@ -3534,29 +3522,17 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ALTNY.IS, BRSAN.IS, ENERY.IS, SOKM.IS</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | BRSAN.IS: 2026-09-07 | ENERY.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>63.58450648919234</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.26% / +0.66% / -1.12% | BRSAN.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +0.43% / +1.28% / -0.26% | SOKM.IS: +0.50% / +1.21% / -1.98%</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.954577013247556</v>
+        <v>-10.77430696274183</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3568,33 +3544,33 @@
         <v>180.1</v>
       </c>
       <c r="O11" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>23.754</v>
+        <v>24.285</v>
       </c>
       <c r="T11" t="n">
-        <v>23.754</v>
+        <v>24.285</v>
       </c>
       <c r="U11" t="n">
-        <v>33.265</v>
+        <v>32.052</v>
       </c>
       <c r="V11" t="n">
-        <v>7.98</v>
+        <v>6.997</v>
       </c>
       <c r="W11" t="n">
-        <v>-41.141</v>
+        <v>-42.354</v>
       </c>
     </row>
     <row r="12">
@@ -3636,14 +3612,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.37% / +20.03% / -1.13% | TKFEN.IS: +12.97% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.13% / +20.01% / -1.13% | TKFEN.IS: +10.72% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>11.04870502319497</v>
+        <v>9.321533433294803</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3675,13 +3651,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>44.397</v>
+        <v>42.152</v>
       </c>
       <c r="V12" t="n">
-        <v>54.736</v>
+        <v>52.329</v>
       </c>
       <c r="W12" t="n">
-        <v>-15.891</v>
+        <v>-18.137</v>
       </c>
     </row>
     <row r="13">
@@ -3695,7 +3671,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3710,42 +3686,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ALARK.IS, ENERY.IS</t>
+          <t>CVKMD.IS, KRDMD.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-02</t>
+          <t>CVKMD.IS: 2026-09-04 | KRDMD.IS: 2026-09-07</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>32.90971238010212</v>
+        <v>-0.49388395046156</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: +5.60% / +6.47% / -2.77%</t>
+          <t>CVKMD.IS: +1.90% / +3.02% / -0.18% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3.175499702073514</v>
+        <v>-19.60937535624424</v>
       </c>
       <c r="K13" t="n">
-        <v>4.794038014733437</v>
+        <v>4.73952218689917</v>
       </c>
       <c r="L13" t="n">
-        <v>18.99889339779883</v>
+        <v>19.61961325199098</v>
       </c>
       <c r="M13" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N13" t="n">
-        <v>43.2</v>
+        <v>88.8</v>
       </c>
       <c r="O13" t="n">
-        <v>50.6</v>
+        <v>45.8</v>
       </c>
       <c r="P13" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3756,19 +3732,19 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>18.999</v>
+        <v>18.132</v>
       </c>
       <c r="T13" t="n">
-        <v>16.472</v>
+        <v>18.132</v>
       </c>
       <c r="U13" t="n">
-        <v>22.017</v>
+        <v>2.129</v>
       </c>
       <c r="V13" t="n">
-        <v>20.126</v>
+        <v>9.369</v>
       </c>
       <c r="W13" t="n">
-        <v>-11.857</v>
+        <v>-9.663</v>
       </c>
     </row>
     <row r="14">
@@ -3782,7 +3758,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
+          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3795,67 +3771,55 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>CVKMD.IS, FENER.IS</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>CVKMD.IS: 2026-09-04 | FENER.IS: 2026-09-07</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>-0.49388395046156</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>CVKMD.IS: +0.11% / +0.64% / -0.19% | FENER.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>8.530010255723974</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>-19.60937535624424</v>
+        <v>0.8142516931666233</v>
       </c>
       <c r="K14" t="n">
-        <v>4.656680042638128</v>
+        <v>3.846414277792909</v>
       </c>
       <c r="L14" t="n">
-        <v>19.61961325199098</v>
+        <v>9.181211458048665</v>
       </c>
       <c r="M14" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N14" t="n">
-        <v>88.8</v>
+        <v>35.7</v>
       </c>
       <c r="O14" t="n">
-        <v>46.4</v>
+        <v>50</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>18.132</v>
+        <v>8.083</v>
       </c>
       <c r="T14" t="n">
-        <v>18.132</v>
+        <v>7.916</v>
       </c>
       <c r="U14" t="n">
-        <v>2.048</v>
+        <v>11.412</v>
       </c>
       <c r="V14" t="n">
-        <v>9.282999999999999</v>
+        <v>4.916</v>
       </c>
       <c r="W14" t="n">
-        <v>-9.744</v>
+        <v>-5.085</v>
       </c>
     </row>
     <row r="16">
@@ -4010,12 +3974,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ALARK.IS, ENERY.IS</t>
+          <t>CANTE.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-04</t>
+          <t>CANTE.IS: 2026-09-07 | ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -4023,14 +3987,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: +0.43% / +1.28% / -0.26%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.56% / +1.25% / -1.20%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6610658042645046</v>
+        <v>-0.2348109215664529</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4039,10 +4003,10 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>92.8</v>
+        <v>93.3</v>
       </c>
       <c r="O18" t="n">
-        <v>44.9</v>
+        <v>44.1</v>
       </c>
       <c r="P18" t="n">
         <v>4.3</v>
@@ -4062,13 +4026,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>277.336</v>
+        <v>273.978</v>
       </c>
       <c r="V18" t="n">
-        <v>102.779</v>
+        <v>100.974</v>
       </c>
       <c r="W18" t="n">
-        <v>-39.356</v>
+        <v>-42.714</v>
       </c>
     </row>
     <row r="19">
@@ -4097,29 +4061,17 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ALTNY.IS, BRSAN.IS, ENERY.IS, SOKM.IS</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | BRSAN.IS: 2026-09-07 | ENERY.IS: 2026-09-02 | SOKM.IS: 2026-09-03</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>85.65134732223945</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.26% / +0.66% / -1.12% | BRSAN.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +5.60% / +6.47% / -2.77% | SOKM.IS: +0.50% / +1.21% / -1.98%</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.02390614601206</v>
+        <v>-10.85755246824225</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4128,36 +4080,36 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>119.1</v>
+        <v>119.6</v>
       </c>
       <c r="O19" t="n">
-        <v>47.1</v>
+        <v>46.9</v>
       </c>
       <c r="P19" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>25.08</v>
+        <v>25.601</v>
       </c>
       <c r="T19" t="n">
-        <v>25.08</v>
+        <v>25.601</v>
       </c>
       <c r="U19" t="n">
-        <v>57.295</v>
+        <v>55.837</v>
       </c>
       <c r="V19" t="n">
-        <v>21.056</v>
+        <v>19.934</v>
       </c>
       <c r="W19" t="n">
-        <v>-52.168</v>
+        <v>-53.625</v>
       </c>
     </row>
     <row r="20">
@@ -4188,12 +4140,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ALARK.IS, ENERY.IS</t>
+          <t>CANTE.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-04</t>
+          <t>CANTE.IS: 2026-09-07 | ENERY.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -4201,14 +4153,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: +0.43% / +1.28% / -0.26%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.56% / +1.25% / -1.20%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6409144155671731</v>
+        <v>-0.2547829642576604</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4217,10 +4169,10 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>81.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="O20" t="n">
-        <v>43</v>
+        <v>42.2</v>
       </c>
       <c r="P20" t="n">
         <v>4.7</v>
@@ -4240,13 +4192,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>274.465</v>
+        <v>271.132</v>
       </c>
       <c r="V20" t="n">
-        <v>84.663</v>
+        <v>83.02</v>
       </c>
       <c r="W20" t="n">
-        <v>-39.009</v>
+        <v>-42.342</v>
       </c>
     </row>
     <row r="21">
@@ -4275,29 +4227,17 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ALTNY.IS, BRSAN.IS, ENERY.IS, SOKM.IS</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-08-31 | ALTNY.IS: 2026-09-04 | BRSAN.IS: 2026-09-07 | ENERY.IS: 2026-09-04 | SOKM.IS: 2026-09-03</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>63.58450648919234</v>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ALTNY.IS: -0.26% / +0.66% / -1.12% | BRSAN.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: +0.43% / +1.28% / -0.26% | SOKM.IS: +0.50% / +1.21% / -1.98%</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.954577013247556</v>
+        <v>-10.77430696274183</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4309,33 +4249,33 @@
         <v>180.1</v>
       </c>
       <c r="O21" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>23.754</v>
+        <v>24.285</v>
       </c>
       <c r="T21" t="n">
-        <v>23.754</v>
+        <v>24.285</v>
       </c>
       <c r="U21" t="n">
-        <v>33.265</v>
+        <v>32.052</v>
       </c>
       <c r="V21" t="n">
-        <v>7.98</v>
+        <v>6.997</v>
       </c>
       <c r="W21" t="n">
-        <v>-41.141</v>
+        <v>-42.354</v>
       </c>
     </row>
     <row r="22">
@@ -4379,14 +4319,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.37% / +20.03% / -1.13% | CANTE.IS: +8.64% / +15.84% / -2.80% | ENERY.IS: +5.60% / +6.47% / -2.77% | SOKM.IS: +0.50% / +1.21% / -1.98% | TKFEN.IS: +12.97% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.13% / +20.01% / -1.13% | CANTE.IS: +5.34% / +15.33% / -2.99% | ENERY.IS: +3.70% / +5.60% / -3.33% | SOKM.IS: -1.09% / +0.81% / -2.78% | TKFEN.IS: +10.72% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-8.433019611033687</v>
+        <v>-10.19569415605796</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4398,7 +4338,7 @@
         <v>138.9</v>
       </c>
       <c r="O22" t="n">
-        <v>42.9</v>
+        <v>42.5</v>
       </c>
       <c r="P22" t="n">
         <v>5.7</v>
@@ -4418,13 +4358,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>24.594</v>
+        <v>22.196</v>
       </c>
       <c r="V22" t="n">
-        <v>13.842</v>
+        <v>11.651</v>
       </c>
       <c r="W22" t="n">
-        <v>-40.53</v>
+        <v>-42.929</v>
       </c>
     </row>
     <row r="23">
@@ -4468,14 +4408,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.37% / +20.03% / -1.13% | CANTE.IS: +0.73% / +3.71% / -2.30% | ENERY.IS: +5.60% / +6.47% / -2.77%</t>
+          <t>BRSAN.IS: +12.13% / +20.01% / -1.13% | CANTE.IS: -2.33% / +3.11% / -3.09% | ENERY.IS: +3.70% / +5.60% / -3.33%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8232801196845552</v>
+        <v>-2.433537307523903</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4487,7 +4427,7 @@
         <v>153.3</v>
       </c>
       <c r="O23" t="n">
-        <v>42.4</v>
+        <v>42.1</v>
       </c>
       <c r="P23" t="n">
         <v>4.2</v>
@@ -4507,13 +4447,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>26.262</v>
+        <v>24.211</v>
       </c>
       <c r="V23" t="n">
-        <v>3.947</v>
+        <v>2.259</v>
       </c>
       <c r="W23" t="n">
-        <v>-29.396</v>
+        <v>-31.446</v>
       </c>
     </row>
     <row r="24">
@@ -4542,29 +4482,17 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ALARK.IS, CANTE.IS, ENERY.IS</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-08-31 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-04</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>38.04089454478734</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | CANTE.IS: +0.73% / +3.71% / -2.30% | ENERY.IS: +0.43% / +1.28% / -0.26%</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.484627807993466</v>
+        <v>-3.00774107970363</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4576,18 +4504,18 @@
         <v>114.1</v>
       </c>
       <c r="O24" t="n">
-        <v>50.9</v>
+        <v>50</v>
       </c>
       <c r="P24" t="n">
         <v>2.4</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>20.181</v>
@@ -4596,29 +4524,29 @@
         <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>12.7</v>
+        <v>10.958</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.895</v>
+        <v>-2.427</v>
       </c>
       <c r="W24" t="n">
-        <v>-25.47</v>
+        <v>-27.213</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4631,83 +4559,71 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ALARK.IS, ENERY.IS</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ALARK.IS: 2026-08-31 | ENERY.IS: 2026-09-02</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>32.90971238010212</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>ALARK.IS: +3.40% / +4.80% / -3.23% | ENERY.IS: +5.60% / +6.47% / -2.77%</t>
-        </is>
-      </c>
+        <v>28.40086810394897</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>3.175499702073514</v>
+        <v>15.38514121842653</v>
       </c>
       <c r="K25" t="n">
-        <v>4.794038014733437</v>
+        <v>-6.616392554049999</v>
       </c>
       <c r="L25" t="n">
-        <v>18.99889339779883</v>
+        <v>5.127814043936619</v>
       </c>
       <c r="M25" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>43.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>50.6</v>
+        <v>49.3</v>
       </c>
       <c r="P25" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>18.999</v>
+        <v>13.28</v>
       </c>
       <c r="T25" t="n">
-        <v>16.472</v>
+        <v>13.28</v>
       </c>
       <c r="U25" t="n">
-        <v>22.017</v>
+        <v>9.141</v>
       </c>
       <c r="V25" t="n">
-        <v>20.126</v>
+        <v>-0.962</v>
       </c>
       <c r="W25" t="n">
-        <v>-11.857</v>
+        <v>-16.714</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
+          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4723,29 +4639,29 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>28.40086810394897</v>
+        <v>8.530010255723974</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>15.38514121842653</v>
+        <v>0.8142516931666233</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.616392554049999</v>
+        <v>3.846414277792909</v>
       </c>
       <c r="L26" t="n">
-        <v>5.127814043936619</v>
+        <v>9.181211458048665</v>
       </c>
       <c r="M26" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>75.40000000000001</v>
+        <v>35.7</v>
       </c>
       <c r="O26" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="P26" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4756,19 +4672,19 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>13.28</v>
+        <v>8.083</v>
       </c>
       <c r="T26" t="n">
-        <v>13.28</v>
+        <v>7.916</v>
       </c>
       <c r="U26" t="n">
-        <v>9.141</v>
+        <v>11.412</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.962</v>
+        <v>4.916</v>
       </c>
       <c r="W26" t="n">
-        <v>-16.714</v>
+        <v>-5.085</v>
       </c>
     </row>
     <row r="27">
@@ -4812,14 +4728,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.37% / +20.03% / -1.13% | TKFEN.IS: +12.97% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.13% / +20.01% / -1.13% | TKFEN.IS: +10.72% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>11.04870502319497</v>
+        <v>9.321533433294803</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4851,13 +4767,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>44.397</v>
+        <v>42.152</v>
       </c>
       <c r="V27" t="n">
-        <v>54.736</v>
+        <v>52.329</v>
       </c>
       <c r="W27" t="n">
-        <v>-15.891</v>
+        <v>-18.137</v>
       </c>
     </row>
     <row r="28">
@@ -4868,7 +4784,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4888,12 +4804,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CVKMD.IS, FENER.IS</t>
+          <t>CVKMD.IS, KRDMD.IS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CVKMD.IS: 2026-09-04 | FENER.IS: 2026-09-07</t>
+          <t>CVKMD.IS: 2026-09-04 | KRDMD.IS: 2026-09-07</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4901,14 +4817,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CVKMD.IS: +0.11% / +0.64% / -0.19% | FENER.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CVKMD.IS: +1.90% / +3.02% / -0.18% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>4.656680042638128</v>
+        <v>4.73952218689917</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4920,7 +4836,7 @@
         <v>88.8</v>
       </c>
       <c r="O28" t="n">
-        <v>46.4</v>
+        <v>45.8</v>
       </c>
       <c r="P28" t="n">
         <v>2.2</v>
@@ -4940,13 +4856,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>2.048</v>
+        <v>2.129</v>
       </c>
       <c r="V28" t="n">
-        <v>9.282999999999999</v>
+        <v>9.369</v>
       </c>
       <c r="W28" t="n">
-        <v>-9.744</v>
+        <v>-9.663</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -743,12 +743,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CANTE.IS, VAKBN.IS</t>
+          <t>CANTE.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | VAKBN.IS: 2026-09-02</t>
+          <t>CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-07</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -2.26% | VAKBN.IS: -1.90% / +2.23% / -3.17%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-16.96617214553331</v>
+        <v>-17.87873491988869</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -772,13 +772,13 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>102.3</v>
+        <v>102.8</v>
       </c>
       <c r="O3" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="P3" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -789,19 +789,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>23.001</v>
+        <v>23.848</v>
       </c>
       <c r="T3" t="n">
-        <v>23.001</v>
+        <v>23.848</v>
       </c>
       <c r="U3" t="n">
-        <v>63.106</v>
+        <v>61.313</v>
       </c>
       <c r="V3" t="n">
-        <v>12.808</v>
+        <v>11.568</v>
       </c>
       <c r="W3" t="n">
-        <v>-48.723</v>
+        <v>-50.516</v>
       </c>
     </row>
     <row r="4">
@@ -980,12 +980,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CANTE.IS, VAKBN.IS</t>
+          <t>CANTE.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | VAKBN.IS: 2026-09-02</t>
+          <t>CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-07</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -2.26% | VAKBN.IS: -1.90% / +2.23% / -3.17%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-16.96617214553331</v>
+        <v>-17.87873491988869</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1009,13 +1009,13 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>102.3</v>
+        <v>102.8</v>
       </c>
       <c r="O6" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="P6" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>23.001</v>
+        <v>23.848</v>
       </c>
       <c r="T6" t="n">
-        <v>23.001</v>
+        <v>23.848</v>
       </c>
       <c r="U6" t="n">
-        <v>63.106</v>
+        <v>61.313</v>
       </c>
       <c r="V6" t="n">
-        <v>12.808</v>
+        <v>11.568</v>
       </c>
       <c r="W6" t="n">
-        <v>-48.723</v>
+        <v>-50.516</v>
       </c>
     </row>
     <row r="7">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | VAKBN.IS: 2026-09-02</t>
+          <t>CANTE.IS: 2026-09-02 | VAKBN.IS: 2026-09-07</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -2.26% | VAKBN.IS: -1.90% / +2.23% / -3.17%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.641508809352303</v>
+        <v>-7.667542245747583</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1096,13 +1096,13 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>134.4</v>
+        <v>134.9</v>
       </c>
       <c r="O7" t="n">
-        <v>47.1</v>
+        <v>46.9</v>
       </c>
       <c r="P7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>18.852</v>
+        <v>19.743</v>
       </c>
       <c r="T7" t="n">
-        <v>18.852</v>
+        <v>19.743</v>
       </c>
       <c r="U7" t="n">
-        <v>69.36</v>
+        <v>67.499</v>
       </c>
       <c r="V7" t="n">
-        <v>27.748</v>
+        <v>26.344</v>
       </c>
       <c r="W7" t="n">
-        <v>-39.344</v>
+        <v>-41.205</v>
       </c>
     </row>
     <row r="8">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.25% / +1.61% / -1.61% | ENERY.IS: -0.56% / +1.27% / -1.18% | ENJSA.IS: -1.50% / +0.61% / -1.66%</t>
+          <t>ALARK.IS: +0.88% / +1.61% / -1.61% | ENERY.IS: -1.83% / +1.27% / -3.44% | ENJSA.IS: -1.16% / +0.61% / -2.01%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-15.4836702712576</v>
+        <v>-15.57297309055231</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>45.503</v>
+        <v>45.349</v>
       </c>
       <c r="V8" t="n">
-        <v>12.212</v>
+        <v>12.093</v>
       </c>
       <c r="W8" t="n">
-        <v>-29.399</v>
+        <v>-29.552</v>
       </c>
     </row>
     <row r="9">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CANTE.IS, VAKBN.IS</t>
+          <t>CANTE.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | VAKBN.IS: 2026-09-02</t>
+          <t>CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-07</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -2.26% | VAKBN.IS: -1.90% / +2.23% / -3.17%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-16.96617214553331</v>
+        <v>-17.87873491988869</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1270,13 +1270,13 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>102.3</v>
+        <v>102.8</v>
       </c>
       <c r="O9" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="P9" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1287,19 +1287,19 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>23.001</v>
+        <v>23.848</v>
       </c>
       <c r="T9" t="n">
-        <v>23.001</v>
+        <v>23.848</v>
       </c>
       <c r="U9" t="n">
-        <v>63.106</v>
+        <v>61.313</v>
       </c>
       <c r="V9" t="n">
-        <v>12.808</v>
+        <v>11.568</v>
       </c>
       <c r="W9" t="n">
-        <v>-48.723</v>
+        <v>-50.516</v>
       </c>
     </row>
     <row r="10">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KUYAS.IS: -2.08% / +0.50% / -2.91%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KUYAS.IS: -2.15% / +0.50% / -2.91%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.380609280387859</v>
+        <v>-4.109172398895833</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>15.788</v>
+        <v>16.117</v>
       </c>
       <c r="V10" t="n">
-        <v>7.659</v>
+        <v>7.965</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.6</v>
+        <v>-9.271000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1490,12 +1490,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
+          <t>BRSAN.IS, CANTE.IS, RALYH.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
+          <t>BRSAN.IS: 2026-08-13 | CANTE.IS: 2026-09-07 | RALYH.IS: 2026-07-13</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.91% / +20.94% / 0.00% | RALYH.IS: +31.22% / +35.10% / -0.91% | VAKBN.IS: -1.90% / +2.23% / -3.17%</t>
+          <t>BRSAN.IS: +14.15% / +20.94% / 0.00% | CANTE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: +26.06% / +35.10% / -0.91%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K12" t="n">
-        <v>13.25456862715306</v>
+        <v>10.93785639077705</v>
       </c>
       <c r="L12" t="n">
         <v>34.56349599547857</v>
@@ -1519,10 +1519,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>69.7</v>
+        <v>70.2</v>
       </c>
       <c r="O12" t="n">
-        <v>44</v>
+        <v>43.7</v>
       </c>
       <c r="P12" t="n">
         <v>6.1</v>
@@ -1542,13 +1542,13 @@
         <v>23.777</v>
       </c>
       <c r="U12" t="n">
-        <v>49.792</v>
+        <v>46.728</v>
       </c>
       <c r="V12" t="n">
-        <v>43.525</v>
+        <v>40.589</v>
       </c>
       <c r="W12" t="n">
-        <v>-10.246</v>
+        <v>-13.31</v>
       </c>
     </row>
     <row r="13">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +3.39% / +3.92% / -1.28% | TRALT.IS: -2.63% / +2.03% / -3.29%</t>
+          <t>ASTOR.IS: +2.96% / +3.92% / -1.28% | TRALT.IS: -1.18% / +2.03% / -3.29%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-3.767340978838807</v>
       </c>
       <c r="K13" t="n">
-        <v>10.36439988450466</v>
+        <v>10.927816856916</v>
       </c>
       <c r="L13" t="n">
         <v>16.57596537747867</v>
@@ -1629,13 +1629,13 @@
         <v>17.404</v>
       </c>
       <c r="U13" t="n">
-        <v>49.274</v>
+        <v>50.036</v>
       </c>
       <c r="V13" t="n">
-        <v>41.879</v>
+        <v>42.603</v>
       </c>
       <c r="W13" t="n">
-        <v>-5.428</v>
+        <v>-4.666</v>
       </c>
     </row>
     <row r="14">
@@ -1865,12 +1865,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CANTE.IS, VAKBN.IS</t>
+          <t>CANTE.IS, ENERY.IS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | VAKBN.IS: 2026-09-02</t>
+          <t>CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-07</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1878,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -2.26% | VAKBN.IS: -1.90% / +2.23% / -3.17%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-16.96617214553331</v>
+        <v>-17.87873491988869</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1894,13 +1894,13 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>102.3</v>
+        <v>102.8</v>
       </c>
       <c r="O18" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="P18" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1911,19 +1911,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>23.001</v>
+        <v>23.848</v>
       </c>
       <c r="T18" t="n">
-        <v>23.001</v>
+        <v>23.848</v>
       </c>
       <c r="U18" t="n">
-        <v>63.106</v>
+        <v>61.313</v>
       </c>
       <c r="V18" t="n">
-        <v>12.808</v>
+        <v>11.568</v>
       </c>
       <c r="W18" t="n">
-        <v>-48.723</v>
+        <v>-50.516</v>
       </c>
     </row>
     <row r="19">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.25% / +1.61% / -1.61% | ENERY.IS: -0.56% / +1.27% / -1.18% | ENJSA.IS: -1.50% / +0.61% / -1.66%</t>
+          <t>ALARK.IS: +0.88% / +1.61% / -1.61% | ENERY.IS: -1.83% / +1.27% / -3.44% | ENJSA.IS: -1.16% / +0.61% / -2.01%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-15.4836702712576</v>
+        <v>-15.57297309055231</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2160,13 +2160,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>45.503</v>
+        <v>45.349</v>
       </c>
       <c r="V21" t="n">
-        <v>12.212</v>
+        <v>12.093</v>
       </c>
       <c r="W21" t="n">
-        <v>-29.399</v>
+        <v>-29.552</v>
       </c>
     </row>
     <row r="22">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | VAKBN.IS: 2026-09-02</t>
+          <t>CANTE.IS: 2026-09-02 | VAKBN.IS: 2026-09-07</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2210,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -2.26% | VAKBN.IS: -1.90% / +2.23% / -3.17%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.641508809352303</v>
+        <v>-7.667542245747583</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2226,13 +2226,13 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>134.4</v>
+        <v>134.9</v>
       </c>
       <c r="O22" t="n">
-        <v>47.1</v>
+        <v>46.9</v>
       </c>
       <c r="P22" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2243,19 +2243,19 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>18.852</v>
+        <v>19.743</v>
       </c>
       <c r="T22" t="n">
-        <v>18.852</v>
+        <v>19.743</v>
       </c>
       <c r="U22" t="n">
-        <v>69.36</v>
+        <v>67.499</v>
       </c>
       <c r="V22" t="n">
-        <v>27.748</v>
+        <v>26.344</v>
       </c>
       <c r="W22" t="n">
-        <v>-39.344</v>
+        <v>-41.205</v>
       </c>
     </row>
     <row r="23">
@@ -2376,14 +2376,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KUYAS.IS: -2.08% / +0.50% / -2.91%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KUYAS.IS: -2.15% / +0.50% / -2.91%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.380609280387859</v>
+        <v>-4.109172398895833</v>
       </c>
       <c r="L24" t="n">
         <v>4.543450519200398</v>
@@ -2415,13 +2415,13 @@
         <v>10.072</v>
       </c>
       <c r="U24" t="n">
-        <v>15.788</v>
+        <v>16.117</v>
       </c>
       <c r="V24" t="n">
-        <v>7.659</v>
+        <v>7.965</v>
       </c>
       <c r="W24" t="n">
-        <v>-9.6</v>
+        <v>-9.271000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -2542,14 +2542,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +3.39% / +3.92% / -1.28% | TRALT.IS: -2.63% / +2.03% / -3.29%</t>
+          <t>ASTOR.IS: +2.96% / +3.92% / -1.28% | TRALT.IS: -1.18% / +2.03% / -3.29%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-3.767340978838807</v>
       </c>
       <c r="K26" t="n">
-        <v>10.36439988450466</v>
+        <v>10.927816856916</v>
       </c>
       <c r="L26" t="n">
         <v>16.57596537747867</v>
@@ -2581,13 +2581,13 @@
         <v>17.404</v>
       </c>
       <c r="U26" t="n">
-        <v>49.274</v>
+        <v>50.036</v>
       </c>
       <c r="V26" t="n">
-        <v>41.879</v>
+        <v>42.603</v>
       </c>
       <c r="W26" t="n">
-        <v>-5.428</v>
+        <v>-4.666</v>
       </c>
     </row>
     <row r="27">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BRSAN.IS, RALYH.IS, VAKBN.IS</t>
+          <t>BRSAN.IS, CANTE.IS, RALYH.IS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-13 | RALYH.IS: 2026-07-13 | VAKBN.IS: 2026-09-02</t>
+          <t>BRSAN.IS: 2026-08-13 | CANTE.IS: 2026-09-07 | RALYH.IS: 2026-07-13</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.91% / +20.94% / 0.00% | RALYH.IS: +31.22% / +35.10% / -0.91% | VAKBN.IS: -1.90% / +2.23% / -3.17%</t>
+          <t>BRSAN.IS: +14.15% / +20.94% / 0.00% | CANTE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: +26.06% / +35.10% / -0.91%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>13.25456862715306</v>
+        <v>10.93785639077705</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2647,10 +2647,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N27" t="n">
-        <v>69.7</v>
+        <v>70.2</v>
       </c>
       <c r="O27" t="n">
-        <v>44</v>
+        <v>43.7</v>
       </c>
       <c r="P27" t="n">
         <v>6.1</v>
@@ -2670,13 +2670,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>49.792</v>
+        <v>46.728</v>
       </c>
       <c r="V27" t="n">
-        <v>43.525</v>
+        <v>40.589</v>
       </c>
       <c r="W27" t="n">
-        <v>-10.246</v>
+        <v>-13.31</v>
       </c>
     </row>
   </sheetData>
@@ -2711,7 +2711,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2889,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.56% / +1.25% / -1.20%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.83% / +1.25% / -3.46%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2348109215664529</v>
+        <v>-0.8674734929105754</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2928,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>273.978</v>
+        <v>271.606</v>
       </c>
       <c r="V3" t="n">
-        <v>100.974</v>
+        <v>99.7</v>
       </c>
       <c r="W3" t="n">
-        <v>-42.714</v>
+        <v>-45.086</v>
       </c>
     </row>
     <row r="4">
@@ -2971,7 +2971,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.85755246824225</v>
+        <v>-10.92398646602792</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2983,7 +2983,7 @@
         <v>119.6</v>
       </c>
       <c r="O4" t="n">
-        <v>46.9</v>
+        <v>47.3</v>
       </c>
       <c r="P4" t="n">
         <v>3.8</v>
@@ -2997,19 +2997,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>25.601</v>
+        <v>25.657</v>
       </c>
       <c r="T4" t="n">
-        <v>25.601</v>
+        <v>25.657</v>
       </c>
       <c r="U4" t="n">
-        <v>55.837</v>
+        <v>55.721</v>
       </c>
       <c r="V4" t="n">
-        <v>19.934</v>
+        <v>19.845</v>
       </c>
       <c r="W4" t="n">
-        <v>-53.625</v>
+        <v>-53.741</v>
       </c>
     </row>
     <row r="5">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.56% / +1.25% / -1.20%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.83% / +1.25% / -3.46%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2547829642576604</v>
+        <v>-0.8873188825677891</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3090,13 +3090,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>271.132</v>
+        <v>268.778</v>
       </c>
       <c r="V5" t="n">
-        <v>83.02</v>
+        <v>81.85899999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-42.342</v>
+        <v>-44.695</v>
       </c>
     </row>
     <row r="6">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-02 | SOKM.IS: 2026-09-03 | TKFEN.IS: 2026-08-05</t>
+          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-07 | SOKM.IS: 2026-09-03 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3138,14 +3138,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.13% / +20.01% / -1.13% | CANTE.IS: +5.34% / +15.33% / -2.99% | ENERY.IS: +3.70% / +5.60% / -3.33% | SOKM.IS: -1.09% / +0.81% / -2.78% | TKFEN.IS: +10.72% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.37% / +20.01% / -1.13% | CANTE.IS: +5.34% / +15.33% / -2.99% | ENERY.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.00% / +0.82% / -2.95% | TKFEN.IS: +9.72% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.19569415605796</v>
+        <v>-10.5729679392092</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3154,10 +3154,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>138.9</v>
+        <v>139.4</v>
       </c>
       <c r="O6" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="P6" t="n">
         <v>5.7</v>
@@ -3177,13 +3177,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>22.196</v>
+        <v>21.683</v>
       </c>
       <c r="V6" t="n">
-        <v>11.651</v>
+        <v>11.182</v>
       </c>
       <c r="W6" t="n">
-        <v>-42.929</v>
+        <v>-43.442</v>
       </c>
     </row>
     <row r="7">
@@ -3220,7 +3220,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.85755246824225</v>
+        <v>-10.92398646602792</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3232,7 +3232,7 @@
         <v>119.6</v>
       </c>
       <c r="O7" t="n">
-        <v>46.9</v>
+        <v>47.3</v>
       </c>
       <c r="P7" t="n">
         <v>3.8</v>
@@ -3246,19 +3246,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>25.601</v>
+        <v>25.657</v>
       </c>
       <c r="T7" t="n">
-        <v>25.601</v>
+        <v>25.657</v>
       </c>
       <c r="U7" t="n">
-        <v>55.837</v>
+        <v>55.721</v>
       </c>
       <c r="V7" t="n">
-        <v>19.934</v>
+        <v>19.845</v>
       </c>
       <c r="W7" t="n">
-        <v>-53.625</v>
+        <v>-53.741</v>
       </c>
     </row>
     <row r="8">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-02</t>
+          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-07</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -3300,14 +3300,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.13% / +20.01% / -1.13% | CANTE.IS: -2.33% / +3.11% / -3.09% | ENERY.IS: +3.70% / +5.60% / -3.33%</t>
+          <t>BRSAN.IS: +12.37% / +20.01% / -1.13% | CANTE.IS: -2.32% / +3.11% / -3.84% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.433537307523903</v>
+        <v>-2.750964312711535</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3316,10 +3316,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>153.3</v>
+        <v>153.8</v>
       </c>
       <c r="O8" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="P8" t="n">
         <v>4.2</v>
@@ -3339,13 +3339,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>24.211</v>
+        <v>23.807</v>
       </c>
       <c r="V8" t="n">
-        <v>2.259</v>
+        <v>1.927</v>
       </c>
       <c r="W8" t="n">
-        <v>-31.446</v>
+        <v>-31.85</v>
       </c>
     </row>
     <row r="9">
@@ -3457,7 +3457,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.00774107970363</v>
+        <v>-3.203214460105674</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3469,7 +3469,7 @@
         <v>114.1</v>
       </c>
       <c r="O10" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="P10" t="n">
         <v>2.4</v>
@@ -3489,13 +3489,13 @@
         <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>10.958</v>
+        <v>10.734</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.427</v>
+        <v>-2.624</v>
       </c>
       <c r="W10" t="n">
-        <v>-27.213</v>
+        <v>-27.437</v>
       </c>
     </row>
     <row r="11">
@@ -3532,7 +3532,7 @@
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.77430696274183</v>
+        <v>-10.8408029997903</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3544,7 +3544,7 @@
         <v>180.1</v>
       </c>
       <c r="O11" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
@@ -3558,19 +3558,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>24.285</v>
+        <v>24.341</v>
       </c>
       <c r="T11" t="n">
-        <v>24.285</v>
+        <v>24.341</v>
       </c>
       <c r="U11" t="n">
-        <v>32.052</v>
+        <v>31.953</v>
       </c>
       <c r="V11" t="n">
-        <v>6.997</v>
+        <v>6.917</v>
       </c>
       <c r="W11" t="n">
-        <v>-42.354</v>
+        <v>-42.452</v>
       </c>
     </row>
     <row r="12">
@@ -3612,14 +3612,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.13% / +20.01% / -1.13% | TKFEN.IS: +10.72% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.37% / +20.01% / -1.13% | TKFEN.IS: +9.72% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>9.321533433294803</v>
+        <v>8.92475944531197</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3651,13 +3651,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>42.152</v>
+        <v>41.636</v>
       </c>
       <c r="V12" t="n">
-        <v>52.329</v>
+        <v>51.776</v>
       </c>
       <c r="W12" t="n">
-        <v>-18.137</v>
+        <v>-18.653</v>
       </c>
     </row>
     <row r="13">
@@ -3699,14 +3699,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CVKMD.IS: +1.90% / +3.02% / -0.18% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CVKMD.IS: +1.00% / +3.02% / -0.17% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K13" t="n">
-        <v>4.73952218689917</v>
+        <v>4.27493107425605</v>
       </c>
       <c r="L13" t="n">
         <v>19.61961325199098</v>
@@ -3738,13 +3738,13 @@
         <v>18.132</v>
       </c>
       <c r="U13" t="n">
-        <v>2.129</v>
+        <v>1.676</v>
       </c>
       <c r="V13" t="n">
-        <v>9.369</v>
+        <v>8.884</v>
       </c>
       <c r="W13" t="n">
-        <v>-9.663</v>
+        <v>-10.116</v>
       </c>
     </row>
     <row r="14">
@@ -3987,14 +3987,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.56% / +1.25% / -1.20%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.83% / +1.25% / -3.46%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2348109215664529</v>
+        <v>-0.8674734929105754</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4026,13 +4026,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>273.978</v>
+        <v>271.606</v>
       </c>
       <c r="V18" t="n">
-        <v>100.974</v>
+        <v>99.7</v>
       </c>
       <c r="W18" t="n">
-        <v>-42.714</v>
+        <v>-45.086</v>
       </c>
     </row>
     <row r="19">
@@ -4071,7 +4071,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.85755246824225</v>
+        <v>-10.92398646602792</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4083,7 +4083,7 @@
         <v>119.6</v>
       </c>
       <c r="O19" t="n">
-        <v>46.9</v>
+        <v>47.3</v>
       </c>
       <c r="P19" t="n">
         <v>3.8</v>
@@ -4097,19 +4097,19 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>25.601</v>
+        <v>25.657</v>
       </c>
       <c r="T19" t="n">
-        <v>25.601</v>
+        <v>25.657</v>
       </c>
       <c r="U19" t="n">
-        <v>55.837</v>
+        <v>55.721</v>
       </c>
       <c r="V19" t="n">
-        <v>19.934</v>
+        <v>19.845</v>
       </c>
       <c r="W19" t="n">
-        <v>-53.625</v>
+        <v>-53.741</v>
       </c>
     </row>
     <row r="20">
@@ -4153,14 +4153,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -0.56% / +1.25% / -1.20%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.83% / +1.25% / -3.46%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2547829642576604</v>
+        <v>-0.8873188825677891</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4192,13 +4192,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>271.132</v>
+        <v>268.778</v>
       </c>
       <c r="V20" t="n">
-        <v>83.02</v>
+        <v>81.85899999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>-42.342</v>
+        <v>-44.695</v>
       </c>
     </row>
     <row r="21">
@@ -4237,7 +4237,7 @@
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.77430696274183</v>
+        <v>-10.8408029997903</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4249,7 +4249,7 @@
         <v>180.1</v>
       </c>
       <c r="O21" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
@@ -4263,19 +4263,19 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>24.285</v>
+        <v>24.341</v>
       </c>
       <c r="T21" t="n">
-        <v>24.285</v>
+        <v>24.341</v>
       </c>
       <c r="U21" t="n">
-        <v>32.052</v>
+        <v>31.953</v>
       </c>
       <c r="V21" t="n">
-        <v>6.997</v>
+        <v>6.917</v>
       </c>
       <c r="W21" t="n">
-        <v>-42.354</v>
+        <v>-42.452</v>
       </c>
     </row>
     <row r="22">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-02 | SOKM.IS: 2026-09-03 | TKFEN.IS: 2026-08-05</t>
+          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-08-19 | ENERY.IS: 2026-09-07 | SOKM.IS: 2026-09-03 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -4319,14 +4319,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.13% / +20.01% / -1.13% | CANTE.IS: +5.34% / +15.33% / -2.99% | ENERY.IS: +3.70% / +5.60% / -3.33% | SOKM.IS: -1.09% / +0.81% / -2.78% | TKFEN.IS: +10.72% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.37% / +20.01% / -1.13% | CANTE.IS: +5.34% / +15.33% / -2.99% | ENERY.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.00% / +0.82% / -2.95% | TKFEN.IS: +9.72% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.19569415605796</v>
+        <v>-10.5729679392092</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4335,10 +4335,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>138.9</v>
+        <v>139.4</v>
       </c>
       <c r="O22" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="P22" t="n">
         <v>5.7</v>
@@ -4358,13 +4358,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>22.196</v>
+        <v>21.683</v>
       </c>
       <c r="V22" t="n">
-        <v>11.651</v>
+        <v>11.182</v>
       </c>
       <c r="W22" t="n">
-        <v>-42.929</v>
+        <v>-43.442</v>
       </c>
     </row>
     <row r="23">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-02</t>
+          <t>BRSAN.IS: 2026-08-12 | CANTE.IS: 2026-09-02 | ENERY.IS: 2026-09-07</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -4408,14 +4408,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.13% / +20.01% / -1.13% | CANTE.IS: -2.33% / +3.11% / -3.09% | ENERY.IS: +3.70% / +5.60% / -3.33%</t>
+          <t>BRSAN.IS: +12.37% / +20.01% / -1.13% | CANTE.IS: -2.32% / +3.11% / -3.84% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.433537307523903</v>
+        <v>-2.750964312711535</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4424,10 +4424,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>153.3</v>
+        <v>153.8</v>
       </c>
       <c r="O23" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="P23" t="n">
         <v>4.2</v>
@@ -4447,13 +4447,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>24.211</v>
+        <v>23.807</v>
       </c>
       <c r="V23" t="n">
-        <v>2.259</v>
+        <v>1.927</v>
       </c>
       <c r="W23" t="n">
-        <v>-31.446</v>
+        <v>-31.85</v>
       </c>
     </row>
     <row r="24">
@@ -4492,7 +4492,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.00774107970363</v>
+        <v>-3.203214460105674</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4504,7 +4504,7 @@
         <v>114.1</v>
       </c>
       <c r="O24" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="P24" t="n">
         <v>2.4</v>
@@ -4524,13 +4524,13 @@
         <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>10.958</v>
+        <v>10.734</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.427</v>
+        <v>-2.624</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.213</v>
+        <v>-27.437</v>
       </c>
     </row>
     <row r="25">
@@ -4728,14 +4728,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.13% / +20.01% / -1.13% | TKFEN.IS: +10.72% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.37% / +20.01% / -1.13% | TKFEN.IS: +9.72% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>9.321533433294803</v>
+        <v>8.92475944531197</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4767,13 +4767,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>42.152</v>
+        <v>41.636</v>
       </c>
       <c r="V27" t="n">
-        <v>52.329</v>
+        <v>51.776</v>
       </c>
       <c r="W27" t="n">
-        <v>-18.137</v>
+        <v>-18.653</v>
       </c>
     </row>
     <row r="28">
@@ -4817,14 +4817,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CVKMD.IS: +1.90% / +3.02% / -0.18% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CVKMD.IS: +1.00% / +3.02% / -0.17% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>4.73952218689917</v>
+        <v>4.27493107425605</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4856,13 +4856,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>2.129</v>
+        <v>1.676</v>
       </c>
       <c r="V28" t="n">
-        <v>9.369</v>
+        <v>8.884</v>
       </c>
       <c r="W28" t="n">
-        <v>-9.663</v>
+        <v>-10.116</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.88% / +1.61% / -1.61% | ENERY.IS: -1.83% / +1.27% / -3.44% | ENJSA.IS: -1.16% / +0.61% / -2.01%</t>
+          <t>ALARK.IS: +1.95% / +1.97% / -1.61% | ENERY.IS: -2.28% / +1.27% / -3.44% | ENJSA.IS: -1.33% / +0.61% / -2.01%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-15.57297309055231</v>
+        <v>-15.44940657817463</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>45.349</v>
+        <v>45.561</v>
       </c>
       <c r="V8" t="n">
-        <v>12.093</v>
+        <v>12.257</v>
       </c>
       <c r="W8" t="n">
-        <v>-29.552</v>
+        <v>-29.34</v>
       </c>
     </row>
     <row r="9">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KUYAS.IS: -2.15% / +0.50% / -2.91%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KUYAS.IS: -1.94% / +0.50% / -2.91%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.109172398895833</v>
+        <v>-3.991968366845922</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1380,13 +1380,13 @@
         <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>16.117</v>
+        <v>16.259</v>
       </c>
       <c r="V10" t="n">
-        <v>7.965</v>
+        <v>8.097</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.271000000000001</v>
+        <v>-9.129</v>
       </c>
     </row>
     <row r="11">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.15% / +20.94% / 0.00% | CANTE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: +26.06% / +35.10% / -0.91%</t>
+          <t>BRSAN.IS: +15.90% / +20.94% / 0.00% | CANTE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: +26.78% / +35.10% / -0.91%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K12" t="n">
-        <v>10.93785639077705</v>
+        <v>11.72390766361568</v>
       </c>
       <c r="L12" t="n">
         <v>34.56349599547857</v>
@@ -1542,13 +1542,13 @@
         <v>23.777</v>
       </c>
       <c r="U12" t="n">
-        <v>46.728</v>
+        <v>47.767</v>
       </c>
       <c r="V12" t="n">
-        <v>40.589</v>
+        <v>41.585</v>
       </c>
       <c r="W12" t="n">
-        <v>-13.31</v>
+        <v>-12.271</v>
       </c>
     </row>
     <row r="13">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +2.96% / +3.92% / -1.28% | TRALT.IS: -1.18% / +2.03% / -3.29%</t>
+          <t>ASTOR.IS: +2.53% / +3.92% / -1.28% | TRALT.IS: -0.79% / +2.03% / -3.29%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-3.767340978838807</v>
       </c>
       <c r="K13" t="n">
-        <v>10.927816856916</v>
+        <v>10.90639846598009</v>
       </c>
       <c r="L13" t="n">
         <v>16.57596537747867</v>
@@ -1629,13 +1629,13 @@
         <v>17.404</v>
       </c>
       <c r="U13" t="n">
-        <v>50.036</v>
+        <v>50.007</v>
       </c>
       <c r="V13" t="n">
-        <v>42.603</v>
+        <v>42.575</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.666</v>
+        <v>-4.695</v>
       </c>
     </row>
     <row r="14">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +0.88% / +1.61% / -1.61% | ENERY.IS: -1.83% / +1.27% / -3.44% | ENJSA.IS: -1.16% / +0.61% / -2.01%</t>
+          <t>ALARK.IS: +1.95% / +1.97% / -1.61% | ENERY.IS: -2.28% / +1.27% / -3.44% | ENJSA.IS: -1.33% / +0.61% / -2.01%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-15.57297309055231</v>
+        <v>-15.44940657817463</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2160,13 +2160,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>45.349</v>
+        <v>45.561</v>
       </c>
       <c r="V21" t="n">
-        <v>12.093</v>
+        <v>12.257</v>
       </c>
       <c r="W21" t="n">
-        <v>-29.552</v>
+        <v>-29.34</v>
       </c>
     </row>
     <row r="22">
@@ -2376,14 +2376,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KUYAS.IS: -2.15% / +0.50% / -2.91%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KUYAS.IS: -1.94% / +0.50% / -2.91%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.109172398895833</v>
+        <v>-3.991968366845922</v>
       </c>
       <c r="L24" t="n">
         <v>4.543450519200398</v>
@@ -2415,13 +2415,13 @@
         <v>10.072</v>
       </c>
       <c r="U24" t="n">
-        <v>16.117</v>
+        <v>16.259</v>
       </c>
       <c r="V24" t="n">
-        <v>7.965</v>
+        <v>8.097</v>
       </c>
       <c r="W24" t="n">
-        <v>-9.271000000000001</v>
+        <v>-9.129</v>
       </c>
     </row>
     <row r="25">
@@ -2542,14 +2542,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +2.96% / +3.92% / -1.28% | TRALT.IS: -1.18% / +2.03% / -3.29%</t>
+          <t>ASTOR.IS: +2.53% / +3.92% / -1.28% | TRALT.IS: -0.79% / +2.03% / -3.29%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-3.767340978838807</v>
       </c>
       <c r="K26" t="n">
-        <v>10.927816856916</v>
+        <v>10.90639846598009</v>
       </c>
       <c r="L26" t="n">
         <v>16.57596537747867</v>
@@ -2581,13 +2581,13 @@
         <v>17.404</v>
       </c>
       <c r="U26" t="n">
-        <v>50.036</v>
+        <v>50.007</v>
       </c>
       <c r="V26" t="n">
-        <v>42.603</v>
+        <v>42.575</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.666</v>
+        <v>-4.695</v>
       </c>
     </row>
     <row r="27">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.15% / +20.94% / 0.00% | CANTE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: +26.06% / +35.10% / -0.91%</t>
+          <t>BRSAN.IS: +15.90% / +20.94% / 0.00% | CANTE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: +26.78% / +35.10% / -0.91%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>10.93785639077705</v>
+        <v>11.72390766361568</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2670,13 +2670,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>46.728</v>
+        <v>47.767</v>
       </c>
       <c r="V27" t="n">
-        <v>40.589</v>
+        <v>41.585</v>
       </c>
       <c r="W27" t="n">
-        <v>-13.31</v>
+        <v>-12.271</v>
       </c>
     </row>
   </sheetData>
@@ -2889,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.83% / +1.25% / -3.46%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -2.27% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8674734929105754</v>
+        <v>-1.088167795945294</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2928,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>271.606</v>
+        <v>270.779</v>
       </c>
       <c r="V3" t="n">
-        <v>99.7</v>
+        <v>99.255</v>
       </c>
       <c r="W3" t="n">
-        <v>-45.086</v>
+        <v>-45.913</v>
       </c>
     </row>
     <row r="4">
@@ -2971,7 +2971,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.92398646602792</v>
+        <v>-11.24912228187798</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -2983,7 +2983,7 @@
         <v>119.6</v>
       </c>
       <c r="O4" t="n">
-        <v>47.3</v>
+        <v>46.9</v>
       </c>
       <c r="P4" t="n">
         <v>3.8</v>
@@ -2997,19 +2997,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>25.657</v>
+        <v>25.928</v>
       </c>
       <c r="T4" t="n">
-        <v>25.657</v>
+        <v>25.928</v>
       </c>
       <c r="U4" t="n">
-        <v>55.721</v>
+        <v>55.153</v>
       </c>
       <c r="V4" t="n">
-        <v>19.845</v>
+        <v>19.407</v>
       </c>
       <c r="W4" t="n">
-        <v>-53.741</v>
+        <v>-54.31</v>
       </c>
     </row>
     <row r="5">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.83% / +1.25% / -3.46%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -2.27% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8873188825677891</v>
+        <v>-1.107969004700493</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3090,13 +3090,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>268.778</v>
+        <v>267.957</v>
       </c>
       <c r="V5" t="n">
-        <v>81.85899999999999</v>
+        <v>81.45399999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-44.695</v>
+        <v>-45.516</v>
       </c>
     </row>
     <row r="6">
@@ -3138,14 +3138,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.37% / +20.01% / -1.13% | CANTE.IS: +5.34% / +15.33% / -2.99% | ENERY.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.00% / +0.82% / -2.95% | TKFEN.IS: +9.72% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +14.11% / +20.01% / -1.13% | CANTE.IS: +5.36% / +15.33% / -2.99% | ENERY.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.82% / +0.83% / -2.93% | TKFEN.IS: +9.84% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.5729679392092</v>
+        <v>-10.28633977786256</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3177,13 +3177,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>21.683</v>
+        <v>22.073</v>
       </c>
       <c r="V6" t="n">
-        <v>11.182</v>
+        <v>11.538</v>
       </c>
       <c r="W6" t="n">
-        <v>-43.442</v>
+        <v>-43.052</v>
       </c>
     </row>
     <row r="7">
@@ -3220,7 +3220,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.92398646602792</v>
+        <v>-11.24912228187798</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3232,7 +3232,7 @@
         <v>119.6</v>
       </c>
       <c r="O7" t="n">
-        <v>47.3</v>
+        <v>46.9</v>
       </c>
       <c r="P7" t="n">
         <v>3.8</v>
@@ -3246,19 +3246,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>25.657</v>
+        <v>25.928</v>
       </c>
       <c r="T7" t="n">
-        <v>25.657</v>
+        <v>25.928</v>
       </c>
       <c r="U7" t="n">
-        <v>55.721</v>
+        <v>55.153</v>
       </c>
       <c r="V7" t="n">
-        <v>19.845</v>
+        <v>19.407</v>
       </c>
       <c r="W7" t="n">
-        <v>-53.741</v>
+        <v>-54.31</v>
       </c>
     </row>
     <row r="8">
@@ -3300,14 +3300,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.37% / +20.01% / -1.13% | CANTE.IS: -2.32% / +3.11% / -3.84% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +14.11% / +20.01% / -1.13% | CANTE.IS: -2.31% / +3.11% / -3.83% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.750964312711535</v>
+        <v>-2.448690665428277</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3339,13 +3339,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>23.807</v>
+        <v>24.192</v>
       </c>
       <c r="V8" t="n">
-        <v>1.927</v>
+        <v>2.244</v>
       </c>
       <c r="W8" t="n">
-        <v>-31.85</v>
+        <v>-31.465</v>
       </c>
     </row>
     <row r="9">
@@ -3457,7 +3457,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.203214460105674</v>
+        <v>-3.035426863396262</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3489,13 +3489,13 @@
         <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>10.734</v>
+        <v>10.926</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.624</v>
+        <v>-2.455</v>
       </c>
       <c r="W10" t="n">
-        <v>-27.437</v>
+        <v>-27.245</v>
       </c>
     </row>
     <row r="11">
@@ -3532,7 +3532,7 @@
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.8408029997903</v>
+        <v>-11.16624244310511</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3544,7 +3544,7 @@
         <v>180.1</v>
       </c>
       <c r="O11" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
@@ -3558,19 +3558,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>24.341</v>
+        <v>24.617</v>
       </c>
       <c r="T11" t="n">
-        <v>24.341</v>
+        <v>24.617</v>
       </c>
       <c r="U11" t="n">
-        <v>31.953</v>
+        <v>31.472</v>
       </c>
       <c r="V11" t="n">
-        <v>6.917</v>
+        <v>6.527</v>
       </c>
       <c r="W11" t="n">
-        <v>-42.452</v>
+        <v>-42.934</v>
       </c>
     </row>
     <row r="12">
@@ -3612,14 +3612,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.37% / +20.01% / -1.13% | TKFEN.IS: +9.72% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +14.11% / +20.01% / -1.13% | TKFEN.IS: +9.84% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>8.92475944531197</v>
+        <v>9.808448101895584</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3651,13 +3651,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>41.636</v>
+        <v>42.785</v>
       </c>
       <c r="V12" t="n">
-        <v>51.776</v>
+        <v>53.008</v>
       </c>
       <c r="W12" t="n">
-        <v>-18.653</v>
+        <v>-17.504</v>
       </c>
     </row>
     <row r="13">
@@ -3699,14 +3699,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CVKMD.IS: +1.00% / +3.02% / -0.17% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CVKMD.IS: +0.70% / +3.03% / -0.16% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K13" t="n">
-        <v>4.27493107425605</v>
+        <v>4.120217744298538</v>
       </c>
       <c r="L13" t="n">
         <v>19.61961325199098</v>
@@ -3738,13 +3738,13 @@
         <v>18.132</v>
       </c>
       <c r="U13" t="n">
-        <v>1.676</v>
+        <v>1.525</v>
       </c>
       <c r="V13" t="n">
-        <v>8.884</v>
+        <v>8.723000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>-10.116</v>
+        <v>-10.267</v>
       </c>
     </row>
     <row r="14">
@@ -3987,14 +3987,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.83% / +1.25% / -3.46%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -2.27% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8674734929105754</v>
+        <v>-1.088167795945294</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4026,13 +4026,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>271.606</v>
+        <v>270.779</v>
       </c>
       <c r="V18" t="n">
-        <v>99.7</v>
+        <v>99.255</v>
       </c>
       <c r="W18" t="n">
-        <v>-45.086</v>
+        <v>-45.913</v>
       </c>
     </row>
     <row r="19">
@@ -4071,7 +4071,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.92398646602792</v>
+        <v>-11.24912228187798</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4083,7 +4083,7 @@
         <v>119.6</v>
       </c>
       <c r="O19" t="n">
-        <v>47.3</v>
+        <v>46.9</v>
       </c>
       <c r="P19" t="n">
         <v>3.8</v>
@@ -4097,19 +4097,19 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>25.657</v>
+        <v>25.928</v>
       </c>
       <c r="T19" t="n">
-        <v>25.657</v>
+        <v>25.928</v>
       </c>
       <c r="U19" t="n">
-        <v>55.721</v>
+        <v>55.153</v>
       </c>
       <c r="V19" t="n">
-        <v>19.845</v>
+        <v>19.407</v>
       </c>
       <c r="W19" t="n">
-        <v>-53.741</v>
+        <v>-54.31</v>
       </c>
     </row>
     <row r="20">
@@ -4153,14 +4153,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -1.83% / +1.25% / -3.46%</t>
+          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -2.27% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8873188825677891</v>
+        <v>-1.107969004700493</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4192,13 +4192,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>268.778</v>
+        <v>267.957</v>
       </c>
       <c r="V20" t="n">
-        <v>81.85899999999999</v>
+        <v>81.45399999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>-44.695</v>
+        <v>-45.516</v>
       </c>
     </row>
     <row r="21">
@@ -4237,7 +4237,7 @@
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.8408029997903</v>
+        <v>-11.16624244310511</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4249,7 +4249,7 @@
         <v>180.1</v>
       </c>
       <c r="O21" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
@@ -4263,19 +4263,19 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>24.341</v>
+        <v>24.617</v>
       </c>
       <c r="T21" t="n">
-        <v>24.341</v>
+        <v>24.617</v>
       </c>
       <c r="U21" t="n">
-        <v>31.953</v>
+        <v>31.472</v>
       </c>
       <c r="V21" t="n">
-        <v>6.917</v>
+        <v>6.527</v>
       </c>
       <c r="W21" t="n">
-        <v>-42.452</v>
+        <v>-42.934</v>
       </c>
     </row>
     <row r="22">
@@ -4319,14 +4319,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.37% / +20.01% / -1.13% | CANTE.IS: +5.34% / +15.33% / -2.99% | ENERY.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -1.00% / +0.82% / -2.95% | TKFEN.IS: +9.72% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +14.11% / +20.01% / -1.13% | CANTE.IS: +5.36% / +15.33% / -2.99% | ENERY.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.82% / +0.83% / -2.93% | TKFEN.IS: +9.84% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.5729679392092</v>
+        <v>-10.28633977786256</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4358,13 +4358,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>21.683</v>
+        <v>22.073</v>
       </c>
       <c r="V22" t="n">
-        <v>11.182</v>
+        <v>11.538</v>
       </c>
       <c r="W22" t="n">
-        <v>-43.442</v>
+        <v>-43.052</v>
       </c>
     </row>
     <row r="23">
@@ -4408,14 +4408,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.37% / +20.01% / -1.13% | CANTE.IS: -2.32% / +3.11% / -3.84% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +14.11% / +20.01% / -1.13% | CANTE.IS: -2.31% / +3.11% / -3.83% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.750964312711535</v>
+        <v>-2.448690665428277</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4447,13 +4447,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>23.807</v>
+        <v>24.192</v>
       </c>
       <c r="V23" t="n">
-        <v>1.927</v>
+        <v>2.244</v>
       </c>
       <c r="W23" t="n">
-        <v>-31.85</v>
+        <v>-31.465</v>
       </c>
     </row>
     <row r="24">
@@ -4492,7 +4492,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.203214460105674</v>
+        <v>-3.035426863396262</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4524,13 +4524,13 @@
         <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>10.734</v>
+        <v>10.926</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.624</v>
+        <v>-2.455</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.437</v>
+        <v>-27.245</v>
       </c>
     </row>
     <row r="25">
@@ -4728,14 +4728,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.37% / +20.01% / -1.13% | TKFEN.IS: +9.72% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +14.11% / +20.01% / -1.13% | TKFEN.IS: +9.84% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>8.92475944531197</v>
+        <v>9.808448101895584</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4767,13 +4767,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>41.636</v>
+        <v>42.785</v>
       </c>
       <c r="V27" t="n">
-        <v>51.776</v>
+        <v>53.008</v>
       </c>
       <c r="W27" t="n">
-        <v>-18.653</v>
+        <v>-17.504</v>
       </c>
     </row>
     <row r="28">
@@ -4817,14 +4817,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CVKMD.IS: +1.00% / +3.02% / -0.17% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CVKMD.IS: +0.70% / +3.03% / -0.16% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>4.27493107425605</v>
+        <v>4.120217744298538</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4856,13 +4856,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>1.676</v>
+        <v>1.525</v>
       </c>
       <c r="V28" t="n">
-        <v>8.884</v>
+        <v>8.723000000000001</v>
       </c>
       <c r="W28" t="n">
-        <v>-10.116</v>
+        <v>-10.267</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -573,7 +573,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | ENERY.IS: +0.91% / +1.67% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-17.87873491988869</v>
+        <v>-17.18554929213719</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -772,10 +772,10 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>102.8</v>
+        <v>102.6</v>
       </c>
       <c r="O3" t="n">
-        <v>42.8</v>
+        <v>43.3</v>
       </c>
       <c r="P3" t="n">
         <v>6.7</v>
@@ -789,19 +789,19 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>23.848</v>
+        <v>23.832</v>
       </c>
       <c r="T3" t="n">
-        <v>23.848</v>
+        <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>61.313</v>
+        <v>64.27200000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>11.568</v>
+        <v>12.51</v>
       </c>
       <c r="W3" t="n">
-        <v>-50.516</v>
+        <v>-49.637</v>
       </c>
     </row>
     <row r="4">
@@ -820,12 +820,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -847,7 +847,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="O4" t="n">
         <v>48.8</v>
@@ -870,13 +870,13 @@
         <v>21.057</v>
       </c>
       <c r="U4" t="n">
-        <v>148.349</v>
+        <v>151.738</v>
       </c>
       <c r="V4" t="n">
         <v>111.543</v>
       </c>
       <c r="W4" t="n">
-        <v>-12.575</v>
+        <v>-12.747</v>
       </c>
     </row>
     <row r="5">
@@ -895,12 +895,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N5" t="n">
-        <v>64.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>46.6</v>
@@ -945,13 +945,13 @@
         <v>19.637</v>
       </c>
       <c r="U5" t="n">
-        <v>114.762</v>
+        <v>120.159</v>
       </c>
       <c r="V5" t="n">
         <v>117.535</v>
       </c>
       <c r="W5" t="n">
-        <v>-15.987</v>
+        <v>-16.389</v>
       </c>
     </row>
     <row r="6">
@@ -970,12 +970,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | ENERY.IS: +0.91% / +1.67% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-17.87873491988869</v>
+        <v>-17.18554929213719</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1009,10 +1009,10 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>102.8</v>
+        <v>102.6</v>
       </c>
       <c r="O6" t="n">
-        <v>42.8</v>
+        <v>43.3</v>
       </c>
       <c r="P6" t="n">
         <v>6.7</v>
@@ -1026,19 +1026,19 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>23.848</v>
+        <v>23.832</v>
       </c>
       <c r="T6" t="n">
-        <v>23.848</v>
+        <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>61.313</v>
+        <v>64.27200000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>11.568</v>
+        <v>12.51</v>
       </c>
       <c r="W6" t="n">
-        <v>-50.516</v>
+        <v>-49.637</v>
       </c>
     </row>
     <row r="7">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | VAKBN.IS: +0.88% / +1.44% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.667542245747583</v>
+        <v>-6.900205957831329</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1096,13 +1096,13 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>134.9</v>
+        <v>134.6</v>
       </c>
       <c r="O7" t="n">
-        <v>46.9</v>
+        <v>47.3</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>19.743</v>
+        <v>19.727</v>
       </c>
       <c r="T7" t="n">
-        <v>19.743</v>
+        <v>19.727</v>
       </c>
       <c r="U7" t="n">
-        <v>67.499</v>
+        <v>75.999</v>
       </c>
       <c r="V7" t="n">
-        <v>26.344</v>
+        <v>27.394</v>
       </c>
       <c r="W7" t="n">
-        <v>-41.205</v>
+        <v>-41.489</v>
       </c>
     </row>
     <row r="8">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.95% / +1.97% / -1.61% | ENERY.IS: -2.28% / +1.27% / -3.44% | ENJSA.IS: -1.33% / +0.61% / -2.01%</t>
+          <t>ALARK.IS: +1.86% / +2.33% / -1.61% | ENERY.IS: -1.38% / +1.27% / -3.44% | ENJSA.IS: -0.81% / +0.61% / -2.01%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-15.44940657817463</v>
+        <v>-15.07555155078539</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1183,7 +1183,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>192.2</v>
+        <v>191.8</v>
       </c>
       <c r="O8" t="n">
         <v>46.8</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>45.561</v>
+        <v>48.201</v>
       </c>
       <c r="V8" t="n">
-        <v>12.257</v>
+        <v>12.754</v>
       </c>
       <c r="W8" t="n">
-        <v>-29.34</v>
+        <v>-29.088</v>
       </c>
     </row>
     <row r="9">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | ENERY.IS: +0.91% / +1.67% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-17.87873491988869</v>
+        <v>-17.18554929213719</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1270,10 +1270,10 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>102.8</v>
+        <v>102.6</v>
       </c>
       <c r="O9" t="n">
-        <v>42.8</v>
+        <v>43.3</v>
       </c>
       <c r="P9" t="n">
         <v>6.7</v>
@@ -1287,19 +1287,19 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>23.848</v>
+        <v>23.832</v>
       </c>
       <c r="T9" t="n">
-        <v>23.848</v>
+        <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>61.313</v>
+        <v>64.27200000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>11.568</v>
+        <v>12.51</v>
       </c>
       <c r="W9" t="n">
-        <v>-50.516</v>
+        <v>-49.637</v>
       </c>
     </row>
     <row r="10">
@@ -1318,22 +1318,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AGHOL.IS, KUYAS.IS</t>
+          <t>AGHOL.IS, ENKAI.IS, SASA.IS, TSKB.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-09-07 | KUYAS.IS: 2026-09-03</t>
+          <t>AGHOL.IS: 2026-09-07 | ENKAI.IS: 2026-09-08 | SASA.IS: 2026-09-08 | TSKB.IS: 2026-09-08</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KUYAS.IS: -1.94% / +0.50% / -2.91%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | ENKAI.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TSKB.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.991968366845922</v>
+        <v>-23.34764362257953</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1357,10 +1357,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>175.4</v>
+        <v>176.1</v>
       </c>
       <c r="O10" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>10.072</v>
+        <v>25.974</v>
       </c>
       <c r="T10" t="n">
-        <v>10.072</v>
+        <v>25.974</v>
       </c>
       <c r="U10" t="n">
-        <v>16.259</v>
+        <v>-7.18</v>
       </c>
       <c r="V10" t="n">
-        <v>8.097</v>
+        <v>-13.696</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.129</v>
+        <v>-32.568</v>
       </c>
     </row>
     <row r="11">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>66.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="O11" t="n">
         <v>51.9</v>
@@ -1455,13 +1455,13 @@
         <v>7.033</v>
       </c>
       <c r="U11" t="n">
-        <v>84.07599999999999</v>
+        <v>85.218</v>
       </c>
       <c r="V11" t="n">
         <v>58.898</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.608</v>
+        <v>-1.618</v>
       </c>
     </row>
     <row r="12">
@@ -1475,57 +1475,57 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BRSAN.IS, CANTE.IS, RALYH.IS</t>
+          <t>TRALT.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-13 | CANTE.IS: 2026-09-07 | RALYH.IS: 2026-07-13</t>
+          <t>TRALT.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>13.58351811074014</v>
+        <v>25.65141339163128</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +15.90% / +20.94% / 0.00% | CANTE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: +26.78% / +35.10% / -0.91%</t>
+          <t>TRALT.IS: +3.36% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-10.39434387728287</v>
+        <v>-5.044425134583063</v>
       </c>
       <c r="K12" t="n">
-        <v>11.72390766361568</v>
+        <v>11.5843629794812</v>
       </c>
       <c r="L12" t="n">
-        <v>34.56349599547857</v>
+        <v>9.344627019167174</v>
       </c>
       <c r="M12" t="n">
-        <v>77.77777777777779</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N12" t="n">
-        <v>70.2</v>
+        <v>58.7</v>
       </c>
       <c r="O12" t="n">
-        <v>43.7</v>
+        <v>51.3</v>
       </c>
       <c r="P12" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>23.777</v>
+        <v>12.101</v>
       </c>
       <c r="T12" t="n">
-        <v>23.777</v>
+        <v>12.101</v>
       </c>
       <c r="U12" t="n">
-        <v>47.767</v>
+        <v>30.188</v>
       </c>
       <c r="V12" t="n">
-        <v>41.585</v>
+        <v>35.623</v>
       </c>
       <c r="W12" t="n">
-        <v>-12.271</v>
+        <v>-7.591</v>
       </c>
     </row>
     <row r="13">
@@ -1562,57 +1562,57 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASTOR.IS, TRALT.IS</t>
+          <t>BRSAN.IS, CANTE.IS, RALYH.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-03 | TRALT.IS: 2026-09-03</t>
+          <t>BRSAN.IS: 2026-08-13 | CANTE.IS: 2026-09-07 | RALYH.IS: 2026-07-13</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>20.48700524499634</v>
+        <v>13.58351811074014</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +2.53% / +3.92% / -1.28% | TRALT.IS: -0.79% / +2.03% / -3.29%</t>
+          <t>BRSAN.IS: +14.39% / +20.94% / 0.00% | CANTE.IS: +0.74% / +0.76% / 0.00% | RALYH.IS: +26.06% / +35.10% / -0.91%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-3.767340978838807</v>
+        <v>-10.39434387728287</v>
       </c>
       <c r="K13" t="n">
-        <v>10.90639846598009</v>
+        <v>11.28345449600658</v>
       </c>
       <c r="L13" t="n">
-        <v>16.57596537747867</v>
+        <v>34.56349599547857</v>
       </c>
       <c r="M13" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>88.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="O13" t="n">
-        <v>47.5</v>
+        <v>44.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.6</v>
+        <v>6.1</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1620,22 +1620,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
-        <v>17.404</v>
+        <v>23.777</v>
       </c>
       <c r="T13" t="n">
-        <v>17.404</v>
+        <v>23.777</v>
       </c>
       <c r="U13" t="n">
-        <v>50.007</v>
+        <v>47.185</v>
       </c>
       <c r="V13" t="n">
-        <v>42.575</v>
+        <v>41.027</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.695</v>
+        <v>-12.853</v>
       </c>
     </row>
     <row r="14">
@@ -1649,68 +1649,80 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T1_genislik_skor|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CANTE.IS, ENERY.IS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CANTE.IS: 2026-09-07 | ENERY.IS: 2026-09-07</t>
+        </is>
+      </c>
       <c r="H14" t="n">
-        <v>21.76975999384314</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>55.72500398673659</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CANTE.IS: +0.74% / +0.76% / 0.00% | ENERY.IS: +0.91% / +1.67% / 0.00%</t>
+        </is>
+      </c>
       <c r="J14" t="n">
-        <v>-28.45194989279852</v>
+        <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>4.847592357308117</v>
+        <v>5.691426106672592</v>
       </c>
       <c r="L14" t="n">
-        <v>29.12044822069533</v>
+        <v>22.73189287884475</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>62.8</v>
+        <v>59.7</v>
       </c>
       <c r="O14" t="n">
-        <v>43.3</v>
+        <v>45.5</v>
       </c>
       <c r="P14" t="n">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>25.589</v>
+        <v>25.345</v>
       </c>
       <c r="T14" t="n">
-        <v>25.589</v>
+        <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>83.911</v>
+        <v>82.506</v>
       </c>
       <c r="V14" t="n">
-        <v>103.043</v>
+        <v>94.745</v>
       </c>
       <c r="W14" t="n">
-        <v>-30.679</v>
+        <v>-28.744</v>
       </c>
     </row>
     <row r="16">
@@ -1855,12 +1867,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1878,14 +1890,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | ENERY.IS: +0.91% / +1.67% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-17.87873491988869</v>
+        <v>-17.18554929213719</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1894,10 +1906,10 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>102.8</v>
+        <v>102.6</v>
       </c>
       <c r="O18" t="n">
-        <v>42.8</v>
+        <v>43.3</v>
       </c>
       <c r="P18" t="n">
         <v>6.7</v>
@@ -1911,19 +1923,19 @@
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>23.848</v>
+        <v>23.832</v>
       </c>
       <c r="T18" t="n">
-        <v>23.848</v>
+        <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>61.313</v>
+        <v>64.27200000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>11.568</v>
+        <v>12.51</v>
       </c>
       <c r="W18" t="n">
-        <v>-50.516</v>
+        <v>-49.637</v>
       </c>
     </row>
     <row r="19">
@@ -1944,12 +1956,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1971,7 +1983,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="O19" t="n">
         <v>48.8</v>
@@ -1994,13 +2006,13 @@
         <v>21.057</v>
       </c>
       <c r="U19" t="n">
-        <v>148.349</v>
+        <v>151.738</v>
       </c>
       <c r="V19" t="n">
         <v>111.543</v>
       </c>
       <c r="W19" t="n">
-        <v>-12.575</v>
+        <v>-12.747</v>
       </c>
     </row>
     <row r="20">
@@ -2021,12 +2033,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2048,7 +2060,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>64.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="O20" t="n">
         <v>46.6</v>
@@ -2071,13 +2083,13 @@
         <v>19.637</v>
       </c>
       <c r="U20" t="n">
-        <v>114.762</v>
+        <v>120.159</v>
       </c>
       <c r="V20" t="n">
         <v>117.535</v>
       </c>
       <c r="W20" t="n">
-        <v>-15.987</v>
+        <v>-16.389</v>
       </c>
     </row>
     <row r="21">
@@ -2098,12 +2110,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2121,14 +2133,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.95% / +1.97% / -1.61% | ENERY.IS: -2.28% / +1.27% / -3.44% | ENJSA.IS: -1.33% / +0.61% / -2.01%</t>
+          <t>ALARK.IS: +1.86% / +2.33% / -1.61% | ENERY.IS: -1.38% / +1.27% / -3.44% | ENJSA.IS: -0.81% / +0.61% / -2.01%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-15.44940657817463</v>
+        <v>-15.07555155078539</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2137,7 +2149,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>192.2</v>
+        <v>191.8</v>
       </c>
       <c r="O21" t="n">
         <v>46.8</v>
@@ -2160,13 +2172,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>45.561</v>
+        <v>48.201</v>
       </c>
       <c r="V21" t="n">
-        <v>12.257</v>
+        <v>12.754</v>
       </c>
       <c r="W21" t="n">
-        <v>-29.34</v>
+        <v>-29.088</v>
       </c>
     </row>
     <row r="22">
@@ -2187,12 +2199,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2210,14 +2222,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | VAKBN.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | VAKBN.IS: +0.88% / +1.44% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.667542245747583</v>
+        <v>-6.900205957831329</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2226,13 +2238,13 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>134.9</v>
+        <v>134.6</v>
       </c>
       <c r="O22" t="n">
-        <v>46.9</v>
+        <v>47.3</v>
       </c>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2243,25 +2255,25 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>19.743</v>
+        <v>19.727</v>
       </c>
       <c r="T22" t="n">
-        <v>19.743</v>
+        <v>19.727</v>
       </c>
       <c r="U22" t="n">
-        <v>67.499</v>
+        <v>75.999</v>
       </c>
       <c r="V22" t="n">
-        <v>26.344</v>
+        <v>27.394</v>
       </c>
       <c r="W22" t="n">
-        <v>-41.205</v>
+        <v>-41.489</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2271,68 +2283,80 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|coklu_zarf</t>
+          <t>T1_genislik_skor|E30|S2|M0|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CANTE.IS, ENERY.IS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CANTE.IS: 2026-09-07 | ENERY.IS: 2026-09-07</t>
+        </is>
+      </c>
       <c r="H23" t="n">
-        <v>50.58108284302749</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>55.72500398673659</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>CANTE.IS: +0.74% / +0.76% / 0.00% | ENERY.IS: +0.91% / +1.67% / 0.00%</t>
+        </is>
+      </c>
       <c r="J23" t="n">
-        <v>13.3215021172385</v>
+        <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.400004582905126e-07</v>
+        <v>5.691426106672592</v>
       </c>
       <c r="L23" t="n">
-        <v>5.668150937989602</v>
+        <v>22.73189287884475</v>
       </c>
       <c r="M23" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>66.7</v>
+        <v>59.7</v>
       </c>
       <c r="O23" t="n">
-        <v>51.9</v>
+        <v>45.5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.4</v>
+        <v>6.3</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>7.033</v>
+        <v>25.345</v>
       </c>
       <c r="T23" t="n">
-        <v>7.033</v>
+        <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>84.07599999999999</v>
+        <v>82.506</v>
       </c>
       <c r="V23" t="n">
-        <v>58.898</v>
+        <v>94.745</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.608</v>
+        <v>-28.744</v>
       </c>
     </row>
     <row r="24">
@@ -2343,85 +2367,73 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|coklu_zarf</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, KUYAS.IS</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-09-07 | KUYAS.IS: 2026-09-03</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>23.02092795860866</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | KUYAS.IS: -1.94% / +0.50% / -2.91%</t>
-        </is>
-      </c>
+        <v>50.58108284302749</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>12.86015270141232</v>
+        <v>13.3215021172385</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.991968366845922</v>
+        <v>-4.400004582905126e-07</v>
       </c>
       <c r="L24" t="n">
-        <v>4.543450519200398</v>
+        <v>5.668150937989602</v>
       </c>
       <c r="M24" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>175.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>48.7</v>
+        <v>51.9</v>
       </c>
       <c r="P24" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>10.072</v>
+        <v>7.033</v>
       </c>
       <c r="T24" t="n">
-        <v>10.072</v>
+        <v>7.033</v>
       </c>
       <c r="U24" t="n">
-        <v>16.259</v>
+        <v>85.218</v>
       </c>
       <c r="V24" t="n">
-        <v>8.097</v>
+        <v>58.898</v>
       </c>
       <c r="W24" t="n">
-        <v>-9.129</v>
+        <v>-1.618</v>
       </c>
     </row>
     <row r="25">
@@ -2432,79 +2444,91 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E30|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>TRALT.IS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>TRALT.IS: 2026-09-02</t>
+        </is>
+      </c>
       <c r="H25" t="n">
-        <v>21.76975999384314</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>25.65141339163128</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TRALT.IS: +3.36% / +4.87% / -2.03%</t>
+        </is>
+      </c>
       <c r="J25" t="n">
-        <v>-28.45194989279852</v>
+        <v>-5.044425134583063</v>
       </c>
       <c r="K25" t="n">
-        <v>4.847592357308117</v>
+        <v>11.5843629794812</v>
       </c>
       <c r="L25" t="n">
-        <v>29.12044822069533</v>
+        <v>9.344627019167174</v>
       </c>
       <c r="M25" t="n">
-        <v>100</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N25" t="n">
-        <v>62.8</v>
+        <v>58.7</v>
       </c>
       <c r="O25" t="n">
-        <v>43.3</v>
+        <v>51.3</v>
       </c>
       <c r="P25" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>25.589</v>
+        <v>12.101</v>
       </c>
       <c r="T25" t="n">
-        <v>25.589</v>
+        <v>12.101</v>
       </c>
       <c r="U25" t="n">
-        <v>83.911</v>
+        <v>30.188</v>
       </c>
       <c r="V25" t="n">
-        <v>103.043</v>
+        <v>35.623</v>
       </c>
       <c r="W25" t="n">
-        <v>-30.679</v>
+        <v>-7.591</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2514,57 +2538,57 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
+          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ASTOR.IS, TRALT.IS</t>
+          <t>AGHOL.IS, ENKAI.IS, SASA.IS, TSKB.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-03 | TRALT.IS: 2026-09-03</t>
+          <t>AGHOL.IS: 2026-09-07 | ENKAI.IS: 2026-09-08 | SASA.IS: 2026-09-08 | TSKB.IS: 2026-09-08</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>20.48700524499634</v>
+        <v>23.02092795860866</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +2.53% / +3.92% / -1.28% | TRALT.IS: -0.79% / +2.03% / -3.29%</t>
+          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | ENKAI.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TSKB.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-3.767340978838807</v>
+        <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>10.90639846598009</v>
+        <v>-23.34764362257953</v>
       </c>
       <c r="L26" t="n">
-        <v>16.57596537747867</v>
+        <v>4.543450519200398</v>
       </c>
       <c r="M26" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>88.40000000000001</v>
+        <v>176.1</v>
       </c>
       <c r="O26" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2572,22 +2596,22 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
-        <v>17.404</v>
+        <v>25.974</v>
       </c>
       <c r="T26" t="n">
-        <v>17.404</v>
+        <v>25.974</v>
       </c>
       <c r="U26" t="n">
-        <v>50.007</v>
+        <v>-7.18</v>
       </c>
       <c r="V26" t="n">
-        <v>42.575</v>
+        <v>-13.696</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.695</v>
+        <v>-32.568</v>
       </c>
     </row>
     <row r="27">
@@ -2598,7 +2622,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2608,12 +2632,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2631,14 +2655,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +15.90% / +20.94% / 0.00% | CANTE.IS: -0.02% / +0.00% / 0.00% | RALYH.IS: +26.78% / +35.10% / -0.91%</t>
+          <t>BRSAN.IS: +14.39% / +20.94% / 0.00% | CANTE.IS: +0.74% / +0.76% / 0.00% | RALYH.IS: +26.06% / +35.10% / -0.91%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>11.72390766361568</v>
+        <v>11.28345449600658</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2647,10 +2671,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N27" t="n">
-        <v>70.2</v>
+        <v>70</v>
       </c>
       <c r="O27" t="n">
-        <v>43.7</v>
+        <v>44.4</v>
       </c>
       <c r="P27" t="n">
         <v>6.1</v>
@@ -2670,13 +2694,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>47.767</v>
+        <v>47.185</v>
       </c>
       <c r="V27" t="n">
-        <v>41.585</v>
+        <v>41.027</v>
       </c>
       <c r="W27" t="n">
-        <v>-12.271</v>
+        <v>-12.853</v>
       </c>
     </row>
   </sheetData>
@@ -2711,7 +2735,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2866,12 +2890,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2889,14 +2913,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -2.27% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +0.67% / +0.51% / -0.25% | ENERY.IS: -0.72% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.088167795945294</v>
+        <v>0.02900081220775785</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2905,10 +2929,10 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>93.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>44.1</v>
+        <v>44.7</v>
       </c>
       <c r="P3" t="n">
         <v>4.3</v>
@@ -2928,13 +2952,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>270.779</v>
+        <v>285.803</v>
       </c>
       <c r="V3" t="n">
-        <v>99.255</v>
+        <v>101.505</v>
       </c>
       <c r="W3" t="n">
-        <v>-45.913</v>
+        <v>-42.931</v>
       </c>
     </row>
     <row r="4">
@@ -2953,12 +2977,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2980,7 +3004,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>119.6</v>
+        <v>119.3</v>
       </c>
       <c r="O4" t="n">
         <v>46.9</v>
@@ -3003,13 +3027,13 @@
         <v>25.928</v>
       </c>
       <c r="U4" t="n">
-        <v>55.153</v>
+        <v>56.945</v>
       </c>
       <c r="V4" t="n">
         <v>19.407</v>
       </c>
       <c r="W4" t="n">
-        <v>-54.31</v>
+        <v>-54.937</v>
       </c>
     </row>
     <row r="5">
@@ -3028,12 +3052,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3051,14 +3075,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -2.27% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +0.67% / +0.51% / -0.25% | ENERY.IS: -0.72% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.107969004700493</v>
+        <v>0.008975956914714089</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3067,10 +3091,10 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="O5" t="n">
-        <v>42.2</v>
+        <v>42.8</v>
       </c>
       <c r="P5" t="n">
         <v>4.7</v>
@@ -3090,13 +3114,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>267.957</v>
+        <v>282.839</v>
       </c>
       <c r="V5" t="n">
-        <v>81.45399999999999</v>
+        <v>83.504</v>
       </c>
       <c r="W5" t="n">
-        <v>-45.516</v>
+        <v>-42.552</v>
       </c>
     </row>
     <row r="6">
@@ -3115,12 +3139,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3138,14 +3162,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.11% / +20.01% / -1.13% | CANTE.IS: +5.36% / +15.33% / -2.99% | ENERY.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.82% / +0.83% / -2.93% | TKFEN.IS: +9.84% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | CANTE.IS: +6.08% / +15.33% / -2.99% | ENERY.IS: +1.57% / +1.60% / 0.00% | SOKM.IS: -0.38% / +0.83% / -2.93% | TKFEN.IS: +10.49% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.28633977786256</v>
+        <v>-9.981740252180193</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3154,10 +3178,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>139.4</v>
+        <v>139.1</v>
       </c>
       <c r="O6" t="n">
-        <v>42.3</v>
+        <v>42.7</v>
       </c>
       <c r="P6" t="n">
         <v>5.7</v>
@@ -3177,13 +3201,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>22.073</v>
+        <v>22.487</v>
       </c>
       <c r="V6" t="n">
-        <v>11.538</v>
+        <v>11.917</v>
       </c>
       <c r="W6" t="n">
-        <v>-43.052</v>
+        <v>-42.638</v>
       </c>
     </row>
     <row r="7">
@@ -3202,12 +3226,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3229,7 +3253,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>119.6</v>
+        <v>119.3</v>
       </c>
       <c r="O7" t="n">
         <v>46.9</v>
@@ -3252,13 +3276,13 @@
         <v>25.928</v>
       </c>
       <c r="U7" t="n">
-        <v>55.153</v>
+        <v>56.945</v>
       </c>
       <c r="V7" t="n">
         <v>19.407</v>
       </c>
       <c r="W7" t="n">
-        <v>-54.31</v>
+        <v>-54.937</v>
       </c>
     </row>
     <row r="8">
@@ -3277,12 +3301,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3300,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.11% / +20.01% / -1.13% | CANTE.IS: -2.31% / +3.11% / -3.83% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | CANTE.IS: -1.64% / +3.11% / -3.83% | ENERY.IS: +1.57% / +1.60% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.448690665428277</v>
+        <v>-2.227581041817817</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3316,10 +3340,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>153.8</v>
+        <v>153.5</v>
       </c>
       <c r="O8" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="P8" t="n">
         <v>4.2</v>
@@ -3339,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>24.192</v>
+        <v>25.421</v>
       </c>
       <c r="V8" t="n">
-        <v>2.244</v>
+        <v>2.475</v>
       </c>
       <c r="W8" t="n">
-        <v>-31.465</v>
+        <v>-31.421</v>
       </c>
     </row>
     <row r="9">
@@ -3364,12 +3388,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3391,7 +3415,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N9" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="O9" t="n">
         <v>49.3</v>
@@ -3414,13 +3438,13 @@
         <v>13.28</v>
       </c>
       <c r="U9" t="n">
-        <v>9.141</v>
+        <v>8.964</v>
       </c>
       <c r="V9" t="n">
         <v>-0.962</v>
       </c>
       <c r="W9" t="n">
-        <v>-16.714</v>
+        <v>-16.687</v>
       </c>
     </row>
     <row r="10">
@@ -3439,12 +3463,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3466,7 +3490,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>114.1</v>
+        <v>113.9</v>
       </c>
       <c r="O10" t="n">
         <v>50.4</v>
@@ -3489,13 +3513,13 @@
         <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>10.926</v>
+        <v>11.77</v>
       </c>
       <c r="V10" t="n">
         <v>-2.455</v>
       </c>
       <c r="W10" t="n">
-        <v>-27.245</v>
+        <v>-27.452</v>
       </c>
     </row>
     <row r="11">
@@ -3514,12 +3538,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3541,7 +3565,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>180.1</v>
+        <v>179.7</v>
       </c>
       <c r="O11" t="n">
         <v>52.1</v>
@@ -3564,13 +3588,13 @@
         <v>24.617</v>
       </c>
       <c r="U11" t="n">
-        <v>31.472</v>
+        <v>32.991</v>
       </c>
       <c r="V11" t="n">
         <v>6.527</v>
       </c>
       <c r="W11" t="n">
-        <v>-42.934</v>
+        <v>-43.43</v>
       </c>
     </row>
     <row r="12">
@@ -3589,12 +3613,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3612,14 +3636,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.11% / +20.01% / -1.13% | TKFEN.IS: +9.84% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | TKFEN.IS: +10.49% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>9.808448101895584</v>
+        <v>9.433467422417575</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3628,7 +3652,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="O12" t="n">
         <v>43.3</v>
@@ -3651,13 +3675,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>42.785</v>
+        <v>42.297</v>
       </c>
       <c r="V12" t="n">
-        <v>53.008</v>
+        <v>52.485</v>
       </c>
       <c r="W12" t="n">
-        <v>-17.504</v>
+        <v>-17.991</v>
       </c>
     </row>
     <row r="13">
@@ -3671,80 +3695,68 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
+          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CVKMD.IS, KRDMD.IS</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>CVKMD.IS: 2026-09-04 | KRDMD.IS: 2026-09-07</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>-0.49388395046156</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>CVKMD.IS: +0.70% / +3.03% / -0.16% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>8.530010255723974</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>-19.60937535624424</v>
+        <v>0.8142516931666233</v>
       </c>
       <c r="K13" t="n">
-        <v>4.120217744298538</v>
+        <v>3.846414277792909</v>
       </c>
       <c r="L13" t="n">
-        <v>19.61961325199098</v>
+        <v>9.181211458048665</v>
       </c>
       <c r="M13" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N13" t="n">
-        <v>88.8</v>
+        <v>35.6</v>
       </c>
       <c r="O13" t="n">
-        <v>45.8</v>
+        <v>50</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>18.132</v>
+        <v>8.083</v>
       </c>
       <c r="T13" t="n">
-        <v>18.132</v>
+        <v>7.916</v>
       </c>
       <c r="U13" t="n">
-        <v>1.525</v>
+        <v>13.72</v>
       </c>
       <c r="V13" t="n">
-        <v>8.723000000000001</v>
+        <v>4.916</v>
       </c>
       <c r="W13" t="n">
-        <v>-10.267</v>
+        <v>-5.191</v>
       </c>
     </row>
     <row r="14">
@@ -3758,45 +3770,45 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>8.530010255723974</v>
+        <v>32.90971238010212</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>0.8142516931666233</v>
+        <v>3.175499702073514</v>
       </c>
       <c r="K14" t="n">
-        <v>3.846414277792909</v>
+        <v>3.422248513714998</v>
       </c>
       <c r="L14" t="n">
-        <v>9.181211458048665</v>
+        <v>18.99889339779883</v>
       </c>
       <c r="M14" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N14" t="n">
-        <v>35.7</v>
+        <v>43.6</v>
       </c>
       <c r="O14" t="n">
-        <v>50</v>
+        <v>51.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3807,19 +3819,19 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>8.083</v>
+        <v>18.999</v>
       </c>
       <c r="T14" t="n">
-        <v>7.916</v>
+        <v>16.472</v>
       </c>
       <c r="U14" t="n">
-        <v>11.412</v>
+        <v>23.959</v>
       </c>
       <c r="V14" t="n">
-        <v>4.916</v>
+        <v>18.553</v>
       </c>
       <c r="W14" t="n">
-        <v>-5.085</v>
+        <v>-13.85</v>
       </c>
     </row>
     <row r="16">
@@ -3964,12 +3976,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3987,14 +3999,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -2.27% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +0.67% / +0.51% / -0.25% | ENERY.IS: -0.72% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.088167795945294</v>
+        <v>0.02900081220775785</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4003,10 +4015,10 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>93.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>44.1</v>
+        <v>44.7</v>
       </c>
       <c r="P18" t="n">
         <v>4.3</v>
@@ -4026,13 +4038,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>270.779</v>
+        <v>285.803</v>
       </c>
       <c r="V18" t="n">
-        <v>99.255</v>
+        <v>101.505</v>
       </c>
       <c r="W18" t="n">
-        <v>-45.913</v>
+        <v>-42.931</v>
       </c>
     </row>
     <row r="19">
@@ -4053,12 +4065,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -4080,7 +4092,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>119.6</v>
+        <v>119.3</v>
       </c>
       <c r="O19" t="n">
         <v>46.9</v>
@@ -4103,13 +4115,13 @@
         <v>25.928</v>
       </c>
       <c r="U19" t="n">
-        <v>55.153</v>
+        <v>56.945</v>
       </c>
       <c r="V19" t="n">
         <v>19.407</v>
       </c>
       <c r="W19" t="n">
-        <v>-54.31</v>
+        <v>-54.937</v>
       </c>
     </row>
     <row r="20">
@@ -4130,12 +4142,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4153,14 +4165,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.00% / 0.00% | ENERY.IS: -2.27% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +0.67% / +0.51% / -0.25% | ENERY.IS: -0.72% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.107969004700493</v>
+        <v>0.008975956914714089</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4169,10 +4181,10 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="O20" t="n">
-        <v>42.2</v>
+        <v>42.8</v>
       </c>
       <c r="P20" t="n">
         <v>4.7</v>
@@ -4192,13 +4204,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>267.957</v>
+        <v>282.839</v>
       </c>
       <c r="V20" t="n">
-        <v>81.45399999999999</v>
+        <v>83.504</v>
       </c>
       <c r="W20" t="n">
-        <v>-45.516</v>
+        <v>-42.552</v>
       </c>
     </row>
     <row r="21">
@@ -4219,12 +4231,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4246,7 +4258,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>180.1</v>
+        <v>179.7</v>
       </c>
       <c r="O21" t="n">
         <v>52.1</v>
@@ -4269,13 +4281,13 @@
         <v>24.617</v>
       </c>
       <c r="U21" t="n">
-        <v>31.472</v>
+        <v>32.991</v>
       </c>
       <c r="V21" t="n">
         <v>6.527</v>
       </c>
       <c r="W21" t="n">
-        <v>-42.934</v>
+        <v>-43.43</v>
       </c>
     </row>
     <row r="22">
@@ -4296,12 +4308,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4319,14 +4331,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.11% / +20.01% / -1.13% | CANTE.IS: +5.36% / +15.33% / -2.99% | ENERY.IS: -0.02% / +0.00% / 0.00% | SOKM.IS: -0.82% / +0.83% / -2.93% | TKFEN.IS: +9.84% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | CANTE.IS: +6.08% / +15.33% / -2.99% | ENERY.IS: +1.57% / +1.60% / 0.00% | SOKM.IS: -0.38% / +0.83% / -2.93% | TKFEN.IS: +10.49% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.28633977786256</v>
+        <v>-9.981740252180193</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4335,10 +4347,10 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>139.4</v>
+        <v>139.1</v>
       </c>
       <c r="O22" t="n">
-        <v>42.3</v>
+        <v>42.7</v>
       </c>
       <c r="P22" t="n">
         <v>5.7</v>
@@ -4358,13 +4370,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>22.073</v>
+        <v>22.487</v>
       </c>
       <c r="V22" t="n">
-        <v>11.538</v>
+        <v>11.917</v>
       </c>
       <c r="W22" t="n">
-        <v>-43.052</v>
+        <v>-42.638</v>
       </c>
     </row>
     <row r="23">
@@ -4385,12 +4397,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4408,14 +4420,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.11% / +20.01% / -1.13% | CANTE.IS: -2.31% / +3.11% / -3.83% | ENERY.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | CANTE.IS: -1.64% / +3.11% / -3.83% | ENERY.IS: +1.57% / +1.60% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.448690665428277</v>
+        <v>-2.227581041817817</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4424,10 +4436,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>153.8</v>
+        <v>153.5</v>
       </c>
       <c r="O23" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="P23" t="n">
         <v>4.2</v>
@@ -4447,13 +4459,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>24.192</v>
+        <v>25.421</v>
       </c>
       <c r="V23" t="n">
-        <v>2.244</v>
+        <v>2.475</v>
       </c>
       <c r="W23" t="n">
-        <v>-31.465</v>
+        <v>-31.421</v>
       </c>
     </row>
     <row r="24">
@@ -4474,12 +4486,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4501,7 +4513,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>114.1</v>
+        <v>113.9</v>
       </c>
       <c r="O24" t="n">
         <v>50.4</v>
@@ -4524,67 +4536,67 @@
         <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>10.926</v>
+        <v>11.77</v>
       </c>
       <c r="V24" t="n">
         <v>-2.455</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.245</v>
+        <v>-27.452</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>28.40086810394897</v>
+        <v>32.90971238010212</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>15.38514121842653</v>
+        <v>3.175499702073514</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.616392554049999</v>
+        <v>3.422248513714998</v>
       </c>
       <c r="L25" t="n">
-        <v>5.127814043936619</v>
+        <v>18.99889339779883</v>
       </c>
       <c r="M25" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>75.40000000000001</v>
+        <v>43.6</v>
       </c>
       <c r="O25" t="n">
-        <v>49.3</v>
+        <v>51.1</v>
       </c>
       <c r="P25" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4595,73 +4607,73 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>13.28</v>
+        <v>18.999</v>
       </c>
       <c r="T25" t="n">
-        <v>13.28</v>
+        <v>16.472</v>
       </c>
       <c r="U25" t="n">
-        <v>9.141</v>
+        <v>23.959</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.962</v>
+        <v>18.553</v>
       </c>
       <c r="W25" t="n">
-        <v>-16.714</v>
+        <v>-13.85</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>8.530010255723974</v>
+        <v>28.40086810394897</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>0.8142516931666233</v>
+        <v>15.38514121842653</v>
       </c>
       <c r="K26" t="n">
-        <v>3.846414277792909</v>
+        <v>-6.616392554049999</v>
       </c>
       <c r="L26" t="n">
-        <v>9.181211458048665</v>
+        <v>5.127814043936619</v>
       </c>
       <c r="M26" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>35.7</v>
+        <v>75.3</v>
       </c>
       <c r="O26" t="n">
-        <v>50</v>
+        <v>49.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4672,19 +4684,19 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>8.083</v>
+        <v>13.28</v>
       </c>
       <c r="T26" t="n">
-        <v>7.916</v>
+        <v>13.28</v>
       </c>
       <c r="U26" t="n">
-        <v>11.412</v>
+        <v>8.964</v>
       </c>
       <c r="V26" t="n">
-        <v>4.916</v>
+        <v>-0.962</v>
       </c>
       <c r="W26" t="n">
-        <v>-5.085</v>
+        <v>-16.687</v>
       </c>
     </row>
     <row r="27">
@@ -4695,85 +4707,73 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>6.880672511445463</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>BRSAN.IS: +14.11% / +20.01% / -1.13% | TKFEN.IS: +9.84% / +31.83% / -0.56%</t>
-        </is>
-      </c>
+        <v>8.530010255723974</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>-18.9000927288166</v>
+        <v>0.8142516931666233</v>
       </c>
       <c r="K27" t="n">
-        <v>9.808448101895584</v>
+        <v>3.846414277792909</v>
       </c>
       <c r="L27" t="n">
-        <v>31.31195090134997</v>
+        <v>9.181211458048665</v>
       </c>
       <c r="M27" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N27" t="n">
-        <v>48.1</v>
+        <v>35.6</v>
       </c>
       <c r="O27" t="n">
-        <v>43.3</v>
+        <v>50</v>
       </c>
       <c r="P27" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>28.439</v>
+        <v>8.083</v>
       </c>
       <c r="T27" t="n">
-        <v>28.439</v>
+        <v>7.916</v>
       </c>
       <c r="U27" t="n">
-        <v>42.785</v>
+        <v>13.72</v>
       </c>
       <c r="V27" t="n">
-        <v>53.008</v>
+        <v>4.916</v>
       </c>
       <c r="W27" t="n">
-        <v>-17.504</v>
+        <v>-5.191</v>
       </c>
     </row>
     <row r="28">
@@ -4784,62 +4784,62 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CVKMD.IS, KRDMD.IS</t>
+          <t>BRSAN.IS, TKFEN.IS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CVKMD.IS: 2026-09-04 | KRDMD.IS: 2026-09-07</t>
+          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>-0.49388395046156</v>
+        <v>6.880672511445463</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CVKMD.IS: +0.70% / +3.03% / -0.16% | KRDMD.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | TKFEN.IS: +10.49% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>-19.60937535624424</v>
+        <v>-18.9000927288166</v>
       </c>
       <c r="K28" t="n">
-        <v>4.120217744298538</v>
+        <v>9.433467422417575</v>
       </c>
       <c r="L28" t="n">
-        <v>19.61961325199098</v>
+        <v>31.31195090134997</v>
       </c>
       <c r="M28" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N28" t="n">
-        <v>88.8</v>
+        <v>48</v>
       </c>
       <c r="O28" t="n">
-        <v>45.8</v>
+        <v>43.3</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4850,19 +4850,19 @@
         <v>2</v>
       </c>
       <c r="S28" t="n">
-        <v>18.132</v>
+        <v>28.439</v>
       </c>
       <c r="T28" t="n">
-        <v>18.132</v>
+        <v>28.439</v>
       </c>
       <c r="U28" t="n">
-        <v>1.525</v>
+        <v>42.297</v>
       </c>
       <c r="V28" t="n">
-        <v>8.723000000000001</v>
+        <v>52.485</v>
       </c>
       <c r="W28" t="n">
-        <v>-10.267</v>
+        <v>-17.991</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | ENERY.IS: +0.91% / +1.67% / 0.00%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | ENERY.IS: +0.17% / +2.04% / -0.28%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-17.18554929213719</v>
+        <v>-17.80360150045105</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -795,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>64.27200000000001</v>
+        <v>63.046</v>
       </c>
       <c r="V3" t="n">
-        <v>12.51</v>
+        <v>11.67</v>
       </c>
       <c r="W3" t="n">
-        <v>-49.637</v>
+        <v>-50.863</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | ENERY.IS: +0.91% / +1.67% / 0.00%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | ENERY.IS: +0.17% / +2.04% / -0.28%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-17.18554929213719</v>
+        <v>-17.80360150045105</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1032,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>64.27200000000001</v>
+        <v>63.046</v>
       </c>
       <c r="V6" t="n">
-        <v>12.51</v>
+        <v>11.67</v>
       </c>
       <c r="W6" t="n">
-        <v>-49.637</v>
+        <v>-50.863</v>
       </c>
     </row>
     <row r="7">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | VAKBN.IS: +0.88% / +1.44% / 0.00%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | VAKBN.IS: +1.12% / +3.24% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.900205957831329</v>
+        <v>-7.147794950461972</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1119,13 +1119,13 @@
         <v>19.727</v>
       </c>
       <c r="U7" t="n">
-        <v>75.999</v>
+        <v>75.53100000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>27.394</v>
+        <v>27.055</v>
       </c>
       <c r="W7" t="n">
-        <v>-41.489</v>
+        <v>-41.957</v>
       </c>
     </row>
     <row r="8">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.86% / +2.33% / -1.61% | ENERY.IS: -1.38% / +1.27% / -3.44% | ENJSA.IS: -0.81% / +0.61% / -2.01%</t>
+          <t>ALARK.IS: +1.41% / +2.33% / -1.61% | ENERY.IS: -2.10% / +1.27% / -3.44% | ENJSA.IS: +0.07% / +0.61% / -2.01%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-15.07555155078539</v>
+        <v>-15.16780016374798</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1186,7 +1186,7 @@
         <v>191.8</v>
       </c>
       <c r="O8" t="n">
-        <v>46.8</v>
+        <v>47</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>48.201</v>
+        <v>48.04</v>
       </c>
       <c r="V8" t="n">
-        <v>12.754</v>
+        <v>12.631</v>
       </c>
       <c r="W8" t="n">
-        <v>-29.088</v>
+        <v>-29.249</v>
       </c>
     </row>
     <row r="9">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | ENERY.IS: +0.91% / +1.67% / 0.00%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | ENERY.IS: +0.17% / +2.04% / -0.28%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-17.18554929213719</v>
+        <v>-17.80360150045105</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1293,13 +1293,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>64.27200000000001</v>
+        <v>63.046</v>
       </c>
       <c r="V9" t="n">
-        <v>12.51</v>
+        <v>11.67</v>
       </c>
       <c r="W9" t="n">
-        <v>-49.637</v>
+        <v>-50.863</v>
       </c>
     </row>
     <row r="10">
@@ -1348,7 +1348,7 @@
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-23.34764362257953</v>
+        <v>-23.196743525561</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1374,19 +1374,19 @@
         <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>25.974</v>
+        <v>25.828</v>
       </c>
       <c r="T10" t="n">
-        <v>25.974</v>
+        <v>25.828</v>
       </c>
       <c r="U10" t="n">
-        <v>-7.18</v>
+        <v>-6.997</v>
       </c>
       <c r="V10" t="n">
-        <v>-13.696</v>
+        <v>-13.526</v>
       </c>
       <c r="W10" t="n">
-        <v>-32.568</v>
+        <v>-32.385</v>
       </c>
     </row>
     <row r="11">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TRALT.IS: +3.36% / +4.87% / -2.03%</t>
+          <t>TRALT.IS: +3.76% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-5.044425134583063</v>
       </c>
       <c r="K12" t="n">
-        <v>11.5843629794812</v>
+        <v>11.80183879379411</v>
       </c>
       <c r="L12" t="n">
         <v>9.344627019167174</v>
@@ -1542,13 +1542,13 @@
         <v>12.101</v>
       </c>
       <c r="U12" t="n">
-        <v>30.188</v>
+        <v>30.442</v>
       </c>
       <c r="V12" t="n">
-        <v>35.623</v>
+        <v>35.887</v>
       </c>
       <c r="W12" t="n">
-        <v>-7.591</v>
+        <v>-7.337</v>
       </c>
     </row>
     <row r="13">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.39% / +20.94% / 0.00% | CANTE.IS: +0.74% / +0.76% / 0.00% | RALYH.IS: +26.06% / +35.10% / -0.91%</t>
+          <t>BRSAN.IS: +13.99% / +20.94% / 0.00% | CANTE.IS: -0.02% / +0.76% / -0.76% | RALYH.IS: +27.50% / +35.10% / -0.91%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K13" t="n">
-        <v>11.28345449600658</v>
+        <v>11.33334983782466</v>
       </c>
       <c r="L13" t="n">
         <v>34.56349599547857</v>
@@ -1609,7 +1609,7 @@
         <v>70</v>
       </c>
       <c r="O13" t="n">
-        <v>44.4</v>
+        <v>43.7</v>
       </c>
       <c r="P13" t="n">
         <v>6.1</v>
@@ -1629,13 +1629,13 @@
         <v>23.777</v>
       </c>
       <c r="U13" t="n">
-        <v>47.185</v>
+        <v>47.251</v>
       </c>
       <c r="V13" t="n">
-        <v>41.027</v>
+        <v>41.09</v>
       </c>
       <c r="W13" t="n">
-        <v>-12.853</v>
+        <v>-12.787</v>
       </c>
     </row>
     <row r="14">
@@ -1677,14 +1677,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.74% / +0.76% / 0.00% | ENERY.IS: +0.91% / +1.67% / 0.00%</t>
+          <t>CANTE.IS: -0.02% / +0.76% / -0.76% | ENERY.IS: +0.17% / +2.04% / -0.28%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>5.691426106672592</v>
+        <v>4.902795597554532</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1696,7 +1696,7 @@
         <v>59.7</v>
       </c>
       <c r="O14" t="n">
-        <v>45.5</v>
+        <v>44.6</v>
       </c>
       <c r="P14" t="n">
         <v>6.3</v>
@@ -1716,13 +1716,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>82.506</v>
+        <v>81.14400000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>94.745</v>
+        <v>93.291</v>
       </c>
       <c r="W14" t="n">
-        <v>-28.744</v>
+        <v>-30.106</v>
       </c>
     </row>
     <row r="16">
@@ -1890,14 +1890,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | ENERY.IS: +0.91% / +1.67% / 0.00%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | ENERY.IS: +0.17% / +2.04% / -0.28%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-17.18554929213719</v>
+        <v>-17.80360150045105</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1929,13 +1929,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>64.27200000000001</v>
+        <v>63.046</v>
       </c>
       <c r="V18" t="n">
-        <v>12.51</v>
+        <v>11.67</v>
       </c>
       <c r="W18" t="n">
-        <v>-49.637</v>
+        <v>-50.863</v>
       </c>
     </row>
     <row r="19">
@@ -2133,14 +2133,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.86% / +2.33% / -1.61% | ENERY.IS: -1.38% / +1.27% / -3.44% | ENJSA.IS: -0.81% / +0.61% / -2.01%</t>
+          <t>ALARK.IS: +1.41% / +2.33% / -1.61% | ENERY.IS: -2.10% / +1.27% / -3.44% | ENJSA.IS: +0.07% / +0.61% / -2.01%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-15.07555155078539</v>
+        <v>-15.16780016374798</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2152,7 +2152,7 @@
         <v>191.8</v>
       </c>
       <c r="O21" t="n">
-        <v>46.8</v>
+        <v>47</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2172,13 +2172,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>48.201</v>
+        <v>48.04</v>
       </c>
       <c r="V21" t="n">
-        <v>12.754</v>
+        <v>12.631</v>
       </c>
       <c r="W21" t="n">
-        <v>-29.088</v>
+        <v>-29.249</v>
       </c>
     </row>
     <row r="22">
@@ -2222,14 +2222,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | VAKBN.IS: +0.88% / +1.44% / 0.00%</t>
+          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | VAKBN.IS: +1.12% / +3.24% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.900205957831329</v>
+        <v>-7.147794950461972</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2261,13 +2261,13 @@
         <v>19.727</v>
       </c>
       <c r="U22" t="n">
-        <v>75.999</v>
+        <v>75.53100000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>27.394</v>
+        <v>27.055</v>
       </c>
       <c r="W22" t="n">
-        <v>-41.489</v>
+        <v>-41.957</v>
       </c>
     </row>
     <row r="23">
@@ -2311,14 +2311,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.74% / +0.76% / 0.00% | ENERY.IS: +0.91% / +1.67% / 0.00%</t>
+          <t>CANTE.IS: -0.02% / +0.76% / -0.76% | ENERY.IS: +0.17% / +2.04% / -0.28%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>5.691426106672592</v>
+        <v>4.902795597554532</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2330,7 +2330,7 @@
         <v>59.7</v>
       </c>
       <c r="O23" t="n">
-        <v>45.5</v>
+        <v>44.6</v>
       </c>
       <c r="P23" t="n">
         <v>6.3</v>
@@ -2350,13 +2350,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>82.506</v>
+        <v>81.14400000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>94.745</v>
+        <v>93.291</v>
       </c>
       <c r="W23" t="n">
-        <v>-28.744</v>
+        <v>-30.106</v>
       </c>
     </row>
     <row r="24">
@@ -2477,14 +2477,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TRALT.IS: +3.36% / +4.87% / -2.03%</t>
+          <t>TRALT.IS: +3.76% / +4.87% / -2.03%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-5.044425134583063</v>
       </c>
       <c r="K25" t="n">
-        <v>11.5843629794812</v>
+        <v>11.80183879379411</v>
       </c>
       <c r="L25" t="n">
         <v>9.344627019167174</v>
@@ -2516,13 +2516,13 @@
         <v>12.101</v>
       </c>
       <c r="U25" t="n">
-        <v>30.188</v>
+        <v>30.442</v>
       </c>
       <c r="V25" t="n">
-        <v>35.623</v>
+        <v>35.887</v>
       </c>
       <c r="W25" t="n">
-        <v>-7.591</v>
+        <v>-7.337</v>
       </c>
     </row>
     <row r="26">
@@ -2573,7 +2573,7 @@
         <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>-23.34764362257953</v>
+        <v>-23.196743525561</v>
       </c>
       <c r="L26" t="n">
         <v>4.543450519200398</v>
@@ -2599,19 +2599,19 @@
         <v>4</v>
       </c>
       <c r="S26" t="n">
-        <v>25.974</v>
+        <v>25.828</v>
       </c>
       <c r="T26" t="n">
-        <v>25.974</v>
+        <v>25.828</v>
       </c>
       <c r="U26" t="n">
-        <v>-7.18</v>
+        <v>-6.997</v>
       </c>
       <c r="V26" t="n">
-        <v>-13.696</v>
+        <v>-13.526</v>
       </c>
       <c r="W26" t="n">
-        <v>-32.568</v>
+        <v>-32.385</v>
       </c>
     </row>
     <row r="27">
@@ -2655,14 +2655,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.39% / +20.94% / 0.00% | CANTE.IS: +0.74% / +0.76% / 0.00% | RALYH.IS: +26.06% / +35.10% / -0.91%</t>
+          <t>BRSAN.IS: +13.99% / +20.94% / 0.00% | CANTE.IS: -0.02% / +0.76% / -0.76% | RALYH.IS: +27.50% / +35.10% / -0.91%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>11.28345449600658</v>
+        <v>11.33334983782466</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2674,7 +2674,7 @@
         <v>70</v>
       </c>
       <c r="O27" t="n">
-        <v>44.4</v>
+        <v>43.7</v>
       </c>
       <c r="P27" t="n">
         <v>6.1</v>
@@ -2694,13 +2694,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>47.185</v>
+        <v>47.251</v>
       </c>
       <c r="V27" t="n">
-        <v>41.027</v>
+        <v>41.09</v>
       </c>
       <c r="W27" t="n">
-        <v>-12.853</v>
+        <v>-12.787</v>
       </c>
     </row>
   </sheetData>
@@ -2735,7 +2735,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2913,14 +2913,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.67% / +0.51% / -0.25% | ENERY.IS: -0.72% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: -0.86% / +0.51% / -1.01% | ENERY.IS: -2.25% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02900081220775785</v>
+        <v>-1.495439511291763</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2932,7 +2932,7 @@
         <v>93.09999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>44.7</v>
+        <v>44.1</v>
       </c>
       <c r="P3" t="n">
         <v>4.3</v>
@@ -2952,13 +2952,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>285.803</v>
+        <v>279.923</v>
       </c>
       <c r="V3" t="n">
-        <v>101.505</v>
+        <v>98.435</v>
       </c>
       <c r="W3" t="n">
-        <v>-42.931</v>
+        <v>-48.811</v>
       </c>
     </row>
     <row r="4">
@@ -3075,14 +3075,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.67% / +0.51% / -0.25% | ENERY.IS: -0.72% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: -0.86% / +0.51% / -1.01% | ENERY.IS: -2.25% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008975956914714089</v>
+        <v>-1.515159188120219</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3094,7 +3094,7 @@
         <v>82.2</v>
       </c>
       <c r="O5" t="n">
-        <v>42.8</v>
+        <v>42.2</v>
       </c>
       <c r="P5" t="n">
         <v>4.7</v>
@@ -3114,13 +3114,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>282.839</v>
+        <v>277.004</v>
       </c>
       <c r="V5" t="n">
-        <v>83.504</v>
+        <v>80.70699999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-42.552</v>
+        <v>-48.387</v>
       </c>
     </row>
     <row r="6">
@@ -3162,14 +3162,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | CANTE.IS: +6.08% / +15.33% / -2.99% | ENERY.IS: +1.57% / +1.60% / 0.00% | SOKM.IS: -0.38% / +0.83% / -2.93% | TKFEN.IS: +10.49% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.14% / +20.01% / -1.13% | CANTE.IS: +4.47% / +15.33% / -2.99% | ENERY.IS: -0.00% / +1.97% / -0.34% | SOKM.IS: -0.90% / +1.35% / -2.93% | TKFEN.IS: +11.66% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.981740252180193</v>
+        <v>-10.48334673483699</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3201,13 +3201,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>22.487</v>
+        <v>21.804</v>
       </c>
       <c r="V6" t="n">
-        <v>11.917</v>
+        <v>11.293</v>
       </c>
       <c r="W6" t="n">
-        <v>-42.638</v>
+        <v>-43.32</v>
       </c>
     </row>
     <row r="7">
@@ -3324,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | CANTE.IS: -1.64% / +3.11% / -3.83% | ENERY.IS: +1.57% / +1.60% / 0.00%</t>
+          <t>BRSAN.IS: +12.14% / +20.01% / -1.13% | CANTE.IS: -3.13% / +3.11% / -3.83% | ENERY.IS: -0.00% / +1.97% / -0.34%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.227581041817817</v>
+        <v>-3.136569046306426</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3363,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>25.421</v>
+        <v>24.255</v>
       </c>
       <c r="V8" t="n">
-        <v>2.475</v>
+        <v>1.523</v>
       </c>
       <c r="W8" t="n">
-        <v>-31.421</v>
+        <v>-32.587</v>
       </c>
     </row>
     <row r="9">
@@ -3636,14 +3636,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | TKFEN.IS: +10.49% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.14% / +20.01% / -1.13% | TKFEN.IS: +11.66% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>9.433467422417575</v>
+        <v>9.803058637924366</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3675,13 +3675,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>42.297</v>
+        <v>42.778</v>
       </c>
       <c r="V12" t="n">
-        <v>52.485</v>
+        <v>53</v>
       </c>
       <c r="W12" t="n">
-        <v>-17.991</v>
+        <v>-17.511</v>
       </c>
     </row>
     <row r="13">
@@ -3999,14 +3999,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.67% / +0.51% / -0.25% | ENERY.IS: -0.72% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: -0.86% / +0.51% / -1.01% | ENERY.IS: -2.25% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02900081220775785</v>
+        <v>-1.495439511291763</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4018,7 +4018,7 @@
         <v>93.09999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>44.7</v>
+        <v>44.1</v>
       </c>
       <c r="P18" t="n">
         <v>4.3</v>
@@ -4038,13 +4038,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>285.803</v>
+        <v>279.923</v>
       </c>
       <c r="V18" t="n">
-        <v>101.505</v>
+        <v>98.435</v>
       </c>
       <c r="W18" t="n">
-        <v>-42.931</v>
+        <v>-48.811</v>
       </c>
     </row>
     <row r="19">
@@ -4165,14 +4165,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.67% / +0.51% / -0.25% | ENERY.IS: -0.72% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: -0.86% / +0.51% / -1.01% | ENERY.IS: -2.25% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>0.008975956914714089</v>
+        <v>-1.515159188120219</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4184,7 +4184,7 @@
         <v>82.2</v>
       </c>
       <c r="O20" t="n">
-        <v>42.8</v>
+        <v>42.2</v>
       </c>
       <c r="P20" t="n">
         <v>4.7</v>
@@ -4204,13 +4204,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>282.839</v>
+        <v>277.004</v>
       </c>
       <c r="V20" t="n">
-        <v>83.504</v>
+        <v>80.70699999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>-42.552</v>
+        <v>-48.387</v>
       </c>
     </row>
     <row r="21">
@@ -4331,14 +4331,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | CANTE.IS: +6.08% / +15.33% / -2.99% | ENERY.IS: +1.57% / +1.60% / 0.00% | SOKM.IS: -0.38% / +0.83% / -2.93% | TKFEN.IS: +10.49% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.14% / +20.01% / -1.13% | CANTE.IS: +4.47% / +15.33% / -2.99% | ENERY.IS: -0.00% / +1.97% / -0.34% | SOKM.IS: -0.90% / +1.35% / -2.93% | TKFEN.IS: +11.66% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-9.981740252180193</v>
+        <v>-10.48334673483699</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4370,13 +4370,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>22.487</v>
+        <v>21.804</v>
       </c>
       <c r="V22" t="n">
-        <v>11.917</v>
+        <v>11.293</v>
       </c>
       <c r="W22" t="n">
-        <v>-42.638</v>
+        <v>-43.32</v>
       </c>
     </row>
     <row r="23">
@@ -4420,14 +4420,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | CANTE.IS: -1.64% / +3.11% / -3.83% | ENERY.IS: +1.57% / +1.60% / 0.00%</t>
+          <t>BRSAN.IS: +12.14% / +20.01% / -1.13% | CANTE.IS: -3.13% / +3.11% / -3.83% | ENERY.IS: -0.00% / +1.97% / -0.34%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.227581041817817</v>
+        <v>-3.136569046306426</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4459,13 +4459,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>25.421</v>
+        <v>24.255</v>
       </c>
       <c r="V23" t="n">
-        <v>2.475</v>
+        <v>1.523</v>
       </c>
       <c r="W23" t="n">
-        <v>-31.421</v>
+        <v>-32.587</v>
       </c>
     </row>
     <row r="24">
@@ -4817,14 +4817,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | TKFEN.IS: +10.49% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.14% / +20.01% / -1.13% | TKFEN.IS: +11.66% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K28" t="n">
-        <v>9.433467422417575</v>
+        <v>9.803058637924366</v>
       </c>
       <c r="L28" t="n">
         <v>31.31195090134997</v>
@@ -4856,13 +4856,13 @@
         <v>28.439</v>
       </c>
       <c r="U28" t="n">
-        <v>42.297</v>
+        <v>42.778</v>
       </c>
       <c r="V28" t="n">
-        <v>52.485</v>
+        <v>53</v>
       </c>
       <c r="W28" t="n">
-        <v>-17.991</v>
+        <v>-17.511</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | ENERY.IS: +0.17% / +2.04% / -0.28%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | ENERY.IS: +0.26% / +2.04% / -0.28%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-17.80360150045105</v>
+        <v>-17.44850906618763</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -795,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>63.046</v>
+        <v>63.75</v>
       </c>
       <c r="V3" t="n">
-        <v>11.67</v>
+        <v>12.152</v>
       </c>
       <c r="W3" t="n">
-        <v>-50.863</v>
+        <v>-50.159</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | ENERY.IS: +0.17% / +2.04% / -0.28%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | ENERY.IS: +0.26% / +2.04% / -0.28%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-17.80360150045105</v>
+        <v>-17.44850906618763</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1032,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>63.046</v>
+        <v>63.75</v>
       </c>
       <c r="V6" t="n">
-        <v>11.67</v>
+        <v>12.152</v>
       </c>
       <c r="W6" t="n">
-        <v>-50.863</v>
+        <v>-50.159</v>
       </c>
     </row>
     <row r="7">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | VAKBN.IS: +1.12% / +3.24% / 0.00%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | VAKBN.IS: +2.50% / +3.24% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.147794950461972</v>
+        <v>-6.16162134261018</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1119,13 +1119,13 @@
         <v>19.727</v>
       </c>
       <c r="U7" t="n">
-        <v>75.53100000000001</v>
+        <v>77.396</v>
       </c>
       <c r="V7" t="n">
-        <v>27.055</v>
+        <v>28.404</v>
       </c>
       <c r="W7" t="n">
-        <v>-41.957</v>
+        <v>-40.093</v>
       </c>
     </row>
     <row r="8">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.41% / +2.33% / -1.61% | ENERY.IS: -2.10% / +1.27% / -3.44% | ENJSA.IS: +0.07% / +0.61% / -2.01%</t>
+          <t>ALARK.IS: +2.13% / +2.33% / -1.61% | ENERY.IS: -2.01% / +1.27% / -3.44% | ENJSA.IS: +0.24% / +1.14% / -2.01%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-15.16780016374798</v>
+        <v>-14.89520007800421</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>48.04</v>
+        <v>48.515</v>
       </c>
       <c r="V8" t="n">
-        <v>12.631</v>
+        <v>12.993</v>
       </c>
       <c r="W8" t="n">
-        <v>-29.249</v>
+        <v>-28.773</v>
       </c>
     </row>
     <row r="9">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | ENERY.IS: +0.17% / +2.04% / -0.28%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | ENERY.IS: +0.26% / +2.04% / -0.28%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-17.80360150045105</v>
+        <v>-17.44850906618763</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1293,13 +1293,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>63.046</v>
+        <v>63.75</v>
       </c>
       <c r="V9" t="n">
-        <v>11.67</v>
+        <v>12.152</v>
       </c>
       <c r="W9" t="n">
-        <v>-50.863</v>
+        <v>-50.159</v>
       </c>
     </row>
     <row r="10">
@@ -1348,7 +1348,7 @@
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-23.196743525561</v>
+        <v>-23.21046171619905</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1374,19 +1374,19 @@
         <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>25.828</v>
+        <v>25.841</v>
       </c>
       <c r="T10" t="n">
-        <v>25.828</v>
+        <v>25.841</v>
       </c>
       <c r="U10" t="n">
-        <v>-6.997</v>
+        <v>-7.014</v>
       </c>
       <c r="V10" t="n">
-        <v>-13.526</v>
+        <v>-13.542</v>
       </c>
       <c r="W10" t="n">
-        <v>-32.385</v>
+        <v>-32.402</v>
       </c>
     </row>
     <row r="11">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1490,42 +1490,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TRALT.IS</t>
+          <t>BRSAN.IS, CANTE.IS, RALYH.IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>TRALT.IS: 2026-09-02</t>
+          <t>BRSAN.IS: 2026-08-13 | CANTE.IS: 2026-09-07 | RALYH.IS: 2026-07-13</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>25.65141339163128</v>
+        <v>13.58351811074014</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TRALT.IS: +3.76% / +4.87% / -2.03%</t>
+          <t>BRSAN.IS: +14.39% / +20.94% / 0.00% | CANTE.IS: +0.74% / +0.76% / -0.76% | RALYH.IS: +30.86% / +35.10% / -0.91%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-5.044425134583063</v>
+        <v>-10.39434387728287</v>
       </c>
       <c r="K12" t="n">
-        <v>11.80183879379411</v>
+        <v>12.77228390050964</v>
       </c>
       <c r="L12" t="n">
-        <v>9.344627019167174</v>
+        <v>34.56349599547857</v>
       </c>
       <c r="M12" t="n">
-        <v>66.66666666666666</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>58.7</v>
+        <v>70</v>
       </c>
       <c r="O12" t="n">
-        <v>51.3</v>
+        <v>44.4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>12.101</v>
+        <v>23.777</v>
       </c>
       <c r="T12" t="n">
-        <v>12.101</v>
+        <v>23.777</v>
       </c>
       <c r="U12" t="n">
-        <v>30.442</v>
+        <v>49.154</v>
       </c>
       <c r="V12" t="n">
-        <v>35.887</v>
+        <v>42.914</v>
       </c>
       <c r="W12" t="n">
-        <v>-7.337</v>
+        <v>-10.884</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BRSAN.IS, CANTE.IS, RALYH.IS</t>
+          <t>TRALT.IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-13 | CANTE.IS: 2026-09-07 | RALYH.IS: 2026-07-13</t>
+          <t>TRALT.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>13.58351811074014</v>
+        <v>25.65141339163128</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.99% / +20.94% / 0.00% | CANTE.IS: -0.02% / +0.76% / -0.76% | RALYH.IS: +27.50% / +35.10% / -0.91%</t>
+          <t>TRALT.IS: +4.65% / +5.07% / -2.03%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-10.39434387728287</v>
+        <v>-5.044425134583063</v>
       </c>
       <c r="K13" t="n">
-        <v>11.33334983782466</v>
+        <v>12.29115937599823</v>
       </c>
       <c r="L13" t="n">
-        <v>34.56349599547857</v>
+        <v>9.344627019167174</v>
       </c>
       <c r="M13" t="n">
-        <v>77.77777777777779</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N13" t="n">
-        <v>70</v>
+        <v>58.7</v>
       </c>
       <c r="O13" t="n">
-        <v>43.7</v>
+        <v>51.3</v>
       </c>
       <c r="P13" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1620,22 +1620,22 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>23.777</v>
+        <v>12.101</v>
       </c>
       <c r="T13" t="n">
-        <v>23.777</v>
+        <v>12.101</v>
       </c>
       <c r="U13" t="n">
-        <v>47.251</v>
+        <v>31.013</v>
       </c>
       <c r="V13" t="n">
-        <v>41.09</v>
+        <v>36.482</v>
       </c>
       <c r="W13" t="n">
-        <v>-12.787</v>
+        <v>-6.766</v>
       </c>
     </row>
     <row r="14">
@@ -1677,14 +1677,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.76% / -0.76% | ENERY.IS: +0.17% / +2.04% / -0.28%</t>
+          <t>CANTE.IS: +0.74% / +0.76% / -0.76% | ENERY.IS: +0.26% / +2.04% / -0.28%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>4.902795597554532</v>
+        <v>5.351463350312224</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1696,7 +1696,7 @@
         <v>59.7</v>
       </c>
       <c r="O14" t="n">
-        <v>44.6</v>
+        <v>45.5</v>
       </c>
       <c r="P14" t="n">
         <v>6.3</v>
@@ -1716,13 +1716,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>81.14400000000001</v>
+        <v>81.919</v>
       </c>
       <c r="V14" t="n">
-        <v>93.291</v>
+        <v>94.11799999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>-30.106</v>
+        <v>-29.331</v>
       </c>
     </row>
     <row r="16">
@@ -1890,14 +1890,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | ENERY.IS: +0.17% / +2.04% / -0.28%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | ENERY.IS: +0.26% / +2.04% / -0.28%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-17.80360150045105</v>
+        <v>-17.44850906618763</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1929,13 +1929,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>63.046</v>
+        <v>63.75</v>
       </c>
       <c r="V18" t="n">
-        <v>11.67</v>
+        <v>12.152</v>
       </c>
       <c r="W18" t="n">
-        <v>-50.863</v>
+        <v>-50.159</v>
       </c>
     </row>
     <row r="19">
@@ -2133,14 +2133,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +1.41% / +2.33% / -1.61% | ENERY.IS: -2.10% / +1.27% / -3.44% | ENJSA.IS: +0.07% / +0.61% / -2.01%</t>
+          <t>ALARK.IS: +2.13% / +2.33% / -1.61% | ENERY.IS: -2.01% / +1.27% / -3.44% | ENJSA.IS: +0.24% / +1.14% / -2.01%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-15.16780016374798</v>
+        <v>-14.89520007800421</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2172,13 +2172,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>48.04</v>
+        <v>48.515</v>
       </c>
       <c r="V21" t="n">
-        <v>12.631</v>
+        <v>12.993</v>
       </c>
       <c r="W21" t="n">
-        <v>-29.249</v>
+        <v>-28.773</v>
       </c>
     </row>
     <row r="22">
@@ -2222,14 +2222,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -1.52% / +3.76% / -3.01% | VAKBN.IS: +1.12% / +3.24% / 0.00%</t>
+          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | VAKBN.IS: +2.50% / +3.24% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.147794950461972</v>
+        <v>-6.16162134261018</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2261,13 +2261,13 @@
         <v>19.727</v>
       </c>
       <c r="U22" t="n">
-        <v>75.53100000000001</v>
+        <v>77.396</v>
       </c>
       <c r="V22" t="n">
-        <v>27.055</v>
+        <v>28.404</v>
       </c>
       <c r="W22" t="n">
-        <v>-41.957</v>
+        <v>-40.093</v>
       </c>
     </row>
     <row r="23">
@@ -2311,14 +2311,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +0.76% / -0.76% | ENERY.IS: +0.17% / +2.04% / -0.28%</t>
+          <t>CANTE.IS: +0.74% / +0.76% / -0.76% | ENERY.IS: +0.26% / +2.04% / -0.28%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>4.902795597554532</v>
+        <v>5.351463350312224</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2330,7 +2330,7 @@
         <v>59.7</v>
       </c>
       <c r="O23" t="n">
-        <v>44.6</v>
+        <v>45.5</v>
       </c>
       <c r="P23" t="n">
         <v>6.3</v>
@@ -2350,13 +2350,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>81.14400000000001</v>
+        <v>81.919</v>
       </c>
       <c r="V23" t="n">
-        <v>93.291</v>
+        <v>94.11799999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>-30.106</v>
+        <v>-29.331</v>
       </c>
     </row>
     <row r="24">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2477,14 +2477,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TRALT.IS: +3.76% / +4.87% / -2.03%</t>
+          <t>TRALT.IS: +4.65% / +5.07% / -2.03%</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>-5.044425134583063</v>
       </c>
       <c r="K25" t="n">
-        <v>11.80183879379411</v>
+        <v>12.29115937599823</v>
       </c>
       <c r="L25" t="n">
         <v>9.344627019167174</v>
@@ -2516,13 +2516,13 @@
         <v>12.101</v>
       </c>
       <c r="U25" t="n">
-        <v>30.442</v>
+        <v>31.013</v>
       </c>
       <c r="V25" t="n">
-        <v>35.887</v>
+        <v>36.482</v>
       </c>
       <c r="W25" t="n">
-        <v>-7.337</v>
+        <v>-6.766</v>
       </c>
     </row>
     <row r="26">
@@ -2573,7 +2573,7 @@
         <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>-23.196743525561</v>
+        <v>-23.21046171619905</v>
       </c>
       <c r="L26" t="n">
         <v>4.543450519200398</v>
@@ -2599,19 +2599,19 @@
         <v>4</v>
       </c>
       <c r="S26" t="n">
-        <v>25.828</v>
+        <v>25.841</v>
       </c>
       <c r="T26" t="n">
-        <v>25.828</v>
+        <v>25.841</v>
       </c>
       <c r="U26" t="n">
-        <v>-6.997</v>
+        <v>-7.014</v>
       </c>
       <c r="V26" t="n">
-        <v>-13.526</v>
+        <v>-13.542</v>
       </c>
       <c r="W26" t="n">
-        <v>-32.385</v>
+        <v>-32.402</v>
       </c>
     </row>
     <row r="27">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2655,14 +2655,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +13.99% / +20.94% / 0.00% | CANTE.IS: -0.02% / +0.76% / -0.76% | RALYH.IS: +27.50% / +35.10% / -0.91%</t>
+          <t>BRSAN.IS: +14.39% / +20.94% / 0.00% | CANTE.IS: +0.74% / +0.76% / -0.76% | RALYH.IS: +30.86% / +35.10% / -0.91%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>11.33334983782466</v>
+        <v>12.77228390050964</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2674,7 +2674,7 @@
         <v>70</v>
       </c>
       <c r="O27" t="n">
-        <v>43.7</v>
+        <v>44.4</v>
       </c>
       <c r="P27" t="n">
         <v>6.1</v>
@@ -2694,13 +2694,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>47.251</v>
+        <v>49.154</v>
       </c>
       <c r="V27" t="n">
-        <v>41.09</v>
+        <v>42.914</v>
       </c>
       <c r="W27" t="n">
-        <v>-12.787</v>
+        <v>-10.884</v>
       </c>
     </row>
   </sheetData>
@@ -2735,7 +2735,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2913,14 +2913,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.86% / +0.51% / -1.01% | ENERY.IS: -2.25% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +1.43% / +1.28% / -1.01% | ENERY.IS: -2.07% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.495439511291763</v>
+        <v>-0.2709940569649016</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2932,7 +2932,7 @@
         <v>93.09999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>44.1</v>
+        <v>44.7</v>
       </c>
       <c r="P3" t="n">
         <v>4.3</v>
@@ -2952,13 +2952,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>279.923</v>
+        <v>284.645</v>
       </c>
       <c r="V3" t="n">
-        <v>98.435</v>
+        <v>100.901</v>
       </c>
       <c r="W3" t="n">
-        <v>-48.811</v>
+        <v>-44.088</v>
       </c>
     </row>
     <row r="4">
@@ -3075,14 +3075,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.86% / +0.51% / -1.01% | ENERY.IS: -2.25% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +1.43% / +1.28% / -1.01% | ENERY.IS: -2.07% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.515159188120219</v>
+        <v>-0.2909588561362586</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3094,7 +3094,7 @@
         <v>82.2</v>
       </c>
       <c r="O5" t="n">
-        <v>42.2</v>
+        <v>42.8</v>
       </c>
       <c r="P5" t="n">
         <v>4.7</v>
@@ -3114,13 +3114,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>277.004</v>
+        <v>281.691</v>
       </c>
       <c r="V5" t="n">
-        <v>80.70699999999999</v>
+        <v>82.953</v>
       </c>
       <c r="W5" t="n">
-        <v>-48.387</v>
+        <v>-43.7</v>
       </c>
     </row>
     <row r="6">
@@ -3162,14 +3162,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.14% / +20.01% / -1.13% | CANTE.IS: +4.47% / +15.33% / -2.99% | ENERY.IS: -0.00% / +1.97% / -0.34% | SOKM.IS: -0.90% / +1.35% / -2.93% | TKFEN.IS: +11.66% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | CANTE.IS: +6.88% / +15.33% / -2.99% | ENERY.IS: +0.18% / +1.98% / -0.34% | SOKM.IS: -0.04% / +1.35% / -2.93% | TKFEN.IS: +12.88% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.48334673483699</v>
+        <v>-9.60114731880034</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3201,13 +3201,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>21.804</v>
+        <v>23.005</v>
       </c>
       <c r="V6" t="n">
-        <v>11.293</v>
+        <v>12.39</v>
       </c>
       <c r="W6" t="n">
-        <v>-43.32</v>
+        <v>-42.12</v>
       </c>
     </row>
     <row r="7">
@@ -3324,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.14% / +20.01% / -1.13% | CANTE.IS: -3.13% / +3.11% / -3.83% | ENERY.IS: -0.00% / +1.97% / -0.34%</t>
+          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | CANTE.IS: -0.89% / +3.11% / -3.83% | ENERY.IS: +0.18% / +1.98% / -0.34%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.136569046306426</v>
+        <v>-2.401789892096018</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3363,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>24.255</v>
+        <v>25.198</v>
       </c>
       <c r="V8" t="n">
-        <v>1.523</v>
+        <v>2.293</v>
       </c>
       <c r="W8" t="n">
-        <v>-32.587</v>
+        <v>-31.645</v>
       </c>
     </row>
     <row r="9">
@@ -3636,14 +3636,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.14% / +20.01% / -1.13% | TKFEN.IS: +11.66% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | TKFEN.IS: +12.88% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>9.803058637924366</v>
+        <v>10.64702958474606</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3675,13 +3675,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>42.778</v>
+        <v>43.875</v>
       </c>
       <c r="V12" t="n">
-        <v>53</v>
+        <v>54.176</v>
       </c>
       <c r="W12" t="n">
-        <v>-17.511</v>
+        <v>-16.413</v>
       </c>
     </row>
     <row r="13">
@@ -3999,14 +3999,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.86% / +0.51% / -1.01% | ENERY.IS: -2.25% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +1.43% / +1.28% / -1.01% | ENERY.IS: -2.07% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.495439511291763</v>
+        <v>-0.2709940569649016</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4018,7 +4018,7 @@
         <v>93.09999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>44.1</v>
+        <v>44.7</v>
       </c>
       <c r="P18" t="n">
         <v>4.3</v>
@@ -4038,13 +4038,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>279.923</v>
+        <v>284.645</v>
       </c>
       <c r="V18" t="n">
-        <v>98.435</v>
+        <v>100.901</v>
       </c>
       <c r="W18" t="n">
-        <v>-48.811</v>
+        <v>-44.088</v>
       </c>
     </row>
     <row r="19">
@@ -4165,14 +4165,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.86% / +0.51% / -1.01% | ENERY.IS: -2.25% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +1.43% / +1.28% / -1.01% | ENERY.IS: -2.07% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.515159188120219</v>
+        <v>-0.2909588561362586</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4184,7 +4184,7 @@
         <v>82.2</v>
       </c>
       <c r="O20" t="n">
-        <v>42.2</v>
+        <v>42.8</v>
       </c>
       <c r="P20" t="n">
         <v>4.7</v>
@@ -4204,13 +4204,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>277.004</v>
+        <v>281.691</v>
       </c>
       <c r="V20" t="n">
-        <v>80.70699999999999</v>
+        <v>82.953</v>
       </c>
       <c r="W20" t="n">
-        <v>-48.387</v>
+        <v>-43.7</v>
       </c>
     </row>
     <row r="21">
@@ -4331,14 +4331,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.14% / +20.01% / -1.13% | CANTE.IS: +4.47% / +15.33% / -2.99% | ENERY.IS: -0.00% / +1.97% / -0.34% | SOKM.IS: -0.90% / +1.35% / -2.93% | TKFEN.IS: +11.66% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | CANTE.IS: +6.88% / +15.33% / -2.99% | ENERY.IS: +0.18% / +1.98% / -0.34% | SOKM.IS: -0.04% / +1.35% / -2.93% | TKFEN.IS: +12.88% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.48334673483699</v>
+        <v>-9.60114731880034</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4370,13 +4370,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>21.804</v>
+        <v>23.005</v>
       </c>
       <c r="V22" t="n">
-        <v>11.293</v>
+        <v>12.39</v>
       </c>
       <c r="W22" t="n">
-        <v>-43.32</v>
+        <v>-42.12</v>
       </c>
     </row>
     <row r="23">
@@ -4420,14 +4420,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.14% / +20.01% / -1.13% | CANTE.IS: -3.13% / +3.11% / -3.83% | ENERY.IS: -0.00% / +1.97% / -0.34%</t>
+          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | CANTE.IS: -0.89% / +3.11% / -3.83% | ENERY.IS: +0.18% / +1.98% / -0.34%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.136569046306426</v>
+        <v>-2.401789892096018</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4459,13 +4459,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>24.255</v>
+        <v>25.198</v>
       </c>
       <c r="V23" t="n">
-        <v>1.523</v>
+        <v>2.293</v>
       </c>
       <c r="W23" t="n">
-        <v>-32.587</v>
+        <v>-31.645</v>
       </c>
     </row>
     <row r="24">
@@ -4817,14 +4817,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.14% / +20.01% / -1.13% | TKFEN.IS: +11.66% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | TKFEN.IS: +12.88% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K28" t="n">
-        <v>9.803058637924366</v>
+        <v>10.64702958474606</v>
       </c>
       <c r="L28" t="n">
         <v>31.31195090134997</v>
@@ -4856,13 +4856,13 @@
         <v>28.439</v>
       </c>
       <c r="U28" t="n">
-        <v>42.778</v>
+        <v>43.875</v>
       </c>
       <c r="V28" t="n">
-        <v>53</v>
+        <v>54.176</v>
       </c>
       <c r="W28" t="n">
-        <v>-17.511</v>
+        <v>-16.413</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | ENERY.IS: +0.26% / +2.04% / -0.28%</t>
+          <t>CANTE.IS: -0.02% / +3.76% / -3.01% | ENERY.IS: +0.26% / +2.04% / -0.46%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-17.44850906618763</v>
+        <v>-17.13098220836055</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -795,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>63.75</v>
+        <v>64.38</v>
       </c>
       <c r="V3" t="n">
-        <v>12.152</v>
+        <v>12.584</v>
       </c>
       <c r="W3" t="n">
-        <v>-50.159</v>
+        <v>-49.529</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | ENERY.IS: +0.26% / +2.04% / -0.28%</t>
+          <t>CANTE.IS: -0.02% / +3.76% / -3.01% | ENERY.IS: +0.26% / +2.04% / -0.46%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-17.44850906618763</v>
+        <v>-17.13098220836055</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1032,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>63.75</v>
+        <v>64.38</v>
       </c>
       <c r="V6" t="n">
-        <v>12.152</v>
+        <v>12.584</v>
       </c>
       <c r="W6" t="n">
-        <v>-50.159</v>
+        <v>-49.529</v>
       </c>
     </row>
     <row r="7">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CANTE.IS, VAKBN.IS</t>
+          <t>BRSAN.IS, CANTE.IS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | VAKBN.IS: 2026-09-07</t>
+          <t>BRSAN.IS: 2026-09-08 | CANTE.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | VAKBN.IS: +2.50% / +3.24% / 0.00%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.02% / +3.76% / -3.01%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.16162134261018</v>
+        <v>-2.432112961359056</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1096,13 +1096,13 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>134.6</v>
+        <v>135.1</v>
       </c>
       <c r="O7" t="n">
-        <v>47.3</v>
+        <v>47.1</v>
       </c>
       <c r="P7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1119,13 +1119,13 @@
         <v>19.727</v>
       </c>
       <c r="U7" t="n">
-        <v>77.396</v>
+        <v>84.446</v>
       </c>
       <c r="V7" t="n">
-        <v>28.404</v>
+        <v>33.508</v>
       </c>
       <c r="W7" t="n">
-        <v>-40.093</v>
+        <v>-33.042</v>
       </c>
     </row>
     <row r="8">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.13% / +2.33% / -1.61% | ENERY.IS: -2.01% / +1.27% / -3.44% | ENJSA.IS: +0.24% / +1.14% / -2.01%</t>
+          <t>ALARK.IS: +2.93% / +2.95% / -1.61% | ENERY.IS: -2.01% / +1.27% / -3.44% | ENJSA.IS: +0.68% / +1.14% / -2.01%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-14.89520007800421</v>
+        <v>-14.5520555000352</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>48.515</v>
+        <v>49.114</v>
       </c>
       <c r="V8" t="n">
-        <v>12.993</v>
+        <v>13.449</v>
       </c>
       <c r="W8" t="n">
-        <v>-28.773</v>
+        <v>-28.174</v>
       </c>
     </row>
     <row r="9">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | ENERY.IS: +0.26% / +2.04% / -0.28%</t>
+          <t>CANTE.IS: -0.02% / +3.76% / -3.01% | ENERY.IS: +0.26% / +2.04% / -0.46%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-17.44850906618763</v>
+        <v>-17.13098220836055</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1293,13 +1293,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>63.75</v>
+        <v>64.38</v>
       </c>
       <c r="V9" t="n">
-        <v>12.152</v>
+        <v>12.584</v>
       </c>
       <c r="W9" t="n">
-        <v>-50.159</v>
+        <v>-49.529</v>
       </c>
     </row>
     <row r="10">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | ENKAI.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TSKB.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: +1.77% / +2.03% / -2.37% | ENKAI.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TSKB.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-23.21046171619905</v>
+        <v>-3.108002940387544</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1357,10 +1357,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>176.1</v>
+        <v>176.5</v>
       </c>
       <c r="O10" t="n">
-        <v>48.5</v>
+        <v>48.9</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1374,19 +1374,19 @@
         <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>25.841</v>
+        <v>10.072</v>
       </c>
       <c r="T10" t="n">
-        <v>25.841</v>
+        <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>-7.014</v>
+        <v>17.329</v>
       </c>
       <c r="V10" t="n">
-        <v>-13.542</v>
+        <v>9.092000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>-32.402</v>
+        <v>-8.058999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.39% / +20.94% / 0.00% | CANTE.IS: +0.74% / +0.76% / -0.76% | RALYH.IS: +30.86% / +35.10% / -0.91%</t>
+          <t>BRSAN.IS: +15.98% / +20.94% / 0.00% | CANTE.IS: +1.51% / +1.53% / -0.76% | RALYH.IS: +31.58% / +35.10% / -0.91%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K12" t="n">
-        <v>12.77228390050964</v>
+        <v>13.77604027218235</v>
       </c>
       <c r="L12" t="n">
         <v>34.56349599547857</v>
@@ -1542,13 +1542,13 @@
         <v>23.777</v>
       </c>
       <c r="U12" t="n">
-        <v>49.154</v>
+        <v>50.481</v>
       </c>
       <c r="V12" t="n">
-        <v>42.914</v>
+        <v>44.186</v>
       </c>
       <c r="W12" t="n">
-        <v>-10.884</v>
+        <v>-9.557</v>
       </c>
     </row>
     <row r="13">
@@ -1575,29 +1575,17 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>TRALT.IS</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>TRALT.IS: 2026-09-02</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>25.65141339163128</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>TRALT.IS: +4.65% / +5.07% / -2.03%</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
         <v>-5.044425134583063</v>
       </c>
       <c r="K13" t="n">
-        <v>12.29115937599823</v>
+        <v>12.67174205104589</v>
       </c>
       <c r="L13" t="n">
         <v>9.344627019167174</v>
@@ -1616,11 +1604,11 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>12.101</v>
@@ -1629,13 +1617,13 @@
         <v>12.101</v>
       </c>
       <c r="U13" t="n">
-        <v>31.013</v>
+        <v>31.457</v>
       </c>
       <c r="V13" t="n">
-        <v>36.482</v>
+        <v>36.945</v>
       </c>
       <c r="W13" t="n">
-        <v>-6.766</v>
+        <v>-6.322</v>
       </c>
     </row>
     <row r="14">
@@ -1677,14 +1665,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.74% / +0.76% / -0.76% | ENERY.IS: +0.26% / +2.04% / -0.28%</t>
+          <t>CANTE.IS: +1.51% / +1.53% / -0.76% | ENERY.IS: +0.26% / +2.04% / -0.46%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>5.351463350312224</v>
+        <v>5.751565089875621</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1716,13 +1704,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>81.919</v>
+        <v>82.61</v>
       </c>
       <c r="V14" t="n">
-        <v>94.11799999999999</v>
+        <v>94.855</v>
       </c>
       <c r="W14" t="n">
-        <v>-29.331</v>
+        <v>-28.64</v>
       </c>
     </row>
     <row r="16">
@@ -1890,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | ENERY.IS: +0.26% / +2.04% / -0.28%</t>
+          <t>CANTE.IS: -0.02% / +3.76% / -3.01% | ENERY.IS: +0.26% / +2.04% / -0.46%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-17.44850906618763</v>
+        <v>-17.13098220836055</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1929,13 +1917,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>63.75</v>
+        <v>64.38</v>
       </c>
       <c r="V18" t="n">
-        <v>12.152</v>
+        <v>12.584</v>
       </c>
       <c r="W18" t="n">
-        <v>-50.159</v>
+        <v>-49.529</v>
       </c>
     </row>
     <row r="19">
@@ -2133,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.13% / +2.33% / -1.61% | ENERY.IS: -2.01% / +1.27% / -3.44% | ENJSA.IS: +0.24% / +1.14% / -2.01%</t>
+          <t>ALARK.IS: +2.93% / +2.95% / -1.61% | ENERY.IS: -2.01% / +1.27% / -3.44% | ENJSA.IS: +0.68% / +1.14% / -2.01%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-14.89520007800421</v>
+        <v>-14.5520555000352</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2172,13 +2160,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>48.515</v>
+        <v>49.114</v>
       </c>
       <c r="V21" t="n">
-        <v>12.993</v>
+        <v>13.449</v>
       </c>
       <c r="W21" t="n">
-        <v>-28.773</v>
+        <v>-28.174</v>
       </c>
     </row>
     <row r="22">
@@ -2209,12 +2197,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CANTE.IS, VAKBN.IS</t>
+          <t>BRSAN.IS, CANTE.IS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CANTE.IS: 2026-09-02 | VAKBN.IS: 2026-09-07</t>
+          <t>BRSAN.IS: 2026-09-08 | CANTE.IS: 2026-09-02</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2222,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.77% / +3.76% / -3.01% | VAKBN.IS: +2.50% / +3.24% / 0.00%</t>
+          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.02% / +3.76% / -3.01%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.16162134261018</v>
+        <v>-2.432112961359056</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2238,13 +2226,13 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>134.6</v>
+        <v>135.1</v>
       </c>
       <c r="O22" t="n">
-        <v>47.3</v>
+        <v>47.1</v>
       </c>
       <c r="P22" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2261,13 +2249,13 @@
         <v>19.727</v>
       </c>
       <c r="U22" t="n">
-        <v>77.396</v>
+        <v>84.446</v>
       </c>
       <c r="V22" t="n">
-        <v>28.404</v>
+        <v>33.508</v>
       </c>
       <c r="W22" t="n">
-        <v>-40.093</v>
+        <v>-33.042</v>
       </c>
     </row>
     <row r="23">
@@ -2311,14 +2299,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CANTE.IS: +0.74% / +0.76% / -0.76% | ENERY.IS: +0.26% / +2.04% / -0.28%</t>
+          <t>CANTE.IS: +1.51% / +1.53% / -0.76% | ENERY.IS: +0.26% / +2.04% / -0.46%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>5.351463350312224</v>
+        <v>5.751565089875621</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2350,13 +2338,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>81.919</v>
+        <v>82.61</v>
       </c>
       <c r="V23" t="n">
-        <v>94.11799999999999</v>
+        <v>94.855</v>
       </c>
       <c r="W23" t="n">
-        <v>-29.331</v>
+        <v>-28.64</v>
       </c>
     </row>
     <row r="24">
@@ -2462,29 +2450,17 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>TRALT.IS</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>TRALT.IS: 2026-09-02</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>25.65141339163128</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>TRALT.IS: +4.65% / +5.07% / -2.03%</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
         <v>-5.044425134583063</v>
       </c>
       <c r="K25" t="n">
-        <v>12.29115937599823</v>
+        <v>12.67174205104589</v>
       </c>
       <c r="L25" t="n">
         <v>9.344627019167174</v>
@@ -2503,11 +2479,11 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>12.101</v>
@@ -2516,13 +2492,13 @@
         <v>12.101</v>
       </c>
       <c r="U25" t="n">
-        <v>31.013</v>
+        <v>31.457</v>
       </c>
       <c r="V25" t="n">
-        <v>36.482</v>
+        <v>36.945</v>
       </c>
       <c r="W25" t="n">
-        <v>-6.766</v>
+        <v>-6.322</v>
       </c>
     </row>
     <row r="26">
@@ -2566,14 +2542,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +0.00% / 0.00% | ENKAI.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TSKB.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: +1.77% / +2.03% / -2.37% | ENKAI.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TSKB.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>-23.21046171619905</v>
+        <v>-3.108002940387544</v>
       </c>
       <c r="L26" t="n">
         <v>4.543450519200398</v>
@@ -2582,10 +2558,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>176.1</v>
+        <v>176.5</v>
       </c>
       <c r="O26" t="n">
-        <v>48.5</v>
+        <v>48.9</v>
       </c>
       <c r="P26" t="n">
         <v>1.9</v>
@@ -2599,19 +2575,19 @@
         <v>4</v>
       </c>
       <c r="S26" t="n">
-        <v>25.841</v>
+        <v>10.072</v>
       </c>
       <c r="T26" t="n">
-        <v>25.841</v>
+        <v>10.072</v>
       </c>
       <c r="U26" t="n">
-        <v>-7.014</v>
+        <v>17.329</v>
       </c>
       <c r="V26" t="n">
-        <v>-13.542</v>
+        <v>9.092000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>-32.402</v>
+        <v>-8.058999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -2655,14 +2631,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.39% / +20.94% / 0.00% | CANTE.IS: +0.74% / +0.76% / -0.76% | RALYH.IS: +30.86% / +35.10% / -0.91%</t>
+          <t>BRSAN.IS: +15.98% / +20.94% / 0.00% | CANTE.IS: +1.51% / +1.53% / -0.76% | RALYH.IS: +31.58% / +35.10% / -0.91%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>12.77228390050964</v>
+        <v>13.77604027218235</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2694,13 +2670,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>49.154</v>
+        <v>50.481</v>
       </c>
       <c r="V27" t="n">
-        <v>42.914</v>
+        <v>44.186</v>
       </c>
       <c r="W27" t="n">
-        <v>-10.884</v>
+        <v>-9.557</v>
       </c>
     </row>
   </sheetData>
@@ -2735,7 +2711,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2913,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.43% / +1.28% / -1.01% | ENERY.IS: -2.07% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +1.44% / +1.29% / -0.99% | ENERY.IS: -2.06% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2709940569649016</v>
+        <v>-0.257420415954579</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2952,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>284.645</v>
+        <v>284.698</v>
       </c>
       <c r="V3" t="n">
-        <v>100.901</v>
+        <v>100.928</v>
       </c>
       <c r="W3" t="n">
-        <v>-44.088</v>
+        <v>-44.036</v>
       </c>
     </row>
     <row r="4">
@@ -2995,7 +2971,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K4" t="n">
-        <v>-11.24912228187798</v>
+        <v>-11.24959773313421</v>
       </c>
       <c r="L4" t="n">
         <v>13.10602576687011</v>
@@ -3021,19 +2997,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>25.928</v>
+        <v>25.929</v>
       </c>
       <c r="T4" t="n">
-        <v>25.928</v>
+        <v>25.929</v>
       </c>
       <c r="U4" t="n">
-        <v>56.945</v>
+        <v>56.944</v>
       </c>
       <c r="V4" t="n">
         <v>19.407</v>
       </c>
       <c r="W4" t="n">
-        <v>-54.937</v>
+        <v>-54.938</v>
       </c>
     </row>
     <row r="5">
@@ -3075,14 +3051,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.43% / +1.28% / -1.01% | ENERY.IS: -2.07% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +1.44% / +1.29% / -0.99% | ENERY.IS: -2.06% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2909588561362586</v>
+        <v>-0.2773879324398765</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3114,13 +3090,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>281.691</v>
+        <v>281.743</v>
       </c>
       <c r="V5" t="n">
-        <v>82.953</v>
+        <v>82.97799999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-43.7</v>
+        <v>-43.649</v>
       </c>
     </row>
     <row r="6">
@@ -3162,14 +3138,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | CANTE.IS: +6.88% / +15.33% / -2.99% | ENERY.IS: +0.18% / +1.98% / -0.34% | SOKM.IS: -0.04% / +1.35% / -2.93% | TKFEN.IS: +12.88% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +14.12% / +20.01% / -1.13% | CANTE.IS: +6.90% / +15.33% / -2.99% | ENERY.IS: +0.20% / +1.99% / -0.51% | SOKM.IS: +0.83% / +1.36% / -2.94% | TKFEN.IS: +14.59% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.60114731880034</v>
+        <v>-8.906663108177215</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3181,7 +3157,7 @@
         <v>139.1</v>
       </c>
       <c r="O6" t="n">
-        <v>42.7</v>
+        <v>43.1</v>
       </c>
       <c r="P6" t="n">
         <v>5.7</v>
@@ -3201,13 +3177,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>23.005</v>
+        <v>23.95</v>
       </c>
       <c r="V6" t="n">
-        <v>12.39</v>
+        <v>13.253</v>
       </c>
       <c r="W6" t="n">
-        <v>-42.12</v>
+        <v>-41.175</v>
       </c>
     </row>
     <row r="7">
@@ -3244,7 +3220,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K7" t="n">
-        <v>-11.24912228187798</v>
+        <v>-11.24959773313421</v>
       </c>
       <c r="L7" t="n">
         <v>13.10602576687011</v>
@@ -3270,19 +3246,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>25.928</v>
+        <v>25.929</v>
       </c>
       <c r="T7" t="n">
-        <v>25.928</v>
+        <v>25.929</v>
       </c>
       <c r="U7" t="n">
-        <v>56.945</v>
+        <v>56.944</v>
       </c>
       <c r="V7" t="n">
         <v>19.407</v>
       </c>
       <c r="W7" t="n">
-        <v>-54.937</v>
+        <v>-54.938</v>
       </c>
     </row>
     <row r="8">
@@ -3324,14 +3300,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | CANTE.IS: -0.89% / +3.11% / -3.83% | ENERY.IS: +0.18% / +1.98% / -0.34%</t>
+          <t>BRSAN.IS: +14.12% / +20.01% / -1.13% | CANTE.IS: -0.88% / +3.11% / -3.83% | ENERY.IS: +0.20% / +1.99% / -0.51%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.401789892096018</v>
+        <v>-2.025382791314656</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3363,13 +3339,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>25.198</v>
+        <v>25.68</v>
       </c>
       <c r="V8" t="n">
-        <v>2.293</v>
+        <v>2.687</v>
       </c>
       <c r="W8" t="n">
-        <v>-31.645</v>
+        <v>-31.162</v>
       </c>
     </row>
     <row r="9">
@@ -3481,7 +3457,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.035426863396262</v>
+        <v>-3.035858361542709</v>
       </c>
       <c r="L10" t="n">
         <v>5.808640829284117</v>
@@ -3516,7 +3492,7 @@
         <v>11.77</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.455</v>
+        <v>-2.456</v>
       </c>
       <c r="W10" t="n">
         <v>-27.452</v>
@@ -3556,7 +3532,7 @@
         <v>22.72353327191259</v>
       </c>
       <c r="K11" t="n">
-        <v>-11.16624244310511</v>
+        <v>-11.1667183383606</v>
       </c>
       <c r="L11" t="n">
         <v>9.664716767669679</v>
@@ -3582,19 +3558,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>24.617</v>
+        <v>24.618</v>
       </c>
       <c r="T11" t="n">
-        <v>24.617</v>
+        <v>24.618</v>
       </c>
       <c r="U11" t="n">
-        <v>32.991</v>
+        <v>32.99</v>
       </c>
       <c r="V11" t="n">
-        <v>6.527</v>
+        <v>6.526</v>
       </c>
       <c r="W11" t="n">
-        <v>-43.43</v>
+        <v>-43.431</v>
       </c>
     </row>
     <row r="12">
@@ -3636,14 +3612,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | TKFEN.IS: +12.88% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +14.12% / +20.01% / -1.13% | TKFEN.IS: +14.59% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>10.64702958474606</v>
+        <v>12.22834030813578</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3675,13 +3651,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>43.875</v>
+        <v>45.931</v>
       </c>
       <c r="V12" t="n">
-        <v>54.176</v>
+        <v>56.379</v>
       </c>
       <c r="W12" t="n">
-        <v>-16.413</v>
+        <v>-14.357</v>
       </c>
     </row>
     <row r="13">
@@ -3770,7 +3746,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3783,55 +3759,67 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CVKMD.IS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CVKMD.IS: 2026-09-04</t>
+        </is>
+      </c>
       <c r="H14" t="n">
-        <v>32.90971238010212</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>-0.49388395046156</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CVKMD.IS: -1.79% / +3.03% / -3.48%</t>
+        </is>
+      </c>
       <c r="J14" t="n">
-        <v>3.175499702073514</v>
+        <v>-19.60937535624424</v>
       </c>
       <c r="K14" t="n">
-        <v>3.422248513714998</v>
+        <v>3.673840076745183</v>
       </c>
       <c r="L14" t="n">
-        <v>18.99889339779883</v>
+        <v>19.61961325199098</v>
       </c>
       <c r="M14" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N14" t="n">
-        <v>43.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>51.1</v>
+        <v>45.8</v>
       </c>
       <c r="P14" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>18.999</v>
+        <v>18.132</v>
       </c>
       <c r="T14" t="n">
-        <v>16.472</v>
+        <v>18.132</v>
       </c>
       <c r="U14" t="n">
-        <v>23.959</v>
+        <v>1.09</v>
       </c>
       <c r="V14" t="n">
-        <v>18.553</v>
+        <v>8.257</v>
       </c>
       <c r="W14" t="n">
-        <v>-13.85</v>
+        <v>-10.702</v>
       </c>
     </row>
     <row r="16">
@@ -3999,14 +3987,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.43% / +1.28% / -1.01% | ENERY.IS: -2.07% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +1.44% / +1.29% / -0.99% | ENERY.IS: -2.06% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2709940569649016</v>
+        <v>-0.257420415954579</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4038,13 +4026,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>284.645</v>
+        <v>284.698</v>
       </c>
       <c r="V18" t="n">
-        <v>100.901</v>
+        <v>100.928</v>
       </c>
       <c r="W18" t="n">
-        <v>-44.088</v>
+        <v>-44.036</v>
       </c>
     </row>
     <row r="19">
@@ -4083,7 +4071,7 @@
         <v>23.84260439688612</v>
       </c>
       <c r="K19" t="n">
-        <v>-11.24912228187798</v>
+        <v>-11.24959773313421</v>
       </c>
       <c r="L19" t="n">
         <v>13.10602576687011</v>
@@ -4109,19 +4097,19 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>25.928</v>
+        <v>25.929</v>
       </c>
       <c r="T19" t="n">
-        <v>25.928</v>
+        <v>25.929</v>
       </c>
       <c r="U19" t="n">
-        <v>56.945</v>
+        <v>56.944</v>
       </c>
       <c r="V19" t="n">
         <v>19.407</v>
       </c>
       <c r="W19" t="n">
-        <v>-54.937</v>
+        <v>-54.938</v>
       </c>
     </row>
     <row r="20">
@@ -4165,14 +4153,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.43% / +1.28% / -1.01% | ENERY.IS: -2.07% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +1.44% / +1.29% / -0.99% | ENERY.IS: -2.06% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2909588561362586</v>
+        <v>-0.2773879324398765</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4204,13 +4192,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>281.691</v>
+        <v>281.743</v>
       </c>
       <c r="V20" t="n">
-        <v>82.953</v>
+        <v>82.97799999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>-43.7</v>
+        <v>-43.649</v>
       </c>
     </row>
     <row r="21">
@@ -4249,7 +4237,7 @@
         <v>22.72353327191259</v>
       </c>
       <c r="K21" t="n">
-        <v>-11.16624244310511</v>
+        <v>-11.1667183383606</v>
       </c>
       <c r="L21" t="n">
         <v>9.664716767669679</v>
@@ -4275,19 +4263,19 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>24.617</v>
+        <v>24.618</v>
       </c>
       <c r="T21" t="n">
-        <v>24.617</v>
+        <v>24.618</v>
       </c>
       <c r="U21" t="n">
-        <v>32.991</v>
+        <v>32.99</v>
       </c>
       <c r="V21" t="n">
-        <v>6.527</v>
+        <v>6.526</v>
       </c>
       <c r="W21" t="n">
-        <v>-43.43</v>
+        <v>-43.431</v>
       </c>
     </row>
     <row r="22">
@@ -4331,14 +4319,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | CANTE.IS: +6.88% / +15.33% / -2.99% | ENERY.IS: +0.18% / +1.98% / -0.34% | SOKM.IS: -0.04% / +1.35% / -2.93% | TKFEN.IS: +12.88% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +14.12% / +20.01% / -1.13% | CANTE.IS: +6.90% / +15.33% / -2.99% | ENERY.IS: +0.20% / +1.99% / -0.51% | SOKM.IS: +0.83% / +1.36% / -2.94% | TKFEN.IS: +14.59% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-9.60114731880034</v>
+        <v>-8.906663108177215</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4350,7 +4338,7 @@
         <v>139.1</v>
       </c>
       <c r="O22" t="n">
-        <v>42.7</v>
+        <v>43.1</v>
       </c>
       <c r="P22" t="n">
         <v>5.7</v>
@@ -4370,13 +4358,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>23.005</v>
+        <v>23.95</v>
       </c>
       <c r="V22" t="n">
-        <v>12.39</v>
+        <v>13.253</v>
       </c>
       <c r="W22" t="n">
-        <v>-42.12</v>
+        <v>-41.175</v>
       </c>
     </row>
     <row r="23">
@@ -4420,14 +4408,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | CANTE.IS: -0.89% / +3.11% / -3.83% | ENERY.IS: +0.18% / +1.98% / -0.34%</t>
+          <t>BRSAN.IS: +14.12% / +20.01% / -1.13% | CANTE.IS: -0.88% / +3.11% / -3.83% | ENERY.IS: +0.20% / +1.99% / -0.51%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.401789892096018</v>
+        <v>-2.025382791314656</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4459,13 +4447,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>25.198</v>
+        <v>25.68</v>
       </c>
       <c r="V23" t="n">
-        <v>2.293</v>
+        <v>2.687</v>
       </c>
       <c r="W23" t="n">
-        <v>-31.645</v>
+        <v>-31.162</v>
       </c>
     </row>
     <row r="24">
@@ -4504,7 +4492,7 @@
         <v>13.75066280702224</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.035426863396262</v>
+        <v>-3.035858361542709</v>
       </c>
       <c r="L24" t="n">
         <v>5.808640829284117</v>
@@ -4539,7 +4527,7 @@
         <v>11.77</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.455</v>
+        <v>-2.456</v>
       </c>
       <c r="W24" t="n">
         <v>-27.452</v>
@@ -4548,17 +4536,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|coklu_zarf</t>
+          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4574,29 +4562,29 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>32.90971238010212</v>
+        <v>28.40086810394897</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>3.175499702073514</v>
+        <v>15.38514121842653</v>
       </c>
       <c r="K25" t="n">
-        <v>3.422248513714998</v>
+        <v>-6.616392554049999</v>
       </c>
       <c r="L25" t="n">
-        <v>18.99889339779883</v>
+        <v>5.127814043936619</v>
       </c>
       <c r="M25" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>43.6</v>
+        <v>75.3</v>
       </c>
       <c r="O25" t="n">
-        <v>51.1</v>
+        <v>49.3</v>
       </c>
       <c r="P25" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4607,35 +4595,35 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>18.999</v>
+        <v>13.28</v>
       </c>
       <c r="T25" t="n">
-        <v>16.472</v>
+        <v>13.28</v>
       </c>
       <c r="U25" t="n">
-        <v>23.959</v>
+        <v>8.964</v>
       </c>
       <c r="V25" t="n">
-        <v>18.553</v>
+        <v>-0.962</v>
       </c>
       <c r="W25" t="n">
-        <v>-13.85</v>
+        <v>-16.687</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S3|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|keltner_kirilim</t>
+          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4651,29 +4639,29 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>28.40086810394897</v>
+        <v>8.530010255723974</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>15.38514121842653</v>
+        <v>0.8142516931666233</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.616392554049999</v>
+        <v>3.846414277792909</v>
       </c>
       <c r="L26" t="n">
-        <v>5.127814043936619</v>
+        <v>9.181211458048665</v>
       </c>
       <c r="M26" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>75.3</v>
+        <v>35.6</v>
       </c>
       <c r="O26" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="P26" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4684,19 +4672,19 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>13.28</v>
+        <v>8.083</v>
       </c>
       <c r="T26" t="n">
-        <v>13.28</v>
+        <v>7.916</v>
       </c>
       <c r="U26" t="n">
-        <v>8.964</v>
+        <v>13.72</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.962</v>
+        <v>4.916</v>
       </c>
       <c r="W26" t="n">
-        <v>-16.687</v>
+        <v>-5.191</v>
       </c>
     </row>
     <row r="27">
@@ -4707,12 +4695,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4725,55 +4713,67 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>BRSAN.IS, TKFEN.IS</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
+        </is>
+      </c>
       <c r="H27" t="n">
-        <v>8.530010255723974</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>6.880672511445463</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BRSAN.IS: +14.12% / +20.01% / -1.13% | TKFEN.IS: +14.59% / +31.83% / -0.56%</t>
+        </is>
+      </c>
       <c r="J27" t="n">
-        <v>0.8142516931666233</v>
+        <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>3.846414277792909</v>
+        <v>12.22834030813578</v>
       </c>
       <c r="L27" t="n">
-        <v>9.181211458048665</v>
+        <v>31.31195090134997</v>
       </c>
       <c r="M27" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N27" t="n">
-        <v>35.6</v>
+        <v>48</v>
       </c>
       <c r="O27" t="n">
-        <v>50</v>
+        <v>43.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
-        <v>8.083</v>
+        <v>28.439</v>
       </c>
       <c r="T27" t="n">
-        <v>7.916</v>
+        <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>13.72</v>
+        <v>45.931</v>
       </c>
       <c r="V27" t="n">
-        <v>4.916</v>
+        <v>56.379</v>
       </c>
       <c r="W27" t="n">
-        <v>-5.191</v>
+        <v>-14.357</v>
       </c>
     </row>
     <row r="28">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|keltner_kirilim</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4804,42 +4804,42 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BRSAN.IS, TKFEN.IS</t>
+          <t>CVKMD.IS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>BRSAN.IS: 2026-08-12 | TKFEN.IS: 2026-08-05</t>
+          <t>CVKMD.IS: 2026-09-04</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>6.880672511445463</v>
+        <v>-0.49388395046156</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.61% / +20.01% / -1.13% | TKFEN.IS: +12.88% / +31.83% / -0.56%</t>
+          <t>CVKMD.IS: -1.79% / +3.03% / -3.48%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>-18.9000927288166</v>
+        <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>10.64702958474606</v>
+        <v>3.673840076745183</v>
       </c>
       <c r="L28" t="n">
-        <v>31.31195090134997</v>
+        <v>19.61961325199098</v>
       </c>
       <c r="M28" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N28" t="n">
-        <v>48</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>43.3</v>
+        <v>45.8</v>
       </c>
       <c r="P28" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4847,22 +4847,22 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>28.439</v>
+        <v>18.132</v>
       </c>
       <c r="T28" t="n">
-        <v>28.439</v>
+        <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>43.875</v>
+        <v>1.09</v>
       </c>
       <c r="V28" t="n">
-        <v>54.176</v>
+        <v>8.257</v>
       </c>
       <c r="W28" t="n">
-        <v>-16.413</v>
+        <v>-10.702</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -573,7 +573,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +3.76% / -3.01% | ENERY.IS: +0.26% / +2.04% / -0.46%</t>
+          <t>CANTE.IS: +1.48% / +3.76% / -3.01% | ENERY.IS: +1.18% / +2.04% / -0.46%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-17.13098220836055</v>
+        <v>-16.12027198934688</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -772,13 +772,13 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>102.6</v>
+        <v>102.4</v>
       </c>
       <c r="O3" t="n">
-        <v>43.3</v>
+        <v>43.8</v>
       </c>
       <c r="P3" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -795,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>64.38</v>
+        <v>64.244</v>
       </c>
       <c r="V3" t="n">
-        <v>12.584</v>
+        <v>13.957</v>
       </c>
       <c r="W3" t="n">
-        <v>-49.529</v>
+        <v>-46.912</v>
       </c>
     </row>
     <row r="4">
@@ -820,12 +820,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -847,7 +847,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>63.6</v>
+        <v>63.5</v>
       </c>
       <c r="O4" t="n">
         <v>48.8</v>
@@ -870,13 +870,13 @@
         <v>21.057</v>
       </c>
       <c r="U4" t="n">
-        <v>151.738</v>
+        <v>152.823</v>
       </c>
       <c r="V4" t="n">
         <v>111.543</v>
       </c>
       <c r="W4" t="n">
-        <v>-12.747</v>
+        <v>-12.802</v>
       </c>
     </row>
     <row r="5">
@@ -895,12 +895,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N5" t="n">
-        <v>64.59999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="O5" t="n">
         <v>46.6</v>
@@ -945,13 +945,13 @@
         <v>19.637</v>
       </c>
       <c r="U5" t="n">
-        <v>120.159</v>
+        <v>117.451</v>
       </c>
       <c r="V5" t="n">
         <v>117.535</v>
       </c>
       <c r="W5" t="n">
-        <v>-16.389</v>
+        <v>-16.188</v>
       </c>
     </row>
     <row r="6">
@@ -970,12 +970,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +3.76% / -3.01% | ENERY.IS: +0.26% / +2.04% / -0.46%</t>
+          <t>CANTE.IS: +1.48% / +3.76% / -3.01% | ENERY.IS: +1.18% / +2.04% / -0.46%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-17.13098220836055</v>
+        <v>-16.12027198934688</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1009,13 +1009,13 @@
         <v>100</v>
       </c>
       <c r="N6" t="n">
-        <v>102.6</v>
+        <v>102.4</v>
       </c>
       <c r="O6" t="n">
-        <v>43.3</v>
+        <v>43.8</v>
       </c>
       <c r="P6" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1032,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>64.38</v>
+        <v>64.244</v>
       </c>
       <c r="V6" t="n">
-        <v>12.584</v>
+        <v>13.957</v>
       </c>
       <c r="W6" t="n">
-        <v>-49.529</v>
+        <v>-46.912</v>
       </c>
     </row>
     <row r="7">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.02% / +3.76% / -3.01%</t>
+          <t>BRSAN.IS: -1.60% / +0.00% / -1.65% | CANTE.IS: +1.48% / +3.76% / -3.01%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.432112961359056</v>
+        <v>-2.488268056801768</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1096,13 +1096,13 @@
         <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>135.1</v>
+        <v>134.9</v>
       </c>
       <c r="O7" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1119,13 +1119,13 @@
         <v>19.727</v>
       </c>
       <c r="U7" t="n">
-        <v>84.446</v>
+        <v>79.91200000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>33.508</v>
+        <v>33.431</v>
       </c>
       <c r="W7" t="n">
-        <v>-33.042</v>
+        <v>-32.352</v>
       </c>
     </row>
     <row r="8">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.93% / +2.95% / -1.61% | ENERY.IS: -2.01% / +1.27% / -3.44% | ENJSA.IS: +0.68% / +1.14% / -2.01%</t>
+          <t>ALARK.IS: +2.75% / +2.95% / -1.61% | ENERY.IS: -1.11% / +1.27% / -3.44% | ENJSA.IS: +1.90% / +2.62% / -2.01%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-14.5520555000352</v>
+        <v>-14.01315872661779</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1183,7 +1183,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>191.8</v>
+        <v>191.5</v>
       </c>
       <c r="O8" t="n">
         <v>47</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>49.114</v>
+        <v>50.701</v>
       </c>
       <c r="V8" t="n">
-        <v>13.449</v>
+        <v>14.164</v>
       </c>
       <c r="W8" t="n">
-        <v>-28.174</v>
+        <v>-27.351</v>
       </c>
     </row>
     <row r="9">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +3.76% / -3.01% | ENERY.IS: +0.26% / +2.04% / -0.46%</t>
+          <t>CANTE.IS: +1.48% / +3.76% / -3.01% | ENERY.IS: +1.18% / +2.04% / -0.46%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-17.13098220836055</v>
+        <v>-16.12027198934688</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1270,13 +1270,13 @@
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>102.6</v>
+        <v>102.4</v>
       </c>
       <c r="O9" t="n">
-        <v>43.3</v>
+        <v>43.8</v>
       </c>
       <c r="P9" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1293,13 +1293,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>64.38</v>
+        <v>64.244</v>
       </c>
       <c r="V9" t="n">
-        <v>12.584</v>
+        <v>13.957</v>
       </c>
       <c r="W9" t="n">
-        <v>-49.529</v>
+        <v>-46.912</v>
       </c>
     </row>
     <row r="10">
@@ -1318,22 +1318,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AGHOL.IS, ENKAI.IS, SASA.IS, TSKB.IS</t>
+          <t>AGHOL.IS, ENKAI.IS, KRDMD.IS, SASA.IS, TSKB.IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-09-07 | ENKAI.IS: 2026-09-08 | SASA.IS: 2026-09-08 | TSKB.IS: 2026-09-08</t>
+          <t>AGHOL.IS: 2026-09-07 | ENKAI.IS: 2026-09-08 | KRDMD.IS: 2026-09-09 | SASA.IS: 2026-09-08 | TSKB.IS: 2026-09-08</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +1.77% / +2.03% / -2.37% | ENKAI.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TSKB.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: -0.02% / +2.03% / -2.37% | ENKAI.IS: -0.41% / +1.34% / -0.84% | KRDMD.IS: -0.02% / +0.00% / 0.00% | SASA.IS: +1.07% / +1.81% / -1.81% | TSKB.IS: -1.05% / +0.86% / -3.01%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.108002940387544</v>
+        <v>-22.72403658622732</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1357,7 +1357,7 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>176.5</v>
+        <v>176.2</v>
       </c>
       <c r="O10" t="n">
         <v>48.9</v>
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S10" t="n">
-        <v>10.072</v>
+        <v>25.371</v>
       </c>
       <c r="T10" t="n">
-        <v>10.072</v>
+        <v>25.371</v>
       </c>
       <c r="U10" t="n">
-        <v>17.329</v>
+        <v>-6.425</v>
       </c>
       <c r="V10" t="n">
-        <v>9.092000000000001</v>
+        <v>-12.994</v>
       </c>
       <c r="W10" t="n">
-        <v>-8.058999999999999</v>
+        <v>-31.813</v>
       </c>
     </row>
     <row r="11">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>66.59999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>51.9</v>
@@ -1455,13 +1455,13 @@
         <v>7.033</v>
       </c>
       <c r="U11" t="n">
-        <v>85.218</v>
+        <v>85.90600000000001</v>
       </c>
       <c r="V11" t="n">
         <v>58.898</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.618</v>
+        <v>-1.624</v>
       </c>
     </row>
     <row r="12">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +15.98% / +20.94% / 0.00% | CANTE.IS: +1.51% / +1.53% / -0.76% | RALYH.IS: +31.58% / +35.10% / -0.91%</t>
+          <t>BRSAN.IS: +14.15% / +20.94% / 0.00% | CANTE.IS: +3.03% / +3.05% / -0.76% | RALYH.IS: +32.31% / +35.10% / -0.91%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K12" t="n">
-        <v>13.77604027218235</v>
+        <v>13.94878027323467</v>
       </c>
       <c r="L12" t="n">
         <v>34.56349599547857</v>
@@ -1519,7 +1519,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>70</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>44.4</v>
@@ -1542,13 +1542,13 @@
         <v>23.777</v>
       </c>
       <c r="U12" t="n">
-        <v>50.481</v>
+        <v>50.71</v>
       </c>
       <c r="V12" t="n">
-        <v>44.186</v>
+        <v>44.405</v>
       </c>
       <c r="W12" t="n">
-        <v>-9.557</v>
+        <v>-9.327999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1562,68 +1562,80 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ASTOR.IS, CVKMD.IS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ASTOR.IS: 2026-09-03 | CVKMD.IS: 2026-09-09</t>
+        </is>
+      </c>
       <c r="H13" t="n">
-        <v>25.65141339163128</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>20.48700524499634</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASTOR.IS: +3.73% / +4.51% / -1.28% | CVKMD.IS: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J13" t="n">
-        <v>-5.044425134583063</v>
+        <v>-3.767340978838807</v>
       </c>
       <c r="K13" t="n">
-        <v>12.67174205104589</v>
+        <v>13.93158196968245</v>
       </c>
       <c r="L13" t="n">
-        <v>9.344627019167174</v>
+        <v>16.57596537747867</v>
       </c>
       <c r="M13" t="n">
-        <v>66.66666666666666</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>58.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>51.3</v>
+        <v>47.8</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>12.101</v>
+        <v>17.404</v>
       </c>
       <c r="T13" t="n">
-        <v>12.101</v>
+        <v>17.404</v>
       </c>
       <c r="U13" t="n">
-        <v>31.457</v>
+        <v>54.099</v>
       </c>
       <c r="V13" t="n">
-        <v>36.945</v>
+        <v>46.464</v>
       </c>
       <c r="W13" t="n">
-        <v>-6.322</v>
+        <v>-0.603</v>
       </c>
     </row>
     <row r="14">
@@ -1642,12 +1654,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1665,14 +1677,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.51% / +1.53% / -0.76% | ENERY.IS: +0.26% / +2.04% / -0.46%</t>
+          <t>CANTE.IS: +3.03% / +3.05% / -0.76% | ENERY.IS: +1.18% / +2.04% / -0.46%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>5.751565089875621</v>
+        <v>7.037429364945602</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1681,7 +1693,7 @@
         <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>59.7</v>
+        <v>59.6</v>
       </c>
       <c r="O14" t="n">
         <v>45.5</v>
@@ -1704,13 +1716,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>82.61</v>
+        <v>84.83</v>
       </c>
       <c r="V14" t="n">
-        <v>94.855</v>
+        <v>97.22499999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>-28.64</v>
+        <v>-26.42</v>
       </c>
     </row>
     <row r="16">
@@ -1855,12 +1867,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1878,14 +1890,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: -0.02% / +3.76% / -3.01% | ENERY.IS: +0.26% / +2.04% / -0.46%</t>
+          <t>CANTE.IS: +1.48% / +3.76% / -3.01% | ENERY.IS: +1.18% / +2.04% / -0.46%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-17.13098220836055</v>
+        <v>-16.12027198934688</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1894,13 +1906,13 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>102.6</v>
+        <v>102.4</v>
       </c>
       <c r="O18" t="n">
-        <v>43.3</v>
+        <v>43.8</v>
       </c>
       <c r="P18" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1917,13 +1929,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>64.38</v>
+        <v>64.244</v>
       </c>
       <c r="V18" t="n">
-        <v>12.584</v>
+        <v>13.957</v>
       </c>
       <c r="W18" t="n">
-        <v>-49.529</v>
+        <v>-46.912</v>
       </c>
     </row>
     <row r="19">
@@ -1944,12 +1956,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1971,7 +1983,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>63.6</v>
+        <v>63.5</v>
       </c>
       <c r="O19" t="n">
         <v>48.8</v>
@@ -1994,13 +2006,13 @@
         <v>21.057</v>
       </c>
       <c r="U19" t="n">
-        <v>151.738</v>
+        <v>152.823</v>
       </c>
       <c r="V19" t="n">
         <v>111.543</v>
       </c>
       <c r="W19" t="n">
-        <v>-12.747</v>
+        <v>-12.802</v>
       </c>
     </row>
     <row r="20">
@@ -2021,12 +2033,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2048,7 +2060,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N20" t="n">
-        <v>64.59999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="O20" t="n">
         <v>46.6</v>
@@ -2071,13 +2083,13 @@
         <v>19.637</v>
       </c>
       <c r="U20" t="n">
-        <v>120.159</v>
+        <v>117.451</v>
       </c>
       <c r="V20" t="n">
         <v>117.535</v>
       </c>
       <c r="W20" t="n">
-        <v>-16.389</v>
+        <v>-16.188</v>
       </c>
     </row>
     <row r="21">
@@ -2098,12 +2110,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2121,14 +2133,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.93% / +2.95% / -1.61% | ENERY.IS: -2.01% / +1.27% / -3.44% | ENJSA.IS: +0.68% / +1.14% / -2.01%</t>
+          <t>ALARK.IS: +2.75% / +2.95% / -1.61% | ENERY.IS: -1.11% / +1.27% / -3.44% | ENJSA.IS: +1.90% / +2.62% / -2.01%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-14.5520555000352</v>
+        <v>-14.01315872661779</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2137,7 +2149,7 @@
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>191.8</v>
+        <v>191.5</v>
       </c>
       <c r="O21" t="n">
         <v>47</v>
@@ -2160,13 +2172,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>49.114</v>
+        <v>50.701</v>
       </c>
       <c r="V21" t="n">
-        <v>13.449</v>
+        <v>14.164</v>
       </c>
       <c r="W21" t="n">
-        <v>-28.174</v>
+        <v>-27.351</v>
       </c>
     </row>
     <row r="22">
@@ -2187,12 +2199,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2210,14 +2222,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -0.02% / +0.00% / 0.00% | CANTE.IS: -0.02% / +3.76% / -3.01%</t>
+          <t>BRSAN.IS: -1.60% / +0.00% / -1.65% | CANTE.IS: +1.48% / +3.76% / -3.01%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.432112961359056</v>
+        <v>-2.488268056801768</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2226,13 +2238,13 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>135.1</v>
+        <v>134.9</v>
       </c>
       <c r="O22" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2249,13 +2261,13 @@
         <v>19.727</v>
       </c>
       <c r="U22" t="n">
-        <v>84.446</v>
+        <v>79.91200000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>33.508</v>
+        <v>33.431</v>
       </c>
       <c r="W22" t="n">
-        <v>-33.042</v>
+        <v>-32.352</v>
       </c>
     </row>
     <row r="23">
@@ -2276,12 +2288,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2299,14 +2311,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.51% / +1.53% / -0.76% | ENERY.IS: +0.26% / +2.04% / -0.46%</t>
+          <t>CANTE.IS: +3.03% / +3.05% / -0.76% | ENERY.IS: +1.18% / +2.04% / -0.46%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>5.751565089875621</v>
+        <v>7.037429364945602</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2315,7 +2327,7 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>59.7</v>
+        <v>59.6</v>
       </c>
       <c r="O23" t="n">
         <v>45.5</v>
@@ -2338,13 +2350,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>82.61</v>
+        <v>84.83</v>
       </c>
       <c r="V23" t="n">
-        <v>94.855</v>
+        <v>97.22499999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>-28.64</v>
+        <v>-26.42</v>
       </c>
     </row>
     <row r="24">
@@ -2365,12 +2377,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2392,7 +2404,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>66.59999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O24" t="n">
         <v>51.9</v>
@@ -2415,19 +2427,19 @@
         <v>7.033</v>
       </c>
       <c r="U24" t="n">
-        <v>85.218</v>
+        <v>85.90600000000001</v>
       </c>
       <c r="V24" t="n">
         <v>58.898</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.618</v>
+        <v>-1.624</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2437,74 +2449,86 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gskor|Ppuan|geri_cekilme</t>
+          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>AGHOL.IS, ENKAI.IS, KRDMD.IS, SASA.IS, TSKB.IS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: 2026-09-07 | ENKAI.IS: 2026-09-08 | KRDMD.IS: 2026-09-09 | SASA.IS: 2026-09-08 | TSKB.IS: 2026-09-08</t>
+        </is>
+      </c>
       <c r="H25" t="n">
-        <v>25.65141339163128</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>23.02092795860866</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>AGHOL.IS: -0.02% / +2.03% / -2.37% | ENKAI.IS: -0.41% / +1.34% / -0.84% | KRDMD.IS: -0.02% / +0.00% / 0.00% | SASA.IS: +1.07% / +1.81% / -1.81% | TSKB.IS: -1.05% / +0.86% / -3.01%</t>
+        </is>
+      </c>
       <c r="J25" t="n">
-        <v>-5.044425134583063</v>
+        <v>12.86015270141232</v>
       </c>
       <c r="K25" t="n">
-        <v>12.67174205104589</v>
+        <v>-22.72403658622732</v>
       </c>
       <c r="L25" t="n">
-        <v>9.344627019167174</v>
+        <v>4.543450519200398</v>
       </c>
       <c r="M25" t="n">
-        <v>66.66666666666666</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N25" t="n">
-        <v>58.7</v>
+        <v>176.2</v>
       </c>
       <c r="O25" t="n">
-        <v>51.3</v>
+        <v>48.9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S25" t="n">
-        <v>12.101</v>
+        <v>25.371</v>
       </c>
       <c r="T25" t="n">
-        <v>12.101</v>
+        <v>25.371</v>
       </c>
       <c r="U25" t="n">
-        <v>31.457</v>
+        <v>-6.425</v>
       </c>
       <c r="V25" t="n">
-        <v>36.945</v>
+        <v>-12.994</v>
       </c>
       <c r="W25" t="n">
-        <v>-6.322</v>
+        <v>-31.813</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2514,57 +2538,57 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AGHOL.IS, ENKAI.IS, SASA.IS, TSKB.IS</t>
+          <t>ASTOR.IS, CVKMD.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AGHOL.IS: 2026-09-07 | ENKAI.IS: 2026-09-08 | SASA.IS: 2026-09-08 | TSKB.IS: 2026-09-08</t>
+          <t>ASTOR.IS: 2026-09-03 | CVKMD.IS: 2026-09-09</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>23.02092795860866</v>
+        <v>20.48700524499634</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AGHOL.IS: +1.77% / +2.03% / -2.37% | ENKAI.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -0.02% / +0.00% / 0.00% | TSKB.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>ASTOR.IS: +3.73% / +4.51% / -1.28% | CVKMD.IS: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>12.86015270141232</v>
+        <v>-3.767340978838807</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.108002940387544</v>
+        <v>13.93158196968245</v>
       </c>
       <c r="L26" t="n">
-        <v>4.543450519200398</v>
+        <v>16.57596537747867</v>
       </c>
       <c r="M26" t="n">
-        <v>72.22222222222221</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N26" t="n">
-        <v>176.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>48.9</v>
+        <v>47.8</v>
       </c>
       <c r="P26" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2572,22 +2596,22 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>10.072</v>
+        <v>17.404</v>
       </c>
       <c r="T26" t="n">
-        <v>10.072</v>
+        <v>17.404</v>
       </c>
       <c r="U26" t="n">
-        <v>17.329</v>
+        <v>54.099</v>
       </c>
       <c r="V26" t="n">
-        <v>9.092000000000001</v>
+        <v>46.464</v>
       </c>
       <c r="W26" t="n">
-        <v>-8.058999999999999</v>
+        <v>-0.603</v>
       </c>
     </row>
     <row r="27">
@@ -2608,12 +2632,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2631,14 +2655,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +15.98% / +20.94% / 0.00% | CANTE.IS: +1.51% / +1.53% / -0.76% | RALYH.IS: +31.58% / +35.10% / -0.91%</t>
+          <t>BRSAN.IS: +14.15% / +20.94% / 0.00% | CANTE.IS: +3.03% / +3.05% / -0.76% | RALYH.IS: +32.31% / +35.10% / -0.91%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>13.77604027218235</v>
+        <v>13.94878027323467</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2647,7 +2671,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N27" t="n">
-        <v>70</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="O27" t="n">
         <v>44.4</v>
@@ -2670,13 +2694,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>50.481</v>
+        <v>50.71</v>
       </c>
       <c r="V27" t="n">
-        <v>44.186</v>
+        <v>44.405</v>
       </c>
       <c r="W27" t="n">
-        <v>-9.557</v>
+        <v>-9.327999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2866,12 +2890,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2889,14 +2913,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.44% / +1.29% / -0.99% | ENERY.IS: -2.06% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +2.92% / +2.76% / -0.99% | ENERY.IS: -1.29% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.257420415954579</v>
+        <v>0.8541789633736974</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2905,7 +2929,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>93.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>44.7</v>
@@ -2928,13 +2952,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>284.698</v>
+        <v>290.845</v>
       </c>
       <c r="V3" t="n">
-        <v>100.928</v>
+        <v>103.168</v>
       </c>
       <c r="W3" t="n">
-        <v>-44.036</v>
+        <v>-39.938</v>
       </c>
     </row>
     <row r="4">
@@ -2953,12 +2977,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2980,7 +3004,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N4" t="n">
-        <v>119.3</v>
+        <v>119.1</v>
       </c>
       <c r="O4" t="n">
         <v>46.9</v>
@@ -3003,13 +3027,13 @@
         <v>25.929</v>
       </c>
       <c r="U4" t="n">
-        <v>56.944</v>
+        <v>58.058</v>
       </c>
       <c r="V4" t="n">
         <v>19.407</v>
       </c>
       <c r="W4" t="n">
-        <v>-54.938</v>
+        <v>-55.328</v>
       </c>
     </row>
     <row r="5">
@@ -3028,12 +3052,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3051,14 +3075,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.44% / +1.29% / -0.99% | ENERY.IS: -2.06% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +2.92% / +2.76% / -0.99% | ENERY.IS: -1.29% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2773879324398765</v>
+        <v>0.8339889152572333</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3067,7 +3091,7 @@
         <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>82.2</v>
+        <v>82</v>
       </c>
       <c r="O5" t="n">
         <v>42.8</v>
@@ -3090,13 +3114,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>281.743</v>
+        <v>287.842</v>
       </c>
       <c r="V5" t="n">
-        <v>82.97799999999999</v>
+        <v>85.018</v>
       </c>
       <c r="W5" t="n">
-        <v>-43.649</v>
+        <v>-39.582</v>
       </c>
     </row>
     <row r="6">
@@ -3115,12 +3139,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3138,14 +3162,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.12% / +20.01% / -1.13% | CANTE.IS: +6.90% / +15.33% / -2.99% | ENERY.IS: +0.20% / +1.99% / -0.51% | SOKM.IS: +0.83% / +1.36% / -2.94% | TKFEN.IS: +14.59% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.10% / +20.01% / -1.13% | CANTE.IS: +8.45% / +15.33% / -2.99% | ENERY.IS: +0.98% / +1.99% / -0.51% | SOKM.IS: +1.72% / +1.91% / -2.94% | TKFEN.IS: +15.33% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.906663108177215</v>
+        <v>-8.630762857397711</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3154,7 +3178,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N6" t="n">
-        <v>139.1</v>
+        <v>138.8</v>
       </c>
       <c r="O6" t="n">
         <v>43.1</v>
@@ -3177,13 +3201,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>23.95</v>
+        <v>24.325</v>
       </c>
       <c r="V6" t="n">
-        <v>13.253</v>
+        <v>13.596</v>
       </c>
       <c r="W6" t="n">
-        <v>-41.175</v>
+        <v>-40.799</v>
       </c>
     </row>
     <row r="7">
@@ -3202,12 +3226,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3229,7 +3253,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N7" t="n">
-        <v>119.3</v>
+        <v>119.1</v>
       </c>
       <c r="O7" t="n">
         <v>46.9</v>
@@ -3252,13 +3276,13 @@
         <v>25.929</v>
       </c>
       <c r="U7" t="n">
-        <v>56.944</v>
+        <v>58.058</v>
       </c>
       <c r="V7" t="n">
         <v>19.407</v>
       </c>
       <c r="W7" t="n">
-        <v>-54.938</v>
+        <v>-55.328</v>
       </c>
     </row>
     <row r="8">
@@ -3277,12 +3301,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3300,14 +3324,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.12% / +20.01% / -1.13% | CANTE.IS: -0.88% / +3.11% / -3.83% | ENERY.IS: +0.20% / +1.99% / -0.51%</t>
+          <t>BRSAN.IS: +12.10% / +20.01% / -1.13% | CANTE.IS: +0.56% / +3.11% / -3.83% | ENERY.IS: +0.98% / +1.99% / -0.51%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.025382791314656</v>
+        <v>-1.948325988485078</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3316,10 +3340,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>153.5</v>
+        <v>153.2</v>
       </c>
       <c r="O8" t="n">
-        <v>42.3</v>
+        <v>42.6</v>
       </c>
       <c r="P8" t="n">
         <v>4.2</v>
@@ -3339,13 +3363,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>25.68</v>
+        <v>24.549</v>
       </c>
       <c r="V8" t="n">
-        <v>2.687</v>
+        <v>2.768</v>
       </c>
       <c r="W8" t="n">
-        <v>-31.162</v>
+        <v>-30.759</v>
       </c>
     </row>
     <row r="9">
@@ -3364,12 +3388,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3391,7 +3415,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N9" t="n">
-        <v>75.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="O9" t="n">
         <v>49.3</v>
@@ -3414,13 +3438,13 @@
         <v>13.28</v>
       </c>
       <c r="U9" t="n">
-        <v>8.964</v>
+        <v>7.136</v>
       </c>
       <c r="V9" t="n">
         <v>-0.962</v>
       </c>
       <c r="W9" t="n">
-        <v>-16.687</v>
+        <v>-16.407</v>
       </c>
     </row>
     <row r="10">
@@ -3439,12 +3463,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3466,7 +3490,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N10" t="n">
-        <v>113.9</v>
+        <v>113.6</v>
       </c>
       <c r="O10" t="n">
         <v>50.4</v>
@@ -3489,13 +3513,13 @@
         <v>20.181</v>
       </c>
       <c r="U10" t="n">
-        <v>11.77</v>
+        <v>10.676</v>
       </c>
       <c r="V10" t="n">
         <v>-2.456</v>
       </c>
       <c r="W10" t="n">
-        <v>-27.452</v>
+        <v>-27.184</v>
       </c>
     </row>
     <row r="11">
@@ -3514,12 +3538,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3541,7 +3565,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N11" t="n">
-        <v>179.7</v>
+        <v>179.4</v>
       </c>
       <c r="O11" t="n">
         <v>52.1</v>
@@ -3564,13 +3588,13 @@
         <v>24.618</v>
       </c>
       <c r="U11" t="n">
-        <v>32.99</v>
+        <v>33.934</v>
       </c>
       <c r="V11" t="n">
         <v>6.526</v>
       </c>
       <c r="W11" t="n">
-        <v>-43.431</v>
+        <v>-43.739</v>
       </c>
     </row>
     <row r="12">
@@ -3589,12 +3613,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3612,14 +3636,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.12% / +20.01% / -1.13% | TKFEN.IS: +14.59% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.10% / +20.01% / -1.13% | TKFEN.IS: +15.33% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>12.22834030813578</v>
+        <v>11.64809993992229</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3628,7 +3652,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N12" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="O12" t="n">
         <v>43.3</v>
@@ -3651,13 +3675,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>45.931</v>
+        <v>45.177</v>
       </c>
       <c r="V12" t="n">
-        <v>56.379</v>
+        <v>55.571</v>
       </c>
       <c r="W12" t="n">
-        <v>-14.357</v>
+        <v>-15.111</v>
       </c>
     </row>
     <row r="13">
@@ -3676,12 +3700,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -3726,13 +3750,13 @@
         <v>7.916</v>
       </c>
       <c r="U13" t="n">
-        <v>13.72</v>
+        <v>14.275</v>
       </c>
       <c r="V13" t="n">
         <v>4.916</v>
       </c>
       <c r="W13" t="n">
-        <v>-5.191</v>
+        <v>-5.216</v>
       </c>
     </row>
     <row r="14">
@@ -3751,12 +3775,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3774,14 +3798,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CVKMD.IS: -1.79% / +3.03% / -3.48%</t>
+          <t>CVKMD.IS: -2.10% / +3.03% / -3.48%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K14" t="n">
-        <v>3.673840076745183</v>
+        <v>3.514266871123217</v>
       </c>
       <c r="L14" t="n">
         <v>19.61961325199098</v>
@@ -3790,7 +3814,7 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N14" t="n">
-        <v>88.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="O14" t="n">
         <v>45.8</v>
@@ -3813,13 +3837,13 @@
         <v>18.132</v>
       </c>
       <c r="U14" t="n">
-        <v>1.09</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>8.257</v>
+        <v>8.09</v>
       </c>
       <c r="W14" t="n">
-        <v>-10.702</v>
+        <v>-10.858</v>
       </c>
     </row>
     <row r="16">
@@ -3964,12 +3988,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3987,14 +4011,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.44% / +1.29% / -0.99% | ENERY.IS: -2.06% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +2.92% / +2.76% / -0.99% | ENERY.IS: -1.29% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.257420415954579</v>
+        <v>0.8541789633736974</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4003,7 +4027,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>93.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O18" t="n">
         <v>44.7</v>
@@ -4026,13 +4050,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>284.698</v>
+        <v>290.845</v>
       </c>
       <c r="V18" t="n">
-        <v>100.928</v>
+        <v>103.168</v>
       </c>
       <c r="W18" t="n">
-        <v>-44.036</v>
+        <v>-39.938</v>
       </c>
     </row>
     <row r="19">
@@ -4053,12 +4077,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -4080,7 +4104,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N19" t="n">
-        <v>119.3</v>
+        <v>119.1</v>
       </c>
       <c r="O19" t="n">
         <v>46.9</v>
@@ -4103,13 +4127,13 @@
         <v>25.929</v>
       </c>
       <c r="U19" t="n">
-        <v>56.944</v>
+        <v>58.058</v>
       </c>
       <c r="V19" t="n">
         <v>19.407</v>
       </c>
       <c r="W19" t="n">
-        <v>-54.938</v>
+        <v>-55.328</v>
       </c>
     </row>
     <row r="20">
@@ -4130,12 +4154,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4153,14 +4177,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.44% / +1.29% / -0.99% | ENERY.IS: -2.06% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +2.92% / +2.76% / -0.99% | ENERY.IS: -1.29% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2773879324398765</v>
+        <v>0.8339889152572333</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4169,7 +4193,7 @@
         <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>82.2</v>
+        <v>82</v>
       </c>
       <c r="O20" t="n">
         <v>42.8</v>
@@ -4192,13 +4216,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>281.743</v>
+        <v>287.842</v>
       </c>
       <c r="V20" t="n">
-        <v>82.97799999999999</v>
+        <v>85.018</v>
       </c>
       <c r="W20" t="n">
-        <v>-43.649</v>
+        <v>-39.582</v>
       </c>
     </row>
     <row r="21">
@@ -4219,12 +4243,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4246,7 +4270,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>179.7</v>
+        <v>179.4</v>
       </c>
       <c r="O21" t="n">
         <v>52.1</v>
@@ -4269,13 +4293,13 @@
         <v>24.618</v>
       </c>
       <c r="U21" t="n">
-        <v>32.99</v>
+        <v>33.934</v>
       </c>
       <c r="V21" t="n">
         <v>6.526</v>
       </c>
       <c r="W21" t="n">
-        <v>-43.431</v>
+        <v>-43.739</v>
       </c>
     </row>
     <row r="22">
@@ -4296,12 +4320,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4319,14 +4343,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.12% / +20.01% / -1.13% | CANTE.IS: +6.90% / +15.33% / -2.99% | ENERY.IS: +0.20% / +1.99% / -0.51% | SOKM.IS: +0.83% / +1.36% / -2.94% | TKFEN.IS: +14.59% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.10% / +20.01% / -1.13% | CANTE.IS: +8.45% / +15.33% / -2.99% | ENERY.IS: +0.98% / +1.99% / -0.51% | SOKM.IS: +1.72% / +1.91% / -2.94% | TKFEN.IS: +15.33% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K22" t="n">
-        <v>-8.906663108177215</v>
+        <v>-8.630762857397711</v>
       </c>
       <c r="L22" t="n">
         <v>19.41140710190506</v>
@@ -4335,7 +4359,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>139.1</v>
+        <v>138.8</v>
       </c>
       <c r="O22" t="n">
         <v>43.1</v>
@@ -4358,13 +4382,13 @@
         <v>26.35</v>
       </c>
       <c r="U22" t="n">
-        <v>23.95</v>
+        <v>24.325</v>
       </c>
       <c r="V22" t="n">
-        <v>13.253</v>
+        <v>13.596</v>
       </c>
       <c r="W22" t="n">
-        <v>-41.175</v>
+        <v>-40.799</v>
       </c>
     </row>
     <row r="23">
@@ -4385,12 +4409,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4408,14 +4432,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.12% / +20.01% / -1.13% | CANTE.IS: -0.88% / +3.11% / -3.83% | ENERY.IS: +0.20% / +1.99% / -0.51%</t>
+          <t>BRSAN.IS: +12.10% / +20.01% / -1.13% | CANTE.IS: +0.56% / +3.11% / -3.83% | ENERY.IS: +0.98% / +1.99% / -0.51%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.025382791314656</v>
+        <v>-1.948325988485078</v>
       </c>
       <c r="L23" t="n">
         <v>16.16102048107813</v>
@@ -4424,10 +4448,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>153.5</v>
+        <v>153.2</v>
       </c>
       <c r="O23" t="n">
-        <v>42.3</v>
+        <v>42.6</v>
       </c>
       <c r="P23" t="n">
         <v>4.2</v>
@@ -4447,13 +4471,13 @@
         <v>21.943</v>
       </c>
       <c r="U23" t="n">
-        <v>25.68</v>
+        <v>24.549</v>
       </c>
       <c r="V23" t="n">
-        <v>2.687</v>
+        <v>2.768</v>
       </c>
       <c r="W23" t="n">
-        <v>-31.162</v>
+        <v>-30.759</v>
       </c>
     </row>
     <row r="24">
@@ -4474,12 +4498,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4501,7 +4525,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>113.9</v>
+        <v>113.6</v>
       </c>
       <c r="O24" t="n">
         <v>50.4</v>
@@ -4524,13 +4548,13 @@
         <v>20.181</v>
       </c>
       <c r="U24" t="n">
-        <v>11.77</v>
+        <v>10.676</v>
       </c>
       <c r="V24" t="n">
         <v>-2.456</v>
       </c>
       <c r="W24" t="n">
-        <v>-27.452</v>
+        <v>-27.184</v>
       </c>
     </row>
     <row r="25">
@@ -4551,12 +4575,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -4578,7 +4602,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N25" t="n">
-        <v>75.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="O25" t="n">
         <v>49.3</v>
@@ -4601,13 +4625,13 @@
         <v>13.28</v>
       </c>
       <c r="U25" t="n">
-        <v>8.964</v>
+        <v>7.136</v>
       </c>
       <c r="V25" t="n">
         <v>-0.962</v>
       </c>
       <c r="W25" t="n">
-        <v>-16.687</v>
+        <v>-16.407</v>
       </c>
     </row>
     <row r="26">
@@ -4628,12 +4652,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -4678,13 +4702,13 @@
         <v>7.916</v>
       </c>
       <c r="U26" t="n">
-        <v>13.72</v>
+        <v>14.275</v>
       </c>
       <c r="V26" t="n">
         <v>4.916</v>
       </c>
       <c r="W26" t="n">
-        <v>-5.191</v>
+        <v>-5.216</v>
       </c>
     </row>
     <row r="27">
@@ -4705,12 +4729,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4728,14 +4752,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.12% / +20.01% / -1.13% | TKFEN.IS: +14.59% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.10% / +20.01% / -1.13% | TKFEN.IS: +15.33% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K27" t="n">
-        <v>12.22834030813578</v>
+        <v>11.64809993992229</v>
       </c>
       <c r="L27" t="n">
         <v>31.31195090134997</v>
@@ -4744,7 +4768,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N27" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="O27" t="n">
         <v>43.3</v>
@@ -4767,13 +4791,13 @@
         <v>28.439</v>
       </c>
       <c r="U27" t="n">
-        <v>45.931</v>
+        <v>45.177</v>
       </c>
       <c r="V27" t="n">
-        <v>56.379</v>
+        <v>55.571</v>
       </c>
       <c r="W27" t="n">
-        <v>-14.357</v>
+        <v>-15.111</v>
       </c>
     </row>
     <row r="28">
@@ -4794,12 +4818,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4817,14 +4841,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CVKMD.IS: -1.79% / +3.03% / -3.48%</t>
+          <t>CVKMD.IS: -2.10% / +3.03% / -3.48%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-19.60937535624424</v>
       </c>
       <c r="K28" t="n">
-        <v>3.673840076745183</v>
+        <v>3.514266871123217</v>
       </c>
       <c r="L28" t="n">
         <v>19.61961325199098</v>
@@ -4833,7 +4857,7 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N28" t="n">
-        <v>88.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="O28" t="n">
         <v>45.8</v>
@@ -4856,13 +4880,13 @@
         <v>18.132</v>
       </c>
       <c r="U28" t="n">
-        <v>1.09</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="V28" t="n">
-        <v>8.257</v>
+        <v>8.09</v>
       </c>
       <c r="W28" t="n">
-        <v>-10.702</v>
+        <v>-10.858</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_tr.xlsx
+++ b/ATL_tr.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.48% / +3.76% / -3.01% | ENERY.IS: +1.18% / +2.04% / -0.46%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +2.76% / +3.15% / -0.46%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K3" t="n">
-        <v>-16.12027198934688</v>
+        <v>-16.11670706614458</v>
       </c>
       <c r="L3" t="n">
         <v>18.08648750869864</v>
@@ -775,7 +775,7 @@
         <v>102.4</v>
       </c>
       <c r="O3" t="n">
-        <v>43.8</v>
+        <v>43.3</v>
       </c>
       <c r="P3" t="n">
         <v>6.8</v>
@@ -795,13 +795,13 @@
         <v>23.832</v>
       </c>
       <c r="U3" t="n">
-        <v>64.244</v>
+        <v>64.251</v>
       </c>
       <c r="V3" t="n">
-        <v>13.957</v>
+        <v>13.962</v>
       </c>
       <c r="W3" t="n">
-        <v>-46.912</v>
+        <v>-46.905</v>
       </c>
     </row>
     <row r="4">
@@ -993,14 +993,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.48% / +3.76% / -3.01% | ENERY.IS: +1.18% / +2.04% / -0.46%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +2.76% / +3.15% / -0.46%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K6" t="n">
-        <v>-16.12027198934688</v>
+        <v>-16.11670706614458</v>
       </c>
       <c r="L6" t="n">
         <v>18.08648750869864</v>
@@ -1012,7 +1012,7 @@
         <v>102.4</v>
       </c>
       <c r="O6" t="n">
-        <v>43.8</v>
+        <v>43.3</v>
       </c>
       <c r="P6" t="n">
         <v>6.8</v>
@@ -1032,13 +1032,13 @@
         <v>23.832</v>
       </c>
       <c r="U6" t="n">
-        <v>64.244</v>
+        <v>64.251</v>
       </c>
       <c r="V6" t="n">
-        <v>13.957</v>
+        <v>13.962</v>
       </c>
       <c r="W6" t="n">
-        <v>-46.912</v>
+        <v>-46.905</v>
       </c>
     </row>
     <row r="7">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -1.60% / +0.00% / -1.65% | CANTE.IS: +1.48% / +3.76% / -3.01%</t>
+          <t>BRSAN.IS: -1.80% / +0.00% / -1.99% | CANTE.IS: -0.02% / +4.51% / -3.01%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.488268056801768</v>
+        <v>-3.302741657235275</v>
       </c>
       <c r="L7" t="n">
         <v>15.27952105135885</v>
@@ -1099,7 +1099,7 @@
         <v>134.9</v>
       </c>
       <c r="O7" t="n">
-        <v>47.4</v>
+        <v>47.1</v>
       </c>
       <c r="P7" t="n">
         <v>3.1</v>
@@ -1119,13 +1119,13 @@
         <v>19.727</v>
       </c>
       <c r="U7" t="n">
-        <v>79.91200000000001</v>
+        <v>78.40900000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>33.431</v>
+        <v>32.316</v>
       </c>
       <c r="W7" t="n">
-        <v>-32.352</v>
+        <v>-33.855</v>
       </c>
     </row>
     <row r="8">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.75% / +2.95% / -1.61% | ENERY.IS: -1.11% / +1.27% / -3.44% | ENJSA.IS: +1.90% / +2.62% / -2.01%</t>
+          <t>ALARK.IS: +4.10% / +7.34% / -1.61% | ENERY.IS: +0.43% / +1.27% / -3.44% | ENJSA.IS: +3.56% / +4.02% / -2.01%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K8" t="n">
-        <v>-14.01315872661779</v>
+        <v>-12.75222574360618</v>
       </c>
       <c r="L8" t="n">
         <v>14.40134401582471</v>
@@ -1186,7 +1186,7 @@
         <v>191.5</v>
       </c>
       <c r="O8" t="n">
-        <v>47</v>
+        <v>47.3</v>
       </c>
       <c r="P8" t="n">
         <v>3.1</v>
@@ -1206,13 +1206,13 @@
         <v>17.749</v>
       </c>
       <c r="U8" t="n">
-        <v>50.701</v>
+        <v>52.911</v>
       </c>
       <c r="V8" t="n">
-        <v>14.164</v>
+        <v>15.838</v>
       </c>
       <c r="W8" t="n">
-        <v>-27.351</v>
+        <v>-25.141</v>
       </c>
     </row>
     <row r="9">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.48% / +3.76% / -3.01% | ENERY.IS: +1.18% / +2.04% / -0.46%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +2.76% / +3.15% / -0.46%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K9" t="n">
-        <v>-16.12027198934688</v>
+        <v>-16.11670706614458</v>
       </c>
       <c r="L9" t="n">
         <v>18.08648750869864</v>
@@ -1273,7 +1273,7 @@
         <v>102.4</v>
       </c>
       <c r="O9" t="n">
-        <v>43.8</v>
+        <v>43.3</v>
       </c>
       <c r="P9" t="n">
         <v>6.8</v>
@@ -1293,13 +1293,13 @@
         <v>23.832</v>
       </c>
       <c r="U9" t="n">
-        <v>64.244</v>
+        <v>64.251</v>
       </c>
       <c r="V9" t="n">
-        <v>13.957</v>
+        <v>13.962</v>
       </c>
       <c r="W9" t="n">
-        <v>-46.912</v>
+        <v>-46.905</v>
       </c>
     </row>
     <row r="10">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AGHOL.IS: -0.02% / +2.03% / -2.37% | ENKAI.IS: -0.41% / +1.34% / -0.84% | KRDMD.IS: -0.02% / +0.00% / 0.00% | SASA.IS: +1.07% / +1.81% / -1.81% | TSKB.IS: -1.05% / +0.86% / -3.01%</t>
+          <t>AGHOL.IS: +2.99% / +3.36% / -2.37% | ENKAI.IS: +0.76% / +1.90% / -0.84% | KRDMD.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -1.11% / +6.16% / -1.81% | TSKB.IS: -2.00% / +0.86% / -3.01%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>12.86015270141232</v>
       </c>
       <c r="K10" t="n">
-        <v>-22.72403658622732</v>
+        <v>-3.325141981027546</v>
       </c>
       <c r="L10" t="n">
         <v>4.543450519200398</v>
@@ -1357,10 +1357,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N10" t="n">
-        <v>176.2</v>
+        <v>176.7</v>
       </c>
       <c r="O10" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
@@ -1374,19 +1374,19 @@
         <v>5</v>
       </c>
       <c r="S10" t="n">
-        <v>25.371</v>
+        <v>10.072</v>
       </c>
       <c r="T10" t="n">
-        <v>25.371</v>
+        <v>10.072</v>
       </c>
       <c r="U10" t="n">
-        <v>-6.425</v>
+        <v>17.066</v>
       </c>
       <c r="V10" t="n">
-        <v>-12.994</v>
+        <v>8.848000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>-31.813</v>
+        <v>-8.321999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1503,14 +1503,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.15% / +20.94% / 0.00% | CANTE.IS: +3.03% / +3.05% / -0.76% | RALYH.IS: +32.31% / +35.10% / -0.91%</t>
+          <t>BRSAN.IS: +13.91% / +20.94% / 0.00% | CANTE.IS: +1.51% / +6.11% / -0.76% | RALYH.IS: +33.75% / +38.22% / -0.91%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K12" t="n">
-        <v>13.94878027323467</v>
+        <v>13.78097266710678</v>
       </c>
       <c r="L12" t="n">
         <v>34.56349599547857</v>
@@ -1542,13 +1542,13 @@
         <v>23.777</v>
       </c>
       <c r="U12" t="n">
-        <v>50.71</v>
+        <v>50.488</v>
       </c>
       <c r="V12" t="n">
-        <v>44.405</v>
+        <v>44.192</v>
       </c>
       <c r="W12" t="n">
-        <v>-9.327999999999999</v>
+        <v>-9.550000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1575,67 +1575,55 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ASTOR.IS, CVKMD.IS</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ASTOR.IS: 2026-09-03 | CVKMD.IS: 2026-09-09</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>20.48700524499634</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ASTOR.IS: +3.73% / +4.51% / -1.28% | CVKMD.IS: -0.02% / +0.00% / 0.00%</t>
-        </is>
-      </c>
+        <v>26.23135974315276</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>-3.767340978838807</v>
+        <v>-4.560732390712419</v>
       </c>
       <c r="K13" t="n">
-        <v>13.93158196968245</v>
+        <v>13.5396968022099</v>
       </c>
       <c r="L13" t="n">
-        <v>16.57596537747867</v>
+        <v>9.344627019167174</v>
       </c>
       <c r="M13" t="n">
-        <v>77.77777777777779</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N13" t="n">
-        <v>88.59999999999999</v>
+        <v>54.6</v>
       </c>
       <c r="O13" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>17.404</v>
+        <v>11.957</v>
       </c>
       <c r="T13" t="n">
-        <v>17.404</v>
+        <v>11.957</v>
       </c>
       <c r="U13" t="n">
-        <v>54.099</v>
+        <v>33.587</v>
       </c>
       <c r="V13" t="n">
-        <v>46.464</v>
+        <v>38.164</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.603</v>
+        <v>-5.167</v>
       </c>
     </row>
     <row r="14">
@@ -1677,14 +1665,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CANTE.IS: +3.03% / +3.05% / -0.76% | ENERY.IS: +1.18% / +2.04% / -0.46%</t>
+          <t>CANTE.IS: +1.51% / +6.11% / -0.76% | ENERY.IS: +2.76% / +3.15% / -0.46%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K14" t="n">
-        <v>7.037429364945602</v>
+        <v>7.062852241306672</v>
       </c>
       <c r="L14" t="n">
         <v>22.73189287884475</v>
@@ -1716,13 +1704,13 @@
         <v>25.345</v>
       </c>
       <c r="U14" t="n">
-        <v>84.83</v>
+        <v>84.874</v>
       </c>
       <c r="V14" t="n">
-        <v>97.22499999999999</v>
+        <v>97.27200000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>-26.42</v>
+        <v>-26.376</v>
       </c>
     </row>
     <row r="16">
@@ -1890,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: +1.48% / +3.76% / -3.01% | ENERY.IS: +1.18% / +2.04% / -0.46%</t>
+          <t>CANTE.IS: -0.02% / +4.51% / -3.01% | ENERY.IS: +2.76% / +3.15% / -0.46%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>49.01214426917304</v>
       </c>
       <c r="K18" t="n">
-        <v>-16.12027198934688</v>
+        <v>-16.11670706614458</v>
       </c>
       <c r="L18" t="n">
         <v>18.08648750869864</v>
@@ -1909,7 +1897,7 @@
         <v>102.4</v>
       </c>
       <c r="O18" t="n">
-        <v>43.8</v>
+        <v>43.3</v>
       </c>
       <c r="P18" t="n">
         <v>6.8</v>
@@ -1929,13 +1917,13 @@
         <v>23.832</v>
       </c>
       <c r="U18" t="n">
-        <v>64.244</v>
+        <v>64.251</v>
       </c>
       <c r="V18" t="n">
-        <v>13.957</v>
+        <v>13.962</v>
       </c>
       <c r="W18" t="n">
-        <v>-46.912</v>
+        <v>-46.905</v>
       </c>
     </row>
     <row r="19">
@@ -2133,14 +2121,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALARK.IS: +2.75% / +2.95% / -1.61% | ENERY.IS: -1.11% / +1.27% / -3.44% | ENJSA.IS: +1.90% / +2.62% / -2.01%</t>
+          <t>ALARK.IS: +4.10% / +7.34% / -1.61% | ENERY.IS: +0.43% / +1.27% / -3.44% | ENJSA.IS: +3.56% / +4.02% / -2.01%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>27.97836072130362</v>
       </c>
       <c r="K21" t="n">
-        <v>-14.01315872661779</v>
+        <v>-12.75222574360618</v>
       </c>
       <c r="L21" t="n">
         <v>14.40134401582471</v>
@@ -2152,7 +2140,7 @@
         <v>191.5</v>
       </c>
       <c r="O21" t="n">
-        <v>47</v>
+        <v>47.3</v>
       </c>
       <c r="P21" t="n">
         <v>3.1</v>
@@ -2172,13 +2160,13 @@
         <v>17.749</v>
       </c>
       <c r="U21" t="n">
-        <v>50.701</v>
+        <v>52.911</v>
       </c>
       <c r="V21" t="n">
-        <v>14.164</v>
+        <v>15.838</v>
       </c>
       <c r="W21" t="n">
-        <v>-27.351</v>
+        <v>-25.141</v>
       </c>
     </row>
     <row r="22">
@@ -2222,14 +2210,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>BRSAN.IS: -1.60% / +0.00% / -1.65% | CANTE.IS: +1.48% / +3.76% / -3.01%</t>
+          <t>BRSAN.IS: -1.80% / +0.00% / -1.99% | CANTE.IS: -0.02% / +4.51% / -3.01%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>29.78173657371126</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.488268056801768</v>
+        <v>-3.302741657235275</v>
       </c>
       <c r="L22" t="n">
         <v>15.27952105135885</v>
@@ -2241,7 +2229,7 @@
         <v>134.9</v>
       </c>
       <c r="O22" t="n">
-        <v>47.4</v>
+        <v>47.1</v>
       </c>
       <c r="P22" t="n">
         <v>3.1</v>
@@ -2261,13 +2249,13 @@
         <v>19.727</v>
       </c>
       <c r="U22" t="n">
-        <v>79.91200000000001</v>
+        <v>78.40900000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>33.431</v>
+        <v>32.316</v>
       </c>
       <c r="W22" t="n">
-        <v>-32.352</v>
+        <v>-33.855</v>
       </c>
     </row>
     <row r="23">
@@ -2311,14 +2299,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CANTE.IS: +3.03% / +3.05% / -0.76% | ENERY.IS: +1.18% / +2.04% / -0.46%</t>
+          <t>CANTE.IS: +1.51% / +6.11% / -0.76% | ENERY.IS: +2.76% / +3.15% / -0.46%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>-8.265155599016705</v>
       </c>
       <c r="K23" t="n">
-        <v>7.037429364945602</v>
+        <v>7.062852241306672</v>
       </c>
       <c r="L23" t="n">
         <v>22.73189287884475</v>
@@ -2350,13 +2338,13 @@
         <v>25.345</v>
       </c>
       <c r="U23" t="n">
-        <v>84.83</v>
+        <v>84.874</v>
       </c>
       <c r="V23" t="n">
-        <v>97.22499999999999</v>
+        <v>97.27200000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>-26.42</v>
+        <v>-26.376</v>
       </c>
     </row>
     <row r="24">
@@ -2439,7 +2427,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,7 +2437,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2462,73 +2450,61 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>AGHOL.IS, ENKAI.IS, KRDMD.IS, SASA.IS, TSKB.IS</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: 2026-09-07 | ENKAI.IS: 2026-09-08 | KRDMD.IS: 2026-09-09 | SASA.IS: 2026-09-08 | TSKB.IS: 2026-09-08</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>23.02092795860866</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>AGHOL.IS: -0.02% / +2.03% / -2.37% | ENKAI.IS: -0.41% / +1.34% / -0.84% | KRDMD.IS: -0.02% / +0.00% / 0.00% | SASA.IS: +1.07% / +1.81% / -1.81% | TSKB.IS: -1.05% / +0.86% / -3.01%</t>
-        </is>
-      </c>
+        <v>26.23135974315276</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>12.86015270141232</v>
+        <v>-4.560732390712419</v>
       </c>
       <c r="K25" t="n">
-        <v>-22.72403658622732</v>
+        <v>13.5396968022099</v>
       </c>
       <c r="L25" t="n">
-        <v>4.543450519200398</v>
+        <v>9.344627019167174</v>
       </c>
       <c r="M25" t="n">
-        <v>72.22222222222221</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N25" t="n">
-        <v>176.2</v>
+        <v>54.6</v>
       </c>
       <c r="O25" t="n">
-        <v>48.9</v>
+        <v>47.7</v>
       </c>
       <c r="P25" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>25.371</v>
+        <v>11.957</v>
       </c>
       <c r="T25" t="n">
-        <v>25.371</v>
+        <v>11.957</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.425</v>
+        <v>33.587</v>
       </c>
       <c r="V25" t="n">
-        <v>-12.994</v>
+        <v>38.164</v>
       </c>
       <c r="W25" t="n">
-        <v>-31.813</v>
+        <v>-5.167</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2538,7 +2514,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|geri_cekilme</t>
+          <t>T6_skor_momentum|E30|S5|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2553,42 +2529,42 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ASTOR.IS, CVKMD.IS</t>
+          <t>AGHOL.IS, ENKAI.IS, KRDMD.IS, SASA.IS, TSKB.IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: 2026-09-03 | CVKMD.IS: 2026-09-09</t>
+          <t>AGHOL.IS: 2026-09-07 | ENKAI.IS: 2026-09-08 | KRDMD.IS: 2026-09-09 | SASA.IS: 2026-09-08 | TSKB.IS: 2026-09-08</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>20.48700524499634</v>
+        <v>23.02092795860866</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASTOR.IS: +3.73% / +4.51% / -1.28% | CVKMD.IS: -0.02% / +0.00% / 0.00%</t>
+          <t>AGHOL.IS: +2.99% / +3.36% / -2.37% | ENKAI.IS: +0.76% / +1.90% / -0.84% | KRDMD.IS: -0.02% / +0.00% / 0.00% | SASA.IS: -1.11% / +6.16% / -1.81% | TSKB.IS: -2.00% / +0.86% / -3.01%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-3.767340978838807</v>
+        <v>12.86015270141232</v>
       </c>
       <c r="K26" t="n">
-        <v>13.93158196968245</v>
+        <v>-3.325141981027546</v>
       </c>
       <c r="L26" t="n">
-        <v>16.57596537747867</v>
+        <v>4.543450519200398</v>
       </c>
       <c r="M26" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="N26" t="n">
-        <v>88.59999999999999</v>
+        <v>176.7</v>
       </c>
       <c r="O26" t="n">
-        <v>47.8</v>
+        <v>49</v>
       </c>
       <c r="P26" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2596,22 +2572,22 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S26" t="n">
-        <v>17.404</v>
+        <v>10.072</v>
       </c>
       <c r="T26" t="n">
-        <v>17.404</v>
+        <v>10.072</v>
       </c>
       <c r="U26" t="n">
-        <v>54.099</v>
+        <v>17.066</v>
       </c>
       <c r="V26" t="n">
-        <v>46.464</v>
+        <v>8.848000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.603</v>
+        <v>-8.321999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -2655,14 +2631,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +14.15% / +20.94% / 0.00% | CANTE.IS: +3.03% / +3.05% / -0.76% | RALYH.IS: +32.31% / +35.10% / -0.91%</t>
+          <t>BRSAN.IS: +13.91% / +20.94% / 0.00% | CANTE.IS: +1.51% / +6.11% / -0.76% | RALYH.IS: +33.75% / +38.22% / -0.91%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-10.39434387728287</v>
       </c>
       <c r="K27" t="n">
-        <v>13.94878027323467</v>
+        <v>13.78097266710678</v>
       </c>
       <c r="L27" t="n">
         <v>34.56349599547857</v>
@@ -2694,13 +2670,13 @@
         <v>23.777</v>
       </c>
       <c r="U27" t="n">
-        <v>50.71</v>
+        <v>50.488</v>
       </c>
       <c r="V27" t="n">
-        <v>44.405</v>
+        <v>44.192</v>
       </c>
       <c r="W27" t="n">
-        <v>-9.327999999999999</v>
+        <v>-9.550000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2913,14 +2889,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CANTE.IS: +2.92% / +2.76% / -0.99% | ENERY.IS: -1.29% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +1.40% / +5.82% / -0.99% | ENERY.IS: +0.34% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8541789633736974</v>
+        <v>0.9236953113281876</v>
       </c>
       <c r="L3" t="n">
         <v>28.4081875</v>
@@ -2932,7 +2908,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>44.7</v>
+        <v>45.2</v>
       </c>
       <c r="P3" t="n">
         <v>4.3</v>
@@ -2952,13 +2928,13 @@
         <v>18.106</v>
       </c>
       <c r="U3" t="n">
-        <v>290.845</v>
+        <v>291.114</v>
       </c>
       <c r="V3" t="n">
-        <v>103.168</v>
+        <v>103.308</v>
       </c>
       <c r="W3" t="n">
-        <v>-39.938</v>
+        <v>-39.669</v>
       </c>
     </row>
     <row r="4">
@@ -3075,14 +3051,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CANTE.IS: +2.92% / +2.76% / -0.99% | ENERY.IS: -1.29% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +1.40% / +5.82% / -0.99% | ENERY.IS: +0.34% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8339889152572333</v>
+        <v>0.9034913466995587</v>
       </c>
       <c r="L5" t="n">
         <v>32.3216328125</v>
@@ -3094,7 +3070,7 @@
         <v>82</v>
       </c>
       <c r="O5" t="n">
-        <v>42.8</v>
+        <v>43.4</v>
       </c>
       <c r="P5" t="n">
         <v>4.7</v>
@@ -3114,13 +3090,13 @@
         <v>21.096</v>
       </c>
       <c r="U5" t="n">
-        <v>287.842</v>
+        <v>288.11</v>
       </c>
       <c r="V5" t="n">
-        <v>85.018</v>
+        <v>85.145</v>
       </c>
       <c r="W5" t="n">
-        <v>-39.582</v>
+        <v>-39.315</v>
       </c>
     </row>
     <row r="6">
@@ -3162,14 +3138,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.10% / +20.01% / -1.13% | CANTE.IS: +8.45% / +15.33% / -2.99% | ENERY.IS: +0.98% / +1.99% / -0.51% | SOKM.IS: +1.72% / +1.91% / -2.94% | TKFEN.IS: +15.33% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.03% / +20.01% / -1.13% | CANTE.IS: +6.85% / +15.33% / -2.99% | ENERY.IS: +2.65% / +3.06% / -0.50% | SOKM.IS: +3.18% / +3.71% / -2.94% | TKFEN.IS: +11.31% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>33.48059201172197</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.630762857397711</v>
+        <v>-9.239828428156372</v>
       </c>
       <c r="L6" t="n">
         <v>19.41140710190506</v>
@@ -3201,13 +3177,13 @@
         <v>26.35</v>
       </c>
       <c r="U6" t="n">
-        <v>24.325</v>
+        <v>23.497</v>
       </c>
       <c r="V6" t="n">
-        <v>13.596</v>
+        <v>12.839</v>
       </c>
       <c r="W6" t="n">
-        <v>-40.799</v>
+        <v>-41.628</v>
       </c>
     </row>
     <row r="7">
@@ -3324,14 +3300,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.10% / +20.01% / -1.13% | CANTE.IS: +0.56% / +3.11% / -3.83% | ENERY.IS: +0.98% / +1.99% / -0.51%</t>
+          <t>BRSAN.IS: +12.03% / +20.01% / -1.13% | CANTE.IS: -0.92% / +3.52% / -3.83% | ENERY.IS: +2.65% / +3.06% / -0.50%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>21.4002873140223</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.948325988485078</v>
+        <v>-1.901209558780503</v>
       </c>
       <c r="L8" t="n">
         <v>16.16102048107813</v>
@@ -3343,7 +3319,7 @@
         <v>153.2</v>
       </c>
       <c r="O8" t="n">
-        <v>42.6</v>
+        <v>42.3</v>
       </c>
       <c r="P8" t="n">
         <v>4.2</v>
@@ -3363,13 +3339,13 @@
         <v>21.943</v>
       </c>
       <c r="U8" t="n">
-        <v>24.549</v>
+        <v>24.608</v>
       </c>
       <c r="V8" t="n">
-        <v>2.768</v>
+        <v>2.817</v>
       </c>
       <c r="W8" t="n">
-        <v>-30.759</v>
+        <v>-30.699</v>
       </c>
     </row>
     <row r="9">
@@ -3636,14 +3612,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BRSAN.IS: +12.10% / +20.01% / -1.13% | TKFEN.IS: +15.33% / +31.83% / -0.56%</t>
+          <t>BRSAN.IS: +12.03% / +20.01% / -1.13% | TKFEN.IS: +11.31% / +31.83% / -0.56%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-18.9000927288166</v>
       </c>
       <c r="K12" t="n">
-        <v>11.64809993992229</v>
+        <v>9.575741415582307</v>
       </c>
       <c r="L12" t="n">
         <v>31.31195090134997</v>
@@ -3675,13 +3651,13 @@
         <v>28.439</v>
       </c>
       <c r="U12" t="n">
-        <v>45.177</v>
+        <v>42.482</v>
       </c>
       <c r="V12" t="n">
-        <v>55.571</v>
+        <v>52.683</v>
       </c>
       <c r="W12" t="n">
-        <v>-15.111</v>
+        <v>-17.806</v>
       </c>
     </row>
     <row r="13">
@@ -3695,7 +3671,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3708,55 +3684,67 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CVKMD.IS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CVKMD.IS: 2026-09-04</t>
+        </is>
+      </c>
       <c r="H13" t="n">
-        <v>8.530010255723974</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>-0.49388395046156</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CVKMD.IS: -0.43% / +3.03% / -3.47%</t>
+        </is>
+      </c>
       <c r="J13" t="n">
-        <v>0.8142516931666233</v>
+        <v>-19.60937535624424</v>
       </c>
       <c r="K13" t="n">
-        <v>3.846414277792909</v>
+        <v>4.391164317842189</v>
       </c>
       <c r="L13" t="n">
-        <v>9.181211458048665</v>
+        <v>19.61961325199098</v>
       </c>
       <c r="M13" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N13" t="n">
-        <v>35.6</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>50</v>
+        <v>45.8</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>8.083</v>
+        <v>18.132</v>
       </c>
       <c r="T13" t="n">
-        <v>7.916</v>
+        <v>18.132</v>
       </c>
       <c r="U13" t="n">
-        <v>14.275</v>
+        <v>1.789</v>
       </c>
       <c r="V13" t="n">
-        <v>4.916</v>
+        <v>9.006</v>
       </c>
       <c r="W13" t="n">
-        <v>-5.216</v>
+        <v>-10.003</v>
       </c>
     </row>
     <row r="14">
@@ -3770,7 +3758,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|geri_cekilme</t>
+          <t>T4_konsensus|E30|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3783,67 +3771,55 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>CVKMD.IS</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>CVKMD.IS: 2026-09-04</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>-0.49388395046156</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>CVKMD.IS: -2.10% / +3.03% / -3.48%</t>
-        </is>
-      </c>
+        <v>8.530010255723974</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>-19.60937535624424</v>
+        <v>0.8142516931666233</v>
       </c>
       <c r="K14" t="n">
-        <v>3.514266871123217</v>
+        <v>3.846414277792909</v>
       </c>
       <c r="L14" t="n">
-        <v>19.61961325199098</v>
+        <v>9.181211458048665</v>
       </c>
       <c r="M14" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N14" t="n">
-        <v>88.40000000000001</v>
+        <v>35.6</v>
       </c>
       <c r="O14" t="n">
-        <v>45.8</v>
+        <v>50</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>18.132</v>
+        <v>8.083</v>
       </c>
       <c r="T14" t="n">
-        <v>18.132</v>
+        <v>7.916</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9340000000000001</v>
+        <v>14.275</v>
       </c>
       <c r="V14" t="n">
-        <v>8.09</v>
+        <v>4.916</v>
       </c>
       <c r="W14" t="n">
-        <v>-10.858</v>
+        <v>-5.216</v>
       </c>
     </row>
     <row r="16">
@@ -4011,14 +3987,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CANTE.IS: +2.92% / +2.76% / -0.99% | ENERY.IS: -1.29% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +1.40% / +5.82% / -0.99% | ENERY.IS: +0.34% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>1.0581145912685</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8541789633736974</v>
+        <v>0.9236953113281876</v>
       </c>
       <c r="L18" t="n">
         <v>28.4081875</v>
@@ -4030,7 +4006,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>44.7</v>
+        <v>45.2</v>
       </c>
       <c r="P18" t="n">
         <v>4.3</v>
@@ -4050,13 +4026,13 @@
         <v>18.106</v>
       </c>
       <c r="U18" t="n">
-        <v>290.845</v>
+        <v>291.114</v>
       </c>
       <c r="V18" t="n">
-        <v>103.168</v>
+        <v>103.308</v>
       </c>
       <c r="W18" t="n">
-        <v>-39.938</v>
+        <v>-39.669</v>
       </c>
     </row>
     <row r="19">
@@ -4177,14 +4153,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CANTE.IS: +2.92% / +2.76% / -0.99% | ENERY.IS: -1.29% / +1.26% / -3.45%</t>
+          <t>CANTE.IS: +1.40% / +5.82% / -0.99% | ENERY.IS: +0.34% / +1.26% / -3.45%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>-0.4421645194713886</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8339889152572333</v>
+        <v>0.9034913466995587</v>
       </c>
       <c r="L20" t="n">
         <v>32.3216328125</v>
@@ -4196,7 +4172,7 @@
         <v>82</v>
       </c>
       <c r="O20" t="n">
-        <v>42.8</v>
+        <v>43.4</v>
       </c>
       <c r="P20" t="n">
         <v>4.7</v>
@@ -4216,13 +4192,13 @@
         <v>21.096</v>
       </c>
       <c r="U20" t="n">
-        <v>287.842</v>
+        <v>288.11</v>
       </c>
       <c r="V20" t="n">
-        <v>85.018</v>
+        <v>85.145</v>
       </c>
       <c r="W20" t="n">
-        <